--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9EAE436-7FAD-4CC8-BADA-7D2A757A570C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3723DDC9-D3E6-4DB4-8806-9FA0070514F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="116">
   <si>
     <t>Name</t>
   </si>
@@ -76,9 +76,6 @@
     <t>C0014</t>
   </si>
   <si>
-    <t>C0005</t>
-  </si>
-  <si>
     <t>0083.HK</t>
   </si>
   <si>
@@ -103,30 +100,9 @@
     <t>C0008</t>
   </si>
   <si>
-    <t>C0010</t>
-  </si>
-  <si>
     <t>C0012</t>
   </si>
   <si>
-    <t>0857.HK</t>
-  </si>
-  <si>
-    <t>C0013</t>
-  </si>
-  <si>
-    <t>0868.HK</t>
-  </si>
-  <si>
-    <t>0887.HK</t>
-  </si>
-  <si>
-    <t>0939.HK</t>
-  </si>
-  <si>
-    <t>0941.HK</t>
-  </si>
-  <si>
     <t>0992.HK</t>
   </si>
   <si>
@@ -253,21 +229,6 @@
     <t>SiriusXM</t>
   </si>
   <si>
-    <t>中國石油股份</t>
-  </si>
-  <si>
-    <t>信義玻璃</t>
-  </si>
-  <si>
-    <t>英皇鐘錶珠寶</t>
-  </si>
-  <si>
-    <t>建设银行</t>
-  </si>
-  <si>
-    <t>中国移动</t>
-  </si>
-  <si>
     <t>聯想集團</t>
   </si>
   <si>
@@ -355,193 +316,22 @@
     <t>HOLD</t>
   </si>
   <si>
-    <t>0005.HK</t>
-  </si>
-  <si>
-    <t>HSBC</t>
-  </si>
-  <si>
-    <t>0011.HK</t>
-  </si>
-  <si>
-    <t>恒生銀行</t>
-  </si>
-  <si>
-    <t>0016.HK</t>
-  </si>
-  <si>
-    <t>新鴻基地產</t>
-  </si>
-  <si>
-    <t>0027.HK</t>
-  </si>
-  <si>
-    <t>銀河娛樂</t>
-  </si>
-  <si>
-    <t>C0011</t>
-  </si>
-  <si>
-    <t>0069.HK</t>
-  </si>
-  <si>
-    <t>SHANGRI-LA ASIA</t>
-  </si>
-  <si>
     <t>0116.HK</t>
   </si>
   <si>
     <t>周生生</t>
   </si>
   <si>
-    <t>0175.HK</t>
-  </si>
-  <si>
-    <t>吉利汽車</t>
-  </si>
-  <si>
-    <t>0179.HK</t>
-  </si>
-  <si>
-    <t>德昌電機</t>
-  </si>
-  <si>
-    <t>0220.HK</t>
-  </si>
-  <si>
-    <t>统一中国</t>
-  </si>
-  <si>
-    <t>0268.HK</t>
-  </si>
-  <si>
-    <t>金蝶国际</t>
-  </si>
-  <si>
-    <t>0300.HK</t>
-  </si>
-  <si>
-    <t>美的集團</t>
-  </si>
-  <si>
-    <t>0303.HK</t>
-  </si>
-  <si>
-    <t>VTECH</t>
-  </si>
-  <si>
-    <t>0322.HK</t>
-  </si>
-  <si>
-    <t>康师傅控股</t>
-  </si>
-  <si>
-    <t>0345.HK</t>
-  </si>
-  <si>
-    <t>維他奶國際</t>
-  </si>
-  <si>
-    <t>0398.HK</t>
-  </si>
-  <si>
-    <t>東方表行集團</t>
-  </si>
-  <si>
-    <t>0468.HK</t>
-  </si>
-  <si>
-    <t>紛美包裝</t>
-  </si>
-  <si>
-    <t>0564.HK</t>
-  </si>
-  <si>
-    <t>鄭煤機</t>
-  </si>
-  <si>
-    <t>0586.HK</t>
-  </si>
-  <si>
-    <t>海螺創業</t>
-  </si>
-  <si>
     <t>0590.HK</t>
   </si>
   <si>
     <t>六福珠宝</t>
   </si>
   <si>
-    <t>0639.HK</t>
-  </si>
-  <si>
-    <t>首鋼資源</t>
-  </si>
-  <si>
-    <t>0669.HK</t>
-  </si>
-  <si>
-    <t>創科實業</t>
-  </si>
-  <si>
-    <t>0683.HK</t>
-  </si>
-  <si>
-    <t>嘉里建設</t>
-  </si>
-  <si>
-    <t>0696.HK</t>
-  </si>
-  <si>
-    <t>中國民航信息網絡</t>
-  </si>
-  <si>
     <t>0697.HK</t>
   </si>
   <si>
     <t>首程控股</t>
-  </si>
-  <si>
-    <t>0700.HK</t>
-  </si>
-  <si>
-    <t>騰訊控股</t>
-  </si>
-  <si>
-    <t>0710.HK</t>
-  </si>
-  <si>
-    <t>京东方精电</t>
-  </si>
-  <si>
-    <t>0762.HK</t>
-  </si>
-  <si>
-    <t>中国联通</t>
-  </si>
-  <si>
-    <t>0788.HK</t>
-  </si>
-  <si>
-    <t>中国铁塔</t>
-  </si>
-  <si>
-    <t>0806.HK</t>
-  </si>
-  <si>
-    <t>VALUE PARTNERS</t>
-  </si>
-  <si>
-    <t>0811.HK</t>
-  </si>
-  <si>
-    <t>新华文轩</t>
-  </si>
-  <si>
-    <t>0831.HK</t>
-  </si>
-  <si>
-    <t>利亞零售</t>
   </si>
   <si>
     <t>C0001</t>
@@ -587,6 +377,12 @@
   <si>
     <t>Market Annual Yield</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Low Growth Asset Play</t>
+  </si>
+  <si>
+    <t>Not Held</t>
   </si>
 </sst>
 </file>
@@ -727,7 +523,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -771,67 +567,37 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="4" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="179" formatCode="0.00_ "/>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
@@ -1158,11 +924,13 @@
     <col min="2" max="2" width="13.46484375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" style="2" customWidth="1"/>
-    <col min="5" max="6" width="10.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" style="4" customWidth="1"/>
     <col min="7" max="8" width="13.1328125" style="2" customWidth="1"/>
     <col min="9" max="9" width="13.1328125" style="4" customWidth="1"/>
     <col min="10" max="11" width="13.1328125" style="1" customWidth="1"/>
-    <col min="12" max="13" width="12" style="1" customWidth="1"/>
+    <col min="12" max="12" width="12" style="1" customWidth="1"/>
+    <col min="13" max="13" width="18.06640625" style="27" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.796875" style="3" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.796875" style="16" customWidth="1"/>
     <col min="16" max="16" width="8.796875" style="12"/>
@@ -1174,18 +942,18 @@
       <c r="B1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="23"/>
+      <c r="E1" s="19"/>
       <c r="F1" s="24"/>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
       <c r="J1" s="22" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="K1" s="22"/>
       <c r="L1" s="20"/>
@@ -1207,1384 +975,576 @@
       <c r="E2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>183</v>
+      <c r="F2" s="25" t="s">
+        <v>113</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>176</v>
+        <v>106</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="I2" s="21" t="s">
-        <v>178</v>
+        <v>107</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>108</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>175</v>
+        <v>105</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>174</v>
+        <v>104</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="8" t="s">
-        <v>182</v>
+      <c r="M2" s="25" t="s">
+        <v>112</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="O2" s="11" t="s">
         <v>8</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>181</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="B3" s="12" t="s">
-        <v>110</v>
+        <v>17</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D3" s="2">
-        <v>75.55</v>
+        <v>7.83</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="2">
-        <v>62.986551102246409</v>
-      </c>
+      <c r="F3" s="23"/>
       <c r="H3" s="2">
-        <v>53.538568436909443</v>
-      </c>
-      <c r="J3" s="4">
-        <v>6.284698307080272E-2</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="I3" s="4">
+        <f t="shared" ref="I3:I8" si="0">IFERROR(G3/H3-1, "nm")</f>
+        <v>-1</v>
+      </c>
+      <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="M3" s="14"/>
-      <c r="N3" s="15">
-        <v>45716</v>
-      </c>
+      <c r="L3" s="14"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="15"/>
       <c r="O3" s="16">
-        <f>IFERROR(D3/G3-1,"nm")</f>
-        <v>0.19946240392428027</v>
+        <f t="shared" ref="O3:O8" si="1">IFERROR(D3/H3-1, "nm")</f>
+        <v>38.15</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="B4" s="12" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D4" s="2">
-        <v>91.75</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="2">
-        <v>94.092949962379592</v>
-      </c>
-      <c r="H4" s="2">
-        <v>79.979007468022658</v>
-      </c>
-      <c r="J4" s="4">
-        <v>7.4114441416893731E-2</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E4" s="13"/>
+      <c r="F4" s="23"/>
+      <c r="I4" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>nm</v>
+      </c>
+      <c r="J4" s="4"/>
       <c r="K4" s="4"/>
-      <c r="L4" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="M4" s="14"/>
-      <c r="N4" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O4" s="16">
-        <f t="shared" ref="O4:O67" si="0">IFERROR(D4/G4-1,"nm")</f>
-        <v>-2.4900377374886817E-2</v>
+      <c r="L4" s="14"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>nm</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="B5" s="12" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="D5" s="2">
-        <v>70.3</v>
+        <v>15.68</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="2">
-        <v>35.979606182657591</v>
-      </c>
+      <c r="F5" s="23"/>
       <c r="H5" s="2">
-        <v>30.582665255258952</v>
-      </c>
-      <c r="J5" s="4">
-        <v>5.3342816500711238E-2</v>
-      </c>
+        <v>12.298691768409206</v>
+      </c>
+      <c r="I5" s="4">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="J5" s="4"/>
       <c r="K5" s="4"/>
-      <c r="L5" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="M5" s="14"/>
-      <c r="N5" s="15">
-        <v>45716</v>
-      </c>
+      <c r="L5" s="14"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="15"/>
       <c r="O5" s="16">
-        <f t="shared" si="0"/>
-        <v>0.95388464351466595</v>
+        <f t="shared" si="1"/>
+        <v>0.27493235014443762</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="B6" s="12" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="D6" s="2">
-        <v>31.85</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="2">
-        <v>12.948980662416149</v>
-      </c>
-      <c r="H6" s="2">
-        <v>11.006633563053727</v>
-      </c>
-      <c r="J6" s="4">
-        <v>1.5698587127158554E-2</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E6" s="13"/>
+      <c r="F6" s="23"/>
+      <c r="I6" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>nm</v>
+      </c>
+      <c r="J6" s="4"/>
       <c r="K6" s="4"/>
-      <c r="L6" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="M6" s="14"/>
-      <c r="N6" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O6" s="16">
-        <f t="shared" si="0"/>
-        <v>1.4596530669354721</v>
+      <c r="L6" s="14"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>nm</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="12" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="D7" s="2">
-        <v>5.21</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="2">
-        <v>2.4114308159686257</v>
-      </c>
-      <c r="H7" s="2">
-        <v>2.0497161935733317</v>
-      </c>
-      <c r="J7" s="4">
-        <v>3.8307758231608674E-2</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E7" s="13"/>
+      <c r="F7" s="23"/>
+      <c r="I7" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>nm</v>
+      </c>
+      <c r="J7" s="4"/>
       <c r="K7" s="4"/>
-      <c r="L7" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="M7" s="14"/>
-      <c r="N7" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O7" s="16">
-        <f t="shared" si="0"/>
-        <v>1.160543012679069</v>
+      <c r="L7" s="14"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>nm</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="B8" s="12" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="D8" s="2">
-        <v>7.61</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="13"/>
+      <c r="F8" s="23">
+        <v>4.3110984690918341E-2</v>
+      </c>
       <c r="G8" s="2">
-        <v>8.045278302904924</v>
+        <v>1.5453771778827836</v>
       </c>
       <c r="H8" s="2">
-        <v>6.8384865574691851</v>
+        <v>2.2416197633814501</v>
+      </c>
+      <c r="I8" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.31059798672027894</v>
       </c>
       <c r="J8" s="4">
-        <v>7.6215505913272003E-2</v>
-      </c>
-      <c r="K8" s="4"/>
+        <v>3.3342925997552272E-2</v>
+      </c>
+      <c r="K8" s="4">
+        <v>5.1217391304347833E-2</v>
+      </c>
       <c r="L8" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="M8" s="14"/>
+        <v>103</v>
+      </c>
+      <c r="M8" s="26" t="s">
+        <v>114</v>
+      </c>
       <c r="N8" s="15">
         <v>45716</v>
       </c>
       <c r="O8" s="16">
-        <f t="shared" si="0"/>
-        <v>-5.4103573116638715E-2</v>
+        <f t="shared" si="1"/>
+        <v>2.6043773155570271E-2</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:16">
-      <c r="B9" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="D9" s="2">
-        <v>6.4</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="2">
-        <v>6.9593803981760711</v>
-      </c>
-      <c r="H9" s="2">
-        <v>5.9154733384496607</v>
-      </c>
-      <c r="J9" s="4">
-        <v>8.59375E-2</v>
-      </c>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="23"/>
+      <c r="J9" s="4"/>
       <c r="K9" s="4"/>
-      <c r="L9" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="M9" s="14"/>
-      <c r="N9" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O9" s="16">
-        <f t="shared" si="0"/>
-        <v>-8.0377902366520204E-2</v>
-      </c>
+      <c r="L9" s="14"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="15"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="B10" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="D10" s="2">
-        <v>13.72</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="13"/>
-      <c r="G10" s="2">
-        <v>3.175480632531122</v>
-      </c>
-      <c r="H10" s="2">
-        <v>2.6991585376514537</v>
-      </c>
-      <c r="J10" s="4">
-        <v>1.4715758062209455E-2</v>
-      </c>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="23"/>
+      <c r="J10" s="4"/>
       <c r="K10" s="4"/>
-      <c r="L10" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" s="17"/>
-      <c r="N10" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O10" s="16">
-        <f t="shared" si="0"/>
-        <v>3.3206057878123536</v>
-      </c>
+      <c r="L10" s="17"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="15"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="B11" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="D11" s="2">
-        <v>10.72</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F11" s="13"/>
-      <c r="G11" s="2">
-        <v>9.7449160825583423</v>
-      </c>
-      <c r="H11" s="2">
-        <v>7.7762720989696694</v>
-      </c>
-      <c r="J11" s="4">
-        <v>5.6780738385755619E-2</v>
-      </c>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="23"/>
+      <c r="J11" s="4"/>
       <c r="K11" s="4"/>
-      <c r="L11" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" s="14"/>
-      <c r="N11" s="15">
-        <v>45808</v>
-      </c>
-      <c r="O11" s="16">
-        <f t="shared" si="0"/>
-        <v>0.10006078135314933</v>
-      </c>
+      <c r="L11" s="14"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="15"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="B12" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="D12" s="2">
-        <v>7.55</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="13"/>
-      <c r="G12" s="2">
-        <v>2.5451227337364464</v>
-      </c>
-      <c r="H12" s="2">
-        <v>2.1633543236759794</v>
-      </c>
-      <c r="J12" s="4">
-        <v>5.9679958717712499E-2</v>
-      </c>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="23"/>
+      <c r="J12" s="4"/>
       <c r="K12" s="4"/>
-      <c r="L12" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="M12" s="14"/>
-      <c r="N12" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O12" s="16">
-        <f t="shared" si="0"/>
-        <v>1.9664581200435816</v>
-      </c>
+      <c r="L12" s="14"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="15"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="B13" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="D13" s="2">
-        <v>8.1199999999999992</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F13" s="13"/>
-      <c r="G13" s="2">
-        <v>0</v>
-      </c>
-      <c r="H13" s="2">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4">
-        <v>0</v>
-      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="23"/>
+      <c r="J13" s="4"/>
       <c r="K13" s="4"/>
-      <c r="L13" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="M13" s="14"/>
-      <c r="N13" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O13" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>nm</v>
-      </c>
+      <c r="L13" s="14"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="15"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="B14" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="D14" s="2">
-        <v>75.099999999999994</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="13"/>
-      <c r="G14" s="2">
-        <v>37.080642745641171</v>
-      </c>
-      <c r="H14" s="2">
-        <v>31.518546333794994</v>
-      </c>
-      <c r="J14" s="4">
-        <v>0</v>
-      </c>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="23"/>
+      <c r="J14" s="4"/>
       <c r="K14" s="4"/>
-      <c r="L14" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="M14" s="14"/>
-      <c r="N14" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O14" s="16">
-        <f t="shared" si="0"/>
-        <v>1.0253154864428016</v>
-      </c>
+      <c r="L14" s="14"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="15"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="B15" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="D15" s="2">
-        <v>50.05</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="13"/>
-      <c r="G15" s="2">
-        <v>31.708341621722621</v>
-      </c>
-      <c r="H15" s="2">
-        <v>26.952090378464227</v>
-      </c>
-      <c r="J15" s="4">
-        <v>0.10108770642961774</v>
-      </c>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="23"/>
+      <c r="J15" s="4"/>
       <c r="K15" s="4"/>
-      <c r="L15" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="M15" s="14"/>
-      <c r="N15" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O15" s="16">
-        <f t="shared" si="0"/>
-        <v>0.57844899607464639</v>
-      </c>
+      <c r="L15" s="14"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="15"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="B16" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="D16" s="2">
-        <v>10.78</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F16" s="13"/>
-      <c r="G16" s="2">
-        <v>4.5625398611204986</v>
-      </c>
-      <c r="H16" s="2">
-        <v>3.8781588819524235</v>
-      </c>
-      <c r="J16" s="4">
-        <v>2.7235238704699093E-2</v>
-      </c>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="23"/>
+      <c r="J16" s="4"/>
       <c r="K16" s="4"/>
-      <c r="L16" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="M16" s="14"/>
-      <c r="N16" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O16" s="16">
-        <f t="shared" si="0"/>
-        <v>1.3627190836975123</v>
-      </c>
-    </row>
-    <row r="17" spans="2:16">
-      <c r="B17" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="D17" s="2">
-        <v>9.5399999999999991</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F17" s="13"/>
-      <c r="G17" s="2">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2">
-        <v>0</v>
-      </c>
-      <c r="J17" s="4">
-        <v>1.3587956952977557E-3</v>
-      </c>
+      <c r="L16" s="14"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="15"/>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="23"/>
+      <c r="J17" s="4"/>
       <c r="K17" s="4"/>
-      <c r="L17" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="M17" s="14"/>
-      <c r="N17" s="15">
-        <v>45626</v>
-      </c>
-      <c r="O17" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>nm</v>
-      </c>
-    </row>
-    <row r="18" spans="2:16">
-      <c r="B18" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D18" s="2">
-        <v>3.45</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F18" s="13"/>
-      <c r="G18" s="2">
-        <v>3.1150802359800442</v>
-      </c>
-      <c r="H18" s="2">
-        <v>2.6478182005830377</v>
-      </c>
-      <c r="J18" s="4">
-        <v>7.0492753623188409E-2</v>
-      </c>
+      <c r="L17" s="14"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="15"/>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="23"/>
+      <c r="J18" s="4"/>
       <c r="K18" s="4"/>
-      <c r="L18" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="M18" s="14"/>
-      <c r="N18" s="15">
-        <v>45626</v>
-      </c>
-      <c r="O18" s="16">
-        <f t="shared" si="0"/>
-        <v>0.10751561393236009</v>
-      </c>
-    </row>
-    <row r="19" spans="2:16">
-      <c r="B19" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="D19" s="2">
-        <v>2.57</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F19" s="13"/>
-      <c r="G19" s="2">
-        <v>1.6912803965150771</v>
-      </c>
-      <c r="H19" s="2">
-        <v>1.4375883370378155</v>
-      </c>
-      <c r="J19" s="4">
-        <v>2.4780832839847076E-2</v>
-      </c>
+      <c r="L18" s="14"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="15"/>
+    </row>
+    <row r="19" spans="2:14">
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="23"/>
+      <c r="J19" s="4"/>
       <c r="K19" s="4"/>
-      <c r="L19" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="M19" s="14"/>
-      <c r="N19" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O19" s="16">
-        <f t="shared" si="0"/>
-        <v>0.51955879421031836</v>
-      </c>
-    </row>
-    <row r="20" spans="2:16">
-      <c r="B20" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="D20" s="2">
-        <v>9.83</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="13"/>
-      <c r="G20" s="2">
-        <v>9.4696282976697326</v>
-      </c>
-      <c r="H20" s="2">
-        <v>8.0491840530192729</v>
-      </c>
-      <c r="J20" s="4">
-        <v>9.0703394260193054E-2</v>
-      </c>
+      <c r="L19" s="14"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="15"/>
+    </row>
+    <row r="20" spans="2:14">
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="23"/>
+      <c r="J20" s="4"/>
       <c r="K20" s="4"/>
-      <c r="L20" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" s="14"/>
-      <c r="N20" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O20" s="16">
-        <f t="shared" si="0"/>
-        <v>3.8055527735861405E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="2:16">
-      <c r="B21" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D21" s="2">
-        <v>6.1</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="13"/>
-      <c r="G21" s="2">
-        <v>2.5782155438595891</v>
-      </c>
-      <c r="H21" s="2">
-        <v>2.1914832122806507</v>
-      </c>
-      <c r="J21" s="4">
-        <v>3.2786885245901641E-2</v>
-      </c>
+      <c r="L20" s="14"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="15"/>
+    </row>
+    <row r="21" spans="2:14">
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="23"/>
+      <c r="J21" s="4"/>
       <c r="K21" s="4"/>
-      <c r="L21" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="M21" s="14"/>
-      <c r="N21" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O21" s="16">
-        <f t="shared" si="0"/>
-        <v>1.365977512829784</v>
-      </c>
-    </row>
-    <row r="22" spans="2:16">
-      <c r="B22" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="D22" s="2">
-        <v>13.82</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="13"/>
-      <c r="G22" s="2">
-        <v>16.072921931882622</v>
-      </c>
-      <c r="H22" s="2">
-        <v>13.661983642100228</v>
-      </c>
-      <c r="J22" s="4">
-        <v>7.9594790159189591E-2</v>
-      </c>
+      <c r="L21" s="14"/>
+      <c r="M21" s="26"/>
+      <c r="N21" s="15"/>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="23"/>
+      <c r="J22" s="4"/>
       <c r="K22" s="4"/>
-      <c r="L22" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="M22" s="14"/>
-      <c r="N22" s="15">
-        <v>45626</v>
-      </c>
-      <c r="O22" s="16">
-        <f t="shared" si="0"/>
-        <v>-0.14016878458257631</v>
-      </c>
-      <c r="P22" s="12" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="23" spans="2:16">
-      <c r="B23" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="D23" s="2">
-        <v>2.2799999999999998</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F23" s="13"/>
-      <c r="G23" s="2">
-        <v>2.0793011714984888</v>
-      </c>
-      <c r="H23" s="2">
-        <v>1.7674059957737154</v>
-      </c>
-      <c r="J23" s="4">
-        <v>7.2368421052631582E-2</v>
-      </c>
+      <c r="L22" s="14"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="15"/>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="23"/>
+      <c r="J23" s="4"/>
       <c r="K23" s="4"/>
-      <c r="L23" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="M23" s="14"/>
-      <c r="N23" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O23" s="16">
-        <f t="shared" si="0"/>
-        <v>9.6522250481335226E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="2:16">
-      <c r="B24" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="D24" s="2">
-        <v>96.8</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F24" s="13"/>
-      <c r="G24" s="2">
-        <v>27.927833010475759</v>
-      </c>
-      <c r="H24" s="2">
-        <v>23.738658058904399</v>
-      </c>
-      <c r="J24" s="4">
-        <v>1.9974011811343107E-2</v>
-      </c>
+      <c r="L23" s="14"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="15"/>
+    </row>
+    <row r="24" spans="2:14">
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="23"/>
+      <c r="J24" s="4"/>
       <c r="K24" s="4"/>
-      <c r="L24" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="M24" s="14"/>
-      <c r="N24" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O24" s="16">
-        <f t="shared" si="0"/>
-        <v>2.4660762961340472</v>
-      </c>
-    </row>
-    <row r="25" spans="2:16">
-      <c r="B25" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="D25" s="2">
-        <v>14.92</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F25" s="13"/>
-      <c r="G25" s="2">
-        <v>12.934469726537158</v>
-      </c>
-      <c r="H25" s="2">
-        <v>7.6776086571019206</v>
-      </c>
-      <c r="J25" s="4">
-        <v>9.0482322719137018E-2</v>
-      </c>
+      <c r="L24" s="14"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="15"/>
+    </row>
+    <row r="25" spans="2:14">
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="23"/>
+      <c r="J25" s="4"/>
       <c r="K25" s="4"/>
-      <c r="L25" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="M25" s="14"/>
-      <c r="N25" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O25" s="16">
-        <f t="shared" si="0"/>
-        <v>0.15350689401585638</v>
-      </c>
-    </row>
-    <row r="26" spans="2:16">
-      <c r="B26" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="D26" s="2">
-        <v>9.06</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F26" s="13"/>
-      <c r="G26" s="2">
-        <v>1.7431606174350143</v>
-      </c>
-      <c r="H26" s="2">
-        <v>1.4816865248197622</v>
-      </c>
-      <c r="J26" s="4">
-        <v>1.8745177453541421E-2</v>
-      </c>
+      <c r="L25" s="14"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="15"/>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="23"/>
+      <c r="J26" s="4"/>
       <c r="K26" s="4"/>
-      <c r="L26" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="M26" s="14"/>
-      <c r="N26" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O26" s="16">
-        <f t="shared" si="0"/>
-        <v>4.1974556500314932</v>
-      </c>
-    </row>
-    <row r="27" spans="2:16">
-      <c r="B27" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="D27" s="2">
-        <v>0.99</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F27" s="13"/>
-      <c r="G27" s="2">
-        <v>0.10837595768821706</v>
-      </c>
-      <c r="H27" s="2">
-        <v>9.2119564034984502E-2</v>
-      </c>
-      <c r="J27" s="4">
-        <v>5.5353535353535356E-2</v>
-      </c>
+      <c r="L26" s="14"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="15"/>
+    </row>
+    <row r="27" spans="2:14">
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="23"/>
+      <c r="J27" s="4"/>
       <c r="K27" s="4"/>
-      <c r="L27" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="M27" s="14"/>
-      <c r="N27" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O27" s="16">
-        <f t="shared" si="0"/>
-        <v>8.1348673738883654</v>
-      </c>
-    </row>
-    <row r="28" spans="2:16">
-      <c r="B28" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="D28" s="2">
-        <v>371.8</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F28" s="13"/>
-      <c r="G28" s="2">
-        <v>102.63423277834117</v>
-      </c>
-      <c r="H28" s="2">
-        <v>87.239097861589997</v>
-      </c>
-      <c r="J28" s="4">
-        <v>9.1447014523937595E-3</v>
-      </c>
+      <c r="L27" s="14"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="15"/>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="23"/>
+      <c r="J28" s="4"/>
       <c r="K28" s="4"/>
-      <c r="L28" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="M28" s="14"/>
-      <c r="N28" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O28" s="16">
-        <f t="shared" si="0"/>
-        <v>2.6225729947528844</v>
-      </c>
-    </row>
-    <row r="29" spans="2:16">
-      <c r="B29" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="D29" s="2">
-        <v>6.04</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F29" s="13"/>
-      <c r="G29" s="2">
-        <v>0</v>
-      </c>
-      <c r="H29" s="2">
-        <v>0</v>
-      </c>
-      <c r="J29" s="4">
-        <v>2.7801441310783621E-2</v>
-      </c>
+      <c r="L28" s="14"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="15"/>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="23"/>
+      <c r="J29" s="4"/>
       <c r="K29" s="4"/>
-      <c r="L29" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="M29" s="14"/>
-      <c r="N29" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O29" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>nm</v>
-      </c>
-    </row>
-    <row r="30" spans="2:16">
-      <c r="B30" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="D30" s="2">
-        <v>7.28</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F30" s="13"/>
-      <c r="G30" s="2">
-        <v>2.3399188408583842</v>
-      </c>
-      <c r="H30" s="2">
-        <v>1.9889310147296264</v>
-      </c>
-      <c r="J30" s="4">
-        <v>0</v>
-      </c>
+      <c r="L29" s="14"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="15"/>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="23"/>
+      <c r="J30" s="4"/>
       <c r="K30" s="4"/>
-      <c r="L30" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="M30" s="14"/>
-      <c r="N30" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O30" s="16">
-        <f t="shared" si="0"/>
-        <v>2.1112190187457012</v>
-      </c>
-    </row>
-    <row r="31" spans="2:16">
-      <c r="B31" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="D31" s="2">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F31" s="13"/>
-      <c r="G31" s="2">
-        <v>0.60802806789784225</v>
-      </c>
-      <c r="H31" s="2">
-        <v>0.51682385771316586</v>
-      </c>
-      <c r="J31" s="4">
-        <v>4.7024964737600504E-2</v>
-      </c>
+      <c r="L30" s="14"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="15"/>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="23"/>
+      <c r="J31" s="4"/>
       <c r="K31" s="4"/>
-      <c r="L31" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="M31" s="17"/>
-      <c r="N31" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O31" s="16">
-        <f t="shared" si="0"/>
-        <v>0.79268040004879547</v>
-      </c>
-    </row>
-    <row r="32" spans="2:16">
-      <c r="B32" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="D32" s="2">
-        <v>1.38</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="13"/>
-      <c r="G32" s="2">
-        <v>0.23253409172156309</v>
-      </c>
-      <c r="H32" s="2">
-        <v>0.19765397796332862</v>
-      </c>
-      <c r="J32" s="4">
-        <v>2.1739130434782608E-2</v>
-      </c>
+      <c r="L31" s="17"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="15"/>
+    </row>
+    <row r="32" spans="2:14">
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="23"/>
+      <c r="J32" s="4"/>
       <c r="K32" s="4"/>
-      <c r="L32" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="M32" s="14"/>
-      <c r="N32" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O32" s="16">
-        <f t="shared" si="0"/>
-        <v>4.9346136722713991</v>
-      </c>
+      <c r="L32" s="14"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="15"/>
     </row>
     <row r="33" spans="2:15">
-      <c r="B33" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="D33" s="2">
-        <v>10.44</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F33" s="13"/>
-      <c r="G33" s="2">
-        <v>7.533686568392123</v>
-      </c>
-      <c r="H33" s="2">
-        <v>6.4036335831333044</v>
-      </c>
-      <c r="J33" s="4">
-        <v>5.9985914487643871E-2</v>
-      </c>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="23"/>
+      <c r="J33" s="4"/>
       <c r="K33" s="4"/>
-      <c r="L33" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="M33" s="14"/>
-      <c r="N33" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O33" s="16">
-        <f t="shared" si="0"/>
-        <v>0.38577572948168948</v>
-      </c>
+      <c r="L33" s="14"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="15"/>
     </row>
     <row r="34" spans="2:15">
-      <c r="B34" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="D34" s="2">
-        <v>0.40500000000000003</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F34" s="13"/>
-      <c r="G34" s="2">
-        <v>0.27097481399542533</v>
-      </c>
-      <c r="H34" s="2">
-        <v>0</v>
-      </c>
-      <c r="J34" s="4">
-        <v>0.14814814814814814</v>
-      </c>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="23"/>
+      <c r="J34" s="4"/>
       <c r="K34" s="4"/>
-      <c r="L34" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="M34" s="17"/>
-      <c r="N34" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O34" s="16">
-        <f t="shared" si="0"/>
-        <v>0.49460384907520361</v>
-      </c>
+      <c r="L34" s="17"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="15"/>
     </row>
     <row r="35" spans="2:15">
-      <c r="B35" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D35" s="2">
-        <v>6.27</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F35" s="13"/>
-      <c r="G35" s="2">
-        <v>5.3593919843092221</v>
-      </c>
-      <c r="H35" s="2">
-        <v>4.5554831866628387</v>
-      </c>
-      <c r="J35" s="4">
-        <v>7.6180311481348073E-2</v>
-      </c>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="23"/>
+      <c r="J35" s="4"/>
       <c r="K35" s="4"/>
-      <c r="L35" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="M35" s="14"/>
-      <c r="N35" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O35" s="16">
-        <f t="shared" si="0"/>
-        <v>0.16990882890387171</v>
-      </c>
+      <c r="L35" s="14"/>
+      <c r="M35" s="26"/>
+      <c r="N35" s="15"/>
     </row>
     <row r="36" spans="2:15">
-      <c r="B36" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D36" s="2">
-        <v>6.84</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F36" s="13"/>
-      <c r="G36" s="2">
-        <v>4.9175737170431972</v>
-      </c>
-      <c r="H36" s="2">
-        <v>4.1799376594867175</v>
-      </c>
-      <c r="J36" s="4">
-        <v>9.2105263157894746E-2</v>
-      </c>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="23"/>
+      <c r="J36" s="4"/>
       <c r="K36" s="4"/>
-      <c r="L36" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="M36" s="14"/>
-      <c r="N36" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O36" s="16">
-        <f t="shared" si="0"/>
-        <v>0.39092983523441815</v>
-      </c>
+      <c r="L36" s="14"/>
+      <c r="M36" s="26"/>
+      <c r="N36" s="15"/>
     </row>
     <row r="37" spans="2:15">
-      <c r="B37" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D37" s="2">
-        <v>0.17199999999999999</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F37" s="13"/>
-      <c r="G37" s="2">
-        <v>0.16509453059637313</v>
-      </c>
-      <c r="H37" s="2">
-        <v>0.14033035100691715</v>
-      </c>
-      <c r="J37" s="4">
-        <v>7.0348837209302323E-2</v>
-      </c>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="23"/>
+      <c r="J37" s="4"/>
       <c r="K37" s="4"/>
-      <c r="L37" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="M37" s="14"/>
-      <c r="N37" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O37" s="16">
-        <f t="shared" si="0"/>
-        <v>4.1827366289374446E-2</v>
-      </c>
+      <c r="L37" s="14"/>
+      <c r="M37" s="26"/>
+      <c r="N37" s="15"/>
     </row>
     <row r="38" spans="2:15">
-      <c r="B38" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D38" s="2">
-        <v>5.89</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F38" s="13"/>
-      <c r="G38" s="2">
-        <v>5.3447989608771485</v>
-      </c>
-      <c r="H38" s="2">
-        <v>4.5430791167455764</v>
-      </c>
-      <c r="J38" s="4">
-        <v>7.208459581030785E-2</v>
-      </c>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="23"/>
+      <c r="J38" s="4"/>
       <c r="K38" s="4"/>
-      <c r="L38" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="M38" s="14"/>
-      <c r="N38" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O38" s="16">
-        <f t="shared" si="0"/>
-        <v>0.10200590202056481</v>
-      </c>
+      <c r="L38" s="14"/>
+      <c r="M38" s="26"/>
+      <c r="N38" s="15"/>
     </row>
     <row r="39" spans="2:15">
-      <c r="B39" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D39" s="2">
-        <v>74.3</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F39" s="13"/>
-      <c r="G39" s="2">
-        <v>59.17375769038906</v>
-      </c>
-      <c r="H39" s="2">
-        <v>50.297694036830698</v>
-      </c>
-      <c r="J39" s="4">
-        <v>6.4972475399720717E-2</v>
-      </c>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="23"/>
+      <c r="J39" s="4"/>
       <c r="K39" s="4"/>
-      <c r="L39" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="M39" s="14"/>
-      <c r="N39" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O39" s="16">
-        <f t="shared" si="0"/>
-        <v>0.25562416348062555</v>
-      </c>
+      <c r="L39" s="14"/>
+      <c r="M39" s="26"/>
+      <c r="N39" s="15"/>
     </row>
     <row r="40" spans="2:15">
       <c r="B40" s="12" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="D40" s="2">
         <v>9.17</v>
@@ -2592,7 +1552,7 @@
       <c r="E40" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F40" s="13"/>
+      <c r="F40" s="23"/>
       <c r="G40" s="2">
         <v>6.4392993083359604</v>
       </c>
@@ -2604,23 +1564,23 @@
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="M40" s="14"/>
+        <v>20</v>
+      </c>
+      <c r="M40" s="26"/>
       <c r="N40" s="15">
         <v>45716</v>
       </c>
       <c r="O40" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="O40:O67" si="2">IFERROR(D40/G40-1,"nm")</f>
         <v>0.42406798642346466</v>
       </c>
     </row>
     <row r="41" spans="2:15">
       <c r="B41" s="12" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D41" s="2">
         <v>5.14</v>
@@ -2628,7 +1588,7 @@
       <c r="E41" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F41" s="13"/>
+      <c r="F41" s="23"/>
       <c r="G41" s="2">
         <v>4.2807534371073093</v>
       </c>
@@ -2642,21 +1602,21 @@
       <c r="L41" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="M41" s="14"/>
+      <c r="M41" s="26"/>
       <c r="N41" s="15">
         <v>45716</v>
       </c>
       <c r="O41" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.20072320807930488</v>
       </c>
     </row>
     <row r="42" spans="2:15">
       <c r="B42" s="12" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D42" s="2">
         <v>20</v>
@@ -2664,7 +1624,7 @@
       <c r="E42" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F42" s="13"/>
+      <c r="F42" s="23"/>
       <c r="G42" s="2">
         <v>16.286981483416568</v>
       </c>
@@ -2676,23 +1636,23 @@
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="M42" s="14"/>
+        <v>22</v>
+      </c>
+      <c r="M42" s="26"/>
       <c r="N42" s="15">
         <v>45716</v>
       </c>
       <c r="O42" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.22797462625987719</v>
       </c>
     </row>
     <row r="43" spans="2:15">
       <c r="B43" s="12" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D43" s="2">
         <v>4.18</v>
@@ -2700,7 +1660,7 @@
       <c r="E43" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F43" s="13"/>
+      <c r="F43" s="23"/>
       <c r="G43" s="2">
         <v>4.1768439125951957</v>
       </c>
@@ -2712,23 +1672,23 @@
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="M43" s="14"/>
+        <v>22</v>
+      </c>
+      <c r="M43" s="26"/>
       <c r="N43" s="15">
         <v>45716</v>
       </c>
       <c r="O43" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>7.5561535715684691E-4</v>
       </c>
     </row>
     <row r="44" spans="2:15">
       <c r="B44" s="12" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D44" s="2">
         <v>8.18</v>
@@ -2736,7 +1696,7 @@
       <c r="E44" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F44" s="13"/>
+      <c r="F44" s="23"/>
       <c r="G44" s="2">
         <v>8.3657953760452042</v>
       </c>
@@ -2748,23 +1708,23 @@
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="M44" s="14"/>
+        <v>21</v>
+      </c>
+      <c r="M44" s="26"/>
       <c r="N44" s="15">
         <v>45716</v>
       </c>
       <c r="O44" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-2.2208931451660252E-2</v>
       </c>
     </row>
     <row r="45" spans="2:15">
       <c r="B45" s="12" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="D45" s="2">
         <v>7.88</v>
@@ -2772,7 +1732,7 @@
       <c r="E45" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F45" s="13"/>
+      <c r="F45" s="23"/>
       <c r="G45" s="2">
         <v>7.2438894799757669</v>
       </c>
@@ -2784,23 +1744,23 @@
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="M45" s="14"/>
+        <v>23</v>
+      </c>
+      <c r="M45" s="26"/>
       <c r="N45" s="15">
         <v>45716</v>
       </c>
       <c r="O45" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>8.7813393865633804E-2</v>
       </c>
     </row>
     <row r="46" spans="2:15">
       <c r="B46" s="12" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D46" s="2">
         <v>4.17</v>
@@ -2808,7 +1768,7 @@
       <c r="E46" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F46" s="13"/>
+      <c r="F46" s="23"/>
       <c r="G46" s="2">
         <v>2.9348928674977937</v>
       </c>
@@ -2822,21 +1782,21 @@
       <c r="L46" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="M46" s="14"/>
+      <c r="M46" s="26"/>
       <c r="N46" s="15">
         <v>45716</v>
       </c>
       <c r="O46" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.42083550857351182</v>
       </c>
     </row>
     <row r="47" spans="2:15">
       <c r="B47" s="12" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="D47" s="2">
         <v>4.83</v>
@@ -2844,7 +1804,7 @@
       <c r="E47" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F47" s="13"/>
+      <c r="F47" s="23"/>
       <c r="G47" s="2">
         <v>4.0220415716970601</v>
       </c>
@@ -2858,21 +1818,21 @@
       <c r="L47" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="M47" s="14"/>
+      <c r="M47" s="26"/>
       <c r="N47" s="15">
         <v>45716</v>
       </c>
       <c r="O47" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.20088266466177518</v>
       </c>
     </row>
     <row r="48" spans="2:15">
       <c r="B48" s="12" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D48" s="2">
         <v>73.349999999999994</v>
@@ -2880,7 +1840,7 @@
       <c r="E48" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F48" s="13"/>
+      <c r="F48" s="23"/>
       <c r="G48" s="2">
         <v>0</v>
       </c>
@@ -2892,23 +1852,23 @@
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="M48" s="17"/>
+        <v>21</v>
+      </c>
+      <c r="M48" s="26"/>
       <c r="N48" s="15">
         <v>45716</v>
       </c>
       <c r="O48" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>nm</v>
       </c>
     </row>
     <row r="49" spans="2:15">
       <c r="B49" s="12" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="D49" s="2">
         <v>3.67</v>
@@ -2916,7 +1876,7 @@
       <c r="E49" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F49" s="13"/>
+      <c r="F49" s="23"/>
       <c r="G49" s="2">
         <v>3.2725855442261613</v>
       </c>
@@ -2928,23 +1888,23 @@
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="M49" s="14"/>
+        <v>37</v>
+      </c>
+      <c r="M49" s="26"/>
       <c r="N49" s="15">
         <v>45716</v>
       </c>
       <c r="O49" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.12143745378176551</v>
       </c>
     </row>
     <row r="50" spans="2:15">
       <c r="B50" s="12" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D50" s="2">
         <v>5.77</v>
@@ -2952,7 +1912,7 @@
       <c r="E50" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F50" s="13"/>
+      <c r="F50" s="23"/>
       <c r="G50" s="2">
         <v>4.7182661671250088</v>
       </c>
@@ -2964,23 +1924,23 @@
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="M50" s="14"/>
+        <v>21</v>
+      </c>
+      <c r="M50" s="26"/>
       <c r="N50" s="15">
         <v>45716</v>
       </c>
       <c r="O50" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.22290684663002924</v>
       </c>
     </row>
     <row r="51" spans="2:15">
       <c r="B51" s="12" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D51" s="2">
         <v>4.43</v>
@@ -2988,7 +1948,7 @@
       <c r="E51" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F51" s="13"/>
+      <c r="F51" s="23"/>
       <c r="G51" s="2">
         <v>3.3648935418115595</v>
       </c>
@@ -3002,21 +1962,21 @@
       <c r="L51" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="M51" s="14"/>
+      <c r="M51" s="26"/>
       <c r="N51" s="15">
         <v>45716</v>
       </c>
       <c r="O51" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.31653496461436892</v>
       </c>
     </row>
     <row r="52" spans="2:15">
       <c r="B52" s="12" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D52" s="2">
         <v>4.79</v>
@@ -3024,7 +1984,7 @@
       <c r="E52" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F52" s="13"/>
+      <c r="F52" s="23"/>
       <c r="G52" s="2">
         <v>2.4061254319986021</v>
       </c>
@@ -3036,23 +1996,23 @@
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="M52" s="14"/>
+        <v>42</v>
+      </c>
+      <c r="M52" s="26"/>
       <c r="N52" s="15">
         <v>45716</v>
       </c>
       <c r="O52" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.9907524089553712</v>
       </c>
     </row>
     <row r="53" spans="2:15">
       <c r="B53" s="12" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D53" s="2">
         <v>17.22</v>
@@ -3060,7 +2020,7 @@
       <c r="E53" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F53" s="13"/>
+      <c r="F53" s="23"/>
       <c r="G53" s="2">
         <v>11.847371178678728</v>
       </c>
@@ -3072,23 +2032,23 @@
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="M53" s="14"/>
+        <v>22</v>
+      </c>
+      <c r="M53" s="26"/>
       <c r="N53" s="15">
         <v>45716</v>
       </c>
       <c r="O53" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.45348700064282532</v>
       </c>
     </row>
     <row r="54" spans="2:15">
       <c r="B54" s="12" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D54" s="2">
         <v>22.7</v>
@@ -3096,7 +2056,7 @@
       <c r="E54" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F54" s="13"/>
+      <c r="F54" s="23"/>
       <c r="G54" s="2">
         <v>15.891475739819455</v>
       </c>
@@ -3108,23 +2068,23 @@
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="M54" s="14"/>
+        <v>22</v>
+      </c>
+      <c r="M54" s="26"/>
       <c r="N54" s="15">
         <v>45716</v>
       </c>
       <c r="O54" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.42843876627016741</v>
       </c>
     </row>
     <row r="55" spans="2:15">
       <c r="B55" s="12" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D55" s="2">
         <v>6.59</v>
@@ -3132,7 +2092,7 @@
       <c r="E55" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F55" s="13"/>
+      <c r="F55" s="23"/>
       <c r="G55" s="2">
         <v>6.9011468861157468</v>
       </c>
@@ -3144,23 +2104,23 @@
       </c>
       <c r="K55" s="4"/>
       <c r="L55" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="M55" s="14"/>
+        <v>19</v>
+      </c>
+      <c r="M55" s="26"/>
       <c r="N55" s="15">
         <v>45808</v>
       </c>
       <c r="O55" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-4.5086257581582023E-2</v>
       </c>
     </row>
     <row r="56" spans="2:15">
       <c r="B56" s="12" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D56" s="2">
         <v>4.2300000000000004</v>
@@ -3168,7 +2128,7 @@
       <c r="E56" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F56" s="13"/>
+      <c r="F56" s="23"/>
       <c r="G56" s="2">
         <v>3.9087842724427571</v>
       </c>
@@ -3180,23 +2140,23 @@
       </c>
       <c r="K56" s="4"/>
       <c r="L56" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="M56" s="14"/>
+        <v>48</v>
+      </c>
+      <c r="M56" s="26"/>
       <c r="N56" s="15">
         <v>45716</v>
       </c>
       <c r="O56" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>8.2177911383301439E-2</v>
       </c>
     </row>
     <row r="57" spans="2:15">
       <c r="B57" s="12" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="D57" s="2">
         <v>15.12</v>
@@ -3204,7 +2164,7 @@
       <c r="E57" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F57" s="13"/>
+      <c r="F57" s="23"/>
       <c r="G57" s="2">
         <v>12.640799825099876</v>
       </c>
@@ -3216,23 +2176,23 @@
       </c>
       <c r="K57" s="4"/>
       <c r="L57" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="M57" s="14"/>
+        <v>21</v>
+      </c>
+      <c r="M57" s="26"/>
       <c r="N57" s="15">
         <v>45716</v>
       </c>
       <c r="O57" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.19612684396578794</v>
       </c>
     </row>
     <row r="58" spans="2:15">
       <c r="B58" s="12" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="D58" s="2">
         <v>24.35</v>
@@ -3240,7 +2200,7 @@
       <c r="E58" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F58" s="13"/>
+      <c r="F58" s="23"/>
       <c r="G58" s="2">
         <v>19.480918389247329</v>
       </c>
@@ -3254,21 +2214,21 @@
       <c r="L58" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="M58" s="14"/>
+      <c r="M58" s="26"/>
       <c r="N58" s="15">
         <v>45716</v>
       </c>
       <c r="O58" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.24994107122999942</v>
       </c>
     </row>
     <row r="59" spans="2:15">
       <c r="B59" s="12" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D59" s="2">
         <v>96.35</v>
@@ -3276,7 +2236,7 @@
       <c r="E59" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F59" s="13"/>
+      <c r="F59" s="23"/>
       <c r="G59" s="2">
         <v>26.715062598200028</v>
       </c>
@@ -3290,21 +2250,21 @@
       <c r="L59" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="M59" s="14"/>
+      <c r="M59" s="26"/>
       <c r="N59" s="15">
         <v>45716</v>
       </c>
       <c r="O59" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.6065796082578423</v>
       </c>
     </row>
     <row r="60" spans="2:15">
       <c r="B60" s="12" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D60" s="2">
         <v>6.11</v>
@@ -3312,7 +2272,7 @@
       <c r="E60" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F60" s="13"/>
+      <c r="F60" s="23"/>
       <c r="G60" s="2">
         <v>4.882283658811315</v>
       </c>
@@ -3326,21 +2286,21 @@
       <c r="L60" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="M60" s="14"/>
+      <c r="M60" s="26"/>
       <c r="N60" s="15">
         <v>45716</v>
       </c>
       <c r="O60" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.25146354185565611</v>
       </c>
     </row>
     <row r="61" spans="2:15">
       <c r="B61" s="12" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="D61" s="2">
         <v>52.05</v>
@@ -3348,7 +2308,7 @@
       <c r="E61" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F61" s="13"/>
+      <c r="F61" s="23"/>
       <c r="G61" s="2">
         <v>39.836259703774758</v>
       </c>
@@ -3360,23 +2320,23 @@
       </c>
       <c r="K61" s="4"/>
       <c r="L61" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="M61" s="14"/>
+        <v>20</v>
+      </c>
+      <c r="M61" s="26"/>
       <c r="N61" s="15">
         <v>45716</v>
       </c>
       <c r="O61" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.30659857092627352</v>
       </c>
     </row>
     <row r="62" spans="2:15">
       <c r="B62" s="12" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D62" s="2">
         <v>39.1</v>
@@ -3384,7 +2344,7 @@
       <c r="E62" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F62" s="13"/>
+      <c r="F62" s="23"/>
       <c r="G62" s="2">
         <v>24.572872856406878</v>
       </c>
@@ -3398,21 +2358,21 @@
       <c r="L62" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="M62" s="14"/>
+      <c r="M62" s="26"/>
       <c r="N62" s="15">
         <v>45716</v>
       </c>
       <c r="O62" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.59118554140915069</v>
       </c>
     </row>
     <row r="63" spans="2:15">
       <c r="B63" s="12" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D63" s="2">
         <v>3.76</v>
@@ -3420,7 +2380,7 @@
       <c r="E63" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F63" s="13"/>
+      <c r="F63" s="23"/>
       <c r="G63" s="2">
         <v>4.2004774926652244</v>
       </c>
@@ -3434,21 +2394,21 @@
       <c r="L63" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="M63" s="14"/>
+      <c r="M63" s="26"/>
       <c r="N63" s="15">
         <v>45716</v>
       </c>
       <c r="O63" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-0.10486367167408372</v>
       </c>
     </row>
     <row r="64" spans="2:15">
       <c r="B64" s="12" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="D64" s="2">
         <v>296</v>
@@ -3456,7 +2416,7 @@
       <c r="E64" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F64" s="13"/>
+      <c r="F64" s="23"/>
       <c r="G64" s="2">
         <v>0</v>
       </c>
@@ -3468,23 +2428,23 @@
       </c>
       <c r="K64" s="4"/>
       <c r="L64" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="M64" s="14"/>
+        <v>19</v>
+      </c>
+      <c r="M64" s="26"/>
       <c r="N64" s="15">
         <v>45716</v>
       </c>
       <c r="O64" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>nm</v>
       </c>
     </row>
     <row r="65" spans="2:16">
       <c r="B65" s="12" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="D65" s="2">
         <v>5.0999999999999996</v>
@@ -3492,7 +2452,7 @@
       <c r="E65" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F65" s="13"/>
+      <c r="F65" s="23"/>
       <c r="G65" s="2">
         <v>4.9737925149172781</v>
       </c>
@@ -3504,23 +2464,23 @@
       </c>
       <c r="K65" s="4"/>
       <c r="L65" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="M65" s="14"/>
+        <v>21</v>
+      </c>
+      <c r="M65" s="26"/>
       <c r="N65" s="15">
         <v>45716</v>
       </c>
       <c r="O65" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.5374497368799265E-2</v>
       </c>
     </row>
     <row r="66" spans="2:16">
       <c r="B66" s="12" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="D66" s="2">
         <v>1.77</v>
@@ -3528,7 +2488,7 @@
       <c r="E66" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F66" s="13"/>
+      <c r="F66" s="23"/>
       <c r="G66" s="2">
         <v>1.5223126471290205</v>
       </c>
@@ -3540,26 +2500,26 @@
       </c>
       <c r="K66" s="4"/>
       <c r="L66" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M66" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="M66" s="26"/>
       <c r="N66" s="15">
         <v>45716</v>
       </c>
       <c r="O66" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.162704654223363</v>
       </c>
       <c r="P66" s="12" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
     </row>
     <row r="67" spans="2:16">
       <c r="B67" s="12" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D67" s="2">
         <v>2.8</v>
@@ -3567,7 +2527,7 @@
       <c r="E67" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F67" s="13"/>
+      <c r="F67" s="23"/>
       <c r="G67" s="2">
         <v>2.8856224953599261</v>
       </c>
@@ -3581,12 +2541,12 @@
       <c r="L67" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="M67" s="14"/>
+      <c r="M67" s="26"/>
       <c r="N67" s="15">
         <v>45716</v>
       </c>
       <c r="O67" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-2.9672105584707342E-2</v>
       </c>
     </row>
@@ -3595,7 +2555,7 @@
         <v>11</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="D68" s="2">
         <v>132</v>
@@ -3603,7 +2563,7 @@
       <c r="E68" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F68" s="13"/>
+      <c r="F68" s="23"/>
       <c r="G68" s="2">
         <v>0</v>
       </c>
@@ -3617,21 +2577,21 @@
       <c r="L68" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M68" s="14"/>
+      <c r="M68" s="26"/>
       <c r="N68" s="15">
         <v>45716</v>
       </c>
       <c r="O68" s="16" t="str">
-        <f t="shared" ref="O68:O75" si="1">IFERROR(D68/G68-1,"nm")</f>
+        <f t="shared" ref="O68:O75" si="3">IFERROR(D68/G68-1,"nm")</f>
         <v>nm</v>
       </c>
     </row>
     <row r="69" spans="2:16">
       <c r="B69" s="12" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D69" s="2">
         <v>1.41</v>
@@ -3639,7 +2599,7 @@
       <c r="E69" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F69" s="13"/>
+      <c r="F69" s="23"/>
       <c r="G69" s="2">
         <v>1.3522007268709235</v>
       </c>
@@ -3651,14 +2611,14 @@
       </c>
       <c r="K69" s="4"/>
       <c r="L69" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="M69" s="17"/>
+        <v>24</v>
+      </c>
+      <c r="M69" s="26"/>
       <c r="N69" s="15">
         <v>45716</v>
       </c>
       <c r="O69" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.2744595517876682E-2</v>
       </c>
     </row>
@@ -3667,7 +2627,7 @@
         <v>10</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="D70" s="2">
         <v>79.05</v>
@@ -3675,7 +2635,7 @@
       <c r="E70" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F70" s="13"/>
+      <c r="F70" s="23"/>
       <c r="G70" s="2">
         <v>84.367105392034958</v>
       </c>
@@ -3689,21 +2649,21 @@
       <c r="L70" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M70" s="14"/>
+      <c r="M70" s="26"/>
       <c r="N70" s="15">
         <v>45626</v>
       </c>
       <c r="O70" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-6.3023442221083248E-2</v>
       </c>
     </row>
     <row r="71" spans="2:16">
       <c r="B71" s="12" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D71" s="2">
         <v>83.4</v>
@@ -3711,7 +2671,7 @@
       <c r="E71" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F71" s="13"/>
+      <c r="F71" s="23"/>
       <c r="G71" s="2">
         <v>6.4774046315152001</v>
       </c>
@@ -3723,14 +2683,14 @@
       </c>
       <c r="K71" s="4"/>
       <c r="L71" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="M71" s="14"/>
+        <v>22</v>
+      </c>
+      <c r="M71" s="26"/>
       <c r="N71" s="15">
         <v>45716</v>
       </c>
       <c r="O71" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>11.875527274338427</v>
       </c>
     </row>
@@ -3747,7 +2707,7 @@
       <c r="E72" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F72" s="13"/>
+      <c r="F72" s="23"/>
       <c r="G72" s="2">
         <v>4.8608451071750238</v>
       </c>
@@ -3761,21 +2721,21 @@
       <c r="L72" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M72" s="14"/>
+      <c r="M72" s="26"/>
       <c r="N72" s="15">
         <v>45716</v>
       </c>
       <c r="O72" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>43.942802163667864</v>
       </c>
     </row>
     <row r="73" spans="2:16">
       <c r="B73" s="12" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D73" s="2">
         <v>28.78</v>
@@ -3783,7 +2743,7 @@
       <c r="E73" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F73" s="13"/>
+      <c r="F73" s="23"/>
       <c r="G73" s="2">
         <v>17.10038599230516</v>
       </c>
@@ -3795,14 +2755,14 @@
       </c>
       <c r="K73" s="4"/>
       <c r="L73" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="M73" s="14"/>
+        <v>21</v>
+      </c>
+      <c r="M73" s="26"/>
       <c r="N73" s="15">
         <v>45716</v>
       </c>
       <c r="O73" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.68300294583703791</v>
       </c>
     </row>
@@ -3811,7 +2771,7 @@
         <v>15</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="D74" s="2">
         <v>95.98</v>
@@ -3819,7 +2779,7 @@
       <c r="E74" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F74" s="13"/>
+      <c r="F74" s="23"/>
       <c r="G74" s="2">
         <v>43.127964446940894</v>
       </c>
@@ -3833,21 +2793,21 @@
       <c r="L74" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M74" s="14"/>
+      <c r="M74" s="26"/>
       <c r="N74" s="15">
         <v>45716</v>
       </c>
       <c r="O74" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.2254702078063868</v>
       </c>
     </row>
     <row r="75" spans="2:16">
       <c r="B75" s="12" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D75" s="2">
         <v>20.9</v>
@@ -3855,7 +2815,7 @@
       <c r="E75" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F75" s="13"/>
+      <c r="F75" s="23"/>
       <c r="G75" s="2">
         <v>30.597249721884417</v>
       </c>
@@ -3867,14 +2827,14 @@
       </c>
       <c r="K75" s="4"/>
       <c r="L75" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="M75" s="14"/>
+        <v>25</v>
+      </c>
+      <c r="M75" s="26"/>
       <c r="N75" s="15">
         <v>45716</v>
       </c>
       <c r="O75" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-0.31693207102037491</v>
       </c>
     </row>
@@ -3882,2154 +2842,1954 @@
       <c r="B76" s="12"/>
       <c r="C76" s="12"/>
       <c r="E76" s="13"/>
-      <c r="F76" s="13"/>
+      <c r="F76" s="23"/>
       <c r="J76" s="4"/>
       <c r="K76" s="4"/>
       <c r="L76" s="14"/>
-      <c r="M76" s="14"/>
+      <c r="M76" s="26"/>
       <c r="N76" s="15"/>
     </row>
     <row r="77" spans="2:16">
       <c r="B77" s="12"/>
       <c r="C77" s="12"/>
       <c r="E77" s="13"/>
-      <c r="F77" s="13"/>
+      <c r="F77" s="23"/>
       <c r="J77" s="4"/>
       <c r="K77" s="4"/>
       <c r="L77" s="14"/>
-      <c r="M77" s="14"/>
+      <c r="M77" s="26"/>
       <c r="N77" s="15"/>
     </row>
     <row r="78" spans="2:16">
       <c r="B78" s="12"/>
       <c r="C78" s="12"/>
       <c r="E78" s="13"/>
-      <c r="F78" s="13"/>
+      <c r="F78" s="23"/>
       <c r="J78" s="4"/>
       <c r="K78" s="4"/>
       <c r="L78" s="14"/>
-      <c r="M78" s="14"/>
+      <c r="M78" s="26"/>
       <c r="N78" s="15"/>
     </row>
     <row r="79" spans="2:16">
       <c r="B79" s="12"/>
       <c r="C79" s="12"/>
       <c r="E79" s="13"/>
-      <c r="F79" s="13"/>
+      <c r="F79" s="23"/>
       <c r="J79" s="4"/>
       <c r="K79" s="4"/>
       <c r="L79" s="14"/>
-      <c r="M79" s="14"/>
+      <c r="M79" s="26"/>
       <c r="N79" s="15"/>
     </row>
     <row r="80" spans="2:16">
       <c r="B80" s="12"/>
       <c r="C80" s="12"/>
       <c r="E80" s="13"/>
-      <c r="F80" s="13"/>
+      <c r="F80" s="23"/>
       <c r="J80" s="4"/>
       <c r="K80" s="4"/>
       <c r="L80" s="14"/>
-      <c r="M80" s="14"/>
+      <c r="M80" s="26"/>
       <c r="N80" s="15"/>
     </row>
     <row r="81" spans="2:14">
       <c r="B81" s="12"/>
       <c r="C81" s="12"/>
       <c r="E81" s="13"/>
-      <c r="F81" s="13"/>
+      <c r="F81" s="23"/>
       <c r="J81" s="4"/>
       <c r="K81" s="4"/>
       <c r="L81" s="14"/>
-      <c r="M81" s="14"/>
+      <c r="M81" s="26"/>
       <c r="N81" s="15"/>
     </row>
     <row r="82" spans="2:14">
       <c r="B82" s="12"/>
       <c r="C82" s="12"/>
       <c r="E82" s="13"/>
-      <c r="F82" s="13"/>
+      <c r="F82" s="23"/>
       <c r="J82" s="4"/>
       <c r="K82" s="4"/>
       <c r="L82" s="14"/>
-      <c r="M82" s="14"/>
+      <c r="M82" s="26"/>
       <c r="N82" s="15"/>
     </row>
     <row r="83" spans="2:14">
       <c r="B83" s="12"/>
       <c r="C83" s="12"/>
       <c r="E83" s="13"/>
-      <c r="F83" s="13"/>
+      <c r="F83" s="23"/>
       <c r="J83" s="4"/>
       <c r="K83" s="4"/>
       <c r="L83" s="14"/>
-      <c r="M83" s="14"/>
+      <c r="M83" s="26"/>
       <c r="N83" s="15"/>
     </row>
     <row r="84" spans="2:14">
       <c r="B84" s="12"/>
       <c r="C84" s="12"/>
       <c r="E84" s="13"/>
-      <c r="F84" s="13"/>
+      <c r="F84" s="23"/>
       <c r="J84" s="4"/>
       <c r="K84" s="4"/>
       <c r="L84" s="14"/>
-      <c r="M84" s="14"/>
+      <c r="M84" s="26"/>
       <c r="N84" s="15"/>
     </row>
     <row r="85" spans="2:14">
       <c r="B85" s="12"/>
       <c r="C85" s="12"/>
       <c r="E85" s="13"/>
-      <c r="F85" s="13"/>
+      <c r="F85" s="23"/>
       <c r="J85" s="4"/>
       <c r="K85" s="4"/>
       <c r="L85" s="14"/>
-      <c r="M85" s="14"/>
+      <c r="M85" s="26"/>
       <c r="N85" s="15"/>
     </row>
     <row r="86" spans="2:14">
       <c r="B86" s="12"/>
       <c r="C86" s="12"/>
       <c r="E86" s="13"/>
-      <c r="F86" s="13"/>
+      <c r="F86" s="23"/>
       <c r="J86" s="4"/>
       <c r="K86" s="4"/>
       <c r="L86" s="14"/>
-      <c r="M86" s="14"/>
+      <c r="M86" s="26"/>
       <c r="N86" s="15"/>
     </row>
     <row r="87" spans="2:14">
       <c r="B87" s="12"/>
       <c r="C87" s="12"/>
       <c r="E87" s="13"/>
-      <c r="F87" s="13"/>
+      <c r="F87" s="23"/>
       <c r="J87" s="4"/>
       <c r="K87" s="4"/>
       <c r="L87" s="14"/>
-      <c r="M87" s="14"/>
+      <c r="M87" s="26"/>
       <c r="N87" s="15"/>
     </row>
     <row r="88" spans="2:14">
       <c r="B88" s="12"/>
       <c r="C88" s="12"/>
       <c r="E88" s="13"/>
-      <c r="F88" s="13"/>
+      <c r="F88" s="23"/>
       <c r="J88" s="4"/>
       <c r="K88" s="4"/>
       <c r="L88" s="14"/>
-      <c r="M88" s="14"/>
+      <c r="M88" s="26"/>
       <c r="N88" s="15"/>
     </row>
     <row r="89" spans="2:14">
       <c r="B89" s="12"/>
       <c r="C89" s="12"/>
       <c r="E89" s="13"/>
-      <c r="F89" s="13"/>
+      <c r="F89" s="23"/>
       <c r="J89" s="4"/>
       <c r="K89" s="4"/>
       <c r="L89" s="14"/>
-      <c r="M89" s="14"/>
+      <c r="M89" s="26"/>
       <c r="N89" s="15"/>
     </row>
     <row r="90" spans="2:14">
       <c r="B90" s="12"/>
       <c r="C90" s="12"/>
       <c r="E90" s="13"/>
-      <c r="F90" s="13"/>
+      <c r="F90" s="23"/>
       <c r="J90" s="4"/>
       <c r="K90" s="4"/>
       <c r="L90" s="14"/>
-      <c r="M90" s="14"/>
+      <c r="M90" s="26"/>
       <c r="N90" s="15"/>
     </row>
     <row r="91" spans="2:14">
       <c r="B91" s="12"/>
       <c r="C91" s="12"/>
       <c r="E91" s="13"/>
-      <c r="F91" s="13"/>
+      <c r="F91" s="23"/>
       <c r="J91" s="4"/>
       <c r="K91" s="4"/>
       <c r="L91" s="14"/>
-      <c r="M91" s="14"/>
+      <c r="M91" s="26"/>
       <c r="N91" s="15"/>
     </row>
     <row r="92" spans="2:14">
       <c r="B92" s="12"/>
       <c r="C92" s="12"/>
       <c r="E92" s="13"/>
-      <c r="F92" s="13"/>
+      <c r="F92" s="23"/>
       <c r="J92" s="4"/>
       <c r="K92" s="4"/>
       <c r="L92" s="14"/>
-      <c r="M92" s="14"/>
+      <c r="M92" s="26"/>
       <c r="N92" s="15"/>
     </row>
     <row r="93" spans="2:14">
       <c r="B93" s="12"/>
       <c r="C93" s="12"/>
       <c r="E93" s="13"/>
-      <c r="F93" s="13"/>
+      <c r="F93" s="23"/>
       <c r="J93" s="4"/>
       <c r="K93" s="4"/>
       <c r="L93" s="14"/>
-      <c r="M93" s="14"/>
+      <c r="M93" s="26"/>
       <c r="N93" s="15"/>
     </row>
     <row r="94" spans="2:14">
       <c r="B94" s="12"/>
       <c r="C94" s="12"/>
       <c r="E94" s="13"/>
-      <c r="F94" s="13"/>
+      <c r="F94" s="23"/>
       <c r="J94" s="4"/>
       <c r="K94" s="4"/>
       <c r="L94" s="14"/>
-      <c r="M94" s="14"/>
+      <c r="M94" s="26"/>
       <c r="N94" s="15"/>
     </row>
     <row r="95" spans="2:14">
       <c r="B95" s="12"/>
       <c r="C95" s="12"/>
       <c r="E95" s="13"/>
-      <c r="F95" s="13"/>
+      <c r="F95" s="23"/>
       <c r="J95" s="4"/>
       <c r="K95" s="4"/>
       <c r="L95" s="14"/>
-      <c r="M95" s="14"/>
+      <c r="M95" s="26"/>
       <c r="N95" s="15"/>
     </row>
     <row r="96" spans="2:14">
       <c r="B96" s="12"/>
       <c r="C96" s="12"/>
       <c r="E96" s="13"/>
-      <c r="F96" s="13"/>
+      <c r="F96" s="23"/>
       <c r="J96" s="4"/>
       <c r="K96" s="4"/>
       <c r="L96" s="14"/>
-      <c r="M96" s="14"/>
+      <c r="M96" s="26"/>
       <c r="N96" s="15"/>
     </row>
     <row r="97" spans="2:14">
       <c r="B97" s="12"/>
       <c r="C97" s="12"/>
       <c r="E97" s="13"/>
-      <c r="F97" s="13"/>
+      <c r="F97" s="23"/>
       <c r="J97" s="4"/>
       <c r="K97" s="4"/>
       <c r="L97" s="14"/>
-      <c r="M97" s="14"/>
+      <c r="M97" s="26"/>
       <c r="N97" s="15"/>
     </row>
     <row r="98" spans="2:14">
       <c r="B98" s="12"/>
       <c r="C98" s="12"/>
       <c r="E98" s="13"/>
-      <c r="F98" s="13"/>
+      <c r="F98" s="23"/>
       <c r="J98" s="4"/>
       <c r="K98" s="4"/>
       <c r="L98" s="14"/>
-      <c r="M98" s="14"/>
+      <c r="M98" s="26"/>
       <c r="N98" s="15"/>
     </row>
     <row r="99" spans="2:14">
       <c r="B99" s="12"/>
       <c r="C99" s="12"/>
       <c r="E99" s="13"/>
-      <c r="F99" s="13"/>
+      <c r="F99" s="23"/>
       <c r="J99" s="4"/>
       <c r="K99" s="4"/>
       <c r="L99" s="14"/>
-      <c r="M99" s="14"/>
+      <c r="M99" s="26"/>
       <c r="N99" s="15"/>
     </row>
     <row r="100" spans="2:14">
       <c r="B100" s="12"/>
       <c r="C100" s="12"/>
       <c r="E100" s="13"/>
-      <c r="F100" s="13"/>
+      <c r="F100" s="23"/>
       <c r="J100" s="4"/>
       <c r="K100" s="4"/>
       <c r="L100" s="14"/>
-      <c r="M100" s="14"/>
+      <c r="M100" s="26"/>
       <c r="N100" s="15"/>
     </row>
     <row r="101" spans="2:14">
       <c r="B101" s="12"/>
       <c r="C101" s="12"/>
       <c r="E101" s="13"/>
-      <c r="F101" s="13"/>
+      <c r="F101" s="23"/>
       <c r="J101" s="4"/>
       <c r="K101" s="4"/>
       <c r="L101" s="14"/>
-      <c r="M101" s="14"/>
+      <c r="M101" s="26"/>
       <c r="N101" s="15"/>
     </row>
     <row r="102" spans="2:14">
       <c r="B102" s="12"/>
       <c r="C102" s="12"/>
       <c r="E102" s="13"/>
-      <c r="F102" s="13"/>
+      <c r="F102" s="23"/>
       <c r="J102" s="4"/>
       <c r="K102" s="4"/>
       <c r="L102" s="14"/>
-      <c r="M102" s="14"/>
+      <c r="M102" s="26"/>
       <c r="N102" s="15"/>
     </row>
     <row r="103" spans="2:14">
       <c r="B103" s="12"/>
       <c r="C103" s="12"/>
       <c r="E103" s="13"/>
-      <c r="F103" s="13"/>
+      <c r="F103" s="23"/>
       <c r="J103" s="4"/>
       <c r="K103" s="4"/>
       <c r="L103" s="14"/>
-      <c r="M103" s="14"/>
+      <c r="M103" s="26"/>
       <c r="N103" s="15"/>
     </row>
     <row r="104" spans="2:14">
       <c r="B104" s="12"/>
       <c r="C104" s="12"/>
       <c r="E104" s="13"/>
-      <c r="F104" s="13"/>
+      <c r="F104" s="23"/>
       <c r="J104" s="4"/>
       <c r="K104" s="4"/>
       <c r="L104" s="14"/>
-      <c r="M104" s="14"/>
+      <c r="M104" s="26"/>
       <c r="N104" s="15"/>
     </row>
     <row r="105" spans="2:14">
       <c r="B105" s="12"/>
       <c r="C105" s="12"/>
       <c r="E105" s="13"/>
-      <c r="F105" s="13"/>
+      <c r="F105" s="23"/>
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
       <c r="L105" s="14"/>
-      <c r="M105" s="14"/>
+      <c r="M105" s="26"/>
       <c r="N105" s="15"/>
     </row>
     <row r="106" spans="2:14">
       <c r="B106" s="12"/>
       <c r="C106" s="12"/>
       <c r="E106" s="13"/>
-      <c r="F106" s="13"/>
+      <c r="F106" s="23"/>
       <c r="J106" s="4"/>
       <c r="K106" s="4"/>
       <c r="L106" s="14"/>
-      <c r="M106" s="14"/>
+      <c r="M106" s="26"/>
       <c r="N106" s="15"/>
     </row>
     <row r="107" spans="2:14">
       <c r="B107" s="12"/>
       <c r="C107" s="12"/>
       <c r="E107" s="13"/>
-      <c r="F107" s="13"/>
+      <c r="F107" s="23"/>
       <c r="J107" s="4"/>
       <c r="K107" s="4"/>
       <c r="L107" s="14"/>
-      <c r="M107" s="14"/>
+      <c r="M107" s="26"/>
       <c r="N107" s="15"/>
     </row>
     <row r="108" spans="2:14">
       <c r="B108" s="12"/>
       <c r="C108" s="12"/>
       <c r="E108" s="13"/>
-      <c r="F108" s="13"/>
+      <c r="F108" s="23"/>
       <c r="J108" s="4"/>
       <c r="K108" s="4"/>
       <c r="L108" s="14"/>
-      <c r="M108" s="14"/>
+      <c r="M108" s="26"/>
       <c r="N108" s="15"/>
     </row>
     <row r="109" spans="2:14">
       <c r="B109" s="12"/>
       <c r="C109" s="12"/>
       <c r="E109" s="13"/>
-      <c r="F109" s="13"/>
+      <c r="F109" s="23"/>
       <c r="J109" s="4"/>
       <c r="K109" s="4"/>
       <c r="L109" s="14"/>
-      <c r="M109" s="14"/>
+      <c r="M109" s="26"/>
       <c r="N109" s="15"/>
     </row>
     <row r="110" spans="2:14">
       <c r="B110" s="12"/>
       <c r="C110" s="12"/>
       <c r="E110" s="13"/>
-      <c r="F110" s="13"/>
+      <c r="F110" s="23"/>
       <c r="J110" s="4"/>
       <c r="K110" s="4"/>
       <c r="L110" s="14"/>
-      <c r="M110" s="14"/>
+      <c r="M110" s="26"/>
       <c r="N110" s="15"/>
     </row>
     <row r="111" spans="2:14">
       <c r="B111" s="12"/>
       <c r="C111" s="12"/>
       <c r="E111" s="13"/>
-      <c r="F111" s="13"/>
+      <c r="F111" s="23"/>
       <c r="J111" s="4"/>
       <c r="K111" s="4"/>
       <c r="L111" s="14"/>
-      <c r="M111" s="14"/>
+      <c r="M111" s="26"/>
       <c r="N111" s="15"/>
     </row>
     <row r="112" spans="2:14">
       <c r="B112" s="12"/>
       <c r="C112" s="12"/>
       <c r="E112" s="13"/>
-      <c r="F112" s="13"/>
+      <c r="F112" s="23"/>
       <c r="J112" s="4"/>
       <c r="K112" s="4"/>
       <c r="L112" s="14"/>
-      <c r="M112" s="14"/>
+      <c r="M112" s="26"/>
       <c r="N112" s="15"/>
     </row>
     <row r="113" spans="2:14">
       <c r="B113" s="12"/>
       <c r="C113" s="12"/>
       <c r="E113" s="13"/>
-      <c r="F113" s="13"/>
+      <c r="F113" s="23"/>
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
       <c r="L113" s="14"/>
-      <c r="M113" s="14"/>
+      <c r="M113" s="26"/>
       <c r="N113" s="15"/>
     </row>
     <row r="114" spans="2:14">
       <c r="B114" s="12"/>
       <c r="C114" s="12"/>
       <c r="E114" s="13"/>
-      <c r="F114" s="13"/>
+      <c r="F114" s="23"/>
       <c r="J114" s="4"/>
       <c r="K114" s="4"/>
       <c r="L114" s="14"/>
-      <c r="M114" s="14"/>
+      <c r="M114" s="26"/>
       <c r="N114" s="15"/>
     </row>
     <row r="115" spans="2:14">
       <c r="B115" s="12"/>
       <c r="C115" s="12"/>
       <c r="E115" s="13"/>
-      <c r="F115" s="13"/>
+      <c r="F115" s="23"/>
       <c r="J115" s="4"/>
       <c r="K115" s="4"/>
       <c r="L115" s="14"/>
-      <c r="M115" s="14"/>
+      <c r="M115" s="26"/>
       <c r="N115" s="15"/>
     </row>
     <row r="116" spans="2:14">
       <c r="B116" s="12"/>
       <c r="C116" s="12"/>
       <c r="E116" s="13"/>
-      <c r="F116" s="13"/>
+      <c r="F116" s="23"/>
       <c r="J116" s="4"/>
       <c r="K116" s="4"/>
       <c r="L116" s="14"/>
-      <c r="M116" s="14"/>
+      <c r="M116" s="26"/>
       <c r="N116" s="15"/>
     </row>
     <row r="117" spans="2:14">
       <c r="B117" s="12"/>
       <c r="C117" s="12"/>
       <c r="E117" s="13"/>
-      <c r="F117" s="13"/>
+      <c r="F117" s="23"/>
       <c r="J117" s="4"/>
       <c r="K117" s="4"/>
       <c r="L117" s="14"/>
-      <c r="M117" s="14"/>
+      <c r="M117" s="26"/>
       <c r="N117" s="15"/>
     </row>
     <row r="118" spans="2:14">
       <c r="B118" s="12"/>
       <c r="C118" s="12"/>
       <c r="E118" s="13"/>
-      <c r="F118" s="13"/>
+      <c r="F118" s="23"/>
       <c r="J118" s="4"/>
       <c r="K118" s="4"/>
       <c r="L118" s="14"/>
-      <c r="M118" s="14"/>
+      <c r="M118" s="26"/>
       <c r="N118" s="15"/>
     </row>
     <row r="119" spans="2:14">
       <c r="B119" s="12"/>
       <c r="C119" s="12"/>
       <c r="E119" s="13"/>
-      <c r="F119" s="13"/>
+      <c r="F119" s="23"/>
       <c r="J119" s="4"/>
       <c r="K119" s="4"/>
       <c r="L119" s="14"/>
-      <c r="M119" s="14"/>
+      <c r="M119" s="26"/>
       <c r="N119" s="15"/>
     </row>
     <row r="120" spans="2:14">
       <c r="B120" s="12"/>
       <c r="C120" s="12"/>
       <c r="E120" s="13"/>
-      <c r="F120" s="13"/>
+      <c r="F120" s="23"/>
       <c r="J120" s="4"/>
       <c r="K120" s="4"/>
       <c r="L120" s="14"/>
-      <c r="M120" s="14"/>
+      <c r="M120" s="26"/>
       <c r="N120" s="15"/>
     </row>
     <row r="121" spans="2:14">
       <c r="B121" s="12"/>
       <c r="C121" s="12"/>
       <c r="E121" s="13"/>
-      <c r="F121" s="13"/>
+      <c r="F121" s="23"/>
       <c r="J121" s="4"/>
       <c r="K121" s="4"/>
       <c r="L121" s="14"/>
-      <c r="M121" s="14"/>
+      <c r="M121" s="26"/>
       <c r="N121" s="15"/>
     </row>
     <row r="122" spans="2:14">
       <c r="B122" s="12"/>
       <c r="C122" s="12"/>
       <c r="E122" s="13"/>
-      <c r="F122" s="13"/>
+      <c r="F122" s="23"/>
       <c r="J122" s="4"/>
       <c r="K122" s="4"/>
       <c r="L122" s="14"/>
-      <c r="M122" s="14"/>
+      <c r="M122" s="26"/>
       <c r="N122" s="15"/>
     </row>
     <row r="123" spans="2:14">
       <c r="B123" s="12"/>
       <c r="C123" s="12"/>
       <c r="E123" s="13"/>
-      <c r="F123" s="13"/>
+      <c r="F123" s="23"/>
       <c r="J123" s="4"/>
       <c r="K123" s="4"/>
       <c r="L123" s="14"/>
-      <c r="M123" s="14"/>
+      <c r="M123" s="26"/>
       <c r="N123" s="15"/>
     </row>
     <row r="124" spans="2:14">
       <c r="B124" s="12"/>
       <c r="C124" s="12"/>
       <c r="E124" s="13"/>
-      <c r="F124" s="13"/>
+      <c r="F124" s="23"/>
       <c r="J124" s="4"/>
       <c r="K124" s="4"/>
       <c r="L124" s="14"/>
-      <c r="M124" s="14"/>
+      <c r="M124" s="26"/>
       <c r="N124" s="15"/>
     </row>
     <row r="125" spans="2:14">
       <c r="B125" s="12"/>
       <c r="C125" s="12"/>
       <c r="E125" s="13"/>
-      <c r="F125" s="13"/>
+      <c r="F125" s="23"/>
       <c r="J125" s="4"/>
       <c r="K125" s="4"/>
       <c r="L125" s="14"/>
-      <c r="M125" s="14"/>
+      <c r="M125" s="26"/>
       <c r="N125" s="15"/>
     </row>
     <row r="126" spans="2:14">
       <c r="B126" s="12"/>
       <c r="C126" s="12"/>
       <c r="E126" s="13"/>
-      <c r="F126" s="13"/>
+      <c r="F126" s="23"/>
       <c r="J126" s="4"/>
       <c r="K126" s="4"/>
       <c r="L126" s="14"/>
-      <c r="M126" s="14"/>
+      <c r="M126" s="26"/>
       <c r="N126" s="15"/>
     </row>
     <row r="127" spans="2:14">
       <c r="B127" s="12"/>
       <c r="C127" s="12"/>
       <c r="E127" s="13"/>
-      <c r="F127" s="13"/>
+      <c r="F127" s="23"/>
       <c r="J127" s="4"/>
       <c r="K127" s="4"/>
       <c r="L127" s="14"/>
-      <c r="M127" s="14"/>
+      <c r="M127" s="26"/>
       <c r="N127" s="15"/>
     </row>
     <row r="128" spans="2:14">
       <c r="B128" s="12"/>
       <c r="C128" s="12"/>
       <c r="E128" s="13"/>
-      <c r="F128" s="13"/>
+      <c r="F128" s="23"/>
       <c r="J128" s="4"/>
       <c r="K128" s="4"/>
       <c r="L128" s="14"/>
-      <c r="M128" s="14"/>
+      <c r="M128" s="26"/>
       <c r="N128" s="15"/>
     </row>
     <row r="129" spans="2:14">
       <c r="B129" s="12"/>
       <c r="C129" s="12"/>
       <c r="E129" s="13"/>
-      <c r="F129" s="13"/>
+      <c r="F129" s="23"/>
       <c r="J129" s="4"/>
       <c r="K129" s="4"/>
       <c r="L129" s="14"/>
-      <c r="M129" s="14"/>
+      <c r="M129" s="26"/>
       <c r="N129" s="15"/>
     </row>
     <row r="130" spans="2:14">
       <c r="B130" s="12"/>
       <c r="C130" s="12"/>
       <c r="E130" s="13"/>
-      <c r="F130" s="13"/>
+      <c r="F130" s="23"/>
       <c r="J130" s="4"/>
       <c r="K130" s="4"/>
       <c r="L130" s="14"/>
-      <c r="M130" s="14"/>
+      <c r="M130" s="26"/>
       <c r="N130" s="15"/>
     </row>
     <row r="131" spans="2:14">
       <c r="B131" s="12"/>
       <c r="C131" s="12"/>
       <c r="E131" s="13"/>
-      <c r="F131" s="13"/>
+      <c r="F131" s="23"/>
       <c r="J131" s="4"/>
       <c r="K131" s="4"/>
       <c r="L131" s="14"/>
-      <c r="M131" s="14"/>
+      <c r="M131" s="26"/>
       <c r="N131" s="15"/>
     </row>
     <row r="132" spans="2:14">
       <c r="B132" s="12"/>
       <c r="C132" s="12"/>
       <c r="E132" s="13"/>
-      <c r="F132" s="13"/>
+      <c r="F132" s="23"/>
       <c r="J132" s="4"/>
       <c r="K132" s="4"/>
       <c r="L132" s="14"/>
-      <c r="M132" s="14"/>
+      <c r="M132" s="26"/>
       <c r="N132" s="15"/>
     </row>
     <row r="133" spans="2:14">
       <c r="B133" s="12"/>
       <c r="C133" s="12"/>
       <c r="E133" s="13"/>
-      <c r="F133" s="13"/>
+      <c r="F133" s="23"/>
       <c r="J133" s="4"/>
       <c r="K133" s="4"/>
       <c r="L133" s="14"/>
-      <c r="M133" s="14"/>
+      <c r="M133" s="26"/>
       <c r="N133" s="15"/>
     </row>
     <row r="134" spans="2:14">
       <c r="B134" s="12"/>
       <c r="C134" s="12"/>
       <c r="E134" s="13"/>
-      <c r="F134" s="13"/>
+      <c r="F134" s="23"/>
       <c r="J134" s="4"/>
       <c r="K134" s="4"/>
       <c r="L134" s="14"/>
-      <c r="M134" s="14"/>
+      <c r="M134" s="26"/>
       <c r="N134" s="15"/>
     </row>
     <row r="135" spans="2:14">
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
       <c r="E135" s="13"/>
-      <c r="F135" s="13"/>
+      <c r="F135" s="23"/>
       <c r="J135" s="4"/>
       <c r="K135" s="4"/>
       <c r="L135" s="14"/>
-      <c r="M135" s="14"/>
+      <c r="M135" s="26"/>
       <c r="N135" s="15"/>
     </row>
     <row r="136" spans="2:14">
       <c r="B136" s="12"/>
       <c r="C136" s="12"/>
       <c r="E136" s="13"/>
-      <c r="F136" s="13"/>
+      <c r="F136" s="23"/>
       <c r="J136" s="4"/>
       <c r="K136" s="4"/>
       <c r="L136" s="14"/>
-      <c r="M136" s="14"/>
+      <c r="M136" s="26"/>
       <c r="N136" s="15"/>
     </row>
     <row r="137" spans="2:14">
       <c r="B137" s="12"/>
       <c r="C137" s="12"/>
       <c r="E137" s="13"/>
-      <c r="F137" s="13"/>
+      <c r="F137" s="23"/>
       <c r="J137" s="4"/>
       <c r="K137" s="4"/>
       <c r="L137" s="14"/>
-      <c r="M137" s="14"/>
+      <c r="M137" s="26"/>
       <c r="N137" s="15"/>
     </row>
     <row r="138" spans="2:14">
       <c r="B138" s="12"/>
       <c r="C138" s="12"/>
       <c r="E138" s="13"/>
-      <c r="F138" s="13"/>
+      <c r="F138" s="23"/>
       <c r="J138" s="4"/>
       <c r="K138" s="4"/>
       <c r="L138" s="14"/>
-      <c r="M138" s="14"/>
+      <c r="M138" s="26"/>
       <c r="N138" s="15"/>
     </row>
     <row r="139" spans="2:14">
       <c r="B139" s="12"/>
       <c r="C139" s="12"/>
       <c r="E139" s="13"/>
-      <c r="F139" s="13"/>
+      <c r="F139" s="23"/>
       <c r="J139" s="4"/>
       <c r="K139" s="4"/>
       <c r="L139" s="14"/>
-      <c r="M139" s="14"/>
+      <c r="M139" s="26"/>
       <c r="N139" s="15"/>
     </row>
     <row r="140" spans="2:14">
       <c r="B140" s="12"/>
       <c r="C140" s="12"/>
       <c r="E140" s="13"/>
-      <c r="F140" s="13"/>
+      <c r="F140" s="23"/>
       <c r="J140" s="4"/>
       <c r="K140" s="4"/>
       <c r="L140" s="14"/>
-      <c r="M140" s="14"/>
+      <c r="M140" s="26"/>
       <c r="N140" s="15"/>
     </row>
     <row r="141" spans="2:14">
       <c r="B141" s="12"/>
       <c r="C141" s="12"/>
       <c r="E141" s="13"/>
-      <c r="F141" s="13"/>
+      <c r="F141" s="23"/>
       <c r="J141" s="4"/>
       <c r="K141" s="4"/>
       <c r="L141" s="14"/>
-      <c r="M141" s="14"/>
+      <c r="M141" s="26"/>
       <c r="N141" s="15"/>
     </row>
     <row r="142" spans="2:14">
       <c r="B142" s="12"/>
       <c r="C142" s="12"/>
       <c r="E142" s="13"/>
-      <c r="F142" s="13"/>
+      <c r="F142" s="23"/>
       <c r="J142" s="4"/>
       <c r="K142" s="4"/>
       <c r="L142" s="14"/>
-      <c r="M142" s="14"/>
+      <c r="M142" s="26"/>
       <c r="N142" s="15"/>
     </row>
     <row r="143" spans="2:14">
       <c r="B143" s="12"/>
       <c r="C143" s="12"/>
       <c r="E143" s="13"/>
-      <c r="F143" s="13"/>
+      <c r="F143" s="23"/>
       <c r="J143" s="4"/>
       <c r="K143" s="4"/>
       <c r="L143" s="14"/>
-      <c r="M143" s="14"/>
+      <c r="M143" s="26"/>
       <c r="N143" s="15"/>
     </row>
     <row r="144" spans="2:14">
       <c r="B144" s="12"/>
       <c r="C144" s="12"/>
       <c r="E144" s="13"/>
-      <c r="F144" s="13"/>
+      <c r="F144" s="23"/>
       <c r="J144" s="4"/>
       <c r="K144" s="4"/>
       <c r="L144" s="14"/>
-      <c r="M144" s="14"/>
+      <c r="M144" s="26"/>
       <c r="N144" s="15"/>
     </row>
     <row r="145" spans="2:14">
       <c r="B145" s="12"/>
       <c r="C145" s="12"/>
       <c r="E145" s="13"/>
-      <c r="F145" s="13"/>
+      <c r="F145" s="23"/>
       <c r="J145" s="4"/>
       <c r="K145" s="4"/>
       <c r="L145" s="14"/>
-      <c r="M145" s="14"/>
+      <c r="M145" s="26"/>
       <c r="N145" s="15"/>
     </row>
     <row r="146" spans="2:14">
       <c r="B146" s="12"/>
       <c r="C146" s="12"/>
       <c r="E146" s="13"/>
-      <c r="F146" s="13"/>
+      <c r="F146" s="23"/>
       <c r="J146" s="4"/>
       <c r="K146" s="4"/>
       <c r="L146" s="14"/>
-      <c r="M146" s="14"/>
+      <c r="M146" s="26"/>
       <c r="N146" s="15"/>
     </row>
     <row r="147" spans="2:14">
       <c r="B147" s="12"/>
       <c r="C147" s="12"/>
       <c r="E147" s="13"/>
-      <c r="F147" s="13"/>
+      <c r="F147" s="23"/>
       <c r="J147" s="4"/>
       <c r="K147" s="4"/>
       <c r="L147" s="14"/>
-      <c r="M147" s="14"/>
+      <c r="M147" s="26"/>
       <c r="N147" s="15"/>
     </row>
     <row r="148" spans="2:14">
       <c r="B148" s="12"/>
       <c r="C148" s="12"/>
       <c r="E148" s="13"/>
-      <c r="F148" s="13"/>
+      <c r="F148" s="23"/>
       <c r="J148" s="4"/>
       <c r="K148" s="4"/>
       <c r="L148" s="14"/>
-      <c r="M148" s="14"/>
+      <c r="M148" s="26"/>
       <c r="N148" s="15"/>
     </row>
     <row r="149" spans="2:14">
       <c r="B149" s="12"/>
       <c r="C149" s="12"/>
       <c r="E149" s="13"/>
-      <c r="F149" s="13"/>
+      <c r="F149" s="23"/>
       <c r="J149" s="4"/>
       <c r="K149" s="4"/>
       <c r="L149" s="14"/>
-      <c r="M149" s="14"/>
+      <c r="M149" s="26"/>
       <c r="N149" s="15"/>
     </row>
     <row r="150" spans="2:14">
       <c r="B150" s="12"/>
       <c r="C150" s="12"/>
       <c r="E150" s="13"/>
-      <c r="F150" s="13"/>
+      <c r="F150" s="23"/>
       <c r="J150" s="4"/>
       <c r="K150" s="4"/>
       <c r="L150" s="14"/>
-      <c r="M150" s="14"/>
+      <c r="M150" s="26"/>
       <c r="N150" s="15"/>
     </row>
     <row r="151" spans="2:14">
       <c r="B151" s="12"/>
       <c r="C151" s="12"/>
       <c r="E151" s="13"/>
-      <c r="F151" s="13"/>
+      <c r="F151" s="23"/>
       <c r="J151" s="4"/>
       <c r="K151" s="4"/>
       <c r="L151" s="14"/>
-      <c r="M151" s="14"/>
+      <c r="M151" s="26"/>
       <c r="N151" s="15"/>
     </row>
     <row r="152" spans="2:14">
       <c r="B152" s="12"/>
       <c r="C152" s="12"/>
       <c r="E152" s="13"/>
-      <c r="F152" s="13"/>
+      <c r="F152" s="23"/>
       <c r="J152" s="4"/>
       <c r="K152" s="4"/>
       <c r="L152" s="14"/>
-      <c r="M152" s="14"/>
+      <c r="M152" s="26"/>
       <c r="N152" s="15"/>
     </row>
     <row r="153" spans="2:14">
       <c r="B153" s="12"/>
       <c r="C153" s="12"/>
       <c r="E153" s="13"/>
-      <c r="F153" s="13"/>
+      <c r="F153" s="23"/>
       <c r="J153" s="4"/>
       <c r="K153" s="4"/>
       <c r="L153" s="14"/>
-      <c r="M153" s="14"/>
+      <c r="M153" s="26"/>
       <c r="N153" s="15"/>
     </row>
     <row r="154" spans="2:14">
       <c r="B154" s="12"/>
       <c r="C154" s="12"/>
       <c r="E154" s="13"/>
-      <c r="F154" s="13"/>
+      <c r="F154" s="23"/>
       <c r="J154" s="4"/>
       <c r="K154" s="4"/>
       <c r="L154" s="14"/>
-      <c r="M154" s="14"/>
+      <c r="M154" s="26"/>
       <c r="N154" s="15"/>
     </row>
     <row r="155" spans="2:14">
       <c r="B155" s="12"/>
       <c r="C155" s="12"/>
       <c r="E155" s="13"/>
-      <c r="F155" s="13"/>
+      <c r="F155" s="23"/>
       <c r="J155" s="4"/>
       <c r="K155" s="4"/>
       <c r="L155" s="14"/>
-      <c r="M155" s="14"/>
+      <c r="M155" s="26"/>
       <c r="N155" s="15"/>
     </row>
     <row r="156" spans="2:14">
       <c r="B156" s="12"/>
       <c r="C156" s="12"/>
       <c r="E156" s="13"/>
-      <c r="F156" s="13"/>
+      <c r="F156" s="23"/>
       <c r="J156" s="4"/>
       <c r="K156" s="4"/>
       <c r="L156" s="14"/>
-      <c r="M156" s="14"/>
+      <c r="M156" s="26"/>
       <c r="N156" s="15"/>
     </row>
     <row r="157" spans="2:14">
       <c r="B157" s="12"/>
       <c r="C157" s="12"/>
       <c r="E157" s="13"/>
-      <c r="F157" s="13"/>
+      <c r="F157" s="23"/>
       <c r="J157" s="4"/>
       <c r="K157" s="4"/>
       <c r="L157" s="14"/>
-      <c r="M157" s="14"/>
+      <c r="M157" s="26"/>
       <c r="N157" s="15"/>
     </row>
     <row r="158" spans="2:14">
       <c r="B158" s="12"/>
       <c r="C158" s="12"/>
       <c r="E158" s="13"/>
-      <c r="F158" s="13"/>
+      <c r="F158" s="23"/>
       <c r="J158" s="4"/>
       <c r="K158" s="4"/>
       <c r="L158" s="14"/>
-      <c r="M158" s="14"/>
+      <c r="M158" s="26"/>
       <c r="N158" s="15"/>
     </row>
     <row r="159" spans="2:14">
       <c r="B159" s="12"/>
       <c r="C159" s="12"/>
       <c r="E159" s="13"/>
-      <c r="F159" s="13"/>
+      <c r="F159" s="23"/>
       <c r="J159" s="4"/>
       <c r="K159" s="4"/>
       <c r="L159" s="14"/>
-      <c r="M159" s="14"/>
+      <c r="M159" s="26"/>
       <c r="N159" s="15"/>
     </row>
     <row r="160" spans="2:14">
       <c r="B160" s="12"/>
       <c r="C160" s="12"/>
       <c r="E160" s="13"/>
-      <c r="F160" s="13"/>
+      <c r="F160" s="23"/>
       <c r="J160" s="4"/>
       <c r="K160" s="4"/>
       <c r="L160" s="14"/>
-      <c r="M160" s="14"/>
+      <c r="M160" s="26"/>
       <c r="N160" s="15"/>
     </row>
     <row r="161" spans="2:14">
       <c r="B161" s="12"/>
       <c r="C161" s="12"/>
       <c r="E161" s="13"/>
-      <c r="F161" s="13"/>
+      <c r="F161" s="23"/>
       <c r="J161" s="4"/>
       <c r="K161" s="4"/>
       <c r="L161" s="14"/>
-      <c r="M161" s="14"/>
+      <c r="M161" s="26"/>
       <c r="N161" s="15"/>
     </row>
     <row r="162" spans="2:14">
       <c r="B162" s="12"/>
       <c r="C162" s="12"/>
       <c r="E162" s="13"/>
-      <c r="F162" s="13"/>
+      <c r="F162" s="23"/>
       <c r="J162" s="4"/>
       <c r="K162" s="4"/>
       <c r="L162" s="14"/>
-      <c r="M162" s="14"/>
+      <c r="M162" s="26"/>
       <c r="N162" s="15"/>
     </row>
     <row r="163" spans="2:14">
       <c r="B163" s="12"/>
       <c r="C163" s="12"/>
       <c r="E163" s="13"/>
-      <c r="F163" s="13"/>
+      <c r="F163" s="23"/>
       <c r="J163" s="4"/>
       <c r="K163" s="4"/>
       <c r="L163" s="14"/>
-      <c r="M163" s="14"/>
+      <c r="M163" s="26"/>
       <c r="N163" s="15"/>
     </row>
     <row r="164" spans="2:14">
       <c r="B164" s="12"/>
       <c r="C164" s="12"/>
       <c r="E164" s="13"/>
-      <c r="F164" s="13"/>
+      <c r="F164" s="23"/>
       <c r="J164" s="4"/>
       <c r="K164" s="4"/>
       <c r="L164" s="14"/>
-      <c r="M164" s="14"/>
+      <c r="M164" s="26"/>
       <c r="N164" s="15"/>
     </row>
     <row r="165" spans="2:14">
       <c r="B165" s="12"/>
       <c r="C165" s="12"/>
       <c r="E165" s="13"/>
-      <c r="F165" s="13"/>
+      <c r="F165" s="23"/>
       <c r="J165" s="4"/>
       <c r="K165" s="4"/>
       <c r="L165" s="14"/>
-      <c r="M165" s="14"/>
+      <c r="M165" s="26"/>
       <c r="N165" s="15"/>
     </row>
     <row r="166" spans="2:14">
       <c r="B166" s="12"/>
       <c r="C166" s="12"/>
       <c r="E166" s="13"/>
-      <c r="F166" s="13"/>
+      <c r="F166" s="23"/>
       <c r="J166" s="4"/>
       <c r="K166" s="4"/>
       <c r="L166" s="14"/>
-      <c r="M166" s="14"/>
+      <c r="M166" s="26"/>
       <c r="N166" s="15"/>
     </row>
     <row r="167" spans="2:14">
       <c r="B167" s="12"/>
       <c r="C167" s="12"/>
       <c r="E167" s="13"/>
-      <c r="F167" s="13"/>
+      <c r="F167" s="23"/>
       <c r="J167" s="4"/>
       <c r="K167" s="4"/>
       <c r="L167" s="14"/>
-      <c r="M167" s="14"/>
+      <c r="M167" s="26"/>
       <c r="N167" s="15"/>
     </row>
     <row r="168" spans="2:14">
       <c r="B168" s="12"/>
       <c r="C168" s="12"/>
       <c r="E168" s="13"/>
-      <c r="F168" s="13"/>
+      <c r="F168" s="23"/>
       <c r="J168" s="4"/>
       <c r="K168" s="4"/>
       <c r="L168" s="14"/>
-      <c r="M168" s="14"/>
+      <c r="M168" s="26"/>
       <c r="N168" s="15"/>
     </row>
     <row r="169" spans="2:14">
       <c r="B169" s="12"/>
       <c r="C169" s="12"/>
       <c r="E169" s="13"/>
-      <c r="F169" s="13"/>
+      <c r="F169" s="23"/>
       <c r="J169" s="4"/>
       <c r="K169" s="4"/>
       <c r="L169" s="14"/>
-      <c r="M169" s="14"/>
+      <c r="M169" s="26"/>
       <c r="N169" s="15"/>
     </row>
     <row r="170" spans="2:14">
       <c r="B170" s="12"/>
       <c r="C170" s="12"/>
       <c r="E170" s="13"/>
-      <c r="F170" s="13"/>
+      <c r="F170" s="23"/>
       <c r="J170" s="4"/>
       <c r="K170" s="4"/>
       <c r="L170" s="14"/>
-      <c r="M170" s="14"/>
+      <c r="M170" s="26"/>
       <c r="N170" s="15"/>
     </row>
     <row r="171" spans="2:14">
       <c r="B171" s="12"/>
       <c r="C171" s="12"/>
       <c r="E171" s="13"/>
-      <c r="F171" s="13"/>
+      <c r="F171" s="23"/>
       <c r="J171" s="4"/>
       <c r="K171" s="4"/>
       <c r="L171" s="14"/>
-      <c r="M171" s="14"/>
+      <c r="M171" s="26"/>
       <c r="N171" s="15"/>
     </row>
     <row r="172" spans="2:14">
       <c r="B172" s="12"/>
       <c r="C172" s="12"/>
       <c r="E172" s="13"/>
-      <c r="F172" s="13"/>
+      <c r="F172" s="23"/>
       <c r="J172" s="4"/>
       <c r="K172" s="4"/>
       <c r="L172" s="14"/>
-      <c r="M172" s="14"/>
+      <c r="M172" s="26"/>
       <c r="N172" s="15"/>
     </row>
     <row r="173" spans="2:14">
       <c r="B173" s="12"/>
       <c r="C173" s="12"/>
       <c r="E173" s="13"/>
-      <c r="F173" s="13"/>
+      <c r="F173" s="23"/>
       <c r="J173" s="4"/>
       <c r="K173" s="4"/>
       <c r="L173" s="14"/>
-      <c r="M173" s="14"/>
+      <c r="M173" s="26"/>
       <c r="N173" s="15"/>
     </row>
     <row r="174" spans="2:14">
       <c r="B174" s="12"/>
       <c r="C174" s="12"/>
       <c r="E174" s="13"/>
-      <c r="F174" s="13"/>
+      <c r="F174" s="23"/>
       <c r="J174" s="4"/>
       <c r="K174" s="4"/>
       <c r="L174" s="14"/>
-      <c r="M174" s="14"/>
+      <c r="M174" s="26"/>
       <c r="N174" s="15"/>
     </row>
     <row r="175" spans="2:14">
       <c r="B175" s="12"/>
       <c r="C175" s="12"/>
       <c r="E175" s="13"/>
-      <c r="F175" s="13"/>
+      <c r="F175" s="23"/>
       <c r="J175" s="4"/>
       <c r="K175" s="4"/>
       <c r="L175" s="14"/>
-      <c r="M175" s="14"/>
+      <c r="M175" s="26"/>
       <c r="N175" s="15"/>
     </row>
     <row r="176" spans="2:14">
       <c r="B176" s="12"/>
       <c r="C176" s="12"/>
       <c r="E176" s="13"/>
-      <c r="F176" s="13"/>
+      <c r="F176" s="23"/>
       <c r="J176" s="4"/>
       <c r="K176" s="4"/>
       <c r="L176" s="14"/>
-      <c r="M176" s="14"/>
+      <c r="M176" s="26"/>
       <c r="N176" s="15"/>
     </row>
     <row r="177" spans="2:14">
       <c r="B177" s="12"/>
       <c r="C177" s="12"/>
       <c r="E177" s="13"/>
-      <c r="F177" s="13"/>
+      <c r="F177" s="23"/>
       <c r="J177" s="4"/>
       <c r="K177" s="4"/>
       <c r="L177" s="14"/>
-      <c r="M177" s="14"/>
+      <c r="M177" s="26"/>
       <c r="N177" s="15"/>
     </row>
     <row r="178" spans="2:14">
       <c r="B178" s="12"/>
       <c r="C178" s="12"/>
       <c r="E178" s="13"/>
-      <c r="F178" s="13"/>
+      <c r="F178" s="23"/>
       <c r="J178" s="4"/>
       <c r="K178" s="4"/>
       <c r="L178" s="14"/>
-      <c r="M178" s="14"/>
+      <c r="M178" s="26"/>
       <c r="N178" s="15"/>
     </row>
     <row r="179" spans="2:14">
       <c r="B179" s="12"/>
       <c r="C179" s="12"/>
       <c r="E179" s="13"/>
-      <c r="F179" s="13"/>
+      <c r="F179" s="23"/>
       <c r="J179" s="4"/>
       <c r="K179" s="4"/>
       <c r="L179" s="14"/>
-      <c r="M179" s="14"/>
+      <c r="M179" s="26"/>
       <c r="N179" s="15"/>
     </row>
     <row r="180" spans="2:14">
       <c r="B180" s="12"/>
       <c r="C180" s="12"/>
       <c r="E180" s="13"/>
-      <c r="F180" s="13"/>
+      <c r="F180" s="23"/>
       <c r="J180" s="4"/>
       <c r="K180" s="4"/>
       <c r="L180" s="14"/>
-      <c r="M180" s="14"/>
+      <c r="M180" s="26"/>
       <c r="N180" s="15"/>
     </row>
     <row r="181" spans="2:14">
       <c r="B181" s="12"/>
       <c r="C181" s="12"/>
       <c r="E181" s="13"/>
-      <c r="F181" s="13"/>
+      <c r="F181" s="23"/>
       <c r="J181" s="4"/>
       <c r="K181" s="4"/>
       <c r="L181" s="14"/>
-      <c r="M181" s="14"/>
+      <c r="M181" s="26"/>
       <c r="N181" s="15"/>
     </row>
     <row r="182" spans="2:14">
       <c r="B182" s="12"/>
       <c r="C182" s="12"/>
       <c r="E182" s="13"/>
-      <c r="F182" s="13"/>
+      <c r="F182" s="23"/>
       <c r="J182" s="4"/>
       <c r="K182" s="4"/>
       <c r="L182" s="14"/>
-      <c r="M182" s="14"/>
+      <c r="M182" s="26"/>
       <c r="N182" s="15"/>
     </row>
     <row r="183" spans="2:14">
       <c r="B183" s="12"/>
       <c r="C183" s="12"/>
       <c r="E183" s="13"/>
-      <c r="F183" s="13"/>
+      <c r="F183" s="23"/>
       <c r="J183" s="4"/>
       <c r="K183" s="4"/>
       <c r="L183" s="14"/>
-      <c r="M183" s="14"/>
+      <c r="M183" s="26"/>
       <c r="N183" s="15"/>
     </row>
     <row r="184" spans="2:14">
       <c r="B184" s="12"/>
       <c r="C184" s="12"/>
       <c r="E184" s="13"/>
-      <c r="F184" s="13"/>
+      <c r="F184" s="23"/>
       <c r="J184" s="4"/>
       <c r="K184" s="4"/>
       <c r="L184" s="14"/>
-      <c r="M184" s="14"/>
+      <c r="M184" s="26"/>
       <c r="N184" s="15"/>
     </row>
     <row r="185" spans="2:14">
       <c r="B185" s="12"/>
       <c r="C185" s="12"/>
       <c r="E185" s="13"/>
-      <c r="F185" s="13"/>
+      <c r="F185" s="23"/>
       <c r="J185" s="4"/>
       <c r="K185" s="4"/>
       <c r="L185" s="14"/>
-      <c r="M185" s="14"/>
+      <c r="M185" s="26"/>
       <c r="N185" s="15"/>
     </row>
     <row r="186" spans="2:14">
       <c r="B186" s="12"/>
       <c r="C186" s="12"/>
       <c r="E186" s="13"/>
-      <c r="F186" s="13"/>
+      <c r="F186" s="23"/>
       <c r="J186" s="4"/>
       <c r="K186" s="4"/>
       <c r="L186" s="14"/>
-      <c r="M186" s="14"/>
+      <c r="M186" s="26"/>
       <c r="N186" s="15"/>
     </row>
     <row r="187" spans="2:14">
       <c r="B187" s="12"/>
       <c r="C187" s="12"/>
       <c r="E187" s="13"/>
-      <c r="F187" s="13"/>
+      <c r="F187" s="23"/>
       <c r="J187" s="4"/>
       <c r="K187" s="4"/>
       <c r="L187" s="14"/>
-      <c r="M187" s="14"/>
+      <c r="M187" s="26"/>
       <c r="N187" s="15"/>
     </row>
     <row r="188" spans="2:14">
       <c r="B188" s="12"/>
       <c r="C188" s="12"/>
       <c r="E188" s="13"/>
-      <c r="F188" s="13"/>
+      <c r="F188" s="23"/>
       <c r="J188" s="4"/>
       <c r="K188" s="4"/>
       <c r="L188" s="14"/>
-      <c r="M188" s="14"/>
+      <c r="M188" s="26"/>
       <c r="N188" s="15"/>
     </row>
     <row r="189" spans="2:14">
       <c r="B189" s="12"/>
       <c r="C189" s="12"/>
       <c r="E189" s="13"/>
-      <c r="F189" s="13"/>
+      <c r="F189" s="23"/>
       <c r="J189" s="4"/>
       <c r="K189" s="4"/>
       <c r="L189" s="14"/>
-      <c r="M189" s="14"/>
+      <c r="M189" s="26"/>
       <c r="N189" s="15"/>
     </row>
     <row r="190" spans="2:14">
       <c r="B190" s="12"/>
       <c r="C190" s="12"/>
       <c r="E190" s="13"/>
-      <c r="F190" s="13"/>
+      <c r="F190" s="23"/>
       <c r="J190" s="4"/>
       <c r="K190" s="4"/>
       <c r="L190" s="14"/>
-      <c r="M190" s="14"/>
+      <c r="M190" s="26"/>
       <c r="N190" s="15"/>
     </row>
     <row r="191" spans="2:14">
       <c r="B191" s="12"/>
       <c r="C191" s="12"/>
       <c r="E191" s="13"/>
-      <c r="F191" s="13"/>
+      <c r="F191" s="23"/>
       <c r="J191" s="4"/>
       <c r="K191" s="4"/>
       <c r="L191" s="14"/>
-      <c r="M191" s="14"/>
+      <c r="M191" s="26"/>
       <c r="N191" s="15"/>
     </row>
     <row r="192" spans="2:14">
       <c r="B192" s="12"/>
       <c r="C192" s="12"/>
       <c r="E192" s="13"/>
-      <c r="F192" s="13"/>
+      <c r="F192" s="23"/>
       <c r="J192" s="4"/>
       <c r="K192" s="4"/>
       <c r="L192" s="14"/>
-      <c r="M192" s="14"/>
+      <c r="M192" s="26"/>
       <c r="N192" s="15"/>
     </row>
     <row r="193" spans="2:14">
       <c r="B193" s="12"/>
       <c r="C193" s="12"/>
       <c r="E193" s="13"/>
-      <c r="F193" s="13"/>
+      <c r="F193" s="23"/>
       <c r="J193" s="4"/>
       <c r="K193" s="4"/>
       <c r="L193" s="14"/>
-      <c r="M193" s="14"/>
+      <c r="M193" s="26"/>
       <c r="N193" s="15"/>
     </row>
     <row r="194" spans="2:14">
       <c r="B194" s="12"/>
       <c r="C194" s="12"/>
       <c r="E194" s="13"/>
-      <c r="F194" s="13"/>
+      <c r="F194" s="23"/>
       <c r="J194" s="4"/>
       <c r="K194" s="4"/>
       <c r="L194" s="14"/>
-      <c r="M194" s="14"/>
+      <c r="M194" s="26"/>
       <c r="N194" s="15"/>
     </row>
     <row r="195" spans="2:14">
       <c r="B195" s="12"/>
       <c r="C195" s="12"/>
       <c r="E195" s="13"/>
-      <c r="F195" s="13"/>
+      <c r="F195" s="23"/>
       <c r="J195" s="4"/>
       <c r="K195" s="4"/>
       <c r="L195" s="14"/>
-      <c r="M195" s="14"/>
+      <c r="M195" s="26"/>
       <c r="N195" s="15"/>
     </row>
     <row r="196" spans="2:14">
       <c r="B196" s="12"/>
       <c r="C196" s="12"/>
       <c r="E196" s="13"/>
-      <c r="F196" s="13"/>
+      <c r="F196" s="23"/>
       <c r="J196" s="4"/>
       <c r="K196" s="4"/>
       <c r="L196" s="14"/>
-      <c r="M196" s="14"/>
+      <c r="M196" s="26"/>
       <c r="N196" s="15"/>
     </row>
     <row r="197" spans="2:14">
       <c r="B197" s="12"/>
       <c r="C197" s="12"/>
       <c r="E197" s="13"/>
-      <c r="F197" s="13"/>
+      <c r="F197" s="23"/>
       <c r="J197" s="4"/>
       <c r="K197" s="4"/>
       <c r="L197" s="14"/>
-      <c r="M197" s="14"/>
+      <c r="M197" s="26"/>
       <c r="N197" s="15"/>
     </row>
     <row r="198" spans="2:14">
       <c r="B198" s="12"/>
       <c r="C198" s="12"/>
       <c r="E198" s="13"/>
-      <c r="F198" s="13"/>
+      <c r="F198" s="23"/>
       <c r="J198" s="4"/>
       <c r="K198" s="4"/>
       <c r="L198" s="14"/>
-      <c r="M198" s="14"/>
+      <c r="M198" s="26"/>
       <c r="N198" s="15"/>
     </row>
     <row r="199" spans="2:14">
       <c r="L199" s="18"/>
-      <c r="M199" s="18"/>
     </row>
     <row r="200" spans="2:14">
       <c r="L200" s="18"/>
-      <c r="M200" s="18"/>
     </row>
     <row r="201" spans="2:14">
       <c r="L201" s="18"/>
-      <c r="M201" s="18"/>
     </row>
     <row r="202" spans="2:14">
       <c r="L202" s="18"/>
-      <c r="M202" s="18"/>
     </row>
     <row r="203" spans="2:14">
       <c r="L203" s="18"/>
-      <c r="M203" s="18"/>
     </row>
     <row r="204" spans="2:14">
       <c r="L204" s="18"/>
-      <c r="M204" s="18"/>
     </row>
     <row r="205" spans="2:14">
       <c r="L205" s="18"/>
-      <c r="M205" s="18"/>
     </row>
     <row r="206" spans="2:14">
       <c r="L206" s="18"/>
-      <c r="M206" s="18"/>
     </row>
     <row r="207" spans="2:14">
       <c r="L207" s="18"/>
-      <c r="M207" s="18"/>
     </row>
     <row r="208" spans="2:14">
       <c r="L208" s="18"/>
-      <c r="M208" s="18"/>
-    </row>
-    <row r="209" spans="12:13">
+    </row>
+    <row r="209" spans="12:12">
       <c r="L209" s="18"/>
-      <c r="M209" s="18"/>
-    </row>
-    <row r="210" spans="12:13">
+    </row>
+    <row r="210" spans="12:12">
       <c r="L210" s="18"/>
-      <c r="M210" s="18"/>
-    </row>
-    <row r="211" spans="12:13">
+    </row>
+    <row r="211" spans="12:12">
       <c r="L211" s="18"/>
-      <c r="M211" s="18"/>
-    </row>
-    <row r="212" spans="12:13">
+    </row>
+    <row r="212" spans="12:12">
       <c r="L212" s="18"/>
-      <c r="M212" s="18"/>
-    </row>
-    <row r="213" spans="12:13">
+    </row>
+    <row r="213" spans="12:12">
       <c r="L213" s="18"/>
-      <c r="M213" s="18"/>
-    </row>
-    <row r="214" spans="12:13">
+    </row>
+    <row r="214" spans="12:12">
       <c r="L214" s="18"/>
-      <c r="M214" s="18"/>
-    </row>
-    <row r="215" spans="12:13">
+    </row>
+    <row r="215" spans="12:12">
       <c r="L215" s="18"/>
-      <c r="M215" s="18"/>
-    </row>
-    <row r="216" spans="12:13">
+    </row>
+    <row r="216" spans="12:12">
       <c r="L216" s="18"/>
-      <c r="M216" s="18"/>
-    </row>
-    <row r="217" spans="12:13">
+    </row>
+    <row r="217" spans="12:12">
       <c r="L217" s="18"/>
-      <c r="M217" s="18"/>
-    </row>
-    <row r="218" spans="12:13">
+    </row>
+    <row r="218" spans="12:12">
       <c r="L218" s="18"/>
-      <c r="M218" s="18"/>
-    </row>
-    <row r="219" spans="12:13">
+    </row>
+    <row r="219" spans="12:12">
       <c r="L219" s="18"/>
-      <c r="M219" s="18"/>
-    </row>
-    <row r="220" spans="12:13">
+    </row>
+    <row r="220" spans="12:12">
       <c r="L220" s="18"/>
-      <c r="M220" s="18"/>
-    </row>
-    <row r="221" spans="12:13">
+    </row>
+    <row r="221" spans="12:12">
       <c r="L221" s="18"/>
-      <c r="M221" s="18"/>
-    </row>
-    <row r="222" spans="12:13">
+    </row>
+    <row r="222" spans="12:12">
       <c r="L222" s="18"/>
-      <c r="M222" s="18"/>
-    </row>
-    <row r="223" spans="12:13">
+    </row>
+    <row r="223" spans="12:12">
       <c r="L223" s="18"/>
-      <c r="M223" s="18"/>
-    </row>
-    <row r="224" spans="12:13">
+    </row>
+    <row r="224" spans="12:12">
       <c r="L224" s="18"/>
-      <c r="M224" s="18"/>
-    </row>
-    <row r="225" spans="12:13">
+    </row>
+    <row r="225" spans="12:12">
       <c r="L225" s="18"/>
-      <c r="M225" s="18"/>
-    </row>
-    <row r="226" spans="12:13">
+    </row>
+    <row r="226" spans="12:12">
       <c r="L226" s="18"/>
-      <c r="M226" s="18"/>
-    </row>
-    <row r="227" spans="12:13">
+    </row>
+    <row r="227" spans="12:12">
       <c r="L227" s="18"/>
-      <c r="M227" s="18"/>
-    </row>
-    <row r="228" spans="12:13">
+    </row>
+    <row r="228" spans="12:12">
       <c r="L228" s="18"/>
-      <c r="M228" s="18"/>
-    </row>
-    <row r="229" spans="12:13">
+    </row>
+    <row r="229" spans="12:12">
       <c r="L229" s="18"/>
-      <c r="M229" s="18"/>
-    </row>
-    <row r="230" spans="12:13">
+    </row>
+    <row r="230" spans="12:12">
       <c r="L230" s="18"/>
-      <c r="M230" s="18"/>
-    </row>
-    <row r="231" spans="12:13">
+    </row>
+    <row r="231" spans="12:12">
       <c r="L231" s="18"/>
-      <c r="M231" s="18"/>
-    </row>
-    <row r="232" spans="12:13">
+    </row>
+    <row r="232" spans="12:12">
       <c r="L232" s="18"/>
-      <c r="M232" s="18"/>
-    </row>
-    <row r="233" spans="12:13">
+    </row>
+    <row r="233" spans="12:12">
       <c r="L233" s="18"/>
-      <c r="M233" s="18"/>
-    </row>
-    <row r="234" spans="12:13">
+    </row>
+    <row r="234" spans="12:12">
       <c r="L234" s="18"/>
-      <c r="M234" s="18"/>
-    </row>
-    <row r="235" spans="12:13">
+    </row>
+    <row r="235" spans="12:12">
       <c r="L235" s="18"/>
-      <c r="M235" s="18"/>
-    </row>
-    <row r="236" spans="12:13">
+    </row>
+    <row r="236" spans="12:12">
       <c r="L236" s="18"/>
-      <c r="M236" s="18"/>
-    </row>
-    <row r="237" spans="12:13">
+    </row>
+    <row r="237" spans="12:12">
       <c r="L237" s="18"/>
-      <c r="M237" s="18"/>
-    </row>
-    <row r="238" spans="12:13">
+    </row>
+    <row r="238" spans="12:12">
       <c r="L238" s="18"/>
-      <c r="M238" s="18"/>
-    </row>
-    <row r="239" spans="12:13">
+    </row>
+    <row r="239" spans="12:12">
       <c r="L239" s="18"/>
-      <c r="M239" s="18"/>
-    </row>
-    <row r="240" spans="12:13">
+    </row>
+    <row r="240" spans="12:12">
       <c r="L240" s="18"/>
-      <c r="M240" s="18"/>
-    </row>
-    <row r="241" spans="12:13">
+    </row>
+    <row r="241" spans="12:12">
       <c r="L241" s="18"/>
-      <c r="M241" s="18"/>
-    </row>
-    <row r="242" spans="12:13">
+    </row>
+    <row r="242" spans="12:12">
       <c r="L242" s="18"/>
-      <c r="M242" s="18"/>
-    </row>
-    <row r="243" spans="12:13">
+    </row>
+    <row r="243" spans="12:12">
       <c r="L243" s="18"/>
-      <c r="M243" s="18"/>
-    </row>
-    <row r="244" spans="12:13">
+    </row>
+    <row r="244" spans="12:12">
       <c r="L244" s="18"/>
-      <c r="M244" s="18"/>
-    </row>
-    <row r="245" spans="12:13">
+    </row>
+    <row r="245" spans="12:12">
       <c r="L245" s="18"/>
-      <c r="M245" s="18"/>
-    </row>
-    <row r="246" spans="12:13">
+    </row>
+    <row r="246" spans="12:12">
       <c r="L246" s="18"/>
-      <c r="M246" s="18"/>
-    </row>
-    <row r="247" spans="12:13">
+    </row>
+    <row r="247" spans="12:12">
       <c r="L247" s="18"/>
-      <c r="M247" s="18"/>
-    </row>
-    <row r="248" spans="12:13">
+    </row>
+    <row r="248" spans="12:12">
       <c r="L248" s="18"/>
-      <c r="M248" s="18"/>
-    </row>
-    <row r="249" spans="12:13">
+    </row>
+    <row r="249" spans="12:12">
       <c r="L249" s="18"/>
-      <c r="M249" s="18"/>
-    </row>
-    <row r="250" spans="12:13">
+    </row>
+    <row r="250" spans="12:12">
       <c r="L250" s="18"/>
-      <c r="M250" s="18"/>
-    </row>
-    <row r="251" spans="12:13">
+    </row>
+    <row r="251" spans="12:12">
       <c r="L251" s="18"/>
-      <c r="M251" s="18"/>
-    </row>
-    <row r="252" spans="12:13">
+    </row>
+    <row r="252" spans="12:12">
       <c r="L252" s="18"/>
-      <c r="M252" s="18"/>
-    </row>
-    <row r="253" spans="12:13">
+    </row>
+    <row r="253" spans="12:12">
       <c r="L253" s="18"/>
-      <c r="M253" s="18"/>
-    </row>
-    <row r="254" spans="12:13">
+    </row>
+    <row r="254" spans="12:12">
       <c r="L254" s="18"/>
-      <c r="M254" s="18"/>
-    </row>
-    <row r="255" spans="12:13">
+    </row>
+    <row r="255" spans="12:12">
       <c r="L255" s="18"/>
-      <c r="M255" s="18"/>
-    </row>
-    <row r="256" spans="12:13">
+    </row>
+    <row r="256" spans="12:12">
       <c r="L256" s="18"/>
-      <c r="M256" s="18"/>
-    </row>
-    <row r="257" spans="12:13">
+    </row>
+    <row r="257" spans="12:12">
       <c r="L257" s="18"/>
-      <c r="M257" s="18"/>
-    </row>
-    <row r="258" spans="12:13">
+    </row>
+    <row r="258" spans="12:12">
       <c r="L258" s="18"/>
-      <c r="M258" s="18"/>
-    </row>
-    <row r="259" spans="12:13">
+    </row>
+    <row r="259" spans="12:12">
       <c r="L259" s="18"/>
-      <c r="M259" s="18"/>
-    </row>
-    <row r="260" spans="12:13">
+    </row>
+    <row r="260" spans="12:12">
       <c r="L260" s="18"/>
-      <c r="M260" s="18"/>
-    </row>
-    <row r="261" spans="12:13">
+    </row>
+    <row r="261" spans="12:12">
       <c r="L261" s="18"/>
-      <c r="M261" s="18"/>
-    </row>
-    <row r="262" spans="12:13">
+    </row>
+    <row r="262" spans="12:12">
       <c r="L262" s="18"/>
-      <c r="M262" s="18"/>
-    </row>
-    <row r="263" spans="12:13">
+    </row>
+    <row r="263" spans="12:12">
       <c r="L263" s="18"/>
-      <c r="M263" s="18"/>
-    </row>
-    <row r="264" spans="12:13">
+    </row>
+    <row r="264" spans="12:12">
       <c r="L264" s="18"/>
-      <c r="M264" s="18"/>
-    </row>
-    <row r="265" spans="12:13">
+    </row>
+    <row r="265" spans="12:12">
       <c r="L265" s="18"/>
-      <c r="M265" s="18"/>
-    </row>
-    <row r="266" spans="12:13">
+    </row>
+    <row r="266" spans="12:12">
       <c r="L266" s="18"/>
-      <c r="M266" s="18"/>
-    </row>
-    <row r="267" spans="12:13">
+    </row>
+    <row r="267" spans="12:12">
       <c r="L267" s="18"/>
-      <c r="M267" s="18"/>
-    </row>
-    <row r="268" spans="12:13">
+    </row>
+    <row r="268" spans="12:12">
       <c r="L268" s="18"/>
-      <c r="M268" s="18"/>
-    </row>
-    <row r="269" spans="12:13">
+    </row>
+    <row r="269" spans="12:12">
       <c r="L269" s="18"/>
-      <c r="M269" s="18"/>
-    </row>
-    <row r="270" spans="12:13">
+    </row>
+    <row r="270" spans="12:12">
       <c r="L270" s="18"/>
-      <c r="M270" s="18"/>
-    </row>
-    <row r="271" spans="12:13">
+    </row>
+    <row r="271" spans="12:12">
       <c r="L271" s="18"/>
-      <c r="M271" s="18"/>
-    </row>
-    <row r="272" spans="12:13">
+    </row>
+    <row r="272" spans="12:12">
       <c r="L272" s="18"/>
-      <c r="M272" s="18"/>
-    </row>
-    <row r="273" spans="12:13">
+    </row>
+    <row r="273" spans="12:12">
       <c r="L273" s="18"/>
-      <c r="M273" s="18"/>
-    </row>
-    <row r="274" spans="12:13">
+    </row>
+    <row r="274" spans="12:12">
       <c r="L274" s="18"/>
-      <c r="M274" s="18"/>
-    </row>
-    <row r="275" spans="12:13">
+    </row>
+    <row r="275" spans="12:12">
       <c r="L275" s="18"/>
-      <c r="M275" s="18"/>
-    </row>
-    <row r="276" spans="12:13">
+    </row>
+    <row r="276" spans="12:12">
       <c r="L276" s="18"/>
-      <c r="M276" s="18"/>
-    </row>
-    <row r="277" spans="12:13">
+    </row>
+    <row r="277" spans="12:12">
       <c r="L277" s="18"/>
-      <c r="M277" s="18"/>
-    </row>
-    <row r="278" spans="12:13">
+    </row>
+    <row r="278" spans="12:12">
       <c r="L278" s="18"/>
-      <c r="M278" s="18"/>
-    </row>
-    <row r="279" spans="12:13">
+    </row>
+    <row r="279" spans="12:12">
       <c r="L279" s="18"/>
-      <c r="M279" s="18"/>
-    </row>
-    <row r="280" spans="12:13">
+    </row>
+    <row r="280" spans="12:12">
       <c r="L280" s="18"/>
-      <c r="M280" s="18"/>
-    </row>
-    <row r="281" spans="12:13">
+    </row>
+    <row r="281" spans="12:12">
       <c r="L281" s="18"/>
-      <c r="M281" s="18"/>
-    </row>
-    <row r="282" spans="12:13">
+    </row>
+    <row r="282" spans="12:12">
       <c r="L282" s="18"/>
-      <c r="M282" s="18"/>
-    </row>
-    <row r="283" spans="12:13">
+    </row>
+    <row r="283" spans="12:12">
       <c r="L283" s="18"/>
-      <c r="M283" s="18"/>
-    </row>
-    <row r="284" spans="12:13">
+    </row>
+    <row r="284" spans="12:12">
       <c r="L284" s="18"/>
-      <c r="M284" s="18"/>
-    </row>
-    <row r="285" spans="12:13">
+    </row>
+    <row r="285" spans="12:12">
       <c r="L285" s="18"/>
-      <c r="M285" s="18"/>
-    </row>
-    <row r="286" spans="12:13">
+    </row>
+    <row r="286" spans="12:12">
       <c r="L286" s="18"/>
-      <c r="M286" s="18"/>
-    </row>
-    <row r="287" spans="12:13">
+    </row>
+    <row r="287" spans="12:12">
       <c r="L287" s="18"/>
-      <c r="M287" s="18"/>
-    </row>
-    <row r="288" spans="12:13">
+    </row>
+    <row r="288" spans="12:12">
       <c r="L288" s="18"/>
-      <c r="M288" s="18"/>
-    </row>
-    <row r="289" spans="12:13">
+    </row>
+    <row r="289" spans="12:12">
       <c r="L289" s="18"/>
-      <c r="M289" s="18"/>
-    </row>
-    <row r="290" spans="12:13">
+    </row>
+    <row r="290" spans="12:12">
       <c r="L290" s="18"/>
-      <c r="M290" s="18"/>
-    </row>
-    <row r="291" spans="12:13">
+    </row>
+    <row r="291" spans="12:12">
       <c r="L291" s="18"/>
-      <c r="M291" s="18"/>
-    </row>
-    <row r="292" spans="12:13">
+    </row>
+    <row r="292" spans="12:12">
       <c r="L292" s="18"/>
-      <c r="M292" s="18"/>
-    </row>
-    <row r="293" spans="12:13">
+    </row>
+    <row r="293" spans="12:12">
       <c r="L293" s="18"/>
-      <c r="M293" s="18"/>
-    </row>
-    <row r="294" spans="12:13">
+    </row>
+    <row r="294" spans="12:12">
       <c r="L294" s="18"/>
-      <c r="M294" s="18"/>
-    </row>
-    <row r="295" spans="12:13">
+    </row>
+    <row r="295" spans="12:12">
       <c r="L295" s="18"/>
-      <c r="M295" s="18"/>
-    </row>
-    <row r="296" spans="12:13">
+    </row>
+    <row r="296" spans="12:12">
       <c r="L296" s="18"/>
-      <c r="M296" s="18"/>
-    </row>
-    <row r="297" spans="12:13">
+    </row>
+    <row r="297" spans="12:12">
       <c r="L297" s="18"/>
-      <c r="M297" s="18"/>
-    </row>
-    <row r="298" spans="12:13">
+    </row>
+    <row r="298" spans="12:12">
       <c r="L298" s="18"/>
-      <c r="M298" s="18"/>
-    </row>
-    <row r="299" spans="12:13">
+    </row>
+    <row r="299" spans="12:12">
       <c r="L299" s="18"/>
-      <c r="M299" s="18"/>
-    </row>
-    <row r="300" spans="12:13">
+    </row>
+    <row r="300" spans="12:12">
       <c r="L300" s="18"/>
-      <c r="M300" s="18"/>
-    </row>
-    <row r="301" spans="12:13">
+    </row>
+    <row r="301" spans="12:12">
       <c r="L301" s="18"/>
-      <c r="M301" s="18"/>
-    </row>
-    <row r="302" spans="12:13">
+    </row>
+    <row r="302" spans="12:12">
       <c r="L302" s="18"/>
-      <c r="M302" s="18"/>
-    </row>
-    <row r="303" spans="12:13">
+    </row>
+    <row r="303" spans="12:12">
       <c r="L303" s="18"/>
-      <c r="M303" s="18"/>
-    </row>
-    <row r="304" spans="12:13">
+    </row>
+    <row r="304" spans="12:12">
       <c r="L304" s="18"/>
-      <c r="M304" s="18"/>
-    </row>
-    <row r="305" spans="12:13">
+    </row>
+    <row r="305" spans="12:12">
       <c r="L305" s="18"/>
-      <c r="M305" s="18"/>
-    </row>
-    <row r="306" spans="12:13">
+    </row>
+    <row r="306" spans="12:12">
       <c r="L306" s="18"/>
-      <c r="M306" s="18"/>
-    </row>
-    <row r="307" spans="12:13">
+    </row>
+    <row r="307" spans="12:12">
       <c r="L307" s="18"/>
-      <c r="M307" s="18"/>
-    </row>
-    <row r="308" spans="12:13">
+    </row>
+    <row r="308" spans="12:12">
       <c r="L308" s="18"/>
-      <c r="M308" s="18"/>
-    </row>
-    <row r="309" spans="12:13">
+    </row>
+    <row r="309" spans="12:12">
       <c r="L309" s="18"/>
-      <c r="M309" s="18"/>
-    </row>
-    <row r="310" spans="12:13">
+    </row>
+    <row r="310" spans="12:12">
       <c r="L310" s="18"/>
-      <c r="M310" s="18"/>
-    </row>
-    <row r="311" spans="12:13">
+    </row>
+    <row r="311" spans="12:12">
       <c r="L311" s="18"/>
-      <c r="M311" s="18"/>
-    </row>
-    <row r="312" spans="12:13">
+    </row>
+    <row r="312" spans="12:12">
       <c r="L312" s="18"/>
-      <c r="M312" s="18"/>
-    </row>
-    <row r="313" spans="12:13">
+    </row>
+    <row r="313" spans="12:12">
       <c r="L313" s="18"/>
-      <c r="M313" s="18"/>
-    </row>
-    <row r="314" spans="12:13">
+    </row>
+    <row r="314" spans="12:12">
       <c r="L314" s="18"/>
-      <c r="M314" s="18"/>
-    </row>
-    <row r="315" spans="12:13">
+    </row>
+    <row r="315" spans="12:12">
       <c r="L315" s="18"/>
-      <c r="M315" s="18"/>
-    </row>
-    <row r="316" spans="12:13">
+    </row>
+    <row r="316" spans="12:12">
       <c r="L316" s="18"/>
-      <c r="M316" s="18"/>
-    </row>
-    <row r="317" spans="12:13">
+    </row>
+    <row r="317" spans="12:12">
       <c r="L317" s="18"/>
-      <c r="M317" s="18"/>
-    </row>
-    <row r="318" spans="12:13">
+    </row>
+    <row r="318" spans="12:12">
       <c r="L318" s="18"/>
-      <c r="M318" s="18"/>
-    </row>
-    <row r="319" spans="12:13">
+    </row>
+    <row r="319" spans="12:12">
       <c r="L319" s="18"/>
-      <c r="M319" s="18"/>
-    </row>
-    <row r="320" spans="12:13">
+    </row>
+    <row r="320" spans="12:12">
       <c r="L320" s="18"/>
-      <c r="M320" s="18"/>
-    </row>
-    <row r="321" spans="12:13">
+    </row>
+    <row r="321" spans="12:12">
       <c r="L321" s="18"/>
-      <c r="M321" s="18"/>
-    </row>
-    <row r="322" spans="12:13">
+    </row>
+    <row r="322" spans="12:12">
       <c r="L322" s="18"/>
-      <c r="M322" s="18"/>
-    </row>
-    <row r="323" spans="12:13">
+    </row>
+    <row r="323" spans="12:12">
       <c r="L323" s="18"/>
-      <c r="M323" s="18"/>
-    </row>
-    <row r="324" spans="12:13">
+    </row>
+    <row r="324" spans="12:12">
       <c r="L324" s="18"/>
-      <c r="M324" s="18"/>
-    </row>
-    <row r="325" spans="12:13">
+    </row>
+    <row r="325" spans="12:12">
       <c r="L325" s="18"/>
-      <c r="M325" s="18"/>
-    </row>
-    <row r="326" spans="12:13">
+    </row>
+    <row r="326" spans="12:12">
       <c r="L326" s="18"/>
-      <c r="M326" s="18"/>
-    </row>
-    <row r="327" spans="12:13">
+    </row>
+    <row r="327" spans="12:12">
       <c r="L327" s="18"/>
-      <c r="M327" s="18"/>
-    </row>
-    <row r="328" spans="12:13">
+    </row>
+    <row r="328" spans="12:12">
       <c r="L328" s="18"/>
-      <c r="M328" s="18"/>
-    </row>
-    <row r="329" spans="12:13">
+    </row>
+    <row r="329" spans="12:12">
       <c r="L329" s="18"/>
-      <c r="M329" s="18"/>
-    </row>
-    <row r="330" spans="12:13">
+    </row>
+    <row r="330" spans="12:12">
       <c r="L330" s="18"/>
-      <c r="M330" s="18"/>
-    </row>
-    <row r="331" spans="12:13">
+    </row>
+    <row r="331" spans="12:12">
       <c r="L331" s="18"/>
-      <c r="M331" s="18"/>
-    </row>
-    <row r="332" spans="12:13">
+    </row>
+    <row r="332" spans="12:12">
       <c r="L332" s="18"/>
-      <c r="M332" s="18"/>
-    </row>
-    <row r="333" spans="12:13">
+    </row>
+    <row r="333" spans="12:12">
       <c r="L333" s="18"/>
-      <c r="M333" s="18"/>
-    </row>
-    <row r="334" spans="12:13">
+    </row>
+    <row r="334" spans="12:12">
       <c r="L334" s="18"/>
-      <c r="M334" s="18"/>
-    </row>
-    <row r="335" spans="12:13">
+    </row>
+    <row r="335" spans="12:12">
       <c r="L335" s="18"/>
-      <c r="M335" s="18"/>
-    </row>
-    <row r="336" spans="12:13">
+    </row>
+    <row r="336" spans="12:12">
       <c r="L336" s="18"/>
-      <c r="M336" s="18"/>
-    </row>
-    <row r="337" spans="12:13">
+    </row>
+    <row r="337" spans="12:12">
       <c r="L337" s="18"/>
-      <c r="M337" s="18"/>
-    </row>
-    <row r="338" spans="12:13">
+    </row>
+    <row r="338" spans="12:12">
       <c r="L338" s="18"/>
-      <c r="M338" s="18"/>
-    </row>
-    <row r="339" spans="12:13">
+    </row>
+    <row r="339" spans="12:12">
       <c r="L339" s="18"/>
-      <c r="M339" s="18"/>
-    </row>
-    <row r="340" spans="12:13">
+    </row>
+    <row r="340" spans="12:12">
       <c r="L340" s="18"/>
-      <c r="M340" s="18"/>
-    </row>
-    <row r="341" spans="12:13">
+    </row>
+    <row r="341" spans="12:12">
       <c r="L341" s="18"/>
-      <c r="M341" s="18"/>
-    </row>
-    <row r="342" spans="12:13">
+    </row>
+    <row r="342" spans="12:12">
       <c r="L342" s="18"/>
-      <c r="M342" s="18"/>
-    </row>
-    <row r="343" spans="12:13">
+    </row>
+    <row r="343" spans="12:12">
       <c r="L343" s="18"/>
-      <c r="M343" s="18"/>
-    </row>
-    <row r="344" spans="12:13">
+    </row>
+    <row r="344" spans="12:12">
       <c r="L344" s="18"/>
-      <c r="M344" s="18"/>
-    </row>
-    <row r="345" spans="12:13">
+    </row>
+    <row r="345" spans="12:12">
       <c r="L345" s="18"/>
-      <c r="M345" s="18"/>
-    </row>
-    <row r="346" spans="12:13">
+    </row>
+    <row r="346" spans="12:12">
       <c r="L346" s="18"/>
-      <c r="M346" s="18"/>
-    </row>
-    <row r="347" spans="12:13">
+    </row>
+    <row r="347" spans="12:12">
       <c r="L347" s="18"/>
-      <c r="M347" s="18"/>
-    </row>
-    <row r="348" spans="12:13">
+    </row>
+    <row r="348" spans="12:12">
       <c r="L348" s="18"/>
-      <c r="M348" s="18"/>
-    </row>
-    <row r="349" spans="12:13">
+    </row>
+    <row r="349" spans="12:12">
       <c r="L349" s="18"/>
-      <c r="M349" s="18"/>
-    </row>
-    <row r="350" spans="12:13">
+    </row>
+    <row r="350" spans="12:12">
       <c r="L350" s="18"/>
-      <c r="M350" s="18"/>
-    </row>
-    <row r="351" spans="12:13">
+    </row>
+    <row r="351" spans="12:12">
       <c r="L351" s="18"/>
-      <c r="M351" s="18"/>
-    </row>
-    <row r="352" spans="12:13">
+    </row>
+    <row r="352" spans="12:12">
       <c r="L352" s="18"/>
-      <c r="M352" s="18"/>
-    </row>
-    <row r="353" spans="12:13">
+    </row>
+    <row r="353" spans="12:12">
       <c r="L353" s="18"/>
-      <c r="M353" s="18"/>
-    </row>
-    <row r="354" spans="12:13">
+    </row>
+    <row r="354" spans="12:12">
       <c r="L354" s="18"/>
-      <c r="M354" s="18"/>
-    </row>
-    <row r="355" spans="12:13">
+    </row>
+    <row r="355" spans="12:12">
       <c r="L355" s="18"/>
-      <c r="M355" s="18"/>
-    </row>
-    <row r="356" spans="12:13">
+    </row>
+    <row r="356" spans="12:12">
       <c r="L356" s="18"/>
-      <c r="M356" s="18"/>
-    </row>
-    <row r="357" spans="12:13">
+    </row>
+    <row r="357" spans="12:12">
       <c r="L357" s="18"/>
-      <c r="M357" s="18"/>
-    </row>
-    <row r="358" spans="12:13">
+    </row>
+    <row r="358" spans="12:12">
       <c r="L358" s="18"/>
-      <c r="M358" s="18"/>
-    </row>
-    <row r="359" spans="12:13">
+    </row>
+    <row r="359" spans="12:12">
       <c r="L359" s="18"/>
-      <c r="M359" s="18"/>
-    </row>
-    <row r="360" spans="12:13">
+    </row>
+    <row r="360" spans="12:12">
       <c r="L360" s="18"/>
-      <c r="M360" s="18"/>
-    </row>
-    <row r="361" spans="12:13">
+    </row>
+    <row r="361" spans="12:12">
       <c r="L361" s="18"/>
-      <c r="M361" s="18"/>
-    </row>
-    <row r="362" spans="12:13">
+    </row>
+    <row r="362" spans="12:12">
       <c r="L362" s="18"/>
-      <c r="M362" s="18"/>
-    </row>
-    <row r="363" spans="12:13">
+    </row>
+    <row r="363" spans="12:12">
       <c r="L363" s="18"/>
-      <c r="M363" s="18"/>
-    </row>
-    <row r="364" spans="12:13">
+    </row>
+    <row r="364" spans="12:12">
       <c r="L364" s="18"/>
-      <c r="M364" s="18"/>
-    </row>
-    <row r="365" spans="12:13">
+    </row>
+    <row r="365" spans="12:12">
       <c r="L365" s="18"/>
-      <c r="M365" s="18"/>
-    </row>
-    <row r="366" spans="12:13">
+    </row>
+    <row r="366" spans="12:12">
       <c r="L366" s="18"/>
-      <c r="M366" s="18"/>
-    </row>
-    <row r="367" spans="12:13">
+    </row>
+    <row r="367" spans="12:12">
       <c r="L367" s="18"/>
-      <c r="M367" s="18"/>
-    </row>
-    <row r="368" spans="12:13">
+    </row>
+    <row r="368" spans="12:12">
       <c r="L368" s="18"/>
-      <c r="M368" s="18"/>
-    </row>
-    <row r="369" spans="12:13">
+    </row>
+    <row r="369" spans="12:12">
       <c r="L369" s="18"/>
-      <c r="M369" s="18"/>
-    </row>
-    <row r="370" spans="12:13">
+    </row>
+    <row r="370" spans="12:12">
       <c r="L370" s="18"/>
-      <c r="M370" s="18"/>
-    </row>
-    <row r="371" spans="12:13">
+    </row>
+    <row r="371" spans="12:12">
       <c r="L371" s="18"/>
-      <c r="M371" s="18"/>
-    </row>
-    <row r="372" spans="12:13">
+    </row>
+    <row r="372" spans="12:12">
       <c r="L372" s="18"/>
-      <c r="M372" s="18"/>
-    </row>
-    <row r="373" spans="12:13">
+    </row>
+    <row r="373" spans="12:12">
       <c r="L373" s="18"/>
-      <c r="M373" s="18"/>
-    </row>
-    <row r="374" spans="12:13">
+    </row>
+    <row r="374" spans="12:12">
       <c r="L374" s="18"/>
-      <c r="M374" s="18"/>
-    </row>
-    <row r="375" spans="12:13">
+    </row>
+    <row r="375" spans="12:12">
       <c r="L375" s="18"/>
-      <c r="M375" s="18"/>
-    </row>
-    <row r="376" spans="12:13">
+    </row>
+    <row r="376" spans="12:12">
       <c r="L376" s="18"/>
-      <c r="M376" s="18"/>
-    </row>
-    <row r="377" spans="12:13">
+    </row>
+    <row r="377" spans="12:12">
       <c r="L377" s="18"/>
-      <c r="M377" s="18"/>
-    </row>
-    <row r="378" spans="12:13">
+    </row>
+    <row r="378" spans="12:12">
       <c r="L378" s="18"/>
-      <c r="M378" s="18"/>
-    </row>
-    <row r="379" spans="12:13">
+    </row>
+    <row r="379" spans="12:12">
       <c r="L379" s="18"/>
-      <c r="M379" s="18"/>
-    </row>
-    <row r="380" spans="12:13">
+    </row>
+    <row r="380" spans="12:12">
       <c r="L380" s="18"/>
-      <c r="M380" s="18"/>
-    </row>
-    <row r="381" spans="12:13">
+    </row>
+    <row r="381" spans="12:12">
       <c r="L381" s="18"/>
-      <c r="M381" s="18"/>
-    </row>
-    <row r="382" spans="12:13">
+    </row>
+    <row r="382" spans="12:12">
       <c r="L382" s="18"/>
-      <c r="M382" s="18"/>
-    </row>
-    <row r="383" spans="12:13">
+    </row>
+    <row r="383" spans="12:12">
       <c r="L383" s="18"/>
-      <c r="M383" s="18"/>
-    </row>
-    <row r="384" spans="12:13">
+    </row>
+    <row r="384" spans="12:12">
       <c r="L384" s="18"/>
-      <c r="M384" s="18"/>
-    </row>
-    <row r="385" spans="12:13">
+    </row>
+    <row r="385" spans="12:12">
       <c r="L385" s="18"/>
-      <c r="M385" s="18"/>
-    </row>
-    <row r="386" spans="12:13">
+    </row>
+    <row r="386" spans="12:12">
       <c r="L386" s="18"/>
-      <c r="M386" s="18"/>
-    </row>
-    <row r="387" spans="12:13">
+    </row>
+    <row r="387" spans="12:12">
       <c r="L387" s="18"/>
-      <c r="M387" s="18"/>
-    </row>
-    <row r="388" spans="12:13">
+    </row>
+    <row r="388" spans="12:12">
       <c r="L388" s="18"/>
-      <c r="M388" s="18"/>
-    </row>
-    <row r="389" spans="12:13">
+    </row>
+    <row r="389" spans="12:12">
       <c r="L389" s="18"/>
-      <c r="M389" s="18"/>
-    </row>
-    <row r="390" spans="12:13">
+    </row>
+    <row r="390" spans="12:12">
       <c r="L390" s="18"/>
-      <c r="M390" s="18"/>
-    </row>
-    <row r="391" spans="12:13">
+    </row>
+    <row r="391" spans="12:12">
       <c r="L391" s="18"/>
-      <c r="M391" s="18"/>
-    </row>
-    <row r="392" spans="12:13">
+    </row>
+    <row r="392" spans="12:12">
       <c r="L392" s="18"/>
-      <c r="M392" s="18"/>
-    </row>
-    <row r="393" spans="12:13">
+    </row>
+    <row r="393" spans="12:12">
       <c r="L393" s="18"/>
-      <c r="M393" s="18"/>
-    </row>
-    <row r="394" spans="12:13">
+    </row>
+    <row r="394" spans="12:12">
       <c r="L394" s="18"/>
-      <c r="M394" s="18"/>
-    </row>
-    <row r="395" spans="12:13">
+    </row>
+    <row r="395" spans="12:12">
       <c r="L395" s="18"/>
-      <c r="M395" s="18"/>
-    </row>
-    <row r="396" spans="12:13">
+    </row>
+    <row r="396" spans="12:12">
       <c r="L396" s="18"/>
-      <c r="M396" s="18"/>
-    </row>
-    <row r="397" spans="12:13">
+    </row>
+    <row r="397" spans="12:12">
       <c r="L397" s="18"/>
-      <c r="M397" s="18"/>
-    </row>
-    <row r="398" spans="12:13">
+    </row>
+    <row r="398" spans="12:12">
       <c r="L398" s="18"/>
-      <c r="M398" s="18"/>
     </row>
   </sheetData>
   <autoFilter ref="B2:P2" xr:uid="{00000000-0001-0000-0000-000000000000}">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A6F98D-C699-4183-9FF2-AB44CFD401F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B8500DB-05CB-45C4-968A-8A54F8070109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opportunities" sheetId="1" r:id="rId1"/>
@@ -34,9 +34,6 @@
     <t>Currency</t>
   </si>
   <si>
-    <t>HKD</t>
-  </si>
-  <si>
     <t>Symbol</t>
   </si>
   <si>
@@ -47,30 +44,6 @@
   </si>
   <si>
     <t>Comp Group</t>
-  </si>
-  <si>
-    <t>0083.HK</t>
-  </si>
-  <si>
-    <t>SINO LAND</t>
-  </si>
-  <si>
-    <t>C0003</t>
-  </si>
-  <si>
-    <t>6601.HK</t>
-  </si>
-  <si>
-    <t>朝云集团</t>
-  </si>
-  <si>
-    <t>0590.HK</t>
-  </si>
-  <si>
-    <t>六福珠宝</t>
-  </si>
-  <si>
-    <t>C0001</t>
   </si>
   <si>
     <t>Dividend Yield</t>
@@ -106,15 +79,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Low Growth Asset Play</t>
-  </si>
-  <si>
-    <t>Not Held</t>
-  </si>
-  <si>
-    <t>Negative Growth Asset Play</t>
-  </si>
-  <si>
     <t>Held</t>
   </si>
   <si>
@@ -130,6 +94,42 @@
     <t>Price 
 Alert</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0083.HK</t>
+  </si>
+  <si>
+    <t>SINO LAND</t>
+  </si>
+  <si>
+    <t>HKD</t>
+  </si>
+  <si>
+    <t>C0003</t>
+  </si>
+  <si>
+    <t>Negative Growth Asset Play</t>
+  </si>
+  <si>
+    <t>0590.HK</t>
+  </si>
+  <si>
+    <t>六福珠宝</t>
+  </si>
+  <si>
+    <t>Low Growth Asset Play</t>
+  </si>
+  <si>
+    <t>6601.HK</t>
+  </si>
+  <si>
+    <t>朝云集团</t>
+  </si>
+  <si>
+    <t>C0001</t>
+  </si>
+  <si>
+    <t>Not Held</t>
   </si>
 </sst>
 </file>
@@ -679,7 +679,7 @@
     <row r="1" spans="1:16">
       <c r="A1" s="5"/>
       <c r="B1" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D1" s="21" t="s">
         <v>1</v>
@@ -687,12 +687,12 @@
       <c r="E1" s="21"/>
       <c r="F1" s="20"/>
       <c r="G1" s="23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1" s="23"/>
       <c r="I1" s="23"/>
       <c r="J1" s="24" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="K1" s="24"/>
       <c r="L1" s="22"/>
@@ -703,7 +703,7 @@
     </row>
     <row r="2" spans="1:16" ht="26" customHeight="1">
       <c r="B2" s="8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>0</v>
@@ -715,54 +715,54 @@
         <v>2</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="G2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="8" t="s">
+      <c r="K2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>30</v>
-      </c>
       <c r="P2" s="11" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="B3" s="12" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D3" s="2">
-        <v>7.9</v>
+        <v>7.95</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F3" s="19">
-        <v>0.17349059186547722</v>
+        <v>0.17086981192202799</v>
       </c>
       <c r="G3" s="2">
         <v>7.4179368510878518</v>
@@ -775,124 +775,124 @@
         <v>-0.30718778376753109</v>
       </c>
       <c r="J3" s="4">
-        <v>5.401287075648549E-2</v>
+        <v>5.3673167166822057E-2</v>
       </c>
       <c r="K3" s="4">
-        <v>7.3417721518987331E-2</v>
+        <v>7.2955974842767293E-2</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N3" s="15">
         <v>45716</v>
       </c>
       <c r="O3" s="16">
         <f>IFERROR(D3/H3-1, "nm")</f>
-        <v>-0.26216458590721914</v>
+        <v>-0.2574947415142268</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="B4" s="12" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D4" s="2">
-        <v>15.38</v>
+        <v>15.1</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F4" s="19">
-        <v>0.14601322135335382</v>
+        <v>0.41634009110381465</v>
       </c>
       <c r="G4" s="2">
-        <v>13.538366385360966</v>
+        <v>24.211917955907118</v>
       </c>
       <c r="H4" s="2">
-        <v>18.443897113903752</v>
+        <v>36.887794227807504</v>
       </c>
       <c r="I4" s="4">
         <f>IFERROR(G4/H4-1, "nm")</f>
-        <v>-0.26597040193012134</v>
+        <v>-0.34363334911320886</v>
       </c>
       <c r="J4" s="4">
-        <v>0.11361779174212065</v>
+        <v>0.23144922344288948</v>
       </c>
       <c r="K4" s="4">
-        <v>8.8426527958387513E-2</v>
+        <v>9.0066225165562924E-2</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N4" s="15">
         <v>45716</v>
       </c>
       <c r="O4" s="16">
         <f>IFERROR(D4/H4-1, "nm")</f>
-        <v>-0.16611983329673108</v>
+        <v>-0.59065050334137326</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="B5" s="12" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D5" s="2">
-        <v>2.2999999999999998</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F5" s="19">
-        <v>8.8876330035536411E-2</v>
+        <v>0.51174977411698808</v>
       </c>
       <c r="G5" s="2">
-        <v>1.7432969171114687</v>
+        <v>4.479709740951396</v>
       </c>
       <c r="H5" s="2">
-        <v>2.5836250727686179</v>
+        <v>7.3121464323640124</v>
       </c>
       <c r="I5" s="4">
         <f>IFERROR(G5/H5-1, "nm")</f>
-        <v>-0.32525158720365399</v>
+        <v>-0.38736049908356274</v>
       </c>
       <c r="J5" s="4">
-        <v>3.3342925997552272E-2</v>
+        <v>9.519455039023117E-2</v>
       </c>
       <c r="K5" s="4">
-        <v>5.1217391304347833E-2</v>
+        <v>5.1666666666666673E-2</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="M5" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N5" s="15">
         <v>45716</v>
       </c>
       <c r="O5" s="16">
         <f>IFERROR(D5/H5-1, "nm")</f>
-        <v>-0.1097779533718044</v>
+        <v>-0.68819005184188065</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:16">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B8500DB-05CB-45C4-968A-8A54F8070109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD00E55B-7A66-4588-8A1E-87FA11871E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -756,13 +756,13 @@
         <v>20</v>
       </c>
       <c r="D3" s="2">
-        <v>7.95</v>
+        <v>7.91</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>21</v>
       </c>
       <c r="F3" s="19">
-        <v>0.17086981192202799</v>
+        <v>0.17296459645475393</v>
       </c>
       <c r="G3" s="2">
         <v>7.4179368510878518</v>
@@ -775,10 +775,10 @@
         <v>-0.30718778376753109</v>
       </c>
       <c r="J3" s="4">
-        <v>5.3673167166822057E-2</v>
+        <v>5.3944586469814836E-2</v>
       </c>
       <c r="K3" s="4">
-        <v>7.2955974842767293E-2</v>
+        <v>7.332490518331225E-2</v>
       </c>
       <c r="L3" s="14" t="s">
         <v>22</v>
@@ -791,7 +791,7 @@
       </c>
       <c r="O3" s="16">
         <f>IFERROR(D3/H3-1, "nm")</f>
-        <v>-0.2574947415142268</v>
+        <v>-0.26123061702862072</v>
       </c>
       <c r="P3" s="12" t="s">
         <v>15</v>
@@ -811,20 +811,20 @@
         <v>21</v>
       </c>
       <c r="F4" s="19">
-        <v>0.41634009110381465</v>
+        <v>0.15361989461854253</v>
       </c>
       <c r="G4" s="2">
-        <v>24.211917955907118</v>
+        <v>13.538366385360966</v>
       </c>
       <c r="H4" s="2">
-        <v>36.887794227807504</v>
+        <v>18.443897113903752</v>
       </c>
       <c r="I4" s="4">
         <f>IFERROR(G4/H4-1, "nm")</f>
-        <v>-0.34363334911320886</v>
+        <v>-0.26597040193012134</v>
       </c>
       <c r="J4" s="4">
-        <v>0.23144922344288948</v>
+        <v>0.11572461172144474</v>
       </c>
       <c r="K4" s="4">
         <v>9.0066225165562924E-2</v>
@@ -840,7 +840,7 @@
       </c>
       <c r="O4" s="16">
         <f>IFERROR(D4/H4-1, "nm")</f>
-        <v>-0.59065050334137326</v>
+        <v>-0.18130100668274651</v>
       </c>
       <c r="P4" s="12" t="s">
         <v>15</v>
@@ -854,29 +854,29 @@
         <v>28</v>
       </c>
       <c r="D5" s="2">
-        <v>2.2799999999999998</v>
+        <v>2.29</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>21</v>
       </c>
       <c r="F5" s="19">
-        <v>0.51174977411698808</v>
+        <v>9.4453005765433362E-2</v>
       </c>
       <c r="G5" s="2">
-        <v>4.479709740951396</v>
+        <v>1.7610376174468114</v>
       </c>
       <c r="H5" s="2">
-        <v>7.3121464323640124</v>
+        <v>2.6142810029480898</v>
       </c>
       <c r="I5" s="4">
         <f>IFERROR(G5/H5-1, "nm")</f>
-        <v>-0.38736049908356274</v>
+        <v>-0.32637783946679311</v>
       </c>
       <c r="J5" s="4">
-        <v>9.519455039023117E-2</v>
+        <v>3.3885885479174496E-2</v>
       </c>
       <c r="K5" s="4">
-        <v>5.1666666666666673E-2</v>
+        <v>5.1441048034934496E-2</v>
       </c>
       <c r="L5" s="14" t="s">
         <v>29</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="O5" s="16">
         <f>IFERROR(D5/H5-1, "nm")</f>
-        <v>-0.68819005184188065</v>
+        <v>-0.12404213723865276</v>
       </c>
       <c r="P5" s="12" t="s">
         <v>30</v>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD00E55B-7A66-4588-8A1E-87FA11871E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FE2A58-E459-493F-9CF0-1F64B8593058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opportunities" sheetId="1" r:id="rId1"/>
@@ -756,13 +756,13 @@
         <v>20</v>
       </c>
       <c r="D3" s="2">
-        <v>7.91</v>
+        <v>7.9</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>21</v>
       </c>
       <c r="F3" s="19">
-        <v>0.17296459645475393</v>
+        <v>0.17349059186547722</v>
       </c>
       <c r="G3" s="2">
         <v>7.4179368510878518</v>
@@ -775,10 +775,10 @@
         <v>-0.30718778376753109</v>
       </c>
       <c r="J3" s="4">
-        <v>5.3944586469814836E-2</v>
+        <v>5.401287075648549E-2</v>
       </c>
       <c r="K3" s="4">
-        <v>7.332490518331225E-2</v>
+        <v>7.3417721518987331E-2</v>
       </c>
       <c r="L3" s="14" t="s">
         <v>22</v>
@@ -791,7 +791,7 @@
       </c>
       <c r="O3" s="16">
         <f>IFERROR(D3/H3-1, "nm")</f>
-        <v>-0.26123061702862072</v>
+        <v>-0.26216458590721914</v>
       </c>
       <c r="P3" s="12" t="s">
         <v>15</v>
@@ -854,29 +854,29 @@
         <v>28</v>
       </c>
       <c r="D5" s="2">
-        <v>2.29</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>21</v>
       </c>
       <c r="F5" s="19">
-        <v>9.4453005765433362E-2</v>
+        <v>9.6153062008305534E-2</v>
       </c>
       <c r="G5" s="2">
-        <v>1.7610376174468114</v>
+        <v>1.7611544086745501</v>
       </c>
       <c r="H5" s="2">
-        <v>2.6142810029480898</v>
+        <v>2.6144828181896225</v>
       </c>
       <c r="I5" s="4">
         <f>IFERROR(G5/H5-1, "nm")</f>
-        <v>-0.32637783946679311</v>
+        <v>-0.32638516634274639</v>
       </c>
       <c r="J5" s="4">
-        <v>3.3885885479174496E-2</v>
+        <v>3.4037135153498488E-2</v>
       </c>
       <c r="K5" s="4">
-        <v>5.1441048034934496E-2</v>
+        <v>5.1666666666666673E-2</v>
       </c>
       <c r="L5" s="14" t="s">
         <v>29</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="O5" s="16">
         <f>IFERROR(D5/H5-1, "nm")</f>
-        <v>-0.12404213723865276</v>
+        <v>-0.12793460177383476</v>
       </c>
       <c r="P5" s="12" t="s">
         <v>30</v>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FE2A58-E459-493F-9CF0-1F64B8593058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF1D159-267F-466A-AEB9-C1836524A243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opportunities" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
   <si>
     <t>Name</t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t>Not Held</t>
+  </si>
+  <si>
+    <t>0700.HK</t>
   </si>
 </sst>
 </file>
@@ -805,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="D4" s="2">
-        <v>15.1</v>
+        <v>14.86</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>21</v>
       </c>
       <c r="F4" s="19">
-        <v>0.15361989461854253</v>
+        <v>0.16029914466500483</v>
       </c>
       <c r="G4" s="2">
         <v>13.538366385360966</v>
@@ -824,10 +827,10 @@
         <v>-0.26597040193012134</v>
       </c>
       <c r="J4" s="4">
-        <v>0.11572461172144474</v>
+        <v>0.11759364986499432</v>
       </c>
       <c r="K4" s="4">
-        <v>9.0066225165562924E-2</v>
+        <v>9.1520861372812928E-2</v>
       </c>
       <c r="L4" s="14" t="s">
         <v>22</v>
@@ -840,7 +843,7 @@
       </c>
       <c r="O4" s="16">
         <f>IFERROR(D4/H4-1, "nm")</f>
-        <v>-0.18130100668274651</v>
+        <v>-0.19431344101361669</v>
       </c>
       <c r="P4" s="12" t="s">
         <v>15</v>
@@ -848,63 +851,101 @@
     </row>
     <row r="5" spans="1:16">
       <c r="B5" s="12" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D5" s="2">
-        <v>2.2799999999999998</v>
+        <v>511.5</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>21</v>
       </c>
       <c r="F5" s="19">
-        <v>9.6153062008305534E-2</v>
+        <v>-0.19189388513342065</v>
       </c>
       <c r="G5" s="2">
-        <v>1.7611544086745501</v>
+        <v>156.60505097964941</v>
       </c>
       <c r="H5" s="2">
-        <v>2.6144828181896225</v>
+        <v>268.50232809283415</v>
       </c>
       <c r="I5" s="4">
         <f>IFERROR(G5/H5-1, "nm")</f>
-        <v>-0.32638516634274639</v>
+        <v>-0.41674602193578181</v>
       </c>
       <c r="J5" s="4">
-        <v>3.4037135153498488E-2</v>
+        <v>5.392009146885552E-2</v>
       </c>
       <c r="K5" s="4">
-        <v>5.1666666666666673E-2</v>
+        <v>1.133919843597263E-3</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M5" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N5" s="15">
         <v>45716</v>
       </c>
       <c r="O5" s="16">
         <f>IFERROR(D5/H5-1, "nm")</f>
-        <v>-0.12793460177383476</v>
+        <v>0.90501141510828864</v>
       </c>
       <c r="P5" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="B6" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2.23</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="19">
+        <v>0.10446582016168726</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1.7601941816673556</v>
+      </c>
+      <c r="H6" s="2">
+        <v>2.6128235459211906</v>
+      </c>
+      <c r="I6" s="4">
+        <f>IFERROR(G6/H6-1, "nm")</f>
+        <v>-0.32632489307777868</v>
+      </c>
+      <c r="J6" s="4">
+        <v>3.4778213731821772E-2</v>
+      </c>
+      <c r="K6" s="4">
+        <v>5.282511210762332E-2</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" s="15">
+        <v>45716</v>
+      </c>
+      <c r="O6" s="16">
+        <f>IFERROR(D6/H6-1, "nm")</f>
+        <v>-0.1465171831135732</v>
+      </c>
+      <c r="P6" s="12" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="19"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="15"/>
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="12"/>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF1D159-267F-466A-AEB9-C1836524A243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F75426-0783-46A1-B44F-850CE32C74D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
   <si>
     <t>Name</t>
   </si>
@@ -130,9 +130,6 @@
   </si>
   <si>
     <t>Not Held</t>
-  </si>
-  <si>
-    <t>0700.HK</t>
   </si>
 </sst>
 </file>
@@ -753,48 +750,48 @@
     </row>
     <row r="3" spans="1:16">
       <c r="B3" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D3" s="2">
-        <v>7.9</v>
+        <v>14.86</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>21</v>
       </c>
       <c r="F3" s="19">
-        <v>0.17349059186547722</v>
+        <v>0.19796385260234528</v>
       </c>
       <c r="G3" s="2">
-        <v>7.4179368510878518</v>
+        <v>14.789930718256866</v>
       </c>
       <c r="H3" s="2">
-        <v>10.706994878679808</v>
+        <v>20.606600281147866</v>
       </c>
       <c r="I3" s="4">
         <f>IFERROR(G3/H3-1, "nm")</f>
-        <v>-0.30718778376753109</v>
+        <v>-0.28227215957658158</v>
       </c>
       <c r="J3" s="4">
-        <v>5.401287075648549E-2</v>
+        <v>0.11620144005527505</v>
       </c>
       <c r="K3" s="4">
-        <v>7.3417721518987331E-2</v>
+        <v>9.1520861372812928E-2</v>
       </c>
       <c r="L3" s="14" t="s">
         <v>22</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N3" s="15">
         <v>45716</v>
       </c>
       <c r="O3" s="16">
-        <f>IFERROR(D3/H3-1, "nm")</f>
-        <v>-0.26216458590721914</v>
+        <f>IFERROR(D3/G3-1, "nm")</f>
+        <v>4.7376342105942548E-3</v>
       </c>
       <c r="P3" s="12" t="s">
         <v>15</v>
@@ -802,48 +799,48 @@
     </row>
     <row r="4" spans="1:16">
       <c r="B4" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D4" s="2">
-        <v>14.86</v>
+        <v>7.9</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>21</v>
       </c>
       <c r="F4" s="19">
-        <v>0.16029914466500483</v>
+        <v>0.11614149089878545</v>
       </c>
       <c r="G4" s="2">
-        <v>13.538366385360966</v>
+        <v>6.4501768017717804</v>
       </c>
       <c r="H4" s="2">
-        <v>18.443897113903752</v>
+        <v>9.0347055134616365</v>
       </c>
       <c r="I4" s="4">
         <f>IFERROR(G4/H4-1, "nm")</f>
-        <v>-0.26597040193012134</v>
+        <v>-0.28606673541699057</v>
       </c>
       <c r="J4" s="4">
-        <v>0.11759364986499432</v>
+        <v>3.9354193616452378E-2</v>
       </c>
       <c r="K4" s="4">
-        <v>9.1520861372812928E-2</v>
+        <v>7.3417721518987331E-2</v>
       </c>
       <c r="L4" s="14" t="s">
         <v>22</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N4" s="15">
         <v>45716</v>
       </c>
       <c r="O4" s="16">
-        <f>IFERROR(D4/H4-1, "nm")</f>
-        <v>-0.19431344101361669</v>
+        <f>IFERROR(D4/G4-1, "nm")</f>
+        <v>0.2247726291518044</v>
       </c>
       <c r="P4" s="12" t="s">
         <v>15</v>
@@ -851,101 +848,63 @@
     </row>
     <row r="5" spans="1:16">
       <c r="B5" s="12" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D5" s="2">
-        <v>511.5</v>
+        <v>2.23</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>21</v>
       </c>
       <c r="F5" s="19">
-        <v>-0.19189388513342065</v>
+        <v>6.1633064159671846E-2</v>
       </c>
       <c r="G5" s="2">
-        <v>156.60505097964941</v>
+        <v>1.5748978886562173</v>
       </c>
       <c r="H5" s="2">
-        <v>268.50232809283415</v>
+        <v>2.2926315515979434</v>
       </c>
       <c r="I5" s="4">
         <f>IFERROR(G5/H5-1, "nm")</f>
-        <v>-0.41674602193578181</v>
+        <v>-0.31306105965499442</v>
       </c>
       <c r="J5" s="4">
-        <v>5.392009146885552E-2</v>
+        <v>2.0531182016336334E-2</v>
       </c>
       <c r="K5" s="4">
-        <v>1.133919843597263E-3</v>
+        <v>5.282511210762332E-2</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M5" s="12" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N5" s="15">
         <v>45716</v>
       </c>
       <c r="O5" s="16">
-        <f>IFERROR(D5/H5-1, "nm")</f>
-        <v>0.90501141510828864</v>
+        <f>IFERROR(D5/G5-1, "nm")</f>
+        <v>0.41596481655248718</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:16">
-      <c r="B6" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="2">
-        <v>2.23</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="19">
-        <v>0.10446582016168726</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1.7601941816673556</v>
-      </c>
-      <c r="H6" s="2">
-        <v>2.6128235459211906</v>
-      </c>
-      <c r="I6" s="4">
-        <f>IFERROR(G6/H6-1, "nm")</f>
-        <v>-0.32632489307777868</v>
-      </c>
-      <c r="J6" s="4">
-        <v>3.4778213731821772E-2</v>
-      </c>
-      <c r="K6" s="4">
-        <v>5.282511210762332E-2</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="N6" s="15">
-        <v>45716</v>
-      </c>
-      <c r="O6" s="16">
-        <f>IFERROR(D6/H6-1, "nm")</f>
-        <v>-0.1465171831135732</v>
-      </c>
-      <c r="P6" s="12" t="s">
-        <v>30</v>
-      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="19"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="15"/>
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="12"/>
@@ -3221,7 +3180,7 @@
     </row>
   </sheetData>
   <autoFilter ref="B2:P2" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:P75">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:P5">
       <sortCondition ref="O2"/>
     </sortState>
   </autoFilter>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F75426-0783-46A1-B44F-850CE32C74D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29A65FD2-AE42-480F-87FC-5784783A6232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
   <si>
     <t>Name</t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t>Not Held</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low Growth </t>
   </si>
 </sst>
 </file>
@@ -756,13 +759,13 @@
         <v>25</v>
       </c>
       <c r="D3" s="2">
-        <v>14.86</v>
+        <v>14.96</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>21</v>
       </c>
       <c r="F3" s="19">
-        <v>0.19796385260234528</v>
+        <v>0.1950811274187132</v>
       </c>
       <c r="G3" s="2">
         <v>14.789930718256866</v>
@@ -775,23 +778,23 @@
         <v>-0.28227215957658158</v>
       </c>
       <c r="J3" s="4">
-        <v>0.11620144005527505</v>
+        <v>0.11542469246132268</v>
       </c>
       <c r="K3" s="4">
-        <v>9.1520861372812928E-2</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="L3" s="14" t="s">
         <v>22</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="N3" s="15">
         <v>45716</v>
       </c>
       <c r="O3" s="16">
         <f>IFERROR(D3/G3-1, "nm")</f>
-        <v>4.7376342105942548E-3</v>
+        <v>1.1498991102994127E-2</v>
       </c>
       <c r="P3" s="12" t="s">
         <v>15</v>
@@ -805,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="D4" s="2">
-        <v>7.9</v>
+        <v>7.79</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>21</v>
       </c>
       <c r="F4" s="19">
-        <v>0.11614149089878545</v>
+        <v>0.12172735692567005</v>
       </c>
       <c r="G4" s="2">
         <v>6.4501768017717804</v>
@@ -824,10 +827,10 @@
         <v>-0.28606673541699057</v>
       </c>
       <c r="J4" s="4">
-        <v>3.9354193616452378E-2</v>
+        <v>3.9909901100125003E-2</v>
       </c>
       <c r="K4" s="4">
-        <v>7.3417721518987331E-2</v>
+        <v>7.4454428754813853E-2</v>
       </c>
       <c r="L4" s="14" t="s">
         <v>22</v>
@@ -840,7 +843,7 @@
       </c>
       <c r="O4" s="16">
         <f>IFERROR(D4/G4-1, "nm")</f>
-        <v>0.2247726291518044</v>
+        <v>0.20771883304969063</v>
       </c>
       <c r="P4" s="12" t="s">
         <v>15</v>
@@ -854,29 +857,29 @@
         <v>28</v>
       </c>
       <c r="D5" s="2">
-        <v>2.23</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>21</v>
       </c>
       <c r="F5" s="19">
-        <v>6.1633064159671846E-2</v>
+        <v>6.9675781490122768E-2</v>
       </c>
       <c r="G5" s="2">
-        <v>1.5748978886562173</v>
+        <v>1.5731270460314282</v>
       </c>
       <c r="H5" s="2">
-        <v>2.2926315515979434</v>
+        <v>2.2895715355423079</v>
       </c>
       <c r="I5" s="4">
         <f>IFERROR(G5/H5-1, "nm")</f>
-        <v>-0.31306105965499442</v>
+        <v>-0.31291640308638913</v>
       </c>
       <c r="J5" s="4">
-        <v>2.0531182016336334E-2</v>
+        <v>2.0974048836286365E-2</v>
       </c>
       <c r="K5" s="4">
-        <v>5.282511210762332E-2</v>
+        <v>5.4036697247706419E-2</v>
       </c>
       <c r="L5" s="14" t="s">
         <v>29</v>
@@ -889,7 +892,7 @@
       </c>
       <c r="O5" s="16">
         <f>IFERROR(D5/G5-1, "nm")</f>
-        <v>0.41596481655248718</v>
+        <v>0.38577491595452984</v>
       </c>
       <c r="P5" s="12" t="s">
         <v>30</v>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29A65FD2-AE42-480F-87FC-5784783A6232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B46044E7-5D23-442E-8140-F3D3B5BD7396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opportunities" sheetId="1" r:id="rId1"/>
@@ -774,8 +774,8 @@
         <v>20.606600281147866</v>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(G3/H3-1, "nm")</f>
-        <v>-0.28227215957658158</v>
+        <f>IFERROR(1-G3/H3, "nm")</f>
+        <v>0.28227215957658158</v>
       </c>
       <c r="J3" s="4">
         <v>0.11542469246132268</v>
@@ -823,8 +823,8 @@
         <v>9.0347055134616365</v>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(G4/H4-1, "nm")</f>
-        <v>-0.28606673541699057</v>
+        <f>IFERROR(1-G4/H4, "nm")</f>
+        <v>0.28606673541699057</v>
       </c>
       <c r="J4" s="4">
         <v>3.9909901100125003E-2</v>
@@ -866,14 +866,14 @@
         <v>6.9675781490122768E-2</v>
       </c>
       <c r="G5" s="2">
-        <v>1.5731270460314282</v>
+        <v>1.5731270460314284</v>
       </c>
       <c r="H5" s="2">
-        <v>2.2895715355423079</v>
+        <v>2.2895715355423083</v>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(G5/H5-1, "nm")</f>
-        <v>-0.31291640308638913</v>
+        <f>IFERROR(1-G5/H5, "nm")</f>
+        <v>0.31291640308638913</v>
       </c>
       <c r="J5" s="4">
         <v>2.0974048836286365E-2</v>
@@ -892,7 +892,7 @@
       </c>
       <c r="O5" s="16">
         <f>IFERROR(D5/G5-1, "nm")</f>
-        <v>0.38577491595452984</v>
+        <v>0.38577491595452962</v>
       </c>
       <c r="P5" s="12" t="s">
         <v>30</v>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,25 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEB675F-BB1A-4697-8293-1AD639DE1770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3465B868-AA30-41FE-81C9-8E8B2429FBE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41325" yWindow="4065" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opportunities" sheetId="1" r:id="rId1"/>
-    <sheet name="Market_Yield" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="4" r:id="rId3"/>
+    <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
+    <sheet name="Opportunities" sheetId="1" r:id="rId2"/>
+    <sheet name="Market_Yield" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Opportunities!$B$2:$P$2</definedName>
-    <definedName name="stock_benchmark">Market_Yield!$C$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Opportunities!$B$2:$P$2</definedName>
+    <definedName name="benchmark">Portfolio_Mgmt!$C$10</definedName>
+    <definedName name="Cash_Yield">Portfolio_Mgmt!$C$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="146">
   <si>
     <t>Name</t>
   </si>
@@ -265,14 +266,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Benchmark rate for stocks</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stock Attractiveness</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Selected</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -285,16 +278,544 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Portfolio Allocation</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Others</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>I want to determine the optimal percentage of my AUM to hold in cash. My portfolio's target return is around 20%, and I typically aim for fewer than 10 investments. Each investment has a soft lock-up period of up to 3 years, meaning it takes a maximum of 3 years to realize the expected return.
-Currently, I have three target investments with expected returns of 19%, 11%, and 4% at their current prices. The benchmark return for investments is 9%, while cash yields 5%, implying a risk premium of 4%. While I don’t intend to time the market, I’m willing to take on some risk by waiting due to the soft lock-up period. Achieving the target return is desirable but not a strict requirement.</t>
+    <t>Cash Yield</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Executive Summary</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Portfolio Management</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>assuming a Lock-up period of</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Historical Avg Return</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Timing Risk Management</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Key Metrics:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Excess Return over Benchmark (ERB)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Excess Return over Cash (ERC)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>= Investment's Market Annual Return - Cash Yield</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Key Calculation:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decision Rules:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ERB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ERC</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Limits:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Single Investment Cap</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>= Investment's Market Annual Return - Benchmark Return</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Benchmark Return</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Benchmarket Return</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>i.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Concentration vs. Diversification Management</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ii. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">iii. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 1: Determine Risk Appetite &amp; Cash Position</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Market P/E Ratio</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Credit Spreads	</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Economic Growth Forecast	</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Investor Sentiment**	</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrow (below historical median)	</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recession expected</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Overly bullish	</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt; Historical 75th percentile	</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt; Historical 25th percentile</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wide (above historical median)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Expansion expected</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Panic/selling</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Risk Appetite Score</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Minimum Return: ERB &gt; 0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Data: Rank eligible investments by ERB.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 2: Portfolio Allocation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Filter Investment Opportunities given Criteria:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. Calculate Attractiveness:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A_i = ERB_i/Benchmark Return</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. Rank &amp; Select:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 3: Monitoring &amp; Rebalancing</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rebalance if:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Guidance Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>This Portfolio Management plan is designed to optimize returns while managing risk by balancing Timing Risk and Concentration vs. Diversification. It ensures capital is deployed effectively during favorable market conditions and maintains diversification to mitigate uncertainties.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Objective: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Deploy capital when investment opportunities exceed the benchmark return, while holding sufficient cash reserves to hedge against market uncertainty.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- Only investments with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ERB &gt; 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> are eligible for portfolio allocation.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- Cash reserves are determined by a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Risk Appetite Score</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (see Step 1).</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Objective: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Balance focused investments to maximize returns with diversified holdings to minimize risk, using defined allocation thresholds.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maximum Number of Holdings</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Notes:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Target Annual Return</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Represents the investor’s hurdle rate, guiding the expected performance of the portfolio over the lock-up period.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Cost of Equity</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Reflects the company’s risk profile and provides a consistent discount rate for valuations. Using a uniform cost of equity eliminates volatile and subjective inputs, ensuring conservative discounting of FCF and reducing downside risk.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Indicators and Scoring:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Process: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Assess market cycles using four indicators to calculate a Risk Appetite Score, which determines the portfolio’s cash allocation.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>P_i = (A_i / Sum of A_j for all selected investments) * (100% - Cash %)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Score &lt;= 2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Score 3–5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Score &gt;= 6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cash Allocation Rule:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cash Allocation Decision:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scenario</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cash Allocation</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicator	</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>Low Risk Appetite (Hold Cash)</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>High Risk Appetite (Deploy Cash)</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>Score (0-2)</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Rank investments by Attractiveness</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. Allocate with Caps:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>For each selected investment i:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Compute Initial Weights:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Enforce Single Investment Cap:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>If any P_i &gt; 10%, cap it at 10% and redistribute the excess proportionally to other investments.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>New Opportunities:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> If new investments have higher ERB than current holdings, replace underperformers.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Valuation Changes: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>IF the market annual return output by valuation model changes materially.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Market Shifts: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>If market cycle indicators change significantly, reassess the Risk Appetite Score.</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -305,9 +826,9 @@
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="177" formatCode="[$-13C09]d\ mmm\ yyyy;@"/>
-    <numFmt numFmtId="178" formatCode="&quot;for &quot;0&quot; Yrs&quot;"/>
+    <numFmt numFmtId="178" formatCode="0&quot; yrs&quot;"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -383,18 +904,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -414,8 +923,79 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="DengXian"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -443,6 +1023,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF003871"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0047AB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -503,7 +1095,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -549,38 +1141,68 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="10" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="178" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -593,6 +1215,10 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -916,6 +1542,487 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E843BBF0-63C3-41BD-B5E6-C3103399E754}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E84"/>
+  <sheetFormatPr defaultRowHeight="11.65"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.06640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.59765625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="35" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+    </row>
+    <row r="4" spans="1:5" ht="36.6" customHeight="1">
+      <c r="B4" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="34"/>
+    </row>
+    <row r="7" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B7" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="B9" s="41" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="4">
+        <f>Market_Yield!C16</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="B11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="4">
+        <f>Market_Yield!C6</f>
+        <v>3.4500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="B13" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="B14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="B17" s="41" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="B18" s="42" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="B19" s="42" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="34"/>
+    </row>
+    <row r="22" spans="1:5" ht="24.4" customHeight="1">
+      <c r="A22" s="32"/>
+      <c r="B22" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="32"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="32"/>
+      <c r="B24" s="41" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="B25" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="B26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="58">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="34"/>
+      <c r="D28" s="37"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="B29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="59">
+        <v>0.2</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="E29" s="40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="B30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="39">
+        <f>MAX(8%,Market_Yield!C4:D6)</f>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="B32" s="35" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B33" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="C33" s="53"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+    </row>
+    <row r="34" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B34" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="C34" s="53"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="B36" s="36"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="B38" s="48" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="B40" s="41" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="12.4">
+      <c r="B42" s="52" t="s">
+        <v>131</v>
+      </c>
+      <c r="C42" s="52" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="B43" s="44" t="s">
+        <v>126</v>
+      </c>
+      <c r="C43" s="50">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="B44" s="44" t="s">
+        <v>127</v>
+      </c>
+      <c r="C44" s="50">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="B45" s="44" t="s">
+        <v>128</v>
+      </c>
+      <c r="C45" s="50">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="B47" s="41" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="12.4">
+      <c r="B49" s="52" t="s">
+        <v>133</v>
+      </c>
+      <c r="C49" s="52" t="s">
+        <v>134</v>
+      </c>
+      <c r="D49" s="52" t="s">
+        <v>135</v>
+      </c>
+      <c r="E49" s="52" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="B50" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="C50" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="D50" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="E50" s="45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="B51" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C51" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="D51" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="E51" s="45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="B52" s="44" t="s">
+        <v>94</v>
+      </c>
+      <c r="C52" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="D52" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="E52" s="45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="B53" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="C53" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="D53" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="E53" s="45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="D54" s="46" t="s">
+        <v>104</v>
+      </c>
+      <c r="E54" s="49">
+        <f>SUM(E50:E53)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="B56" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="C56" s="51">
+        <f>IF(E54&lt;=2,C43,IF(E54&gt;=6,C45,C44))</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="B58" s="36"/>
+      <c r="C58" s="36"/>
+      <c r="D58" s="36"/>
+      <c r="E58" s="36"/>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="B60" s="35" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="B61" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="B62" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="B64" s="47" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="B65" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="B67" s="35" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="B68" s="42" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="B69" s="1" t="str">
+        <f>"- Select the top "&amp;C25&amp;" or fewer investments, respecting the maximum holdings limit."</f>
+        <v>- Select the top 10 or fewer investments, respecting the maximum holdings limit.</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="B71" s="35" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="B72" s="42" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="B73" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="B74" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="B76" s="42" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="B77" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="B79" s="36"/>
+      <c r="C79" s="36"/>
+      <c r="D79" s="36"/>
+      <c r="E79" s="36"/>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="35" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82" s="42" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" s="42" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84" s="42" t="s">
+        <v>144</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="93" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -928,7 +2035,7 @@
     <col min="3" max="3" width="18.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" style="2" customWidth="1"/>
     <col min="5" max="5" width="10.33203125" style="1" customWidth="1"/>
-    <col min="6" max="8" width="13.53125" style="15" customWidth="1"/>
+    <col min="6" max="8" width="10.33203125" style="15" customWidth="1"/>
     <col min="9" max="10" width="8.6640625" style="2" customWidth="1"/>
     <col min="11" max="13" width="8.6640625" style="1" customWidth="1"/>
     <col min="14" max="14" width="22.73046875" style="1" bestFit="1" customWidth="1"/>
@@ -943,27 +2050,27 @@
       <c r="B1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="36" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="36"/>
-      <c r="K1" s="37" t="s">
+      <c r="J1" s="54"/>
+      <c r="K1" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="37"/>
-      <c r="M1" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="57" t="s">
+        <v>67</v>
+      </c>
+      <c r="N1" s="57"/>
+      <c r="O1" s="57"/>
+      <c r="P1" s="57"/>
     </row>
     <row r="2" spans="1:16" ht="26" customHeight="1">
       <c r="B2" s="7" t="s">
@@ -982,10 +2089,10 @@
         <v>11</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="I2" s="8" t="s">
         <v>8</v>
@@ -1009,7 +2116,7 @@
         <v>10</v>
       </c>
       <c r="P2" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1029,12 +2136,12 @@
         <v>0.1950811274187132</v>
       </c>
       <c r="G3" s="15">
-        <f>MAX((F3-stock_benchmark)/stock_benchmark,0)</f>
-        <v>0.66167910918835771</v>
+        <f>F3-benchmark</f>
+        <v>7.7681127418713192E-2</v>
       </c>
       <c r="H3" s="15">
-        <f>G3/SUMIF($P$3:$P$5,"Y",$G$3:$G$5)</f>
-        <v>0.94723281425982819</v>
+        <f>F3-Cash_Yield</f>
+        <v>0.16058112741871319</v>
       </c>
       <c r="I3" s="2">
         <v>14.789930718256866</v>
@@ -1058,7 +2165,7 @@
         <v>45716</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1078,12 +2185,12 @@
         <v>0.12172735692567005</v>
       </c>
       <c r="G4" s="15">
-        <f>MAX((F4-stock_benchmark)/stock_benchmark,0)</f>
-        <v>3.6859939741652852E-2</v>
+        <f>F4-benchmark</f>
+        <v>4.327356925670045E-3</v>
       </c>
       <c r="H4" s="15">
-        <f>G4/SUMIF($P$3:$P$5,"Y",$G$3:$G$5)</f>
-        <v>5.2767185740171842E-2</v>
+        <f>F4-Cash_Yield</f>
+        <v>8.7227356925670047E-2</v>
       </c>
       <c r="I4" s="2">
         <v>6.4501768017717804</v>
@@ -1107,7 +2214,7 @@
         <v>45716</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1127,12 +2234,12 @@
         <v>6.9675781490122768E-2</v>
       </c>
       <c r="G5" s="15">
-        <f>MAX((F5-stock_benchmark)/stock_benchmark,0)</f>
-        <v>0</v>
+        <f>F5-benchmark</f>
+        <v>-4.7724218509877236E-2</v>
       </c>
       <c r="H5" s="15">
-        <f>MAX(G5/SUMIF($P$3:$P$5,"Y",$G$3:$G$5),0)</f>
-        <v>0</v>
+        <f>F5-Cash_Yield</f>
+        <v>3.5175781490122765E-2</v>
       </c>
       <c r="I5" s="2">
         <v>1.5731270460314284</v>
@@ -1156,7 +2263,7 @@
         <v>45716</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -3294,18 +4401,18 @@
   <mergeCells count="4">
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D1:G1"/>
     <mergeCell ref="M1:P1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="51" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+  <pageSetup scale="75" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62760D14-1F64-4D73-BBAC-22718A84BD18}">
-  <dimension ref="A2:E35"/>
+  <dimension ref="A2:E31"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="2.46484375" style="22" customWidth="1"/>
@@ -3317,291 +4424,243 @@
     <row r="2" spans="1:5" ht="15">
       <c r="A2" s="18"/>
       <c r="B2" s="19" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="21"/>
       <c r="E2" s="20"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="20"/>
-      <c r="B3" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="23">
-        <v>0.2</v>
-      </c>
-      <c r="D3" s="24">
-        <v>3</v>
-      </c>
-      <c r="E3" s="25"/>
+      <c r="C3" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="20"/>
-      <c r="B4" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="26">
-        <f>MAX(8%,C8:D10)</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15">
-      <c r="A6" s="18"/>
-      <c r="B6" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="20"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="C7" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="B8" s="28" t="s">
+      <c r="B4" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C4" s="25">
         <v>4.2500000000000003E-2</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D4" s="25">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E8" s="30">
-        <f>D8-C8</f>
+      <c r="E4" s="26">
+        <f>D4-C4</f>
         <v>3.2499999999999994E-2</v>
       </c>
     </row>
+    <row r="5" spans="1:5">
+      <c r="B5" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="25">
+        <v>1.9E-2</v>
+      </c>
+      <c r="D5" s="25">
+        <v>3.1E-2</v>
+      </c>
+      <c r="E5" s="26">
+        <f>D5-C5</f>
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="B6" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="25">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="D6" s="25">
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="E6" s="26">
+        <f>D6-C6</f>
+        <v>1.7999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15">
+      <c r="A8" s="18"/>
+      <c r="B8" s="19" t="s">
+        <v>37</v>
+      </c>
+    </row>
     <row r="9" spans="1:5">
-      <c r="B9" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="29">
-        <v>1.9E-2</v>
-      </c>
-      <c r="D9" s="29">
-        <v>3.1E-2</v>
-      </c>
-      <c r="E9" s="30">
-        <f>D9-C9</f>
-        <v>1.2E-2</v>
+      <c r="B9" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="B10" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="29">
+      <c r="B10" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="25">
+        <v>9.9400000000000002E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="B11" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="25">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="B12" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="25">
         <v>3.4500000000000003E-2</v>
       </c>
-      <c r="D10" s="29">
-        <v>5.2499999999999998E-2</v>
-      </c>
-      <c r="E10" s="30">
-        <f>D10-C10</f>
-        <v>1.7999999999999995E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15">
-      <c r="A12" s="18"/>
-      <c r="B12" s="19" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="C13" s="27" t="s">
-        <v>38</v>
+      <c r="B13" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="25">
+        <v>3.3099999999999997E-2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="B14" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="29">
-        <v>9.9400000000000002E-2</v>
+      <c r="B14" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="25">
+        <v>4.2299999999999997E-2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="B15" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="29">
+      <c r="B15" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="25">
+        <v>5.1200000000000002E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="B16" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="29">
+        <f>MAX(Portfolio_Mgmt!C30,C10:C15)</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="B16" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="29">
-        <v>3.4500000000000003E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="B17" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="29">
-        <v>3.3099999999999997E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="B18" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="29">
-        <v>4.2299999999999997E-2</v>
-      </c>
+    <row r="18" spans="1:5" ht="15">
+      <c r="A18" s="18"/>
+      <c r="B18" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="20"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="20"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="B19" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="29">
-        <v>5.1200000000000002E-2</v>
+      <c r="B19" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="B20" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="33">
-        <f>MAX(C4,C14:C19)</f>
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15">
-      <c r="A22" s="18"/>
-      <c r="B22" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="20"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="20"/>
+      <c r="B20" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="B21" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="C22" s="30"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="B23" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="34" t="s">
-        <v>47</v>
+      <c r="B23" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="B24" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="34" t="s">
-        <v>49</v>
+        <v>54</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="B25" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="34" t="s">
-        <v>51</v>
-      </c>
+      <c r="C25" s="30"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="C26" s="34"/>
+      <c r="B26" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="30" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="27" spans="1:5">
       <c r="B27" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" s="34" t="s">
-        <v>53</v>
+        <v>58</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="B28" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="34" t="s">
-        <v>55</v>
-      </c>
+      <c r="C28" s="30"/>
     </row>
     <row r="29" spans="1:5">
-      <c r="C29" s="34"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="B30" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="34" t="s">
-        <v>57</v>
+      <c r="B29" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="B31" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" s="34" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="C32" s="34"/>
-    </row>
-    <row r="33" spans="2:3">
-      <c r="B33" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="C33" s="34" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3">
-      <c r="B35" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C35" s="34" t="s">
+      <c r="C31" s="30" t="s">
         <v>63</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C27" r:id="rId1" xr:uid="{6B546AA7-2B0C-4428-81DD-DF73E91105ED}"/>
-    <hyperlink ref="C23" r:id="rId2" xr:uid="{FBF6514A-AA7C-492E-837D-9693F4B1BF61}"/>
-    <hyperlink ref="C33" r:id="rId3" xr:uid="{0B536BD0-1C9D-48D9-BE87-499C48D7A2DA}"/>
-    <hyperlink ref="C24" r:id="rId4" xr:uid="{64320D73-0C91-4543-A716-CC8C239E517C}"/>
-    <hyperlink ref="C28" r:id="rId5" xr:uid="{46AE8994-AE24-48A7-A28B-525FF601CDC5}"/>
-    <hyperlink ref="C30" r:id="rId6" xr:uid="{93438CEE-3750-4D25-A9C7-1AB257F771BF}"/>
-    <hyperlink ref="C31" r:id="rId7" xr:uid="{6BFFE2DD-44EE-4536-9535-5B23C094A18E}"/>
-    <hyperlink ref="C25" r:id="rId8" xr:uid="{343B68E0-A2FF-4A26-9F49-F7D9A2BDC147}"/>
-    <hyperlink ref="C35" r:id="rId9" xr:uid="{05CFC315-F57E-4B19-9DA2-2DADD0FC3616}"/>
+    <hyperlink ref="C23" r:id="rId1" xr:uid="{6B546AA7-2B0C-4428-81DD-DF73E91105ED}"/>
+    <hyperlink ref="C19" r:id="rId2" xr:uid="{FBF6514A-AA7C-492E-837D-9693F4B1BF61}"/>
+    <hyperlink ref="C29" r:id="rId3" xr:uid="{0B536BD0-1C9D-48D9-BE87-499C48D7A2DA}"/>
+    <hyperlink ref="C20" r:id="rId4" xr:uid="{64320D73-0C91-4543-A716-CC8C239E517C}"/>
+    <hyperlink ref="C24" r:id="rId5" xr:uid="{46AE8994-AE24-48A7-A28B-525FF601CDC5}"/>
+    <hyperlink ref="C26" r:id="rId6" xr:uid="{93438CEE-3750-4D25-A9C7-1AB257F771BF}"/>
+    <hyperlink ref="C27" r:id="rId7" xr:uid="{6BFFE2DD-44EE-4536-9535-5B23C094A18E}"/>
+    <hyperlink ref="C21" r:id="rId8" xr:uid="{343B68E0-A2FF-4A26-9F49-F7D9A2BDC147}"/>
+    <hyperlink ref="C31" r:id="rId9" xr:uid="{05CFC315-F57E-4B19-9DA2-2DADD0FC3616}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId10"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{369C36B6-834B-4D77-91B3-6CB0D60A5F89}">
-  <dimension ref="B2"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
-  <cols>
-    <col min="2" max="2" width="119.06640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:2" ht="97.15">
-      <c r="B2" s="35" t="s">
-        <v>71</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId10"/>
 </worksheet>
 </file>
--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3465B868-AA30-41FE-81C9-8E8B2429FBE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27BE6465-163E-4521-8644-5D8C8384A53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -430,19 +430,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Minimum Return: ERB &gt; 0</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Data: Rank eligible investments by ERB.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Step 2: Portfolio Allocation</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. Filter Investment Opportunities given Criteria:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -816,6 +808,14 @@
       </rPr>
       <t>If market cycle indicators change significantly, reassess the Risk Appetite Score.</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note on cost of keeping cash</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Rank Investment Opportunities given Criteria:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1201,6 +1201,10 @@
     <xf numFmtId="0" fontId="23" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1215,10 +1219,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1546,7 +1546,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
@@ -1571,12 +1571,12 @@
       <c r="E2" s="36"/>
     </row>
     <row r="4" spans="1:5" ht="36.6" customHeight="1">
-      <c r="B4" s="53" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
+      <c r="B4" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="35" t="s">
@@ -1588,12 +1588,12 @@
       <c r="C6" s="34"/>
     </row>
     <row r="7" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B7" s="53" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
+      <c r="B7" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="41" t="s">
@@ -1650,12 +1650,12 @@
     </row>
     <row r="18" spans="1:5">
       <c r="B18" s="42" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="B19" s="42" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1669,12 +1669,12 @@
     </row>
     <row r="22" spans="1:5" ht="24.4" customHeight="1">
       <c r="A22" s="32"/>
-      <c r="B22" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
+      <c r="B22" s="55" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="32"/>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="B25" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C25" s="38">
         <v>10</v>
@@ -1697,7 +1697,7 @@
       <c r="B26" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="58">
+      <c r="C26" s="53">
         <v>0.3</v>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
       <c r="B29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="59">
+      <c r="C29" s="54">
         <v>0.2</v>
       </c>
       <c r="D29" s="32" t="s">
@@ -1736,24 +1736,24 @@
     </row>
     <row r="32" spans="1:5">
       <c r="B32" s="35" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B33" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+    </row>
+    <row r="34" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B34" s="55" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B33" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="C33" s="53"/>
-      <c r="D33" s="53"/>
-      <c r="E33" s="53"/>
-    </row>
-    <row r="34" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B34" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="C34" s="53"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="53"/>
+      <c r="C34" s="55"/>
+      <c r="D34" s="55"/>
+      <c r="E34" s="55"/>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="36" t="s">
@@ -1764,27 +1764,30 @@
       <c r="D36" s="36"/>
       <c r="E36" s="36"/>
     </row>
-    <row r="38" spans="1:5">
-      <c r="B38" s="48" t="s">
-        <v>124</v>
-      </c>
+    <row r="38" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B38" s="55" t="s">
+        <v>122</v>
+      </c>
+      <c r="C38" s="55"/>
+      <c r="D38" s="55"/>
+      <c r="E38" s="55"/>
     </row>
     <row r="40" spans="1:5">
       <c r="B40" s="41" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="12.4">
       <c r="B42" s="52" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C42" s="52" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="B43" s="44" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C43" s="50">
         <v>0.5</v>
@@ -1792,7 +1795,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="B44" s="44" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C44" s="50">
         <v>0.3</v>
@@ -1800,7 +1803,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="B45" s="44" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C45" s="50">
         <v>0.2</v>
@@ -1808,21 +1811,21 @@
     </row>
     <row r="47" spans="1:5">
       <c r="B47" s="41" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="12.4">
       <c r="B49" s="52" t="s">
+        <v>131</v>
+      </c>
+      <c r="C49" s="52" t="s">
+        <v>132</v>
+      </c>
+      <c r="D49" s="52" t="s">
         <v>133</v>
       </c>
-      <c r="C49" s="52" t="s">
+      <c r="E49" s="52" t="s">
         <v>134</v>
-      </c>
-      <c r="D49" s="52" t="s">
-        <v>135</v>
-      </c>
-      <c r="E49" s="52" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1892,7 +1895,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="B56" s="41" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C56" s="51">
         <f>IF(E54&lt;=2,C43,IF(E54&gt;=6,C45,C44))</f>
@@ -1900,116 +1903,117 @@
       </c>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="36" t="s">
+      <c r="B58" s="48" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="B60" s="36"/>
+      <c r="C60" s="36"/>
+      <c r="D60" s="36"/>
+      <c r="E60" s="36"/>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="B62" s="35" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="B63" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="B65" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="B58" s="36"/>
-      <c r="C58" s="36"/>
-      <c r="D58" s="36"/>
-      <c r="E58" s="36"/>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="B60" s="35" t="s">
+    </row>
+    <row r="66" spans="1:5">
+      <c r="B66" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
-      <c r="B61" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="B62" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="B64" s="47" t="s">
+    <row r="68" spans="1:5">
+      <c r="B68" s="35" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
-      <c r="B65" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="B67" s="35" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="B68" s="42" t="s">
-        <v>137</v>
-      </c>
-    </row>
     <row r="69" spans="1:5">
-      <c r="B69" s="1" t="str">
+      <c r="B69" s="42" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="B70" s="1" t="str">
         <f>"- Select the top "&amp;C25&amp;" or fewer investments, respecting the maximum holdings limit."</f>
         <v>- Select the top 10 or fewer investments, respecting the maximum holdings limit.</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
-      <c r="B71" s="35" t="s">
+    <row r="72" spans="1:5">
+      <c r="B72" s="35" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="B73" s="42" t="s">
         <v>138</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="B72" s="42" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="B73" s="1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="B74" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="B76" s="42" t="s">
-        <v>141</v>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="B75" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="77" spans="1:5">
-      <c r="B77" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="36" t="s">
-        <v>112</v>
-      </c>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-    </row>
-    <row r="81" spans="2:2">
-      <c r="B81" s="35" t="s">
-        <v>113</v>
-      </c>
+      <c r="B77" s="42" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="B78" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="B80" s="36"/>
+      <c r="C80" s="36"/>
+      <c r="D80" s="36"/>
+      <c r="E80" s="36"/>
     </row>
     <row r="82" spans="2:2">
-      <c r="B82" s="42" t="s">
-        <v>143</v>
+      <c r="B82" s="35" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="83" spans="2:2">
       <c r="B83" s="42" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="84" spans="2:2">
       <c r="B84" s="42" t="s">
-        <v>144</v>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85" s="42" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="B38:E38"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B22:E22"/>
@@ -2050,27 +2054,27 @@
       <c r="B1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="56" t="s">
+      <c r="D1" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
       <c r="H1" s="31"/>
-      <c r="I1" s="54" t="s">
+      <c r="I1" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="54"/>
-      <c r="K1" s="55" t="s">
+      <c r="J1" s="56"/>
+      <c r="K1" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="55"/>
-      <c r="M1" s="57" t="s">
+      <c r="L1" s="57"/>
+      <c r="M1" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
     </row>
     <row r="2" spans="1:16" ht="26" customHeight="1">
       <c r="B2" s="7" t="s">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27BE6465-163E-4521-8644-5D8C8384A53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F8E314-4E37-4939-A396-ECA57E24AB65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Market_Yield" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Opportunities!$B$2:$P$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Opportunities!$B$2:$Q$2</definedName>
     <definedName name="benchmark">Portfolio_Mgmt!$C$10</definedName>
     <definedName name="Cash_Yield">Portfolio_Mgmt!$C$11</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="149">
   <si>
     <t>Name</t>
   </si>
@@ -427,10 +427,6 @@
   </si>
   <si>
     <t>Risk Appetite Score</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Data: Rank eligible investments by ERB.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -816,6 +812,43 @@
   </si>
   <si>
     <t>1. Rank Investment Opportunities given Criteria:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- Only investments with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>the Selected Flag</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> are eligible for portfolio allocation.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Data: Rank eligible investments by ERB. However, show all the opportunities in the Opportunities sheet regardless of ERB or is_selected flag</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Portfolio Management</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Allocation Percentage</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -995,7 +1028,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1035,6 +1068,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0047AB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1159,9 +1198,6 @@
     </xf>
     <xf numFmtId="10" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1218,6 +1254,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1546,7 +1585,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
@@ -1557,46 +1596,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="34" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
     </row>
     <row r="4" spans="1:5" ht="36.6" customHeight="1">
-      <c r="B4" s="55" t="s">
+      <c r="B4" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="33"/>
+    </row>
+    <row r="7" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B7" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="34"/>
-    </row>
-    <row r="7" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B7" s="55" t="s">
-        <v>113</v>
-      </c>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="40" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1622,7 +1661,7 @@
       <c r="C12" s="4"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="40" t="s">
         <v>78</v>
       </c>
       <c r="C13" s="4"/>
@@ -1631,7 +1670,7 @@
       <c r="B14" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="42" t="s">
+      <c r="C14" s="41" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1639,386 +1678,391 @@
       <c r="B15" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="42" t="s">
+      <c r="C15" s="41" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="B17" s="41" t="s">
+      <c r="B17" s="40" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="41" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="B19" s="41" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="B20" s="41" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="B19" s="42" t="s">
+    <row r="22" spans="1:5">
+      <c r="A22" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="33"/>
+    </row>
+    <row r="23" spans="1:5" ht="24.4" customHeight="1">
+      <c r="A23" s="31"/>
+      <c r="B23" s="54" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="43" t="s">
-        <v>89</v>
-      </c>
-      <c r="B21" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" s="34"/>
-    </row>
-    <row r="22" spans="1:5" ht="24.4" customHeight="1">
-      <c r="A22" s="32"/>
-      <c r="B22" s="55" t="s">
-        <v>116</v>
-      </c>
-      <c r="C22" s="55"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="55"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="32"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="32"/>
-      <c r="B24" s="41" t="s">
+      <c r="A24" s="31"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="31"/>
+      <c r="B25" s="40" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="B25" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C25" s="38">
-        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="B26" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C26" s="37">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="B27" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="53">
+      <c r="C27" s="52">
         <v>0.3</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="35" t="s">
+    <row r="29" spans="1:5">
+      <c r="A29" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="B28" s="33" t="s">
+      <c r="B29" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="34"/>
-      <c r="D28" s="37"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="B29" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="54">
-        <v>0.2</v>
-      </c>
-      <c r="D29" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="E29" s="40">
-        <v>3</v>
-      </c>
+      <c r="C29" s="33"/>
+      <c r="D29" s="36"/>
     </row>
     <row r="30" spans="1:5">
       <c r="B30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="53">
+        <v>0.2</v>
+      </c>
+      <c r="D30" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E30" s="39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="B31" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="39">
+      <c r="C31" s="38">
         <f>MAX(8%,Market_Yield!C4:D6)</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="B32" s="35" t="s">
+    <row r="33" spans="1:5">
+      <c r="B33" s="34" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B34" s="54" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B33" s="55" t="s">
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+    </row>
+    <row r="35" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B35" s="54" t="s">
         <v>119</v>
       </c>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-    </row>
-    <row r="34" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B34" s="55" t="s">
+      <c r="C35" s="54"/>
+      <c r="D35" s="54"/>
+      <c r="E35" s="54"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37" s="35"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="35"/>
+    </row>
+    <row r="39" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B39" s="54" t="s">
+        <v>121</v>
+      </c>
+      <c r="C39" s="54"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="54"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="B41" s="40" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="12.4">
+      <c r="B43" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="C43" s="51" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="B44" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="C44" s="49">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="B45" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="C45" s="49">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="B46" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="C46" s="49">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="B48" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="C34" s="55"/>
-      <c r="D34" s="55"/>
-      <c r="E34" s="55"/>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="B36" s="36"/>
-      <c r="C36" s="36"/>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
-    </row>
-    <row r="38" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B38" s="55" t="s">
+    </row>
+    <row r="50" spans="1:5" ht="12.4">
+      <c r="B50" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="C50" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="D50" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="E50" s="51" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="B51" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="D51" s="43" t="s">
+        <v>100</v>
+      </c>
+      <c r="E51" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="B52" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="C52" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="D52" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="E52" s="44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="B53" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="C53" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="D53" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="E53" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="B54" s="43" t="s">
+        <v>95</v>
+      </c>
+      <c r="C54" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="D54" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="E54" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="D55" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="E55" s="48">
+        <f>SUM(E51:E54)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="B57" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="C57" s="50">
+        <f>IF(E55&lt;=2,C44,IF(E55&gt;=6,C46,C45))</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="B59" s="47" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="B61" s="35"/>
+      <c r="C61" s="35"/>
+      <c r="D61" s="35"/>
+      <c r="E61" s="35"/>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="B63" s="34" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="B64" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="46" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" s="34" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="41" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="1" t="str">
+        <f>"- Select the top "&amp;C26&amp;" or fewer investments, respecting the maximum holdings limit."</f>
+        <v>- Select the top 10 or fewer investments, respecting the maximum holdings limit.</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" s="34" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="41" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C38" s="55"/>
-      <c r="D38" s="55"/>
-      <c r="E38" s="55"/>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="B40" s="41" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="12.4">
-      <c r="B42" s="52" t="s">
-        <v>129</v>
-      </c>
-      <c r="C42" s="52" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="B43" s="44" t="s">
-        <v>124</v>
-      </c>
-      <c r="C43" s="50">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="B44" s="44" t="s">
-        <v>125</v>
-      </c>
-      <c r="C44" s="50">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="B45" s="44" t="s">
-        <v>126</v>
-      </c>
-      <c r="C45" s="50">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="B47" s="41" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="12.4">
-      <c r="B49" s="52" t="s">
-        <v>131</v>
-      </c>
-      <c r="C49" s="52" t="s">
-        <v>132</v>
-      </c>
-      <c r="D49" s="52" t="s">
-        <v>133</v>
-      </c>
-      <c r="E49" s="52" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="B50" s="44" t="s">
-        <v>92</v>
-      </c>
-      <c r="C50" s="44" t="s">
-        <v>99</v>
-      </c>
-      <c r="D50" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="E50" s="45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="B51" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="C51" s="44" t="s">
-        <v>96</v>
-      </c>
-      <c r="D51" s="44" t="s">
-        <v>101</v>
-      </c>
-      <c r="E51" s="45">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="B52" s="44" t="s">
-        <v>94</v>
-      </c>
-      <c r="C52" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="D52" s="44" t="s">
-        <v>102</v>
-      </c>
-      <c r="E52" s="45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="B53" s="44" t="s">
-        <v>95</v>
-      </c>
-      <c r="C53" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="D53" s="44" t="s">
-        <v>103</v>
-      </c>
-      <c r="E53" s="45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="D54" s="46" t="s">
-        <v>104</v>
-      </c>
-      <c r="E54" s="49">
-        <f>SUM(E50:E53)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="B56" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="C56" s="51">
-        <f>IF(E54&lt;=2,C43,IF(E54&gt;=6,C45,C44))</f>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="B58" s="48" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="B60" s="36"/>
-      <c r="C60" s="36"/>
-      <c r="D60" s="36"/>
-      <c r="E60" s="36"/>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="B62" s="35" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="B63" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="B65" s="47" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="B66" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="B68" s="35" t="s">
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78" s="41" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="35" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="B69" s="42" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="B70" s="1" t="str">
-        <f>"- Select the top "&amp;C25&amp;" or fewer investments, respecting the maximum holdings limit."</f>
-        <v>- Select the top 10 or fewer investments, respecting the maximum holdings limit.</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="B72" s="35" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="B73" s="42" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="B74" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="B75" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="B77" s="42" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="B78" s="1" t="s">
+      <c r="B81" s="35"/>
+      <c r="C81" s="35"/>
+      <c r="D81" s="35"/>
+      <c r="E81" s="35"/>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="B83" s="34" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="B84" s="41" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="B80" s="36"/>
-      <c r="C80" s="36"/>
-      <c r="D80" s="36"/>
-      <c r="E80" s="36"/>
-    </row>
-    <row r="82" spans="2:2">
-      <c r="B82" s="35" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2">
-      <c r="B83" s="42" t="s">
+    <row r="85" spans="1:5">
+      <c r="B85" s="41" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="B86" s="41" t="s">
         <v>141</v>
-      </c>
-    </row>
-    <row r="84" spans="2:2">
-      <c r="B84" s="42" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="85" spans="2:2">
-      <c r="B85" s="42" t="s">
-        <v>142</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B39:E39"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B23:E23"/>
     <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2031,7 +2075,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P358"/>
+  <dimension ref="A1:Q358"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.46484375" style="1" customWidth="1"/>
@@ -2039,44 +2083,47 @@
     <col min="3" max="3" width="18.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" style="2" customWidth="1"/>
     <col min="5" max="5" width="10.33203125" style="1" customWidth="1"/>
-    <col min="6" max="8" width="10.33203125" style="15" customWidth="1"/>
-    <col min="9" max="10" width="8.6640625" style="2" customWidth="1"/>
-    <col min="11" max="13" width="8.6640625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="22.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.796875" style="11"/>
-    <col min="17" max="17" width="16.3984375" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="8.796875" style="1"/>
+    <col min="6" max="9" width="10.33203125" style="15" customWidth="1"/>
+    <col min="10" max="11" width="8.6640625" style="2" customWidth="1"/>
+    <col min="12" max="14" width="8.6640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="22.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.796875" style="11"/>
+    <col min="18" max="18" width="16.3984375" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="5"/>
       <c r="B1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="58" t="s">
+      <c r="D1" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="56" t="s">
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="59" t="s">
+        <v>147</v>
+      </c>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="56"/>
-      <c r="K1" s="57" t="s">
+      <c r="K1" s="55"/>
+      <c r="L1" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="57"/>
-      <c r="M1" s="59" t="s">
+      <c r="M1" s="56"/>
+      <c r="N1" s="58" t="s">
         <v>67</v>
       </c>
-      <c r="N1" s="59"/>
-      <c r="O1" s="59"/>
-      <c r="P1" s="59"/>
-    </row>
-    <row r="2" spans="1:16" ht="26" customHeight="1">
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
+      <c r="Q1" s="58"/>
+    </row>
+    <row r="2" spans="1:17" ht="26" customHeight="1">
       <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
@@ -2098,32 +2145,35 @@
       <c r="H2" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="L2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="M2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="N2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="O2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="P2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="Q2" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:17">
       <c r="B3" s="11" t="s">
         <v>19</v>
       </c>
@@ -2147,32 +2197,32 @@
         <f>F3-Cash_Yield</f>
         <v>0.16058112741871319</v>
       </c>
-      <c r="I3" s="2">
+      <c r="J3" s="2">
         <v>14.789930718256866</v>
       </c>
-      <c r="J3" s="2">
+      <c r="K3" s="2">
         <v>20.606600281147866</v>
       </c>
-      <c r="K3" s="4">
+      <c r="L3" s="4">
         <v>0.11542469246132268</v>
       </c>
-      <c r="L3" s="4">
+      <c r="M3" s="4">
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="N3" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="O3" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="14">
+      <c r="P3" s="14">
         <v>45716</v>
       </c>
-      <c r="P3" s="11" t="s">
+      <c r="Q3" s="11" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:17">
       <c r="B4" s="11" t="s">
         <v>14</v>
       </c>
@@ -2196,32 +2246,32 @@
         <f>F4-Cash_Yield</f>
         <v>8.7227356925670047E-2</v>
       </c>
-      <c r="I4" s="2">
+      <c r="J4" s="2">
         <v>6.4501768017717804</v>
       </c>
-      <c r="J4" s="2">
+      <c r="K4" s="2">
         <v>9.0347055134616365</v>
       </c>
-      <c r="K4" s="4">
+      <c r="L4" s="4">
         <v>3.9909901100125003E-2</v>
       </c>
-      <c r="L4" s="4">
+      <c r="M4" s="4">
         <v>7.4454428754813853E-2</v>
       </c>
-      <c r="M4" s="13" t="s">
+      <c r="N4" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="O4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="O4" s="14">
+      <c r="P4" s="14">
         <v>45716</v>
       </c>
-      <c r="P4" s="11" t="s">
+      <c r="Q4" s="11" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:17">
       <c r="B5" s="11" t="s">
         <v>22</v>
       </c>
@@ -2245,2168 +2295,2169 @@
         <f>F5-Cash_Yield</f>
         <v>3.5175781490122765E-2</v>
       </c>
-      <c r="I5" s="2">
+      <c r="J5" s="2">
         <v>1.5731270460314284</v>
       </c>
-      <c r="J5" s="2">
+      <c r="K5" s="2">
         <v>2.2895715355423083</v>
       </c>
-      <c r="K5" s="4">
+      <c r="L5" s="4">
         <v>2.0974048836286365E-2</v>
       </c>
-      <c r="L5" s="4">
+      <c r="M5" s="4">
         <v>5.4036697247706419E-2</v>
       </c>
-      <c r="M5" s="13" t="s">
+      <c r="N5" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="O5" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="O5" s="14">
+      <c r="P5" s="14">
         <v>45716</v>
       </c>
-      <c r="P5" s="11" t="s">
+      <c r="Q5" s="11" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:17">
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
       <c r="E6" s="12"/>
-      <c r="K6" s="4"/>
       <c r="L6" s="4"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="14"/>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="M6" s="4"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="14"/>
+    </row>
+    <row r="7" spans="1:17">
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="E7" s="12"/>
-      <c r="K7" s="4"/>
       <c r="L7" s="4"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="14"/>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="M7" s="4"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="14"/>
+    </row>
+    <row r="8" spans="1:17">
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
       <c r="E8" s="12"/>
-      <c r="K8" s="4"/>
       <c r="L8" s="4"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="14"/>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="M8" s="4"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="14"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="E9" s="12"/>
-      <c r="K9" s="4"/>
       <c r="L9" s="4"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="14"/>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="M9" s="4"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="14"/>
+    </row>
+    <row r="10" spans="1:17">
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
       <c r="E10" s="12"/>
-      <c r="K10" s="4"/>
       <c r="L10" s="4"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="14"/>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="M10" s="4"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="14"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="E11" s="12"/>
-      <c r="K11" s="4"/>
       <c r="L11" s="4"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="14"/>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="M11" s="4"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="14"/>
+    </row>
+    <row r="12" spans="1:17">
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="E12" s="12"/>
-      <c r="K12" s="4"/>
       <c r="L12" s="4"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="14"/>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="M12" s="4"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="14"/>
+    </row>
+    <row r="13" spans="1:17">
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
       <c r="E13" s="12"/>
-      <c r="K13" s="4"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="14"/>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="M13" s="4"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="14"/>
+    </row>
+    <row r="14" spans="1:17">
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
       <c r="E14" s="12"/>
-      <c r="K14" s="4"/>
       <c r="L14" s="4"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="14"/>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="M14" s="4"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="14"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
       <c r="E15" s="12"/>
-      <c r="K15" s="4"/>
       <c r="L15" s="4"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="14"/>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="M15" s="4"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="14"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
       <c r="E16" s="12"/>
-      <c r="K16" s="4"/>
       <c r="L16" s="4"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="14"/>
-    </row>
-    <row r="17" spans="2:15">
+      <c r="M16" s="4"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="14"/>
+    </row>
+    <row r="17" spans="2:16">
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="E17" s="12"/>
-      <c r="K17" s="4"/>
       <c r="L17" s="4"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="14"/>
-    </row>
-    <row r="18" spans="2:15">
+      <c r="M17" s="4"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="14"/>
+    </row>
+    <row r="18" spans="2:16">
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
       <c r="E18" s="12"/>
-      <c r="K18" s="4"/>
       <c r="L18" s="4"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="14"/>
-    </row>
-    <row r="19" spans="2:15">
+      <c r="M18" s="4"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="11"/>
+      <c r="P18" s="14"/>
+    </row>
+    <row r="19" spans="2:16">
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
       <c r="E19" s="12"/>
-      <c r="K19" s="4"/>
       <c r="L19" s="4"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="14"/>
-    </row>
-    <row r="20" spans="2:15">
+      <c r="M19" s="4"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="14"/>
+    </row>
+    <row r="20" spans="2:16">
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
       <c r="E20" s="12"/>
-      <c r="K20" s="4"/>
       <c r="L20" s="4"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="14"/>
-    </row>
-    <row r="21" spans="2:15">
+      <c r="M20" s="4"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="11"/>
+      <c r="P20" s="14"/>
+    </row>
+    <row r="21" spans="2:16">
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
       <c r="E21" s="12"/>
-      <c r="K21" s="4"/>
       <c r="L21" s="4"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="14"/>
-    </row>
-    <row r="22" spans="2:15">
+      <c r="M21" s="4"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="14"/>
+    </row>
+    <row r="22" spans="2:16">
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="E22" s="12"/>
-      <c r="K22" s="4"/>
       <c r="L22" s="4"/>
-      <c r="M22" s="13"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="14"/>
-    </row>
-    <row r="23" spans="2:15">
+      <c r="M22" s="4"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="14"/>
+    </row>
+    <row r="23" spans="2:16">
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="E23" s="12"/>
-      <c r="K23" s="4"/>
       <c r="L23" s="4"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="14"/>
-    </row>
-    <row r="24" spans="2:15">
+      <c r="M23" s="4"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="14"/>
+    </row>
+    <row r="24" spans="2:16">
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="E24" s="12"/>
-      <c r="K24" s="4"/>
       <c r="L24" s="4"/>
-      <c r="M24" s="13"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="14"/>
-    </row>
-    <row r="25" spans="2:15">
+      <c r="M24" s="4"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="14"/>
+    </row>
+    <row r="25" spans="2:16">
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="E25" s="12"/>
-      <c r="K25" s="4"/>
       <c r="L25" s="4"/>
-      <c r="M25" s="13"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="14"/>
-    </row>
-    <row r="26" spans="2:15">
+      <c r="M25" s="4"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="14"/>
+    </row>
+    <row r="26" spans="2:16">
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="E26" s="12"/>
-      <c r="K26" s="4"/>
       <c r="L26" s="4"/>
-      <c r="M26" s="13"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="14"/>
-    </row>
-    <row r="27" spans="2:15">
+      <c r="M26" s="4"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="14"/>
+    </row>
+    <row r="27" spans="2:16">
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="E27" s="12"/>
-      <c r="K27" s="4"/>
       <c r="L27" s="4"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="14"/>
-    </row>
-    <row r="28" spans="2:15">
+      <c r="M27" s="4"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="14"/>
+    </row>
+    <row r="28" spans="2:16">
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="E28" s="12"/>
-      <c r="K28" s="4"/>
       <c r="L28" s="4"/>
-      <c r="M28" s="13"/>
-      <c r="N28" s="11"/>
-      <c r="O28" s="14"/>
-    </row>
-    <row r="29" spans="2:15">
+      <c r="M28" s="4"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="11"/>
+      <c r="P28" s="14"/>
+    </row>
+    <row r="29" spans="2:16">
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
       <c r="E29" s="12"/>
-      <c r="K29" s="4"/>
       <c r="L29" s="4"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="14"/>
-    </row>
-    <row r="30" spans="2:15">
+      <c r="M29" s="4"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="14"/>
+    </row>
+    <row r="30" spans="2:16">
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="E30" s="12"/>
-      <c r="K30" s="4"/>
       <c r="L30" s="4"/>
-      <c r="M30" s="13"/>
-      <c r="N30" s="11"/>
-      <c r="O30" s="14"/>
-    </row>
-    <row r="31" spans="2:15">
+      <c r="M30" s="4"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="11"/>
+      <c r="P30" s="14"/>
+    </row>
+    <row r="31" spans="2:16">
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="E31" s="12"/>
-      <c r="K31" s="4"/>
       <c r="L31" s="4"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="11"/>
-      <c r="O31" s="14"/>
-    </row>
-    <row r="32" spans="2:15">
+      <c r="M31" s="4"/>
+      <c r="N31" s="16"/>
+      <c r="O31" s="11"/>
+      <c r="P31" s="14"/>
+    </row>
+    <row r="32" spans="2:16">
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
       <c r="E32" s="12"/>
-      <c r="K32" s="4"/>
       <c r="L32" s="4"/>
-      <c r="M32" s="13"/>
-      <c r="N32" s="11"/>
-      <c r="O32" s="14"/>
-    </row>
-    <row r="33" spans="2:15">
+      <c r="M32" s="4"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="11"/>
+      <c r="P32" s="14"/>
+    </row>
+    <row r="33" spans="2:16">
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
       <c r="E33" s="12"/>
-      <c r="K33" s="4"/>
       <c r="L33" s="4"/>
-      <c r="M33" s="13"/>
-      <c r="N33" s="11"/>
-      <c r="O33" s="14"/>
-    </row>
-    <row r="34" spans="2:15">
+      <c r="M33" s="4"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="11"/>
+      <c r="P33" s="14"/>
+    </row>
+    <row r="34" spans="2:16">
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="E34" s="12"/>
-      <c r="K34" s="4"/>
       <c r="L34" s="4"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="11"/>
-      <c r="O34" s="14"/>
-    </row>
-    <row r="35" spans="2:15">
+      <c r="M34" s="4"/>
+      <c r="N34" s="16"/>
+      <c r="O34" s="11"/>
+      <c r="P34" s="14"/>
+    </row>
+    <row r="35" spans="2:16">
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
       <c r="E35" s="12"/>
-      <c r="K35" s="4"/>
       <c r="L35" s="4"/>
-      <c r="M35" s="13"/>
-      <c r="N35" s="11"/>
-      <c r="O35" s="14"/>
-    </row>
-    <row r="36" spans="2:15">
+      <c r="M35" s="4"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="11"/>
+      <c r="P35" s="14"/>
+    </row>
+    <row r="36" spans="2:16">
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
       <c r="E36" s="12"/>
-      <c r="K36" s="4"/>
       <c r="L36" s="4"/>
-      <c r="M36" s="13"/>
-      <c r="N36" s="11"/>
-      <c r="O36" s="14"/>
-    </row>
-    <row r="37" spans="2:15">
+      <c r="M36" s="4"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="11"/>
+      <c r="P36" s="14"/>
+    </row>
+    <row r="37" spans="2:16">
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
       <c r="E37" s="12"/>
-      <c r="K37" s="4"/>
       <c r="L37" s="4"/>
-      <c r="M37" s="13"/>
-      <c r="N37" s="11"/>
-      <c r="O37" s="14"/>
-    </row>
-    <row r="38" spans="2:15">
+      <c r="M37" s="4"/>
+      <c r="N37" s="13"/>
+      <c r="O37" s="11"/>
+      <c r="P37" s="14"/>
+    </row>
+    <row r="38" spans="2:16">
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
       <c r="E38" s="12"/>
-      <c r="K38" s="4"/>
       <c r="L38" s="4"/>
-      <c r="M38" s="13"/>
-      <c r="N38" s="11"/>
-      <c r="O38" s="14"/>
-    </row>
-    <row r="39" spans="2:15">
+      <c r="M38" s="4"/>
+      <c r="N38" s="13"/>
+      <c r="O38" s="11"/>
+      <c r="P38" s="14"/>
+    </row>
+    <row r="39" spans="2:16">
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
       <c r="E39" s="12"/>
-      <c r="K39" s="4"/>
       <c r="L39" s="4"/>
-      <c r="M39" s="13"/>
-      <c r="N39" s="11"/>
-      <c r="O39" s="14"/>
-    </row>
-    <row r="40" spans="2:15">
+      <c r="M39" s="4"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="11"/>
+      <c r="P39" s="14"/>
+    </row>
+    <row r="40" spans="2:16">
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
       <c r="E40" s="12"/>
-      <c r="K40" s="4"/>
       <c r="L40" s="4"/>
-      <c r="M40" s="13"/>
-      <c r="N40" s="11"/>
-      <c r="O40" s="14"/>
-    </row>
-    <row r="41" spans="2:15">
+      <c r="M40" s="4"/>
+      <c r="N40" s="13"/>
+      <c r="O40" s="11"/>
+      <c r="P40" s="14"/>
+    </row>
+    <row r="41" spans="2:16">
       <c r="B41" s="11"/>
       <c r="C41" s="11"/>
       <c r="E41" s="12"/>
-      <c r="K41" s="4"/>
       <c r="L41" s="4"/>
-      <c r="M41" s="13"/>
-      <c r="N41" s="11"/>
-      <c r="O41" s="14"/>
-    </row>
-    <row r="42" spans="2:15">
+      <c r="M41" s="4"/>
+      <c r="N41" s="13"/>
+      <c r="O41" s="11"/>
+      <c r="P41" s="14"/>
+    </row>
+    <row r="42" spans="2:16">
       <c r="B42" s="11"/>
       <c r="C42" s="11"/>
       <c r="E42" s="12"/>
-      <c r="K42" s="4"/>
       <c r="L42" s="4"/>
-      <c r="M42" s="13"/>
-      <c r="N42" s="11"/>
-      <c r="O42" s="14"/>
-    </row>
-    <row r="43" spans="2:15">
+      <c r="M42" s="4"/>
+      <c r="N42" s="13"/>
+      <c r="O42" s="11"/>
+      <c r="P42" s="14"/>
+    </row>
+    <row r="43" spans="2:16">
       <c r="B43" s="11"/>
       <c r="C43" s="11"/>
       <c r="E43" s="12"/>
-      <c r="K43" s="4"/>
       <c r="L43" s="4"/>
-      <c r="M43" s="13"/>
-      <c r="N43" s="11"/>
-      <c r="O43" s="14"/>
-    </row>
-    <row r="44" spans="2:15">
+      <c r="M43" s="4"/>
+      <c r="N43" s="13"/>
+      <c r="O43" s="11"/>
+      <c r="P43" s="14"/>
+    </row>
+    <row r="44" spans="2:16">
       <c r="B44" s="11"/>
       <c r="C44" s="11"/>
       <c r="E44" s="12"/>
-      <c r="K44" s="4"/>
       <c r="L44" s="4"/>
-      <c r="M44" s="13"/>
-      <c r="N44" s="11"/>
-      <c r="O44" s="14"/>
-    </row>
-    <row r="45" spans="2:15">
+      <c r="M44" s="4"/>
+      <c r="N44" s="13"/>
+      <c r="O44" s="11"/>
+      <c r="P44" s="14"/>
+    </row>
+    <row r="45" spans="2:16">
       <c r="B45" s="11"/>
       <c r="C45" s="11"/>
       <c r="E45" s="12"/>
-      <c r="K45" s="4"/>
       <c r="L45" s="4"/>
-      <c r="M45" s="13"/>
-      <c r="N45" s="11"/>
-      <c r="O45" s="14"/>
-    </row>
-    <row r="46" spans="2:15">
+      <c r="M45" s="4"/>
+      <c r="N45" s="13"/>
+      <c r="O45" s="11"/>
+      <c r="P45" s="14"/>
+    </row>
+    <row r="46" spans="2:16">
       <c r="B46" s="11"/>
       <c r="C46" s="11"/>
       <c r="E46" s="12"/>
-      <c r="K46" s="4"/>
       <c r="L46" s="4"/>
-      <c r="M46" s="13"/>
-      <c r="N46" s="11"/>
-      <c r="O46" s="14"/>
-    </row>
-    <row r="47" spans="2:15">
+      <c r="M46" s="4"/>
+      <c r="N46" s="13"/>
+      <c r="O46" s="11"/>
+      <c r="P46" s="14"/>
+    </row>
+    <row r="47" spans="2:16">
       <c r="B47" s="11"/>
       <c r="C47" s="11"/>
       <c r="E47" s="12"/>
-      <c r="K47" s="4"/>
       <c r="L47" s="4"/>
-      <c r="M47" s="13"/>
-      <c r="N47" s="11"/>
-      <c r="O47" s="14"/>
-    </row>
-    <row r="48" spans="2:15">
+      <c r="M47" s="4"/>
+      <c r="N47" s="13"/>
+      <c r="O47" s="11"/>
+      <c r="P47" s="14"/>
+    </row>
+    <row r="48" spans="2:16">
       <c r="B48" s="11"/>
       <c r="C48" s="11"/>
       <c r="E48" s="12"/>
-      <c r="K48" s="4"/>
       <c r="L48" s="4"/>
-      <c r="M48" s="13"/>
-      <c r="N48" s="11"/>
-      <c r="O48" s="14"/>
-    </row>
-    <row r="49" spans="2:15">
+      <c r="M48" s="4"/>
+      <c r="N48" s="13"/>
+      <c r="O48" s="11"/>
+      <c r="P48" s="14"/>
+    </row>
+    <row r="49" spans="2:16">
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
       <c r="E49" s="12"/>
-      <c r="K49" s="4"/>
       <c r="L49" s="4"/>
-      <c r="M49" s="13"/>
-      <c r="N49" s="11"/>
-      <c r="O49" s="14"/>
-    </row>
-    <row r="50" spans="2:15">
+      <c r="M49" s="4"/>
+      <c r="N49" s="13"/>
+      <c r="O49" s="11"/>
+      <c r="P49" s="14"/>
+    </row>
+    <row r="50" spans="2:16">
       <c r="B50" s="11"/>
       <c r="C50" s="11"/>
       <c r="E50" s="12"/>
-      <c r="K50" s="4"/>
       <c r="L50" s="4"/>
-      <c r="M50" s="13"/>
-      <c r="N50" s="11"/>
-      <c r="O50" s="14"/>
-    </row>
-    <row r="51" spans="2:15">
+      <c r="M50" s="4"/>
+      <c r="N50" s="13"/>
+      <c r="O50" s="11"/>
+      <c r="P50" s="14"/>
+    </row>
+    <row r="51" spans="2:16">
       <c r="B51" s="11"/>
       <c r="C51" s="11"/>
       <c r="E51" s="12"/>
-      <c r="K51" s="4"/>
       <c r="L51" s="4"/>
-      <c r="M51" s="13"/>
-      <c r="N51" s="11"/>
-      <c r="O51" s="14"/>
-    </row>
-    <row r="52" spans="2:15">
+      <c r="M51" s="4"/>
+      <c r="N51" s="13"/>
+      <c r="O51" s="11"/>
+      <c r="P51" s="14"/>
+    </row>
+    <row r="52" spans="2:16">
       <c r="B52" s="11"/>
       <c r="C52" s="11"/>
       <c r="E52" s="12"/>
-      <c r="K52" s="4"/>
       <c r="L52" s="4"/>
-      <c r="M52" s="13"/>
-      <c r="N52" s="11"/>
-      <c r="O52" s="14"/>
-    </row>
-    <row r="53" spans="2:15">
+      <c r="M52" s="4"/>
+      <c r="N52" s="13"/>
+      <c r="O52" s="11"/>
+      <c r="P52" s="14"/>
+    </row>
+    <row r="53" spans="2:16">
       <c r="B53" s="11"/>
       <c r="C53" s="11"/>
       <c r="E53" s="12"/>
-      <c r="K53" s="4"/>
       <c r="L53" s="4"/>
-      <c r="M53" s="13"/>
-      <c r="N53" s="11"/>
-      <c r="O53" s="14"/>
-    </row>
-    <row r="54" spans="2:15">
+      <c r="M53" s="4"/>
+      <c r="N53" s="13"/>
+      <c r="O53" s="11"/>
+      <c r="P53" s="14"/>
+    </row>
+    <row r="54" spans="2:16">
       <c r="B54" s="11"/>
       <c r="C54" s="11"/>
       <c r="E54" s="12"/>
-      <c r="K54" s="4"/>
       <c r="L54" s="4"/>
-      <c r="M54" s="13"/>
-      <c r="N54" s="11"/>
-      <c r="O54" s="14"/>
-    </row>
-    <row r="55" spans="2:15">
+      <c r="M54" s="4"/>
+      <c r="N54" s="13"/>
+      <c r="O54" s="11"/>
+      <c r="P54" s="14"/>
+    </row>
+    <row r="55" spans="2:16">
       <c r="B55" s="11"/>
       <c r="C55" s="11"/>
       <c r="E55" s="12"/>
-      <c r="K55" s="4"/>
       <c r="L55" s="4"/>
-      <c r="M55" s="13"/>
-      <c r="N55" s="11"/>
-      <c r="O55" s="14"/>
-    </row>
-    <row r="56" spans="2:15">
+      <c r="M55" s="4"/>
+      <c r="N55" s="13"/>
+      <c r="O55" s="11"/>
+      <c r="P55" s="14"/>
+    </row>
+    <row r="56" spans="2:16">
       <c r="B56" s="11"/>
       <c r="C56" s="11"/>
       <c r="E56" s="12"/>
-      <c r="K56" s="4"/>
       <c r="L56" s="4"/>
-      <c r="M56" s="13"/>
-      <c r="N56" s="11"/>
-      <c r="O56" s="14"/>
-    </row>
-    <row r="57" spans="2:15">
+      <c r="M56" s="4"/>
+      <c r="N56" s="13"/>
+      <c r="O56" s="11"/>
+      <c r="P56" s="14"/>
+    </row>
+    <row r="57" spans="2:16">
       <c r="B57" s="11"/>
       <c r="C57" s="11"/>
       <c r="E57" s="12"/>
-      <c r="K57" s="4"/>
       <c r="L57" s="4"/>
-      <c r="M57" s="13"/>
-      <c r="N57" s="11"/>
-      <c r="O57" s="14"/>
-    </row>
-    <row r="58" spans="2:15">
+      <c r="M57" s="4"/>
+      <c r="N57" s="13"/>
+      <c r="O57" s="11"/>
+      <c r="P57" s="14"/>
+    </row>
+    <row r="58" spans="2:16">
       <c r="B58" s="11"/>
       <c r="C58" s="11"/>
       <c r="E58" s="12"/>
-      <c r="K58" s="4"/>
       <c r="L58" s="4"/>
-      <c r="M58" s="13"/>
-      <c r="N58" s="11"/>
-      <c r="O58" s="14"/>
-    </row>
-    <row r="59" spans="2:15">
+      <c r="M58" s="4"/>
+      <c r="N58" s="13"/>
+      <c r="O58" s="11"/>
+      <c r="P58" s="14"/>
+    </row>
+    <row r="59" spans="2:16">
       <c r="B59" s="11"/>
       <c r="C59" s="11"/>
       <c r="E59" s="12"/>
-      <c r="K59" s="4"/>
       <c r="L59" s="4"/>
-      <c r="M59" s="13"/>
-      <c r="N59" s="11"/>
-      <c r="O59" s="14"/>
-    </row>
-    <row r="60" spans="2:15">
+      <c r="M59" s="4"/>
+      <c r="N59" s="13"/>
+      <c r="O59" s="11"/>
+      <c r="P59" s="14"/>
+    </row>
+    <row r="60" spans="2:16">
       <c r="B60" s="11"/>
       <c r="C60" s="11"/>
       <c r="E60" s="12"/>
-      <c r="K60" s="4"/>
       <c r="L60" s="4"/>
-      <c r="M60" s="13"/>
-      <c r="N60" s="11"/>
-      <c r="O60" s="14"/>
-    </row>
-    <row r="61" spans="2:15">
+      <c r="M60" s="4"/>
+      <c r="N60" s="13"/>
+      <c r="O60" s="11"/>
+      <c r="P60" s="14"/>
+    </row>
+    <row r="61" spans="2:16">
       <c r="B61" s="11"/>
       <c r="C61" s="11"/>
       <c r="E61" s="12"/>
-      <c r="K61" s="4"/>
       <c r="L61" s="4"/>
-      <c r="M61" s="13"/>
-      <c r="N61" s="11"/>
-      <c r="O61" s="14"/>
-    </row>
-    <row r="62" spans="2:15">
+      <c r="M61" s="4"/>
+      <c r="N61" s="13"/>
+      <c r="O61" s="11"/>
+      <c r="P61" s="14"/>
+    </row>
+    <row r="62" spans="2:16">
       <c r="B62" s="11"/>
       <c r="C62" s="11"/>
       <c r="E62" s="12"/>
-      <c r="K62" s="4"/>
       <c r="L62" s="4"/>
-      <c r="M62" s="13"/>
-      <c r="N62" s="11"/>
-      <c r="O62" s="14"/>
-    </row>
-    <row r="63" spans="2:15">
+      <c r="M62" s="4"/>
+      <c r="N62" s="13"/>
+      <c r="O62" s="11"/>
+      <c r="P62" s="14"/>
+    </row>
+    <row r="63" spans="2:16">
       <c r="B63" s="11"/>
       <c r="C63" s="11"/>
       <c r="E63" s="12"/>
-      <c r="K63" s="4"/>
       <c r="L63" s="4"/>
-      <c r="M63" s="13"/>
-      <c r="N63" s="11"/>
-      <c r="O63" s="14"/>
-    </row>
-    <row r="64" spans="2:15">
+      <c r="M63" s="4"/>
+      <c r="N63" s="13"/>
+      <c r="O63" s="11"/>
+      <c r="P63" s="14"/>
+    </row>
+    <row r="64" spans="2:16">
       <c r="B64" s="11"/>
       <c r="C64" s="11"/>
       <c r="E64" s="12"/>
-      <c r="K64" s="4"/>
       <c r="L64" s="4"/>
-      <c r="M64" s="13"/>
-      <c r="N64" s="11"/>
-      <c r="O64" s="14"/>
-    </row>
-    <row r="65" spans="2:15">
+      <c r="M64" s="4"/>
+      <c r="N64" s="13"/>
+      <c r="O64" s="11"/>
+      <c r="P64" s="14"/>
+    </row>
+    <row r="65" spans="2:16">
       <c r="B65" s="11"/>
       <c r="C65" s="11"/>
       <c r="E65" s="12"/>
-      <c r="K65" s="4"/>
       <c r="L65" s="4"/>
-      <c r="M65" s="13"/>
-      <c r="N65" s="11"/>
-      <c r="O65" s="14"/>
-    </row>
-    <row r="66" spans="2:15">
+      <c r="M65" s="4"/>
+      <c r="N65" s="13"/>
+      <c r="O65" s="11"/>
+      <c r="P65" s="14"/>
+    </row>
+    <row r="66" spans="2:16">
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
       <c r="E66" s="12"/>
-      <c r="K66" s="4"/>
       <c r="L66" s="4"/>
-      <c r="M66" s="13"/>
-      <c r="N66" s="11"/>
-      <c r="O66" s="14"/>
-    </row>
-    <row r="67" spans="2:15">
+      <c r="M66" s="4"/>
+      <c r="N66" s="13"/>
+      <c r="O66" s="11"/>
+      <c r="P66" s="14"/>
+    </row>
+    <row r="67" spans="2:16">
       <c r="B67" s="11"/>
       <c r="C67" s="11"/>
       <c r="E67" s="12"/>
-      <c r="K67" s="4"/>
       <c r="L67" s="4"/>
-      <c r="M67" s="13"/>
-      <c r="N67" s="11"/>
-      <c r="O67" s="14"/>
-    </row>
-    <row r="68" spans="2:15">
+      <c r="M67" s="4"/>
+      <c r="N67" s="13"/>
+      <c r="O67" s="11"/>
+      <c r="P67" s="14"/>
+    </row>
+    <row r="68" spans="2:16">
       <c r="B68" s="11"/>
       <c r="C68" s="11"/>
       <c r="E68" s="12"/>
-      <c r="K68" s="4"/>
       <c r="L68" s="4"/>
-      <c r="M68" s="13"/>
-      <c r="N68" s="11"/>
-      <c r="O68" s="14"/>
-    </row>
-    <row r="69" spans="2:15">
+      <c r="M68" s="4"/>
+      <c r="N68" s="13"/>
+      <c r="O68" s="11"/>
+      <c r="P68" s="14"/>
+    </row>
+    <row r="69" spans="2:16">
       <c r="B69" s="11"/>
       <c r="C69" s="11"/>
       <c r="E69" s="12"/>
-      <c r="K69" s="4"/>
       <c r="L69" s="4"/>
-      <c r="M69" s="13"/>
-      <c r="N69" s="11"/>
-      <c r="O69" s="14"/>
-    </row>
-    <row r="70" spans="2:15">
+      <c r="M69" s="4"/>
+      <c r="N69" s="13"/>
+      <c r="O69" s="11"/>
+      <c r="P69" s="14"/>
+    </row>
+    <row r="70" spans="2:16">
       <c r="B70" s="11"/>
       <c r="C70" s="11"/>
       <c r="E70" s="12"/>
-      <c r="K70" s="4"/>
       <c r="L70" s="4"/>
-      <c r="M70" s="13"/>
-      <c r="N70" s="11"/>
-      <c r="O70" s="14"/>
-    </row>
-    <row r="71" spans="2:15">
+      <c r="M70" s="4"/>
+      <c r="N70" s="13"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="14"/>
+    </row>
+    <row r="71" spans="2:16">
       <c r="B71" s="11"/>
       <c r="C71" s="11"/>
       <c r="E71" s="12"/>
-      <c r="K71" s="4"/>
       <c r="L71" s="4"/>
-      <c r="M71" s="13"/>
-      <c r="N71" s="11"/>
-      <c r="O71" s="14"/>
-    </row>
-    <row r="72" spans="2:15">
+      <c r="M71" s="4"/>
+      <c r="N71" s="13"/>
+      <c r="O71" s="11"/>
+      <c r="P71" s="14"/>
+    </row>
+    <row r="72" spans="2:16">
       <c r="B72" s="11"/>
       <c r="C72" s="11"/>
       <c r="E72" s="12"/>
-      <c r="K72" s="4"/>
       <c r="L72" s="4"/>
-      <c r="M72" s="13"/>
-      <c r="N72" s="11"/>
-      <c r="O72" s="14"/>
-    </row>
-    <row r="73" spans="2:15">
+      <c r="M72" s="4"/>
+      <c r="N72" s="13"/>
+      <c r="O72" s="11"/>
+      <c r="P72" s="14"/>
+    </row>
+    <row r="73" spans="2:16">
       <c r="B73" s="11"/>
       <c r="C73" s="11"/>
       <c r="E73" s="12"/>
-      <c r="K73" s="4"/>
       <c r="L73" s="4"/>
-      <c r="M73" s="13"/>
-      <c r="N73" s="11"/>
-      <c r="O73" s="14"/>
-    </row>
-    <row r="74" spans="2:15">
+      <c r="M73" s="4"/>
+      <c r="N73" s="13"/>
+      <c r="O73" s="11"/>
+      <c r="P73" s="14"/>
+    </row>
+    <row r="74" spans="2:16">
       <c r="B74" s="11"/>
       <c r="C74" s="11"/>
       <c r="E74" s="12"/>
-      <c r="K74" s="4"/>
       <c r="L74" s="4"/>
-      <c r="M74" s="13"/>
-      <c r="N74" s="11"/>
-      <c r="O74" s="14"/>
-    </row>
-    <row r="75" spans="2:15">
+      <c r="M74" s="4"/>
+      <c r="N74" s="13"/>
+      <c r="O74" s="11"/>
+      <c r="P74" s="14"/>
+    </row>
+    <row r="75" spans="2:16">
       <c r="B75" s="11"/>
       <c r="C75" s="11"/>
       <c r="E75" s="12"/>
-      <c r="K75" s="4"/>
       <c r="L75" s="4"/>
-      <c r="M75" s="13"/>
-      <c r="N75" s="11"/>
-      <c r="O75" s="14"/>
-    </row>
-    <row r="76" spans="2:15">
+      <c r="M75" s="4"/>
+      <c r="N75" s="13"/>
+      <c r="O75" s="11"/>
+      <c r="P75" s="14"/>
+    </row>
+    <row r="76" spans="2:16">
       <c r="B76" s="11"/>
       <c r="C76" s="11"/>
       <c r="E76" s="12"/>
-      <c r="K76" s="4"/>
       <c r="L76" s="4"/>
-      <c r="M76" s="13"/>
-      <c r="N76" s="11"/>
-      <c r="O76" s="14"/>
-    </row>
-    <row r="77" spans="2:15">
+      <c r="M76" s="4"/>
+      <c r="N76" s="13"/>
+      <c r="O76" s="11"/>
+      <c r="P76" s="14"/>
+    </row>
+    <row r="77" spans="2:16">
       <c r="B77" s="11"/>
       <c r="C77" s="11"/>
       <c r="E77" s="12"/>
-      <c r="K77" s="4"/>
       <c r="L77" s="4"/>
-      <c r="M77" s="13"/>
-      <c r="N77" s="11"/>
-      <c r="O77" s="14"/>
-    </row>
-    <row r="78" spans="2:15">
+      <c r="M77" s="4"/>
+      <c r="N77" s="13"/>
+      <c r="O77" s="11"/>
+      <c r="P77" s="14"/>
+    </row>
+    <row r="78" spans="2:16">
       <c r="B78" s="11"/>
       <c r="C78" s="11"/>
       <c r="E78" s="12"/>
-      <c r="K78" s="4"/>
       <c r="L78" s="4"/>
-      <c r="M78" s="13"/>
-      <c r="N78" s="11"/>
-      <c r="O78" s="14"/>
-    </row>
-    <row r="79" spans="2:15">
+      <c r="M78" s="4"/>
+      <c r="N78" s="13"/>
+      <c r="O78" s="11"/>
+      <c r="P78" s="14"/>
+    </row>
+    <row r="79" spans="2:16">
       <c r="B79" s="11"/>
       <c r="C79" s="11"/>
       <c r="E79" s="12"/>
-      <c r="K79" s="4"/>
       <c r="L79" s="4"/>
-      <c r="M79" s="13"/>
-      <c r="N79" s="11"/>
-      <c r="O79" s="14"/>
-    </row>
-    <row r="80" spans="2:15">
+      <c r="M79" s="4"/>
+      <c r="N79" s="13"/>
+      <c r="O79" s="11"/>
+      <c r="P79" s="14"/>
+    </row>
+    <row r="80" spans="2:16">
       <c r="B80" s="11"/>
       <c r="C80" s="11"/>
       <c r="E80" s="12"/>
-      <c r="K80" s="4"/>
       <c r="L80" s="4"/>
-      <c r="M80" s="13"/>
-      <c r="N80" s="11"/>
-      <c r="O80" s="14"/>
-    </row>
-    <row r="81" spans="2:15">
+      <c r="M80" s="4"/>
+      <c r="N80" s="13"/>
+      <c r="O80" s="11"/>
+      <c r="P80" s="14"/>
+    </row>
+    <row r="81" spans="2:16">
       <c r="B81" s="11"/>
       <c r="C81" s="11"/>
       <c r="E81" s="12"/>
-      <c r="K81" s="4"/>
       <c r="L81" s="4"/>
-      <c r="M81" s="13"/>
-      <c r="N81" s="11"/>
-      <c r="O81" s="14"/>
-    </row>
-    <row r="82" spans="2:15">
+      <c r="M81" s="4"/>
+      <c r="N81" s="13"/>
+      <c r="O81" s="11"/>
+      <c r="P81" s="14"/>
+    </row>
+    <row r="82" spans="2:16">
       <c r="B82" s="11"/>
       <c r="C82" s="11"/>
       <c r="E82" s="12"/>
-      <c r="K82" s="4"/>
       <c r="L82" s="4"/>
-      <c r="M82" s="13"/>
-      <c r="N82" s="11"/>
-      <c r="O82" s="14"/>
-    </row>
-    <row r="83" spans="2:15">
+      <c r="M82" s="4"/>
+      <c r="N82" s="13"/>
+      <c r="O82" s="11"/>
+      <c r="P82" s="14"/>
+    </row>
+    <row r="83" spans="2:16">
       <c r="B83" s="11"/>
       <c r="C83" s="11"/>
       <c r="E83" s="12"/>
-      <c r="K83" s="4"/>
       <c r="L83" s="4"/>
-      <c r="M83" s="13"/>
-      <c r="N83" s="11"/>
-      <c r="O83" s="14"/>
-    </row>
-    <row r="84" spans="2:15">
+      <c r="M83" s="4"/>
+      <c r="N83" s="13"/>
+      <c r="O83" s="11"/>
+      <c r="P83" s="14"/>
+    </row>
+    <row r="84" spans="2:16">
       <c r="B84" s="11"/>
       <c r="C84" s="11"/>
       <c r="E84" s="12"/>
-      <c r="K84" s="4"/>
       <c r="L84" s="4"/>
-      <c r="M84" s="13"/>
-      <c r="N84" s="11"/>
-      <c r="O84" s="14"/>
-    </row>
-    <row r="85" spans="2:15">
+      <c r="M84" s="4"/>
+      <c r="N84" s="13"/>
+      <c r="O84" s="11"/>
+      <c r="P84" s="14"/>
+    </row>
+    <row r="85" spans="2:16">
       <c r="B85" s="11"/>
       <c r="C85" s="11"/>
       <c r="E85" s="12"/>
-      <c r="K85" s="4"/>
       <c r="L85" s="4"/>
-      <c r="M85" s="13"/>
-      <c r="N85" s="11"/>
-      <c r="O85" s="14"/>
-    </row>
-    <row r="86" spans="2:15">
+      <c r="M85" s="4"/>
+      <c r="N85" s="13"/>
+      <c r="O85" s="11"/>
+      <c r="P85" s="14"/>
+    </row>
+    <row r="86" spans="2:16">
       <c r="B86" s="11"/>
       <c r="C86" s="11"/>
       <c r="E86" s="12"/>
-      <c r="K86" s="4"/>
       <c r="L86" s="4"/>
-      <c r="M86" s="13"/>
-      <c r="N86" s="11"/>
-      <c r="O86" s="14"/>
-    </row>
-    <row r="87" spans="2:15">
+      <c r="M86" s="4"/>
+      <c r="N86" s="13"/>
+      <c r="O86" s="11"/>
+      <c r="P86" s="14"/>
+    </row>
+    <row r="87" spans="2:16">
       <c r="B87" s="11"/>
       <c r="C87" s="11"/>
       <c r="E87" s="12"/>
-      <c r="K87" s="4"/>
       <c r="L87" s="4"/>
-      <c r="M87" s="13"/>
-      <c r="N87" s="11"/>
-      <c r="O87" s="14"/>
-    </row>
-    <row r="88" spans="2:15">
+      <c r="M87" s="4"/>
+      <c r="N87" s="13"/>
+      <c r="O87" s="11"/>
+      <c r="P87" s="14"/>
+    </row>
+    <row r="88" spans="2:16">
       <c r="B88" s="11"/>
       <c r="C88" s="11"/>
       <c r="E88" s="12"/>
-      <c r="K88" s="4"/>
       <c r="L88" s="4"/>
-      <c r="M88" s="13"/>
-      <c r="N88" s="11"/>
-      <c r="O88" s="14"/>
-    </row>
-    <row r="89" spans="2:15">
+      <c r="M88" s="4"/>
+      <c r="N88" s="13"/>
+      <c r="O88" s="11"/>
+      <c r="P88" s="14"/>
+    </row>
+    <row r="89" spans="2:16">
       <c r="B89" s="11"/>
       <c r="C89" s="11"/>
       <c r="E89" s="12"/>
-      <c r="K89" s="4"/>
       <c r="L89" s="4"/>
-      <c r="M89" s="13"/>
-      <c r="N89" s="11"/>
-      <c r="O89" s="14"/>
-    </row>
-    <row r="90" spans="2:15">
+      <c r="M89" s="4"/>
+      <c r="N89" s="13"/>
+      <c r="O89" s="11"/>
+      <c r="P89" s="14"/>
+    </row>
+    <row r="90" spans="2:16">
       <c r="B90" s="11"/>
       <c r="C90" s="11"/>
       <c r="E90" s="12"/>
-      <c r="K90" s="4"/>
       <c r="L90" s="4"/>
-      <c r="M90" s="13"/>
-      <c r="N90" s="11"/>
-      <c r="O90" s="14"/>
-    </row>
-    <row r="91" spans="2:15">
+      <c r="M90" s="4"/>
+      <c r="N90" s="13"/>
+      <c r="O90" s="11"/>
+      <c r="P90" s="14"/>
+    </row>
+    <row r="91" spans="2:16">
       <c r="B91" s="11"/>
       <c r="C91" s="11"/>
       <c r="E91" s="12"/>
-      <c r="K91" s="4"/>
       <c r="L91" s="4"/>
-      <c r="M91" s="13"/>
-      <c r="N91" s="11"/>
-      <c r="O91" s="14"/>
-    </row>
-    <row r="92" spans="2:15">
+      <c r="M91" s="4"/>
+      <c r="N91" s="13"/>
+      <c r="O91" s="11"/>
+      <c r="P91" s="14"/>
+    </row>
+    <row r="92" spans="2:16">
       <c r="B92" s="11"/>
       <c r="C92" s="11"/>
       <c r="E92" s="12"/>
-      <c r="K92" s="4"/>
       <c r="L92" s="4"/>
-      <c r="M92" s="13"/>
-      <c r="N92" s="11"/>
-      <c r="O92" s="14"/>
-    </row>
-    <row r="93" spans="2:15">
+      <c r="M92" s="4"/>
+      <c r="N92" s="13"/>
+      <c r="O92" s="11"/>
+      <c r="P92" s="14"/>
+    </row>
+    <row r="93" spans="2:16">
       <c r="B93" s="11"/>
       <c r="C93" s="11"/>
       <c r="E93" s="12"/>
-      <c r="K93" s="4"/>
       <c r="L93" s="4"/>
-      <c r="M93" s="13"/>
-      <c r="N93" s="11"/>
-      <c r="O93" s="14"/>
-    </row>
-    <row r="94" spans="2:15">
+      <c r="M93" s="4"/>
+      <c r="N93" s="13"/>
+      <c r="O93" s="11"/>
+      <c r="P93" s="14"/>
+    </row>
+    <row r="94" spans="2:16">
       <c r="B94" s="11"/>
       <c r="C94" s="11"/>
       <c r="E94" s="12"/>
-      <c r="K94" s="4"/>
       <c r="L94" s="4"/>
-      <c r="M94" s="13"/>
-      <c r="N94" s="11"/>
-      <c r="O94" s="14"/>
-    </row>
-    <row r="95" spans="2:15">
+      <c r="M94" s="4"/>
+      <c r="N94" s="13"/>
+      <c r="O94" s="11"/>
+      <c r="P94" s="14"/>
+    </row>
+    <row r="95" spans="2:16">
       <c r="B95" s="11"/>
       <c r="C95" s="11"/>
       <c r="E95" s="12"/>
-      <c r="K95" s="4"/>
       <c r="L95" s="4"/>
-      <c r="M95" s="13"/>
-      <c r="N95" s="11"/>
-      <c r="O95" s="14"/>
-    </row>
-    <row r="96" spans="2:15">
+      <c r="M95" s="4"/>
+      <c r="N95" s="13"/>
+      <c r="O95" s="11"/>
+      <c r="P95" s="14"/>
+    </row>
+    <row r="96" spans="2:16">
       <c r="B96" s="11"/>
       <c r="C96" s="11"/>
       <c r="E96" s="12"/>
-      <c r="K96" s="4"/>
       <c r="L96" s="4"/>
-      <c r="M96" s="13"/>
-      <c r="N96" s="11"/>
-      <c r="O96" s="14"/>
-    </row>
-    <row r="97" spans="2:15">
+      <c r="M96" s="4"/>
+      <c r="N96" s="13"/>
+      <c r="O96" s="11"/>
+      <c r="P96" s="14"/>
+    </row>
+    <row r="97" spans="2:16">
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
       <c r="E97" s="12"/>
-      <c r="K97" s="4"/>
       <c r="L97" s="4"/>
-      <c r="M97" s="13"/>
-      <c r="N97" s="11"/>
-      <c r="O97" s="14"/>
-    </row>
-    <row r="98" spans="2:15">
+      <c r="M97" s="4"/>
+      <c r="N97" s="13"/>
+      <c r="O97" s="11"/>
+      <c r="P97" s="14"/>
+    </row>
+    <row r="98" spans="2:16">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
       <c r="E98" s="12"/>
-      <c r="K98" s="4"/>
       <c r="L98" s="4"/>
-      <c r="M98" s="13"/>
-      <c r="N98" s="11"/>
-      <c r="O98" s="14"/>
-    </row>
-    <row r="99" spans="2:15">
+      <c r="M98" s="4"/>
+      <c r="N98" s="13"/>
+      <c r="O98" s="11"/>
+      <c r="P98" s="14"/>
+    </row>
+    <row r="99" spans="2:16">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
       <c r="E99" s="12"/>
-      <c r="K99" s="4"/>
       <c r="L99" s="4"/>
-      <c r="M99" s="13"/>
-      <c r="N99" s="11"/>
-      <c r="O99" s="14"/>
-    </row>
-    <row r="100" spans="2:15">
+      <c r="M99" s="4"/>
+      <c r="N99" s="13"/>
+      <c r="O99" s="11"/>
+      <c r="P99" s="14"/>
+    </row>
+    <row r="100" spans="2:16">
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="E100" s="12"/>
-      <c r="K100" s="4"/>
       <c r="L100" s="4"/>
-      <c r="M100" s="13"/>
-      <c r="N100" s="11"/>
-      <c r="O100" s="14"/>
-    </row>
-    <row r="101" spans="2:15">
+      <c r="M100" s="4"/>
+      <c r="N100" s="13"/>
+      <c r="O100" s="11"/>
+      <c r="P100" s="14"/>
+    </row>
+    <row r="101" spans="2:16">
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="E101" s="12"/>
-      <c r="K101" s="4"/>
       <c r="L101" s="4"/>
-      <c r="M101" s="13"/>
-      <c r="N101" s="11"/>
-      <c r="O101" s="14"/>
-    </row>
-    <row r="102" spans="2:15">
+      <c r="M101" s="4"/>
+      <c r="N101" s="13"/>
+      <c r="O101" s="11"/>
+      <c r="P101" s="14"/>
+    </row>
+    <row r="102" spans="2:16">
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="E102" s="12"/>
-      <c r="K102" s="4"/>
       <c r="L102" s="4"/>
-      <c r="M102" s="13"/>
-      <c r="N102" s="11"/>
-      <c r="O102" s="14"/>
-    </row>
-    <row r="103" spans="2:15">
+      <c r="M102" s="4"/>
+      <c r="N102" s="13"/>
+      <c r="O102" s="11"/>
+      <c r="P102" s="14"/>
+    </row>
+    <row r="103" spans="2:16">
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="E103" s="12"/>
-      <c r="K103" s="4"/>
       <c r="L103" s="4"/>
-      <c r="M103" s="13"/>
-      <c r="N103" s="11"/>
-      <c r="O103" s="14"/>
-    </row>
-    <row r="104" spans="2:15">
+      <c r="M103" s="4"/>
+      <c r="N103" s="13"/>
+      <c r="O103" s="11"/>
+      <c r="P103" s="14"/>
+    </row>
+    <row r="104" spans="2:16">
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="E104" s="12"/>
-      <c r="K104" s="4"/>
       <c r="L104" s="4"/>
-      <c r="M104" s="13"/>
-      <c r="N104" s="11"/>
-      <c r="O104" s="14"/>
-    </row>
-    <row r="105" spans="2:15">
+      <c r="M104" s="4"/>
+      <c r="N104" s="13"/>
+      <c r="O104" s="11"/>
+      <c r="P104" s="14"/>
+    </row>
+    <row r="105" spans="2:16">
       <c r="B105" s="11"/>
       <c r="C105" s="11"/>
       <c r="E105" s="12"/>
-      <c r="K105" s="4"/>
       <c r="L105" s="4"/>
-      <c r="M105" s="13"/>
-      <c r="N105" s="11"/>
-      <c r="O105" s="14"/>
-    </row>
-    <row r="106" spans="2:15">
+      <c r="M105" s="4"/>
+      <c r="N105" s="13"/>
+      <c r="O105" s="11"/>
+      <c r="P105" s="14"/>
+    </row>
+    <row r="106" spans="2:16">
       <c r="B106" s="11"/>
       <c r="C106" s="11"/>
       <c r="E106" s="12"/>
-      <c r="K106" s="4"/>
       <c r="L106" s="4"/>
-      <c r="M106" s="13"/>
-      <c r="N106" s="11"/>
-      <c r="O106" s="14"/>
-    </row>
-    <row r="107" spans="2:15">
+      <c r="M106" s="4"/>
+      <c r="N106" s="13"/>
+      <c r="O106" s="11"/>
+      <c r="P106" s="14"/>
+    </row>
+    <row r="107" spans="2:16">
       <c r="B107" s="11"/>
       <c r="C107" s="11"/>
       <c r="E107" s="12"/>
-      <c r="K107" s="4"/>
       <c r="L107" s="4"/>
-      <c r="M107" s="13"/>
-      <c r="N107" s="11"/>
-      <c r="O107" s="14"/>
-    </row>
-    <row r="108" spans="2:15">
+      <c r="M107" s="4"/>
+      <c r="N107" s="13"/>
+      <c r="O107" s="11"/>
+      <c r="P107" s="14"/>
+    </row>
+    <row r="108" spans="2:16">
       <c r="B108" s="11"/>
       <c r="C108" s="11"/>
       <c r="E108" s="12"/>
-      <c r="K108" s="4"/>
       <c r="L108" s="4"/>
-      <c r="M108" s="13"/>
-      <c r="N108" s="11"/>
-      <c r="O108" s="14"/>
-    </row>
-    <row r="109" spans="2:15">
+      <c r="M108" s="4"/>
+      <c r="N108" s="13"/>
+      <c r="O108" s="11"/>
+      <c r="P108" s="14"/>
+    </row>
+    <row r="109" spans="2:16">
       <c r="B109" s="11"/>
       <c r="C109" s="11"/>
       <c r="E109" s="12"/>
-      <c r="K109" s="4"/>
       <c r="L109" s="4"/>
-      <c r="M109" s="13"/>
-      <c r="N109" s="11"/>
-      <c r="O109" s="14"/>
-    </row>
-    <row r="110" spans="2:15">
+      <c r="M109" s="4"/>
+      <c r="N109" s="13"/>
+      <c r="O109" s="11"/>
+      <c r="P109" s="14"/>
+    </row>
+    <row r="110" spans="2:16">
       <c r="B110" s="11"/>
       <c r="C110" s="11"/>
       <c r="E110" s="12"/>
-      <c r="K110" s="4"/>
       <c r="L110" s="4"/>
-      <c r="M110" s="13"/>
-      <c r="N110" s="11"/>
-      <c r="O110" s="14"/>
-    </row>
-    <row r="111" spans="2:15">
+      <c r="M110" s="4"/>
+      <c r="N110" s="13"/>
+      <c r="O110" s="11"/>
+      <c r="P110" s="14"/>
+    </row>
+    <row r="111" spans="2:16">
       <c r="B111" s="11"/>
       <c r="C111" s="11"/>
       <c r="E111" s="12"/>
-      <c r="K111" s="4"/>
       <c r="L111" s="4"/>
-      <c r="M111" s="13"/>
-      <c r="N111" s="11"/>
-      <c r="O111" s="14"/>
-    </row>
-    <row r="112" spans="2:15">
+      <c r="M111" s="4"/>
+      <c r="N111" s="13"/>
+      <c r="O111" s="11"/>
+      <c r="P111" s="14"/>
+    </row>
+    <row r="112" spans="2:16">
       <c r="B112" s="11"/>
       <c r="C112" s="11"/>
       <c r="E112" s="12"/>
-      <c r="K112" s="4"/>
       <c r="L112" s="4"/>
-      <c r="M112" s="13"/>
-      <c r="N112" s="11"/>
-      <c r="O112" s="14"/>
-    </row>
-    <row r="113" spans="2:15">
+      <c r="M112" s="4"/>
+      <c r="N112" s="13"/>
+      <c r="O112" s="11"/>
+      <c r="P112" s="14"/>
+    </row>
+    <row r="113" spans="2:16">
       <c r="B113" s="11"/>
       <c r="C113" s="11"/>
       <c r="E113" s="12"/>
-      <c r="K113" s="4"/>
       <c r="L113" s="4"/>
-      <c r="M113" s="13"/>
-      <c r="N113" s="11"/>
-      <c r="O113" s="14"/>
-    </row>
-    <row r="114" spans="2:15">
+      <c r="M113" s="4"/>
+      <c r="N113" s="13"/>
+      <c r="O113" s="11"/>
+      <c r="P113" s="14"/>
+    </row>
+    <row r="114" spans="2:16">
       <c r="B114" s="11"/>
       <c r="C114" s="11"/>
       <c r="E114" s="12"/>
-      <c r="K114" s="4"/>
       <c r="L114" s="4"/>
-      <c r="M114" s="13"/>
-      <c r="N114" s="11"/>
-      <c r="O114" s="14"/>
-    </row>
-    <row r="115" spans="2:15">
+      <c r="M114" s="4"/>
+      <c r="N114" s="13"/>
+      <c r="O114" s="11"/>
+      <c r="P114" s="14"/>
+    </row>
+    <row r="115" spans="2:16">
       <c r="B115" s="11"/>
       <c r="C115" s="11"/>
       <c r="E115" s="12"/>
-      <c r="K115" s="4"/>
       <c r="L115" s="4"/>
-      <c r="M115" s="13"/>
-      <c r="N115" s="11"/>
-      <c r="O115" s="14"/>
-    </row>
-    <row r="116" spans="2:15">
+      <c r="M115" s="4"/>
+      <c r="N115" s="13"/>
+      <c r="O115" s="11"/>
+      <c r="P115" s="14"/>
+    </row>
+    <row r="116" spans="2:16">
       <c r="B116" s="11"/>
       <c r="C116" s="11"/>
       <c r="E116" s="12"/>
-      <c r="K116" s="4"/>
       <c r="L116" s="4"/>
-      <c r="M116" s="13"/>
-      <c r="N116" s="11"/>
-      <c r="O116" s="14"/>
-    </row>
-    <row r="117" spans="2:15">
+      <c r="M116" s="4"/>
+      <c r="N116" s="13"/>
+      <c r="O116" s="11"/>
+      <c r="P116" s="14"/>
+    </row>
+    <row r="117" spans="2:16">
       <c r="B117" s="11"/>
       <c r="C117" s="11"/>
       <c r="E117" s="12"/>
-      <c r="K117" s="4"/>
       <c r="L117" s="4"/>
-      <c r="M117" s="13"/>
-      <c r="N117" s="11"/>
-      <c r="O117" s="14"/>
-    </row>
-    <row r="118" spans="2:15">
+      <c r="M117" s="4"/>
+      <c r="N117" s="13"/>
+      <c r="O117" s="11"/>
+      <c r="P117" s="14"/>
+    </row>
+    <row r="118" spans="2:16">
       <c r="B118" s="11"/>
       <c r="C118" s="11"/>
       <c r="E118" s="12"/>
-      <c r="K118" s="4"/>
       <c r="L118" s="4"/>
-      <c r="M118" s="13"/>
-      <c r="N118" s="11"/>
-      <c r="O118" s="14"/>
-    </row>
-    <row r="119" spans="2:15">
+      <c r="M118" s="4"/>
+      <c r="N118" s="13"/>
+      <c r="O118" s="11"/>
+      <c r="P118" s="14"/>
+    </row>
+    <row r="119" spans="2:16">
       <c r="B119" s="11"/>
       <c r="C119" s="11"/>
       <c r="E119" s="12"/>
-      <c r="K119" s="4"/>
       <c r="L119" s="4"/>
-      <c r="M119" s="13"/>
-      <c r="N119" s="11"/>
-      <c r="O119" s="14"/>
-    </row>
-    <row r="120" spans="2:15">
+      <c r="M119" s="4"/>
+      <c r="N119" s="13"/>
+      <c r="O119" s="11"/>
+      <c r="P119" s="14"/>
+    </row>
+    <row r="120" spans="2:16">
       <c r="B120" s="11"/>
       <c r="C120" s="11"/>
       <c r="E120" s="12"/>
-      <c r="K120" s="4"/>
       <c r="L120" s="4"/>
-      <c r="M120" s="13"/>
-      <c r="N120" s="11"/>
-      <c r="O120" s="14"/>
-    </row>
-    <row r="121" spans="2:15">
+      <c r="M120" s="4"/>
+      <c r="N120" s="13"/>
+      <c r="O120" s="11"/>
+      <c r="P120" s="14"/>
+    </row>
+    <row r="121" spans="2:16">
       <c r="B121" s="11"/>
       <c r="C121" s="11"/>
       <c r="E121" s="12"/>
-      <c r="K121" s="4"/>
       <c r="L121" s="4"/>
-      <c r="M121" s="13"/>
-      <c r="N121" s="11"/>
-      <c r="O121" s="14"/>
-    </row>
-    <row r="122" spans="2:15">
+      <c r="M121" s="4"/>
+      <c r="N121" s="13"/>
+      <c r="O121" s="11"/>
+      <c r="P121" s="14"/>
+    </row>
+    <row r="122" spans="2:16">
       <c r="B122" s="11"/>
       <c r="C122" s="11"/>
       <c r="E122" s="12"/>
-      <c r="K122" s="4"/>
       <c r="L122" s="4"/>
-      <c r="M122" s="13"/>
-      <c r="N122" s="11"/>
-      <c r="O122" s="14"/>
-    </row>
-    <row r="123" spans="2:15">
+      <c r="M122" s="4"/>
+      <c r="N122" s="13"/>
+      <c r="O122" s="11"/>
+      <c r="P122" s="14"/>
+    </row>
+    <row r="123" spans="2:16">
       <c r="B123" s="11"/>
       <c r="C123" s="11"/>
       <c r="E123" s="12"/>
-      <c r="K123" s="4"/>
       <c r="L123" s="4"/>
-      <c r="M123" s="13"/>
-      <c r="N123" s="11"/>
-      <c r="O123" s="14"/>
-    </row>
-    <row r="124" spans="2:15">
+      <c r="M123" s="4"/>
+      <c r="N123" s="13"/>
+      <c r="O123" s="11"/>
+      <c r="P123" s="14"/>
+    </row>
+    <row r="124" spans="2:16">
       <c r="B124" s="11"/>
       <c r="C124" s="11"/>
       <c r="E124" s="12"/>
-      <c r="K124" s="4"/>
       <c r="L124" s="4"/>
-      <c r="M124" s="13"/>
-      <c r="N124" s="11"/>
-      <c r="O124" s="14"/>
-    </row>
-    <row r="125" spans="2:15">
+      <c r="M124" s="4"/>
+      <c r="N124" s="13"/>
+      <c r="O124" s="11"/>
+      <c r="P124" s="14"/>
+    </row>
+    <row r="125" spans="2:16">
       <c r="B125" s="11"/>
       <c r="C125" s="11"/>
       <c r="E125" s="12"/>
-      <c r="K125" s="4"/>
       <c r="L125" s="4"/>
-      <c r="M125" s="13"/>
-      <c r="N125" s="11"/>
-      <c r="O125" s="14"/>
-    </row>
-    <row r="126" spans="2:15">
+      <c r="M125" s="4"/>
+      <c r="N125" s="13"/>
+      <c r="O125" s="11"/>
+      <c r="P125" s="14"/>
+    </row>
+    <row r="126" spans="2:16">
       <c r="B126" s="11"/>
       <c r="C126" s="11"/>
       <c r="E126" s="12"/>
-      <c r="K126" s="4"/>
       <c r="L126" s="4"/>
-      <c r="M126" s="13"/>
-      <c r="N126" s="11"/>
-      <c r="O126" s="14"/>
-    </row>
-    <row r="127" spans="2:15">
+      <c r="M126" s="4"/>
+      <c r="N126" s="13"/>
+      <c r="O126" s="11"/>
+      <c r="P126" s="14"/>
+    </row>
+    <row r="127" spans="2:16">
       <c r="B127" s="11"/>
       <c r="C127" s="11"/>
       <c r="E127" s="12"/>
-      <c r="K127" s="4"/>
       <c r="L127" s="4"/>
-      <c r="M127" s="13"/>
-      <c r="N127" s="11"/>
-      <c r="O127" s="14"/>
-    </row>
-    <row r="128" spans="2:15">
+      <c r="M127" s="4"/>
+      <c r="N127" s="13"/>
+      <c r="O127" s="11"/>
+      <c r="P127" s="14"/>
+    </row>
+    <row r="128" spans="2:16">
       <c r="B128" s="11"/>
       <c r="C128" s="11"/>
       <c r="E128" s="12"/>
-      <c r="K128" s="4"/>
       <c r="L128" s="4"/>
-      <c r="M128" s="13"/>
-      <c r="N128" s="11"/>
-      <c r="O128" s="14"/>
-    </row>
-    <row r="129" spans="2:15">
+      <c r="M128" s="4"/>
+      <c r="N128" s="13"/>
+      <c r="O128" s="11"/>
+      <c r="P128" s="14"/>
+    </row>
+    <row r="129" spans="2:16">
       <c r="B129" s="11"/>
       <c r="C129" s="11"/>
       <c r="E129" s="12"/>
-      <c r="K129" s="4"/>
       <c r="L129" s="4"/>
-      <c r="M129" s="13"/>
-      <c r="N129" s="11"/>
-      <c r="O129" s="14"/>
-    </row>
-    <row r="130" spans="2:15">
+      <c r="M129" s="4"/>
+      <c r="N129" s="13"/>
+      <c r="O129" s="11"/>
+      <c r="P129" s="14"/>
+    </row>
+    <row r="130" spans="2:16">
       <c r="B130" s="11"/>
       <c r="C130" s="11"/>
       <c r="E130" s="12"/>
-      <c r="K130" s="4"/>
       <c r="L130" s="4"/>
-      <c r="M130" s="13"/>
-      <c r="N130" s="11"/>
-      <c r="O130" s="14"/>
-    </row>
-    <row r="131" spans="2:15">
+      <c r="M130" s="4"/>
+      <c r="N130" s="13"/>
+      <c r="O130" s="11"/>
+      <c r="P130" s="14"/>
+    </row>
+    <row r="131" spans="2:16">
       <c r="B131" s="11"/>
       <c r="C131" s="11"/>
       <c r="E131" s="12"/>
-      <c r="K131" s="4"/>
       <c r="L131" s="4"/>
-      <c r="M131" s="13"/>
-      <c r="N131" s="11"/>
-      <c r="O131" s="14"/>
-    </row>
-    <row r="132" spans="2:15">
+      <c r="M131" s="4"/>
+      <c r="N131" s="13"/>
+      <c r="O131" s="11"/>
+      <c r="P131" s="14"/>
+    </row>
+    <row r="132" spans="2:16">
       <c r="B132" s="11"/>
       <c r="C132" s="11"/>
       <c r="E132" s="12"/>
-      <c r="K132" s="4"/>
       <c r="L132" s="4"/>
-      <c r="M132" s="13"/>
-      <c r="N132" s="11"/>
-      <c r="O132" s="14"/>
-    </row>
-    <row r="133" spans="2:15">
+      <c r="M132" s="4"/>
+      <c r="N132" s="13"/>
+      <c r="O132" s="11"/>
+      <c r="P132" s="14"/>
+    </row>
+    <row r="133" spans="2:16">
       <c r="B133" s="11"/>
       <c r="C133" s="11"/>
       <c r="E133" s="12"/>
-      <c r="K133" s="4"/>
       <c r="L133" s="4"/>
-      <c r="M133" s="13"/>
-      <c r="N133" s="11"/>
-      <c r="O133" s="14"/>
-    </row>
-    <row r="134" spans="2:15">
+      <c r="M133" s="4"/>
+      <c r="N133" s="13"/>
+      <c r="O133" s="11"/>
+      <c r="P133" s="14"/>
+    </row>
+    <row r="134" spans="2:16">
       <c r="B134" s="11"/>
       <c r="C134" s="11"/>
       <c r="E134" s="12"/>
-      <c r="K134" s="4"/>
       <c r="L134" s="4"/>
-      <c r="M134" s="13"/>
-      <c r="N134" s="11"/>
-      <c r="O134" s="14"/>
-    </row>
-    <row r="135" spans="2:15">
+      <c r="M134" s="4"/>
+      <c r="N134" s="13"/>
+      <c r="O134" s="11"/>
+      <c r="P134" s="14"/>
+    </row>
+    <row r="135" spans="2:16">
       <c r="B135" s="11"/>
       <c r="C135" s="11"/>
       <c r="E135" s="12"/>
-      <c r="K135" s="4"/>
       <c r="L135" s="4"/>
-      <c r="M135" s="13"/>
-      <c r="N135" s="11"/>
-      <c r="O135" s="14"/>
-    </row>
-    <row r="136" spans="2:15">
+      <c r="M135" s="4"/>
+      <c r="N135" s="13"/>
+      <c r="O135" s="11"/>
+      <c r="P135" s="14"/>
+    </row>
+    <row r="136" spans="2:16">
       <c r="B136" s="11"/>
       <c r="C136" s="11"/>
       <c r="E136" s="12"/>
-      <c r="K136" s="4"/>
       <c r="L136" s="4"/>
-      <c r="M136" s="13"/>
-      <c r="N136" s="11"/>
-      <c r="O136" s="14"/>
-    </row>
-    <row r="137" spans="2:15">
+      <c r="M136" s="4"/>
+      <c r="N136" s="13"/>
+      <c r="O136" s="11"/>
+      <c r="P136" s="14"/>
+    </row>
+    <row r="137" spans="2:16">
       <c r="B137" s="11"/>
       <c r="C137" s="11"/>
       <c r="E137" s="12"/>
-      <c r="K137" s="4"/>
       <c r="L137" s="4"/>
-      <c r="M137" s="13"/>
-      <c r="N137" s="11"/>
-      <c r="O137" s="14"/>
-    </row>
-    <row r="138" spans="2:15">
+      <c r="M137" s="4"/>
+      <c r="N137" s="13"/>
+      <c r="O137" s="11"/>
+      <c r="P137" s="14"/>
+    </row>
+    <row r="138" spans="2:16">
       <c r="B138" s="11"/>
       <c r="C138" s="11"/>
       <c r="E138" s="12"/>
-      <c r="K138" s="4"/>
       <c r="L138" s="4"/>
-      <c r="M138" s="13"/>
-      <c r="N138" s="11"/>
-      <c r="O138" s="14"/>
-    </row>
-    <row r="139" spans="2:15">
+      <c r="M138" s="4"/>
+      <c r="N138" s="13"/>
+      <c r="O138" s="11"/>
+      <c r="P138" s="14"/>
+    </row>
+    <row r="139" spans="2:16">
       <c r="B139" s="11"/>
       <c r="C139" s="11"/>
       <c r="E139" s="12"/>
-      <c r="K139" s="4"/>
       <c r="L139" s="4"/>
-      <c r="M139" s="13"/>
-      <c r="N139" s="11"/>
-      <c r="O139" s="14"/>
-    </row>
-    <row r="140" spans="2:15">
+      <c r="M139" s="4"/>
+      <c r="N139" s="13"/>
+      <c r="O139" s="11"/>
+      <c r="P139" s="14"/>
+    </row>
+    <row r="140" spans="2:16">
       <c r="B140" s="11"/>
       <c r="C140" s="11"/>
       <c r="E140" s="12"/>
-      <c r="K140" s="4"/>
       <c r="L140" s="4"/>
-      <c r="M140" s="13"/>
-      <c r="N140" s="11"/>
-      <c r="O140" s="14"/>
-    </row>
-    <row r="141" spans="2:15">
+      <c r="M140" s="4"/>
+      <c r="N140" s="13"/>
+      <c r="O140" s="11"/>
+      <c r="P140" s="14"/>
+    </row>
+    <row r="141" spans="2:16">
       <c r="B141" s="11"/>
       <c r="C141" s="11"/>
       <c r="E141" s="12"/>
-      <c r="K141" s="4"/>
       <c r="L141" s="4"/>
-      <c r="M141" s="13"/>
-      <c r="N141" s="11"/>
-      <c r="O141" s="14"/>
-    </row>
-    <row r="142" spans="2:15">
+      <c r="M141" s="4"/>
+      <c r="N141" s="13"/>
+      <c r="O141" s="11"/>
+      <c r="P141" s="14"/>
+    </row>
+    <row r="142" spans="2:16">
       <c r="B142" s="11"/>
       <c r="C142" s="11"/>
       <c r="E142" s="12"/>
-      <c r="K142" s="4"/>
       <c r="L142" s="4"/>
-      <c r="M142" s="13"/>
-      <c r="N142" s="11"/>
-      <c r="O142" s="14"/>
-    </row>
-    <row r="143" spans="2:15">
+      <c r="M142" s="4"/>
+      <c r="N142" s="13"/>
+      <c r="O142" s="11"/>
+      <c r="P142" s="14"/>
+    </row>
+    <row r="143" spans="2:16">
       <c r="B143" s="11"/>
       <c r="C143" s="11"/>
       <c r="E143" s="12"/>
-      <c r="K143" s="4"/>
       <c r="L143" s="4"/>
-      <c r="M143" s="13"/>
-      <c r="N143" s="11"/>
-      <c r="O143" s="14"/>
-    </row>
-    <row r="144" spans="2:15">
+      <c r="M143" s="4"/>
+      <c r="N143" s="13"/>
+      <c r="O143" s="11"/>
+      <c r="P143" s="14"/>
+    </row>
+    <row r="144" spans="2:16">
       <c r="B144" s="11"/>
       <c r="C144" s="11"/>
       <c r="E144" s="12"/>
-      <c r="K144" s="4"/>
       <c r="L144" s="4"/>
-      <c r="M144" s="13"/>
-      <c r="N144" s="11"/>
-      <c r="O144" s="14"/>
-    </row>
-    <row r="145" spans="2:15">
+      <c r="M144" s="4"/>
+      <c r="N144" s="13"/>
+      <c r="O144" s="11"/>
+      <c r="P144" s="14"/>
+    </row>
+    <row r="145" spans="2:16">
       <c r="B145" s="11"/>
       <c r="C145" s="11"/>
       <c r="E145" s="12"/>
-      <c r="K145" s="4"/>
       <c r="L145" s="4"/>
-      <c r="M145" s="13"/>
-      <c r="N145" s="11"/>
-      <c r="O145" s="14"/>
-    </row>
-    <row r="146" spans="2:15">
+      <c r="M145" s="4"/>
+      <c r="N145" s="13"/>
+      <c r="O145" s="11"/>
+      <c r="P145" s="14"/>
+    </row>
+    <row r="146" spans="2:16">
       <c r="B146" s="11"/>
       <c r="C146" s="11"/>
       <c r="E146" s="12"/>
-      <c r="K146" s="4"/>
       <c r="L146" s="4"/>
-      <c r="M146" s="13"/>
-      <c r="N146" s="11"/>
-      <c r="O146" s="14"/>
-    </row>
-    <row r="147" spans="2:15">
+      <c r="M146" s="4"/>
+      <c r="N146" s="13"/>
+      <c r="O146" s="11"/>
+      <c r="P146" s="14"/>
+    </row>
+    <row r="147" spans="2:16">
       <c r="B147" s="11"/>
       <c r="C147" s="11"/>
       <c r="E147" s="12"/>
-      <c r="K147" s="4"/>
       <c r="L147" s="4"/>
-      <c r="M147" s="13"/>
-      <c r="N147" s="11"/>
-      <c r="O147" s="14"/>
-    </row>
-    <row r="148" spans="2:15">
+      <c r="M147" s="4"/>
+      <c r="N147" s="13"/>
+      <c r="O147" s="11"/>
+      <c r="P147" s="14"/>
+    </row>
+    <row r="148" spans="2:16">
       <c r="B148" s="11"/>
       <c r="C148" s="11"/>
       <c r="E148" s="12"/>
-      <c r="K148" s="4"/>
       <c r="L148" s="4"/>
-      <c r="M148" s="13"/>
-      <c r="N148" s="11"/>
-      <c r="O148" s="14"/>
-    </row>
-    <row r="149" spans="2:15">
+      <c r="M148" s="4"/>
+      <c r="N148" s="13"/>
+      <c r="O148" s="11"/>
+      <c r="P148" s="14"/>
+    </row>
+    <row r="149" spans="2:16">
       <c r="B149" s="11"/>
       <c r="C149" s="11"/>
       <c r="E149" s="12"/>
-      <c r="K149" s="4"/>
       <c r="L149" s="4"/>
-      <c r="M149" s="13"/>
-      <c r="N149" s="11"/>
-      <c r="O149" s="14"/>
-    </row>
-    <row r="150" spans="2:15">
+      <c r="M149" s="4"/>
+      <c r="N149" s="13"/>
+      <c r="O149" s="11"/>
+      <c r="P149" s="14"/>
+    </row>
+    <row r="150" spans="2:16">
       <c r="B150" s="11"/>
       <c r="C150" s="11"/>
       <c r="E150" s="12"/>
-      <c r="K150" s="4"/>
       <c r="L150" s="4"/>
-      <c r="M150" s="13"/>
-      <c r="N150" s="11"/>
-      <c r="O150" s="14"/>
-    </row>
-    <row r="151" spans="2:15">
+      <c r="M150" s="4"/>
+      <c r="N150" s="13"/>
+      <c r="O150" s="11"/>
+      <c r="P150" s="14"/>
+    </row>
+    <row r="151" spans="2:16">
       <c r="B151" s="11"/>
       <c r="C151" s="11"/>
       <c r="E151" s="12"/>
-      <c r="K151" s="4"/>
       <c r="L151" s="4"/>
-      <c r="M151" s="13"/>
-      <c r="N151" s="11"/>
-      <c r="O151" s="14"/>
-    </row>
-    <row r="152" spans="2:15">
+      <c r="M151" s="4"/>
+      <c r="N151" s="13"/>
+      <c r="O151" s="11"/>
+      <c r="P151" s="14"/>
+    </row>
+    <row r="152" spans="2:16">
       <c r="B152" s="11"/>
       <c r="C152" s="11"/>
       <c r="E152" s="12"/>
-      <c r="K152" s="4"/>
       <c r="L152" s="4"/>
-      <c r="M152" s="13"/>
-      <c r="N152" s="11"/>
-      <c r="O152" s="14"/>
-    </row>
-    <row r="153" spans="2:15">
+      <c r="M152" s="4"/>
+      <c r="N152" s="13"/>
+      <c r="O152" s="11"/>
+      <c r="P152" s="14"/>
+    </row>
+    <row r="153" spans="2:16">
       <c r="B153" s="11"/>
       <c r="C153" s="11"/>
       <c r="E153" s="12"/>
-      <c r="K153" s="4"/>
       <c r="L153" s="4"/>
-      <c r="M153" s="13"/>
-      <c r="N153" s="11"/>
-      <c r="O153" s="14"/>
-    </row>
-    <row r="154" spans="2:15">
+      <c r="M153" s="4"/>
+      <c r="N153" s="13"/>
+      <c r="O153" s="11"/>
+      <c r="P153" s="14"/>
+    </row>
+    <row r="154" spans="2:16">
       <c r="B154" s="11"/>
       <c r="C154" s="11"/>
       <c r="E154" s="12"/>
-      <c r="K154" s="4"/>
       <c r="L154" s="4"/>
-      <c r="M154" s="13"/>
-      <c r="N154" s="11"/>
-      <c r="O154" s="14"/>
-    </row>
-    <row r="155" spans="2:15">
+      <c r="M154" s="4"/>
+      <c r="N154" s="13"/>
+      <c r="O154" s="11"/>
+      <c r="P154" s="14"/>
+    </row>
+    <row r="155" spans="2:16">
       <c r="B155" s="11"/>
       <c r="C155" s="11"/>
       <c r="E155" s="12"/>
-      <c r="K155" s="4"/>
       <c r="L155" s="4"/>
-      <c r="M155" s="13"/>
-      <c r="N155" s="11"/>
-      <c r="O155" s="14"/>
-    </row>
-    <row r="156" spans="2:15">
+      <c r="M155" s="4"/>
+      <c r="N155" s="13"/>
+      <c r="O155" s="11"/>
+      <c r="P155" s="14"/>
+    </row>
+    <row r="156" spans="2:16">
       <c r="B156" s="11"/>
       <c r="C156" s="11"/>
       <c r="E156" s="12"/>
-      <c r="K156" s="4"/>
       <c r="L156" s="4"/>
-      <c r="M156" s="13"/>
-      <c r="N156" s="11"/>
-      <c r="O156" s="14"/>
-    </row>
-    <row r="157" spans="2:15">
+      <c r="M156" s="4"/>
+      <c r="N156" s="13"/>
+      <c r="O156" s="11"/>
+      <c r="P156" s="14"/>
+    </row>
+    <row r="157" spans="2:16">
       <c r="B157" s="11"/>
       <c r="C157" s="11"/>
       <c r="E157" s="12"/>
-      <c r="K157" s="4"/>
       <c r="L157" s="4"/>
-      <c r="M157" s="13"/>
-      <c r="N157" s="11"/>
-      <c r="O157" s="14"/>
-    </row>
-    <row r="158" spans="2:15">
+      <c r="M157" s="4"/>
+      <c r="N157" s="13"/>
+      <c r="O157" s="11"/>
+      <c r="P157" s="14"/>
+    </row>
+    <row r="158" spans="2:16">
       <c r="B158" s="11"/>
       <c r="C158" s="11"/>
       <c r="E158" s="12"/>
-      <c r="K158" s="4"/>
       <c r="L158" s="4"/>
-      <c r="M158" s="13"/>
-      <c r="N158" s="11"/>
-      <c r="O158" s="14"/>
-    </row>
-    <row r="159" spans="2:15">
-      <c r="M159" s="17"/>
-    </row>
-    <row r="160" spans="2:15">
-      <c r="M160" s="17"/>
-    </row>
-    <row r="161" spans="13:13">
-      <c r="M161" s="17"/>
-    </row>
-    <row r="162" spans="13:13">
-      <c r="M162" s="17"/>
-    </row>
-    <row r="163" spans="13:13">
-      <c r="M163" s="17"/>
-    </row>
-    <row r="164" spans="13:13">
-      <c r="M164" s="17"/>
-    </row>
-    <row r="165" spans="13:13">
-      <c r="M165" s="17"/>
-    </row>
-    <row r="166" spans="13:13">
-      <c r="M166" s="17"/>
-    </row>
-    <row r="167" spans="13:13">
-      <c r="M167" s="17"/>
-    </row>
-    <row r="168" spans="13:13">
-      <c r="M168" s="17"/>
-    </row>
-    <row r="169" spans="13:13">
-      <c r="M169" s="17"/>
-    </row>
-    <row r="170" spans="13:13">
-      <c r="M170" s="17"/>
-    </row>
-    <row r="171" spans="13:13">
-      <c r="M171" s="17"/>
-    </row>
-    <row r="172" spans="13:13">
-      <c r="M172" s="17"/>
-    </row>
-    <row r="173" spans="13:13">
-      <c r="M173" s="17"/>
-    </row>
-    <row r="174" spans="13:13">
-      <c r="M174" s="17"/>
-    </row>
-    <row r="175" spans="13:13">
-      <c r="M175" s="17"/>
-    </row>
-    <row r="176" spans="13:13">
-      <c r="M176" s="17"/>
-    </row>
-    <row r="177" spans="13:13">
-      <c r="M177" s="17"/>
-    </row>
-    <row r="178" spans="13:13">
-      <c r="M178" s="17"/>
-    </row>
-    <row r="179" spans="13:13">
-      <c r="M179" s="17"/>
-    </row>
-    <row r="180" spans="13:13">
-      <c r="M180" s="17"/>
-    </row>
-    <row r="181" spans="13:13">
-      <c r="M181" s="17"/>
-    </row>
-    <row r="182" spans="13:13">
-      <c r="M182" s="17"/>
-    </row>
-    <row r="183" spans="13:13">
-      <c r="M183" s="17"/>
-    </row>
-    <row r="184" spans="13:13">
-      <c r="M184" s="17"/>
-    </row>
-    <row r="185" spans="13:13">
-      <c r="M185" s="17"/>
-    </row>
-    <row r="186" spans="13:13">
-      <c r="M186" s="17"/>
-    </row>
-    <row r="187" spans="13:13">
-      <c r="M187" s="17"/>
-    </row>
-    <row r="188" spans="13:13">
-      <c r="M188" s="17"/>
-    </row>
-    <row r="189" spans="13:13">
-      <c r="M189" s="17"/>
-    </row>
-    <row r="190" spans="13:13">
-      <c r="M190" s="17"/>
-    </row>
-    <row r="191" spans="13:13">
-      <c r="M191" s="17"/>
-    </row>
-    <row r="192" spans="13:13">
-      <c r="M192" s="17"/>
-    </row>
-    <row r="193" spans="13:13">
-      <c r="M193" s="17"/>
-    </row>
-    <row r="194" spans="13:13">
-      <c r="M194" s="17"/>
-    </row>
-    <row r="195" spans="13:13">
-      <c r="M195" s="17"/>
-    </row>
-    <row r="196" spans="13:13">
-      <c r="M196" s="17"/>
-    </row>
-    <row r="197" spans="13:13">
-      <c r="M197" s="17"/>
-    </row>
-    <row r="198" spans="13:13">
-      <c r="M198" s="17"/>
-    </row>
-    <row r="199" spans="13:13">
-      <c r="M199" s="17"/>
-    </row>
-    <row r="200" spans="13:13">
-      <c r="M200" s="17"/>
-    </row>
-    <row r="201" spans="13:13">
-      <c r="M201" s="17"/>
-    </row>
-    <row r="202" spans="13:13">
-      <c r="M202" s="17"/>
-    </row>
-    <row r="203" spans="13:13">
-      <c r="M203" s="17"/>
-    </row>
-    <row r="204" spans="13:13">
-      <c r="M204" s="17"/>
-    </row>
-    <row r="205" spans="13:13">
-      <c r="M205" s="17"/>
-    </row>
-    <row r="206" spans="13:13">
-      <c r="M206" s="17"/>
-    </row>
-    <row r="207" spans="13:13">
-      <c r="M207" s="17"/>
-    </row>
-    <row r="208" spans="13:13">
-      <c r="M208" s="17"/>
-    </row>
-    <row r="209" spans="13:13">
-      <c r="M209" s="17"/>
-    </row>
-    <row r="210" spans="13:13">
-      <c r="M210" s="17"/>
-    </row>
-    <row r="211" spans="13:13">
-      <c r="M211" s="17"/>
-    </row>
-    <row r="212" spans="13:13">
-      <c r="M212" s="17"/>
-    </row>
-    <row r="213" spans="13:13">
-      <c r="M213" s="17"/>
-    </row>
-    <row r="214" spans="13:13">
-      <c r="M214" s="17"/>
-    </row>
-    <row r="215" spans="13:13">
-      <c r="M215" s="17"/>
-    </row>
-    <row r="216" spans="13:13">
-      <c r="M216" s="17"/>
-    </row>
-    <row r="217" spans="13:13">
-      <c r="M217" s="17"/>
-    </row>
-    <row r="218" spans="13:13">
-      <c r="M218" s="17"/>
-    </row>
-    <row r="219" spans="13:13">
-      <c r="M219" s="17"/>
-    </row>
-    <row r="220" spans="13:13">
-      <c r="M220" s="17"/>
-    </row>
-    <row r="221" spans="13:13">
-      <c r="M221" s="17"/>
-    </row>
-    <row r="222" spans="13:13">
-      <c r="M222" s="17"/>
-    </row>
-    <row r="223" spans="13:13">
-      <c r="M223" s="17"/>
-    </row>
-    <row r="224" spans="13:13">
-      <c r="M224" s="17"/>
-    </row>
-    <row r="225" spans="13:13">
-      <c r="M225" s="17"/>
-    </row>
-    <row r="226" spans="13:13">
-      <c r="M226" s="17"/>
-    </row>
-    <row r="227" spans="13:13">
-      <c r="M227" s="17"/>
-    </row>
-    <row r="228" spans="13:13">
-      <c r="M228" s="17"/>
-    </row>
-    <row r="229" spans="13:13">
-      <c r="M229" s="17"/>
-    </row>
-    <row r="230" spans="13:13">
-      <c r="M230" s="17"/>
-    </row>
-    <row r="231" spans="13:13">
-      <c r="M231" s="17"/>
-    </row>
-    <row r="232" spans="13:13">
-      <c r="M232" s="17"/>
-    </row>
-    <row r="233" spans="13:13">
-      <c r="M233" s="17"/>
-    </row>
-    <row r="234" spans="13:13">
-      <c r="M234" s="17"/>
-    </row>
-    <row r="235" spans="13:13">
-      <c r="M235" s="17"/>
-    </row>
-    <row r="236" spans="13:13">
-      <c r="M236" s="17"/>
-    </row>
-    <row r="237" spans="13:13">
-      <c r="M237" s="17"/>
-    </row>
-    <row r="238" spans="13:13">
-      <c r="M238" s="17"/>
-    </row>
-    <row r="239" spans="13:13">
-      <c r="M239" s="17"/>
-    </row>
-    <row r="240" spans="13:13">
-      <c r="M240" s="17"/>
-    </row>
-    <row r="241" spans="13:13">
-      <c r="M241" s="17"/>
-    </row>
-    <row r="242" spans="13:13">
-      <c r="M242" s="17"/>
-    </row>
-    <row r="243" spans="13:13">
-      <c r="M243" s="17"/>
-    </row>
-    <row r="244" spans="13:13">
-      <c r="M244" s="17"/>
-    </row>
-    <row r="245" spans="13:13">
-      <c r="M245" s="17"/>
-    </row>
-    <row r="246" spans="13:13">
-      <c r="M246" s="17"/>
-    </row>
-    <row r="247" spans="13:13">
-      <c r="M247" s="17"/>
-    </row>
-    <row r="248" spans="13:13">
-      <c r="M248" s="17"/>
-    </row>
-    <row r="249" spans="13:13">
-      <c r="M249" s="17"/>
-    </row>
-    <row r="250" spans="13:13">
-      <c r="M250" s="17"/>
-    </row>
-    <row r="251" spans="13:13">
-      <c r="M251" s="17"/>
-    </row>
-    <row r="252" spans="13:13">
-      <c r="M252" s="17"/>
-    </row>
-    <row r="253" spans="13:13">
-      <c r="M253" s="17"/>
-    </row>
-    <row r="254" spans="13:13">
-      <c r="M254" s="17"/>
-    </row>
-    <row r="255" spans="13:13">
-      <c r="M255" s="17"/>
-    </row>
-    <row r="256" spans="13:13">
-      <c r="M256" s="17"/>
-    </row>
-    <row r="257" spans="13:13">
-      <c r="M257" s="17"/>
-    </row>
-    <row r="258" spans="13:13">
-      <c r="M258" s="17"/>
-    </row>
-    <row r="259" spans="13:13">
-      <c r="M259" s="17"/>
-    </row>
-    <row r="260" spans="13:13">
-      <c r="M260" s="17"/>
-    </row>
-    <row r="261" spans="13:13">
-      <c r="M261" s="17"/>
-    </row>
-    <row r="262" spans="13:13">
-      <c r="M262" s="17"/>
-    </row>
-    <row r="263" spans="13:13">
-      <c r="M263" s="17"/>
-    </row>
-    <row r="264" spans="13:13">
-      <c r="M264" s="17"/>
-    </row>
-    <row r="265" spans="13:13">
-      <c r="M265" s="17"/>
-    </row>
-    <row r="266" spans="13:13">
-      <c r="M266" s="17"/>
-    </row>
-    <row r="267" spans="13:13">
-      <c r="M267" s="17"/>
-    </row>
-    <row r="268" spans="13:13">
-      <c r="M268" s="17"/>
-    </row>
-    <row r="269" spans="13:13">
-      <c r="M269" s="17"/>
-    </row>
-    <row r="270" spans="13:13">
-      <c r="M270" s="17"/>
-    </row>
-    <row r="271" spans="13:13">
-      <c r="M271" s="17"/>
-    </row>
-    <row r="272" spans="13:13">
-      <c r="M272" s="17"/>
-    </row>
-    <row r="273" spans="13:13">
-      <c r="M273" s="17"/>
-    </row>
-    <row r="274" spans="13:13">
-      <c r="M274" s="17"/>
-    </row>
-    <row r="275" spans="13:13">
-      <c r="M275" s="17"/>
-    </row>
-    <row r="276" spans="13:13">
-      <c r="M276" s="17"/>
-    </row>
-    <row r="277" spans="13:13">
-      <c r="M277" s="17"/>
-    </row>
-    <row r="278" spans="13:13">
-      <c r="M278" s="17"/>
-    </row>
-    <row r="279" spans="13:13">
-      <c r="M279" s="17"/>
-    </row>
-    <row r="280" spans="13:13">
-      <c r="M280" s="17"/>
-    </row>
-    <row r="281" spans="13:13">
-      <c r="M281" s="17"/>
-    </row>
-    <row r="282" spans="13:13">
-      <c r="M282" s="17"/>
-    </row>
-    <row r="283" spans="13:13">
-      <c r="M283" s="17"/>
-    </row>
-    <row r="284" spans="13:13">
-      <c r="M284" s="17"/>
-    </row>
-    <row r="285" spans="13:13">
-      <c r="M285" s="17"/>
-    </row>
-    <row r="286" spans="13:13">
-      <c r="M286" s="17"/>
-    </row>
-    <row r="287" spans="13:13">
-      <c r="M287" s="17"/>
-    </row>
-    <row r="288" spans="13:13">
-      <c r="M288" s="17"/>
-    </row>
-    <row r="289" spans="13:13">
-      <c r="M289" s="17"/>
-    </row>
-    <row r="290" spans="13:13">
-      <c r="M290" s="17"/>
-    </row>
-    <row r="291" spans="13:13">
-      <c r="M291" s="17"/>
-    </row>
-    <row r="292" spans="13:13">
-      <c r="M292" s="17"/>
-    </row>
-    <row r="293" spans="13:13">
-      <c r="M293" s="17"/>
-    </row>
-    <row r="294" spans="13:13">
-      <c r="M294" s="17"/>
-    </row>
-    <row r="295" spans="13:13">
-      <c r="M295" s="17"/>
-    </row>
-    <row r="296" spans="13:13">
-      <c r="M296" s="17"/>
-    </row>
-    <row r="297" spans="13:13">
-      <c r="M297" s="17"/>
-    </row>
-    <row r="298" spans="13:13">
-      <c r="M298" s="17"/>
-    </row>
-    <row r="299" spans="13:13">
-      <c r="M299" s="17"/>
-    </row>
-    <row r="300" spans="13:13">
-      <c r="M300" s="17"/>
-    </row>
-    <row r="301" spans="13:13">
-      <c r="M301" s="17"/>
-    </row>
-    <row r="302" spans="13:13">
-      <c r="M302" s="17"/>
-    </row>
-    <row r="303" spans="13:13">
-      <c r="M303" s="17"/>
-    </row>
-    <row r="304" spans="13:13">
-      <c r="M304" s="17"/>
-    </row>
-    <row r="305" spans="13:13">
-      <c r="M305" s="17"/>
-    </row>
-    <row r="306" spans="13:13">
-      <c r="M306" s="17"/>
-    </row>
-    <row r="307" spans="13:13">
-      <c r="M307" s="17"/>
-    </row>
-    <row r="308" spans="13:13">
-      <c r="M308" s="17"/>
-    </row>
-    <row r="309" spans="13:13">
-      <c r="M309" s="17"/>
-    </row>
-    <row r="310" spans="13:13">
-      <c r="M310" s="17"/>
-    </row>
-    <row r="311" spans="13:13">
-      <c r="M311" s="17"/>
-    </row>
-    <row r="312" spans="13:13">
-      <c r="M312" s="17"/>
-    </row>
-    <row r="313" spans="13:13">
-      <c r="M313" s="17"/>
-    </row>
-    <row r="314" spans="13:13">
-      <c r="M314" s="17"/>
-    </row>
-    <row r="315" spans="13:13">
-      <c r="M315" s="17"/>
-    </row>
-    <row r="316" spans="13:13">
-      <c r="M316" s="17"/>
-    </row>
-    <row r="317" spans="13:13">
-      <c r="M317" s="17"/>
-    </row>
-    <row r="318" spans="13:13">
-      <c r="M318" s="17"/>
-    </row>
-    <row r="319" spans="13:13">
-      <c r="M319" s="17"/>
-    </row>
-    <row r="320" spans="13:13">
-      <c r="M320" s="17"/>
-    </row>
-    <row r="321" spans="13:13">
-      <c r="M321" s="17"/>
-    </row>
-    <row r="322" spans="13:13">
-      <c r="M322" s="17"/>
-    </row>
-    <row r="323" spans="13:13">
-      <c r="M323" s="17"/>
-    </row>
-    <row r="324" spans="13:13">
-      <c r="M324" s="17"/>
-    </row>
-    <row r="325" spans="13:13">
-      <c r="M325" s="17"/>
-    </row>
-    <row r="326" spans="13:13">
-      <c r="M326" s="17"/>
-    </row>
-    <row r="327" spans="13:13">
-      <c r="M327" s="17"/>
-    </row>
-    <row r="328" spans="13:13">
-      <c r="M328" s="17"/>
-    </row>
-    <row r="329" spans="13:13">
-      <c r="M329" s="17"/>
-    </row>
-    <row r="330" spans="13:13">
-      <c r="M330" s="17"/>
-    </row>
-    <row r="331" spans="13:13">
-      <c r="M331" s="17"/>
-    </row>
-    <row r="332" spans="13:13">
-      <c r="M332" s="17"/>
-    </row>
-    <row r="333" spans="13:13">
-      <c r="M333" s="17"/>
-    </row>
-    <row r="334" spans="13:13">
-      <c r="M334" s="17"/>
-    </row>
-    <row r="335" spans="13:13">
-      <c r="M335" s="17"/>
-    </row>
-    <row r="336" spans="13:13">
-      <c r="M336" s="17"/>
-    </row>
-    <row r="337" spans="13:13">
-      <c r="M337" s="17"/>
-    </row>
-    <row r="338" spans="13:13">
-      <c r="M338" s="17"/>
-    </row>
-    <row r="339" spans="13:13">
-      <c r="M339" s="17"/>
-    </row>
-    <row r="340" spans="13:13">
-      <c r="M340" s="17"/>
-    </row>
-    <row r="341" spans="13:13">
-      <c r="M341" s="17"/>
-    </row>
-    <row r="342" spans="13:13">
-      <c r="M342" s="17"/>
-    </row>
-    <row r="343" spans="13:13">
-      <c r="M343" s="17"/>
-    </row>
-    <row r="344" spans="13:13">
-      <c r="M344" s="17"/>
-    </row>
-    <row r="345" spans="13:13">
-      <c r="M345" s="17"/>
-    </row>
-    <row r="346" spans="13:13">
-      <c r="M346" s="17"/>
-    </row>
-    <row r="347" spans="13:13">
-      <c r="M347" s="17"/>
-    </row>
-    <row r="348" spans="13:13">
-      <c r="M348" s="17"/>
-    </row>
-    <row r="349" spans="13:13">
-      <c r="M349" s="17"/>
-    </row>
-    <row r="350" spans="13:13">
-      <c r="M350" s="17"/>
-    </row>
-    <row r="351" spans="13:13">
-      <c r="M351" s="17"/>
-    </row>
-    <row r="352" spans="13:13">
-      <c r="M352" s="17"/>
-    </row>
-    <row r="353" spans="13:13">
-      <c r="M353" s="17"/>
-    </row>
-    <row r="354" spans="13:13">
-      <c r="M354" s="17"/>
-    </row>
-    <row r="355" spans="13:13">
-      <c r="M355" s="17"/>
-    </row>
-    <row r="356" spans="13:13">
-      <c r="M356" s="17"/>
-    </row>
-    <row r="357" spans="13:13">
-      <c r="M357" s="17"/>
-    </row>
-    <row r="358" spans="13:13">
-      <c r="M358" s="17"/>
+      <c r="M158" s="4"/>
+      <c r="N158" s="13"/>
+      <c r="O158" s="11"/>
+      <c r="P158" s="14"/>
+    </row>
+    <row r="159" spans="2:16">
+      <c r="N159" s="17"/>
+    </row>
+    <row r="160" spans="2:16">
+      <c r="N160" s="17"/>
+    </row>
+    <row r="161" spans="14:14">
+      <c r="N161" s="17"/>
+    </row>
+    <row r="162" spans="14:14">
+      <c r="N162" s="17"/>
+    </row>
+    <row r="163" spans="14:14">
+      <c r="N163" s="17"/>
+    </row>
+    <row r="164" spans="14:14">
+      <c r="N164" s="17"/>
+    </row>
+    <row r="165" spans="14:14">
+      <c r="N165" s="17"/>
+    </row>
+    <row r="166" spans="14:14">
+      <c r="N166" s="17"/>
+    </row>
+    <row r="167" spans="14:14">
+      <c r="N167" s="17"/>
+    </row>
+    <row r="168" spans="14:14">
+      <c r="N168" s="17"/>
+    </row>
+    <row r="169" spans="14:14">
+      <c r="N169" s="17"/>
+    </row>
+    <row r="170" spans="14:14">
+      <c r="N170" s="17"/>
+    </row>
+    <row r="171" spans="14:14">
+      <c r="N171" s="17"/>
+    </row>
+    <row r="172" spans="14:14">
+      <c r="N172" s="17"/>
+    </row>
+    <row r="173" spans="14:14">
+      <c r="N173" s="17"/>
+    </row>
+    <row r="174" spans="14:14">
+      <c r="N174" s="17"/>
+    </row>
+    <row r="175" spans="14:14">
+      <c r="N175" s="17"/>
+    </row>
+    <row r="176" spans="14:14">
+      <c r="N176" s="17"/>
+    </row>
+    <row r="177" spans="14:14">
+      <c r="N177" s="17"/>
+    </row>
+    <row r="178" spans="14:14">
+      <c r="N178" s="17"/>
+    </row>
+    <row r="179" spans="14:14">
+      <c r="N179" s="17"/>
+    </row>
+    <row r="180" spans="14:14">
+      <c r="N180" s="17"/>
+    </row>
+    <row r="181" spans="14:14">
+      <c r="N181" s="17"/>
+    </row>
+    <row r="182" spans="14:14">
+      <c r="N182" s="17"/>
+    </row>
+    <row r="183" spans="14:14">
+      <c r="N183" s="17"/>
+    </row>
+    <row r="184" spans="14:14">
+      <c r="N184" s="17"/>
+    </row>
+    <row r="185" spans="14:14">
+      <c r="N185" s="17"/>
+    </row>
+    <row r="186" spans="14:14">
+      <c r="N186" s="17"/>
+    </row>
+    <row r="187" spans="14:14">
+      <c r="N187" s="17"/>
+    </row>
+    <row r="188" spans="14:14">
+      <c r="N188" s="17"/>
+    </row>
+    <row r="189" spans="14:14">
+      <c r="N189" s="17"/>
+    </row>
+    <row r="190" spans="14:14">
+      <c r="N190" s="17"/>
+    </row>
+    <row r="191" spans="14:14">
+      <c r="N191" s="17"/>
+    </row>
+    <row r="192" spans="14:14">
+      <c r="N192" s="17"/>
+    </row>
+    <row r="193" spans="14:14">
+      <c r="N193" s="17"/>
+    </row>
+    <row r="194" spans="14:14">
+      <c r="N194" s="17"/>
+    </row>
+    <row r="195" spans="14:14">
+      <c r="N195" s="17"/>
+    </row>
+    <row r="196" spans="14:14">
+      <c r="N196" s="17"/>
+    </row>
+    <row r="197" spans="14:14">
+      <c r="N197" s="17"/>
+    </row>
+    <row r="198" spans="14:14">
+      <c r="N198" s="17"/>
+    </row>
+    <row r="199" spans="14:14">
+      <c r="N199" s="17"/>
+    </row>
+    <row r="200" spans="14:14">
+      <c r="N200" s="17"/>
+    </row>
+    <row r="201" spans="14:14">
+      <c r="N201" s="17"/>
+    </row>
+    <row r="202" spans="14:14">
+      <c r="N202" s="17"/>
+    </row>
+    <row r="203" spans="14:14">
+      <c r="N203" s="17"/>
+    </row>
+    <row r="204" spans="14:14">
+      <c r="N204" s="17"/>
+    </row>
+    <row r="205" spans="14:14">
+      <c r="N205" s="17"/>
+    </row>
+    <row r="206" spans="14:14">
+      <c r="N206" s="17"/>
+    </row>
+    <row r="207" spans="14:14">
+      <c r="N207" s="17"/>
+    </row>
+    <row r="208" spans="14:14">
+      <c r="N208" s="17"/>
+    </row>
+    <row r="209" spans="14:14">
+      <c r="N209" s="17"/>
+    </row>
+    <row r="210" spans="14:14">
+      <c r="N210" s="17"/>
+    </row>
+    <row r="211" spans="14:14">
+      <c r="N211" s="17"/>
+    </row>
+    <row r="212" spans="14:14">
+      <c r="N212" s="17"/>
+    </row>
+    <row r="213" spans="14:14">
+      <c r="N213" s="17"/>
+    </row>
+    <row r="214" spans="14:14">
+      <c r="N214" s="17"/>
+    </row>
+    <row r="215" spans="14:14">
+      <c r="N215" s="17"/>
+    </row>
+    <row r="216" spans="14:14">
+      <c r="N216" s="17"/>
+    </row>
+    <row r="217" spans="14:14">
+      <c r="N217" s="17"/>
+    </row>
+    <row r="218" spans="14:14">
+      <c r="N218" s="17"/>
+    </row>
+    <row r="219" spans="14:14">
+      <c r="N219" s="17"/>
+    </row>
+    <row r="220" spans="14:14">
+      <c r="N220" s="17"/>
+    </row>
+    <row r="221" spans="14:14">
+      <c r="N221" s="17"/>
+    </row>
+    <row r="222" spans="14:14">
+      <c r="N222" s="17"/>
+    </row>
+    <row r="223" spans="14:14">
+      <c r="N223" s="17"/>
+    </row>
+    <row r="224" spans="14:14">
+      <c r="N224" s="17"/>
+    </row>
+    <row r="225" spans="14:14">
+      <c r="N225" s="17"/>
+    </row>
+    <row r="226" spans="14:14">
+      <c r="N226" s="17"/>
+    </row>
+    <row r="227" spans="14:14">
+      <c r="N227" s="17"/>
+    </row>
+    <row r="228" spans="14:14">
+      <c r="N228" s="17"/>
+    </row>
+    <row r="229" spans="14:14">
+      <c r="N229" s="17"/>
+    </row>
+    <row r="230" spans="14:14">
+      <c r="N230" s="17"/>
+    </row>
+    <row r="231" spans="14:14">
+      <c r="N231" s="17"/>
+    </row>
+    <row r="232" spans="14:14">
+      <c r="N232" s="17"/>
+    </row>
+    <row r="233" spans="14:14">
+      <c r="N233" s="17"/>
+    </row>
+    <row r="234" spans="14:14">
+      <c r="N234" s="17"/>
+    </row>
+    <row r="235" spans="14:14">
+      <c r="N235" s="17"/>
+    </row>
+    <row r="236" spans="14:14">
+      <c r="N236" s="17"/>
+    </row>
+    <row r="237" spans="14:14">
+      <c r="N237" s="17"/>
+    </row>
+    <row r="238" spans="14:14">
+      <c r="N238" s="17"/>
+    </row>
+    <row r="239" spans="14:14">
+      <c r="N239" s="17"/>
+    </row>
+    <row r="240" spans="14:14">
+      <c r="N240" s="17"/>
+    </row>
+    <row r="241" spans="14:14">
+      <c r="N241" s="17"/>
+    </row>
+    <row r="242" spans="14:14">
+      <c r="N242" s="17"/>
+    </row>
+    <row r="243" spans="14:14">
+      <c r="N243" s="17"/>
+    </row>
+    <row r="244" spans="14:14">
+      <c r="N244" s="17"/>
+    </row>
+    <row r="245" spans="14:14">
+      <c r="N245" s="17"/>
+    </row>
+    <row r="246" spans="14:14">
+      <c r="N246" s="17"/>
+    </row>
+    <row r="247" spans="14:14">
+      <c r="N247" s="17"/>
+    </row>
+    <row r="248" spans="14:14">
+      <c r="N248" s="17"/>
+    </row>
+    <row r="249" spans="14:14">
+      <c r="N249" s="17"/>
+    </row>
+    <row r="250" spans="14:14">
+      <c r="N250" s="17"/>
+    </row>
+    <row r="251" spans="14:14">
+      <c r="N251" s="17"/>
+    </row>
+    <row r="252" spans="14:14">
+      <c r="N252" s="17"/>
+    </row>
+    <row r="253" spans="14:14">
+      <c r="N253" s="17"/>
+    </row>
+    <row r="254" spans="14:14">
+      <c r="N254" s="17"/>
+    </row>
+    <row r="255" spans="14:14">
+      <c r="N255" s="17"/>
+    </row>
+    <row r="256" spans="14:14">
+      <c r="N256" s="17"/>
+    </row>
+    <row r="257" spans="14:14">
+      <c r="N257" s="17"/>
+    </row>
+    <row r="258" spans="14:14">
+      <c r="N258" s="17"/>
+    </row>
+    <row r="259" spans="14:14">
+      <c r="N259" s="17"/>
+    </row>
+    <row r="260" spans="14:14">
+      <c r="N260" s="17"/>
+    </row>
+    <row r="261" spans="14:14">
+      <c r="N261" s="17"/>
+    </row>
+    <row r="262" spans="14:14">
+      <c r="N262" s="17"/>
+    </row>
+    <row r="263" spans="14:14">
+      <c r="N263" s="17"/>
+    </row>
+    <row r="264" spans="14:14">
+      <c r="N264" s="17"/>
+    </row>
+    <row r="265" spans="14:14">
+      <c r="N265" s="17"/>
+    </row>
+    <row r="266" spans="14:14">
+      <c r="N266" s="17"/>
+    </row>
+    <row r="267" spans="14:14">
+      <c r="N267" s="17"/>
+    </row>
+    <row r="268" spans="14:14">
+      <c r="N268" s="17"/>
+    </row>
+    <row r="269" spans="14:14">
+      <c r="N269" s="17"/>
+    </row>
+    <row r="270" spans="14:14">
+      <c r="N270" s="17"/>
+    </row>
+    <row r="271" spans="14:14">
+      <c r="N271" s="17"/>
+    </row>
+    <row r="272" spans="14:14">
+      <c r="N272" s="17"/>
+    </row>
+    <row r="273" spans="14:14">
+      <c r="N273" s="17"/>
+    </row>
+    <row r="274" spans="14:14">
+      <c r="N274" s="17"/>
+    </row>
+    <row r="275" spans="14:14">
+      <c r="N275" s="17"/>
+    </row>
+    <row r="276" spans="14:14">
+      <c r="N276" s="17"/>
+    </row>
+    <row r="277" spans="14:14">
+      <c r="N277" s="17"/>
+    </row>
+    <row r="278" spans="14:14">
+      <c r="N278" s="17"/>
+    </row>
+    <row r="279" spans="14:14">
+      <c r="N279" s="17"/>
+    </row>
+    <row r="280" spans="14:14">
+      <c r="N280" s="17"/>
+    </row>
+    <row r="281" spans="14:14">
+      <c r="N281" s="17"/>
+    </row>
+    <row r="282" spans="14:14">
+      <c r="N282" s="17"/>
+    </row>
+    <row r="283" spans="14:14">
+      <c r="N283" s="17"/>
+    </row>
+    <row r="284" spans="14:14">
+      <c r="N284" s="17"/>
+    </row>
+    <row r="285" spans="14:14">
+      <c r="N285" s="17"/>
+    </row>
+    <row r="286" spans="14:14">
+      <c r="N286" s="17"/>
+    </row>
+    <row r="287" spans="14:14">
+      <c r="N287" s="17"/>
+    </row>
+    <row r="288" spans="14:14">
+      <c r="N288" s="17"/>
+    </row>
+    <row r="289" spans="14:14">
+      <c r="N289" s="17"/>
+    </row>
+    <row r="290" spans="14:14">
+      <c r="N290" s="17"/>
+    </row>
+    <row r="291" spans="14:14">
+      <c r="N291" s="17"/>
+    </row>
+    <row r="292" spans="14:14">
+      <c r="N292" s="17"/>
+    </row>
+    <row r="293" spans="14:14">
+      <c r="N293" s="17"/>
+    </row>
+    <row r="294" spans="14:14">
+      <c r="N294" s="17"/>
+    </row>
+    <row r="295" spans="14:14">
+      <c r="N295" s="17"/>
+    </row>
+    <row r="296" spans="14:14">
+      <c r="N296" s="17"/>
+    </row>
+    <row r="297" spans="14:14">
+      <c r="N297" s="17"/>
+    </row>
+    <row r="298" spans="14:14">
+      <c r="N298" s="17"/>
+    </row>
+    <row r="299" spans="14:14">
+      <c r="N299" s="17"/>
+    </row>
+    <row r="300" spans="14:14">
+      <c r="N300" s="17"/>
+    </row>
+    <row r="301" spans="14:14">
+      <c r="N301" s="17"/>
+    </row>
+    <row r="302" spans="14:14">
+      <c r="N302" s="17"/>
+    </row>
+    <row r="303" spans="14:14">
+      <c r="N303" s="17"/>
+    </row>
+    <row r="304" spans="14:14">
+      <c r="N304" s="17"/>
+    </row>
+    <row r="305" spans="14:14">
+      <c r="N305" s="17"/>
+    </row>
+    <row r="306" spans="14:14">
+      <c r="N306" s="17"/>
+    </row>
+    <row r="307" spans="14:14">
+      <c r="N307" s="17"/>
+    </row>
+    <row r="308" spans="14:14">
+      <c r="N308" s="17"/>
+    </row>
+    <row r="309" spans="14:14">
+      <c r="N309" s="17"/>
+    </row>
+    <row r="310" spans="14:14">
+      <c r="N310" s="17"/>
+    </row>
+    <row r="311" spans="14:14">
+      <c r="N311" s="17"/>
+    </row>
+    <row r="312" spans="14:14">
+      <c r="N312" s="17"/>
+    </row>
+    <row r="313" spans="14:14">
+      <c r="N313" s="17"/>
+    </row>
+    <row r="314" spans="14:14">
+      <c r="N314" s="17"/>
+    </row>
+    <row r="315" spans="14:14">
+      <c r="N315" s="17"/>
+    </row>
+    <row r="316" spans="14:14">
+      <c r="N316" s="17"/>
+    </row>
+    <row r="317" spans="14:14">
+      <c r="N317" s="17"/>
+    </row>
+    <row r="318" spans="14:14">
+      <c r="N318" s="17"/>
+    </row>
+    <row r="319" spans="14:14">
+      <c r="N319" s="17"/>
+    </row>
+    <row r="320" spans="14:14">
+      <c r="N320" s="17"/>
+    </row>
+    <row r="321" spans="14:14">
+      <c r="N321" s="17"/>
+    </row>
+    <row r="322" spans="14:14">
+      <c r="N322" s="17"/>
+    </row>
+    <row r="323" spans="14:14">
+      <c r="N323" s="17"/>
+    </row>
+    <row r="324" spans="14:14">
+      <c r="N324" s="17"/>
+    </row>
+    <row r="325" spans="14:14">
+      <c r="N325" s="17"/>
+    </row>
+    <row r="326" spans="14:14">
+      <c r="N326" s="17"/>
+    </row>
+    <row r="327" spans="14:14">
+      <c r="N327" s="17"/>
+    </row>
+    <row r="328" spans="14:14">
+      <c r="N328" s="17"/>
+    </row>
+    <row r="329" spans="14:14">
+      <c r="N329" s="17"/>
+    </row>
+    <row r="330" spans="14:14">
+      <c r="N330" s="17"/>
+    </row>
+    <row r="331" spans="14:14">
+      <c r="N331" s="17"/>
+    </row>
+    <row r="332" spans="14:14">
+      <c r="N332" s="17"/>
+    </row>
+    <row r="333" spans="14:14">
+      <c r="N333" s="17"/>
+    </row>
+    <row r="334" spans="14:14">
+      <c r="N334" s="17"/>
+    </row>
+    <row r="335" spans="14:14">
+      <c r="N335" s="17"/>
+    </row>
+    <row r="336" spans="14:14">
+      <c r="N336" s="17"/>
+    </row>
+    <row r="337" spans="14:14">
+      <c r="N337" s="17"/>
+    </row>
+    <row r="338" spans="14:14">
+      <c r="N338" s="17"/>
+    </row>
+    <row r="339" spans="14:14">
+      <c r="N339" s="17"/>
+    </row>
+    <row r="340" spans="14:14">
+      <c r="N340" s="17"/>
+    </row>
+    <row r="341" spans="14:14">
+      <c r="N341" s="17"/>
+    </row>
+    <row r="342" spans="14:14">
+      <c r="N342" s="17"/>
+    </row>
+    <row r="343" spans="14:14">
+      <c r="N343" s="17"/>
+    </row>
+    <row r="344" spans="14:14">
+      <c r="N344" s="17"/>
+    </row>
+    <row r="345" spans="14:14">
+      <c r="N345" s="17"/>
+    </row>
+    <row r="346" spans="14:14">
+      <c r="N346" s="17"/>
+    </row>
+    <row r="347" spans="14:14">
+      <c r="N347" s="17"/>
+    </row>
+    <row r="348" spans="14:14">
+      <c r="N348" s="17"/>
+    </row>
+    <row r="349" spans="14:14">
+      <c r="N349" s="17"/>
+    </row>
+    <row r="350" spans="14:14">
+      <c r="N350" s="17"/>
+    </row>
+    <row r="351" spans="14:14">
+      <c r="N351" s="17"/>
+    </row>
+    <row r="352" spans="14:14">
+      <c r="N352" s="17"/>
+    </row>
+    <row r="353" spans="14:14">
+      <c r="N353" s="17"/>
+    </row>
+    <row r="354" spans="14:14">
+      <c r="N354" s="17"/>
+    </row>
+    <row r="355" spans="14:14">
+      <c r="N355" s="17"/>
+    </row>
+    <row r="356" spans="14:14">
+      <c r="N356" s="17"/>
+    </row>
+    <row r="357" spans="14:14">
+      <c r="N357" s="17"/>
+    </row>
+    <row r="358" spans="14:14">
+      <c r="N358" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:P2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <mergeCells count="4">
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="M1:P1"/>
+  <autoFilter ref="B2:Q2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <mergeCells count="5">
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="N1:Q1"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4557,7 +4608,7 @@
         <v>86</v>
       </c>
       <c r="C16" s="29">
-        <f>MAX(Portfolio_Mgmt!C30,C10:C15)</f>
+        <f>MAX(Portfolio_Mgmt!C31,C10:C15)</f>
         <v>0.1174</v>
       </c>
     </row>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F8E314-4E37-4939-A396-ECA57E24AB65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D5BC640-7EF0-4C3D-9DEA-A919D6BE7CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -267,14 +267,6 @@
   </si>
   <si>
     <t>Selected</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Y</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -850,6 +842,12 @@
   <si>
     <t>Allocation Percentage</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
 </sst>
 </file>
@@ -1250,10 +1248,10 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1597,12 +1595,12 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="34" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="35" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B2" s="35"/>
       <c r="C2" s="35"/>
@@ -1611,7 +1609,7 @@
     </row>
     <row r="4" spans="1:5" ht="36.6" customHeight="1">
       <c r="B4" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C4" s="54"/>
       <c r="D4" s="54"/>
@@ -1619,16 +1617,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="34" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C6" s="33"/>
     </row>
     <row r="7" spans="1:5" ht="24.4" customHeight="1">
       <c r="B7" s="54" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C7" s="54"/>
       <c r="D7" s="54"/>
@@ -1636,12 +1634,12 @@
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="40" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C10" s="4">
         <f>Market_Yield!C16</f>
@@ -1650,7 +1648,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="B11" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C11" s="4">
         <f>Market_Yield!C6</f>
@@ -1662,59 +1660,59 @@
     </row>
     <row r="13" spans="1:5">
       <c r="B13" s="40" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C13" s="4"/>
     </row>
     <row r="14" spans="1:5">
       <c r="B14" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C14" s="41" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="B15" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="B17" s="40" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="B18" s="41" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="B19" s="41" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="B20" s="41" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B22" s="32" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C22" s="33"/>
     </row>
     <row r="23" spans="1:5" ht="24.4" customHeight="1">
       <c r="A23" s="31"/>
       <c r="B23" s="54" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C23" s="54"/>
       <c r="D23" s="54"/>
@@ -1726,12 +1724,12 @@
     <row r="25" spans="1:5">
       <c r="A25" s="31"/>
       <c r="B25" s="40" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="B26" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C26" s="37">
         <v>10</v>
@@ -1739,7 +1737,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="B27" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C27" s="52">
         <v>0.3</v>
@@ -1747,7 +1745,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="34" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B29" s="32" t="s">
         <v>27</v>
@@ -1763,7 +1761,7 @@
         <v>0.2</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E30" s="39">
         <v>3</v>
@@ -1780,12 +1778,12 @@
     </row>
     <row r="33" spans="1:5">
       <c r="B33" s="34" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="24.4" customHeight="1">
       <c r="B34" s="54" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C34" s="54"/>
       <c r="D34" s="54"/>
@@ -1793,7 +1791,7 @@
     </row>
     <row r="35" spans="1:5" ht="24.4" customHeight="1">
       <c r="B35" s="54" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C35" s="54"/>
       <c r="D35" s="54"/>
@@ -1801,7 +1799,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="35" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B37" s="35"/>
       <c r="C37" s="35"/>
@@ -1810,7 +1808,7 @@
     </row>
     <row r="39" spans="1:5" ht="24.4" customHeight="1">
       <c r="B39" s="54" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C39" s="54"/>
       <c r="D39" s="54"/>
@@ -1818,20 +1816,20 @@
     </row>
     <row r="41" spans="1:5">
       <c r="B41" s="40" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="12.4">
       <c r="B43" s="51" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C43" s="51" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="B44" s="43" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C44" s="49">
         <v>0.5</v>
@@ -1839,7 +1837,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="B45" s="43" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C45" s="49">
         <v>0.3</v>
@@ -1847,7 +1845,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C46" s="49">
         <v>0.2</v>
@@ -1855,32 +1853,32 @@
     </row>
     <row r="48" spans="1:5">
       <c r="B48" s="40" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="12.4">
       <c r="B50" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="C50" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="D50" s="51" t="s">
         <v>130</v>
       </c>
-      <c r="C50" s="51" t="s">
+      <c r="E50" s="51" t="s">
         <v>131</v>
-      </c>
-      <c r="D50" s="51" t="s">
-        <v>132</v>
-      </c>
-      <c r="E50" s="51" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="B51" s="43" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C51" s="43" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D51" s="43" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E51" s="44">
         <v>1</v>
@@ -1888,13 +1886,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="B52" s="43" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C52" s="43" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D52" s="43" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E52" s="44">
         <v>2</v>
@@ -1902,13 +1900,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="B53" s="43" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C53" s="43" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D53" s="43" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E53" s="44">
         <v>1</v>
@@ -1916,13 +1914,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="B54" s="43" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C54" s="43" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D54" s="43" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E54" s="44">
         <v>1</v>
@@ -1930,7 +1928,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="D55" s="45" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E55" s="48">
         <f>SUM(E51:E54)</f>
@@ -1939,7 +1937,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="B57" s="40" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C57" s="50">
         <f>IF(E55&lt;=2,C44,IF(E55&gt;=6,C46,C45))</f>
@@ -1948,12 +1946,12 @@
     </row>
     <row r="59" spans="1:5">
       <c r="B59" s="47" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="35" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B61" s="35"/>
       <c r="C61" s="35"/>
@@ -1962,32 +1960,32 @@
     </row>
     <row r="63" spans="1:5">
       <c r="B63" s="34" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="B64" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" s="46" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="69" spans="2:2">
       <c r="B69" s="34" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" s="41" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="71" spans="2:2">
@@ -1998,37 +1996,37 @@
     </row>
     <row r="73" spans="2:2">
       <c r="B73" s="34" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="74" spans="2:2">
       <c r="B74" s="41" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="76" spans="2:2">
       <c r="B76" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78" s="41" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="79" spans="2:2">
       <c r="B79" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="35" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B81" s="35"/>
       <c r="C81" s="35"/>
@@ -2037,22 +2035,22 @@
     </row>
     <row r="83" spans="1:5">
       <c r="B83" s="34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="B84" s="41" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="B85" s="41" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="B86" s="41" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2098,13 +2096,13 @@
       <c r="B1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="57" t="s">
+      <c r="D1" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
       <c r="G1" s="59" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H1" s="59"/>
       <c r="I1" s="59"/>
@@ -2116,12 +2114,12 @@
         <v>9</v>
       </c>
       <c r="M1" s="56"/>
-      <c r="N1" s="58" t="s">
-        <v>67</v>
-      </c>
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
+      <c r="N1" s="57" t="s">
+        <v>65</v>
+      </c>
+      <c r="O1" s="57"/>
+      <c r="P1" s="57"/>
+      <c r="Q1" s="57"/>
     </row>
     <row r="2" spans="1:17" ht="26" customHeight="1">
       <c r="B2" s="7" t="s">
@@ -2140,13 +2138,13 @@
         <v>11</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>8</v>
@@ -2175,100 +2173,106 @@
     </row>
     <row r="3" spans="1:17">
       <c r="B3" s="11" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D3" s="2">
-        <v>14.96</v>
+        <v>7.79</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="15">
-        <v>0.1950811274187132</v>
+        <v>0.12411921460409614</v>
       </c>
       <c r="G3" s="15">
-        <f>F3-benchmark</f>
-        <v>7.7681127418713192E-2</v>
+        <f>F3 - Portfolio_Mgmt!$C$10</f>
+        <v>6.7192146040961354E-3</v>
       </c>
       <c r="H3" s="15">
-        <f>F3-Cash_Yield</f>
-        <v>0.16058112741871319</v>
+        <f>F3 - Portfolio_Mgmt!$C$11</f>
+        <v>8.9619214604096137E-2</v>
+      </c>
+      <c r="I3" s="15">
+        <v>0.39999999999999997</v>
       </c>
       <c r="J3" s="2">
-        <v>14.789930718256866</v>
+        <v>6.4883606756817951</v>
       </c>
       <c r="K3" s="2">
-        <v>20.606600281147866</v>
+        <v>9.1006872475781417</v>
       </c>
       <c r="L3" s="4">
-        <v>0.11542469246132268</v>
+        <v>3.9653192809019897E-2</v>
       </c>
       <c r="M3" s="4">
-        <v>9.0909090909090912E-2</v>
+        <v>7.4454428754813853E-2</v>
       </c>
       <c r="N3" s="13" t="s">
         <v>17</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="P3" s="14">
         <v>45716</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>65</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="B4" s="11" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D4" s="2">
-        <v>7.79</v>
+        <v>14.96</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="15">
-        <v>0.12172735692567005</v>
+        <v>0.19343775079136272</v>
       </c>
       <c r="G4" s="15">
-        <f>F4-benchmark</f>
-        <v>4.327356925670045E-3</v>
+        <f>F4 - Portfolio_Mgmt!$C$10</f>
+        <v>7.6037750791362713E-2</v>
       </c>
       <c r="H4" s="15">
-        <f>F4-Cash_Yield</f>
-        <v>8.7227356925670047E-2</v>
+        <f>F4 - Portfolio_Mgmt!$C$11</f>
+        <v>0.15893775079136271</v>
+      </c>
+      <c r="I4" s="15">
+        <v>0.3</v>
       </c>
       <c r="J4" s="2">
-        <v>6.4501768017717804</v>
+        <v>14.733437767356989</v>
       </c>
       <c r="K4" s="2">
-        <v>9.0347055134616365</v>
+        <v>20.508980461992877</v>
       </c>
       <c r="L4" s="4">
-        <v>3.9909901100125003E-2</v>
+        <v>0.11550708685625866</v>
       </c>
       <c r="M4" s="4">
-        <v>7.4454428754813853E-2</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="N4" s="13" t="s">
         <v>17</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="P4" s="14">
         <v>45716</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>65</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -2285,24 +2289,27 @@
         <v>16</v>
       </c>
       <c r="F5" s="15">
-        <v>6.9675781490122768E-2</v>
+        <v>6.3214262000776955E-2</v>
       </c>
       <c r="G5" s="15">
-        <f>F5-benchmark</f>
-        <v>-4.7724218509877236E-2</v>
+        <f>F5 - Portfolio_Mgmt!$C$10</f>
+        <v>-5.4185737999223049E-2</v>
       </c>
       <c r="H5" s="15">
-        <f>F5-Cash_Yield</f>
-        <v>3.5175781490122765E-2</v>
+        <f>F5 - Portfolio_Mgmt!$C$11</f>
+        <v>2.8714262000776952E-2</v>
+      </c>
+      <c r="I5" s="15">
+        <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>1.5731270460314284</v>
+        <v>1.5466941106484338</v>
       </c>
       <c r="K5" s="2">
-        <v>2.2895715355423083</v>
+        <v>2.2438954232004935</v>
       </c>
       <c r="L5" s="4">
-        <v>2.0974048836286365E-2</v>
+        <v>2.1574888673832972E-2</v>
       </c>
       <c r="M5" s="4">
         <v>5.4036697247706419E-2</v>
@@ -2317,7 +2324,7 @@
         <v>45716</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>66</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -4451,7 +4458,6 @@
       <c r="N358" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:Q2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="5">
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="L1:M1"/>
@@ -4546,10 +4552,16 @@
       <c r="B8" s="19" t="s">
         <v>37</v>
       </c>
+      <c r="C8" s="22">
+        <v>4.3099999999999999E-2</v>
+      </c>
+      <c r="D8" s="22">
+        <v>7.4999999999999997E-2</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C9" s="23" t="s">
         <v>38</v>
@@ -4605,7 +4617,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="B16" s="28" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C16" s="29">
         <f>MAX(Portfolio_Mgmt!C31,C10:C15)</f>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D5BC640-7EF0-4C3D-9DEA-A919D6BE7CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1C9F5F-7B0A-4617-A0E7-F369DE2CC95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
     <sheet name="Opportunities" sheetId="1" r:id="rId2"/>
     <sheet name="Market_Yield" sheetId="2" r:id="rId3"/>
+    <sheet name="Comp_Group" sheetId="6" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Opportunities!$B$2:$Q$2</definedName>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="194">
   <si>
     <t>Name</t>
   </si>
@@ -89,9 +90,6 @@
     <t>HKD</t>
   </si>
   <si>
-    <t>C0003</t>
-  </si>
-  <si>
     <t>Negative Growth Asset Play</t>
   </si>
   <si>
@@ -108,9 +106,6 @@
   </si>
   <si>
     <t>朝云集团</t>
-  </si>
-  <si>
-    <t>C0001</t>
   </si>
   <si>
     <t xml:space="preserve">Low Growth </t>
@@ -677,27 +672,27 @@
   </si>
   <si>
     <t>Scenario</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Cash Allocation</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">Indicator	</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Low Risk Appetite (Hold Cash)</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>High Risk Appetite (Deploy Cash)</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Score (0-2)</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>- Rank investments by Attractiveness</t>
@@ -849,6 +844,317 @@
   <si>
     <t>N</t>
   </si>
+  <si>
+    <t>Guidance Note: Comparison Group Classification System</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Overview</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The classification uses two mutually exclusive and collectively exhaustive (MECE) layers:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Format: [Layer 1 Code]_[Layer 2 Number] (e.g., TMT_02, CNS_10).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Layer 1: Broad industry categories (3-character codes).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Layer 2: Granular subcategories (two-digit numbers, 01–99).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Layer 1: Broad Industry Categories</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Purpose: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Group investments by overarching industries.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Structure: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3-character codes (e.g., TMT, CNS, FIN).</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TMT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FIN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HLT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Technology, Media, Telecom</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Consumer</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Financials</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Healthcare</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Code</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Industry</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Layer 2: Subcategory Numbering</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Purpose: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Refine peer groups into specific segments within Layer 1 industries.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Purpose: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Two-digit numbers (01–99), appended to Layer 1 codes (e.g., TMT_01).</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assigning Classifications</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Identify Layer 1:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map the investment to the broadest applicable industry (e.g., a fintech firm → FIN).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assign Layer 2:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ii.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Select the most specific subcategory number (e.g., fintech → FIN_10).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use Cases</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Peer Benchmarking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Compare HLT_03 (Biotech) companies against each other.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Portfolio Analysis:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Aggregate exposures by Layer 1 (e.g., “30% of portfolio is in TMT”).</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Reporting:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Standardize disclosures using codes (e.g., “Investment X (CNS_05) outperformed peers”).</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IND</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Industrials</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ENG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Energy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MAT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Materials</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UTL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Utilities</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>9 Standard Industry Codes:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RES</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Real Estate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RES_01</t>
+  </si>
+  <si>
+    <t>CNS_05</t>
+  </si>
+  <si>
+    <t>CNS_04</t>
+  </si>
+  <si>
+    <t>Market Yields Tracker</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -859,7 +1165,7 @@
     <numFmt numFmtId="177" formatCode="[$-13C09]d\ mmm\ yyyy;@"/>
     <numFmt numFmtId="178" formatCode="0&quot; yrs&quot;"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -914,45 +1220,6 @@
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF002060"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -1024,6 +1291,19 @@
       <name val="DengXian"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1132,7 +1412,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1173,47 +1453,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="178" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1222,24 +1479,24 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1257,6 +1514,31 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1594,52 +1876,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="34" t="s">
-        <v>68</v>
+      <c r="A1" s="21" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
+      <c r="A2" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
     </row>
     <row r="4" spans="1:5" ht="36.6" customHeight="1">
-      <c r="B4" s="54" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
+      <c r="B4" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="33"/>
+      <c r="A6" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="20"/>
     </row>
     <row r="7" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B7" s="54" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
+      <c r="B7" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="B9" s="40" t="s">
-        <v>72</v>
+      <c r="B9" s="27" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C10" s="4">
         <f>Market_Yield!C16</f>
@@ -1648,7 +1930,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="B11" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C11" s="4">
         <f>Market_Yield!C6</f>
@@ -1659,333 +1941,333 @@
       <c r="C12" s="4"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="B13" s="40" t="s">
-        <v>76</v>
+      <c r="B13" s="27" t="s">
+        <v>74</v>
       </c>
       <c r="C13" s="4"/>
     </row>
     <row r="14" spans="1:5">
       <c r="B14" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="41" t="s">
-        <v>82</v>
+        <v>71</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="B15" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="B17" s="27" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="B17" s="40" t="s">
-        <v>77</v>
-      </c>
-    </row>
     <row r="18" spans="1:5">
-      <c r="B18" s="41" t="s">
-        <v>143</v>
+      <c r="B18" s="28" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="28" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="B20" s="28" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" s="20"/>
+    </row>
+    <row r="23" spans="1:5" ht="24.4" customHeight="1">
+      <c r="A23" s="18"/>
+      <c r="B23" s="41" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="B20" s="41" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="B22" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="C22" s="33"/>
-    </row>
-    <row r="23" spans="1:5" ht="24.4" customHeight="1">
-      <c r="A23" s="31"/>
-      <c r="B23" s="54" t="s">
-        <v>113</v>
-      </c>
-      <c r="C23" s="54"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="54"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="31"/>
+      <c r="A24" s="18"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="31"/>
-      <c r="B25" s="40" t="s">
-        <v>80</v>
+      <c r="A25" s="18"/>
+      <c r="B25" s="27" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="B26" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C26" s="37">
+        <v>112</v>
+      </c>
+      <c r="C26" s="24">
         <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="B27" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" s="52">
+        <v>79</v>
+      </c>
+      <c r="C27" s="39">
         <v>0.3</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="B29" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="33"/>
-      <c r="D29" s="36"/>
+      <c r="A29" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="20"/>
+      <c r="D29" s="23"/>
     </row>
     <row r="30" spans="1:5">
       <c r="B30" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30" s="53">
+        <v>26</v>
+      </c>
+      <c r="C30" s="40">
         <v>0.2</v>
       </c>
-      <c r="D30" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="E30" s="39">
+      <c r="D30" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E30" s="26">
         <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="B31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="38">
+        <v>27</v>
+      </c>
+      <c r="C31" s="25">
         <f>MAX(8%,Market_Yield!C4:D6)</f>
         <v>0.08</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="B33" s="34" t="s">
+      <c r="B33" s="21" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B34" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+    </row>
+    <row r="35" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B35" s="41" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B34" s="54" t="s">
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+    </row>
+    <row r="39" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B39" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="C39" s="41"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="B41" s="27" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="12.4">
+      <c r="B43" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="C43" s="38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="B44" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="C44" s="36">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="B45" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="C45" s="36">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="B46" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="C46" s="36">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="B48" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="54"/>
-      <c r="D34" s="54"/>
-      <c r="E34" s="54"/>
-    </row>
-    <row r="35" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B35" s="54" t="s">
-        <v>117</v>
-      </c>
-      <c r="C35" s="54"/>
-      <c r="D35" s="54"/>
-      <c r="E35" s="54"/>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="35" t="s">
+    </row>
+    <row r="50" spans="1:5" ht="12.4">
+      <c r="B50" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="C50" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="D50" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="E50" s="38" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="B51" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="D51" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="E51" s="31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="B52" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="B37" s="35"/>
-      <c r="C37" s="35"/>
-      <c r="D37" s="35"/>
-      <c r="E37" s="35"/>
-    </row>
-    <row r="39" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B39" s="54" t="s">
-        <v>119</v>
-      </c>
-      <c r="C39" s="54"/>
-      <c r="D39" s="54"/>
-      <c r="E39" s="54"/>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="B41" s="40" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="12.4">
-      <c r="B43" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="C43" s="51" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="B44" s="43" t="s">
-        <v>121</v>
-      </c>
-      <c r="C44" s="49">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="B45" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="C45" s="49">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="B46" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="C46" s="49">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="B48" s="40" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="12.4">
-      <c r="B50" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="C50" s="51" t="s">
-        <v>129</v>
-      </c>
-      <c r="D50" s="51" t="s">
-        <v>130</v>
-      </c>
-      <c r="E50" s="51" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="B51" s="43" t="s">
+      <c r="C52" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D52" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="E52" s="31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="B53" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="C51" s="43" t="s">
-        <v>97</v>
-      </c>
-      <c r="D51" s="43" t="s">
+      <c r="C53" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="D53" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="E51" s="44">
+      <c r="E53" s="31">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
-      <c r="B52" s="43" t="s">
+    <row r="54" spans="1:5">
+      <c r="B54" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="C52" s="43" t="s">
+      <c r="C54" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="D52" s="43" t="s">
+      <c r="D54" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="E52" s="44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="B53" s="43" t="s">
-        <v>92</v>
-      </c>
-      <c r="C53" s="43" t="s">
-        <v>95</v>
-      </c>
-      <c r="D53" s="43" t="s">
+      <c r="E54" s="31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="D55" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="E53" s="44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="B54" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="C54" s="43" t="s">
-        <v>96</v>
-      </c>
-      <c r="D54" s="43" t="s">
-        <v>101</v>
-      </c>
-      <c r="E54" s="44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="D55" s="45" t="s">
-        <v>102</v>
-      </c>
-      <c r="E55" s="48">
+      <c r="E55" s="35">
         <f>SUM(E51:E54)</f>
         <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:5">
-      <c r="B57" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="C57" s="50">
+      <c r="B57" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C57" s="37">
         <f>IF(E55&lt;=2,C44,IF(E55&gt;=6,C46,C45))</f>
         <v>0.3</v>
       </c>
     </row>
     <row r="59" spans="1:5">
-      <c r="B59" s="47" t="s">
-        <v>141</v>
+      <c r="B59" s="34" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="B61" s="35"/>
-      <c r="C61" s="35"/>
-      <c r="D61" s="35"/>
-      <c r="E61" s="35"/>
+      <c r="A61" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="B61" s="22"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
     </row>
     <row r="63" spans="1:5">
-      <c r="B63" s="34" t="s">
-        <v>142</v>
+      <c r="B63" s="21" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="B64" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="66" spans="2:2">
-      <c r="B66" s="46" t="s">
-        <v>104</v>
+      <c r="B66" s="33" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="69" spans="2:2">
-      <c r="B69" s="34" t="s">
-        <v>106</v>
+      <c r="B69" s="21" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="70" spans="2:2">
-      <c r="B70" s="41" t="s">
-        <v>132</v>
+      <c r="B70" s="28" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="71" spans="2:2">
@@ -1995,62 +2277,62 @@
       </c>
     </row>
     <row r="73" spans="2:2">
-      <c r="B73" s="34" t="s">
+      <c r="B73" s="21" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="28" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="74" spans="2:2">
-      <c r="B74" s="41" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="76" spans="2:2">
       <c r="B76" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="78" spans="2:2">
-      <c r="B78" s="41" t="s">
-        <v>136</v>
+      <c r="B78" s="28" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="79" spans="2:2">
       <c r="B79" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="B81" s="22"/>
+      <c r="C81" s="22"/>
+      <c r="D81" s="22"/>
+      <c r="E81" s="22"/>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="B83" s="21" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="B84" s="28" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="B85" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="B86" s="28" t="s">
         <v>137</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="B81" s="35"/>
-      <c r="C81" s="35"/>
-      <c r="D81" s="35"/>
-      <c r="E81" s="35"/>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="B83" s="34" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="B84" s="41" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="B85" s="41" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="B86" s="41" t="s">
-        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2096,30 +2378,30 @@
       <c r="B1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="58" t="s">
+      <c r="D1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="59" t="s">
-        <v>145</v>
-      </c>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="55" t="s">
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="55"/>
-      <c r="L1" s="56" t="s">
+      <c r="K1" s="42"/>
+      <c r="L1" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="56"/>
-      <c r="N1" s="57" t="s">
-        <v>65</v>
-      </c>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="44" t="s">
+        <v>63</v>
+      </c>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
     </row>
     <row r="2" spans="1:17" ht="26" customHeight="1">
       <c r="B2" s="7" t="s">
@@ -2138,13 +2420,13 @@
         <v>11</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>8</v>
@@ -2162,13 +2444,13 @@
         <v>6</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P2" s="9" t="s">
         <v>10</v>
       </c>
       <c r="Q2" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -2211,24 +2493,24 @@
         <v>7.4454428754813853E-2</v>
       </c>
       <c r="N3" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="O3" s="11" t="s">
         <v>17</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>18</v>
       </c>
       <c r="P3" s="14">
         <v>45716</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="B4" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>19</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>20</v>
       </c>
       <c r="D4" s="2">
         <v>14.96</v>
@@ -2263,24 +2545,24 @@
         <v>9.0909090909090912E-2</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>17</v>
+        <v>191</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P4" s="14">
         <v>45716</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="B5" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>23</v>
       </c>
       <c r="D5" s="2">
         <v>2.1800000000000002</v>
@@ -2315,16 +2597,16 @@
         <v>5.4036697247706419E-2</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P5" s="14">
         <v>45716</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -4473,245 +4755,250 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62760D14-1F64-4D73-BBAC-22718A84BD18}">
-  <dimension ref="A2:E31"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.9"/>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.46484375" style="22" customWidth="1"/>
-    <col min="2" max="2" width="30.19921875" style="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15.59765625" style="22" customWidth="1"/>
-    <col min="6" max="16384" width="8.796875" style="22"/>
+    <col min="1" max="1" width="2.46484375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15.59765625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" ht="15">
-      <c r="A2" s="18"/>
-      <c r="B2" s="19" t="s">
+    <row r="1" spans="1:5">
+      <c r="B1" s="21" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="18"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="18"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="C3" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="20"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="C3" s="23" t="s">
+      <c r="E3" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="23" t="s">
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="23" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="B4" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="25">
+      <c r="C4" s="53">
         <v>4.2500000000000003E-2</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="53">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="54">
         <f>D4-C4</f>
         <v>3.2499999999999994E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="B5" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="25">
+      <c r="B5" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="53">
         <v>1.9E-2</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="53">
         <v>3.1E-2</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="54">
         <f>D5-C5</f>
         <v>1.2E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="B6" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="25">
+      <c r="B6" s="52" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="53">
         <v>3.4500000000000003E-2</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="53">
         <v>5.2499999999999998E-2</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="54">
         <f>D6-C6</f>
         <v>1.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15">
-      <c r="A8" s="18"/>
-      <c r="B8" s="19" t="s">
+    <row r="8" spans="1:5">
+      <c r="A8" s="50"/>
+      <c r="B8" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="1">
+        <v>4.3099999999999999E-2</v>
+      </c>
+      <c r="D8" s="1">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="B9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="22">
-        <v>4.3099999999999999E-2</v>
-      </c>
-      <c r="D8" s="22">
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="B9" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="23" t="s">
+      <c r="C10" s="53">
+        <v>9.9400000000000002E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="B11" s="30" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="B10" s="27" t="s">
+      <c r="C11" s="53">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="B12" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="25">
-        <v>9.9400000000000002E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="B11" s="27" t="s">
+      <c r="C12" s="53">
+        <v>3.4500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="B13" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="25">
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="B12" s="27" t="s">
+      <c r="C13" s="53">
+        <v>3.3099999999999997E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="B14" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="25">
-        <v>3.4500000000000003E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="B13" s="27" t="s">
+      <c r="C14" s="53">
+        <v>4.2299999999999997E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="25">
-        <v>3.3099999999999997E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="B14" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="25">
-        <v>4.2299999999999997E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="B15" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="25">
+      <c r="C15" s="53">
         <v>5.1200000000000002E-2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="B16" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" s="29">
+      <c r="B16" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="56">
         <f>MAX(Portfolio_Mgmt!C31,C10:C15)</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15">
-      <c r="A18" s="18"/>
-      <c r="B18" s="19" t="s">
+    <row r="18" spans="1:5">
+      <c r="A18" s="50"/>
+      <c r="B18" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="18"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="18"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="B19" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="20"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="20"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="B19" s="20" t="s">
+    </row>
+    <row r="20" spans="1:5">
+      <c r="B20" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="30" t="s">
+      <c r="C20" s="57" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="B20" s="22" t="s">
+    <row r="21" spans="1:5">
+      <c r="B21" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C21" s="57" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="B21" s="22" t="s">
+    <row r="22" spans="1:5">
+      <c r="C22" s="57"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="B23" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="C23" s="57" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
-      <c r="C22" s="30"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="B23" s="22" t="s">
+    <row r="24" spans="1:5">
+      <c r="B24" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="30" t="s">
+      <c r="C24" s="57" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="B24" s="22" t="s">
+    <row r="25" spans="1:5">
+      <c r="C25" s="57"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="B26" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="30" t="s">
+      <c r="C26" s="57" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="C25" s="30"/>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="B26" s="22" t="s">
+    <row r="27" spans="1:5">
+      <c r="B27" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="30" t="s">
+      <c r="C27" s="57" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="B27" s="22" t="s">
+    <row r="28" spans="1:5">
+      <c r="C28" s="57"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="B29" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="30" t="s">
+      <c r="C29" s="57" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="C28" s="30"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="B29" s="22" t="s">
+    <row r="31" spans="1:5">
+      <c r="B31" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="30" t="s">
+      <c r="C31" s="57" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="B31" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31" s="30" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -4730,4 +5017,246 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId10"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE447BDC-FAEF-412F-B13E-867203D1820E}">
+  <dimension ref="A1:D41"/>
+  <sheetFormatPr defaultRowHeight="11.65"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.19921875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="34.265625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.796875" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.06640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="B1" s="21" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="5"/>
+      <c r="B2" s="6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="B3" s="47" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="B5" s="48" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="B6" s="48" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="B8" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="5"/>
+      <c r="B10" s="6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="B11" s="47" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="B12" s="47" t="s">
+        <v>155</v>
+      </c>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="B14" s="27" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="12.4">
+      <c r="B16" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="B17" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="B18" s="30" t="s">
+        <v>157</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="B19" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="B20" s="30" t="s">
+        <v>159</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="B21" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="B22" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="B23" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="B24" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="B25" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="5"/>
+      <c r="B27" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="B28" s="47" t="s">
+        <v>167</v>
+      </c>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="B29" s="47" t="s">
+        <v>168</v>
+      </c>
+      <c r="C29" s="47"/>
+      <c r="D29" s="47"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="5"/>
+      <c r="B31" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="B33" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="B35" s="27" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="B36" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="5"/>
+      <c r="B38" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="B39" s="28" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="B40" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="B41" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1C9F5F-7B0A-4617-A0E7-F369DE2CC95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D49508-1C7A-4E63-90B4-809F2625252A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="217">
   <si>
     <t>Name</t>
   </si>
@@ -297,18 +297,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Excess Return over Benchmark (ERB)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Excess Return over Cash (ERC)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>= Investment's Market Annual Return - Cash Yield</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Key Calculation:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -325,18 +313,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Limits:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Single Investment Cap</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>= Investment's Market Annual Return - Benchmark Return</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Benchmark Return</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -421,71 +401,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2. Calculate Attractiveness:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A_i = ERB_i/Benchmark Return</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3. Rank &amp; Select:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Step 3: Monitoring &amp; Rebalancing</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Rebalance if:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Guidance Note: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>This Portfolio Management plan is designed to optimize returns while managing risk by balancing Timing Risk and Concentration vs. Diversification. It ensures capital is deployed effectively during favorable market conditions and maintains diversification to mitigate uncertainties.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Objective: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Deploy capital when investment opportunities exceed the benchmark return, while holding sufficient cash reserves to hedge against market uncertainty.</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -539,59 +459,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Objective: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Balance focused investments to maximize returns with diversified holdings to minimize risk, using defined allocation thresholds.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Maximum Number of Holdings</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Notes:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Target Annual Return</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>: Represents the investor’s hurdle rate, guiding the expected performance of the portfolio over the lock-up period.</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -623,34 +495,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Process: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Assess market cycles using four indicators to calculate a Risk Appetite Score, which determines the portfolio’s cash allocation.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>P_i = (A_i / Sum of A_j for all selected investments) * (100% - Cash %)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Score &lt;= 2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -667,56 +511,28 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Cash Allocation Decision:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Scenario</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Cash Allocation</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">Indicator	</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Low Risk Appetite (Hold Cash)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>High Risk Appetite (Deploy Cash)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Score (0-2)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>- Rank investments by Attractiveness</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>4. Allocate with Caps:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>For each selected investment i:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>- Compute Initial Weights:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>- Enforce Single Investment Cap:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>If any P_i &gt; 10%, cap it at 10% and redistribute the excess proportionally to other investments.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -794,14 +610,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Note on cost of keeping cash</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. Rank Investment Opportunities given Criteria:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">- Only investments with </t>
     </r>
@@ -827,15 +635,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Data: Rank eligible investments by ERB. However, show all the opportunities in the Opportunities sheet regardless of ERB or is_selected flag</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Portfolio Management</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Allocation Percentage</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -950,11 +750,11 @@
   </si>
   <si>
     <t>Code</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Industry</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Layer 2: Subcategory Numbering</t>
@@ -1155,17 +955,415 @@
     <t>Market Yields Tracker</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>iii.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rank Investment Opportunities given Criteria:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Investment vs. Holding Cash Analysis</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Initial Cash Allocation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Cost of Holding Cash (%) = Initial Cash Allocation (%) × Target Annual Return</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>High Growth</t>
+  </si>
+  <si>
+    <t>Cap</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Negative or Low Growth</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Return given Initial Cash Allocation</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cost of Holding Cash if target is met</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>If the portfolio’s projected annual return falls short of the 20% target, increase cash allocation proportionally to the shortfall using the following formula:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Dynamic Cash Adjustment</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="DengXian"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adjusted Cash Allocation (%) = Initial Cash Allocation + Δcash</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maximum allowable cash allocation</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>/</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Minimum allowable cash allocation</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Δcash = MIN(Sensitivity Factor*(Target Annual Return - Projected Portfolio Return)/Target Annual Return, Maximum allowable cash allocation - Initial Cash Allocation)</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Where:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Key Variable:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sensitivity Factor</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Compute Initial Weights: P_i = (A_i / Sum of A_j for all selected investments) * (100% - Adjusted Cash Allocation)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Distribute Weights:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Objective: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Deploy capital when investment opportunities' Market Annual Return (R_i) exceed the benchmark return, while holding sufficient cash reserves to hedge against market uncertainty.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>= R_i - Benchmark Return</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>= R_i - Cash Yield</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Guidance Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>This plan optimizes portfolio returns while managing risk through a dual focus on</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Timing Risk and Concentration Risk &amp; Diversification</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Capital is strategically deployed during favorable market conditions, while diversification and cash reserves mitigate downside risks.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Excess Return over Benchmark (ERB_i)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Excess Return over Cash (ERC_i)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Objective: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Balance focused high-return investments with diversification to reduce risk, guided by allocation caps and growth themes.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Portfolio Limits</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Growth Classification Limits</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Target Annual Return</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: The target return reflects the investor’s hurdle rate over the lock-up period.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Process: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Calculate a Risk Appetite Score (0–8 scale) using four market indicators to set cash reserves.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Purpose:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Automate allocation to eliminate bias and enforce rules.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Calculate Attractiveness Score: A_i = ERB_i/Benchmark Return</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Calculate Projected Return:  SUM(A_i / SUM(A_j for all selected investments) * R_i) * (100% - Initial Cash Allocation)</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Sensitivity Factor:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> higher values increase cash more aggressively.</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Maximum allowable cash allocation: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>prevents over-conservatism.</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Enforce Single Investment Cap: Redistribute excess weight to other investments or cash</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Enforce Growth Classification Cap: Redistribute excess weight to the other class or cash</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Display all opportunities in the Opportunities Sheet, irrespective of ERB or Selected Flag</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Sort eligible investments by ERB (descending)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Key Outputs:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adjusted Cash Allocation</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Allocation Weight</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adjusted Portfolio Return</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="177" formatCode="[$-13C09]d\ mmm\ yyyy;@"/>
     <numFmt numFmtId="178" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="179" formatCode="#,##0.0_);\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1245,12 +1443,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF00B050"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <i/>
       <sz val="9"/>
       <color theme="1"/>
@@ -1305,6 +1497,35 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="DengXian"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -1356,7 +1577,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1406,13 +1627,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1459,45 +1689,104 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="178" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1515,30 +1804,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1865,7 +2132,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
@@ -1890,16 +2157,16 @@
       <c r="E2" s="22"/>
     </row>
     <row r="4" spans="1:5" ht="36.6" customHeight="1">
-      <c r="B4" s="41" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
+      <c r="B4" s="64" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="21" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>69</v>
@@ -1907,23 +2174,23 @@
       <c r="C6" s="20"/>
     </row>
     <row r="7" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B7" s="41" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
+      <c r="B7" s="64" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="24" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="4">
+        <v>76</v>
+      </c>
+      <c r="C10" s="50">
         <f>Market_Yield!C16</f>
         <v>0.1174</v>
       </c>
@@ -1932,7 +2199,7 @@
       <c r="B11" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="50">
         <f>Market_Yield!C6</f>
         <v>3.4500000000000003E-2</v>
       </c>
@@ -1941,410 +2208,592 @@
       <c r="C12" s="4"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="B13" s="27" t="s">
-        <v>74</v>
+      <c r="B13" s="24" t="s">
+        <v>71</v>
       </c>
       <c r="C13" s="4"/>
     </row>
     <row r="14" spans="1:5">
       <c r="B14" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" s="28" t="s">
-        <v>80</v>
+        <v>197</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="B15" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="B17" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="28" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="B17" s="27" t="s">
-        <v>75</v>
-      </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="B18" s="28" t="s">
-        <v>141</v>
+      <c r="B18" s="25" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="B19" s="28" t="s">
-        <v>109</v>
+      <c r="B19" s="25" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="B20" s="28" t="s">
-        <v>110</v>
+      <c r="B20" s="25" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="29" t="s">
-        <v>85</v>
+      <c r="A22" s="26" t="s">
+        <v>80</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C22" s="20"/>
     </row>
     <row r="23" spans="1:5" ht="24.4" customHeight="1">
       <c r="A23" s="18"/>
-      <c r="B23" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
+      <c r="B23" s="64" t="s">
+        <v>199</v>
+      </c>
+      <c r="C23" s="64"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="64"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
-      <c r="B25" s="27" t="s">
-        <v>78</v>
+      <c r="B25" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="C25" s="58" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="B26" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C26" s="24">
+      <c r="B26" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="54">
         <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="B27" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C27" s="39">
+      <c r="B27" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="55">
         <v>0.3</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="C29" s="58" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="B30" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="C30" s="56">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="B31" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="C31" s="57">
+        <f>1-C30</f>
+        <v>0.19999999999999996</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="20"/>
-      <c r="D29" s="23"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="B30" s="1" t="s">
+      <c r="C33" s="20"/>
+      <c r="D33" s="23"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="B34" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="40">
+      <c r="C34" s="51">
         <v>0.2</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="D34" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="E30" s="26">
+      <c r="E34" s="53">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="B31" s="1" t="s">
+    <row r="35" spans="1:5">
+      <c r="B35" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="25">
+      <c r="C35" s="52">
         <f>MAX(8%,Market_Yield!C4:D6)</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
-      <c r="B33" s="21" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B34" s="41" t="s">
-        <v>114</v>
-      </c>
-      <c r="C34" s="41"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-    </row>
-    <row r="35" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B35" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="41"/>
-    </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="B37" s="22"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
+      <c r="B37" s="21" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="B38" s="64" t="s">
+        <v>202</v>
+      </c>
+      <c r="C38" s="64"/>
+      <c r="D38" s="64"/>
+      <c r="E38" s="64"/>
     </row>
     <row r="39" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B39" s="41" t="s">
-        <v>117</v>
-      </c>
-      <c r="C39" s="41"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="41"/>
+      <c r="B39" s="64" t="s">
+        <v>103</v>
+      </c>
+      <c r="C39" s="64"/>
+      <c r="D39" s="64"/>
+      <c r="E39" s="64"/>
     </row>
     <row r="41" spans="1:5">
-      <c r="B41" s="27" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="12.4">
-      <c r="B43" s="38" t="s">
-        <v>124</v>
-      </c>
-      <c r="C43" s="38" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="B44" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="C44" s="36">
-        <v>0.5</v>
-      </c>
+      <c r="A41" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="B43" s="64" t="s">
+        <v>203</v>
+      </c>
+      <c r="C43" s="64"/>
+      <c r="D43" s="64"/>
+      <c r="E43" s="64"/>
     </row>
     <row r="45" spans="1:5">
-      <c r="B45" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="C45" s="36">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="B46" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="C46" s="36">
-        <v>0.2</v>
-      </c>
+      <c r="B45" s="24" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="B47" s="58" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" s="58" t="s">
+        <v>110</v>
+      </c>
+      <c r="D47" s="61" t="s">
+        <v>182</v>
+      </c>
+      <c r="E47" s="61"/>
     </row>
     <row r="48" spans="1:5">
       <c r="B48" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C48" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="D48" s="65" t="s">
+        <v>183</v>
+      </c>
+      <c r="E48" s="65"/>
+    </row>
+    <row r="49" spans="2:5">
+      <c r="B49" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="C49" s="32">
+        <v>0.3</v>
+      </c>
+      <c r="D49" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="E49" s="65"/>
+    </row>
+    <row r="50" spans="2:5">
+      <c r="B50" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="C50" s="32">
+        <v>0.2</v>
+      </c>
+      <c r="D50" s="65" t="s">
+        <v>185</v>
+      </c>
+      <c r="E50" s="65"/>
+    </row>
+    <row r="52" spans="2:5">
+      <c r="B52" s="24" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5">
+      <c r="B54" s="58" t="s">
+        <v>111</v>
+      </c>
+      <c r="C54" s="58" t="s">
+        <v>112</v>
+      </c>
+      <c r="D54" s="58" t="s">
+        <v>113</v>
+      </c>
+      <c r="E54" s="58" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5">
+      <c r="B55" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C55" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="D55" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="E55" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5">
+      <c r="B56" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="C56" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="D56" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="E56" s="44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5">
+      <c r="B57" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C57" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D57" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="E57" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5">
+      <c r="B58" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C58" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="D58" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="E58" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5">
+      <c r="D59" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="E59" s="43">
+        <f>SUM(E55:E58)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" ht="12" thickBot="1">
+      <c r="D60" s="45" t="s">
+        <v>172</v>
+      </c>
+      <c r="E60" s="46">
+        <f>IF(E59&lt;=2,C48,IF(E59&gt;=6,C50,C49))</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" ht="12" thickTop="1"/>
+    <row r="62" spans="2:5">
+      <c r="B62" s="24" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5">
+      <c r="B63" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="C63" s="49">
+        <f>-E60*C34</f>
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5">
+      <c r="B64" s="48" t="s">
+        <v>177</v>
+      </c>
+      <c r="C64" s="49">
+        <f>C34+C63</f>
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="B65" s="48"/>
+      <c r="C65" s="49"/>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="B66" s="42" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="B68" s="22"/>
+      <c r="C68" s="22"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="B70" s="64" t="s">
+        <v>204</v>
+      </c>
+      <c r="C70" s="64"/>
+      <c r="D70" s="64"/>
+      <c r="E70" s="64"/>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="21" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="B73" s="25" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="B74" s="25" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="B75" s="25" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="B76" s="25" t="str">
+        <f>"- Choose top "&amp;C26&amp;" (or fewer) investments: respecting the maximum holdings limit and selected Flag"</f>
+        <v>- Choose top 10 (or fewer) investments: respecting the maximum holdings limit and selected Flag</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="B77" s="25" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="B79" s="29" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B80" s="64" t="s">
+        <v>179</v>
+      </c>
+      <c r="C80" s="64"/>
+      <c r="D80" s="64"/>
+      <c r="E80" s="64"/>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="B81" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="B83" s="24" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B84" s="62" t="s">
+        <v>186</v>
+      </c>
+      <c r="C84" s="62"/>
+      <c r="D84" s="62"/>
+      <c r="E84" s="62"/>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="B86" s="24" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="B87" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C87" s="60">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="B88" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C88" s="59">
+        <f>C48</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="B90" s="42" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="B91" s="30" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="B92" s="30" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="B94" s="21" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="B95" s="66" t="s">
+        <v>191</v>
+      </c>
+      <c r="C95" s="66"/>
+      <c r="D95" s="66"/>
+      <c r="E95" s="66"/>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="B96" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="C96" s="63"/>
+      <c r="D96" s="63"/>
+      <c r="E96" s="63"/>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="B97" s="63" t="s">
+        <v>210</v>
+      </c>
+      <c r="C97" s="63"/>
+      <c r="D97" s="63"/>
+      <c r="E97" s="63"/>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="B99" s="24" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="B100" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C100" s="47">
+        <v>0.65940393311917622</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="B101" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C101" s="47">
+        <v>8.5819512867283593E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="B103" s="22"/>
+      <c r="C103" s="22"/>
+      <c r="D103" s="22"/>
+      <c r="E103" s="22"/>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="B105" s="21" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="B106" s="25" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="B107" s="25" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="B108" s="25" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="12.4">
-      <c r="B50" s="38" t="s">
-        <v>126</v>
-      </c>
-      <c r="C50" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="D50" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="E50" s="38" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="B51" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C51" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="D51" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="E51" s="31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="B52" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="C52" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="D52" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="E52" s="31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="B53" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="C53" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="D53" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="E53" s="31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="B54" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C54" s="30" t="s">
-        <v>94</v>
-      </c>
-      <c r="D54" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="E54" s="31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="D55" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="E55" s="35">
-        <f>SUM(E51:E54)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="B57" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="C57" s="37">
-        <f>IF(E55&lt;=2,C44,IF(E55&gt;=6,C46,C45))</f>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="B59" s="34" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="B61" s="22"/>
-      <c r="C61" s="22"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="B63" s="21" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="B64" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2">
-      <c r="B66" s="33" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2">
-      <c r="B67" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2">
-      <c r="B69" s="21" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="70" spans="2:2">
-      <c r="B70" s="28" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="71" spans="2:2">
-      <c r="B71" s="1" t="str">
-        <f>"- Select the top "&amp;C26&amp;" or fewer investments, respecting the maximum holdings limit."</f>
-        <v>- Select the top 10 or fewer investments, respecting the maximum holdings limit.</v>
-      </c>
-    </row>
-    <row r="73" spans="2:2">
-      <c r="B73" s="21" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="74" spans="2:2">
-      <c r="B74" s="28" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="75" spans="2:2">
-      <c r="B75" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="76" spans="2:2">
-      <c r="B76" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="78" spans="2:2">
-      <c r="B78" s="28" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="79" spans="2:2">
-      <c r="B79" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="B81" s="22"/>
-      <c r="C81" s="22"/>
-      <c r="D81" s="22"/>
-      <c r="E81" s="22"/>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="B83" s="21" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="B84" s="28" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="B85" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="B86" s="28" t="s">
-        <v>137</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B39:E39"/>
+  <mergeCells count="16">
+    <mergeCell ref="B43:E43"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B80:E80"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B95:E95"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="93" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2378,30 +2827,30 @@
       <c r="B1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="45" t="s">
+      <c r="D1" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="42" t="s">
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="71" t="s">
+        <v>119</v>
+      </c>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="42"/>
-      <c r="L1" s="43" t="s">
+      <c r="K1" s="67"/>
+      <c r="L1" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="43"/>
-      <c r="N1" s="44" t="s">
+      <c r="M1" s="68"/>
+      <c r="N1" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
+      <c r="O1" s="69"/>
+      <c r="P1" s="69"/>
+      <c r="Q1" s="69"/>
     </row>
     <row r="2" spans="1:17" ht="26" customHeight="1">
       <c r="B2" s="7" t="s">
@@ -2420,13 +2869,13 @@
         <v>11</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>144</v>
+        <v>215</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>8</v>
@@ -2470,15 +2919,15 @@
         <v>0.12411921460409614</v>
       </c>
       <c r="G3" s="15">
-        <f>F3 - Portfolio_Mgmt!$C$10</f>
-        <v>6.7192146040961354E-3</v>
+        <f t="shared" ref="G3:G5" si="0">F3 - C10</f>
+        <v>0.12411921460409614</v>
       </c>
       <c r="H3" s="15">
-        <f>F3 - Portfolio_Mgmt!$C$11</f>
-        <v>8.9619214604096137E-2</v>
+        <f t="shared" ref="H3:H5" si="1">F3 - C11</f>
+        <v>0.12411921460409614</v>
       </c>
       <c r="I3" s="15">
-        <v>0.39999999999999997</v>
+        <v>4.0596066880823796E-2</v>
       </c>
       <c r="J3" s="2">
         <v>6.4883606756817951</v>
@@ -2493,7 +2942,7 @@
         <v>7.4454428754813853E-2</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="O3" s="11" t="s">
         <v>17</v>
@@ -2502,7 +2951,7 @@
         <v>45716</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -2522,12 +2971,12 @@
         <v>0.19343775079136272</v>
       </c>
       <c r="G4" s="15">
-        <f>F4 - Portfolio_Mgmt!$C$10</f>
-        <v>7.6037750791362713E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.19343775079136272</v>
       </c>
       <c r="H4" s="15">
-        <f>F4 - Portfolio_Mgmt!$C$11</f>
-        <v>0.15893775079136271</v>
+        <f t="shared" si="1"/>
+        <v>0.19343775079136272</v>
       </c>
       <c r="I4" s="15">
         <v>0.3</v>
@@ -2545,7 +2994,7 @@
         <v>9.0909090909090912E-2</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="O4" s="11" t="s">
         <v>23</v>
@@ -2554,7 +3003,7 @@
         <v>45716</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -2574,12 +3023,12 @@
         <v>6.3214262000776955E-2</v>
       </c>
       <c r="G5" s="15">
-        <f>F5 - Portfolio_Mgmt!$C$10</f>
-        <v>-5.4185737999223049E-2</v>
+        <f t="shared" si="0"/>
+        <v>6.3214262000776955E-2</v>
       </c>
       <c r="H5" s="15">
-        <f>F5 - Portfolio_Mgmt!$C$11</f>
-        <v>2.8714262000776952E-2</v>
+        <f t="shared" si="1"/>
+        <v>6.3214262000776955E-2</v>
       </c>
       <c r="I5" s="15">
         <v>0</v>
@@ -2597,7 +3046,7 @@
         <v>5.4036697247706419E-2</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="O5" s="11" t="s">
         <v>20</v>
@@ -2606,7 +3055,7 @@
         <v>45716</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -4766,12 +5215,12 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="21" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51" t="s">
+      <c r="A2" s="34"/>
+      <c r="B2" s="35" t="s">
         <v>28</v>
       </c>
       <c r="C2" s="18"/>
@@ -4779,64 +5228,64 @@
       <c r="E2" s="18"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="53">
+      <c r="C4" s="37">
         <v>4.2500000000000003E-2</v>
       </c>
-      <c r="D4" s="53">
+      <c r="D4" s="37">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E4" s="54">
+      <c r="E4" s="38">
         <f>D4-C4</f>
         <v>3.2499999999999994E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="53">
+      <c r="C5" s="37">
         <v>1.9E-2</v>
       </c>
-      <c r="D5" s="53">
+      <c r="D5" s="37">
         <v>3.1E-2</v>
       </c>
-      <c r="E5" s="54">
+      <c r="E5" s="38">
         <f>D5-C5</f>
         <v>1.2E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="53">
+      <c r="C6" s="37">
         <v>3.4500000000000003E-2</v>
       </c>
-      <c r="D6" s="53">
+      <c r="D6" s="37">
         <v>5.2499999999999998E-2</v>
       </c>
-      <c r="E6" s="54">
+      <c r="E6" s="38">
         <f>D6-C6</f>
         <v>1.7999999999999995E-2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="50"/>
-      <c r="B8" s="51" t="s">
+      <c r="A8" s="34"/>
+      <c r="B8" s="35" t="s">
         <v>35</v>
       </c>
       <c r="C8" s="1">
@@ -4850,70 +5299,70 @@
       <c r="B9" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="31" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="53">
+      <c r="C10" s="37">
         <v>9.9400000000000002E-2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="53">
+      <c r="C11" s="37">
         <v>0.1174</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="53">
+      <c r="C12" s="37">
         <v>3.4500000000000003E-2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="53">
+      <c r="C13" s="37">
         <v>3.3099999999999997E-2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="53">
+      <c r="C14" s="37">
         <v>4.2299999999999997E-2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="53">
+      <c r="C15" s="37">
         <v>5.1200000000000002E-2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="B16" s="55" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" s="56">
-        <f>MAX(Portfolio_Mgmt!C31,C10:C15)</f>
+      <c r="B16" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="40">
+        <f>MAX(Portfolio_Mgmt!C35,C10:C15)</f>
         <v>0.1174</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="50"/>
-      <c r="B18" s="51" t="s">
+      <c r="A18" s="34"/>
+      <c r="B18" s="35" t="s">
         <v>43</v>
       </c>
       <c r="C18" s="18"/>
@@ -4924,7 +5373,7 @@
       <c r="B19" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="57" t="s">
+      <c r="C19" s="41" t="s">
         <v>45</v>
       </c>
     </row>
@@ -4932,7 +5381,7 @@
       <c r="B20" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="57" t="s">
+      <c r="C20" s="41" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4940,18 +5389,18 @@
       <c r="B21" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="57" t="s">
+      <c r="C21" s="41" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="C22" s="57"/>
+      <c r="C22" s="41"/>
     </row>
     <row r="23" spans="1:5">
       <c r="B23" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="57" t="s">
+      <c r="C23" s="41" t="s">
         <v>51</v>
       </c>
     </row>
@@ -4959,18 +5408,18 @@
       <c r="B24" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="57" t="s">
+      <c r="C24" s="41" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="C25" s="57"/>
+      <c r="C25" s="41"/>
     </row>
     <row r="26" spans="1:5">
       <c r="B26" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="57" t="s">
+      <c r="C26" s="41" t="s">
         <v>55</v>
       </c>
     </row>
@@ -4978,18 +5427,18 @@
       <c r="B27" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="57" t="s">
+      <c r="C27" s="41" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="C28" s="57"/>
+      <c r="C28" s="41"/>
     </row>
     <row r="29" spans="1:5">
       <c r="B29" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="57" t="s">
+      <c r="C29" s="41" t="s">
         <v>59</v>
       </c>
     </row>
@@ -4997,7 +5446,7 @@
       <c r="B31" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="57" t="s">
+      <c r="C31" s="41" t="s">
         <v>61</v>
       </c>
     </row>
@@ -5033,217 +5482,217 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="21" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="B3" s="47" t="s">
-        <v>149</v>
-      </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
+      <c r="B3" s="62" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="B5" s="48" t="s">
-        <v>151</v>
-      </c>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
+      <c r="B5" s="66" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="B6" s="48" t="s">
-        <v>152</v>
-      </c>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
+      <c r="B6" s="66" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="72"/>
+      <c r="D6" s="72"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5"/>
       <c r="B10" s="6" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="62" t="s">
+        <v>129</v>
+      </c>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="B12" s="62" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="62"/>
+      <c r="D12" s="62"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="B14" s="24" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="12.4">
+      <c r="B16" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="B17" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="B18" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="B19" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="B20" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="B21" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="B12" s="47" t="s">
+      <c r="C21" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="C12" s="47"/>
-      <c r="D12" s="47"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="B14" s="27" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="12.4">
-      <c r="B16" s="38" t="s">
+    </row>
+    <row r="22" spans="1:4">
+      <c r="B22" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="B23" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="B24" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="C24" s="27" t="s">
         <v>164</v>
       </c>
-      <c r="C16" s="38" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="B17" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="C17" s="30" t="s">
+    </row>
+    <row r="25" spans="1:4">
+      <c r="B25" s="27" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="B18" s="30" t="s">
-        <v>157</v>
-      </c>
-      <c r="C18" s="30" t="s">
+      <c r="C25" s="27" t="s">
         <v>161</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="B19" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="B20" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="C20" s="30" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="B21" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="C21" s="30" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="B22" s="30" t="s">
-        <v>181</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="B23" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="C23" s="30" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="B24" s="30" t="s">
-        <v>188</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="B25" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="C25" s="30" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="5"/>
       <c r="B27" s="6" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="B28" s="47" t="s">
-        <v>167</v>
-      </c>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
+      <c r="B28" s="62" t="s">
+        <v>142</v>
+      </c>
+      <c r="C28" s="62"/>
+      <c r="D28" s="62"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="B29" s="47" t="s">
-        <v>168</v>
-      </c>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
+      <c r="B29" s="62" t="s">
+        <v>143</v>
+      </c>
+      <c r="C29" s="62"/>
+      <c r="D29" s="62"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="5"/>
       <c r="B31" s="6" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="B32" s="27" t="s">
-        <v>170</v>
+      <c r="A32" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="B33" s="1" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="B35" s="27" t="s">
-        <v>172</v>
+      <c r="A35" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="B35" s="24" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="B36" s="1" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="5"/>
       <c r="B38" s="6" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="B39" s="28" t="s">
-        <v>176</v>
+      <c r="B39" s="25" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="B40" s="1" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="B41" s="1" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D49508-1C7A-4E63-90B4-809F2625252A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E4F7A2A-C7C5-4485-AB96-8BC620767C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="218">
   <si>
     <t>Name</t>
   </si>
@@ -1041,10 +1041,6 @@
   </si>
   <si>
     <t>/</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Minimum allowable cash allocation</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
@@ -1226,30 +1222,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Process: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Calculate a Risk Appetite Score (0–8 scale) using four market indicators to set cash reserves.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>Purpose:</t>
     </r>
     <r>
@@ -1351,6 +1323,38 @@
   <si>
     <t>Adjusted Portfolio Return</t>
     <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max Cash</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Min Cash</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Process: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Calculate a Risk Appetite Score (0–8 scale) using four market indicators to set cash reserves. Automatically adjust the sensitivity factor based on the Risk Appetite Score category. High</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1757,8 +1761,6 @@
     <xf numFmtId="178" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="21" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1769,10 +1771,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1781,9 +1788,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2157,12 +2161,12 @@
       <c r="E2" s="22"/>
     </row>
     <row r="4" spans="1:5" ht="36.6" customHeight="1">
-      <c r="B4" s="64" t="s">
-        <v>196</v>
-      </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
+      <c r="B4" s="65" t="s">
+        <v>195</v>
+      </c>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="21" t="s">
@@ -2174,12 +2178,12 @@
       <c r="C6" s="20"/>
     </row>
     <row r="7" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B7" s="64" t="s">
-        <v>193</v>
-      </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
+      <c r="B7" s="65" t="s">
+        <v>192</v>
+      </c>
+      <c r="C7" s="65"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="24" t="s">
@@ -2215,18 +2219,18 @@
     </row>
     <row r="14" spans="1:5">
       <c r="B14" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="B15" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2260,22 +2264,22 @@
     </row>
     <row r="23" spans="1:5" ht="24.4" customHeight="1">
       <c r="A23" s="18"/>
-      <c r="B23" s="64" t="s">
-        <v>199</v>
-      </c>
-      <c r="C23" s="64"/>
-      <c r="D23" s="64"/>
-      <c r="E23" s="64"/>
+      <c r="B23" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
-      <c r="B25" s="58" t="s">
-        <v>200</v>
-      </c>
-      <c r="C25" s="58" t="s">
+      <c r="B25" s="56" t="s">
+        <v>199</v>
+      </c>
+      <c r="C25" s="56" t="s">
         <v>175</v>
       </c>
     </row>
@@ -2283,7 +2287,7 @@
       <c r="B26" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="C26" s="54">
+      <c r="C26" s="61">
         <v>10</v>
       </c>
     </row>
@@ -2291,15 +2295,15 @@
       <c r="B27" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="55">
+      <c r="C27" s="62">
         <v>0.3</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="B29" s="58" t="s">
-        <v>201</v>
-      </c>
-      <c r="C29" s="58" t="s">
+      <c r="B29" s="56" t="s">
+        <v>200</v>
+      </c>
+      <c r="C29" s="56" t="s">
         <v>175</v>
       </c>
     </row>
@@ -2307,7 +2311,7 @@
       <c r="B30" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="C30" s="56">
+      <c r="C30" s="54">
         <v>0.8</v>
       </c>
     </row>
@@ -2315,7 +2319,7 @@
       <c r="B31" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="C31" s="57">
+      <c r="C31" s="55">
         <f>1-C30</f>
         <v>0.19999999999999996</v>
       </c>
@@ -2359,20 +2363,20 @@
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="B38" s="64" t="s">
-        <v>202</v>
-      </c>
-      <c r="C38" s="64"/>
-      <c r="D38" s="64"/>
-      <c r="E38" s="64"/>
+      <c r="B38" s="65" t="s">
+        <v>201</v>
+      </c>
+      <c r="C38" s="65"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
     </row>
     <row r="39" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B39" s="64" t="s">
+      <c r="B39" s="65" t="s">
         <v>103</v>
       </c>
-      <c r="C39" s="64"/>
-      <c r="D39" s="64"/>
-      <c r="E39" s="64"/>
+      <c r="C39" s="65"/>
+      <c r="D39" s="65"/>
+      <c r="E39" s="65"/>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="22" t="s">
@@ -2383,13 +2387,13 @@
       <c r="D41" s="22"/>
       <c r="E41" s="22"/>
     </row>
-    <row r="43" spans="1:5">
-      <c r="B43" s="64" t="s">
-        <v>203</v>
-      </c>
-      <c r="C43" s="64"/>
-      <c r="D43" s="64"/>
-      <c r="E43" s="64"/>
+    <row r="43" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B43" s="65" t="s">
+        <v>217</v>
+      </c>
+      <c r="C43" s="65"/>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
     </row>
     <row r="45" spans="1:5">
       <c r="B45" s="24" t="s">
@@ -2397,16 +2401,18 @@
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="B47" s="58" t="s">
+      <c r="B47" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="C47" s="58" t="s">
+      <c r="C47" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="D47" s="61" t="s">
+      <c r="D47" s="58" t="s">
+        <v>188</v>
+      </c>
+      <c r="E47" s="58" t="s">
         <v>182</v>
       </c>
-      <c r="E47" s="61"/>
     </row>
     <row r="48" spans="1:5">
       <c r="B48" s="27" t="s">
@@ -2415,10 +2421,12 @@
       <c r="C48" s="32">
         <v>0.5</v>
       </c>
-      <c r="D48" s="65" t="s">
-        <v>183</v>
-      </c>
-      <c r="E48" s="65"/>
+      <c r="D48" s="59">
+        <v>1</v>
+      </c>
+      <c r="E48" s="36" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="49" spans="2:5">
       <c r="B49" s="27" t="s">
@@ -2427,10 +2435,12 @@
       <c r="C49" s="32">
         <v>0.3</v>
       </c>
-      <c r="D49" s="65" t="s">
+      <c r="D49" s="59">
+        <v>1.5</v>
+      </c>
+      <c r="E49" s="36" t="s">
         <v>184</v>
       </c>
-      <c r="E49" s="65"/>
     </row>
     <row r="50" spans="2:5">
       <c r="B50" s="27" t="s">
@@ -2439,10 +2449,12 @@
       <c r="C50" s="32">
         <v>0.2</v>
       </c>
-      <c r="D50" s="65" t="s">
-        <v>185</v>
-      </c>
-      <c r="E50" s="65"/>
+      <c r="D50" s="59">
+        <v>2</v>
+      </c>
+      <c r="E50" s="36" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="52" spans="2:5">
       <c r="B52" s="24" t="s">
@@ -2450,16 +2462,16 @@
       </c>
     </row>
     <row r="54" spans="2:5">
-      <c r="B54" s="58" t="s">
+      <c r="B54" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="C54" s="58" t="s">
+      <c r="C54" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="D54" s="58" t="s">
+      <c r="D54" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="E54" s="58" t="s">
+      <c r="E54" s="56" t="s">
         <v>114</v>
       </c>
     </row>
@@ -2580,12 +2592,12 @@
       <c r="E68" s="22"/>
     </row>
     <row r="70" spans="1:5">
-      <c r="B70" s="64" t="s">
-        <v>204</v>
-      </c>
-      <c r="C70" s="64"/>
-      <c r="D70" s="64"/>
-      <c r="E70" s="64"/>
+      <c r="B70" s="65" t="s">
+        <v>202</v>
+      </c>
+      <c r="C70" s="65"/>
+      <c r="D70" s="65"/>
+      <c r="E70" s="65"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="31" t="s">
@@ -2597,17 +2609,17 @@
     </row>
     <row r="73" spans="1:5">
       <c r="B73" s="25" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="B74" s="25" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="B75" s="25" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2618,7 +2630,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="B77" s="25" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2630,12 +2642,12 @@
       </c>
     </row>
     <row r="80" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B80" s="64" t="s">
+      <c r="B80" s="65" t="s">
         <v>179</v>
       </c>
-      <c r="C80" s="64"/>
-      <c r="D80" s="64"/>
-      <c r="E80" s="64"/>
+      <c r="C80" s="65"/>
+      <c r="D80" s="65"/>
+      <c r="E80" s="65"/>
     </row>
     <row r="81" spans="1:5">
       <c r="B81" s="1" t="s">
@@ -2644,27 +2656,28 @@
     </row>
     <row r="83" spans="1:5">
       <c r="B83" s="24" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B84" s="62" t="s">
-        <v>186</v>
-      </c>
-      <c r="C84" s="62"/>
-      <c r="D84" s="62"/>
-      <c r="E84" s="62"/>
+      <c r="B84" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="C84" s="63"/>
+      <c r="D84" s="63"/>
+      <c r="E84" s="63"/>
     </row>
     <row r="86" spans="1:5">
       <c r="B86" s="24" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="B87" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C87" s="60">
+        <f>IF(E59&lt;=2,D48,IF(E59&gt;=6,D50,D49))</f>
         <v>1.5</v>
       </c>
     </row>
@@ -2672,24 +2685,24 @@
       <c r="B88" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C88" s="59">
+      <c r="C88" s="57">
         <f>C48</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="42" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="B91" s="30" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="B92" s="30" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2697,52 +2710,52 @@
         <v>169</v>
       </c>
       <c r="B94" s="21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="B95" s="66" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C95" s="66"/>
       <c r="D95" s="66"/>
       <c r="E95" s="66"/>
     </row>
     <row r="96" spans="1:5">
-      <c r="B96" s="63" t="s">
-        <v>209</v>
-      </c>
-      <c r="C96" s="63"/>
-      <c r="D96" s="63"/>
-      <c r="E96" s="63"/>
+      <c r="B96" s="64" t="s">
+        <v>207</v>
+      </c>
+      <c r="C96" s="64"/>
+      <c r="D96" s="64"/>
+      <c r="E96" s="64"/>
     </row>
     <row r="97" spans="1:5">
-      <c r="B97" s="63" t="s">
-        <v>210</v>
-      </c>
-      <c r="C97" s="63"/>
-      <c r="D97" s="63"/>
-      <c r="E97" s="63"/>
+      <c r="B97" s="64" t="s">
+        <v>208</v>
+      </c>
+      <c r="C97" s="64"/>
+      <c r="D97" s="64"/>
+      <c r="E97" s="64"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="B100" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C100" s="47">
-        <v>0.65940393311917622</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="B101" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C101" s="47">
-        <v>8.5819512867283593E-2</v>
+        <v>8.0320077174672017E-2</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2775,20 +2788,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="12">
     <mergeCell ref="B43:E43"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B38:E38"/>
     <mergeCell ref="B39:E39"/>
-    <mergeCell ref="D47:E47"/>
     <mergeCell ref="B84:E84"/>
     <mergeCell ref="B97:E97"/>
     <mergeCell ref="B80:E80"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D50:E50"/>
     <mergeCell ref="B70:E70"/>
     <mergeCell ref="B96:E96"/>
     <mergeCell ref="B95:E95"/>
@@ -2875,7 +2884,7 @@
         <v>74</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>8</v>
@@ -2904,48 +2913,48 @@
     </row>
     <row r="3" spans="1:17">
       <c r="B3" s="11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D3" s="2">
-        <v>7.79</v>
+        <v>14.96</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="15">
-        <v>0.12411921460409614</v>
+        <v>0.19343775079136272</v>
       </c>
       <c r="G3" s="15">
-        <f t="shared" ref="G3:G5" si="0">F3 - C10</f>
-        <v>0.12411921460409614</v>
+        <f t="shared" ref="G3:G5" si="0">F3 - $C$10</f>
+        <v>0.19343775079136272</v>
       </c>
       <c r="H3" s="15">
-        <f t="shared" ref="H3:H5" si="1">F3 - C11</f>
-        <v>0.12411921460409614</v>
+        <f t="shared" ref="H3:H5" si="1">F3 - $C$11</f>
+        <v>0.19343775079136272</v>
       </c>
       <c r="I3" s="15">
-        <v>4.0596066880823796E-2</v>
+        <v>0.3</v>
       </c>
       <c r="J3" s="2">
-        <v>6.4883606756817951</v>
+        <v>14.733437767356989</v>
       </c>
       <c r="K3" s="2">
-        <v>9.1006872475781417</v>
+        <v>20.508980461992877</v>
       </c>
       <c r="L3" s="4">
-        <v>3.9653192809019897E-2</v>
+        <v>0.11550708685625866</v>
       </c>
       <c r="M3" s="4">
-        <v>7.4454428754813853E-2</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="P3" s="14">
         <v>45716</v>
@@ -2956,48 +2965,48 @@
     </row>
     <row r="4" spans="1:17">
       <c r="B4" s="11" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2">
-        <v>14.96</v>
+        <v>7.79</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="15">
-        <v>0.19343775079136272</v>
+        <v>0.12411921460409614</v>
       </c>
       <c r="G4" s="15">
         <f t="shared" si="0"/>
-        <v>0.19343775079136272</v>
+        <v>0.12411921460409614</v>
       </c>
       <c r="H4" s="15">
         <f t="shared" si="1"/>
-        <v>0.19343775079136272</v>
+        <v>0.12411921460409614</v>
       </c>
       <c r="I4" s="15">
-        <v>0.3</v>
+        <v>4.0596066880823796E-2</v>
       </c>
       <c r="J4" s="2">
-        <v>14.733437767356989</v>
+        <v>6.4883606756817951</v>
       </c>
       <c r="K4" s="2">
-        <v>20.508980461992877</v>
+        <v>9.1006872475781417</v>
       </c>
       <c r="L4" s="4">
-        <v>0.11550708685625866</v>
+        <v>3.9653192809019897E-2</v>
       </c>
       <c r="M4" s="4">
-        <v>9.0909090909090912E-2</v>
+        <v>7.4454428754813853E-2</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="P4" s="14">
         <v>45716</v>
@@ -5492,11 +5501,11 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="63" t="s">
         <v>124</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
     </row>
     <row r="5" spans="1:4">
       <c r="B5" s="66" t="s">
@@ -5524,18 +5533,18 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="62" t="s">
+      <c r="B11" s="63" t="s">
         <v>129</v>
       </c>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="63"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="B12" s="62" t="s">
+      <c r="B12" s="63" t="s">
         <v>130</v>
       </c>
-      <c r="C12" s="62"/>
-      <c r="D12" s="62"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="63"/>
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="24" t="s">
@@ -5629,18 +5638,18 @@
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="B28" s="62" t="s">
+      <c r="B28" s="63" t="s">
         <v>142</v>
       </c>
-      <c r="C28" s="62"/>
-      <c r="D28" s="62"/>
+      <c r="C28" s="63"/>
+      <c r="D28" s="63"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="B29" s="62" t="s">
+      <c r="B29" s="63" t="s">
         <v>143</v>
       </c>
-      <c r="C29" s="62"/>
-      <c r="D29" s="62"/>
+      <c r="C29" s="63"/>
+      <c r="D29" s="63"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="5"/>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E4F7A2A-C7C5-4485-AB96-8BC620767C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805522B0-4733-4881-895B-788297E357CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -79,36 +79,6 @@
     <t>FCFE
  Yield</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>0083.HK</t>
-  </si>
-  <si>
-    <t>SINO LAND</t>
-  </si>
-  <si>
-    <t>HKD</t>
-  </si>
-  <si>
-    <t>Negative Growth Asset Play</t>
-  </si>
-  <si>
-    <t>0590.HK</t>
-  </si>
-  <si>
-    <t>六福珠宝</t>
-  </si>
-  <si>
-    <t>Low Growth Asset Play</t>
-  </si>
-  <si>
-    <t>6601.HK</t>
-  </si>
-  <si>
-    <t>朝云集团</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low Growth </t>
   </si>
   <si>
     <t>Growth Classification</t>
@@ -639,12 +609,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>Guidance Note: Comparison Group Classification System</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -941,15 +905,6 @@
   <si>
     <t>Real Estate</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>RES_01</t>
-  </si>
-  <si>
-    <t>CNS_05</t>
-  </si>
-  <si>
-    <t>CNS_04</t>
   </si>
   <si>
     <t>Market Yields Tracker</t>
@@ -1355,6 +1310,51 @@
       <t>Calculate a Risk Appetite Score (0–8 scale) using four market indicators to set cash reserves. Automatically adjust the sensitivity factor based on the Risk Appetite Score category. High</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0590.HK</t>
+  </si>
+  <si>
+    <t>六福珠宝</t>
+  </si>
+  <si>
+    <t>HKD</t>
+  </si>
+  <si>
+    <t>CNS_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low Growth </t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>0083.HK</t>
+  </si>
+  <si>
+    <t>SINO LAND</t>
+  </si>
+  <si>
+    <t>RES_01</t>
+  </si>
+  <si>
+    <t>Negative Growth Asset Play</t>
+  </si>
+  <si>
+    <t>6601.HK</t>
+  </si>
+  <si>
+    <t>朝云集团</t>
+  </si>
+  <si>
+    <t>CNS_04</t>
+  </si>
+  <si>
+    <t>Low Growth Asset Play</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
 </sst>
 </file>
@@ -1646,7 +1646,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1783,6 +1783,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1809,6 +1812,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2148,12 +2154,12 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="21" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="22" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -2161,38 +2167,38 @@
       <c r="E2" s="22"/>
     </row>
     <row r="4" spans="1:5" ht="36.6" customHeight="1">
-      <c r="B4" s="65" t="s">
-        <v>195</v>
-      </c>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
+      <c r="B4" s="66" t="s">
+        <v>180</v>
+      </c>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="21" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C6" s="20"/>
     </row>
     <row r="7" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B7" s="65" t="s">
-        <v>192</v>
-      </c>
-      <c r="C7" s="65"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
+      <c r="B7" s="66" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="24" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" s="1" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C10" s="50">
         <f>Market_Yield!C16</f>
@@ -2201,7 +2207,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="B11" s="1" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C11" s="50">
         <f>Market_Yield!C6</f>
@@ -2213,63 +2219,63 @@
     </row>
     <row r="13" spans="1:5">
       <c r="B13" s="24" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C13" s="4"/>
     </row>
     <row r="14" spans="1:5">
       <c r="B14" s="1" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="B15" s="1" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="B17" s="24" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="B18" s="25" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="B19" s="25" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="B20" s="25" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="26" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C22" s="20"/>
     </row>
     <row r="23" spans="1:5" ht="24.4" customHeight="1">
       <c r="A23" s="18"/>
-      <c r="B23" s="65" t="s">
-        <v>198</v>
-      </c>
-      <c r="C23" s="65"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="65"/>
+      <c r="B23" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="C23" s="66"/>
+      <c r="D23" s="66"/>
+      <c r="E23" s="66"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
@@ -2277,15 +2283,15 @@
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
       <c r="B25" s="56" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="C25" s="56" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="B26" s="27" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C26" s="61">
         <v>10</v>
@@ -2293,7 +2299,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="B27" s="27" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C27" s="62">
         <v>0.3</v>
@@ -2301,15 +2307,15 @@
     </row>
     <row r="29" spans="1:5">
       <c r="B29" s="56" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="C29" s="56" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="B30" s="27" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C30" s="54">
         <v>0.8</v>
@@ -2317,7 +2323,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="B31" s="27" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C31" s="55">
         <f>1-C30</f>
@@ -2326,23 +2332,23 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="21" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="23"/>
     </row>
     <row r="34" spans="1:5">
       <c r="B34" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C34" s="51">
         <v>0.2</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E34" s="53">
         <v>3</v>
@@ -2350,7 +2356,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="B35" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C35" s="52">
         <f>MAX(8%,Market_Yield!C4:D6)</f>
@@ -2359,28 +2365,28 @@
     </row>
     <row r="37" spans="1:5">
       <c r="B37" s="21" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="B38" s="65" t="s">
-        <v>201</v>
-      </c>
-      <c r="C38" s="65"/>
-      <c r="D38" s="65"/>
-      <c r="E38" s="65"/>
+      <c r="B38" s="66" t="s">
+        <v>186</v>
+      </c>
+      <c r="C38" s="66"/>
+      <c r="D38" s="66"/>
+      <c r="E38" s="66"/>
     </row>
     <row r="39" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B39" s="65" t="s">
-        <v>103</v>
-      </c>
-      <c r="C39" s="65"/>
-      <c r="D39" s="65"/>
-      <c r="E39" s="65"/>
+      <c r="B39" s="66" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" s="66"/>
+      <c r="D39" s="66"/>
+      <c r="E39" s="66"/>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="22" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B41" s="22"/>
       <c r="C41" s="22"/>
@@ -2388,35 +2394,35 @@
       <c r="E41" s="22"/>
     </row>
     <row r="43" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B43" s="65" t="s">
-        <v>217</v>
-      </c>
-      <c r="C43" s="65"/>
-      <c r="D43" s="65"/>
-      <c r="E43" s="65"/>
+      <c r="B43" s="66" t="s">
+        <v>202</v>
+      </c>
+      <c r="C43" s="66"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
     </row>
     <row r="45" spans="1:5">
       <c r="B45" s="24" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="B47" s="56" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C47" s="56" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D47" s="58" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="E47" s="58" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="B48" s="27" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C48" s="32">
         <v>0.5</v>
@@ -2425,12 +2431,12 @@
         <v>1</v>
       </c>
       <c r="E48" s="36" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
     </row>
     <row r="49" spans="2:5">
       <c r="B49" s="27" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C49" s="32">
         <v>0.3</v>
@@ -2439,12 +2445,12 @@
         <v>1.5</v>
       </c>
       <c r="E49" s="36" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="50" spans="2:5">
       <c r="B50" s="27" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C50" s="32">
         <v>0.2</v>
@@ -2453,37 +2459,37 @@
         <v>2</v>
       </c>
       <c r="E50" s="36" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
     </row>
     <row r="52" spans="2:5">
       <c r="B52" s="24" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
     </row>
     <row r="54" spans="2:5">
       <c r="B54" s="56" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C54" s="56" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="D54" s="56" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E54" s="56" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="2:5">
       <c r="B55" s="27" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C55" s="27" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D55" s="27" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="E55" s="44">
         <v>1</v>
@@ -2491,13 +2497,13 @@
     </row>
     <row r="56" spans="2:5">
       <c r="B56" s="27" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C56" s="27" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D56" s="27" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E56" s="44">
         <v>2</v>
@@ -2505,13 +2511,13 @@
     </row>
     <row r="57" spans="2:5">
       <c r="B57" s="27" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C57" s="27" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E57" s="44">
         <v>1</v>
@@ -2519,13 +2525,13 @@
     </row>
     <row r="58" spans="2:5">
       <c r="B58" s="27" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C58" s="27" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D58" s="27" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E58" s="44">
         <v>1</v>
@@ -2533,7 +2539,7 @@
     </row>
     <row r="59" spans="2:5">
       <c r="D59" s="28" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E59" s="43">
         <f>SUM(E55:E58)</f>
@@ -2542,7 +2548,7 @@
     </row>
     <row r="60" spans="2:5" ht="12" thickBot="1">
       <c r="D60" s="45" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="E60" s="46">
         <f>IF(E59&lt;=2,C48,IF(E59&gt;=6,C50,C49))</f>
@@ -2552,23 +2558,23 @@
     <row r="61" spans="2:5" ht="12" thickTop="1"/>
     <row r="62" spans="2:5">
       <c r="B62" s="24" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
     </row>
     <row r="63" spans="2:5">
-      <c r="B63" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="C63" s="49">
+      <c r="B63" s="63" t="s">
+        <v>163</v>
+      </c>
+      <c r="C63" s="74">
         <f>-E60*C34</f>
         <v>-0.06</v>
       </c>
     </row>
     <row r="64" spans="2:5">
-      <c r="B64" s="48" t="s">
-        <v>177</v>
-      </c>
-      <c r="C64" s="49">
+      <c r="B64" s="63" t="s">
+        <v>162</v>
+      </c>
+      <c r="C64" s="74">
         <f>C34+C63</f>
         <v>0.14000000000000001</v>
       </c>
@@ -2579,12 +2585,12 @@
     </row>
     <row r="66" spans="1:5">
       <c r="B66" s="42" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="22" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B68" s="22"/>
       <c r="C68" s="22"/>
@@ -2592,34 +2598,34 @@
       <c r="E68" s="22"/>
     </row>
     <row r="70" spans="1:5">
-      <c r="B70" s="65" t="s">
-        <v>202</v>
-      </c>
-      <c r="C70" s="65"/>
-      <c r="D70" s="65"/>
-      <c r="E70" s="65"/>
+      <c r="B70" s="66" t="s">
+        <v>187</v>
+      </c>
+      <c r="C70" s="66"/>
+      <c r="D70" s="66"/>
+      <c r="E70" s="66"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="31" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B72" s="21" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="B73" s="25" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="B74" s="25" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="B75" s="25" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2630,51 +2636,51 @@
     </row>
     <row r="77" spans="1:5">
       <c r="B77" s="25" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="31" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="B79" s="29" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B80" s="65" t="s">
-        <v>179</v>
-      </c>
-      <c r="C80" s="65"/>
-      <c r="D80" s="65"/>
-      <c r="E80" s="65"/>
+      <c r="B80" s="66" t="s">
+        <v>164</v>
+      </c>
+      <c r="C80" s="66"/>
+      <c r="D80" s="66"/>
+      <c r="E80" s="66"/>
     </row>
     <row r="81" spans="1:5">
       <c r="B81" s="1" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="B83" s="24" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B84" s="63" t="s">
-        <v>185</v>
-      </c>
-      <c r="C84" s="63"/>
-      <c r="D84" s="63"/>
-      <c r="E84" s="63"/>
+      <c r="B84" s="64" t="s">
+        <v>170</v>
+      </c>
+      <c r="C84" s="64"/>
+      <c r="D84" s="64"/>
+      <c r="E84" s="64"/>
     </row>
     <row r="86" spans="1:5">
       <c r="B86" s="24" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="B87" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="C87" s="60">
         <f>IF(E59&lt;=2,D48,IF(E59&gt;=6,D50,D49))</f>
@@ -2683,84 +2689,84 @@
     </row>
     <row r="88" spans="1:5">
       <c r="B88" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="C88" s="57">
-        <f>C48</f>
-        <v>0.5</v>
+        <f>MIN(80%,C48*1.5)</f>
+        <v>0.75</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="42" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="B91" s="30" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="B92" s="30" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="31" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="B94" s="21" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
     </row>
     <row r="95" spans="1:5">
-      <c r="B95" s="66" t="s">
-        <v>190</v>
-      </c>
-      <c r="C95" s="66"/>
-      <c r="D95" s="66"/>
-      <c r="E95" s="66"/>
+      <c r="B95" s="67" t="s">
+        <v>175</v>
+      </c>
+      <c r="C95" s="67"/>
+      <c r="D95" s="67"/>
+      <c r="E95" s="67"/>
     </row>
     <row r="96" spans="1:5">
-      <c r="B96" s="64" t="s">
-        <v>207</v>
-      </c>
-      <c r="C96" s="64"/>
-      <c r="D96" s="64"/>
-      <c r="E96" s="64"/>
+      <c r="B96" s="65" t="s">
+        <v>192</v>
+      </c>
+      <c r="C96" s="65"/>
+      <c r="D96" s="65"/>
+      <c r="E96" s="65"/>
     </row>
     <row r="97" spans="1:5">
-      <c r="B97" s="64" t="s">
-        <v>208</v>
-      </c>
-      <c r="C97" s="64"/>
-      <c r="D97" s="64"/>
-      <c r="E97" s="64"/>
+      <c r="B97" s="65" t="s">
+        <v>193</v>
+      </c>
+      <c r="C97" s="65"/>
+      <c r="D97" s="65"/>
+      <c r="E97" s="65"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="B100" s="1" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="C100" s="47">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="B101" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="C101" s="47">
-        <v>8.0320077174672017E-2</v>
+        <v>7.2827407732271143E-2</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="22" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B103" s="22"/>
       <c r="C103" s="22"/>
@@ -2769,22 +2775,22 @@
     </row>
     <row r="105" spans="1:5">
       <c r="B105" s="21" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="B106" s="25" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="B107" s="25" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="B108" s="25" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -2836,30 +2842,30 @@
       <c r="B1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="70" t="s">
+      <c r="D1" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="71" t="s">
-        <v>119</v>
-      </c>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="67" t="s">
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="72" t="s">
+        <v>109</v>
+      </c>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="67"/>
-      <c r="L1" s="68" t="s">
+      <c r="K1" s="68"/>
+      <c r="L1" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="68"/>
-      <c r="N1" s="69" t="s">
-        <v>63</v>
-      </c>
-      <c r="O1" s="69"/>
-      <c r="P1" s="69"/>
-      <c r="Q1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="70" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
+      <c r="Q1" s="70"/>
     </row>
     <row r="2" spans="1:17" ht="26" customHeight="1">
       <c r="B2" s="7" t="s">
@@ -2878,13 +2884,13 @@
         <v>11</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>8</v>
@@ -2902,27 +2908,27 @@
         <v>6</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="P2" s="9" t="s">
         <v>10</v>
       </c>
       <c r="Q2" s="10" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="B3" s="11" t="s">
-        <v>18</v>
+        <v>203</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>19</v>
+        <v>204</v>
       </c>
       <c r="D3" s="2">
         <v>14.96</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>16</v>
+        <v>205</v>
       </c>
       <c r="F3" s="15">
         <v>0.19343775079136272</v>
@@ -2936,7 +2942,7 @@
         <v>0.19343775079136272</v>
       </c>
       <c r="I3" s="15">
-        <v>0.3</v>
+        <v>0.22970196655958811</v>
       </c>
       <c r="J3" s="2">
         <v>14.733437767356989</v>
@@ -2951,30 +2957,30 @@
         <v>9.0909090909090912E-2</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>166</v>
+        <v>206</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>23</v>
+        <v>207</v>
       </c>
       <c r="P3" s="14">
         <v>45716</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>120</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="B4" s="11" t="s">
-        <v>14</v>
+        <v>209</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>15</v>
+        <v>210</v>
       </c>
       <c r="D4" s="2">
         <v>7.79</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>16</v>
+        <v>205</v>
       </c>
       <c r="F4" s="15">
         <v>0.12411921460409614</v>
@@ -2988,7 +2994,7 @@
         <v>0.12411921460409614</v>
       </c>
       <c r="I4" s="15">
-        <v>4.0596066880823796E-2</v>
+        <v>2.0298033440411898E-2</v>
       </c>
       <c r="J4" s="2">
         <v>6.4883606756817951</v>
@@ -3003,30 +3009,30 @@
         <v>7.4454428754813853E-2</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>165</v>
+        <v>211</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>17</v>
+        <v>212</v>
       </c>
       <c r="P4" s="14">
         <v>45716</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>120</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="B5" s="11" t="s">
-        <v>21</v>
+        <v>213</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>22</v>
+        <v>214</v>
       </c>
       <c r="D5" s="2">
         <v>2.1800000000000002</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>16</v>
+        <v>205</v>
       </c>
       <c r="F5" s="15">
         <v>6.3214262000776955E-2</v>
@@ -3055,16 +3061,16 @@
         <v>5.4036697247706419E-2</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>167</v>
+        <v>215</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="P5" s="14">
         <v>45716</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>121</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -5224,13 +5230,13 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="21" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="34"/>
       <c r="B2" s="35" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C2" s="18"/>
       <c r="D2" s="23"/>
@@ -5238,18 +5244,18 @@
     </row>
     <row r="3" spans="1:5">
       <c r="C3" s="31" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="B4" s="36" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C4" s="37">
         <v>4.2500000000000003E-2</v>
@@ -5264,7 +5270,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="B5" s="36" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C5" s="37">
         <v>1.9E-2</v>
@@ -5279,7 +5285,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="B6" s="36" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C6" s="37">
         <v>3.4500000000000003E-2</v>
@@ -5295,7 +5301,7 @@
     <row r="8" spans="1:5">
       <c r="A8" s="34"/>
       <c r="B8" s="35" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1">
         <v>4.3099999999999999E-2</v>
@@ -5306,15 +5312,15 @@
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="1" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" s="27" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C10" s="37">
         <v>9.9400000000000002E-2</v>
@@ -5322,7 +5328,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="B11" s="27" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C11" s="37">
         <v>0.1174</v>
@@ -5330,7 +5336,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="B12" s="27" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C12" s="37">
         <v>3.4500000000000003E-2</v>
@@ -5338,7 +5344,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="B13" s="27" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C13" s="37">
         <v>3.3099999999999997E-2</v>
@@ -5346,7 +5352,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="B14" s="27" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C14" s="37">
         <v>4.2299999999999997E-2</v>
@@ -5354,7 +5360,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="B15" s="27" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C15" s="37">
         <v>5.1200000000000002E-2</v>
@@ -5362,7 +5368,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="B16" s="39" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C16" s="40">
         <f>MAX(Portfolio_Mgmt!C35,C10:C15)</f>
@@ -5372,7 +5378,7 @@
     <row r="18" spans="1:5">
       <c r="A18" s="34"/>
       <c r="B18" s="35" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C18" s="18"/>
       <c r="D18" s="23"/>
@@ -5380,26 +5386,26 @@
     </row>
     <row r="19" spans="1:5">
       <c r="B19" s="18" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="B20" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="B21" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -5407,18 +5413,18 @@
     </row>
     <row r="23" spans="1:5">
       <c r="B23" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C23" s="41" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="B24" s="1" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -5426,18 +5432,18 @@
     </row>
     <row r="26" spans="1:5">
       <c r="B26" s="1" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C26" s="41" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="B27" s="1" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C27" s="41" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -5445,18 +5451,18 @@
     </row>
     <row r="29" spans="1:5">
       <c r="B29" s="1" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="B31" s="1" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C31" s="41" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -5491,217 +5497,217 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="21" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="B3" s="63" t="s">
-        <v>124</v>
-      </c>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
+      <c r="B3" s="64" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="B5" s="66" t="s">
-        <v>126</v>
-      </c>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
+      <c r="B5" s="67" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="B6" s="66" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" s="72"/>
-      <c r="D6" s="72"/>
+      <c r="B6" s="67" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5"/>
       <c r="B10" s="6" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="63" t="s">
-        <v>129</v>
-      </c>
-      <c r="C11" s="63"/>
-      <c r="D11" s="63"/>
+      <c r="B11" s="64" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="B12" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="C12" s="63"/>
-      <c r="D12" s="63"/>
+      <c r="B12" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="24" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="12.4">
       <c r="B16" s="33" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="B17" s="27" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="B18" s="27" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="B19" s="27" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="B20" s="27" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="B21" s="27" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="B22" s="27" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="B23" s="27" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="B24" s="27" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="B25" s="27" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="5"/>
       <c r="B27" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="B28" s="63" t="s">
-        <v>142</v>
-      </c>
-      <c r="C28" s="63"/>
-      <c r="D28" s="63"/>
+      <c r="B28" s="64" t="s">
+        <v>130</v>
+      </c>
+      <c r="C28" s="64"/>
+      <c r="D28" s="64"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="B29" s="63" t="s">
-        <v>143</v>
-      </c>
-      <c r="C29" s="63"/>
-      <c r="D29" s="63"/>
+      <c r="B29" s="64" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" s="64"/>
+      <c r="D29" s="64"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="5"/>
       <c r="B31" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="31" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="B33" s="1" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="31" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="B36" s="1" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="5"/>
       <c r="B38" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="B39" s="25" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="B40" s="1" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="B41" s="1" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805522B0-4733-4881-895B-788297E357CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282E62B2-BE39-4D38-9DCE-4F3A09F44718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -244,10 +244,6 @@
   </si>
   <si>
     <t>Executive Summary</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Portfolio Management</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -919,10 +915,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Investment vs. Holding Cash Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Initial Cash Allocation</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -952,14 +944,6 @@
   <si>
     <t>Negative or Low Growth</t>
     <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Return given Initial Cash Allocation</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cost of Holding Cash if target is met</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>If the portfolio’s projected annual return falls short of the 20% target, increase cash allocation proportionally to the shortfall using the following formula:</t>
@@ -1356,6 +1340,22 @@
   <si>
     <t>N</t>
   </si>
+  <si>
+    <t>Portfolio Management Plan</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cost of Holding Cash when target is met</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cost of holding cash</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Return with cash</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1365,7 +1365,7 @@
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="177" formatCode="[$-13C09]d\ mmm\ yyyy;@"/>
     <numFmt numFmtId="178" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="179" formatCode="#,##0.0_);\(#,##0.0\)"/>
+    <numFmt numFmtId="179" formatCode="#,##0.00_);\(#,##0.00\)"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -1774,15 +1774,18 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1812,9 +1815,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2154,7 +2154,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="21" t="s">
-        <v>56</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2167,38 +2167,38 @@
       <c r="E2" s="22"/>
     </row>
     <row r="4" spans="1:5" ht="36.6" customHeight="1">
-      <c r="B4" s="66" t="s">
-        <v>180</v>
-      </c>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
+      <c r="B4" s="67" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6" s="20"/>
     </row>
     <row r="7" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B7" s="66" t="s">
-        <v>177</v>
-      </c>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
+      <c r="B7" s="67" t="s">
+        <v>173</v>
+      </c>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C10" s="50">
         <f>Market_Yield!C16</f>
@@ -2219,63 +2219,63 @@
     </row>
     <row r="13" spans="1:5">
       <c r="B13" s="24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C13" s="4"/>
     </row>
     <row r="14" spans="1:5">
       <c r="B14" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="B15" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="B17" s="24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="B18" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="B19" s="25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="B20" s="25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C22" s="20"/>
     </row>
     <row r="23" spans="1:5" ht="24.4" customHeight="1">
       <c r="A23" s="18"/>
-      <c r="B23" s="66" t="s">
-        <v>183</v>
-      </c>
-      <c r="C23" s="66"/>
-      <c r="D23" s="66"/>
-      <c r="E23" s="66"/>
+      <c r="B23" s="67" t="s">
+        <v>179</v>
+      </c>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
@@ -2283,39 +2283,39 @@
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
       <c r="B25" s="56" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C25" s="56" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="B26" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="C26" s="61">
+        <v>90</v>
+      </c>
+      <c r="C26" s="59">
         <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="B27" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" s="62">
+        <v>64</v>
+      </c>
+      <c r="C27" s="60">
         <v>0.3</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="B29" s="56" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C29" s="56" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="B30" s="27" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C30" s="54">
         <v>0.8</v>
@@ -2323,7 +2323,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="B31" s="27" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C31" s="55">
         <f>1-C30</f>
@@ -2332,7 +2332,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B33" s="19" t="s">
         <v>15</v>
@@ -2348,7 +2348,7 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E34" s="53">
         <v>3</v>
@@ -2365,28 +2365,28 @@
     </row>
     <row r="37" spans="1:5">
       <c r="B37" s="21" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="B38" s="67" t="s">
+        <v>182</v>
+      </c>
+      <c r="C38" s="67"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="67"/>
+    </row>
+    <row r="39" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B39" s="67" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="B38" s="66" t="s">
-        <v>186</v>
-      </c>
-      <c r="C38" s="66"/>
-      <c r="D38" s="66"/>
-      <c r="E38" s="66"/>
-    </row>
-    <row r="39" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B39" s="66" t="s">
-        <v>93</v>
-      </c>
-      <c r="C39" s="66"/>
-      <c r="D39" s="66"/>
-      <c r="E39" s="66"/>
+      <c r="C39" s="67"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67"/>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B41" s="22"/>
       <c r="C41" s="22"/>
@@ -2394,102 +2394,102 @@
       <c r="E41" s="22"/>
     </row>
     <row r="43" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B43" s="66" t="s">
-        <v>202</v>
-      </c>
-      <c r="C43" s="66"/>
-      <c r="D43" s="66"/>
-      <c r="E43" s="66"/>
+      <c r="B43" s="67" t="s">
+        <v>198</v>
+      </c>
+      <c r="C43" s="67"/>
+      <c r="D43" s="67"/>
+      <c r="E43" s="67"/>
     </row>
     <row r="45" spans="1:5">
       <c r="B45" s="24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="B47" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" s="56" t="s">
         <v>99</v>
       </c>
-      <c r="C47" s="56" t="s">
-        <v>100</v>
-      </c>
       <c r="D47" s="58" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E47" s="58" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="B48" s="27" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C48" s="32">
         <v>0.5</v>
       </c>
-      <c r="D48" s="59">
+      <c r="D48" s="63">
         <v>1</v>
       </c>
       <c r="E48" s="36" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="49" spans="2:5">
       <c r="B49" s="27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C49" s="32">
         <v>0.3</v>
       </c>
-      <c r="D49" s="59">
-        <v>1.5</v>
+      <c r="D49" s="63">
+        <v>1.25</v>
       </c>
       <c r="E49" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="50" spans="2:5">
       <c r="B50" s="27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C50" s="32">
         <v>0.2</v>
       </c>
-      <c r="D50" s="59">
-        <v>2</v>
+      <c r="D50" s="63">
+        <v>1.5</v>
       </c>
       <c r="E50" s="36" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="52" spans="2:5">
       <c r="B52" s="24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54" spans="2:5">
       <c r="B54" s="56" t="s">
+        <v>100</v>
+      </c>
+      <c r="C54" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="C54" s="56" t="s">
+      <c r="D54" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="D54" s="56" t="s">
+      <c r="E54" s="56" t="s">
         <v>103</v>
-      </c>
-      <c r="E54" s="56" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="55" spans="2:5">
       <c r="B55" s="27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C55" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="D55" s="27" t="s">
         <v>80</v>
-      </c>
-      <c r="D55" s="27" t="s">
-        <v>81</v>
       </c>
       <c r="E55" s="44">
         <v>1</v>
@@ -2497,13 +2497,13 @@
     </row>
     <row r="56" spans="2:5">
       <c r="B56" s="27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C56" s="27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D56" s="27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E56" s="44">
         <v>2</v>
@@ -2511,13 +2511,13 @@
     </row>
     <row r="57" spans="2:5">
       <c r="B57" s="27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C57" s="27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E57" s="44">
         <v>1</v>
@@ -2525,13 +2525,13 @@
     </row>
     <row r="58" spans="2:5">
       <c r="B58" s="27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C58" s="27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D58" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E58" s="44">
         <v>1</v>
@@ -2539,7 +2539,7 @@
     </row>
     <row r="59" spans="2:5">
       <c r="D59" s="28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E59" s="43">
         <f>SUM(E55:E58)</f>
@@ -2548,7 +2548,7 @@
     </row>
     <row r="60" spans="2:5" ht="12" thickBot="1">
       <c r="D60" s="45" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E60" s="46">
         <f>IF(E59&lt;=2,C48,IF(E59&gt;=6,C50,C49))</f>
@@ -2558,23 +2558,23 @@
     <row r="61" spans="2:5" ht="12" thickTop="1"/>
     <row r="62" spans="2:5">
       <c r="B62" s="24" t="s">
-        <v>156</v>
+        <v>215</v>
       </c>
     </row>
     <row r="63" spans="2:5">
-      <c r="B63" s="63" t="s">
-        <v>163</v>
-      </c>
-      <c r="C63" s="74">
+      <c r="B63" s="61" t="s">
+        <v>216</v>
+      </c>
+      <c r="C63" s="62">
         <f>-E60*C34</f>
         <v>-0.06</v>
       </c>
     </row>
     <row r="64" spans="2:5">
-      <c r="B64" s="63" t="s">
-        <v>162</v>
-      </c>
-      <c r="C64" s="74">
+      <c r="B64" s="61" t="s">
+        <v>217</v>
+      </c>
+      <c r="C64" s="62">
         <f>C34+C63</f>
         <v>0.14000000000000001</v>
       </c>
@@ -2585,12 +2585,12 @@
     </row>
     <row r="66" spans="1:5">
       <c r="B66" s="42" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B68" s="22"/>
       <c r="C68" s="22"/>
@@ -2598,34 +2598,34 @@
       <c r="E68" s="22"/>
     </row>
     <row r="70" spans="1:5">
-      <c r="B70" s="66" t="s">
-        <v>187</v>
-      </c>
-      <c r="C70" s="66"/>
-      <c r="D70" s="66"/>
-      <c r="E70" s="66"/>
+      <c r="B70" s="67" t="s">
+        <v>183</v>
+      </c>
+      <c r="C70" s="67"/>
+      <c r="D70" s="67"/>
+      <c r="E70" s="67"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B72" s="21" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="B73" s="25" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="B74" s="25" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="B75" s="25" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2636,137 +2636,137 @@
     </row>
     <row r="77" spans="1:5">
       <c r="B77" s="25" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="31" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B79" s="29" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B80" s="66" t="s">
-        <v>164</v>
-      </c>
-      <c r="C80" s="66"/>
-      <c r="D80" s="66"/>
-      <c r="E80" s="66"/>
+      <c r="B80" s="67" t="s">
+        <v>160</v>
+      </c>
+      <c r="C80" s="67"/>
+      <c r="D80" s="67"/>
+      <c r="E80" s="67"/>
     </row>
     <row r="81" spans="1:5">
       <c r="B81" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="B83" s="24" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B84" s="64" t="s">
-        <v>170</v>
-      </c>
-      <c r="C84" s="64"/>
-      <c r="D84" s="64"/>
-      <c r="E84" s="64"/>
+      <c r="B84" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="C84" s="65"/>
+      <c r="D84" s="65"/>
+      <c r="E84" s="65"/>
     </row>
     <row r="86" spans="1:5">
       <c r="B86" s="24" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="B87" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C87" s="60">
+        <v>169</v>
+      </c>
+      <c r="C87" s="64">
         <f>IF(E59&lt;=2,D48,IF(E59&gt;=6,D50,D49))</f>
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="B88" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C88" s="57">
-        <f>MIN(80%,C48*1.5)</f>
-        <v>0.75</v>
+        <f>MIN(80%,C48*1.2)</f>
+        <v>0.6</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="42" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="B91" s="30" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="B92" s="30" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="31" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B94" s="21" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="95" spans="1:5">
-      <c r="B95" s="67" t="s">
-        <v>175</v>
-      </c>
-      <c r="C95" s="67"/>
-      <c r="D95" s="67"/>
-      <c r="E95" s="67"/>
+      <c r="B95" s="68" t="s">
+        <v>171</v>
+      </c>
+      <c r="C95" s="68"/>
+      <c r="D95" s="68"/>
+      <c r="E95" s="68"/>
     </row>
     <row r="96" spans="1:5">
-      <c r="B96" s="65" t="s">
-        <v>192</v>
-      </c>
-      <c r="C96" s="65"/>
-      <c r="D96" s="65"/>
-      <c r="E96" s="65"/>
+      <c r="B96" s="66" t="s">
+        <v>188</v>
+      </c>
+      <c r="C96" s="66"/>
+      <c r="D96" s="66"/>
+      <c r="E96" s="66"/>
     </row>
     <row r="97" spans="1:5">
-      <c r="B97" s="65" t="s">
-        <v>193</v>
-      </c>
-      <c r="C97" s="65"/>
-      <c r="D97" s="65"/>
-      <c r="E97" s="65"/>
+      <c r="B97" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C97" s="66"/>
+      <c r="D97" s="66"/>
+      <c r="E97" s="66"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="B100" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C100" s="47">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="B101" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C101" s="47">
-        <v>7.2827407732271143E-2</v>
+        <v>8.276232678721937E-2</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B103" s="22"/>
       <c r="C103" s="22"/>
@@ -2775,22 +2775,22 @@
     </row>
     <row r="105" spans="1:5">
       <c r="B105" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="B106" s="25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="B107" s="25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="B108" s="25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2842,30 +2842,30 @@
       <c r="B1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="71" t="s">
+      <c r="D1" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="72" t="s">
-        <v>109</v>
-      </c>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="68" t="s">
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="73" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="68"/>
-      <c r="L1" s="69" t="s">
+      <c r="K1" s="69"/>
+      <c r="L1" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="69"/>
-      <c r="N1" s="70" t="s">
+      <c r="M1" s="70"/>
+      <c r="N1" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="O1" s="70"/>
-      <c r="P1" s="70"/>
-      <c r="Q1" s="70"/>
+      <c r="O1" s="71"/>
+      <c r="P1" s="71"/>
+      <c r="Q1" s="71"/>
     </row>
     <row r="2" spans="1:17" ht="26" customHeight="1">
       <c r="B2" s="7" t="s">
@@ -2884,13 +2884,13 @@
         <v>11</v>
       </c>
       <c r="G2" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="7" t="s">
-        <v>64</v>
-      </c>
       <c r="I2" s="7" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>8</v>
@@ -2919,16 +2919,16 @@
     </row>
     <row r="3" spans="1:17">
       <c r="B3" s="11" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D3" s="2">
         <v>14.96</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F3" s="15">
         <v>0.19343775079136272</v>
@@ -2942,7 +2942,7 @@
         <v>0.19343775079136272</v>
       </c>
       <c r="I3" s="15">
-        <v>0.22970196655958811</v>
+        <v>0.3</v>
       </c>
       <c r="J3" s="2">
         <v>14.733437767356989</v>
@@ -2957,30 +2957,30 @@
         <v>9.0909090909090912E-2</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P3" s="14">
         <v>45716</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="B4" s="11" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D4" s="2">
         <v>7.79</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F4" s="15">
         <v>0.12411921460409614</v>
@@ -2994,7 +2994,7 @@
         <v>0.12411921460409614</v>
       </c>
       <c r="I4" s="15">
-        <v>2.0298033440411898E-2</v>
+        <v>3.2476853504659037E-2</v>
       </c>
       <c r="J4" s="2">
         <v>6.4883606756817951</v>
@@ -3009,30 +3009,30 @@
         <v>7.4454428754813853E-2</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="P4" s="14">
         <v>45716</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="B5" s="11" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D5" s="2">
         <v>2.1800000000000002</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F5" s="15">
         <v>6.3214262000776955E-2</v>
@@ -3061,16 +3061,16 @@
         <v>5.4036697247706419E-2</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="P5" s="14">
         <v>45716</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -5230,7 +5230,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5304,7 +5304,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="1">
-        <v>4.3099999999999999E-2</v>
+        <v>4.3499999999999997E-2</v>
       </c>
       <c r="D8" s="1">
         <v>7.4999999999999997E-2</v>
@@ -5312,7 +5312,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C9" s="31" t="s">
         <v>26</v>
@@ -5368,7 +5368,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="B16" s="39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C16" s="40">
         <f>MAX(Portfolio_Mgmt!C35,C10:C15)</f>
@@ -5497,217 +5497,217 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="21" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="B3" s="65" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="B3" s="64" t="s">
-        <v>112</v>
-      </c>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="B5" s="67" t="s">
+      <c r="B5" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="B6" s="68" t="s">
         <v>114</v>
       </c>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="B6" s="67" t="s">
-        <v>115</v>
-      </c>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5"/>
       <c r="B10" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="B11" s="65" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="B11" s="64" t="s">
+      <c r="C11" s="65"/>
+      <c r="D11" s="65"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="B12" s="65" t="s">
         <v>117</v>
       </c>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="B12" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="12.4">
       <c r="B16" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="33" t="s">
         <v>127</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="B17" s="27" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="B18" s="27" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="B19" s="27" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="B20" s="27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="B21" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" s="27" t="s">
         <v>142</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="B22" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="C22" s="27" t="s">
         <v>144</v>
-      </c>
-      <c r="C22" s="27" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="B23" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="C23" s="27" t="s">
         <v>146</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="B24" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C24" s="27" t="s">
         <v>151</v>
-      </c>
-      <c r="C24" s="27" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="B25" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="C25" s="27" t="s">
         <v>148</v>
-      </c>
-      <c r="C25" s="27" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="5"/>
       <c r="B27" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="B28" s="65" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="B28" s="64" t="s">
+      <c r="C28" s="65"/>
+      <c r="D28" s="65"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="B29" s="65" t="s">
         <v>130</v>
       </c>
-      <c r="C28" s="64"/>
-      <c r="D28" s="64"/>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="B29" s="64" t="s">
-        <v>131</v>
-      </c>
-      <c r="C29" s="64"/>
-      <c r="D29" s="64"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="65"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="5"/>
       <c r="B31" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="B33" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="31" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="B36" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="5"/>
       <c r="B38" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="B39" s="25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="B40" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="B41" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282E62B2-BE39-4D38-9DCE-4F3A09F44718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E235A3-3226-4EA0-BAD5-3441C42C1F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -1367,7 +1367,7 @@
     <numFmt numFmtId="178" formatCode="0&quot; yrs&quot;"/>
     <numFmt numFmtId="179" formatCode="#,##0.00_);\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1529,6 +1529,12 @@
       <name val="DengXian"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1770,7 +1776,6 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1786,13 +1791,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="179" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -1816,6 +1821,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -2167,12 +2173,12 @@
       <c r="E2" s="22"/>
     </row>
     <row r="4" spans="1:5" ht="36.6" customHeight="1">
-      <c r="B4" s="67" t="s">
+      <c r="B4" s="64" t="s">
         <v>176</v>
       </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="21" t="s">
@@ -2184,12 +2190,12 @@
       <c r="C6" s="20"/>
     </row>
     <row r="7" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B7" s="67" t="s">
+      <c r="B7" s="64" t="s">
         <v>173</v>
       </c>
-      <c r="C7" s="67"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="24" t="s">
@@ -2270,12 +2276,12 @@
     </row>
     <row r="23" spans="1:5" ht="24.4" customHeight="1">
       <c r="A23" s="18"/>
-      <c r="B23" s="67" t="s">
+      <c r="B23" s="64" t="s">
         <v>179</v>
       </c>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="64"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
@@ -2293,7 +2299,7 @@
       <c r="B26" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="C26" s="59">
+      <c r="C26" s="58">
         <v>10</v>
       </c>
     </row>
@@ -2301,7 +2307,7 @@
       <c r="B27" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="60">
+      <c r="C27" s="59">
         <v>0.3</v>
       </c>
     </row>
@@ -2369,20 +2375,20 @@
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="B38" s="67" t="s">
+      <c r="B38" s="64" t="s">
         <v>182</v>
       </c>
-      <c r="C38" s="67"/>
-      <c r="D38" s="67"/>
-      <c r="E38" s="67"/>
+      <c r="C38" s="64"/>
+      <c r="D38" s="64"/>
+      <c r="E38" s="64"/>
     </row>
     <row r="39" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B39" s="67" t="s">
+      <c r="B39" s="64" t="s">
         <v>92</v>
       </c>
-      <c r="C39" s="67"/>
-      <c r="D39" s="67"/>
-      <c r="E39" s="67"/>
+      <c r="C39" s="64"/>
+      <c r="D39" s="64"/>
+      <c r="E39" s="64"/>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="22" t="s">
@@ -2394,12 +2400,12 @@
       <c r="E41" s="22"/>
     </row>
     <row r="43" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B43" s="67" t="s">
+      <c r="B43" s="64" t="s">
         <v>198</v>
       </c>
-      <c r="C43" s="67"/>
-      <c r="D43" s="67"/>
-      <c r="E43" s="67"/>
+      <c r="C43" s="64"/>
+      <c r="D43" s="64"/>
+      <c r="E43" s="64"/>
     </row>
     <row r="45" spans="1:5">
       <c r="B45" s="24" t="s">
@@ -2413,10 +2419,10 @@
       <c r="C47" s="56" t="s">
         <v>99</v>
       </c>
-      <c r="D47" s="58" t="s">
+      <c r="D47" s="57" t="s">
         <v>169</v>
       </c>
-      <c r="E47" s="58" t="s">
+      <c r="E47" s="57" t="s">
         <v>163</v>
       </c>
     </row>
@@ -2427,7 +2433,7 @@
       <c r="C48" s="32">
         <v>0.5</v>
       </c>
-      <c r="D48" s="63">
+      <c r="D48" s="62">
         <v>1</v>
       </c>
       <c r="E48" s="36" t="s">
@@ -2441,7 +2447,7 @@
       <c r="C49" s="32">
         <v>0.3</v>
       </c>
-      <c r="D49" s="63">
+      <c r="D49" s="62">
         <v>1.25</v>
       </c>
       <c r="E49" s="36" t="s">
@@ -2455,7 +2461,7 @@
       <c r="C50" s="32">
         <v>0.2</v>
       </c>
-      <c r="D50" s="63">
+      <c r="D50" s="62">
         <v>1.5</v>
       </c>
       <c r="E50" s="36" t="s">
@@ -2562,19 +2568,19 @@
       </c>
     </row>
     <row r="63" spans="2:5">
-      <c r="B63" s="61" t="s">
+      <c r="B63" s="60" t="s">
         <v>216</v>
       </c>
-      <c r="C63" s="62">
+      <c r="C63" s="61">
         <f>-E60*C34</f>
         <v>-0.06</v>
       </c>
     </row>
     <row r="64" spans="2:5">
-      <c r="B64" s="61" t="s">
+      <c r="B64" s="60" t="s">
         <v>217</v>
       </c>
-      <c r="C64" s="62">
+      <c r="C64" s="61">
         <f>C34+C63</f>
         <v>0.14000000000000001</v>
       </c>
@@ -2598,12 +2604,12 @@
       <c r="E68" s="22"/>
     </row>
     <row r="70" spans="1:5">
-      <c r="B70" s="67" t="s">
+      <c r="B70" s="64" t="s">
         <v>183</v>
       </c>
-      <c r="C70" s="67"/>
-      <c r="D70" s="67"/>
-      <c r="E70" s="67"/>
+      <c r="C70" s="64"/>
+      <c r="D70" s="64"/>
+      <c r="E70" s="64"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="31" t="s">
@@ -2648,12 +2654,12 @@
       </c>
     </row>
     <row r="80" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B80" s="67" t="s">
+      <c r="B80" s="64" t="s">
         <v>160</v>
       </c>
-      <c r="C80" s="67"/>
-      <c r="D80" s="67"/>
-      <c r="E80" s="67"/>
+      <c r="C80" s="64"/>
+      <c r="D80" s="64"/>
+      <c r="E80" s="64"/>
     </row>
     <row r="81" spans="1:5">
       <c r="B81" s="1" t="s">
@@ -2682,7 +2688,7 @@
       <c r="B87" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C87" s="64">
+      <c r="C87" s="63">
         <f>IF(E59&lt;=2,D48,IF(E59&gt;=6,D50,D49))</f>
         <v>1.25</v>
       </c>
@@ -2691,7 +2697,7 @@
       <c r="B88" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C88" s="57">
+      <c r="C88" s="74">
         <f>MIN(80%,C48*1.2)</f>
         <v>0.6</v>
       </c>
@@ -2720,12 +2726,12 @@
       </c>
     </row>
     <row r="95" spans="1:5">
-      <c r="B95" s="68" t="s">
+      <c r="B95" s="67" t="s">
         <v>171</v>
       </c>
-      <c r="C95" s="68"/>
-      <c r="D95" s="68"/>
-      <c r="E95" s="68"/>
+      <c r="C95" s="67"/>
+      <c r="D95" s="67"/>
+      <c r="E95" s="67"/>
     </row>
     <row r="96" spans="1:5">
       <c r="B96" s="66" t="s">
@@ -2761,7 +2767,7 @@
         <v>195</v>
       </c>
       <c r="C101" s="47">
-        <v>8.276232678721937E-2</v>
+        <v>8.3501481333010011E-2</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2795,18 +2801,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B80:E80"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B95:E95"/>
     <mergeCell ref="B43:E43"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B38:E38"/>
     <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B84:E84"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B80:E80"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="B96:E96"/>
-    <mergeCell ref="B95:E95"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2842,30 +2848,30 @@
       <c r="B1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="72" t="s">
+      <c r="D1" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="73" t="s">
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="72" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="69" t="s">
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="69"/>
-      <c r="L1" s="70" t="s">
+      <c r="K1" s="68"/>
+      <c r="L1" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="70"/>
-      <c r="N1" s="71" t="s">
+      <c r="M1" s="69"/>
+      <c r="N1" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="O1" s="71"/>
-      <c r="P1" s="71"/>
-      <c r="Q1" s="71"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
+      <c r="Q1" s="70"/>
     </row>
     <row r="2" spans="1:17" ht="26" customHeight="1">
       <c r="B2" s="7" t="s">
@@ -2925,21 +2931,21 @@
         <v>200</v>
       </c>
       <c r="D3" s="2">
-        <v>14.96</v>
+        <v>14.94</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>201</v>
       </c>
       <c r="F3" s="15">
-        <v>0.19343775079136272</v>
+        <v>0.19401142226230528</v>
       </c>
       <c r="G3" s="15">
         <f t="shared" ref="G3:G5" si="0">F3 - $C$10</f>
-        <v>0.19343775079136272</v>
+        <v>0.19401142226230528</v>
       </c>
       <c r="H3" s="15">
         <f t="shared" ref="H3:H5" si="1">F3 - $C$11</f>
-        <v>0.19343775079136272</v>
+        <v>0.19401142226230528</v>
       </c>
       <c r="I3" s="15">
         <v>0.3</v>
@@ -2951,10 +2957,10 @@
         <v>20.508980461992877</v>
       </c>
       <c r="L3" s="4">
-        <v>0.11550708685625866</v>
+        <v>0.11566171481724427</v>
       </c>
       <c r="M3" s="4">
-        <v>9.0909090909090912E-2</v>
+        <v>9.1030789825970557E-2</v>
       </c>
       <c r="N3" s="13" t="s">
         <v>202</v>
@@ -2977,24 +2983,24 @@
         <v>206</v>
       </c>
       <c r="D4" s="2">
-        <v>7.79</v>
+        <v>7.77</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>201</v>
       </c>
       <c r="F4" s="15">
-        <v>0.12411921460409614</v>
+        <v>0.12514862916378067</v>
       </c>
       <c r="G4" s="15">
         <f t="shared" si="0"/>
-        <v>0.12411921460409614</v>
+        <v>0.12514862916378067</v>
       </c>
       <c r="H4" s="15">
         <f t="shared" si="1"/>
-        <v>0.12411921460409614</v>
+        <v>0.12514862916378067</v>
       </c>
       <c r="I4" s="15">
-        <v>3.2476853504659037E-2</v>
+        <v>3.674075125745891E-2</v>
       </c>
       <c r="J4" s="2">
         <v>6.4883606756817951</v>
@@ -3003,10 +3009,10 @@
         <v>9.1006872475781417</v>
       </c>
       <c r="L4" s="4">
-        <v>3.9653192809019897E-2</v>
+        <v>3.975526022937774E-2</v>
       </c>
       <c r="M4" s="4">
-        <v>7.4454428754813853E-2</v>
+        <v>7.4646074646074645E-2</v>
       </c>
       <c r="N4" s="13" t="s">
         <v>207</v>
@@ -3029,36 +3035,36 @@
         <v>210</v>
       </c>
       <c r="D5" s="2">
-        <v>2.1800000000000002</v>
+        <v>2.15</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>201</v>
       </c>
       <c r="F5" s="15">
-        <v>6.3214262000776955E-2</v>
+        <v>6.9019080849287207E-2</v>
       </c>
       <c r="G5" s="15">
         <f t="shared" si="0"/>
-        <v>6.3214262000776955E-2</v>
+        <v>6.9019080849287207E-2</v>
       </c>
       <c r="H5" s="15">
         <f t="shared" si="1"/>
-        <v>6.3214262000776955E-2</v>
+        <v>6.9019080849287207E-2</v>
       </c>
       <c r="I5" s="15">
         <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>1.5466941106484338</v>
+        <v>1.5492157922151617</v>
       </c>
       <c r="K5" s="2">
-        <v>2.2438954232004935</v>
+        <v>2.2482528889477993</v>
       </c>
       <c r="L5" s="4">
-        <v>2.1574888673832972E-2</v>
+        <v>2.1918414948495051E-2</v>
       </c>
       <c r="M5" s="4">
-        <v>5.4036697247706419E-2</v>
+        <v>5.4790697674418611E-2</v>
       </c>
       <c r="N5" s="13" t="s">
         <v>211</v>
@@ -5304,7 +5310,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="1">
-        <v>4.3499999999999997E-2</v>
+        <v>4.3799999999999999E-2</v>
       </c>
       <c r="D8" s="1">
         <v>7.4999999999999997E-2</v>
@@ -5514,18 +5520,18 @@
       <c r="D3" s="65"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="67" t="s">
         <v>113</v>
       </c>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="B6" s="68" t="s">
+      <c r="B6" s="67" t="s">
         <v>114</v>
       </c>
-      <c r="C6" s="74"/>
-      <c r="D6" s="74"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,27 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E235A3-3226-4EA0-BAD5-3441C42C1F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6416A34F-80DA-46A4-A23A-C31591A75733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
     <sheet name="Opportunities" sheetId="1" r:id="rId2"/>
     <sheet name="Market_Yield" sheetId="2" r:id="rId3"/>
     <sheet name="Comp_Group" sheetId="6" r:id="rId4"/>
+    <sheet name="Holdings" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Opportunities!$B$2:$Q$2</definedName>
-    <definedName name="benchmark">Portfolio_Mgmt!$C$10</definedName>
-    <definedName name="Cash_Yield">Portfolio_Mgmt!$C$11</definedName>
+    <definedName name="benchmark">Portfolio_Mgmt!$C$12</definedName>
+    <definedName name="Cash_Yield">Portfolio_Mgmt!$C$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="230">
   <si>
     <t>Name</t>
   </si>
@@ -255,10 +256,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Timing Risk Management</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Key Metrics:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -295,19 +292,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Concentration vs. Diversification Management</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">ii. </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">iii. </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 1: Determine Risk Appetite &amp; Cash Position</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -396,31 +385,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> are eligible for portfolio allocation.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">- Cash reserves are determined by a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Risk Appetite Score</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (see Step 1).</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -481,10 +445,6 @@
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t>Cash Allocation</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Indicator	</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
@@ -911,16 +871,51 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Rank Investment Opportunities given Criteria:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Initial Cash Allocation</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Note: </t>
+    <t>High Growth</t>
+  </si>
+  <si>
+    <t>Cap</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Negative or Low Growth</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>= R_i - Benchmark Return</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>= R_i - Cash Yield</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Excess Return over Benchmark (ERB_i)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Excess Return over Cash (ERC_i)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Portfolio Limits</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Growth Classification Limits</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Target Annual Return</t>
     </r>
     <r>
       <rPr>
@@ -930,84 +925,367 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Cost of Holding Cash (%) = Initial Cash Allocation (%) × Target Annual Return</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>High Growth</t>
-  </si>
-  <si>
-    <t>Cap</t>
+      <t>: The target return reflects the investor’s hurdle rate over the lock-up period.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Display all opportunities in the Opportunities Sheet, irrespective of ERB or Selected Flag</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Sort eligible investments by ERB (descending)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Key Outputs:</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t>Negative or Low Growth</t>
+    <t>0590.HK</t>
+  </si>
+  <si>
+    <t>六福珠宝</t>
+  </si>
+  <si>
+    <t>HKD</t>
+  </si>
+  <si>
+    <t>CNS_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low Growth </t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>0083.HK</t>
+  </si>
+  <si>
+    <t>SINO LAND</t>
+  </si>
+  <si>
+    <t>RES_01</t>
+  </si>
+  <si>
+    <t>Negative Growth Asset Play</t>
+  </si>
+  <si>
+    <t>6601.HK</t>
+  </si>
+  <si>
+    <t>朝云集团</t>
+  </si>
+  <si>
+    <t>CNS_04</t>
+  </si>
+  <si>
+    <t>Low Growth Asset Play</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Portfolio Management Plan</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Opportunity Cost</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Portfolio Return</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t>If the portfolio’s projected annual return falls short of the 20% target, increase cash allocation proportionally to the shortfall using the following formula:</t>
+    <t>Projected Cash %</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>Dynamic Cash Adjustment</t>
+    <t>Projected Portfolio Return</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Find Eligible Investments (Data Cleaning)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Display Investment Opportunities (Data Preparation)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Filters:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Retain investments with Selected Flag = True and ERB &gt; 0.</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Enforce Maximum Number of Holdings and Growth Classification Limits.</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Logic:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>- If R_i &lt; Target Annual Return: Penalty proportional to the shortfall.</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Portfolio Management Output</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>iv.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. Projected Portfolio Return:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 1: Determine Risk Appetite &amp; Cash Reserve</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- If no eligible investments exist, Set Projected Cash % = 100% and Projected Portfolio Return = Cash Yield.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Single Investment Cap:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> If If an investment’s provisional allocation exceeds the cap, set its allocation to the cap. Excess weight is moved to cash (do not redistribute to other investments).</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Provisional Weight:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>provisional_weight_i = Single Investment Cap, for each eligible investment i with ERB&gt;0.</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Δweight_i = MAX(0, (Target Annual Return - R_i)/Target Annual Return)</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. Δweight Adjustment:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>- If R_i &gt;= Target Annual Return: Δweight_i = 0</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Purpose:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Given current market price, how much should be allocated to each eligible investments.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Minimium Cash Reserve %</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cost of the Minimium Cash Reserve when all investments are earning Targeting Annual Return</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Min. Cash Reserve</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Projected Cash Reserve %:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Projected Cash Reserve % = 1 - allocated_weight </t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Opportunity Cost = Minimium Cash Reserve % × (Target Annual Return - Cash Yield)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Guidance Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>This plan deploys capital into investments exceeding the benchmark return while strategically reserving cash for future opportunities. Risk is managed through:</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="9"/>
         <color theme="1"/>
-        <rFont val="DengXian"/>
+        <rFont val="Arial"/>
         <family val="2"/>
-        <charset val="134"/>
       </rPr>
-      <t>：</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Adjusted Cash Allocation (%) = Initial Cash Allocation + Δcash</t>
+      <t>Timing Risk:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Invest only when returns justify risk.</t>
+    </r>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t>Note</t>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Concentration/Diversification:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Balance high-conviction bets with diversification rules.</t>
+    </r>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t>Maximum allowable cash allocation</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>/</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Δcash = MIN(Sensitivity Factor*(Target Annual Return - Projected Portfolio Return)/Target Annual Return, Maximum allowable cash allocation - Initial Cash Allocation)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Where:</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Key Variable:</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sensitivity Factor</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Note:</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>- Compute Initial Weights: P_i = (A_i / Sum of A_j for all selected investments) * (100% - Adjusted Cash Allocation)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Distribute Weights:</t>
+    <t>Diversification Rules</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Benchmarks</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- Cash reserve is determined by </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Risk Appetite Score (Step 1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Portfolio Allocation (Step 2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1030,16 +1308,39 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Deploy capital when investment opportunities' Market Annual Return (R_i) exceed the benchmark return, while holding sufficient cash reserves to hedge against market uncertainty.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>= R_i - Benchmark Return</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>= R_i - Cash Yield</t>
+      <t>Maximize returns while adhering to risk limits.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Note: When allocated_weight &gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>investable capital</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, then investments are ranked by ERB and allocated until investable capital is exhausted.</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Annual Return (R_i)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1052,7 +1353,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Guidance Note: </t>
+      <t xml:space="preserve">Note: </t>
     </r>
     <r>
       <rPr>
@@ -1062,8 +1363,15 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>This plan optimizes portfolio returns while managing risk through a dual focus on</t>
-    </r>
+      <t>When the Projected Portfolio Return falls below the benchmark, it is due to overly conservative cash reserve settings or a lack of eligible opportunities. Corrective action is needed to address these issues.</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Imported from Valuation models to Opportunities Sheet</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1073,7 +1381,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Timing Risk and Concentration Risk &amp; Diversification</t>
+      <t xml:space="preserve">Process: </t>
     </r>
     <r>
       <rPr>
@@ -1083,17 +1391,13 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>. Capital is strategically deployed during favorable market conditions, while diversification and cash reserves mitigate downside risks.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Excess Return over Benchmark (ERB_i)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Excess Return over Cash (ERC_i)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+      <t>Calculate a Risk Appetite Score (0–8 scale) using four market indicators to set cash reserves.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strategic reserve for strategic opportunities.</t>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1115,17 +1419,58 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Balance focused high-return investments with diversification to reduce risk, guided by allocation caps and growth themes.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Portfolio Limits</t>
+      <t>Determine the optimal capital allocation at current market prices, while reserving capital for strategic deployment.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. Allocation Weight:</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t>Growth Classification Limits</t>
+    <t>allocation_weight_i = provisional_weight_i * (1-Δweight_i)</t>
     <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>allocated_weight = Σ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>allocation_weight_i)</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Return = Σ(allocation_weight_i× R_i) + (Projected Cash % × Cash Yield)</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Allocation Weight</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. Total Allocated Weight:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Calculate Allocation Weight (Data Processing)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1137,7 +1482,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Target Annual Return</t>
+      <t>Total investable capital Consideration:</t>
     </r>
     <r>
       <rPr>
@@ -1147,213 +1492,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>: The target return reflects the investor’s hurdle rate over the lock-up period.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Purpose:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Automate allocation to eliminate bias and enforce rules.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>- Calculate Attractiveness Score: A_i = ERB_i/Benchmark Return</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>- Calculate Projected Return:  SUM(A_i / SUM(A_j for all selected investments) * R_i) * (100% - Initial Cash Allocation)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Sensitivity Factor:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> higher values increase cash more aggressively.</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Maximum allowable cash allocation: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>prevents over-conservatism.</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>- Enforce Single Investment Cap: Redistribute excess weight to other investments or cash</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>- Enforce Growth Classification Cap: Redistribute excess weight to the other class or cash</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>- Display all opportunities in the Opportunities Sheet, irrespective of ERB or Selected Flag</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>- Sort eligible investments by ERB (descending)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Key Outputs:</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Adjusted Cash Allocation</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Allocation Weight</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Adjusted Portfolio Return</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Max Cash</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Min Cash</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Process: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Calculate a Risk Appetite Score (0–8 scale) using four market indicators to set cash reserves. Automatically adjust the sensitivity factor based on the Risk Appetite Score category. High</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>0590.HK</t>
-  </si>
-  <si>
-    <t>六福珠宝</t>
-  </si>
-  <si>
-    <t>HKD</t>
-  </si>
-  <si>
-    <t>CNS_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low Growth </t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>0083.HK</t>
-  </si>
-  <si>
-    <t>SINO LAND</t>
-  </si>
-  <si>
-    <t>RES_01</t>
-  </si>
-  <si>
-    <t>Negative Growth Asset Play</t>
-  </si>
-  <si>
-    <t>6601.HK</t>
-  </si>
-  <si>
-    <t>朝云集团</t>
-  </si>
-  <si>
-    <t>CNS_04</t>
-  </si>
-  <si>
-    <t>Low Growth Asset Play</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Portfolio Management Plan</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cost of Holding Cash when target is met</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cost of holding cash</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Return with cash</t>
+      <t xml:space="preserve"> This issue will be resolved at processing the Total Allocated Weight.</t>
+    </r>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
@@ -1361,13 +1501,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="177" formatCode="[$-13C09]d\ mmm\ yyyy;@"/>
     <numFmt numFmtId="178" formatCode="0&quot; yrs&quot;"/>
     <numFmt numFmtId="179" formatCode="#,##0.00_);\(#,##0.00\)"/>
+    <numFmt numFmtId="180" formatCode="#,##0_);\(#,##0\)"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1523,16 +1664,32 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
+      <i/>
+      <u/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="DengXian"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei UI"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
+      <i/>
       <sz val="9"/>
-      <color rgb="FF00B050"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF7030A0"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1695,7 +1852,6 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1706,10 +1862,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1767,16 +1919,7 @@
     <xf numFmtId="178" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1787,21 +1930,37 @@
     <xf numFmtId="10" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="179" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1819,9 +1978,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -2148,7 +2309,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
@@ -2159,664 +2320,723 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="21" t="s">
-        <v>214</v>
+      <c r="A1" s="20" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-    </row>
-    <row r="4" spans="1:5" ht="36.6" customHeight="1">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+    </row>
+    <row r="4" spans="1:5" ht="24.4" customHeight="1">
       <c r="B4" s="64" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="C4" s="64"/>
       <c r="D4" s="64"/>
       <c r="E4" s="64"/>
     </row>
+    <row r="5" spans="1:5">
+      <c r="B5" s="24" t="s">
+        <v>209</v>
+      </c>
+    </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="24" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="C8" s="62"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="B9" s="64" t="s">
+        <v>221</v>
+      </c>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="B11" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="20"/>
-    </row>
-    <row r="7" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B7" s="64" t="s">
-        <v>173</v>
-      </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="B9" s="24" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="B10" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" s="50">
+    </row>
+    <row r="12" spans="1:5">
+      <c r="B12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="47">
         <f>Market_Yield!C16</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="B11" s="1" t="s">
+    <row r="13" spans="1:5">
+      <c r="B13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="50">
+      <c r="C13" s="47">
         <f>Market_Yield!C6</f>
         <v>3.4500000000000003E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="C12" s="4"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="B13" s="24" t="s">
+    <row r="14" spans="1:5">
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="B16" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="B17" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="B18" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="B20" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="4"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="B14" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="B15" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="B17" s="24" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="B18" s="25" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="B19" s="25" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="B20" s="25" t="s">
-        <v>89</v>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="B21" s="24" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="B23" s="24" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="C25" s="62"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="18"/>
+      <c r="B26" s="64" t="s">
+        <v>214</v>
+      </c>
+      <c r="C26" s="64"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="64"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="18"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="18"/>
+      <c r="B28" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="C28" s="51" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="B29" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" s="52">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="B30" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="53">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="B32" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="C32" s="51" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="B33" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="C33" s="60">
+        <f>C29-C34</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="B34" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="C34" s="59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="20"/>
-    </row>
-    <row r="23" spans="1:5" ht="24.4" customHeight="1">
-      <c r="A23" s="18"/>
-      <c r="B23" s="64" t="s">
-        <v>179</v>
-      </c>
-      <c r="C23" s="64"/>
-      <c r="D23" s="64"/>
-      <c r="E23" s="64"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="18"/>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="18"/>
-      <c r="B25" s="56" t="s">
-        <v>180</v>
-      </c>
-      <c r="C25" s="56" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="B26" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" s="58">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="B27" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" s="59">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="B29" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="C29" s="56" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="B30" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="C30" s="54">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="B31" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="C31" s="55">
-        <f>1-C30</f>
-        <v>0.19999999999999996</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B33" s="19" t="s">
+      <c r="B36" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="20"/>
-      <c r="D33" s="23"/>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="B34" s="1" t="s">
+      <c r="C36" s="62"/>
+      <c r="D36" s="22"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="B37" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="51">
+      <c r="C37" s="48">
         <v>0.2</v>
       </c>
-      <c r="D34" s="18" t="s">
+      <c r="D37" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="E34" s="53">
+      <c r="E37" s="50">
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
-      <c r="B35" s="1" t="s">
+    <row r="38" spans="1:5">
+      <c r="B38" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="52">
+      <c r="C38" s="49">
         <f>MAX(8%,Market_Yield!C4:D6)</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
-      <c r="B37" s="21" t="s">
+    <row r="40" spans="1:5">
+      <c r="B40" s="20" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="B41" s="64" t="s">
+        <v>158</v>
+      </c>
+      <c r="C41" s="64"/>
+      <c r="D41" s="64"/>
+      <c r="E41" s="64"/>
+    </row>
+    <row r="42" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B42" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" s="64"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="B46" s="64" t="s">
+        <v>219</v>
+      </c>
+      <c r="C46" s="64"/>
+      <c r="D46" s="64"/>
+      <c r="E46" s="64"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="B48" s="23" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5">
+      <c r="B50" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="C50" s="51" t="s">
+        <v>204</v>
+      </c>
+      <c r="D50" s="57"/>
+      <c r="E50" s="57"/>
+    </row>
+    <row r="51" spans="2:5">
+      <c r="B51" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C51" s="29">
+        <v>0.5</v>
+      </c>
+      <c r="D51" s="58"/>
+      <c r="E51" s="56"/>
+    </row>
+    <row r="52" spans="2:5">
+      <c r="B52" s="26" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="B38" s="64" t="s">
+      <c r="C52" s="29">
+        <v>0.3</v>
+      </c>
+      <c r="D52" s="58"/>
+      <c r="E52" s="56"/>
+    </row>
+    <row r="53" spans="2:5">
+      <c r="B53" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="C53" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="D53" s="63" t="s">
+        <v>220</v>
+      </c>
+      <c r="E53" s="56"/>
+    </row>
+    <row r="55" spans="2:5">
+      <c r="B55" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5">
+      <c r="B57" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="C57" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="D57" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="E57" s="51" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5">
+      <c r="B58" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C58" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D58" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="E58" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5">
+      <c r="B59" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C59" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D59" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="E59" s="41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5">
+      <c r="B60" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C60" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D60" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="E60" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5">
+      <c r="B61" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="C61" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D61" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="E61" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5">
+      <c r="D62" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E62" s="40">
+        <f>SUM(E58:E61)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" ht="12" thickBot="1">
+      <c r="D63" s="42" t="s">
+        <v>202</v>
+      </c>
+      <c r="E63" s="43">
+        <f>IF(E62&lt;=2,C51,IF(E62&gt;=6,C53,C52))</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" ht="12" thickTop="1"/>
+    <row r="65" spans="1:5">
+      <c r="B65" s="23" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="B66" s="54" t="s">
+        <v>178</v>
+      </c>
+      <c r="C66" s="55">
+        <f>-E63*(C37-Cash_Yield)</f>
+        <v>-4.965E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="B67" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="C67" s="55">
+        <f>C37+C66</f>
+        <v>0.15035000000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="B68" s="45"/>
+      <c r="C68" s="46"/>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="B69" s="39" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B71" s="21"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="B73" s="64" t="s">
+        <v>201</v>
+      </c>
+      <c r="C73" s="64"/>
+      <c r="D73" s="64"/>
+      <c r="E73" s="64"/>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="B75" s="20" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="B76" s="24" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="B77" s="24" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="B79" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="C38" s="64"/>
-      <c r="D38" s="64"/>
-      <c r="E38" s="64"/>
-    </row>
-    <row r="39" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B39" s="64" t="s">
-        <v>92</v>
-      </c>
-      <c r="C39" s="64"/>
-      <c r="D39" s="64"/>
-      <c r="E39" s="64"/>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-    </row>
-    <row r="43" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B43" s="64" t="s">
-        <v>198</v>
-      </c>
-      <c r="C43" s="64"/>
-      <c r="D43" s="64"/>
-      <c r="E43" s="64"/>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="B45" s="24" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="B47" s="56" t="s">
-        <v>98</v>
-      </c>
-      <c r="C47" s="56" t="s">
-        <v>99</v>
-      </c>
-      <c r="D47" s="57" t="s">
-        <v>169</v>
-      </c>
-      <c r="E47" s="57" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="B48" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="C48" s="32">
-        <v>0.5</v>
-      </c>
-      <c r="D48" s="62">
-        <v>1</v>
-      </c>
-      <c r="E48" s="36" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5">
-      <c r="B49" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="C49" s="32">
-        <v>0.3</v>
-      </c>
-      <c r="D49" s="62">
-        <v>1.25</v>
-      </c>
-      <c r="E49" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="50" spans="2:5">
-      <c r="B50" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C50" s="32">
-        <v>0.2</v>
-      </c>
-      <c r="D50" s="62">
-        <v>1.5</v>
-      </c>
-      <c r="E50" s="36" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5">
-      <c r="B52" s="24" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="54" spans="2:5">
-      <c r="B54" s="56" t="s">
-        <v>100</v>
-      </c>
-      <c r="C54" s="56" t="s">
-        <v>101</v>
-      </c>
-      <c r="D54" s="56" t="s">
-        <v>102</v>
-      </c>
-      <c r="E54" s="56" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="55" spans="2:5">
-      <c r="B55" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="C55" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D55" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="E55" s="44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="2:5">
-      <c r="B56" s="27" t="s">
-        <v>73</v>
-      </c>
-      <c r="C56" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="D56" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="E56" s="44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" spans="2:5">
-      <c r="B57" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="C57" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="D57" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="E57" s="44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="2:5">
-      <c r="B58" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="C58" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="D58" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="E58" s="44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="2:5">
-      <c r="D59" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="E59" s="43">
-        <f>SUM(E55:E58)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="2:5" ht="12" thickBot="1">
-      <c r="D60" s="45" t="s">
-        <v>155</v>
-      </c>
-      <c r="E60" s="46">
-        <f>IF(E59&lt;=2,C48,IF(E59&gt;=6,C50,C49))</f>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="61" spans="2:5" ht="12" thickTop="1"/>
-    <row r="62" spans="2:5">
-      <c r="B62" s="24" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="63" spans="2:5">
-      <c r="B63" s="60" t="s">
-        <v>216</v>
-      </c>
-      <c r="C63" s="61">
-        <f>-E60*C34</f>
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="64" spans="2:5">
-      <c r="B64" s="60" t="s">
-        <v>217</v>
-      </c>
-      <c r="C64" s="61">
-        <f>C34+C63</f>
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="B65" s="48"/>
-      <c r="C65" s="49"/>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="B66" s="42" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="B68" s="22"/>
-      <c r="C68" s="22"/>
-      <c r="D68" s="22"/>
-      <c r="E68" s="22"/>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="B70" s="64" t="s">
-        <v>183</v>
-      </c>
-      <c r="C70" s="64"/>
-      <c r="D70" s="64"/>
-      <c r="E70" s="64"/>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="B72" s="21" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="B73" s="25" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="B74" s="25" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="B75" s="25" t="s">
+    </row>
+    <row r="80" spans="1:5">
+      <c r="B80" s="39" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
-      <c r="B76" s="25" t="str">
-        <f>"- Choose top "&amp;C26&amp;" (or fewer) investments: respecting the maximum holdings limit and selected Flag"</f>
-        <v>- Choose top 10 (or fewer) investments: respecting the maximum holdings limit and selected Flag</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="B77" s="25" t="s">
+    <row r="81" spans="1:5">
+      <c r="B81" s="24" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="B79" s="29" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B80" s="64" t="s">
-        <v>160</v>
-      </c>
-      <c r="C80" s="64"/>
-      <c r="D80" s="64"/>
-      <c r="E80" s="64"/>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="B81" s="1" t="s">
-        <v>162</v>
+    <row r="82" spans="1:5">
+      <c r="B82" s="24" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="B83" s="24" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B84" s="65" t="s">
-        <v>166</v>
-      </c>
-      <c r="C84" s="65"/>
-      <c r="D84" s="65"/>
-      <c r="E84" s="65"/>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="B85" s="20" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="86" spans="1:5">
       <c r="B86" s="24" t="s">
-        <v>168</v>
+        <v>196</v>
       </c>
     </row>
     <row r="87" spans="1:5">
-      <c r="B87" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C87" s="63">
-        <f>IF(E59&lt;=2,D48,IF(E59&gt;=6,D50,D49))</f>
-        <v>1.25</v>
-      </c>
+      <c r="B87" s="67" t="s">
+        <v>197</v>
+      </c>
+      <c r="C87" s="67"/>
+      <c r="D87" s="67"/>
+      <c r="E87" s="67"/>
     </row>
     <row r="88" spans="1:5">
-      <c r="B88" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C88" s="74">
-        <f>MIN(80%,C48*1.2)</f>
-        <v>0.6</v>
-      </c>
+      <c r="B88" s="66" t="s">
+        <v>195</v>
+      </c>
+      <c r="C88" s="66"/>
+      <c r="D88" s="66"/>
+      <c r="E88" s="66"/>
+    </row>
+    <row r="89" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B89" s="64" t="s">
+        <v>194</v>
+      </c>
+      <c r="C89" s="64"/>
+      <c r="D89" s="64"/>
+      <c r="E89" s="64"/>
     </row>
     <row r="90" spans="1:5">
-      <c r="B90" s="42" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
-      <c r="B91" s="30" t="s">
-        <v>186</v>
-      </c>
+      <c r="B90" s="64" t="s">
+        <v>229</v>
+      </c>
+      <c r="C90" s="64"/>
+      <c r="D90" s="64"/>
+      <c r="E90" s="64"/>
     </row>
     <row r="92" spans="1:5">
-      <c r="B92" s="30" t="s">
+      <c r="B92" s="24" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="B93" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="B94" s="61" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
-      <c r="A94" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="B94" s="21" t="s">
-        <v>172</v>
-      </c>
-    </row>
     <row r="95" spans="1:5">
-      <c r="B95" s="67" t="s">
-        <v>171</v>
-      </c>
-      <c r="C95" s="67"/>
-      <c r="D95" s="67"/>
-      <c r="E95" s="67"/>
+      <c r="B95" s="24" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="96" spans="1:5">
-      <c r="B96" s="66" t="s">
+      <c r="B96" s="24" t="s">
         <v>188</v>
       </c>
-      <c r="C96" s="66"/>
-      <c r="D96" s="66"/>
-      <c r="E96" s="66"/>
-    </row>
-    <row r="97" spans="1:5">
-      <c r="B97" s="66" t="s">
+    </row>
+    <row r="98" spans="1:5">
+      <c r="B98" s="24" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="B99" s="65" t="s">
+        <v>223</v>
+      </c>
+      <c r="C99" s="65"/>
+      <c r="D99" s="65"/>
+      <c r="E99" s="65"/>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="B101" s="24" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="12.4">
+      <c r="B102" s="65" t="s">
+        <v>224</v>
+      </c>
+      <c r="C102" s="65"/>
+      <c r="D102" s="65"/>
+      <c r="E102" s="65"/>
+    </row>
+    <row r="103" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B103" s="64" t="s">
+        <v>215</v>
+      </c>
+      <c r="C103" s="64"/>
+      <c r="D103" s="64"/>
+      <c r="E103" s="64"/>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="B105" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="C97" s="66"/>
-      <c r="D97" s="66"/>
-      <c r="E97" s="66"/>
-    </row>
-    <row r="99" spans="1:5">
-      <c r="B99" s="24" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
-      <c r="B100" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C100" s="47">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
-      <c r="B101" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C101" s="47">
-        <v>8.3501481333010011E-2</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
-      <c r="A103" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="B103" s="22"/>
-      <c r="C103" s="22"/>
-      <c r="D103" s="22"/>
-      <c r="E103" s="22"/>
-    </row>
-    <row r="105" spans="1:5">
-      <c r="B105" s="21" t="s">
-        <v>87</v>
-      </c>
     </row>
     <row r="106" spans="1:5">
-      <c r="B106" s="25" t="s">
-        <v>104</v>
+      <c r="B106" s="1" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="107" spans="1:5">
-      <c r="B107" s="25" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
-      <c r="B108" s="25" t="s">
-        <v>105</v>
+      <c r="B107" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="B109" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="B110" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="B112" s="23" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="B113" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C113" s="44">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="B114" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C114" s="44">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="D114" s="62" t="str">
+        <f>IF(C114&lt;benchmark,"Warning: Return is lower than the Benchmark.")</f>
+        <v>Warning: Return is lower than the Benchmark.</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B116" s="64" t="s">
+        <v>217</v>
+      </c>
+      <c r="C116" s="64"/>
+      <c r="D116" s="64"/>
+      <c r="E116" s="64"/>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B118" s="21"/>
+      <c r="C118" s="21"/>
+      <c r="D118" s="21"/>
+      <c r="E118" s="21"/>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="B120" s="20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="B121" s="24" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="B122" s="24" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="B123" s="24" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B84:E84"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B80:E80"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="B96:E96"/>
-    <mergeCell ref="B95:E95"/>
-    <mergeCell ref="B43:E43"/>
+  <mergeCells count="15">
+    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="B73:E73"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B46:E46"/>
     <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B116:E116"/>
+    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="B102:E102"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B90:E90"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="93" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2854,7 +3074,7 @@
       <c r="E1" s="71"/>
       <c r="F1" s="71"/>
       <c r="G1" s="72" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H1" s="72"/>
       <c r="I1" s="72"/>
@@ -2890,13 +3110,13 @@
         <v>11</v>
       </c>
       <c r="G2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="H2" s="7" t="s">
-        <v>63</v>
-      </c>
       <c r="I2" s="7" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>8</v>
@@ -2925,16 +3145,16 @@
     </row>
     <row r="3" spans="1:17">
       <c r="B3" s="11" t="s">
-        <v>199</v>
+        <v>162</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>200</v>
+        <v>163</v>
       </c>
       <c r="D3" s="2">
         <v>14.94</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="F3" s="15">
         <v>0.19401142226230528</v>
@@ -2963,30 +3183,30 @@
         <v>9.1030789825970557E-2</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>203</v>
+        <v>166</v>
       </c>
       <c r="P3" s="14">
         <v>45716</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>204</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="B4" s="11" t="s">
-        <v>205</v>
+        <v>168</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="D4" s="2">
         <v>7.77</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="F4" s="15">
         <v>0.12514862916378067</v>
@@ -3015,30 +3235,30 @@
         <v>7.4646074646074645E-2</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>207</v>
+        <v>170</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>208</v>
+        <v>171</v>
       </c>
       <c r="P4" s="14">
         <v>45716</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>204</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="B5" s="11" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="D5" s="2">
         <v>2.15</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="F5" s="15">
         <v>6.9019080849287207E-2</v>
@@ -3067,16 +3287,16 @@
         <v>5.4790697674418611E-2</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>212</v>
+        <v>175</v>
       </c>
       <c r="P5" s="14">
         <v>45716</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>213</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -5235,78 +5455,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="B1" s="21" t="s">
-        <v>152</v>
+      <c r="B1" s="20" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="34"/>
-      <c r="B2" s="35" t="s">
+      <c r="A2" s="31"/>
+      <c r="B2" s="32" t="s">
         <v>18</v>
       </c>
       <c r="C2" s="18"/>
-      <c r="D2" s="23"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="18"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="28" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="37">
+      <c r="C4" s="34">
         <v>4.2500000000000003E-2</v>
       </c>
-      <c r="D4" s="37">
+      <c r="D4" s="34">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E4" s="38">
+      <c r="E4" s="35">
         <f>D4-C4</f>
         <v>3.2499999999999994E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="37">
+      <c r="C5" s="34">
         <v>1.9E-2</v>
       </c>
-      <c r="D5" s="37">
+      <c r="D5" s="34">
         <v>3.1E-2</v>
       </c>
-      <c r="E5" s="38">
+      <c r="E5" s="35">
         <f>D5-C5</f>
         <v>1.2E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="37">
+      <c r="C6" s="34">
         <v>3.4500000000000003E-2</v>
       </c>
-      <c r="D6" s="37">
+      <c r="D6" s="34">
         <v>5.2499999999999998E-2</v>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="35">
         <f>D6-C6</f>
         <v>1.7999999999999995E-2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="34"/>
-      <c r="B8" s="35" t="s">
+      <c r="A8" s="31"/>
+      <c r="B8" s="32" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="1">
@@ -5320,81 +5540,81 @@
       <c r="B9" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="28" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="37">
+      <c r="C10" s="34">
         <v>9.9400000000000002E-2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="37">
+      <c r="C11" s="34">
         <v>0.1174</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="37">
+      <c r="C12" s="34">
         <v>3.4500000000000003E-2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="37">
+      <c r="C13" s="34">
         <v>3.3099999999999997E-2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="34">
         <v>4.2299999999999997E-2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="34">
         <v>5.1200000000000002E-2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="B16" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" s="40">
-        <f>MAX(Portfolio_Mgmt!C35,C10:C15)</f>
+      <c r="B16" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="37">
+        <f>MAX(Portfolio_Mgmt!C38,C10:C15)</f>
         <v>0.1174</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="34"/>
-      <c r="B18" s="35" t="s">
+      <c r="A18" s="31"/>
+      <c r="B18" s="32" t="s">
         <v>33</v>
       </c>
       <c r="C18" s="18"/>
-      <c r="D18" s="23"/>
+      <c r="D18" s="22"/>
       <c r="E18" s="18"/>
     </row>
     <row r="19" spans="1:5">
       <c r="B19" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="41" t="s">
+      <c r="C19" s="38" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5402,7 +5622,7 @@
       <c r="B20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="41" t="s">
+      <c r="C20" s="38" t="s">
         <v>37</v>
       </c>
     </row>
@@ -5410,18 +5630,18 @@
       <c r="B21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="41" t="s">
+      <c r="C21" s="38" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="C22" s="41"/>
+      <c r="C22" s="38"/>
     </row>
     <row r="23" spans="1:5">
       <c r="B23" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="41" t="s">
+      <c r="C23" s="38" t="s">
         <v>41</v>
       </c>
     </row>
@@ -5429,18 +5649,18 @@
       <c r="B24" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="41" t="s">
+      <c r="C24" s="38" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="C25" s="41"/>
+      <c r="C25" s="38"/>
     </row>
     <row r="26" spans="1:5">
       <c r="B26" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="41" t="s">
+      <c r="C26" s="38" t="s">
         <v>45</v>
       </c>
     </row>
@@ -5448,18 +5668,18 @@
       <c r="B27" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="41" t="s">
+      <c r="C27" s="38" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="C28" s="41"/>
+      <c r="C28" s="38"/>
     </row>
     <row r="29" spans="1:5">
       <c r="B29" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="41" t="s">
+      <c r="C29" s="38" t="s">
         <v>49</v>
       </c>
     </row>
@@ -5467,7 +5687,7 @@
       <c r="B31" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C31" s="41" t="s">
+      <c r="C31" s="38" t="s">
         <v>51</v>
       </c>
     </row>
@@ -5502,218 +5722,218 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="B1" s="21" t="s">
-        <v>109</v>
+      <c r="B1" s="20" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="B3" s="65" t="s">
-        <v>111</v>
-      </c>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
+      <c r="B3" s="73" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="B5" s="67" t="s">
-        <v>113</v>
-      </c>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
+      <c r="B5" s="74" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="B6" s="67" t="s">
-        <v>114</v>
-      </c>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
+      <c r="B6" s="74" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5"/>
       <c r="B10" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="B11" s="73" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="73"/>
+      <c r="D11" s="73"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="B12" s="73" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="B14" s="23" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="12.4">
+      <c r="B16" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="B17" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="B18" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="B19" s="26" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="B11" s="65" t="s">
+      <c r="C19" s="26" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="B20" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="65"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="B12" s="65" t="s">
-        <v>117</v>
-      </c>
-      <c r="C12" s="65"/>
-      <c r="D12" s="65"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="B14" s="24" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="12.4">
-      <c r="B16" s="33" t="s">
-        <v>126</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="B17" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="B18" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="B19" s="27" t="s">
+      <c r="C20" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="C19" s="27" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="B20" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>125</v>
-      </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="B22" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="B23" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="C23" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="C21" s="27" t="s">
+    </row>
+    <row r="24" spans="1:4">
+      <c r="B24" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="C24" s="26" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="B25" s="26" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="B22" s="27" t="s">
+      <c r="C25" s="26" t="s">
         <v>143</v>
-      </c>
-      <c r="C22" s="27" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="B23" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="B24" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="C24" s="27" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="B25" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="C25" s="27" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="5"/>
       <c r="B27" s="6" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="B28" s="65" t="s">
-        <v>129</v>
-      </c>
-      <c r="C28" s="65"/>
-      <c r="D28" s="65"/>
+      <c r="B28" s="73" t="s">
+        <v>124</v>
+      </c>
+      <c r="C28" s="73"/>
+      <c r="D28" s="73"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="B29" s="65" t="s">
-        <v>130</v>
-      </c>
-      <c r="C29" s="65"/>
-      <c r="D29" s="65"/>
+      <c r="B29" s="73" t="s">
+        <v>125</v>
+      </c>
+      <c r="C29" s="73"/>
+      <c r="D29" s="73"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="5"/>
       <c r="B31" s="6" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="B32" s="24" t="s">
-        <v>132</v>
+      <c r="A32" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="B33" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="B35" s="24" t="s">
-        <v>134</v>
+      <c r="A35" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="B35" s="23" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="B36" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="5"/>
       <c r="B38" s="6" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="B39" s="25" t="s">
-        <v>138</v>
+      <c r="B39" s="24" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="B40" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="B41" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -5729,4 +5949,14 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D81F047E-EC38-4C3A-BA81-E6C9549453D6}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6416A34F-80DA-46A4-A23A-C31591A75733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D51AEC07-4EE0-4CA7-ACAF-E84B8CAB220C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1344,6 +1344,135 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Imported from Valuation models to Opportunities Sheet</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Process: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Calculate a Risk Appetite Score (0–8 scale) using four market indicators to set cash reserves.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strategic reserve for strategic opportunities.</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Objective: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Determine the optimal capital allocation at current market prices, while reserving capital for strategic deployment.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. Allocation Weight:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>allocation_weight_i = provisional_weight_i * (1-Δweight_i)</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>allocated_weight = Σ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>allocation_weight_i)</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Return = Σ(allocation_weight_i× R_i) + (Projected Cash % × Cash Yield)</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Allocation Weight</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. Total Allocated Weight:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Calculate Allocation Weight (Data Processing)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Total investable capital Consideration:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> This issue will be resolved at processing the Total Allocated Weight.</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1363,136 +1492,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>When the Projected Portfolio Return falls below the benchmark, it is due to overly conservative cash reserve settings or a lack of eligible opportunities. Corrective action is needed to address these issues.</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Imported from Valuation models to Opportunities Sheet</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Process: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Calculate a Risk Appetite Score (0–8 scale) using four market indicators to set cash reserves.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Strategic reserve for strategic opportunities.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Objective: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Determine the optimal capital allocation at current market prices, while reserving capital for strategic deployment.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3. Allocation Weight:</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>allocation_weight_i = provisional_weight_i * (1-Δweight_i)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>allocated_weight = Σ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei UI"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>allocation_weight_i)</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Return = Σ(allocation_weight_i× R_i) + (Projected Cash % × Cash Yield)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Allocation Weight</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>4. Total Allocated Weight:</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Calculate Allocation Weight (Data Processing)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Total investable capital Consideration:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> This issue will be resolved at processing the Total Allocated Weight.</t>
+      <t>When the Projected Portfolio Return falls below the benchmark, it is due to overly conservative cash reserve settings or a lack of eligible opportunities. Manual corrective action is needed to address these issues.</t>
     </r>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
@@ -1950,17 +1950,17 @@
     <xf numFmtId="179" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2334,12 +2334,12 @@
       <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B4" s="64" t="s">
+      <c r="B4" s="65" t="s">
         <v>208</v>
       </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
     </row>
     <row r="5" spans="1:5">
       <c r="B5" s="24" t="s">
@@ -2361,12 +2361,12 @@
       <c r="C8" s="62"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="B9" s="64" t="s">
-        <v>221</v>
-      </c>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
+      <c r="B9" s="65" t="s">
+        <v>220</v>
+      </c>
+      <c r="C9" s="65"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="65"/>
     </row>
     <row r="11" spans="1:5">
       <c r="B11" s="23" t="s">
@@ -2405,7 +2405,7 @@
         <v>216</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2455,12 +2455,12 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="18"/>
-      <c r="B26" s="64" t="s">
+      <c r="B26" s="65" t="s">
         <v>214</v>
       </c>
-      <c r="C26" s="64"/>
-      <c r="D26" s="64"/>
-      <c r="E26" s="64"/>
+      <c r="C26" s="65"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="18"/>
@@ -2554,20 +2554,20 @@
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="B41" s="64" t="s">
+      <c r="B41" s="65" t="s">
         <v>158</v>
       </c>
-      <c r="C41" s="64"/>
-      <c r="D41" s="64"/>
-      <c r="E41" s="64"/>
+      <c r="C41" s="65"/>
+      <c r="D41" s="65"/>
+      <c r="E41" s="65"/>
     </row>
     <row r="42" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B42" s="64" t="s">
+      <c r="B42" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="C42" s="64"/>
-      <c r="D42" s="64"/>
-      <c r="E42" s="64"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="65"/>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="21" t="s">
@@ -2579,12 +2579,12 @@
       <c r="E44" s="21"/>
     </row>
     <row r="46" spans="1:5">
-      <c r="B46" s="64" t="s">
-        <v>219</v>
-      </c>
-      <c r="C46" s="64"/>
-      <c r="D46" s="64"/>
-      <c r="E46" s="64"/>
+      <c r="B46" s="65" t="s">
+        <v>218</v>
+      </c>
+      <c r="C46" s="65"/>
+      <c r="D46" s="65"/>
+      <c r="E46" s="65"/>
     </row>
     <row r="48" spans="1:5">
       <c r="B48" s="23" t="s">
@@ -2629,7 +2629,7 @@
         <v>0.2</v>
       </c>
       <c r="D53" s="63" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E53" s="56"/>
     </row>
@@ -2769,12 +2769,12 @@
       <c r="E71" s="21"/>
     </row>
     <row r="73" spans="1:5">
-      <c r="B73" s="64" t="s">
+      <c r="B73" s="65" t="s">
         <v>201</v>
       </c>
-      <c r="C73" s="64"/>
-      <c r="D73" s="64"/>
-      <c r="E73" s="64"/>
+      <c r="C73" s="65"/>
+      <c r="D73" s="65"/>
+      <c r="E73" s="65"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="28" t="s">
@@ -2827,7 +2827,7 @@
         <v>148</v>
       </c>
       <c r="B85" s="20" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2836,36 +2836,36 @@
       </c>
     </row>
     <row r="87" spans="1:5">
-      <c r="B87" s="67" t="s">
+      <c r="B87" s="66" t="s">
         <v>197</v>
       </c>
-      <c r="C87" s="67"/>
-      <c r="D87" s="67"/>
-      <c r="E87" s="67"/>
+      <c r="C87" s="66"/>
+      <c r="D87" s="66"/>
+      <c r="E87" s="66"/>
     </row>
     <row r="88" spans="1:5">
-      <c r="B88" s="66" t="s">
+      <c r="B88" s="64" t="s">
         <v>195</v>
       </c>
-      <c r="C88" s="66"/>
-      <c r="D88" s="66"/>
-      <c r="E88" s="66"/>
+      <c r="C88" s="64"/>
+      <c r="D88" s="64"/>
+      <c r="E88" s="64"/>
     </row>
     <row r="89" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B89" s="64" t="s">
+      <c r="B89" s="65" t="s">
         <v>194</v>
       </c>
-      <c r="C89" s="64"/>
-      <c r="D89" s="64"/>
-      <c r="E89" s="64"/>
+      <c r="C89" s="65"/>
+      <c r="D89" s="65"/>
+      <c r="E89" s="65"/>
     </row>
     <row r="90" spans="1:5">
-      <c r="B90" s="64" t="s">
-        <v>229</v>
-      </c>
-      <c r="C90" s="64"/>
-      <c r="D90" s="64"/>
-      <c r="E90" s="64"/>
+      <c r="B90" s="65" t="s">
+        <v>228</v>
+      </c>
+      <c r="C90" s="65"/>
+      <c r="D90" s="65"/>
+      <c r="E90" s="65"/>
     </row>
     <row r="92" spans="1:5">
       <c r="B92" s="24" t="s">
@@ -2894,37 +2894,37 @@
     </row>
     <row r="98" spans="1:5">
       <c r="B98" s="24" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="B99" s="67" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="99" spans="1:5">
-      <c r="B99" s="65" t="s">
-        <v>223</v>
-      </c>
-      <c r="C99" s="65"/>
-      <c r="D99" s="65"/>
-      <c r="E99" s="65"/>
+      <c r="C99" s="67"/>
+      <c r="D99" s="67"/>
+      <c r="E99" s="67"/>
     </row>
     <row r="101" spans="1:5">
       <c r="B101" s="24" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="12.4">
-      <c r="B102" s="65" t="s">
-        <v>224</v>
-      </c>
-      <c r="C102" s="65"/>
-      <c r="D102" s="65"/>
-      <c r="E102" s="65"/>
+      <c r="B102" s="67" t="s">
+        <v>223</v>
+      </c>
+      <c r="C102" s="67"/>
+      <c r="D102" s="67"/>
+      <c r="E102" s="67"/>
     </row>
     <row r="103" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B103" s="64" t="s">
+      <c r="B103" s="65" t="s">
         <v>215</v>
       </c>
-      <c r="C103" s="64"/>
-      <c r="D103" s="64"/>
-      <c r="E103" s="64"/>
+      <c r="C103" s="65"/>
+      <c r="D103" s="65"/>
+      <c r="E103" s="65"/>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="28" t="s">
@@ -2951,7 +2951,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="B110" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2972,20 +2972,20 @@
         <v>181</v>
       </c>
       <c r="C114" s="44">
-        <v>0.10199999999999999</v>
+        <v>0.13</v>
       </c>
       <c r="D114" s="62" t="str">
-        <f>IF(C114&lt;benchmark,"Warning: Return is lower than the Benchmark.")</f>
-        <v>Warning: Return is lower than the Benchmark.</v>
+        <f>IF(C114&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
+        <v/>
       </c>
     </row>
     <row r="116" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B116" s="64" t="s">
-        <v>217</v>
-      </c>
-      <c r="C116" s="64"/>
-      <c r="D116" s="64"/>
-      <c r="E116" s="64"/>
+      <c r="B116" s="65" t="s">
+        <v>229</v>
+      </c>
+      <c r="C116" s="65"/>
+      <c r="D116" s="65"/>
+      <c r="E116" s="65"/>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="21" t="s">
@@ -3018,6 +3018,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B116:E116"/>
+    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="B102:E102"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B90:E90"/>
     <mergeCell ref="B88:E88"/>
     <mergeCell ref="B73:E73"/>
     <mergeCell ref="B87:E87"/>
@@ -3027,12 +3033,6 @@
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B41:E41"/>
     <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B116:E116"/>
-    <mergeCell ref="B99:E99"/>
-    <mergeCell ref="B102:E102"/>
-    <mergeCell ref="B103:E103"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B90:E90"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3116,7 +3116,7 @@
         <v>62</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>8</v>
@@ -5743,15 +5743,15 @@
       <c r="B5" s="74" t="s">
         <v>108</v>
       </c>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="74" t="s">
         <v>109</v>
       </c>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D51AEC07-4EE0-4CA7-ACAF-E84B8CAB220C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BC3333-5B2A-4F36-BB10-7F3AAAFEF0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -497,31 +497,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Valuation Changes: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>IF the market annual return output by valuation model changes materially.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">Market Shifts: </t>
     </r>
     <r>
@@ -1495,6 +1470,31 @@
       <t>When the Projected Portfolio Return falls below the benchmark, it is due to overly conservative cash reserve settings or a lack of eligible opportunities. Manual corrective action is needed to address these issues.</t>
     </r>
     <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Valuation Changes: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>If the market annual return output by valuation model changes materially.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1950,17 +1950,17 @@
     <xf numFmtId="179" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2321,7 +2321,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="20" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2334,21 +2334,21 @@
       <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B4" s="65" t="s">
-        <v>208</v>
-      </c>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
+      <c r="B4" s="64" t="s">
+        <v>207</v>
+      </c>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
     </row>
     <row r="5" spans="1:5">
       <c r="B5" s="24" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" s="24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2356,17 +2356,17 @@
         <v>66</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C8" s="62"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="B9" s="65" t="s">
-        <v>220</v>
-      </c>
-      <c r="C9" s="65"/>
-      <c r="D9" s="65"/>
-      <c r="E9" s="65"/>
+      <c r="B9" s="64" t="s">
+        <v>219</v>
+      </c>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
     </row>
     <row r="11" spans="1:5">
       <c r="B11" s="23" t="s">
@@ -2402,26 +2402,26 @@
     </row>
     <row r="16" spans="1:5">
       <c r="B16" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>216</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="B17" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="B18" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2431,7 +2431,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="B21" s="24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2441,7 +2441,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="B23" s="24" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2449,18 +2449,18 @@
         <v>67</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C25" s="62"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="18"/>
-      <c r="B26" s="65" t="s">
-        <v>214</v>
-      </c>
-      <c r="C26" s="65"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
+      <c r="B26" s="64" t="s">
+        <v>213</v>
+      </c>
+      <c r="C26" s="64"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="64"/>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="18"/>
@@ -2468,10 +2468,10 @@
     <row r="28" spans="1:5">
       <c r="A28" s="18"/>
       <c r="B28" s="51" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C28" s="51" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2492,15 +2492,15 @@
     </row>
     <row r="32" spans="1:5">
       <c r="B32" s="51" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C32" s="51" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="B33" s="26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C33" s="60">
         <f>C29-C34</f>
@@ -2509,7 +2509,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="B34" s="26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C34" s="59">
         <v>1</v>
@@ -2554,24 +2554,24 @@
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="B41" s="65" t="s">
-        <v>158</v>
-      </c>
-      <c r="C41" s="65"/>
-      <c r="D41" s="65"/>
-      <c r="E41" s="65"/>
+      <c r="B41" s="64" t="s">
+        <v>157</v>
+      </c>
+      <c r="C41" s="64"/>
+      <c r="D41" s="64"/>
+      <c r="E41" s="64"/>
     </row>
     <row r="42" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B42" s="65" t="s">
+      <c r="B42" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="C42" s="65"/>
-      <c r="D42" s="65"/>
-      <c r="E42" s="65"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
@@ -2579,12 +2579,12 @@
       <c r="E44" s="21"/>
     </row>
     <row r="46" spans="1:5">
-      <c r="B46" s="65" t="s">
-        <v>218</v>
-      </c>
-      <c r="C46" s="65"/>
-      <c r="D46" s="65"/>
-      <c r="E46" s="65"/>
+      <c r="B46" s="64" t="s">
+        <v>217</v>
+      </c>
+      <c r="C46" s="64"/>
+      <c r="D46" s="64"/>
+      <c r="E46" s="64"/>
     </row>
     <row r="48" spans="1:5">
       <c r="B48" s="23" t="s">
@@ -2596,7 +2596,7 @@
         <v>94</v>
       </c>
       <c r="C50" s="51" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D50" s="57"/>
       <c r="E50" s="57"/>
@@ -2629,7 +2629,7 @@
         <v>0.2</v>
       </c>
       <c r="D53" s="63" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E53" s="56"/>
     </row>
@@ -2719,7 +2719,7 @@
     </row>
     <row r="63" spans="2:5" ht="12" thickBot="1">
       <c r="D63" s="42" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E63" s="43">
         <f>IF(E62&lt;=2,C51,IF(E62&gt;=6,C53,C52))</f>
@@ -2729,12 +2729,12 @@
     <row r="64" spans="2:5" ht="12" thickTop="1"/>
     <row r="65" spans="1:5">
       <c r="B65" s="23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="B66" s="54" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C66" s="55">
         <f>-E63*(C37-Cash_Yield)</f>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="B67" s="54" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C67" s="55">
         <f>C37+C66</f>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="B69" s="39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2769,223 +2769,223 @@
       <c r="E71" s="21"/>
     </row>
     <row r="73" spans="1:5">
-      <c r="B73" s="65" t="s">
-        <v>201</v>
-      </c>
-      <c r="C73" s="65"/>
-      <c r="D73" s="65"/>
-      <c r="E73" s="65"/>
+      <c r="B73" s="64" t="s">
+        <v>200</v>
+      </c>
+      <c r="C73" s="64"/>
+      <c r="D73" s="64"/>
+      <c r="E73" s="64"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="28" t="s">
         <v>66</v>
       </c>
       <c r="B75" s="20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="B76" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="B77" s="24" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="28" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B79" s="20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="B80" s="39" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="B81" s="24" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="B82" s="24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="B83" s="24" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="28" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B85" s="20" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="B86" s="24" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="B87" s="67" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="B87" s="66" t="s">
-        <v>197</v>
-      </c>
-      <c r="C87" s="66"/>
-      <c r="D87" s="66"/>
-      <c r="E87" s="66"/>
+      <c r="C87" s="67"/>
+      <c r="D87" s="67"/>
+      <c r="E87" s="67"/>
     </row>
     <row r="88" spans="1:5">
-      <c r="B88" s="64" t="s">
-        <v>195</v>
-      </c>
-      <c r="C88" s="64"/>
-      <c r="D88" s="64"/>
-      <c r="E88" s="64"/>
+      <c r="B88" s="66" t="s">
+        <v>194</v>
+      </c>
+      <c r="C88" s="66"/>
+      <c r="D88" s="66"/>
+      <c r="E88" s="66"/>
     </row>
     <row r="89" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B89" s="65" t="s">
-        <v>194</v>
-      </c>
-      <c r="C89" s="65"/>
-      <c r="D89" s="65"/>
-      <c r="E89" s="65"/>
+      <c r="B89" s="64" t="s">
+        <v>193</v>
+      </c>
+      <c r="C89" s="64"/>
+      <c r="D89" s="64"/>
+      <c r="E89" s="64"/>
     </row>
     <row r="90" spans="1:5">
-      <c r="B90" s="65" t="s">
-        <v>228</v>
-      </c>
-      <c r="C90" s="65"/>
-      <c r="D90" s="65"/>
-      <c r="E90" s="65"/>
+      <c r="B90" s="64" t="s">
+        <v>227</v>
+      </c>
+      <c r="C90" s="64"/>
+      <c r="D90" s="64"/>
+      <c r="E90" s="64"/>
     </row>
     <row r="92" spans="1:5">
       <c r="B92" s="24" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="B93" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="B94" s="61" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="B95" s="24" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="B96" s="24" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="B98" s="24" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="B99" s="65" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="99" spans="1:5">
-      <c r="B99" s="67" t="s">
-        <v>222</v>
-      </c>
-      <c r="C99" s="67"/>
-      <c r="D99" s="67"/>
-      <c r="E99" s="67"/>
+      <c r="C99" s="65"/>
+      <c r="D99" s="65"/>
+      <c r="E99" s="65"/>
     </row>
     <row r="101" spans="1:5">
       <c r="B101" s="24" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="12.4">
-      <c r="B102" s="67" t="s">
-        <v>223</v>
-      </c>
-      <c r="C102" s="67"/>
-      <c r="D102" s="67"/>
-      <c r="E102" s="67"/>
+      <c r="B102" s="65" t="s">
+        <v>222</v>
+      </c>
+      <c r="C102" s="65"/>
+      <c r="D102" s="65"/>
+      <c r="E102" s="65"/>
     </row>
     <row r="103" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B103" s="65" t="s">
-        <v>215</v>
-      </c>
-      <c r="C103" s="65"/>
-      <c r="D103" s="65"/>
-      <c r="E103" s="65"/>
+      <c r="B103" s="64" t="s">
+        <v>214</v>
+      </c>
+      <c r="C103" s="64"/>
+      <c r="D103" s="64"/>
+      <c r="E103" s="64"/>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="28" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B105" s="20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="B106" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="B107" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="B109" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="B110" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="B112" s="23" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="B113" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C113" s="44">
-        <v>0.4</v>
+        <v>0.5490782759805124</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="B114" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C114" s="44">
-        <v>0.13</v>
+        <v>8.956135035007412E-2</v>
       </c>
       <c r="D114" s="62" t="str">
         <f>IF(C114&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
-        <v/>
+        <v>Warning: Return is lower than the Benchmark.</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B116" s="65" t="s">
-        <v>229</v>
-      </c>
-      <c r="C116" s="65"/>
-      <c r="D116" s="65"/>
-      <c r="E116" s="65"/>
+      <c r="B116" s="64" t="s">
+        <v>228</v>
+      </c>
+      <c r="C116" s="64"/>
+      <c r="D116" s="64"/>
+      <c r="E116" s="64"/>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="21" t="s">
@@ -3008,22 +3008,16 @@
     </row>
     <row r="122" spans="1:5">
       <c r="B122" s="24" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="B123" s="24" t="s">
-        <v>100</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B116:E116"/>
-    <mergeCell ref="B99:E99"/>
-    <mergeCell ref="B102:E102"/>
-    <mergeCell ref="B103:E103"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B90:E90"/>
     <mergeCell ref="B88:E88"/>
     <mergeCell ref="B73:E73"/>
     <mergeCell ref="B87:E87"/>
@@ -3033,6 +3027,12 @@
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B41:E41"/>
     <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B116:E116"/>
+    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="B102:E102"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B90:E90"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3074,7 +3074,7 @@
       <c r="E1" s="71"/>
       <c r="F1" s="71"/>
       <c r="G1" s="72" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H1" s="72"/>
       <c r="I1" s="72"/>
@@ -3116,7 +3116,7 @@
         <v>62</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>8</v>
@@ -3145,30 +3145,30 @@
     </row>
     <row r="3" spans="1:17">
       <c r="B3" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="D3" s="2">
+        <v>15.4</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="D3" s="2">
-        <v>14.94</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>164</v>
-      </c>
       <c r="F3" s="15">
-        <v>0.19401142226230528</v>
+        <v>0.18108249888642258</v>
       </c>
       <c r="G3" s="15">
-        <f t="shared" ref="G3:G5" si="0">F3 - $C$10</f>
-        <v>0.19401142226230528</v>
+        <f t="shared" ref="G3:G5" si="0">F3 - $C$12</f>
+        <v>0.18108249888642258</v>
       </c>
       <c r="H3" s="15">
-        <f t="shared" ref="H3:H5" si="1">F3 - $C$11</f>
-        <v>0.19401142226230528</v>
+        <f t="shared" ref="H3:H5" si="1">F3 - $C$13</f>
+        <v>0.18108249888642258</v>
       </c>
       <c r="I3" s="15">
-        <v>0.3</v>
+        <v>0.27162374832963387</v>
       </c>
       <c r="J3" s="2">
         <v>14.733437767356989</v>
@@ -3177,50 +3177,50 @@
         <v>20.508980461992877</v>
       </c>
       <c r="L3" s="4">
-        <v>0.11566171481724427</v>
+        <v>0.11220688437465126</v>
       </c>
       <c r="M3" s="4">
-        <v>9.1030789825970557E-2</v>
+        <v>8.8311688311688313E-2</v>
       </c>
       <c r="N3" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="O3" s="11" t="s">
         <v>165</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>166</v>
       </c>
       <c r="P3" s="14">
         <v>45716</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="B4" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>169</v>
-      </c>
       <c r="D4" s="2">
-        <v>7.77</v>
+        <v>7.88</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F4" s="15">
-        <v>0.12514862916378067</v>
+        <v>0.11953198379323582</v>
       </c>
       <c r="G4" s="15">
         <f t="shared" si="0"/>
-        <v>0.12514862916378067</v>
+        <v>0.11953198379323582</v>
       </c>
       <c r="H4" s="15">
         <f t="shared" si="1"/>
-        <v>0.12514862916378067</v>
+        <v>0.11953198379323582</v>
       </c>
       <c r="I4" s="15">
-        <v>3.674075125745891E-2</v>
+        <v>0.17929797568985373</v>
       </c>
       <c r="J4" s="2">
         <v>6.4883606756817951</v>
@@ -3229,74 +3229,74 @@
         <v>9.1006872475781417</v>
       </c>
       <c r="L4" s="4">
-        <v>3.975526022937774E-2</v>
+        <v>3.9200301012977792E-2</v>
       </c>
       <c r="M4" s="4">
-        <v>7.4646074646074645E-2</v>
+        <v>7.3604060913705582E-2</v>
       </c>
       <c r="N4" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="O4" s="11" t="s">
         <v>170</v>
-      </c>
-      <c r="O4" s="11" t="s">
-        <v>171</v>
       </c>
       <c r="P4" s="14">
         <v>45716</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="B5" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>172</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>173</v>
       </c>
       <c r="D5" s="2">
         <v>2.15</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F5" s="15">
-        <v>6.9019080849287207E-2</v>
+        <v>6.6927308782200656E-2</v>
       </c>
       <c r="G5" s="15">
         <f t="shared" si="0"/>
-        <v>6.9019080849287207E-2</v>
+        <v>6.6927308782200656E-2</v>
       </c>
       <c r="H5" s="15">
         <f t="shared" si="1"/>
-        <v>6.9019080849287207E-2</v>
+        <v>6.6927308782200656E-2</v>
       </c>
       <c r="I5" s="15">
         <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>1.5492157922151617</v>
+        <v>1.5407576206248625</v>
       </c>
       <c r="K5" s="2">
-        <v>2.2482528889477993</v>
+        <v>2.2336371684397625</v>
       </c>
       <c r="L5" s="4">
-        <v>2.1918414948495051E-2</v>
+        <v>2.1775925005107808E-2</v>
       </c>
       <c r="M5" s="4">
         <v>5.4790697674418611E-2</v>
       </c>
       <c r="N5" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="O5" s="11" t="s">
         <v>174</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>175</v>
       </c>
       <c r="P5" s="14">
         <v>45716</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -5456,7 +5456,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="20" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5530,7 +5530,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="1">
-        <v>4.3799999999999999E-2</v>
+        <v>4.1700000000000001E-2</v>
       </c>
       <c r="D8" s="1">
         <v>7.4999999999999997E-2</v>
@@ -5723,162 +5723,162 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="B3" s="73" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C3" s="73"/>
       <c r="D3" s="73"/>
     </row>
     <row r="5" spans="1:4">
       <c r="B5" s="74" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
+        <v>107</v>
+      </c>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="74" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
+        <v>108</v>
+      </c>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5"/>
       <c r="B10" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="B11" s="73" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C11" s="73"/>
       <c r="D11" s="73"/>
     </row>
     <row r="12" spans="1:4">
       <c r="B12" s="73" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C12" s="73"/>
       <c r="D12" s="73"/>
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="12.4">
       <c r="B16" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="30" t="s">
         <v>121</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="B17" s="26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="B18" s="26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="B19" s="26" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="B20" s="26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="B21" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="C21" s="26" t="s">
         <v>136</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="B22" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22" s="26" t="s">
         <v>138</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="B23" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="C23" s="26" t="s">
         <v>140</v>
-      </c>
-      <c r="C23" s="26" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="B24" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="C24" s="26" t="s">
         <v>145</v>
-      </c>
-      <c r="C24" s="26" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="B25" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" s="26" t="s">
         <v>142</v>
-      </c>
-      <c r="C25" s="26" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="5"/>
       <c r="B27" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="B28" s="73" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C28" s="73"/>
       <c r="D28" s="73"/>
     </row>
     <row r="29" spans="1:4">
       <c r="B29" s="73" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C29" s="73"/>
       <c r="D29" s="73"/>
@@ -5886,7 +5886,7 @@
     <row r="31" spans="1:4">
       <c r="A31" s="5"/>
       <c r="B31" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -5894,46 +5894,46 @@
         <v>66</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="B33" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="28" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="B36" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="5"/>
       <c r="B38" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="B39" s="24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="B40" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="B41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BC3333-5B2A-4F36-BB10-7F3AAAFEF0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F9D479-E743-4414-8791-0EF185DCBC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,15 +21,15 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Opportunities!$B$2:$Q$2</definedName>
-    <definedName name="benchmark">Portfolio_Mgmt!$C$12</definedName>
-    <definedName name="Cash_Yield">Portfolio_Mgmt!$C$13</definedName>
+    <definedName name="benchmark">Portfolio_Mgmt!$C$10</definedName>
+    <definedName name="Cash_Yield">Portfolio_Mgmt!$C$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="228">
   <si>
     <t>Name</t>
   </si>
@@ -395,6 +395,945 @@
   <si>
     <t>Notes:</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Indicators and Scoring:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Score &lt;= 2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Score 3–5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Score &gt;= 6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cash Allocation Rule:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scenario</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicator	</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Low Risk Appetite (Hold Cash)</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>High Risk Appetite (Deploy Cash)</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Score (0-2)</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>New Opportunities:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> If new investments have higher ERB than current holdings, replace underperformers.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Market Shifts: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>If market cycle indicators change significantly, reassess the Risk Appetite Score.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- Only investments with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>the Selected Flag</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> are eligible for portfolio allocation.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Portfolio Management</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Guidance Note: Comparison Group Classification System</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Overview</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The classification uses two mutually exclusive and collectively exhaustive (MECE) layers:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Format: [Layer 1 Code]_[Layer 2 Number] (e.g., TMT_02, CNS_10).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Layer 1: Broad industry categories (3-character codes).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Layer 2: Granular subcategories (two-digit numbers, 01–99).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Layer 1: Broad Industry Categories</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Purpose: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Group investments by overarching industries.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Structure: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3-character codes (e.g., TMT, CNS, FIN).</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TMT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FIN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HLT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Technology, Media, Telecom</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Consumer</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Financials</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Healthcare</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Code</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Industry</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Layer 2: Subcategory Numbering</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Purpose: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Refine peer groups into specific segments within Layer 1 industries.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Purpose: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Two-digit numbers (01–99), appended to Layer 1 codes (e.g., TMT_01).</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assigning Classifications</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Identify Layer 1:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map the investment to the broadest applicable industry (e.g., a fintech firm → FIN).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assign Layer 2:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ii.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Select the most specific subcategory number (e.g., fintech → FIN_10).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use Cases</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Peer Benchmarking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Compare HLT_03 (Biotech) companies against each other.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Portfolio Analysis:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Aggregate exposures by Layer 1 (e.g., “30% of portfolio is in TMT”).</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Reporting:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Standardize disclosures using codes (e.g., “Investment X (CNS_05) outperformed peers”).</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IND</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Industrials</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ENG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Energy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MAT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Materials</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UTL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Utilities</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>9 Standard Industry Codes:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RES</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Real Estate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Yields Tracker</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>iii.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>High Growth</t>
+  </si>
+  <si>
+    <t>Cap</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Negative or Low Growth</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>= R_i - Benchmark Return</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>= R_i - Cash Yield</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Excess Return over Benchmark (ERB_i)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Excess Return over Cash (ERC_i)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Portfolio Limits</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Growth Classification Limits</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Target Annual Return</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: The target return reflects the investor’s hurdle rate over the lock-up period.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Key Outputs:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>0590.HK</t>
+  </si>
+  <si>
+    <t>六福珠宝</t>
+  </si>
+  <si>
+    <t>HKD</t>
+  </si>
+  <si>
+    <t>CNS_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low Growth </t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>0083.HK</t>
+  </si>
+  <si>
+    <t>SINO LAND</t>
+  </si>
+  <si>
+    <t>RES_01</t>
+  </si>
+  <si>
+    <t>Negative Growth Asset Play</t>
+  </si>
+  <si>
+    <t>6601.HK</t>
+  </si>
+  <si>
+    <t>朝云集团</t>
+  </si>
+  <si>
+    <t>CNS_04</t>
+  </si>
+  <si>
+    <t>Low Growth Asset Play</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Portfolio Management Plan</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Opportunity Cost</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Portfolio Return</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Projected Cash %</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Projected Portfolio Return</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Find Eligible Investments (Data Cleaning)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Display Investment Opportunities (Data Preparation)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Filters:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Retain investments with Selected Flag = True and ERB &gt; 0.</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Enforce Maximum Number of Holdings and Growth Classification Limits.</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Logic:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>- If R_i &lt; Target Annual Return: Penalty proportional to the shortfall.</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Portfolio Management Output</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>iv.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. Projected Portfolio Return:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 1: Determine Risk Appetite &amp; Cash Reserve</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- If no eligible investments exist, Set Projected Cash % = 100% and Projected Portfolio Return = Cash Yield.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Single Investment Cap:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> If If an investment’s provisional allocation exceeds the cap, set its allocation to the cap. Excess weight is moved to cash (do not redistribute to other investments).</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Provisional Weight:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>provisional_weight_i = Single Investment Cap, for each eligible investment i with ERB&gt;0.</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Δweight_i = MAX(0, (Target Annual Return - R_i)/Target Annual Return)</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. Δweight Adjustment:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>- If R_i &gt;= Target Annual Return: Δweight_i = 0</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Purpose:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Given current market price, how much should be allocated to each eligible investments.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Minimium Cash Reserve %</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cost of the Minimium Cash Reserve when all investments are earning Targeting Annual Return</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Min. Cash Reserve</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Projected Cash Reserve %:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Projected Cash Reserve % = 1 - allocated_weight </t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Opportunity Cost = Minimium Cash Reserve % × (Target Annual Return - Cash Yield)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Diversification Rules</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Benchmarks</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- Cash reserve is determined by </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Risk Appetite Score (Step 1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Portfolio Allocation (Step 2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Annual Return (R_i)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Imported from Valuation models to Opportunities Sheet</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Process: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Calculate a Risk Appetite Score (0–8 scale) using four market indicators to set cash reserves.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Objective: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Determine the optimal capital allocation at current market prices, while reserving capital for strategic deployment.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. Allocation Weight:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>allocation_weight_i = provisional_weight_i * (1-Δweight_i)</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>allocated_weight = Σ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>allocation_weight_i)</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Return = Σ(allocation_weight_i× R_i) + (Projected Cash % × Cash Yield)</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Allocation Weight</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. Total Allocated Weight:</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Calculate Allocation Weight (Data Processing)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>When the Projected Portfolio Return falls below the benchmark, it is due to overly conservative cash reserve settings or a lack of eligible opportunities. Manual corrective action is needed to address these issues.</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Valuation Changes: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>If the market annual return output by valuation model changes materially.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Note on Allocation: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>The allocation process prioritizes higher return potential relative to the benchmark. Eligible investments (meeting criteria in Step 2.ii) are ranked by ERB (descending). Capital is allocated sequentially down this ranked list. Each investment receives its calculated `allocation_weight_i` (from Step iii.3) until the total investable capital (100% - Minimum Cash Reserve % from Step 1) is exhausted. Lower-ranked investments may receive partial allocation (only the remaining capital) or no allocation if capital runs out before they are reached.</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -416,469 +1355,9 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>: Reflects the company’s risk profile and provides a consistent discount rate for valuations. Using a uniform cost of equity eliminates volatile and subjective inputs, ensuring conservative discounting of FCF and reducing downside risk.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Indicators and Scoring:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Score &lt;= 2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Score 3–5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Score &gt;= 6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cash Allocation Rule:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Scenario</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Indicator	</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Low Risk Appetite (Hold Cash)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>High Risk Appetite (Deploy Cash)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Score (0-2)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>New Opportunities:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> If new investments have higher ERB than current holdings, replace underperformers.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Market Shifts: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>If market cycle indicators change significantly, reassess the Risk Appetite Score.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">- Only investments with </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>the Selected Flag</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> are eligible for portfolio allocation.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Portfolio Management</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Guidance Note: Comparison Group Classification System</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Overview</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>The classification uses two mutually exclusive and collectively exhaustive (MECE) layers:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Format: [Layer 1 Code]_[Layer 2 Number] (e.g., TMT_02, CNS_10).</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>- Layer 1: Broad industry categories (3-character codes).</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>- Layer 2: Granular subcategories (two-digit numbers, 01–99).</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Layer 1: Broad Industry Categories</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Purpose: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Group investments by overarching industries.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Structure: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>3-character codes (e.g., TMT, CNS, FIN).</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>TMT</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CNS</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>FIN</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HLT</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Technology, Media, Telecom</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Consumer</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Financials</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Healthcare</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Code</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Industry</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Layer 2: Subcategory Numbering</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Purpose: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Refine peer groups into specific segments within Layer 1 industries.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Purpose: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Two-digit numbers (01–99), appended to Layer 1 codes (e.g., TMT_01).</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assigning Classifications</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Identify Layer 1:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Map the investment to the broadest applicable industry (e.g., a fintech firm → FIN).</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assign Layer 2:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ii.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Select the most specific subcategory number (e.g., fintech → FIN_10).</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Use Cases</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Peer Benchmarking:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Compare HLT_03 (Biotech) companies against each other.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Portfolio Analysis:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Aggregate exposures by Layer 1 (e.g., “30% of portfolio is in TMT”).</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Reporting:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Standardize disclosures using codes (e.g., “Investment X (CNS_05) outperformed peers”).</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>IND</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Industrials</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ENG</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Energy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAT</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Materials</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>UTL</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Utilities</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>9 Standard Industry Codes:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>RES</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Real Estate</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Yields Tracker</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>iii.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>High Growth</t>
-  </si>
-  <si>
-    <t>Cap</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Negative or Low Growth</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>= R_i - Benchmark Return</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>= R_i - Cash Yield</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Excess Return over Benchmark (ERB_i)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Excess Return over Cash (ERC_i)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Portfolio Limits</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Growth Classification Limits</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+      <t>: This plan adopts a value investing perspective, viewing true risk as the potential for permanent capital loss arising from deteriorating business fundamentals or paying too high a price, rather than short-term market price volatility (beta). Consistent with this, a uniform Base Cost of Equity is applied to all potential investments. This rate represents the minimum acceptable long-term return required for committing capital to any equity holding in this portfolio, reflecting long-term risk-free rates plus a required premium for taking on general business ownership risk.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -890,7 +1369,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Target Annual Return</t>
+      <t xml:space="preserve">Objective: </t>
     </r>
     <r>
       <rPr>
@@ -900,240 +1379,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>: The target return reflects the investor’s hurdle rate over the lock-up period.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>- Display all opportunities in the Opportunities Sheet, irrespective of ERB or Selected Flag</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>- Sort eligible investments by ERB (descending)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Key Outputs:</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>0590.HK</t>
-  </si>
-  <si>
-    <t>六福珠宝</t>
-  </si>
-  <si>
-    <t>HKD</t>
-  </si>
-  <si>
-    <t>CNS_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low Growth </t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>0083.HK</t>
-  </si>
-  <si>
-    <t>SINO LAND</t>
-  </si>
-  <si>
-    <t>RES_01</t>
-  </si>
-  <si>
-    <t>Negative Growth Asset Play</t>
-  </si>
-  <si>
-    <t>6601.HK</t>
-  </si>
-  <si>
-    <t>朝云集团</t>
-  </si>
-  <si>
-    <t>CNS_04</t>
-  </si>
-  <si>
-    <t>Low Growth Asset Play</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Portfolio Management Plan</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Opportunity Cost</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Portfolio Return</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Projected Cash %</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Projected Portfolio Return</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Find Eligible Investments (Data Cleaning)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Display Investment Opportunities (Data Preparation)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Filters:</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>- Retain investments with Selected Flag = True and ERB &gt; 0.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>- Enforce Maximum Number of Holdings and Growth Classification Limits.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Logic:</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>- If R_i &lt; Target Annual Return: Penalty proportional to the shortfall.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Portfolio Management Output</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>iv.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2. Projected Portfolio Return:</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 1: Determine Risk Appetite &amp; Cash Reserve</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>- If no eligible investments exist, Set Projected Cash % = 100% and Projected Portfolio Return = Cash Yield.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Single Investment Cap:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> If If an investment’s provisional allocation exceeds the cap, set its allocation to the cap. Excess weight is moved to cash (do not redistribute to other investments).</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Note:</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. Provisional Weight:</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>provisional_weight_i = Single Investment Cap, for each eligible investment i with ERB&gt;0.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Δweight_i = MAX(0, (Target Annual Return - R_i)/Target Annual Return)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>2. Δweight Adjustment:</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>- If R_i &gt;= Target Annual Return: Δweight_i = 0</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Purpose:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Given current market price, how much should be allocated to each eligible investments.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Minimium Cash Reserve %</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cost of the Minimium Cash Reserve when all investments are earning Targeting Annual Return</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Min. Cash Reserve</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. Projected Cash Reserve %:</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Projected Cash Reserve % = 1 - allocated_weight </t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Note: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Opportunity Cost = Minimium Cash Reserve % × (Target Annual Return - Cash Yield)</t>
+      <t>Balance high-conviction bets with diversification rules.</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1157,110 +1403,20 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>This plan deploys capital into investments exceeding the benchmark return while strategically reserving cash for future opportunities. Risk is managed through:</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Timing Risk:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Invest only when returns justify risk.</t>
-    </r>
+      <t>This plan deploys capital into investments exceeding the benchmark return while strategically reserving cash for future opportunities.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strategic reserve for compelling opportunities.</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Concentration/Diversification:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Balance high-conviction bets with diversification rules.</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Diversification Rules</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Benchmarks</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">- Cash reserve is determined by </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Risk Appetite Score (Step 1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Portfolio Allocation (Step 2)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
+    <t>- Display all opportunities, regardless of ERB or Selected Flag, for full visibility.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Sort all potential investments by ERB (descending) in the Opportunities Sheet.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1273,7 +1429,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Objective: </t>
+      <t>Capital Constraints:</t>
     </r>
     <r>
       <rPr>
@@ -1283,218 +1439,9 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Maximize returns while adhering to risk limits.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Note: When allocated_weight &gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei UI"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>investable capital</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>, then investments are ranked by ERB and allocated until investable capital is exhausted.</t>
+      <t xml:space="preserve"> This step calculates the desired weight for each eligible investment before considering capital constraints</t>
     </r>
     <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Annual Return (R_i)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Imported from Valuation models to Opportunities Sheet</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Process: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Calculate a Risk Appetite Score (0–8 scale) using four market indicators to set cash reserves.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Strategic reserve for strategic opportunities.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Objective: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Determine the optimal capital allocation at current market prices, while reserving capital for strategic deployment.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3. Allocation Weight:</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>allocation_weight_i = provisional_weight_i * (1-Δweight_i)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>allocated_weight = Σ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei UI"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>allocation_weight_i)</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Return = Σ(allocation_weight_i× R_i) + (Projected Cash % × Cash Yield)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Allocation Weight</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>4. Total Allocated Weight:</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Calculate Allocation Weight (Data Processing)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Total investable capital Consideration:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> This issue will be resolved at processing the Total Allocated Weight.</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Note: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>When the Projected Portfolio Return falls below the benchmark, it is due to overly conservative cash reserve settings or a lack of eligible opportunities. Manual corrective action is needed to address these issues.</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Valuation Changes: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>If the market annual return output by valuation model changes materially.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1508,7 +1455,7 @@
     <numFmt numFmtId="179" formatCode="#,##0.00_);\(#,##0.00\)"/>
     <numFmt numFmtId="180" formatCode="#,##0_);\(#,##0\)"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1672,14 +1619,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Microsoft YaHei UI"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Microsoft YaHei UI"/>
@@ -1947,7 +1886,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="179" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2309,7 +2248,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:E121"/>
   <sheetFormatPr defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
@@ -2321,7 +2260,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="20" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2335,332 +2274,350 @@
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
       <c r="B4" s="64" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C4" s="64"/>
       <c r="D4" s="64"/>
       <c r="E4" s="64"/>
     </row>
-    <row r="5" spans="1:5">
-      <c r="B5" s="24" t="s">
-        <v>208</v>
-      </c>
-    </row>
     <row r="6" spans="1:5">
-      <c r="B6" s="24" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="20" t="s">
+      <c r="A6" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="C8" s="62"/>
+      <c r="B6" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="C6" s="62"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7" s="64" t="s">
+        <v>210</v>
+      </c>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="B9" s="64" t="s">
-        <v>219</v>
-      </c>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="B11" s="23" t="s">
+      <c r="B9" s="23" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="B12" s="1" t="s">
+    <row r="10" spans="1:5">
+      <c r="B10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="47">
+      <c r="C10" s="47">
         <f>Market_Yield!C16</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="B13" s="1" t="s">
+    <row r="11" spans="1:5">
+      <c r="B11" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="47">
+      <c r="C11" s="47">
         <f>Market_Yield!C6</f>
         <v>3.4500000000000003E-2</v>
       </c>
     </row>
+    <row r="12" spans="1:5">
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="B13" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="4"/>
+    </row>
     <row r="14" spans="1:5">
-      <c r="C14" s="4"/>
+      <c r="B14" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="B15" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="4"/>
+      <c r="B15" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="16" spans="1:5">
       <c r="B16" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="B17" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C16" s="24" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="B18" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>152</v>
+      <c r="B18" s="23" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="B19" s="24" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="B20" s="23" t="s">
-        <v>60</v>
+      <c r="B20" s="24" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="B21" s="24" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="B22" s="24" t="s">
-        <v>85</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="B23" s="24" t="s">
-        <v>212</v>
-      </c>
+      <c r="A23" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="C23" s="62"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="18"/>
+      <c r="B24" s="64" t="s">
+        <v>222</v>
+      </c>
+      <c r="C24" s="64"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="64"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="C25" s="62"/>
+      <c r="A25" s="18"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="18"/>
-      <c r="B26" s="64" t="s">
-        <v>213</v>
-      </c>
-      <c r="C26" s="64"/>
-      <c r="D26" s="64"/>
-      <c r="E26" s="64"/>
+      <c r="B26" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="18"/>
+      <c r="B27" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="52">
+        <v>6</v>
+      </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="18"/>
-      <c r="B28" s="51" t="s">
+      <c r="B28" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="53">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="B30" s="51" t="s">
         <v>155</v>
       </c>
-      <c r="C28" s="51" t="s">
+      <c r="C30" s="51" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="B31" s="26" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="B29" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="C29" s="52">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="B30" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C30" s="53">
-        <v>0.3</v>
+      <c r="C31" s="60">
+        <f>C27-C32</f>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="B32" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="C32" s="51" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="B33" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="C33" s="60">
-        <f>C29-C34</f>
-        <v>5</v>
+      <c r="B32" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="C32" s="59">
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="B34" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="C34" s="59">
-        <v>1</v>
+      <c r="A34" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" s="62"/>
+      <c r="D34" s="22"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="B35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="48">
+        <v>0.2</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E35" s="50">
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="C36" s="62"/>
-      <c r="D36" s="22"/>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="B37" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" s="48">
-        <v>0.2</v>
-      </c>
-      <c r="D37" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="E37" s="50">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="B38" s="1" t="s">
+      <c r="B36" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C38" s="49">
+      <c r="C36" s="49">
         <f>MAX(8%,Market_Yield!C4:D6)</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
-      <c r="B40" s="20" t="s">
+    <row r="38" spans="1:5">
+      <c r="B38" s="20" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
-      <c r="B41" s="64" t="s">
-        <v>157</v>
-      </c>
-      <c r="C41" s="64"/>
-      <c r="D41" s="64"/>
-      <c r="E41" s="64"/>
-    </row>
-    <row r="42" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B42" s="64" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" s="64"/>
-      <c r="D42" s="64"/>
-      <c r="E42" s="64"/>
+    <row r="39" spans="1:5">
+      <c r="B39" s="64" t="s">
+        <v>156</v>
+      </c>
+      <c r="C39" s="64"/>
+      <c r="D39" s="64"/>
+      <c r="E39" s="64"/>
+    </row>
+    <row r="40" spans="1:5" ht="58.5" customHeight="1">
+      <c r="B40" s="64" t="s">
+        <v>221</v>
+      </c>
+      <c r="C40" s="64"/>
+      <c r="D40" s="64"/>
+      <c r="E40" s="64"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="B44" s="21"/>
-      <c r="C44" s="21"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
+      <c r="B44" s="64" t="s">
+        <v>209</v>
+      </c>
+      <c r="C44" s="64"/>
+      <c r="D44" s="64"/>
+      <c r="E44" s="64"/>
     </row>
     <row r="46" spans="1:5">
-      <c r="B46" s="64" t="s">
-        <v>217</v>
-      </c>
-      <c r="C46" s="64"/>
-      <c r="D46" s="64"/>
-      <c r="E46" s="64"/>
+      <c r="B46" s="23" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="B48" s="23" t="s">
+      <c r="B48" s="51" t="s">
         <v>93</v>
       </c>
+      <c r="C48" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="D48" s="57"/>
+      <c r="E48" s="57"/>
+    </row>
+    <row r="49" spans="2:5">
+      <c r="B49" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="C49" s="29">
+        <v>0.5</v>
+      </c>
+      <c r="D49" s="58"/>
+      <c r="E49" s="56"/>
     </row>
     <row r="50" spans="2:5">
-      <c r="B50" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="C50" s="51" t="s">
-        <v>203</v>
-      </c>
-      <c r="D50" s="57"/>
-      <c r="E50" s="57"/>
+      <c r="B50" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C50" s="29">
+        <v>0.3</v>
+      </c>
+      <c r="D50" s="58"/>
+      <c r="E50" s="56"/>
     </row>
     <row r="51" spans="2:5">
       <c r="B51" s="26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C51" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="D51" s="58"/>
+        <v>0.2</v>
+      </c>
+      <c r="D51" s="63" t="s">
+        <v>224</v>
+      </c>
       <c r="E51" s="56"/>
     </row>
-    <row r="52" spans="2:5">
-      <c r="B52" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C52" s="29">
-        <v>0.3</v>
-      </c>
-      <c r="D52" s="58"/>
-      <c r="E52" s="56"/>
-    </row>
     <row r="53" spans="2:5">
-      <c r="B53" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="C53" s="29">
-        <v>0.2</v>
-      </c>
-      <c r="D53" s="63" t="s">
-        <v>218</v>
-      </c>
-      <c r="E53" s="56"/>
+      <c r="B53" s="23" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="55" spans="2:5">
-      <c r="B55" s="23" t="s">
-        <v>89</v>
+      <c r="B55" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="C55" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="D55" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="E55" s="51" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5">
+      <c r="B56" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C56" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D56" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="E56" s="41">
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:5">
-      <c r="B57" s="51" t="s">
-        <v>95</v>
-      </c>
-      <c r="C57" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="D57" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="E57" s="51" t="s">
-        <v>98</v>
+      <c r="B57" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C57" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D57" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="E57" s="41">
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="2:5">
       <c r="B58" s="26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D58" s="26" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E58" s="41">
         <v>1</v>
@@ -2668,371 +2625,343 @@
     </row>
     <row r="59" spans="2:5">
       <c r="B59" s="26" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D59" s="26" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E59" s="41">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="2:5">
-      <c r="B60" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="C60" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="D60" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="E60" s="41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="2:5">
-      <c r="B61" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="C61" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="D61" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="E61" s="41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="2:5">
-      <c r="D62" s="27" t="s">
+      <c r="D60" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="E62" s="40">
-        <f>SUM(E58:E61)</f>
+      <c r="E60" s="40">
+        <f>SUM(E56:E59)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="2:5" ht="12" thickBot="1">
-      <c r="D63" s="42" t="s">
-        <v>201</v>
-      </c>
-      <c r="E63" s="43">
-        <f>IF(E62&lt;=2,C51,IF(E62&gt;=6,C53,C52))</f>
+    <row r="61" spans="2:5" ht="12" thickBot="1">
+      <c r="D61" s="42" t="s">
+        <v>198</v>
+      </c>
+      <c r="E61" s="43">
+        <f>IF(E60&lt;=2,C49,IF(E60&gt;=6,C51,C50))</f>
         <v>0.3</v>
       </c>
     </row>
-    <row r="64" spans="2:5" ht="12" thickTop="1"/>
+    <row r="62" spans="2:5" ht="12" thickTop="1"/>
+    <row r="63" spans="2:5">
+      <c r="B63" s="23" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5">
+      <c r="B64" s="54" t="s">
+        <v>174</v>
+      </c>
+      <c r="C64" s="55">
+        <f>-E61*(C35-Cash_Yield)</f>
+        <v>-4.965E-2</v>
+      </c>
+    </row>
     <row r="65" spans="1:5">
-      <c r="B65" s="23" t="s">
-        <v>202</v>
+      <c r="B65" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="C65" s="55">
+        <f>C35+C64</f>
+        <v>0.15035000000000001</v>
       </c>
     </row>
     <row r="66" spans="1:5">
-      <c r="B66" s="54" t="s">
-        <v>177</v>
-      </c>
-      <c r="C66" s="55">
-        <f>-E63*(C37-Cash_Yield)</f>
-        <v>-4.965E-2</v>
-      </c>
+      <c r="B66" s="45"/>
+      <c r="C66" s="46"/>
     </row>
     <row r="67" spans="1:5">
-      <c r="B67" s="54" t="s">
+      <c r="B67" s="39" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B69" s="21"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="B71" s="64" t="s">
+        <v>197</v>
+      </c>
+      <c r="C71" s="64"/>
+      <c r="D71" s="64"/>
+      <c r="E71" s="64"/>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="B73" s="20" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="B74" s="24" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="B75" s="24" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="B77" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="C67" s="55">
-        <f>C37+C66</f>
-        <v>0.15035000000000001</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="B68" s="45"/>
-      <c r="C68" s="46"/>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="B69" s="39" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="B71" s="21"/>
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="B73" s="64" t="s">
-        <v>200</v>
-      </c>
-      <c r="C73" s="64"/>
-      <c r="D73" s="64"/>
-      <c r="E73" s="64"/>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="B75" s="20" t="s">
+    </row>
+    <row r="78" spans="1:5">
+      <c r="B78" s="39" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="B79" s="24" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="B80" s="24" t="s">
         <v>182</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="B76" s="24" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="B77" s="24" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="B79" s="20" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="B80" s="39" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="B81" s="24" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="B83" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="B84" s="24" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="B85" s="67" t="s">
+        <v>193</v>
+      </c>
+      <c r="C85" s="67"/>
+      <c r="D85" s="67"/>
+      <c r="E85" s="67"/>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="B86" s="66" t="s">
+        <v>191</v>
+      </c>
+      <c r="C86" s="66"/>
+      <c r="D86" s="66"/>
+      <c r="E86" s="66"/>
+    </row>
+    <row r="87" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B87" s="64" t="s">
+        <v>190</v>
+      </c>
+      <c r="C87" s="64"/>
+      <c r="D87" s="64"/>
+      <c r="E87" s="64"/>
+    </row>
+    <row r="88" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B88" s="64" t="s">
+        <v>227</v>
+      </c>
+      <c r="C88" s="64"/>
+      <c r="D88" s="64"/>
+      <c r="E88" s="64"/>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="B90" s="24" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="B91" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="B92" s="61" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="B93" s="24" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="B94" s="24" t="s">
         <v>184</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="B82" s="24" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="B83" s="24" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="28" t="s">
-        <v>147</v>
-      </c>
-      <c r="B85" s="20" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="B86" s="24" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="B87" s="67" t="s">
-        <v>196</v>
-      </c>
-      <c r="C87" s="67"/>
-      <c r="D87" s="67"/>
-      <c r="E87" s="67"/>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="B88" s="66" t="s">
-        <v>194</v>
-      </c>
-      <c r="C88" s="66"/>
-      <c r="D88" s="66"/>
-      <c r="E88" s="66"/>
-    </row>
-    <row r="89" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B89" s="64" t="s">
-        <v>193</v>
-      </c>
-      <c r="C89" s="64"/>
-      <c r="D89" s="64"/>
-      <c r="E89" s="64"/>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="B90" s="64" t="s">
-        <v>227</v>
-      </c>
-      <c r="C90" s="64"/>
-      <c r="D90" s="64"/>
-      <c r="E90" s="64"/>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="B92" s="24" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
-      <c r="B93" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="B94" s="61" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="B95" s="24" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="B96" s="24" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="B98" s="24" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="B97" s="65" t="s">
+        <v>212</v>
+      </c>
+      <c r="C97" s="65"/>
+      <c r="D97" s="65"/>
+      <c r="E97" s="65"/>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="B99" s="24" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="12.4">
+      <c r="B100" s="65" t="s">
+        <v>213</v>
+      </c>
+      <c r="C100" s="65"/>
+      <c r="D100" s="65"/>
+      <c r="E100" s="65"/>
+    </row>
+    <row r="101" spans="1:5" ht="58.5" customHeight="1">
+      <c r="B101" s="64" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="99" spans="1:5">
-      <c r="B99" s="65" t="s">
-        <v>221</v>
-      </c>
-      <c r="C99" s="65"/>
-      <c r="D99" s="65"/>
-      <c r="E99" s="65"/>
-    </row>
-    <row r="101" spans="1:5">
-      <c r="B101" s="24" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" ht="12.4">
-      <c r="B102" s="65" t="s">
-        <v>222</v>
-      </c>
-      <c r="C102" s="65"/>
-      <c r="D102" s="65"/>
-      <c r="E102" s="65"/>
-    </row>
-    <row r="103" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B103" s="64" t="s">
-        <v>214</v>
-      </c>
-      <c r="C103" s="64"/>
-      <c r="D103" s="64"/>
-      <c r="E103" s="64"/>
+      <c r="C101" s="64"/>
+      <c r="D101" s="64"/>
+      <c r="E101" s="64"/>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="B103" s="20" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="B104" s="1" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="105" spans="1:5">
-      <c r="A105" s="28" t="s">
-        <v>189</v>
-      </c>
-      <c r="B105" s="20" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
-      <c r="B106" s="1" t="s">
-        <v>204</v>
+      <c r="B105" s="1" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="B107" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
-      <c r="B109" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="B108" s="1" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="110" spans="1:5">
-      <c r="B110" s="1" t="s">
-        <v>223</v>
+      <c r="B110" s="23" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="B111" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C111" s="44">
+        <v>0.5490782759805124</v>
       </c>
     </row>
     <row r="112" spans="1:5">
-      <c r="B112" s="23" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
-      <c r="B113" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C113" s="44">
-        <v>0.5490782759805124</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
-      <c r="B114" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C114" s="44">
+      <c r="B112" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C112" s="44">
         <v>8.956135035007412E-2</v>
       </c>
-      <c r="D114" s="62" t="str">
-        <f>IF(C114&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
+      <c r="D112" s="62" t="str">
+        <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
         <v>Warning: Return is lower than the Benchmark.</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B116" s="64" t="s">
-        <v>228</v>
-      </c>
-      <c r="C116" s="64"/>
-      <c r="D116" s="64"/>
-      <c r="E116" s="64"/>
+    <row r="114" spans="1:5" ht="24.4" customHeight="1">
+      <c r="B114" s="64" t="s">
+        <v>218</v>
+      </c>
+      <c r="C114" s="64"/>
+      <c r="D114" s="64"/>
+      <c r="E114" s="64"/>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B116" s="21"/>
+      <c r="C116" s="21"/>
+      <c r="D116" s="21"/>
+      <c r="E116" s="21"/>
     </row>
     <row r="118" spans="1:5">
-      <c r="A118" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B118" s="21"/>
-      <c r="C118" s="21"/>
-      <c r="D118" s="21"/>
-      <c r="E118" s="21"/>
+      <c r="B118" s="20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="B119" s="24" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="120" spans="1:5">
-      <c r="B120" s="20" t="s">
-        <v>84</v>
+      <c r="B120" s="24" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="B121" s="24" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5">
-      <c r="B122" s="24" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5">
-      <c r="B123" s="24" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B87:E87"/>
     <mergeCell ref="B88:E88"/>
-    <mergeCell ref="B73:E73"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B116:E116"/>
-    <mergeCell ref="B99:E99"/>
-    <mergeCell ref="B102:E102"/>
-    <mergeCell ref="B103:E103"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B90:E90"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3074,7 +3003,7 @@
       <c r="E1" s="71"/>
       <c r="F1" s="71"/>
       <c r="G1" s="72" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H1" s="72"/>
       <c r="I1" s="72"/>
@@ -3116,7 +3045,7 @@
         <v>62</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>8</v>
@@ -3145,26 +3074,26 @@
     </row>
     <row r="3" spans="1:17">
       <c r="B3" s="11" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D3" s="2">
         <v>15.4</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F3" s="15">
         <v>0.18108249888642258</v>
       </c>
       <c r="G3" s="15">
-        <f t="shared" ref="G3:G5" si="0">F3 - $C$12</f>
+        <f t="shared" ref="G3:G5" si="0">F3 - $C$10</f>
         <v>0.18108249888642258</v>
       </c>
       <c r="H3" s="15">
-        <f t="shared" ref="H3:H5" si="1">F3 - $C$13</f>
+        <f t="shared" ref="H3:H5" si="1">F3 - $C$11</f>
         <v>0.18108249888642258</v>
       </c>
       <c r="I3" s="15">
@@ -3183,30 +3112,30 @@
         <v>8.8311688311688313E-2</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="P3" s="14">
         <v>45716</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="B4" s="11" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D4" s="2">
         <v>7.88</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F4" s="15">
         <v>0.11953198379323582</v>
@@ -3235,30 +3164,30 @@
         <v>7.3604060913705582E-2</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="P4" s="14">
         <v>45716</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="B5" s="11" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D5" s="2">
         <v>2.15</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F5" s="15">
         <v>6.6927308782200656E-2</v>
@@ -3287,16 +3216,16 @@
         <v>5.4790697674418611E-2</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="P5" s="14">
         <v>45716</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -5456,7 +5385,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="20" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5597,7 +5526,7 @@
         <v>65</v>
       </c>
       <c r="C16" s="37">
-        <f>MAX(Portfolio_Mgmt!C38,C10:C15)</f>
+        <f>MAX(Portfolio_Mgmt!C36,C10:C15)</f>
         <v>0.1174</v>
       </c>
     </row>
@@ -5723,162 +5652,162 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="B3" s="73" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C3" s="73"/>
       <c r="D3" s="73"/>
     </row>
     <row r="5" spans="1:4">
       <c r="B5" s="74" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C5" s="65"/>
       <c r="D5" s="65"/>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="74" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" s="65"/>
       <c r="D6" s="65"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5"/>
       <c r="B10" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="B11" s="73" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C11" s="73"/>
       <c r="D11" s="73"/>
     </row>
     <row r="12" spans="1:4">
       <c r="B12" s="73" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C12" s="73"/>
       <c r="D12" s="73"/>
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="23" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="12.4">
       <c r="B16" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="30" t="s">
         <v>120</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="B17" s="26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="B18" s="26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="B19" s="26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="B20" s="26" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="B21" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="C21" s="26" t="s">
         <v>135</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="B22" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="C22" s="26" t="s">
         <v>137</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="B23" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" s="26" t="s">
         <v>139</v>
-      </c>
-      <c r="C23" s="26" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="B24" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="C24" s="26" t="s">
         <v>144</v>
-      </c>
-      <c r="C24" s="26" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="B25" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="C25" s="26" t="s">
         <v>141</v>
-      </c>
-      <c r="C25" s="26" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="5"/>
       <c r="B27" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="B28" s="73" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C28" s="73"/>
       <c r="D28" s="73"/>
     </row>
     <row r="29" spans="1:4">
       <c r="B29" s="73" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C29" s="73"/>
       <c r="D29" s="73"/>
@@ -5886,7 +5815,7 @@
     <row r="31" spans="1:4">
       <c r="A31" s="5"/>
       <c r="B31" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -5894,46 +5823,46 @@
         <v>66</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="B33" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="28" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="B36" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="5"/>
       <c r="B38" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="B39" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="B40" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="B41" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,28 +8,86 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F9D479-E743-4414-8791-0EF185DCBC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3564080-78BF-445F-BAB9-5766E4CAB088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
     <sheet name="Opportunities" sheetId="1" r:id="rId2"/>
-    <sheet name="Market_Yield" sheetId="2" r:id="rId3"/>
-    <sheet name="Comp_Group" sheetId="6" r:id="rId4"/>
-    <sheet name="Holdings" sheetId="7" r:id="rId5"/>
+    <sheet name="Aux&gt;" sheetId="8" r:id="rId3"/>
+    <sheet name="Market_Yield" sheetId="2" r:id="rId4"/>
+    <sheet name="Comp_Group" sheetId="6" r:id="rId5"/>
+    <sheet name="Holdings" sheetId="7" r:id="rId6"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId7"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Opportunities!$B$2:$Q$2</definedName>
+    <definedName name="AddInfoCommentBox1">#REF!</definedName>
+    <definedName name="AddInfoName1">#REF!</definedName>
+    <definedName name="AddInfoTextBox1">#REF!</definedName>
+    <definedName name="AURABOOKMARK4">#REF!</definedName>
+    <definedName name="AuraStyleDefaultsReset" hidden="1">#N/A</definedName>
+    <definedName name="AvgRate202109">#REF!</definedName>
+    <definedName name="AvgRate2022">#REF!</definedName>
+    <definedName name="AvgRate202409">#REF!</definedName>
     <definedName name="benchmark">Portfolio_Mgmt!$C$10</definedName>
     <definedName name="Cash_Yield">Portfolio_Mgmt!$C$11</definedName>
+    <definedName name="CDC">#REF!</definedName>
+    <definedName name="Chinese_Client_Name">#REF!</definedName>
+    <definedName name="Client_Name">#REF!</definedName>
+    <definedName name="ClosingRate202109">#REF!</definedName>
+    <definedName name="ClosingRate2022">#REF!</definedName>
+    <definedName name="ClosingRate202403">#REF!</definedName>
+    <definedName name="ClosingRate202409">#REF!</definedName>
+    <definedName name="CommentBox1a">#REF!</definedName>
+    <definedName name="Currency">#REF!</definedName>
+    <definedName name="CY">#REF!</definedName>
+    <definedName name="exchange_rate">[1]白银数据!$F$2</definedName>
+    <definedName name="GMV">#REF!</definedName>
+    <definedName name="Long_term_loans">#REF!</definedName>
+    <definedName name="Name10c">#REF!</definedName>
+    <definedName name="Name1a">#REF!</definedName>
+    <definedName name="Name1b">#REF!</definedName>
+    <definedName name="Name1c">#REF!</definedName>
+    <definedName name="Name1d">#REF!</definedName>
+    <definedName name="Name1e">#REF!</definedName>
+    <definedName name="Name1f">#REF!</definedName>
+    <definedName name="Name2a">#REF!</definedName>
+    <definedName name="Name2b">#REF!</definedName>
+    <definedName name="Name3a">#REF!</definedName>
+    <definedName name="Name3b">#REF!</definedName>
+    <definedName name="Name3c">#REF!</definedName>
+    <definedName name="Name4a">#REF!</definedName>
+    <definedName name="Name4b">#REF!</definedName>
+    <definedName name="NSProjectionMethodIndex">#REF!</definedName>
+    <definedName name="NSRequiredLevelOfEvidenceItems">#REF!</definedName>
+    <definedName name="NSTargetedTestingItems">#REF!</definedName>
+    <definedName name="PDC">#REF!</definedName>
+    <definedName name="Period_Ended">#REF!</definedName>
+    <definedName name="PIE">#REF!</definedName>
+    <definedName name="PY">#REF!</definedName>
+    <definedName name="Scenario_Copy">#REF!</definedName>
+    <definedName name="Scenario_Count">#REF!</definedName>
+    <definedName name="Scenario_Paste">#REF!</definedName>
+    <definedName name="Scenario_Switch">#REF!</definedName>
+    <definedName name="TextBox1a">#REF!</definedName>
+    <definedName name="TTDesiredLevelOfEvidenceItems">#REF!</definedName>
+    <definedName name="TwoStepMisstatementIdentified">#REF!</definedName>
+    <definedName name="TwoStepTolerableEstMisstmtCalc">#REF!</definedName>
+    <definedName name="WW3f877d8e32714ec8a8180854ed7f8276_634328481945590045" hidden="1">#REF!</definedName>
+    <definedName name="WW3f877d8e32714ec8a8180854ed7f8276_634328482352282765" hidden="1">#REF!</definedName>
+    <definedName name="Year">#REF!</definedName>
+    <definedName name="黄色">#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="241">
   <si>
     <t>Name</t>
   </si>
@@ -1443,6 +1501,59 @@
     </r>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
+  <si>
+    <t>Current Holdings</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Number of Shares</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Price
+Currency</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Price</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HKD</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0083.HK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0590.HK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cash in HK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>nm</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Total</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cash in Mainland</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Value (HKD)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1455,7 +1566,7 @@
     <numFmt numFmtId="179" formatCode="#,##0.00_);\(#,##0.00\)"/>
     <numFmt numFmtId="180" formatCode="#,##0_);\(#,##0\)"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1632,6 +1743,49 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF002060"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -1743,12 +1897,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1889,17 +2046,17 @@
     <xf numFmtId="179" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1922,10 +2079,40 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="180" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="180" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="3" xr:uid="{32ADA8AA-F280-4250-ABBF-7E6B9CB799DC}"/>
     <cellStyle name="超链接" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1946,6 +2133,66 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="财务预测&gt;"/>
+      <sheetName val="数商时代"/>
+      <sheetName val="PSP计划"/>
+      <sheetName val="PSP相关费用"/>
+      <sheetName val="财务分析&gt;"/>
+      <sheetName val="审计数据"/>
+      <sheetName val="白银数据"/>
+      <sheetName val="PSP分析"/>
+      <sheetName val="原始数据&gt;"/>
+      <sheetName val="CK12_PL 20240930"/>
+      <sheetName val="白银智勤 TB 20240930"/>
+      <sheetName val="白银智勤审计数据"/>
+      <sheetName val="智勤商城数据"/>
+      <sheetName val="智勤优品数据"/>
+      <sheetName val="2024年3月31日年度(12個月)"/>
+      <sheetName val="2023年3月31日年度(12個月)"/>
+      <sheetName val="2024年4月至12月(9個月)"/>
+      <sheetName val="利润表2024年9期"/>
+      <sheetName val="链嬴"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6">
+        <row r="2">
+          <cell r="F2">
+            <v>0.92</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2273,12 +2520,12 @@
       <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B4" s="64" t="s">
+      <c r="B4" s="65" t="s">
         <v>223</v>
       </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="20" t="s">
@@ -2290,12 +2537,12 @@
       <c r="C6" s="62"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" s="64" t="s">
+      <c r="B7" s="65" t="s">
         <v>210</v>
       </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="23" t="s">
@@ -2384,12 +2631,12 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
-      <c r="B24" s="64" t="s">
+      <c r="B24" s="65" t="s">
         <v>222</v>
       </c>
-      <c r="C24" s="64"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="64"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="65"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
@@ -2483,20 +2730,20 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="B39" s="64" t="s">
+      <c r="B39" s="65" t="s">
         <v>156</v>
       </c>
-      <c r="C39" s="64"/>
-      <c r="D39" s="64"/>
-      <c r="E39" s="64"/>
+      <c r="C39" s="65"/>
+      <c r="D39" s="65"/>
+      <c r="E39" s="65"/>
     </row>
     <row r="40" spans="1:5" ht="58.5" customHeight="1">
-      <c r="B40" s="64" t="s">
+      <c r="B40" s="65" t="s">
         <v>221</v>
       </c>
-      <c r="C40" s="64"/>
-      <c r="D40" s="64"/>
-      <c r="E40" s="64"/>
+      <c r="C40" s="65"/>
+      <c r="D40" s="65"/>
+      <c r="E40" s="65"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="21" t="s">
@@ -2508,12 +2755,12 @@
       <c r="E42" s="21"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="B44" s="64" t="s">
+      <c r="B44" s="65" t="s">
         <v>209</v>
       </c>
-      <c r="C44" s="64"/>
-      <c r="D44" s="64"/>
-      <c r="E44" s="64"/>
+      <c r="C44" s="65"/>
+      <c r="D44" s="65"/>
+      <c r="E44" s="65"/>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="23" t="s">
@@ -2698,12 +2945,12 @@
       <c r="E69" s="21"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="B71" s="64" t="s">
+      <c r="B71" s="65" t="s">
         <v>197</v>
       </c>
-      <c r="C71" s="64"/>
-      <c r="D71" s="64"/>
-      <c r="E71" s="64"/>
+      <c r="C71" s="65"/>
+      <c r="D71" s="65"/>
+      <c r="E71" s="65"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="28" t="s">
@@ -2765,36 +3012,36 @@
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="B85" s="67" t="s">
+      <c r="B85" s="66" t="s">
         <v>193</v>
       </c>
-      <c r="C85" s="67"/>
-      <c r="D85" s="67"/>
-      <c r="E85" s="67"/>
+      <c r="C85" s="66"/>
+      <c r="D85" s="66"/>
+      <c r="E85" s="66"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="B86" s="66" t="s">
+      <c r="B86" s="64" t="s">
         <v>191</v>
       </c>
-      <c r="C86" s="66"/>
-      <c r="D86" s="66"/>
-      <c r="E86" s="66"/>
+      <c r="C86" s="64"/>
+      <c r="D86" s="64"/>
+      <c r="E86" s="64"/>
     </row>
     <row r="87" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B87" s="64" t="s">
+      <c r="B87" s="65" t="s">
         <v>190</v>
       </c>
-      <c r="C87" s="64"/>
-      <c r="D87" s="64"/>
-      <c r="E87" s="64"/>
+      <c r="C87" s="65"/>
+      <c r="D87" s="65"/>
+      <c r="E87" s="65"/>
     </row>
     <row r="88" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B88" s="64" t="s">
+      <c r="B88" s="65" t="s">
         <v>227</v>
       </c>
-      <c r="C88" s="64"/>
-      <c r="D88" s="64"/>
-      <c r="E88" s="64"/>
+      <c r="C88" s="65"/>
+      <c r="D88" s="65"/>
+      <c r="E88" s="65"/>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="24" t="s">
@@ -2827,12 +3074,12 @@
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="B97" s="65" t="s">
+      <c r="B97" s="67" t="s">
         <v>212</v>
       </c>
-      <c r="C97" s="65"/>
-      <c r="D97" s="65"/>
-      <c r="E97" s="65"/>
+      <c r="C97" s="67"/>
+      <c r="D97" s="67"/>
+      <c r="E97" s="67"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
@@ -2840,20 +3087,20 @@
       </c>
     </row>
     <row r="100" spans="1:5" ht="12.4">
-      <c r="B100" s="65" t="s">
+      <c r="B100" s="67" t="s">
         <v>213</v>
       </c>
-      <c r="C100" s="65"/>
-      <c r="D100" s="65"/>
-      <c r="E100" s="65"/>
+      <c r="C100" s="67"/>
+      <c r="D100" s="67"/>
+      <c r="E100" s="67"/>
     </row>
     <row r="101" spans="1:5" ht="58.5" customHeight="1">
-      <c r="B101" s="64" t="s">
+      <c r="B101" s="65" t="s">
         <v>220</v>
       </c>
-      <c r="C101" s="64"/>
-      <c r="D101" s="64"/>
-      <c r="E101" s="64"/>
+      <c r="C101" s="65"/>
+      <c r="D101" s="65"/>
+      <c r="E101" s="65"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="28" t="s">
@@ -2909,12 +3156,12 @@
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B114" s="64" t="s">
+      <c r="B114" s="65" t="s">
         <v>218</v>
       </c>
-      <c r="C114" s="64"/>
-      <c r="D114" s="64"/>
-      <c r="E114" s="64"/>
+      <c r="C114" s="65"/>
+      <c r="D114" s="65"/>
+      <c r="E114" s="65"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="21" t="s">
@@ -2947,6 +3194,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
     <mergeCell ref="B86:E86"/>
     <mergeCell ref="B71:E71"/>
     <mergeCell ref="B85:E85"/>
@@ -2956,12 +3209,6 @@
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5373,6 +5620,23 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE1B8B86-2106-47AA-B6E8-452642EDB9D4}">
+  <sheetPr>
+    <tabColor theme="4" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75" customHeight="1" zeroHeight="1"/>
+  <cols>
+    <col min="1" max="16384" width="9.06640625" style="85"/>
+  </cols>
+  <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62760D14-1F64-4D73-BBAC-22718A84BD18}">
   <dimension ref="A1:E31"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
@@ -5638,7 +5902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE447BDC-FAEF-412F-B13E-867203D1820E}">
   <dimension ref="A1:D41"/>
   <sheetFormatPr defaultRowHeight="11.65"/>
@@ -5672,15 +5936,15 @@
       <c r="B5" s="74" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="74" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">
@@ -5880,11 +6144,291 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D81F047E-EC38-4C3A-BA81-E6C9549453D6}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
-  <sheetData/>
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" style="77" customWidth="1"/>
+    <col min="2" max="2" width="16.59765625" style="77" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.06640625" style="77"/>
+    <col min="5" max="6" width="15.59765625" style="77" customWidth="1"/>
+    <col min="7" max="16384" width="9.06640625" style="77"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="13.15">
+      <c r="A1" s="75"/>
+      <c r="B1" s="76" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="26.25">
+      <c r="B2" s="78" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="78" t="s">
+        <v>231</v>
+      </c>
+      <c r="D2" s="78" t="s">
+        <v>230</v>
+      </c>
+      <c r="E2" s="78" t="s">
+        <v>229</v>
+      </c>
+      <c r="F2" s="78" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="B3" s="79" t="s">
+        <v>235</v>
+      </c>
+      <c r="C3" s="82" t="s">
+        <v>236</v>
+      </c>
+      <c r="D3" s="79" t="s">
+        <v>232</v>
+      </c>
+      <c r="E3" s="83" t="s">
+        <v>236</v>
+      </c>
+      <c r="F3" s="83">
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="B4" s="79" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" s="82" t="s">
+        <v>236</v>
+      </c>
+      <c r="D4" s="79" t="s">
+        <v>239</v>
+      </c>
+      <c r="E4" s="83" t="s">
+        <v>236</v>
+      </c>
+      <c r="F4" s="83">
+        <f>280000*1.02</f>
+        <v>285600</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5" s="79" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="82">
+        <v>15.4</v>
+      </c>
+      <c r="D5" s="79" t="s">
+        <v>232</v>
+      </c>
+      <c r="E5" s="83">
+        <v>5500</v>
+      </c>
+      <c r="F5" s="83">
+        <f>C5*E5</f>
+        <v>84700</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6" s="79" t="s">
+        <v>233</v>
+      </c>
+      <c r="C6" s="82">
+        <v>8</v>
+      </c>
+      <c r="D6" s="79" t="s">
+        <v>232</v>
+      </c>
+      <c r="E6" s="83">
+        <v>20000</v>
+      </c>
+      <c r="F6" s="83">
+        <f>E6*C6</f>
+        <v>160000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7" s="79"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="79"/>
+    </row>
+    <row r="8" spans="1:6" ht="13.15">
+      <c r="B8" s="79"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="79"/>
+      <c r="E8" s="84" t="s">
+        <v>237</v>
+      </c>
+      <c r="F8" s="84">
+        <f>SUM(F3:F7)</f>
+        <v>1110300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="B9" s="79"/>
+      <c r="C9" s="82"/>
+      <c r="D9" s="79"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10" s="79"/>
+      <c r="C10" s="82"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11" s="79"/>
+      <c r="C11" s="82"/>
+      <c r="D11" s="79"/>
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12" s="79"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="79"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13" s="79"/>
+      <c r="C13" s="82"/>
+      <c r="D13" s="79"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14" s="79"/>
+      <c r="C14" s="82"/>
+      <c r="D14" s="79"/>
+      <c r="E14" s="83"/>
+      <c r="F14" s="83"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="B15" s="79"/>
+      <c r="C15" s="82"/>
+      <c r="D15" s="79"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="83"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="B16" s="79"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="79"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="79"/>
+      <c r="C17" s="82"/>
+      <c r="D17" s="79"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="83"/>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="79"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="79"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="83"/>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19" s="79"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="79"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="83"/>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="79"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="79"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="79"/>
+      <c r="C21" s="82"/>
+      <c r="D21" s="79"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="83"/>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="79"/>
+      <c r="C22" s="82"/>
+      <c r="D22" s="79"/>
+      <c r="E22" s="83"/>
+      <c r="F22" s="83"/>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="79"/>
+      <c r="C23" s="82"/>
+      <c r="D23" s="79"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="83"/>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="79"/>
+      <c r="C24" s="82"/>
+      <c r="D24" s="79"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="79"/>
+      <c r="C25" s="82"/>
+      <c r="D25" s="79"/>
+      <c r="E25" s="83"/>
+      <c r="F25" s="83"/>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="79"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="79"/>
+      <c r="E26" s="83"/>
+      <c r="F26" s="83"/>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27" s="79"/>
+      <c r="C27" s="82"/>
+      <c r="D27" s="79"/>
+      <c r="E27" s="83"/>
+      <c r="F27" s="83"/>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="79"/>
+      <c r="C28" s="82"/>
+      <c r="D28" s="79"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="79"/>
+      <c r="C29" s="82"/>
+      <c r="D29" s="79"/>
+      <c r="E29" s="83"/>
+      <c r="F29" s="83"/>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="79"/>
+      <c r="C30" s="82"/>
+      <c r="D30" s="79"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="83"/>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="79"/>
+      <c r="C31" s="80"/>
+      <c r="D31" s="79"/>
+      <c r="E31" s="81"/>
+      <c r="F31" s="81"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3564080-78BF-445F-BAB9-5766E4CAB088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C0C1083-5175-4F2E-81F2-6FAA5275BFFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1403,30 +1403,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Cost of Equity</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>: This plan adopts a value investing perspective, viewing true risk as the potential for permanent capital loss arising from deteriorating business fundamentals or paying too high a price, rather than short-term market price volatility (beta). Consistent with this, a uniform Base Cost of Equity is applied to all potential investments. This rate represents the minimum acceptable long-term return required for committing capital to any equity holding in this portfolio, reflecting long-term risk-free rates plus a required premium for taking on general business ownership risk.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">Objective: </t>
     </r>
     <r>
@@ -1552,6 +1528,30 @@
   </si>
   <si>
     <t>Market Value (HKD)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Cost of Equity</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: This plan employs a value investing framework, defining true risk as the potential for permanent capital loss due to deteriorating business fundamentals or overvaluation, rather than short-term price volatility (beta). The model uses a standardized base cost of equity as the discount rate in DCF analysis,which serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium to account for ownership risks.</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2046,6 +2046,35 @@
     <xf numFmtId="179" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="180" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="180" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2078,35 +2107,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="180" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="180" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="3">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2520,12 +2520,12 @@
       <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B4" s="65" t="s">
-        <v>223</v>
-      </c>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
+      <c r="B4" s="76" t="s">
+        <v>222</v>
+      </c>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="20" t="s">
@@ -2537,12 +2537,12 @@
       <c r="C6" s="62"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" s="65" t="s">
+      <c r="B7" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="C7" s="65"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="76"/>
+      <c r="E7" s="76"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="23" t="s">
@@ -2631,12 +2631,12 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
-      <c r="B24" s="65" t="s">
-        <v>222</v>
-      </c>
-      <c r="C24" s="65"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="65"/>
+      <c r="B24" s="76" t="s">
+        <v>221</v>
+      </c>
+      <c r="C24" s="76"/>
+      <c r="D24" s="76"/>
+      <c r="E24" s="76"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
@@ -2730,20 +2730,20 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="B39" s="65" t="s">
+      <c r="B39" s="76" t="s">
         <v>156</v>
       </c>
-      <c r="C39" s="65"/>
-      <c r="D39" s="65"/>
-      <c r="E39" s="65"/>
-    </row>
-    <row r="40" spans="1:5" ht="58.5" customHeight="1">
-      <c r="B40" s="65" t="s">
-        <v>221</v>
-      </c>
-      <c r="C40" s="65"/>
-      <c r="D40" s="65"/>
-      <c r="E40" s="65"/>
+      <c r="C39" s="76"/>
+      <c r="D39" s="76"/>
+      <c r="E39" s="76"/>
+    </row>
+    <row r="40" spans="1:5" ht="46.6" customHeight="1">
+      <c r="B40" s="76" t="s">
+        <v>240</v>
+      </c>
+      <c r="C40" s="76"/>
+      <c r="D40" s="76"/>
+      <c r="E40" s="76"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="21" t="s">
@@ -2755,12 +2755,12 @@
       <c r="E42" s="21"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="B44" s="65" t="s">
+      <c r="B44" s="76" t="s">
         <v>209</v>
       </c>
-      <c r="C44" s="65"/>
-      <c r="D44" s="65"/>
-      <c r="E44" s="65"/>
+      <c r="C44" s="76"/>
+      <c r="D44" s="76"/>
+      <c r="E44" s="76"/>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="23" t="s">
@@ -2805,7 +2805,7 @@
         <v>0.2</v>
       </c>
       <c r="D51" s="63" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E51" s="56"/>
     </row>
@@ -2945,12 +2945,12 @@
       <c r="E69" s="21"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="B71" s="65" t="s">
+      <c r="B71" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="C71" s="65"/>
-      <c r="D71" s="65"/>
-      <c r="E71" s="65"/>
+      <c r="C71" s="76"/>
+      <c r="D71" s="76"/>
+      <c r="E71" s="76"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="28" t="s">
@@ -2962,12 +2962,12 @@
     </row>
     <row r="74" spans="1:5">
       <c r="B74" s="24" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="B75" s="24" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -3012,36 +3012,36 @@
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="B85" s="66" t="s">
+      <c r="B85" s="77" t="s">
         <v>193</v>
       </c>
-      <c r="C85" s="66"/>
-      <c r="D85" s="66"/>
-      <c r="E85" s="66"/>
+      <c r="C85" s="77"/>
+      <c r="D85" s="77"/>
+      <c r="E85" s="77"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="B86" s="64" t="s">
+      <c r="B86" s="75" t="s">
         <v>191</v>
       </c>
-      <c r="C86" s="64"/>
-      <c r="D86" s="64"/>
-      <c r="E86" s="64"/>
+      <c r="C86" s="75"/>
+      <c r="D86" s="75"/>
+      <c r="E86" s="75"/>
     </row>
     <row r="87" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B87" s="65" t="s">
+      <c r="B87" s="76" t="s">
         <v>190</v>
       </c>
-      <c r="C87" s="65"/>
-      <c r="D87" s="65"/>
-      <c r="E87" s="65"/>
+      <c r="C87" s="76"/>
+      <c r="D87" s="76"/>
+      <c r="E87" s="76"/>
     </row>
     <row r="88" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B88" s="65" t="s">
-        <v>227</v>
-      </c>
-      <c r="C88" s="65"/>
-      <c r="D88" s="65"/>
-      <c r="E88" s="65"/>
+      <c r="B88" s="76" t="s">
+        <v>226</v>
+      </c>
+      <c r="C88" s="76"/>
+      <c r="D88" s="76"/>
+      <c r="E88" s="76"/>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="24" t="s">
@@ -3074,12 +3074,12 @@
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="B97" s="67" t="s">
+      <c r="B97" s="78" t="s">
         <v>212</v>
       </c>
-      <c r="C97" s="67"/>
-      <c r="D97" s="67"/>
-      <c r="E97" s="67"/>
+      <c r="C97" s="78"/>
+      <c r="D97" s="78"/>
+      <c r="E97" s="78"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
@@ -3087,20 +3087,20 @@
       </c>
     </row>
     <row r="100" spans="1:5" ht="12.4">
-      <c r="B100" s="67" t="s">
+      <c r="B100" s="78" t="s">
         <v>213</v>
       </c>
-      <c r="C100" s="67"/>
-      <c r="D100" s="67"/>
-      <c r="E100" s="67"/>
+      <c r="C100" s="78"/>
+      <c r="D100" s="78"/>
+      <c r="E100" s="78"/>
     </row>
     <row r="101" spans="1:5" ht="58.5" customHeight="1">
-      <c r="B101" s="65" t="s">
+      <c r="B101" s="76" t="s">
         <v>220</v>
       </c>
-      <c r="C101" s="65"/>
-      <c r="D101" s="65"/>
-      <c r="E101" s="65"/>
+      <c r="C101" s="76"/>
+      <c r="D101" s="76"/>
+      <c r="E101" s="76"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="28" t="s">
@@ -3156,12 +3156,12 @@
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B114" s="65" t="s">
+      <c r="B114" s="76" t="s">
         <v>218</v>
       </c>
-      <c r="C114" s="65"/>
-      <c r="D114" s="65"/>
-      <c r="E114" s="65"/>
+      <c r="C114" s="76"/>
+      <c r="D114" s="76"/>
+      <c r="E114" s="76"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="21" t="s">
@@ -3244,30 +3244,30 @@
       <c r="B1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="71" t="s">
+      <c r="D1" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="72" t="s">
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="83" t="s">
         <v>101</v>
       </c>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="68" t="s">
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="68"/>
-      <c r="L1" s="69" t="s">
+      <c r="K1" s="79"/>
+      <c r="L1" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="69"/>
-      <c r="N1" s="70" t="s">
+      <c r="M1" s="80"/>
+      <c r="N1" s="81" t="s">
         <v>53</v>
       </c>
-      <c r="O1" s="70"/>
-      <c r="P1" s="70"/>
-      <c r="Q1" s="70"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
     </row>
     <row r="2" spans="1:17" ht="26" customHeight="1">
       <c r="B2" s="7" t="s">
@@ -5627,7 +5627,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.75" customHeight="1" zeroHeight="1"/>
   <cols>
-    <col min="1" max="16384" width="9.06640625" style="85"/>
+    <col min="1" max="16384" width="9.06640625" style="74"/>
   </cols>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -5721,12 +5721,6 @@
       <c r="A8" s="31"/>
       <c r="B8" s="32" t="s">
         <v>25</v>
-      </c>
-      <c r="C8" s="1">
-        <v>4.1700000000000001E-2</v>
-      </c>
-      <c r="D8" s="1">
-        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5926,25 +5920,25 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="84" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="85" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="B6" s="74" t="s">
+      <c r="B6" s="85" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
+      <c r="C6" s="78"/>
+      <c r="D6" s="78"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">
@@ -5958,18 +5952,18 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="73" t="s">
+      <c r="B11" s="84" t="s">
         <v>109</v>
       </c>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73"/>
+      <c r="C11" s="84"/>
+      <c r="D11" s="84"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="B12" s="73" t="s">
+      <c r="B12" s="84" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73"/>
+      <c r="C12" s="84"/>
+      <c r="D12" s="84"/>
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="23" t="s">
@@ -6063,18 +6057,18 @@
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="B28" s="73" t="s">
+      <c r="B28" s="84" t="s">
         <v>122</v>
       </c>
-      <c r="C28" s="73"/>
-      <c r="D28" s="73"/>
+      <c r="C28" s="84"/>
+      <c r="D28" s="84"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="B29" s="73" t="s">
+      <c r="B29" s="84" t="s">
         <v>123</v>
       </c>
-      <c r="C29" s="73"/>
-      <c r="D29" s="73"/>
+      <c r="C29" s="84"/>
+      <c r="D29" s="84"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="5"/>
@@ -6149,284 +6143,284 @@
   <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="77" customWidth="1"/>
-    <col min="2" max="2" width="16.59765625" style="77" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.06640625" style="77"/>
-    <col min="5" max="6" width="15.59765625" style="77" customWidth="1"/>
-    <col min="7" max="16384" width="9.06640625" style="77"/>
+    <col min="1" max="1" width="2.59765625" style="66" customWidth="1"/>
+    <col min="2" max="2" width="16.59765625" style="66" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.06640625" style="66"/>
+    <col min="5" max="6" width="15.59765625" style="66" customWidth="1"/>
+    <col min="7" max="16384" width="9.06640625" style="66"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="13.15">
-      <c r="A1" s="75"/>
-      <c r="B1" s="76" t="s">
+      <c r="A1" s="64"/>
+      <c r="B1" s="65" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="26.25">
+      <c r="B2" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="67" t="s">
+        <v>230</v>
+      </c>
+      <c r="D2" s="67" t="s">
+        <v>229</v>
+      </c>
+      <c r="E2" s="67" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="26.25">
-      <c r="B2" s="78" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="78" t="s">
+      <c r="F2" s="67" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="B3" s="68" t="s">
+        <v>234</v>
+      </c>
+      <c r="C3" s="71" t="s">
+        <v>235</v>
+      </c>
+      <c r="D3" s="68" t="s">
         <v>231</v>
       </c>
-      <c r="D2" s="78" t="s">
-        <v>230</v>
-      </c>
-      <c r="E2" s="78" t="s">
-        <v>229</v>
-      </c>
-      <c r="F2" s="78" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="B3" s="79" t="s">
+      <c r="E3" s="72" t="s">
         <v>235</v>
       </c>
-      <c r="C3" s="82" t="s">
-        <v>236</v>
-      </c>
-      <c r="D3" s="79" t="s">
-        <v>232</v>
-      </c>
-      <c r="E3" s="83" t="s">
-        <v>236</v>
-      </c>
-      <c r="F3" s="83">
+      <c r="F3" s="72">
         <v>580000</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="B4" s="79" t="s">
+      <c r="B4" s="68" t="s">
+        <v>237</v>
+      </c>
+      <c r="C4" s="71" t="s">
+        <v>235</v>
+      </c>
+      <c r="D4" s="68" t="s">
         <v>238</v>
       </c>
-      <c r="C4" s="82" t="s">
-        <v>236</v>
-      </c>
-      <c r="D4" s="79" t="s">
-        <v>239</v>
-      </c>
-      <c r="E4" s="83" t="s">
-        <v>236</v>
-      </c>
-      <c r="F4" s="83">
+      <c r="E4" s="72" t="s">
+        <v>235</v>
+      </c>
+      <c r="F4" s="72">
         <f>280000*1.02</f>
         <v>285600</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="B5" s="79" t="s">
-        <v>234</v>
-      </c>
-      <c r="C5" s="82">
+      <c r="B5" s="68" t="s">
+        <v>233</v>
+      </c>
+      <c r="C5" s="71">
         <v>15.4</v>
       </c>
-      <c r="D5" s="79" t="s">
-        <v>232</v>
-      </c>
-      <c r="E5" s="83">
+      <c r="D5" s="68" t="s">
+        <v>231</v>
+      </c>
+      <c r="E5" s="72">
         <v>5500</v>
       </c>
-      <c r="F5" s="83">
+      <c r="F5" s="72">
         <f>C5*E5</f>
         <v>84700</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="B6" s="79" t="s">
-        <v>233</v>
-      </c>
-      <c r="C6" s="82">
+      <c r="B6" s="68" t="s">
+        <v>232</v>
+      </c>
+      <c r="C6" s="71">
         <v>8</v>
       </c>
-      <c r="D6" s="79" t="s">
-        <v>232</v>
-      </c>
-      <c r="E6" s="83">
+      <c r="D6" s="68" t="s">
+        <v>231</v>
+      </c>
+      <c r="E6" s="72">
         <v>20000</v>
       </c>
-      <c r="F6" s="83">
+      <c r="F6" s="72">
         <f>E6*C6</f>
         <v>160000</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="B7" s="79"/>
-      <c r="C7" s="82"/>
-      <c r="D7" s="79"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="68"/>
     </row>
     <row r="8" spans="1:6" ht="13.15">
-      <c r="B8" s="79"/>
-      <c r="C8" s="82"/>
-      <c r="D8" s="79"/>
-      <c r="E8" s="84" t="s">
-        <v>237</v>
-      </c>
-      <c r="F8" s="84">
+      <c r="B8" s="68"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="73" t="s">
+        <v>236</v>
+      </c>
+      <c r="F8" s="73">
         <f>SUM(F3:F7)</f>
         <v>1110300</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="B9" s="79"/>
-      <c r="C9" s="82"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="B10" s="79"/>
-      <c r="C10" s="82"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="B11" s="79"/>
-      <c r="C11" s="82"/>
-      <c r="D11" s="79"/>
-      <c r="E11" s="83"/>
-      <c r="F11" s="83"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="B12" s="79"/>
-      <c r="C12" s="82"/>
-      <c r="D12" s="79"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="B13" s="79"/>
-      <c r="C13" s="82"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="83"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="B14" s="79"/>
-      <c r="C14" s="82"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="83"/>
-      <c r="F14" s="83"/>
+      <c r="B14" s="68"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="68"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="B15" s="79"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="83"/>
+      <c r="B15" s="68"/>
+      <c r="C15" s="71"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="72"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="B16" s="79"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="79"/>
-      <c r="E16" s="83"/>
-      <c r="F16" s="83"/>
+      <c r="B16" s="68"/>
+      <c r="C16" s="71"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="72"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="79"/>
-      <c r="C17" s="82"/>
-      <c r="D17" s="79"/>
-      <c r="E17" s="83"/>
-      <c r="F17" s="83"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="71"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="72"/>
+      <c r="F17" s="72"/>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="79"/>
-      <c r="C18" s="82"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="83"/>
-      <c r="F18" s="83"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="72"/>
+      <c r="F18" s="72"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="B19" s="79"/>
-      <c r="C19" s="82"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="83"/>
-      <c r="F19" s="83"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="71"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="72"/>
     </row>
     <row r="20" spans="2:6">
-      <c r="B20" s="79"/>
-      <c r="C20" s="82"/>
-      <c r="D20" s="79"/>
-      <c r="E20" s="83"/>
-      <c r="F20" s="83"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="71"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="72"/>
+      <c r="F20" s="72"/>
     </row>
     <row r="21" spans="2:6">
-      <c r="B21" s="79"/>
-      <c r="C21" s="82"/>
-      <c r="D21" s="79"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="83"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="71"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="72"/>
     </row>
     <row r="22" spans="2:6">
-      <c r="B22" s="79"/>
-      <c r="C22" s="82"/>
-      <c r="D22" s="79"/>
-      <c r="E22" s="83"/>
-      <c r="F22" s="83"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="71"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
     </row>
     <row r="23" spans="2:6">
-      <c r="B23" s="79"/>
-      <c r="C23" s="82"/>
-      <c r="D23" s="79"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="83"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="71"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="72"/>
     </row>
     <row r="24" spans="2:6">
-      <c r="B24" s="79"/>
-      <c r="C24" s="82"/>
-      <c r="D24" s="79"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="83"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="71"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
     </row>
     <row r="25" spans="2:6">
-      <c r="B25" s="79"/>
-      <c r="C25" s="82"/>
-      <c r="D25" s="79"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="71"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="72"/>
+      <c r="F25" s="72"/>
     </row>
     <row r="26" spans="2:6">
-      <c r="B26" s="79"/>
-      <c r="C26" s="82"/>
-      <c r="D26" s="79"/>
-      <c r="E26" s="83"/>
-      <c r="F26" s="83"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="71"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="72"/>
+      <c r="F26" s="72"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="79"/>
-      <c r="C27" s="82"/>
-      <c r="D27" s="79"/>
-      <c r="E27" s="83"/>
-      <c r="F27" s="83"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="71"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="72"/>
+      <c r="F27" s="72"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="B28" s="79"/>
-      <c r="C28" s="82"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="83"/>
-      <c r="F28" s="83"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="71"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="72"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="B29" s="79"/>
-      <c r="C29" s="82"/>
-      <c r="D29" s="79"/>
-      <c r="E29" s="83"/>
-      <c r="F29" s="83"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="71"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="72"/>
+      <c r="F29" s="72"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="B30" s="79"/>
-      <c r="C30" s="82"/>
-      <c r="D30" s="79"/>
-      <c r="E30" s="83"/>
-      <c r="F30" s="83"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="71"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="72"/>
+      <c r="F30" s="72"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="B31" s="79"/>
-      <c r="C31" s="80"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="81"/>
-      <c r="F31" s="81"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="69"/>
+      <c r="D31" s="68"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C0C1083-5175-4F2E-81F2-6FAA5275BFFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2241CF05-457C-4A8A-B3BD-709D3FE17A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -3140,7 +3140,7 @@
         <v>176</v>
       </c>
       <c r="C111" s="44">
-        <v>0.5490782759805124</v>
+        <v>0.50943173286990984</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -3148,7 +3148,7 @@
         <v>177</v>
       </c>
       <c r="C112" s="44">
-        <v>8.956135035007412E-2</v>
+        <v>0.10068927690556406</v>
       </c>
       <c r="D112" s="62" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
@@ -3327,24 +3327,24 @@
         <v>159</v>
       </c>
       <c r="D3" s="2">
-        <v>15.4</v>
+        <v>14.92</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F3" s="15">
-        <v>0.18108249888642258</v>
+        <v>0.19458617050699911</v>
       </c>
       <c r="G3" s="15">
         <f t="shared" ref="G3:G5" si="0">F3 - $C$10</f>
-        <v>0.18108249888642258</v>
+        <v>0.19458617050699911</v>
       </c>
       <c r="H3" s="15">
         <f t="shared" ref="H3:H5" si="1">F3 - $C$11</f>
-        <v>0.18108249888642258</v>
+        <v>0.19458617050699911</v>
       </c>
       <c r="I3" s="15">
-        <v>0.27162374832963387</v>
+        <v>0.29187925576049867</v>
       </c>
       <c r="J3" s="2">
         <v>14.733437767356989</v>
@@ -3353,10 +3353,10 @@
         <v>20.508980461992877</v>
       </c>
       <c r="L3" s="4">
-        <v>0.11220688437465126</v>
+        <v>0.11581675733040411</v>
       </c>
       <c r="M3" s="4">
-        <v>8.8311688311688313E-2</v>
+        <v>9.1152815013404831E-2</v>
       </c>
       <c r="N3" s="13" t="s">
         <v>161</v>
@@ -3379,24 +3379,24 @@
         <v>165</v>
       </c>
       <c r="D4" s="2">
-        <v>7.88</v>
+        <v>7.63</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F4" s="15">
-        <v>0.11953198379323582</v>
+        <v>0.132459340913061</v>
       </c>
       <c r="G4" s="15">
         <f t="shared" si="0"/>
-        <v>0.11953198379323582</v>
+        <v>0.132459340913061</v>
       </c>
       <c r="H4" s="15">
         <f t="shared" si="1"/>
-        <v>0.11953198379323582</v>
+        <v>0.132459340913061</v>
       </c>
       <c r="I4" s="15">
-        <v>0.17929797568985373</v>
+        <v>0.1986890113695915</v>
       </c>
       <c r="J4" s="2">
         <v>6.4883606756817951</v>
@@ -3405,10 +3405,10 @@
         <v>9.1006872475781417</v>
       </c>
       <c r="L4" s="4">
-        <v>3.9200301012977792E-2</v>
+        <v>4.0484714545513105E-2</v>
       </c>
       <c r="M4" s="4">
-        <v>7.3604060913705582E-2</v>
+        <v>7.6015727391874177E-2</v>
       </c>
       <c r="N4" s="13" t="s">
         <v>166</v>
@@ -3431,36 +3431,36 @@
         <v>169</v>
       </c>
       <c r="D5" s="2">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F5" s="15">
-        <v>6.6927308782200656E-2</v>
+        <v>6.9712118192507999E-2</v>
       </c>
       <c r="G5" s="15">
         <f t="shared" si="0"/>
-        <v>6.6927308782200656E-2</v>
+        <v>6.9712118192507999E-2</v>
       </c>
       <c r="H5" s="15">
         <f t="shared" si="1"/>
-        <v>6.6927308782200656E-2</v>
+        <v>6.9712118192507999E-2</v>
       </c>
       <c r="I5" s="15">
         <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>1.5407576206248625</v>
+        <v>1.5378583879236705</v>
       </c>
       <c r="K5" s="2">
-        <v>2.2336371684397625</v>
+        <v>2.2286272943321026</v>
       </c>
       <c r="L5" s="4">
-        <v>2.1775925005107808E-2</v>
+        <v>2.1931093474110992E-2</v>
       </c>
       <c r="M5" s="4">
-        <v>5.4790697674418611E-2</v>
+        <v>5.5305164319248833E-2</v>
       </c>
       <c r="N5" s="13" t="s">
         <v>170</v>
@@ -5677,14 +5677,14 @@
         <v>22</v>
       </c>
       <c r="C4" s="34">
-        <v>4.2500000000000003E-2</v>
+        <v>4.0599999999999997E-2</v>
       </c>
       <c r="D4" s="34">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="E4" s="35">
         <f>D4-C4</f>
-        <v>3.2499999999999994E-2</v>
+        <v>3.44E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6219,11 +6219,11 @@
         <v>231</v>
       </c>
       <c r="E5" s="72">
-        <v>5500</v>
+        <v>10000</v>
       </c>
       <c r="F5" s="72">
         <f>C5*E5</f>
-        <v>84700</v>
+        <v>154000</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="F8" s="73">
         <f>SUM(F3:F7)</f>
-        <v>1110300</v>
+        <v>1179600</v>
       </c>
     </row>
     <row r="9" spans="1:6">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2241CF05-457C-4A8A-B3BD-709D3FE17A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3547F1B7-3AC7-4D2A-94F2-7E75B7942DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
     <sheet name="Opportunities" sheetId="1" r:id="rId2"/>
     <sheet name="Aux&gt;" sheetId="8" r:id="rId3"/>
     <sheet name="Market_Yield" sheetId="2" r:id="rId4"/>
-    <sheet name="Comp_Group" sheetId="6" r:id="rId5"/>
-    <sheet name="Holdings" sheetId="7" r:id="rId6"/>
+    <sheet name="Holdings" sheetId="7" r:id="rId5"/>
+    <sheet name="Comp_Group" sheetId="6" r:id="rId6"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId7"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="244">
   <si>
     <t>Name</t>
   </si>
@@ -1553,6 +1553,15 @@
       <t>: This plan employs a value investing framework, defining true risk as the potential for permanent capital loss due to deteriorating business fundamentals or overvaluation, rather than short-term price volatility (beta). The model uses a standardized base cost of equity as the discount rate in DCF analysis,which serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium to account for ownership risks.</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0857.HK</t>
+  </si>
+  <si>
+    <t>中国石油股份</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negative Growth </t>
   </si>
 </sst>
 </file>
@@ -3140,7 +3149,7 @@
         <v>176</v>
       </c>
       <c r="C111" s="44">
-        <v>0.50943173286990984</v>
+        <v>0.30000000000000004</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -3148,11 +3157,11 @@
         <v>177</v>
       </c>
       <c r="C112" s="44">
-        <v>0.10068927690556406</v>
+        <v>0.15242394233525719</v>
       </c>
       <c r="D112" s="62" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
-        <v>Warning: Return is lower than the Benchmark.</v>
+        <v/>
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
@@ -3321,48 +3330,48 @@
     </row>
     <row r="3" spans="1:17">
       <c r="B3" s="11" t="s">
-        <v>158</v>
+        <v>241</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>159</v>
+        <v>242</v>
       </c>
       <c r="D3" s="2">
-        <v>14.92</v>
+        <v>5.39</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F3" s="15">
-        <v>0.19458617050699911</v>
+        <v>0.22246108266706432</v>
       </c>
       <c r="G3" s="15">
-        <f t="shared" ref="G3:G5" si="0">F3 - $C$10</f>
-        <v>0.19458617050699911</v>
+        <f t="shared" ref="G3:G6" si="0">F3 - $C$10</f>
+        <v>0.22246108266706432</v>
       </c>
       <c r="H3" s="15">
-        <f t="shared" ref="H3:H5" si="1">F3 - $C$11</f>
-        <v>0.19458617050699911</v>
+        <f t="shared" ref="H3:H6" si="1">F3 - $C$11</f>
+        <v>0.22246108266706432</v>
       </c>
       <c r="I3" s="15">
-        <v>0.29187925576049867</v>
+        <v>0.3</v>
       </c>
       <c r="J3" s="2">
-        <v>14.733437767356989</v>
+        <v>5.6787033353656637</v>
       </c>
       <c r="K3" s="2">
-        <v>20.508980461992877</v>
+        <v>8.2041395456413451</v>
       </c>
       <c r="L3" s="4">
-        <v>0.11581675733040411</v>
+        <v>0.14227671203700865</v>
       </c>
       <c r="M3" s="4">
-        <v>9.1152815013404831E-2</v>
+        <v>8.1992488015582468E-2</v>
       </c>
       <c r="N3" s="13" t="s">
         <v>161</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>162</v>
+        <v>243</v>
       </c>
       <c r="P3" s="14">
         <v>45716</v>
@@ -3373,48 +3382,48 @@
     </row>
     <row r="4" spans="1:17">
       <c r="B4" s="11" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D4" s="2">
-        <v>7.63</v>
+        <v>14.44</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F4" s="15">
-        <v>0.132459340913061</v>
+        <v>0.20871253483792285</v>
       </c>
       <c r="G4" s="15">
         <f t="shared" si="0"/>
-        <v>0.132459340913061</v>
+        <v>0.20871253483792285</v>
       </c>
       <c r="H4" s="15">
         <f t="shared" si="1"/>
-        <v>0.132459340913061</v>
+        <v>0.20871253483792285</v>
       </c>
       <c r="I4" s="15">
-        <v>0.1986890113695915</v>
+        <v>0.3</v>
       </c>
       <c r="J4" s="2">
-        <v>6.4883606756817951</v>
+        <v>14.733437767356989</v>
       </c>
       <c r="K4" s="2">
-        <v>9.1006872475781417</v>
+        <v>20.508980461992877</v>
       </c>
       <c r="L4" s="4">
-        <v>4.0484714545513105E-2</v>
+        <v>0.11966662184000204</v>
       </c>
       <c r="M4" s="4">
-        <v>7.6015727391874177E-2</v>
+        <v>9.418282548476456E-2</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="P4" s="14">
         <v>45716</v>
@@ -3425,65 +3434,107 @@
     </row>
     <row r="5" spans="1:17">
       <c r="B5" s="11" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D5" s="2">
-        <v>2.13</v>
+        <v>7.73</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F5" s="15">
-        <v>6.9712118192507999E-2</v>
+        <v>0.12721857083761035</v>
       </c>
       <c r="G5" s="15">
         <f t="shared" si="0"/>
-        <v>6.9712118192507999E-2</v>
+        <v>0.12721857083761035</v>
       </c>
       <c r="H5" s="15">
         <f t="shared" si="1"/>
-        <v>6.9712118192507999E-2</v>
+        <v>0.12721857083761035</v>
       </c>
       <c r="I5" s="15">
-        <v>0</v>
+        <v>9.9999999999999978E-2</v>
       </c>
       <c r="J5" s="2">
-        <v>1.5378583879236705</v>
+        <v>6.4883606756817951</v>
       </c>
       <c r="K5" s="2">
-        <v>2.2286272943321026</v>
+        <v>9.1006872475781417</v>
       </c>
       <c r="L5" s="4">
-        <v>2.1931093474110992E-2</v>
+        <v>3.9960979557860932E-2</v>
       </c>
       <c r="M5" s="4">
-        <v>5.5305164319248833E-2</v>
+        <v>7.5032341526520038E-2</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="P5" s="14">
         <v>45716</v>
       </c>
       <c r="Q5" s="11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="B6" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1.98</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="F6" s="15">
+        <v>9.7593325788780882E-2</v>
+      </c>
+      <c r="G6" s="15">
+        <f t="shared" si="0"/>
+        <v>9.7593325788780882E-2</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" si="1"/>
+        <v>9.7593325788780882E-2</v>
+      </c>
+      <c r="I6" s="15">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1.5381369358980914</v>
+      </c>
+      <c r="K6" s="2">
+        <v>2.2291086252319019</v>
+      </c>
+      <c r="L6" s="4">
+        <v>2.359763538126574E-2</v>
+      </c>
+      <c r="M6" s="4">
+        <v>5.9494949494949496E-2</v>
+      </c>
+      <c r="N6" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="P6" s="14">
+        <v>45716</v>
+      </c>
+      <c r="Q6" s="11" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="E6" s="12"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="14"/>
     </row>
     <row r="7" spans="1:17">
       <c r="B7" s="11"/>
@@ -5897,248 +5948,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE447BDC-FAEF-412F-B13E-867203D1820E}">
-  <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="11.65"/>
-  <cols>
-    <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.19921875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="34.265625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.796875" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.06640625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="B1" s="20" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="5"/>
-      <c r="B2" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="B3" s="84" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="B5" s="85" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="B6" s="85" t="s">
-        <v>107</v>
-      </c>
-      <c r="C6" s="78"/>
-      <c r="D6" s="78"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="B8" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="5"/>
-      <c r="B10" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="B11" s="84" t="s">
-        <v>109</v>
-      </c>
-      <c r="C11" s="84"/>
-      <c r="D11" s="84"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="B12" s="84" t="s">
-        <v>110</v>
-      </c>
-      <c r="C12" s="84"/>
-      <c r="D12" s="84"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="B14" s="23" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="12.4">
-      <c r="B16" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="B17" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="B18" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="B19" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="B20" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="C20" s="26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="B21" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="B22" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="B23" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="C23" s="26" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="B24" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="C24" s="26" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="B25" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="C25" s="26" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="5"/>
-      <c r="B27" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="B28" s="84" t="s">
-        <v>122</v>
-      </c>
-      <c r="C28" s="84"/>
-      <c r="D28" s="84"/>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="B29" s="84" t="s">
-        <v>123</v>
-      </c>
-      <c r="C29" s="84"/>
-      <c r="D29" s="84"/>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="5"/>
-      <c r="B31" s="6" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="B32" s="23" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="B33" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="B35" s="23" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="B36" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="5"/>
-      <c r="B38" s="6" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="B39" s="24" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="B40" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="B41" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-  </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D81F047E-EC38-4C3A-BA81-E6C9549453D6}">
   <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
@@ -6426,4 +6235,246 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE447BDC-FAEF-412F-B13E-867203D1820E}">
+  <dimension ref="A1:D41"/>
+  <sheetFormatPr defaultRowHeight="11.65"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.19921875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="34.265625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.796875" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.06640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="B1" s="20" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="5"/>
+      <c r="B2" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="B3" s="84" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="B5" s="85" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="B6" s="85" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="78"/>
+      <c r="D6" s="78"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="B8" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="5"/>
+      <c r="B10" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="B11" s="84" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" s="84"/>
+      <c r="D11" s="84"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="B12" s="84" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12" s="84"/>
+      <c r="D12" s="84"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="B14" s="23" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="12.4">
+      <c r="B16" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="B17" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="B18" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="B19" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="B20" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="B21" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="B22" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="B23" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="B24" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="C24" s="26" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="B25" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="5"/>
+      <c r="B27" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="B28" s="84" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" s="84"/>
+      <c r="D28" s="84"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="B29" s="84" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29" s="84"/>
+      <c r="D29" s="84"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="5"/>
+      <c r="B31" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="B33" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="B35" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="B36" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="5"/>
+      <c r="B38" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="B39" s="24" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="B40" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="B41" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3547F1B7-3AC7-4D2A-94F2-7E75B7942DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79853F8B-94D1-40B8-87DC-823818918ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="248">
   <si>
     <t>Name</t>
   </si>
@@ -1562,6 +1562,18 @@
   </si>
   <si>
     <t xml:space="preserve">Negative Growth </t>
+  </si>
+  <si>
+    <t>ENG_01</t>
+  </si>
+  <si>
+    <t>0168.HK</t>
+  </si>
+  <si>
+    <t>青島啤酒股份</t>
+  </si>
+  <si>
+    <t>CNS_03</t>
   </si>
 </sst>
 </file>
@@ -2084,17 +2096,17 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2529,12 +2541,12 @@
       <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B4" s="76" t="s">
+      <c r="B4" s="75" t="s">
         <v>222</v>
       </c>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="20" t="s">
@@ -2546,12 +2558,12 @@
       <c r="C6" s="62"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="75" t="s">
         <v>210</v>
       </c>
-      <c r="C7" s="76"/>
-      <c r="D7" s="76"/>
-      <c r="E7" s="76"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="23" t="s">
@@ -2640,12 +2652,12 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
-      <c r="B24" s="76" t="s">
+      <c r="B24" s="75" t="s">
         <v>221</v>
       </c>
-      <c r="C24" s="76"/>
-      <c r="D24" s="76"/>
-      <c r="E24" s="76"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="75"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
@@ -2739,20 +2751,20 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="B39" s="76" t="s">
+      <c r="B39" s="75" t="s">
         <v>156</v>
       </c>
-      <c r="C39" s="76"/>
-      <c r="D39" s="76"/>
-      <c r="E39" s="76"/>
+      <c r="C39" s="75"/>
+      <c r="D39" s="75"/>
+      <c r="E39" s="75"/>
     </row>
     <row r="40" spans="1:5" ht="46.6" customHeight="1">
-      <c r="B40" s="76" t="s">
+      <c r="B40" s="75" t="s">
         <v>240</v>
       </c>
-      <c r="C40" s="76"/>
-      <c r="D40" s="76"/>
-      <c r="E40" s="76"/>
+      <c r="C40" s="75"/>
+      <c r="D40" s="75"/>
+      <c r="E40" s="75"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="21" t="s">
@@ -2764,12 +2776,12 @@
       <c r="E42" s="21"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="B44" s="76" t="s">
+      <c r="B44" s="75" t="s">
         <v>209</v>
       </c>
-      <c r="C44" s="76"/>
-      <c r="D44" s="76"/>
-      <c r="E44" s="76"/>
+      <c r="C44" s="75"/>
+      <c r="D44" s="75"/>
+      <c r="E44" s="75"/>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="23" t="s">
@@ -2954,12 +2966,12 @@
       <c r="E69" s="21"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="B71" s="76" t="s">
+      <c r="B71" s="75" t="s">
         <v>197</v>
       </c>
-      <c r="C71" s="76"/>
-      <c r="D71" s="76"/>
-      <c r="E71" s="76"/>
+      <c r="C71" s="75"/>
+      <c r="D71" s="75"/>
+      <c r="E71" s="75"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="28" t="s">
@@ -3021,36 +3033,36 @@
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="B85" s="77" t="s">
+      <c r="B85" s="78" t="s">
         <v>193</v>
       </c>
-      <c r="C85" s="77"/>
-      <c r="D85" s="77"/>
-      <c r="E85" s="77"/>
+      <c r="C85" s="78"/>
+      <c r="D85" s="78"/>
+      <c r="E85" s="78"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="B86" s="75" t="s">
+      <c r="B86" s="77" t="s">
         <v>191</v>
       </c>
-      <c r="C86" s="75"/>
-      <c r="D86" s="75"/>
-      <c r="E86" s="75"/>
+      <c r="C86" s="77"/>
+      <c r="D86" s="77"/>
+      <c r="E86" s="77"/>
     </row>
     <row r="87" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B87" s="76" t="s">
+      <c r="B87" s="75" t="s">
         <v>190</v>
       </c>
-      <c r="C87" s="76"/>
-      <c r="D87" s="76"/>
-      <c r="E87" s="76"/>
+      <c r="C87" s="75"/>
+      <c r="D87" s="75"/>
+      <c r="E87" s="75"/>
     </row>
     <row r="88" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B88" s="76" t="s">
+      <c r="B88" s="75" t="s">
         <v>226</v>
       </c>
-      <c r="C88" s="76"/>
-      <c r="D88" s="76"/>
-      <c r="E88" s="76"/>
+      <c r="C88" s="75"/>
+      <c r="D88" s="75"/>
+      <c r="E88" s="75"/>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="24" t="s">
@@ -3083,12 +3095,12 @@
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="B97" s="78" t="s">
+      <c r="B97" s="76" t="s">
         <v>212</v>
       </c>
-      <c r="C97" s="78"/>
-      <c r="D97" s="78"/>
-      <c r="E97" s="78"/>
+      <c r="C97" s="76"/>
+      <c r="D97" s="76"/>
+      <c r="E97" s="76"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
@@ -3096,20 +3108,20 @@
       </c>
     </row>
     <row r="100" spans="1:5" ht="12.4">
-      <c r="B100" s="78" t="s">
+      <c r="B100" s="76" t="s">
         <v>213</v>
       </c>
-      <c r="C100" s="78"/>
-      <c r="D100" s="78"/>
-      <c r="E100" s="78"/>
+      <c r="C100" s="76"/>
+      <c r="D100" s="76"/>
+      <c r="E100" s="76"/>
     </row>
     <row r="101" spans="1:5" ht="58.5" customHeight="1">
-      <c r="B101" s="76" t="s">
+      <c r="B101" s="75" t="s">
         <v>220</v>
       </c>
-      <c r="C101" s="76"/>
-      <c r="D101" s="76"/>
-      <c r="E101" s="76"/>
+      <c r="C101" s="75"/>
+      <c r="D101" s="75"/>
+      <c r="E101" s="75"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="28" t="s">
@@ -3165,12 +3177,12 @@
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B114" s="76" t="s">
+      <c r="B114" s="75" t="s">
         <v>218</v>
       </c>
-      <c r="C114" s="76"/>
-      <c r="D114" s="76"/>
-      <c r="E114" s="76"/>
+      <c r="C114" s="75"/>
+      <c r="D114" s="75"/>
+      <c r="E114" s="75"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="21" t="s">
@@ -3203,12 +3215,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
     <mergeCell ref="B86:E86"/>
     <mergeCell ref="B71:E71"/>
     <mergeCell ref="B85:E85"/>
@@ -3218,6 +3224,12 @@
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3345,11 +3357,11 @@
         <v>0.22246108266706432</v>
       </c>
       <c r="G3" s="15">
-        <f t="shared" ref="G3:G6" si="0">F3 - $C$10</f>
+        <f t="shared" ref="G3:G7" si="0">F3 - $C$10</f>
         <v>0.22246108266706432</v>
       </c>
       <c r="H3" s="15">
-        <f t="shared" ref="H3:H6" si="1">F3 - $C$11</f>
+        <f t="shared" ref="H3:H7" si="1">F3 - $C$11</f>
         <v>0.22246108266706432</v>
       </c>
       <c r="I3" s="15">
@@ -3368,7 +3380,7 @@
         <v>8.1992488015582468E-2</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>161</v>
+        <v>244</v>
       </c>
       <c r="O3" s="11" t="s">
         <v>243</v>
@@ -3537,14 +3549,56 @@
       </c>
     </row>
     <row r="7" spans="1:17">
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="E7" s="12"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="14"/>
+      <c r="B7" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="D7" s="2">
+        <v>54.75</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="F7" s="15">
+        <v>-5.7047688184643786E-2</v>
+      </c>
+      <c r="G7" s="15">
+        <f t="shared" si="0"/>
+        <v>-5.7047688184643786E-2</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="1"/>
+        <v>-5.7047688184643786E-2</v>
+      </c>
+      <c r="I7" s="15">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>27.658966981315359</v>
+      </c>
+      <c r="K7" s="2">
+        <v>39.277358206848447</v>
+      </c>
+      <c r="L7" s="4">
+        <v>3.6256932844595753E-2</v>
+      </c>
+      <c r="M7" s="4">
+        <v>4.2738405022151121E-2</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="O7" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="P7" s="14">
+        <v>45900</v>
+      </c>
+      <c r="Q7" s="11" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="8" spans="1:17">
       <c r="B8" s="11"/>
@@ -6271,15 +6325,15 @@
       <c r="B5" s="85" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="85" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="78"/>
-      <c r="D6" s="78"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="76"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79853F8B-94D1-40B8-87DC-823818918ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69BA2C08-964F-4B5F-815A-ED799F5A3906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="246">
   <si>
     <t>Name</t>
   </si>
@@ -983,9 +983,6 @@
   </si>
   <si>
     <t>Low Growth Asset Play</t>
-  </si>
-  <si>
-    <t>N</t>
   </si>
   <si>
     <t>Portfolio Management Plan</t>
@@ -1519,14 +1516,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Cash in Mainland</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CNY</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Market Value (HKD)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1574,6 +1563,10 @@
   </si>
   <si>
     <t>CNS_03</t>
+  </si>
+  <si>
+    <t>0857.HK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2096,17 +2089,17 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2528,7 +2521,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2541,29 +2534,29 @@
       <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B4" s="75" t="s">
-        <v>222</v>
-      </c>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
+      <c r="B4" s="76" t="s">
+        <v>221</v>
+      </c>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="20" t="s">
         <v>66</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C6" s="62"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" s="75" t="s">
-        <v>210</v>
-      </c>
-      <c r="C7" s="75"/>
-      <c r="D7" s="75"/>
-      <c r="E7" s="75"/>
+      <c r="B7" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="C7" s="76"/>
+      <c r="D7" s="76"/>
+      <c r="E7" s="76"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="23" t="s">
@@ -2599,10 +2592,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="B14" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2638,7 +2631,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="B21" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2646,18 +2639,18 @@
         <v>67</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C23" s="62"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
-      <c r="B24" s="75" t="s">
-        <v>221</v>
-      </c>
-      <c r="C24" s="75"/>
-      <c r="D24" s="75"/>
-      <c r="E24" s="75"/>
+      <c r="B24" s="76" t="s">
+        <v>220</v>
+      </c>
+      <c r="C24" s="76"/>
+      <c r="D24" s="76"/>
+      <c r="E24" s="76"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
@@ -2727,7 +2720,7 @@
         <v>16</v>
       </c>
       <c r="C35" s="48">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="D35" s="18" t="s">
         <v>56</v>
@@ -2751,24 +2744,24 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="B39" s="75" t="s">
+      <c r="B39" s="76" t="s">
         <v>156</v>
       </c>
-      <c r="C39" s="75"/>
-      <c r="D39" s="75"/>
-      <c r="E39" s="75"/>
+      <c r="C39" s="76"/>
+      <c r="D39" s="76"/>
+      <c r="E39" s="76"/>
     </row>
     <row r="40" spans="1:5" ht="46.6" customHeight="1">
-      <c r="B40" s="75" t="s">
-        <v>240</v>
-      </c>
-      <c r="C40" s="75"/>
-      <c r="D40" s="75"/>
-      <c r="E40" s="75"/>
+      <c r="B40" s="76" t="s">
+        <v>237</v>
+      </c>
+      <c r="C40" s="76"/>
+      <c r="D40" s="76"/>
+      <c r="E40" s="76"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B42" s="21"/>
       <c r="C42" s="21"/>
@@ -2776,12 +2769,12 @@
       <c r="E42" s="21"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="B44" s="75" t="s">
-        <v>209</v>
-      </c>
-      <c r="C44" s="75"/>
-      <c r="D44" s="75"/>
-      <c r="E44" s="75"/>
+      <c r="B44" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="C44" s="76"/>
+      <c r="D44" s="76"/>
+      <c r="E44" s="76"/>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="23" t="s">
@@ -2793,7 +2786,7 @@
         <v>93</v>
       </c>
       <c r="C48" s="51" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D48" s="57"/>
       <c r="E48" s="57"/>
@@ -2826,7 +2819,7 @@
         <v>0.2</v>
       </c>
       <c r="D51" s="63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E51" s="56"/>
     </row>
@@ -2916,7 +2909,7 @@
     </row>
     <row r="61" spans="2:5" ht="12" thickBot="1">
       <c r="D61" s="42" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E61" s="43">
         <f>IF(E60&lt;=2,C49,IF(E60&gt;=6,C51,C50))</f>
@@ -2926,25 +2919,25 @@
     <row r="62" spans="2:5" ht="12" thickTop="1"/>
     <row r="63" spans="2:5">
       <c r="B63" s="23" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="64" spans="2:5">
       <c r="B64" s="54" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C64" s="55">
         <f>-E61*(C35-Cash_Yield)</f>
-        <v>-4.965E-2</v>
+        <v>-6.4649999999999999E-2</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="B65" s="54" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C65" s="55">
         <f>C35+C64</f>
-        <v>0.15035000000000001</v>
+        <v>0.18535000000000001</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2953,7 +2946,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="B67" s="39" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2966,29 +2959,29 @@
       <c r="E69" s="21"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="B71" s="75" t="s">
-        <v>197</v>
-      </c>
-      <c r="C71" s="75"/>
-      <c r="D71" s="75"/>
-      <c r="E71" s="75"/>
+      <c r="B71" s="76" t="s">
+        <v>196</v>
+      </c>
+      <c r="C71" s="76"/>
+      <c r="D71" s="76"/>
+      <c r="E71" s="76"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="28" t="s">
         <v>66</v>
       </c>
       <c r="B73" s="20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="B74" s="24" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="B75" s="24" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2996,27 +2989,27 @@
         <v>128</v>
       </c>
       <c r="B77" s="20" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="B78" s="39" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="B79" s="24" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="B80" s="24" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="B81" s="24" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -3024,131 +3017,131 @@
         <v>146</v>
       </c>
       <c r="B83" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="B84" s="24" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="B85" s="77" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="B85" s="78" t="s">
-        <v>193</v>
-      </c>
-      <c r="C85" s="78"/>
-      <c r="D85" s="78"/>
-      <c r="E85" s="78"/>
+      <c r="C85" s="77"/>
+      <c r="D85" s="77"/>
+      <c r="E85" s="77"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="B86" s="77" t="s">
-        <v>191</v>
-      </c>
-      <c r="C86" s="77"/>
-      <c r="D86" s="77"/>
-      <c r="E86" s="77"/>
+      <c r="B86" s="75" t="s">
+        <v>190</v>
+      </c>
+      <c r="C86" s="75"/>
+      <c r="D86" s="75"/>
+      <c r="E86" s="75"/>
     </row>
     <row r="87" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B87" s="75" t="s">
-        <v>190</v>
-      </c>
-      <c r="C87" s="75"/>
-      <c r="D87" s="75"/>
-      <c r="E87" s="75"/>
+      <c r="B87" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="C87" s="76"/>
+      <c r="D87" s="76"/>
+      <c r="E87" s="76"/>
     </row>
     <row r="88" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B88" s="75" t="s">
-        <v>226</v>
-      </c>
-      <c r="C88" s="75"/>
-      <c r="D88" s="75"/>
-      <c r="E88" s="75"/>
+      <c r="B88" s="76" t="s">
+        <v>225</v>
+      </c>
+      <c r="C88" s="76"/>
+      <c r="D88" s="76"/>
+      <c r="E88" s="76"/>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="B91" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="B92" s="61" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="B93" s="24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="B94" s="24" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="B96" s="24" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="B97" s="78" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="97" spans="1:5">
-      <c r="B97" s="76" t="s">
-        <v>212</v>
-      </c>
-      <c r="C97" s="76"/>
-      <c r="D97" s="76"/>
-      <c r="E97" s="76"/>
+      <c r="C97" s="78"/>
+      <c r="D97" s="78"/>
+      <c r="E97" s="78"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="12.4">
-      <c r="B100" s="76" t="s">
-        <v>213</v>
-      </c>
-      <c r="C100" s="76"/>
-      <c r="D100" s="76"/>
-      <c r="E100" s="76"/>
+      <c r="B100" s="78" t="s">
+        <v>212</v>
+      </c>
+      <c r="C100" s="78"/>
+      <c r="D100" s="78"/>
+      <c r="E100" s="78"/>
     </row>
     <row r="101" spans="1:5" ht="58.5" customHeight="1">
-      <c r="B101" s="75" t="s">
-        <v>220</v>
-      </c>
-      <c r="C101" s="75"/>
-      <c r="D101" s="75"/>
-      <c r="E101" s="75"/>
+      <c r="B101" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="C101" s="76"/>
+      <c r="D101" s="76"/>
+      <c r="E101" s="76"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="28" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B103" s="20" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="B104" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="B105" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="B107" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="B108" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -3158,7 +3151,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="B111" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C111" s="44">
         <v>0.30000000000000004</v>
@@ -3166,10 +3159,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="B112" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C112" s="44">
-        <v>0.15242394233525719</v>
+        <v>0.14354416065775896</v>
       </c>
       <c r="D112" s="62" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
@@ -3177,12 +3170,12 @@
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B114" s="75" t="s">
-        <v>218</v>
-      </c>
-      <c r="C114" s="75"/>
-      <c r="D114" s="75"/>
-      <c r="E114" s="75"/>
+      <c r="B114" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="C114" s="76"/>
+      <c r="D114" s="76"/>
+      <c r="E114" s="76"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="21" t="s">
@@ -3210,11 +3203,17 @@
     </row>
     <row r="121" spans="1:5">
       <c r="B121" s="24" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
     <mergeCell ref="B86:E86"/>
     <mergeCell ref="B71:E71"/>
     <mergeCell ref="B85:E85"/>
@@ -3224,12 +3223,6 @@
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3313,7 +3306,7 @@
         <v>62</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>8</v>
@@ -3342,51 +3335,51 @@
     </row>
     <row r="3" spans="1:17">
       <c r="B3" s="11" t="s">
-        <v>241</v>
+        <v>158</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>242</v>
+        <v>159</v>
       </c>
       <c r="D3" s="2">
-        <v>5.39</v>
+        <v>14.44</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F3" s="15">
-        <v>0.22246108266706432</v>
+        <v>0.20871253483792285</v>
       </c>
       <c r="G3" s="15">
-        <f t="shared" ref="G3:G7" si="0">F3 - $C$10</f>
-        <v>0.22246108266706432</v>
+        <f>F3 - Portfolio_Mgmt!$C$10</f>
+        <v>9.1312534837922843E-2</v>
       </c>
       <c r="H3" s="15">
-        <f t="shared" ref="H3:H7" si="1">F3 - $C$11</f>
-        <v>0.22246108266706432</v>
+        <f>F3 - Portfolio_Mgmt!$C$11</f>
+        <v>0.17421253483792284</v>
       </c>
       <c r="I3" s="15">
-        <v>0.3</v>
+        <v>0.25045504180550743</v>
       </c>
       <c r="J3" s="2">
-        <v>5.6787033353656637</v>
+        <v>13.155317996540354</v>
       </c>
       <c r="K3" s="2">
-        <v>8.2041395456413451</v>
+        <v>20.508980461992877</v>
       </c>
       <c r="L3" s="4">
-        <v>0.14227671203700865</v>
+        <v>0.11966662184000204</v>
       </c>
       <c r="M3" s="4">
-        <v>8.1992488015582468E-2</v>
+        <v>9.418282548476456E-2</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>244</v>
+        <v>161</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>243</v>
+        <v>162</v>
       </c>
       <c r="P3" s="14">
-        <v>45716</v>
+        <v>45808</v>
       </c>
       <c r="Q3" s="11" t="s">
         <v>163</v>
@@ -3394,51 +3387,51 @@
     </row>
     <row r="4" spans="1:17">
       <c r="B4" s="11" t="s">
-        <v>158</v>
+        <v>238</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>159</v>
+        <v>239</v>
       </c>
       <c r="D4" s="2">
-        <v>14.44</v>
+        <v>5.38</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F4" s="15">
-        <v>0.20871253483792285</v>
+        <v>0.20806555381768388</v>
       </c>
       <c r="G4" s="15">
-        <f t="shared" si="0"/>
-        <v>0.20871253483792285</v>
+        <f>F4 - Portfolio_Mgmt!$C$10</f>
+        <v>9.0665553817683875E-2</v>
       </c>
       <c r="H4" s="15">
-        <f t="shared" si="1"/>
-        <v>0.20871253483792285</v>
+        <f>F4 - Portfolio_Mgmt!$C$11</f>
+        <v>0.17356555381768388</v>
       </c>
       <c r="I4" s="15">
-        <v>0.3</v>
+        <v>0.24967866458122065</v>
       </c>
       <c r="J4" s="2">
-        <v>14.733437767356989</v>
+        <v>4.8893162027611039</v>
       </c>
       <c r="K4" s="2">
-        <v>20.508980461992877</v>
+        <v>7.8645513251025703</v>
       </c>
       <c r="L4" s="4">
-        <v>0.11966662184000204</v>
+        <v>0.14200427847492361</v>
       </c>
       <c r="M4" s="4">
-        <v>9.418282548476456E-2</v>
+        <v>8.2144890409663482E-2</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>161</v>
+        <v>241</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>162</v>
+        <v>240</v>
       </c>
       <c r="P4" s="14">
-        <v>45716</v>
+        <v>45900</v>
       </c>
       <c r="Q4" s="11" t="s">
         <v>163</v>
@@ -3446,51 +3439,51 @@
     </row>
     <row r="5" spans="1:17">
       <c r="B5" s="11" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D5" s="2">
-        <v>7.73</v>
+        <v>2.04</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F5" s="15">
-        <v>0.12721857083761035</v>
+        <v>0.14703263371672559</v>
       </c>
       <c r="G5" s="15">
-        <f t="shared" si="0"/>
-        <v>0.12721857083761035</v>
+        <f>F5 - Portfolio_Mgmt!$C$10</f>
+        <v>2.9632633716725587E-2</v>
       </c>
       <c r="H5" s="15">
-        <f t="shared" si="1"/>
-        <v>0.12721857083761035</v>
+        <f>F5 - Portfolio_Mgmt!$C$11</f>
+        <v>0.11253263371672559</v>
       </c>
       <c r="I5" s="15">
-        <v>9.9999999999999978E-2</v>
+        <v>0.17643916046007072</v>
       </c>
       <c r="J5" s="2">
-        <v>6.4883606756817951</v>
+        <v>1.5968726986927759</v>
       </c>
       <c r="K5" s="2">
-        <v>9.1006872475781417</v>
+        <v>2.6800518466090013</v>
       </c>
       <c r="L5" s="4">
-        <v>3.9960979557860932E-2</v>
+        <v>4.0033864694300855E-2</v>
       </c>
       <c r="M5" s="4">
-        <v>7.5032341526520038E-2</v>
+        <v>5.6424319257515447E-2</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="P5" s="14">
-        <v>45716</v>
+        <v>45900</v>
       </c>
       <c r="Q5" s="11" t="s">
         <v>163</v>
@@ -3498,62 +3491,62 @@
     </row>
     <row r="6" spans="1:17">
       <c r="B6" s="11" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D6" s="2">
-        <v>1.98</v>
+        <v>7.69</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F6" s="15">
-        <v>9.7593325788780882E-2</v>
+        <v>0.12930348429833716</v>
       </c>
       <c r="G6" s="15">
-        <f t="shared" si="0"/>
-        <v>9.7593325788780882E-2</v>
+        <f>F6 - Portfolio_Mgmt!$C$10</f>
+        <v>1.1903484298337152E-2</v>
       </c>
       <c r="H6" s="15">
-        <f t="shared" si="1"/>
-        <v>9.7593325788780882E-2</v>
+        <f>F6 - Portfolio_Mgmt!$C$11</f>
+        <v>9.4803484298337154E-2</v>
       </c>
       <c r="I6" s="15">
-        <v>0</v>
+        <v>2.3427133153201218E-2</v>
       </c>
       <c r="J6" s="2">
-        <v>1.5381369358980914</v>
+        <v>5.7917118707600084</v>
       </c>
       <c r="K6" s="2">
-        <v>2.2291086252319019</v>
+        <v>9.1006872475781417</v>
       </c>
       <c r="L6" s="4">
-        <v>2.359763538126574E-2</v>
+        <v>4.0168839009397266E-2</v>
       </c>
       <c r="M6" s="4">
-        <v>5.9494949494949496E-2</v>
+        <v>7.5422626788036407E-2</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="P6" s="14">
-        <v>45716</v>
+        <v>45900</v>
       </c>
       <c r="Q6" s="11" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="B7" s="11" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D7" s="2">
         <v>54.75</v>
@@ -3562,33 +3555,33 @@
         <v>160</v>
       </c>
       <c r="F7" s="15">
-        <v>-5.7047688184643786E-2</v>
+        <v>-2.7445446695169684E-2</v>
       </c>
       <c r="G7" s="15">
-        <f t="shared" si="0"/>
-        <v>-5.7047688184643786E-2</v>
+        <f>F7 - Portfolio_Mgmt!$C$10</f>
+        <v>-0.14484544669516969</v>
       </c>
       <c r="H7" s="15">
-        <f t="shared" si="1"/>
-        <v>-5.7047688184643786E-2</v>
+        <f>F7 - Portfolio_Mgmt!$C$11</f>
+        <v>-6.1945446695169687E-2</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>27.658966981315359</v>
+        <v>26.736896573077772</v>
       </c>
       <c r="K7" s="2">
-        <v>39.277358206848447</v>
+        <v>44.30699034342598</v>
       </c>
       <c r="L7" s="4">
-        <v>3.6256932844595753E-2</v>
+        <v>4.0850840664093072E-2</v>
       </c>
       <c r="M7" s="4">
-        <v>4.2738405022151121E-2</v>
+        <v>3.7911871371768754E-2</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="O7" s="11" t="s">
         <v>162</v>
@@ -5782,14 +5775,14 @@
         <v>22</v>
       </c>
       <c r="C4" s="34">
-        <v>4.0599999999999997E-2</v>
+        <v>4.0099999999999997E-2</v>
       </c>
       <c r="D4" s="34">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="E4" s="35">
         <f>D4-C4</f>
-        <v>3.44E-2</v>
+        <v>3.49E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6016,7 +6009,7 @@
     <row r="1" spans="1:6" ht="13.15">
       <c r="A1" s="64"/>
       <c r="B1" s="65" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="26.25">
@@ -6024,87 +6017,87 @@
         <v>3</v>
       </c>
       <c r="C2" s="67" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D2" s="67" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E2" s="67" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F2" s="67" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="B3" s="68" t="s">
+        <v>233</v>
+      </c>
+      <c r="C3" s="71" t="s">
         <v>234</v>
       </c>
-      <c r="C3" s="71" t="s">
-        <v>235</v>
-      </c>
       <c r="D3" s="68" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E3" s="72" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F3" s="72">
-        <v>580000</v>
+        <v>395673.88</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" s="68" t="s">
-        <v>237</v>
-      </c>
-      <c r="C4" s="71" t="s">
-        <v>235</v>
+        <v>232</v>
+      </c>
+      <c r="C4" s="71">
+        <v>14.62</v>
       </c>
       <c r="D4" s="68" t="s">
-        <v>238</v>
-      </c>
-      <c r="E4" s="72" t="s">
-        <v>235</v>
+        <v>230</v>
+      </c>
+      <c r="E4" s="72">
+        <v>10000</v>
       </c>
       <c r="F4" s="72">
-        <f>280000*1.02</f>
-        <v>285600</v>
+        <f>C4*E4</f>
+        <v>146200</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5" s="68" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C5" s="71">
-        <v>15.4</v>
+        <v>7.7</v>
       </c>
       <c r="D5" s="68" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E5" s="72">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="F5" s="72">
-        <f>C5*E5</f>
+        <f>E5*C5</f>
         <v>154000</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="B6" s="68" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="C6" s="71">
-        <v>8</v>
+        <v>5.37</v>
       </c>
       <c r="D6" s="68" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E6" s="72">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="F6" s="72">
         <f>E6*C6</f>
-        <v>160000</v>
+        <v>96660</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6117,11 +6110,11 @@
       <c r="C8" s="71"/>
       <c r="D8" s="68"/>
       <c r="E8" s="73" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F8" s="73">
         <f>SUM(F3:F7)</f>
-        <v>1179600</v>
+        <v>792533.88</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6288,6 +6281,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6325,15 +6319,15 @@
       <c r="B5" s="85" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="85" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
+      <c r="C6" s="78"/>
+      <c r="D6" s="78"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69BA2C08-964F-4B5F-815A-ED799F5A3906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE309A25-F26E-4DC9-8A06-0C9155EC4469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="247">
   <si>
     <t>Name</t>
   </si>
@@ -1566,6 +1566,10 @@
   </si>
   <si>
     <t>0857.HK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>%</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1919,7 +1923,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2089,6 +2093,7 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2534,12 +2539,12 @@
       <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B4" s="76" t="s">
+      <c r="B4" s="77" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="20" t="s">
@@ -2551,12 +2556,12 @@
       <c r="C6" s="62"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="77" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="76"/>
-      <c r="D7" s="76"/>
-      <c r="E7" s="76"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="23" t="s">
@@ -2645,12 +2650,12 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
-      <c r="B24" s="76" t="s">
+      <c r="B24" s="77" t="s">
         <v>220</v>
       </c>
-      <c r="C24" s="76"/>
-      <c r="D24" s="76"/>
-      <c r="E24" s="76"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="E24" s="77"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
@@ -2744,20 +2749,20 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="B39" s="76" t="s">
+      <c r="B39" s="77" t="s">
         <v>156</v>
       </c>
-      <c r="C39" s="76"/>
-      <c r="D39" s="76"/>
-      <c r="E39" s="76"/>
+      <c r="C39" s="77"/>
+      <c r="D39" s="77"/>
+      <c r="E39" s="77"/>
     </row>
     <row r="40" spans="1:5" ht="46.6" customHeight="1">
-      <c r="B40" s="76" t="s">
+      <c r="B40" s="77" t="s">
         <v>237</v>
       </c>
-      <c r="C40" s="76"/>
-      <c r="D40" s="76"/>
-      <c r="E40" s="76"/>
+      <c r="C40" s="77"/>
+      <c r="D40" s="77"/>
+      <c r="E40" s="77"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="21" t="s">
@@ -2769,12 +2774,12 @@
       <c r="E42" s="21"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="B44" s="76" t="s">
+      <c r="B44" s="77" t="s">
         <v>208</v>
       </c>
-      <c r="C44" s="76"/>
-      <c r="D44" s="76"/>
-      <c r="E44" s="76"/>
+      <c r="C44" s="77"/>
+      <c r="D44" s="77"/>
+      <c r="E44" s="77"/>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="23" t="s">
@@ -2796,7 +2801,7 @@
         <v>89</v>
       </c>
       <c r="C49" s="29">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D49" s="58"/>
       <c r="E49" s="56"/>
@@ -2806,7 +2811,7 @@
         <v>90</v>
       </c>
       <c r="C50" s="29">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D50" s="58"/>
       <c r="E50" s="56"/>
@@ -2816,7 +2821,7 @@
         <v>91</v>
       </c>
       <c r="C51" s="29">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D51" s="63" t="s">
         <v>222</v>
@@ -2913,7 +2918,7 @@
       </c>
       <c r="E61" s="43">
         <f>IF(E60&lt;=2,C49,IF(E60&gt;=6,C51,C50))</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="62" spans="2:5" ht="12" thickTop="1"/>
@@ -2928,7 +2933,7 @@
       </c>
       <c r="C64" s="55">
         <f>-E61*(C35-Cash_Yield)</f>
-        <v>-6.4649999999999999E-2</v>
+        <v>-8.6199999999999999E-2</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2937,7 +2942,7 @@
       </c>
       <c r="C65" s="55">
         <f>C35+C64</f>
-        <v>0.18535000000000001</v>
+        <v>0.1638</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2959,12 +2964,12 @@
       <c r="E69" s="21"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="B71" s="76" t="s">
+      <c r="B71" s="77" t="s">
         <v>196</v>
       </c>
-      <c r="C71" s="76"/>
-      <c r="D71" s="76"/>
-      <c r="E71" s="76"/>
+      <c r="C71" s="77"/>
+      <c r="D71" s="77"/>
+      <c r="E71" s="77"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="28" t="s">
@@ -3026,36 +3031,36 @@
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="B85" s="77" t="s">
+      <c r="B85" s="78" t="s">
         <v>192</v>
       </c>
-      <c r="C85" s="77"/>
-      <c r="D85" s="77"/>
-      <c r="E85" s="77"/>
+      <c r="C85" s="78"/>
+      <c r="D85" s="78"/>
+      <c r="E85" s="78"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="B86" s="75" t="s">
+      <c r="B86" s="76" t="s">
         <v>190</v>
       </c>
-      <c r="C86" s="75"/>
-      <c r="D86" s="75"/>
-      <c r="E86" s="75"/>
+      <c r="C86" s="76"/>
+      <c r="D86" s="76"/>
+      <c r="E86" s="76"/>
     </row>
     <row r="87" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B87" s="76" t="s">
+      <c r="B87" s="77" t="s">
         <v>189</v>
       </c>
-      <c r="C87" s="76"/>
-      <c r="D87" s="76"/>
-      <c r="E87" s="76"/>
+      <c r="C87" s="77"/>
+      <c r="D87" s="77"/>
+      <c r="E87" s="77"/>
     </row>
     <row r="88" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B88" s="76" t="s">
+      <c r="B88" s="77" t="s">
         <v>225</v>
       </c>
-      <c r="C88" s="76"/>
-      <c r="D88" s="76"/>
-      <c r="E88" s="76"/>
+      <c r="C88" s="77"/>
+      <c r="D88" s="77"/>
+      <c r="E88" s="77"/>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="24" t="s">
@@ -3088,12 +3093,12 @@
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="B97" s="78" t="s">
+      <c r="B97" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="C97" s="78"/>
-      <c r="D97" s="78"/>
-      <c r="E97" s="78"/>
+      <c r="C97" s="79"/>
+      <c r="D97" s="79"/>
+      <c r="E97" s="79"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
@@ -3101,20 +3106,20 @@
       </c>
     </row>
     <row r="100" spans="1:5" ht="12.4">
-      <c r="B100" s="78" t="s">
+      <c r="B100" s="79" t="s">
         <v>212</v>
       </c>
-      <c r="C100" s="78"/>
-      <c r="D100" s="78"/>
-      <c r="E100" s="78"/>
+      <c r="C100" s="79"/>
+      <c r="D100" s="79"/>
+      <c r="E100" s="79"/>
     </row>
     <row r="101" spans="1:5" ht="58.5" customHeight="1">
-      <c r="B101" s="76" t="s">
+      <c r="B101" s="77" t="s">
         <v>219</v>
       </c>
-      <c r="C101" s="76"/>
-      <c r="D101" s="76"/>
-      <c r="E101" s="76"/>
+      <c r="C101" s="77"/>
+      <c r="D101" s="77"/>
+      <c r="E101" s="77"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="28" t="s">
@@ -3154,7 +3159,7 @@
         <v>175</v>
       </c>
       <c r="C111" s="44">
-        <v>0.30000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -3162,7 +3167,7 @@
         <v>176</v>
       </c>
       <c r="C112" s="44">
-        <v>0.14354416065775896</v>
+        <v>0.13270624043020399</v>
       </c>
       <c r="D112" s="62" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
@@ -3170,12 +3175,12 @@
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B114" s="76" t="s">
+      <c r="B114" s="77" t="s">
         <v>217</v>
       </c>
-      <c r="C114" s="76"/>
-      <c r="D114" s="76"/>
-      <c r="E114" s="76"/>
+      <c r="C114" s="77"/>
+      <c r="D114" s="77"/>
+      <c r="E114" s="77"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="21" t="s">
@@ -3258,30 +3263,30 @@
       <c r="B1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="82" t="s">
+      <c r="D1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="83" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="84" t="s">
         <v>101</v>
       </c>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="79" t="s">
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="79"/>
-      <c r="L1" s="80" t="s">
+      <c r="K1" s="80"/>
+      <c r="L1" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="80"/>
-      <c r="N1" s="81" t="s">
+      <c r="M1" s="81"/>
+      <c r="N1" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
+      <c r="O1" s="82"/>
+      <c r="P1" s="82"/>
+      <c r="Q1" s="82"/>
     </row>
     <row r="2" spans="1:17" ht="26" customHeight="1">
       <c r="B2" s="7" t="s">
@@ -3462,7 +3467,7 @@
         <v>0.11253263371672559</v>
       </c>
       <c r="I5" s="15">
-        <v>0.17643916046007072</v>
+        <v>9.9866293613271928E-2</v>
       </c>
       <c r="J5" s="2">
         <v>1.5968726986927759</v>
@@ -3514,7 +3519,7 @@
         <v>9.4803484298337154E-2</v>
       </c>
       <c r="I6" s="15">
-        <v>2.3427133153201218E-2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2">
         <v>5.7917118707600084</v>
@@ -5996,23 +6001,24 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D81F047E-EC38-4C3A-BA81-E6C9549453D6}">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.59765625" style="66" customWidth="1"/>
     <col min="2" max="2" width="16.59765625" style="66" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9.06640625" style="66"/>
     <col min="5" max="6" width="15.59765625" style="66" customWidth="1"/>
-    <col min="7" max="16384" width="9.06640625" style="66"/>
+    <col min="7" max="7" width="9.9296875" style="66" customWidth="1"/>
+    <col min="8" max="16384" width="9.06640625" style="66"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.15">
+    <row r="1" spans="1:7" ht="13.15">
       <c r="A1" s="64"/>
       <c r="B1" s="65" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="26.25">
+    <row r="2" spans="1:7" ht="29.65" customHeight="1">
       <c r="B2" s="67" t="s">
         <v>3</v>
       </c>
@@ -6028,8 +6034,11 @@
       <c r="F2" s="67" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" s="67" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="B3" s="68" t="s">
         <v>233</v>
       </c>
@@ -6045,13 +6054,17 @@
       <c r="F3" s="72">
         <v>395673.88</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3" s="75">
+        <f>F3/$F$8</f>
+        <v>0.50576089073376196</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="B4" s="68" t="s">
         <v>232</v>
       </c>
       <c r="C4" s="71">
-        <v>14.62</v>
+        <v>14.2</v>
       </c>
       <c r="D4" s="68" t="s">
         <v>230</v>
@@ -6061,15 +6074,19 @@
       </c>
       <c r="F4" s="72">
         <f>C4*E4</f>
-        <v>146200</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>142000</v>
+      </c>
+      <c r="G4" s="75">
+        <f t="shared" ref="G4:G6" si="0">F4/$F$8</f>
+        <v>0.18150818164745722</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="B5" s="68" t="s">
         <v>231</v>
       </c>
       <c r="C5" s="71">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="D5" s="68" t="s">
         <v>230</v>
@@ -6079,10 +6096,14 @@
       </c>
       <c r="F5" s="72">
         <f>E5*C5</f>
-        <v>154000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>148000</v>
+      </c>
+      <c r="G5" s="75">
+        <f t="shared" si="0"/>
+        <v>0.18917754143537796</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="B6" s="68" t="s">
         <v>245</v>
       </c>
@@ -6099,13 +6120,17 @@
         <f>E6*C6</f>
         <v>96660</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6" s="75">
+        <f t="shared" si="0"/>
+        <v>0.12355338618340292</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="B7" s="68"/>
       <c r="C7" s="71"/>
       <c r="D7" s="68"/>
     </row>
-    <row r="8" spans="1:6" ht="13.15">
+    <row r="8" spans="1:7" ht="13.15">
       <c r="B8" s="68"/>
       <c r="C8" s="71"/>
       <c r="D8" s="68"/>
@@ -6114,59 +6139,59 @@
       </c>
       <c r="F8" s="73">
         <f>SUM(F3:F7)</f>
-        <v>792533.88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>782333.88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="B9" s="68"/>
       <c r="C9" s="71"/>
       <c r="D9" s="68"/>
       <c r="E9" s="72"/>
       <c r="F9" s="72"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="B10" s="68"/>
       <c r="C10" s="71"/>
       <c r="D10" s="68"/>
       <c r="E10" s="72"/>
       <c r="F10" s="72"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="B11" s="68"/>
       <c r="C11" s="71"/>
       <c r="D11" s="68"/>
       <c r="E11" s="72"/>
       <c r="F11" s="72"/>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:7">
       <c r="B12" s="68"/>
       <c r="C12" s="71"/>
       <c r="D12" s="68"/>
       <c r="E12" s="72"/>
       <c r="F12" s="72"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:7">
       <c r="B13" s="68"/>
       <c r="C13" s="71"/>
       <c r="D13" s="68"/>
       <c r="E13" s="72"/>
       <c r="F13" s="72"/>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:7">
       <c r="B14" s="68"/>
       <c r="C14" s="71"/>
       <c r="D14" s="68"/>
       <c r="E14" s="72"/>
       <c r="F14" s="72"/>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:7">
       <c r="B15" s="68"/>
       <c r="C15" s="71"/>
       <c r="D15" s="68"/>
       <c r="E15" s="72"/>
       <c r="F15" s="72"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:7">
       <c r="B16" s="68"/>
       <c r="C16" s="71"/>
       <c r="D16" s="68"/>
@@ -6309,25 +6334,25 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="85" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="B5" s="85" t="s">
+      <c r="B5" s="86" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="B6" s="85" t="s">
+      <c r="B6" s="86" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="78"/>
-      <c r="D6" s="78"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">
@@ -6341,18 +6366,18 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="85" t="s">
         <v>109</v>
       </c>
-      <c r="C11" s="84"/>
-      <c r="D11" s="84"/>
+      <c r="C11" s="85"/>
+      <c r="D11" s="85"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="B12" s="84" t="s">
+      <c r="B12" s="85" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="84"/>
-      <c r="D12" s="84"/>
+      <c r="C12" s="85"/>
+      <c r="D12" s="85"/>
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="23" t="s">
@@ -6446,18 +6471,18 @@
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="B28" s="84" t="s">
+      <c r="B28" s="85" t="s">
         <v>122</v>
       </c>
-      <c r="C28" s="84"/>
-      <c r="D28" s="84"/>
+      <c r="C28" s="85"/>
+      <c r="D28" s="85"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="B29" s="84" t="s">
+      <c r="B29" s="85" t="s">
         <v>123</v>
       </c>
-      <c r="C29" s="84"/>
-      <c r="D29" s="84"/>
+      <c r="C29" s="85"/>
+      <c r="D29" s="85"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="5"/>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE309A25-F26E-4DC9-8A06-0C9155EC4469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD0FE4B-0288-42B9-81CE-A292DEFA2309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="252">
   <si>
     <t>Name</t>
   </si>
@@ -1571,6 +1571,21 @@
   <si>
     <t>%</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1910.HK</t>
+  </si>
+  <si>
+    <t>新秀麗</t>
+  </si>
+  <si>
+    <t>CNS_02</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High Growth </t>
   </si>
 </sst>
 </file>
@@ -3167,7 +3182,7 @@
         <v>176</v>
       </c>
       <c r="C112" s="44">
-        <v>0.13270624043020399</v>
+        <v>0.13143938180596665</v>
       </c>
       <c r="D112" s="62" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
@@ -3398,36 +3413,36 @@
         <v>239</v>
       </c>
       <c r="D4" s="2">
-        <v>5.38</v>
+        <v>5.39</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F4" s="15">
-        <v>0.20806555381768388</v>
+        <v>0.20602353093461256</v>
       </c>
       <c r="G4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$10</f>
-        <v>9.0665553817683875E-2</v>
+        <v>8.862353093461256E-2</v>
       </c>
       <c r="H4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$11</f>
-        <v>0.17356555381768388</v>
+        <v>0.17152353093461256</v>
       </c>
       <c r="I4" s="15">
-        <v>0.24967866458122065</v>
+        <v>0.24722823712153508</v>
       </c>
       <c r="J4" s="2">
-        <v>4.8893162027611039</v>
+        <v>4.8752893604858043</v>
       </c>
       <c r="K4" s="2">
-        <v>7.8645513251025703</v>
+        <v>7.8371551487836282</v>
       </c>
       <c r="L4" s="4">
-        <v>0.14200427847492361</v>
+        <v>0.14124706534453912</v>
       </c>
       <c r="M4" s="4">
-        <v>8.2144890409663482E-2</v>
+        <v>8.1992488015582371E-2</v>
       </c>
       <c r="N4" s="13" t="s">
         <v>241</v>
@@ -3444,48 +3459,48 @@
     </row>
     <row r="5" spans="1:17">
       <c r="B5" s="11" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D5" s="2">
-        <v>2.04</v>
+        <v>7.47</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F5" s="15">
-        <v>0.14703263371672559</v>
+        <v>0.14104674835105913</v>
       </c>
       <c r="G5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$10</f>
-        <v>2.9632633716725587E-2</v>
+        <v>2.3646748351059121E-2</v>
       </c>
       <c r="H5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$11</f>
-        <v>0.11253263371672559</v>
+        <v>0.10654674835105912</v>
       </c>
       <c r="I5" s="15">
-        <v>9.9866293613271928E-2</v>
+        <v>0.10231672107295747</v>
       </c>
       <c r="J5" s="2">
-        <v>1.5968726986927759</v>
+        <v>5.7917118707600084</v>
       </c>
       <c r="K5" s="2">
-        <v>2.6800518466090013</v>
+        <v>9.1006872475781417</v>
       </c>
       <c r="L5" s="4">
-        <v>4.0033864694300855E-2</v>
+        <v>4.1351857025738292E-2</v>
       </c>
       <c r="M5" s="4">
-        <v>5.6424319257515447E-2</v>
+        <v>7.7643908969210168E-2</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="P5" s="14">
         <v>45900</v>
@@ -3496,48 +3511,48 @@
     </row>
     <row r="6" spans="1:17">
       <c r="B6" s="11" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D6" s="2">
-        <v>7.69</v>
+        <v>2.12</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F6" s="15">
-        <v>0.12930348429833716</v>
+        <v>0.13066415339637483</v>
       </c>
       <c r="G6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$10</f>
-        <v>1.1903484298337152E-2</v>
+        <v>1.3264153396374823E-2</v>
       </c>
       <c r="H6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$11</f>
-        <v>9.4803484298337154E-2</v>
+        <v>9.6164153396374824E-2</v>
       </c>
       <c r="I6" s="15">
         <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>5.7917118707600084</v>
+        <v>1.5928004364498562</v>
       </c>
       <c r="K6" s="2">
-        <v>9.1006872475781417</v>
+        <v>2.6705641652753029</v>
       </c>
       <c r="L6" s="4">
-        <v>4.0168839009397266E-2</v>
+        <v>3.8391219865680747E-2</v>
       </c>
       <c r="M6" s="4">
-        <v>7.5422626788036407E-2</v>
+        <v>5.448489788627562E-2</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="P6" s="14">
         <v>45900</v>
@@ -3548,65 +3563,107 @@
     </row>
     <row r="7" spans="1:17">
       <c r="B7" s="11" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D7" s="2">
-        <v>54.75</v>
+        <v>14.58</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F7" s="15">
-        <v>-2.7445446695169684E-2</v>
+        <v>0.1010567723303204</v>
       </c>
       <c r="G7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$10</f>
-        <v>-0.14484544669516969</v>
+        <v>-1.6343227669679605E-2</v>
       </c>
       <c r="H7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$11</f>
-        <v>-6.1945446695169687E-2</v>
+        <v>6.6556772330320396E-2</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>26.736896573077772</v>
+        <v>10.177519059641918</v>
       </c>
       <c r="K7" s="2">
-        <v>44.30699034342598</v>
+        <v>16.70033318211312</v>
       </c>
       <c r="L7" s="4">
-        <v>4.0850840664093072E-2</v>
+        <v>0.10531435381835931</v>
       </c>
       <c r="M7" s="4">
-        <v>3.7911871371768754E-2</v>
+        <v>5.7165823045267489E-2</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>162</v>
+        <v>251</v>
       </c>
       <c r="P7" s="14">
         <v>45900</v>
       </c>
       <c r="Q7" s="11" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" spans="1:17">
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="E8" s="12"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="14"/>
+      <c r="B8" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="D8" s="2">
+        <v>59.8</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="F8" s="15">
+        <v>-5.7617735553175065E-2</v>
+      </c>
+      <c r="G8" s="15">
+        <f>F8 - Portfolio_Mgmt!$C$10</f>
+        <v>-0.17501773555317507</v>
+      </c>
+      <c r="H8" s="15">
+        <f>F8 - Portfolio_Mgmt!$C$11</f>
+        <v>-9.2117735553175067E-2</v>
+      </c>
+      <c r="I8" s="15">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>26.67162630902984</v>
+      </c>
+      <c r="K8" s="2">
+        <v>44.151846267899231</v>
+      </c>
+      <c r="L8" s="4">
+        <v>3.72713252126061E-2</v>
+      </c>
+      <c r="M8" s="4">
+        <v>3.4831619570918029E-2</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="P8" s="14">
+        <v>45900</v>
+      </c>
+      <c r="Q8" s="11" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="9" spans="1:17">
       <c r="B9" s="11"/>
@@ -5780,14 +5837,14 @@
         <v>22</v>
       </c>
       <c r="C4" s="34">
-        <v>4.0099999999999997E-2</v>
+        <v>4.2599999999999999E-2</v>
       </c>
       <c r="D4" s="34">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="E4" s="35">
         <f>D4-C4</f>
-        <v>3.49E-2</v>
+        <v>3.2399999999999998E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD0FE4B-0288-42B9-81CE-A292DEFA2309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3777231E-71D5-4E6E-A111-2FCE831E0FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -2109,17 +2109,17 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2554,12 +2554,12 @@
       <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="76" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="20" t="s">
@@ -2571,12 +2571,12 @@
       <c r="C6" s="62"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" s="77" t="s">
+      <c r="B7" s="76" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="77"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="77"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="76"/>
+      <c r="E7" s="76"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="23" t="s">
@@ -2665,12 +2665,12 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
-      <c r="B24" s="77" t="s">
+      <c r="B24" s="76" t="s">
         <v>220</v>
       </c>
-      <c r="C24" s="77"/>
-      <c r="D24" s="77"/>
-      <c r="E24" s="77"/>
+      <c r="C24" s="76"/>
+      <c r="D24" s="76"/>
+      <c r="E24" s="76"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
@@ -2764,20 +2764,20 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="B39" s="77" t="s">
+      <c r="B39" s="76" t="s">
         <v>156</v>
       </c>
-      <c r="C39" s="77"/>
-      <c r="D39" s="77"/>
-      <c r="E39" s="77"/>
+      <c r="C39" s="76"/>
+      <c r="D39" s="76"/>
+      <c r="E39" s="76"/>
     </row>
     <row r="40" spans="1:5" ht="46.6" customHeight="1">
-      <c r="B40" s="77" t="s">
+      <c r="B40" s="76" t="s">
         <v>237</v>
       </c>
-      <c r="C40" s="77"/>
-      <c r="D40" s="77"/>
-      <c r="E40" s="77"/>
+      <c r="C40" s="76"/>
+      <c r="D40" s="76"/>
+      <c r="E40" s="76"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="21" t="s">
@@ -2789,12 +2789,12 @@
       <c r="E42" s="21"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="B44" s="77" t="s">
+      <c r="B44" s="76" t="s">
         <v>208</v>
       </c>
-      <c r="C44" s="77"/>
-      <c r="D44" s="77"/>
-      <c r="E44" s="77"/>
+      <c r="C44" s="76"/>
+      <c r="D44" s="76"/>
+      <c r="E44" s="76"/>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="23" t="s">
@@ -2979,12 +2979,12 @@
       <c r="E69" s="21"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="B71" s="77" t="s">
+      <c r="B71" s="76" t="s">
         <v>196</v>
       </c>
-      <c r="C71" s="77"/>
-      <c r="D71" s="77"/>
-      <c r="E71" s="77"/>
+      <c r="C71" s="76"/>
+      <c r="D71" s="76"/>
+      <c r="E71" s="76"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="28" t="s">
@@ -3046,36 +3046,36 @@
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="B85" s="78" t="s">
+      <c r="B85" s="79" t="s">
         <v>192</v>
       </c>
-      <c r="C85" s="78"/>
-      <c r="D85" s="78"/>
-      <c r="E85" s="78"/>
+      <c r="C85" s="79"/>
+      <c r="D85" s="79"/>
+      <c r="E85" s="79"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="B86" s="76" t="s">
+      <c r="B86" s="78" t="s">
         <v>190</v>
       </c>
-      <c r="C86" s="76"/>
-      <c r="D86" s="76"/>
-      <c r="E86" s="76"/>
+      <c r="C86" s="78"/>
+      <c r="D86" s="78"/>
+      <c r="E86" s="78"/>
     </row>
     <row r="87" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B87" s="77" t="s">
+      <c r="B87" s="76" t="s">
         <v>189</v>
       </c>
-      <c r="C87" s="77"/>
-      <c r="D87" s="77"/>
-      <c r="E87" s="77"/>
+      <c r="C87" s="76"/>
+      <c r="D87" s="76"/>
+      <c r="E87" s="76"/>
     </row>
     <row r="88" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B88" s="77" t="s">
+      <c r="B88" s="76" t="s">
         <v>225</v>
       </c>
-      <c r="C88" s="77"/>
-      <c r="D88" s="77"/>
-      <c r="E88" s="77"/>
+      <c r="C88" s="76"/>
+      <c r="D88" s="76"/>
+      <c r="E88" s="76"/>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="24" t="s">
@@ -3108,12 +3108,12 @@
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="B97" s="79" t="s">
+      <c r="B97" s="77" t="s">
         <v>211</v>
       </c>
-      <c r="C97" s="79"/>
-      <c r="D97" s="79"/>
-      <c r="E97" s="79"/>
+      <c r="C97" s="77"/>
+      <c r="D97" s="77"/>
+      <c r="E97" s="77"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
@@ -3121,20 +3121,20 @@
       </c>
     </row>
     <row r="100" spans="1:5" ht="12.4">
-      <c r="B100" s="79" t="s">
+      <c r="B100" s="77" t="s">
         <v>212</v>
       </c>
-      <c r="C100" s="79"/>
-      <c r="D100" s="79"/>
-      <c r="E100" s="79"/>
+      <c r="C100" s="77"/>
+      <c r="D100" s="77"/>
+      <c r="E100" s="77"/>
     </row>
     <row r="101" spans="1:5" ht="58.5" customHeight="1">
-      <c r="B101" s="77" t="s">
+      <c r="B101" s="76" t="s">
         <v>219</v>
       </c>
-      <c r="C101" s="77"/>
-      <c r="D101" s="77"/>
-      <c r="E101" s="77"/>
+      <c r="C101" s="76"/>
+      <c r="D101" s="76"/>
+      <c r="E101" s="76"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="28" t="s">
@@ -3182,7 +3182,7 @@
         <v>176</v>
       </c>
       <c r="C112" s="44">
-        <v>0.13143938180596665</v>
+        <v>0.11859074140485105</v>
       </c>
       <c r="D112" s="62" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
@@ -3190,12 +3190,12 @@
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B114" s="77" t="s">
+      <c r="B114" s="76" t="s">
         <v>217</v>
       </c>
-      <c r="C114" s="77"/>
-      <c r="D114" s="77"/>
-      <c r="E114" s="77"/>
+      <c r="C114" s="76"/>
+      <c r="D114" s="76"/>
+      <c r="E114" s="76"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="21" t="s">
@@ -3228,12 +3228,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
     <mergeCell ref="B86:E86"/>
     <mergeCell ref="B71:E71"/>
     <mergeCell ref="B85:E85"/>
@@ -3243,6 +3237,12 @@
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3355,51 +3355,51 @@
     </row>
     <row r="3" spans="1:17">
       <c r="B3" s="11" t="s">
-        <v>158</v>
+        <v>238</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>159</v>
+        <v>239</v>
       </c>
       <c r="D3" s="2">
-        <v>14.44</v>
+        <v>5.59</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F3" s="15">
-        <v>0.20871253483792285</v>
+        <v>0.19222357225122977</v>
       </c>
       <c r="G3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$10</f>
-        <v>9.1312534837922843E-2</v>
+        <v>7.4823572251229764E-2</v>
       </c>
       <c r="H3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$11</f>
-        <v>0.17421253483792284</v>
+        <v>0.15772357225122977</v>
       </c>
       <c r="I3" s="15">
-        <v>0.25045504180550743</v>
+        <v>0.23066828670147571</v>
       </c>
       <c r="J3" s="2">
-        <v>13.155317996540354</v>
+        <v>4.8951478192697992</v>
       </c>
       <c r="K3" s="2">
-        <v>20.508980461992877</v>
+        <v>7.8759412010961185</v>
       </c>
       <c r="L3" s="4">
-        <v>0.11966662184000204</v>
+        <v>0.13686752422932275</v>
       </c>
       <c r="M3" s="4">
-        <v>9.418282548476456E-2</v>
+        <v>7.9058946405006977E-2</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>161</v>
+        <v>241</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>162</v>
+        <v>240</v>
       </c>
       <c r="P3" s="14">
-        <v>45808</v>
+        <v>45900</v>
       </c>
       <c r="Q3" s="11" t="s">
         <v>163</v>
@@ -3407,51 +3407,51 @@
     </row>
     <row r="4" spans="1:17">
       <c r="B4" s="11" t="s">
-        <v>238</v>
+        <v>158</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>239</v>
+        <v>159</v>
       </c>
       <c r="D4" s="2">
-        <v>5.39</v>
+        <v>15.32</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F4" s="15">
-        <v>0.20602353093461256</v>
+        <v>0.18329188684945863</v>
       </c>
       <c r="G4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$10</f>
-        <v>8.862353093461256E-2</v>
+        <v>6.5891886849458625E-2</v>
       </c>
       <c r="H4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$11</f>
-        <v>0.17152353093461256</v>
+        <v>0.14879188684945863</v>
       </c>
       <c r="I4" s="15">
-        <v>0.24722823712153508</v>
+        <v>0.21995026421935035</v>
       </c>
       <c r="J4" s="2">
-        <v>4.8752893604858043</v>
+        <v>13.155317996540354</v>
       </c>
       <c r="K4" s="2">
-        <v>7.8371551487836282</v>
+        <v>20.508980461992877</v>
       </c>
       <c r="L4" s="4">
-        <v>0.14124706534453912</v>
+        <v>0.11279282110767816</v>
       </c>
       <c r="M4" s="4">
-        <v>8.1992488015582371E-2</v>
+        <v>8.877284595300261E-2</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>241</v>
+        <v>161</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>240</v>
+        <v>162</v>
       </c>
       <c r="P4" s="14">
-        <v>45900</v>
+        <v>45808</v>
       </c>
       <c r="Q4" s="11" t="s">
         <v>163</v>
@@ -3459,100 +3459,100 @@
     </row>
     <row r="5" spans="1:17">
       <c r="B5" s="11" t="s">
-        <v>164</v>
+        <v>242</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>165</v>
+        <v>243</v>
       </c>
       <c r="D5" s="2">
-        <v>7.47</v>
+        <v>58.35</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F5" s="15">
-        <v>0.14104674835105913</v>
+        <v>0.13479424997108347</v>
       </c>
       <c r="G5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$10</f>
-        <v>2.3646748351059121E-2</v>
+        <v>1.7394249971083464E-2</v>
       </c>
       <c r="H5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$11</f>
-        <v>0.10654674835105912</v>
+        <v>0.10029424997108347</v>
       </c>
       <c r="I5" s="15">
-        <v>0.10231672107295747</v>
+        <v>0.14938144907917394</v>
       </c>
       <c r="J5" s="2">
-        <v>5.7917118707600084</v>
+        <v>44.071651534145857</v>
       </c>
       <c r="K5" s="2">
-        <v>9.1006872475781417</v>
+        <v>78.175377834395093</v>
       </c>
       <c r="L5" s="4">
-        <v>4.1351857025738292E-2</v>
+        <v>3.8385758471807176E-2</v>
       </c>
       <c r="M5" s="4">
-        <v>7.7643908969210168E-2</v>
+        <v>3.5521391571982669E-2</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>166</v>
+        <v>244</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="P5" s="14">
         <v>45900</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="B6" s="11" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D6" s="2">
-        <v>2.12</v>
+        <v>7.63</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F6" s="15">
-        <v>0.13066415339637483</v>
+        <v>0.132459340913061</v>
       </c>
       <c r="G6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$10</f>
-        <v>1.3264153396374823E-2</v>
+        <v>1.5059340913060992E-2</v>
       </c>
       <c r="H6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$11</f>
-        <v>9.6164153396374824E-2</v>
+        <v>9.7959340913060994E-2</v>
       </c>
       <c r="I6" s="15">
         <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>1.5928004364498562</v>
+        <v>5.7917118707600084</v>
       </c>
       <c r="K6" s="2">
-        <v>2.6705641652753029</v>
+        <v>9.1006872475781417</v>
       </c>
       <c r="L6" s="4">
-        <v>3.8391219865680747E-2</v>
+        <v>4.0484714545513105E-2</v>
       </c>
       <c r="M6" s="4">
-        <v>5.448489788627562E-2</v>
+        <v>7.6015727391874177E-2</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="P6" s="14">
         <v>45900</v>
@@ -3569,36 +3569,36 @@
         <v>248</v>
       </c>
       <c r="D7" s="2">
-        <v>14.58</v>
+        <v>13.52</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F7" s="15">
-        <v>0.1010567723303204</v>
+        <v>0.13057514345777688</v>
       </c>
       <c r="G7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$10</f>
-        <v>-1.6343227669679605E-2</v>
+        <v>1.3175143457776872E-2</v>
       </c>
       <c r="H7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$11</f>
-        <v>6.6556772330320396E-2</v>
+        <v>9.6075143457776874E-2</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>10.177519059641918</v>
+        <v>10.175590600126672</v>
       </c>
       <c r="K7" s="2">
-        <v>16.70033318211312</v>
+        <v>16.697180853372405</v>
       </c>
       <c r="L7" s="4">
-        <v>0.10531435381835931</v>
+        <v>0.11354918043217686</v>
       </c>
       <c r="M7" s="4">
-        <v>5.7165823045267489E-2</v>
+        <v>6.1635843195266271E-2</v>
       </c>
       <c r="N7" s="13" t="s">
         <v>249</v>
@@ -3615,54 +3615,54 @@
     </row>
     <row r="8" spans="1:17">
       <c r="B8" s="11" t="s">
-        <v>242</v>
+        <v>168</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>243</v>
+        <v>169</v>
       </c>
       <c r="D8" s="2">
-        <v>59.8</v>
+        <v>2.13</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F8" s="15">
-        <v>-5.7617735553175065E-2</v>
+        <v>0.1302840611640077</v>
       </c>
       <c r="G8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$10</f>
-        <v>-0.17501773555317507</v>
+        <v>1.2884061164007699E-2</v>
       </c>
       <c r="H8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$11</f>
-        <v>-9.2117735553175067E-2</v>
+        <v>9.57840611640077E-2</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
       </c>
       <c r="J8" s="2">
-        <v>26.67162630902984</v>
+        <v>1.5985673372765861</v>
       </c>
       <c r="K8" s="2">
-        <v>44.151846267899231</v>
+        <v>2.6839963209253819</v>
       </c>
       <c r="L8" s="4">
-        <v>3.72713252126061E-2</v>
+        <v>3.8396886150880542E-2</v>
       </c>
       <c r="M8" s="4">
-        <v>3.4831619570918029E-2</v>
+        <v>5.3962042292674567E-2</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>244</v>
+        <v>170</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="P8" s="14">
         <v>45900</v>
       </c>
       <c r="Q8" s="11" t="s">
-        <v>250</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -5837,14 +5837,14 @@
         <v>22</v>
       </c>
       <c r="C4" s="34">
-        <v>4.2599999999999999E-2</v>
+        <v>4.3799999999999999E-2</v>
       </c>
       <c r="D4" s="34">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="E4" s="35">
         <f>D4-C4</f>
-        <v>3.2399999999999998E-2</v>
+        <v>3.1199999999999999E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6401,15 +6401,15 @@
       <c r="B5" s="86" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="86" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3777231E-71D5-4E6E-A111-2FCE831E0FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920CA08B-DB51-4206-87DC-82DA4A624B8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="257">
   <si>
     <t>Name</t>
   </si>
@@ -1586,6 +1586,21 @@
   </si>
   <si>
     <t xml:space="preserve">High Growth </t>
+  </si>
+  <si>
+    <t>0303.HK</t>
+  </si>
+  <si>
+    <t>偉易達</t>
+  </si>
+  <si>
+    <t>0806.HK</t>
+  </si>
+  <si>
+    <t>惠理集團</t>
+  </si>
+  <si>
+    <t>FIN_02</t>
   </si>
 </sst>
 </file>
@@ -3182,7 +3197,7 @@
         <v>176</v>
       </c>
       <c r="C112" s="44">
-        <v>0.11859074140485105</v>
+        <v>0.11740265340759549</v>
       </c>
       <c r="D112" s="62" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
@@ -3361,36 +3376,36 @@
         <v>239</v>
       </c>
       <c r="D3" s="2">
-        <v>5.59</v>
+        <v>5.65</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F3" s="15">
-        <v>0.19222357225122977</v>
+        <v>0.18805346196285577</v>
       </c>
       <c r="G3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$10</f>
-        <v>7.4823572251229764E-2</v>
+        <v>7.0653461962855768E-2</v>
       </c>
       <c r="H3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$11</f>
-        <v>0.15772357225122977</v>
+        <v>0.15355346196285577</v>
       </c>
       <c r="I3" s="15">
-        <v>0.23066828670147571</v>
+        <v>0.22566415435542692</v>
       </c>
       <c r="J3" s="2">
-        <v>4.8951478192697992</v>
+        <v>4.8991357331780589</v>
       </c>
       <c r="K3" s="2">
-        <v>7.8759412010961185</v>
+        <v>7.8837300954481879</v>
       </c>
       <c r="L3" s="4">
-        <v>0.13686752422932275</v>
+        <v>0.13554798122911768</v>
       </c>
       <c r="M3" s="4">
-        <v>7.9058946405006977E-2</v>
+        <v>7.821938237238743E-2</v>
       </c>
       <c r="N3" s="13" t="s">
         <v>241</v>
@@ -3413,24 +3428,24 @@
         <v>159</v>
       </c>
       <c r="D4" s="2">
-        <v>15.32</v>
+        <v>15.3</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F4" s="15">
-        <v>0.18329188684945863</v>
+        <v>0.18384675850766619</v>
       </c>
       <c r="G4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$10</f>
-        <v>6.5891886849458625E-2</v>
+        <v>6.6446758507666182E-2</v>
       </c>
       <c r="H4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$11</f>
-        <v>0.14879188684945863</v>
+        <v>0.14934675850766618</v>
       </c>
       <c r="I4" s="15">
-        <v>0.21995026421935035</v>
+        <v>0.22061611020919941</v>
       </c>
       <c r="J4" s="2">
         <v>13.155317996540354</v>
@@ -3439,10 +3454,10 @@
         <v>20.508980461992877</v>
       </c>
       <c r="L4" s="4">
-        <v>0.11279282110767816</v>
+        <v>0.11294026270389734</v>
       </c>
       <c r="M4" s="4">
-        <v>8.877284595300261E-2</v>
+        <v>8.8888888888888892E-2</v>
       </c>
       <c r="N4" s="13" t="s">
         <v>161</v>
@@ -3459,100 +3474,100 @@
     </row>
     <row r="5" spans="1:17">
       <c r="B5" s="11" t="s">
-        <v>242</v>
+        <v>164</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
       <c r="D5" s="2">
-        <v>58.35</v>
+        <v>7.6</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F5" s="15">
-        <v>0.13479424997108347</v>
+        <v>0.13405026456260738</v>
       </c>
       <c r="G5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$10</f>
-        <v>1.7394249971083464E-2</v>
+        <v>1.6650264562607375E-2</v>
       </c>
       <c r="H5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$11</f>
-        <v>0.10029424997108347</v>
+        <v>9.9550264562607377E-2</v>
       </c>
       <c r="I5" s="15">
-        <v>0.14938144907917394</v>
+        <v>0.15371973543537365</v>
       </c>
       <c r="J5" s="2">
-        <v>44.071651534145857</v>
+        <v>5.7917118707600084</v>
       </c>
       <c r="K5" s="2">
-        <v>78.175377834395093</v>
+        <v>9.1006872475781417</v>
       </c>
       <c r="L5" s="4">
-        <v>3.8385758471807176E-2</v>
+        <v>4.0644522629245394E-2</v>
       </c>
       <c r="M5" s="4">
-        <v>3.5521391571982669E-2</v>
+        <v>7.6315789473684212E-2</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>244</v>
+        <v>166</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="P5" s="14">
         <v>45900</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>250</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="B6" s="11" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D6" s="2">
-        <v>7.63</v>
+        <v>2.12</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F6" s="15">
-        <v>0.132459340913061</v>
+        <v>0.13244092382946393</v>
       </c>
       <c r="G6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$10</f>
-        <v>1.5059340913060992E-2</v>
+        <v>1.5040923829463926E-2</v>
       </c>
       <c r="H6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$11</f>
-        <v>9.7959340913060994E-2</v>
+        <v>9.7940923829463927E-2</v>
       </c>
       <c r="I6" s="15">
         <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>5.7917118707600084</v>
+        <v>1.5997267456616144</v>
       </c>
       <c r="K6" s="2">
-        <v>9.1006872475781417</v>
+        <v>2.6866937246321601</v>
       </c>
       <c r="L6" s="4">
-        <v>4.0484714545513105E-2</v>
+        <v>3.8615512854405329E-2</v>
       </c>
       <c r="M6" s="4">
-        <v>7.6015727391874177E-2</v>
+        <v>5.4163015835221838E-2</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="P6" s="14">
         <v>45900</v>
@@ -3569,36 +3584,36 @@
         <v>248</v>
       </c>
       <c r="D7" s="2">
-        <v>13.52</v>
+        <v>13.48</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F7" s="15">
-        <v>0.13057514345777688</v>
+        <v>0.13185476539875873</v>
       </c>
       <c r="G7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$10</f>
-        <v>1.3175143457776872E-2</v>
+        <v>1.4454765398758729E-2</v>
       </c>
       <c r="H7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$11</f>
-        <v>9.6075143457776874E-2</v>
+        <v>9.735476539875873E-2</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>10.175590600126672</v>
+        <v>10.178161876153645</v>
       </c>
       <c r="K7" s="2">
-        <v>16.697180853372405</v>
+        <v>16.701383951862589</v>
       </c>
       <c r="L7" s="4">
-        <v>0.11354918043217686</v>
+        <v>0.11391563292899698</v>
       </c>
       <c r="M7" s="4">
-        <v>6.1635843195266271E-2</v>
+        <v>6.1834673590504444E-2</v>
       </c>
       <c r="N7" s="13" t="s">
         <v>249</v>
@@ -3615,75 +3630,159 @@
     </row>
     <row r="8" spans="1:17">
       <c r="B8" s="11" t="s">
-        <v>168</v>
+        <v>242</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>169</v>
+        <v>243</v>
       </c>
       <c r="D8" s="2">
-        <v>2.13</v>
+        <v>59.9</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F8" s="15">
-        <v>0.1302840611640077</v>
+        <v>0.12493740306462042</v>
       </c>
       <c r="G8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$10</f>
-        <v>1.2884061164007699E-2</v>
+        <v>7.5374030646204182E-3</v>
       </c>
       <c r="H8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$11</f>
-        <v>9.57840611640077E-2</v>
+        <v>9.043740306462042E-2</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
       </c>
       <c r="J8" s="2">
-        <v>1.5985673372765861</v>
+        <v>44.107282041660923</v>
       </c>
       <c r="K8" s="2">
-        <v>2.6839963209253819</v>
+        <v>78.252775679635405</v>
       </c>
       <c r="L8" s="4">
-        <v>3.8396886150880542E-2</v>
+        <v>3.7429294343278158E-2</v>
       </c>
       <c r="M8" s="4">
-        <v>5.3962042292674567E-2</v>
+        <v>3.456803769335158E-2</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>170</v>
+        <v>244</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="P8" s="14">
         <v>45900</v>
       </c>
       <c r="Q8" s="11" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="B9" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="D9" s="2">
+        <v>49.05</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="F9" s="15">
+        <v>0.1151268191287802</v>
+      </c>
+      <c r="G9" s="15">
+        <f>F9 - Portfolio_Mgmt!$C$10</f>
+        <v>-2.2731808712198043E-3</v>
+      </c>
+      <c r="H9" s="15">
+        <f>F9 - Portfolio_Mgmt!$C$11</f>
+        <v>8.0626819128780197E-2</v>
+      </c>
+      <c r="I9" s="15">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>34.82424866299835</v>
+      </c>
+      <c r="K9" s="2">
+        <v>68.016110669918646</v>
+      </c>
+      <c r="L9" s="4">
+        <v>0.10720319069009697</v>
+      </c>
+      <c r="M9" s="4">
+        <v>0</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="P9" s="14">
+        <v>45808</v>
+      </c>
+      <c r="Q9" s="11" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="E9" s="12"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="14"/>
-    </row>
     <row r="10" spans="1:17">
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="E10" s="12"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="14"/>
+      <c r="B10" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1.35</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="F10" s="15">
+        <v>-0.26037178228763347</v>
+      </c>
+      <c r="G10" s="15">
+        <f>F10 - Portfolio_Mgmt!$C$10</f>
+        <v>-0.37777178228763347</v>
+      </c>
+      <c r="H10" s="15">
+        <f>F10 - Portfolio_Mgmt!$C$11</f>
+        <v>-0.29487178228763344</v>
+      </c>
+      <c r="I10" s="15">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.28748108885958823</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0.52336150167888329</v>
+      </c>
+      <c r="L10" s="4">
+        <v>1.6563974747231462E-3</v>
+      </c>
+      <c r="M10" s="4">
+        <v>7.4074074074074068E-3</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="P10" s="14">
+        <v>45900</v>
+      </c>
+      <c r="Q10" s="11" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="11" spans="1:17">
       <c r="B11" s="11"/>
@@ -5837,14 +5936,14 @@
         <v>22</v>
       </c>
       <c r="C4" s="34">
-        <v>4.3799999999999999E-2</v>
+        <v>4.3499999999999997E-2</v>
       </c>
       <c r="D4" s="34">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="E4" s="35">
         <f>D4-C4</f>
-        <v>3.1199999999999999E-2</v>
+        <v>3.15E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920CA08B-DB51-4206-87DC-82DA4A624B8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B05B01-58F6-4DB6-90C6-82BF893C11D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="261">
   <si>
     <t>Name</t>
   </si>
@@ -1601,6 +1601,18 @@
   </si>
   <si>
     <t>FIN_02</t>
+  </si>
+  <si>
+    <t>SIRI</t>
+  </si>
+  <si>
+    <t>Sirius XM Holdings Inc.</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>TMT_05</t>
   </si>
 </sst>
 </file>
@@ -3197,7 +3209,7 @@
         <v>176</v>
       </c>
       <c r="C112" s="44">
-        <v>0.11740265340759549</v>
+        <v>0.1214850482523553</v>
       </c>
       <c r="D112" s="62" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
@@ -3474,48 +3486,48 @@
     </row>
     <row r="5" spans="1:17">
       <c r="B5" s="11" t="s">
-        <v>164</v>
+        <v>257</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>165</v>
+        <v>258</v>
       </c>
       <c r="D5" s="2">
-        <v>7.6</v>
+        <v>20.079999999999998</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>160</v>
+        <v>259</v>
       </c>
       <c r="F5" s="15">
-        <v>0.13405026456260738</v>
+        <v>0.16060765378265396</v>
       </c>
       <c r="G5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$10</f>
-        <v>1.6650264562607375E-2</v>
+        <v>4.3207653782653954E-2</v>
       </c>
       <c r="H5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$11</f>
-        <v>9.9550264562607377E-2</v>
+        <v>0.12610765378265396</v>
       </c>
       <c r="I5" s="15">
         <v>0.15371973543537365</v>
       </c>
       <c r="J5" s="2">
-        <v>5.7917118707600084</v>
+        <v>16.165402289394244</v>
       </c>
       <c r="K5" s="2">
-        <v>9.1006872475781417</v>
+        <v>29.309951346473134</v>
       </c>
       <c r="L5" s="4">
-        <v>4.0644522629245394E-2</v>
+        <v>0.22703991769612522</v>
       </c>
       <c r="M5" s="4">
-        <v>7.6315789473684212E-2</v>
+        <v>2.956175298804781E-2</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>166</v>
+        <v>260</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="P5" s="14">
         <v>45900</v>
@@ -3526,48 +3538,48 @@
     </row>
     <row r="6" spans="1:17">
       <c r="B6" s="11" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D6" s="2">
-        <v>2.12</v>
+        <v>7.6</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F6" s="15">
-        <v>0.13244092382946393</v>
+        <v>0.13405026456260738</v>
       </c>
       <c r="G6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$10</f>
-        <v>1.5040923829463926E-2</v>
+        <v>1.6650264562607375E-2</v>
       </c>
       <c r="H6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$11</f>
-        <v>9.7940923829463927E-2</v>
+        <v>9.9550264562607377E-2</v>
       </c>
       <c r="I6" s="15">
         <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>1.5997267456616144</v>
+        <v>5.7917118707600084</v>
       </c>
       <c r="K6" s="2">
-        <v>2.6866937246321601</v>
+        <v>9.1006872475781417</v>
       </c>
       <c r="L6" s="4">
-        <v>3.8615512854405329E-2</v>
+        <v>4.0644522629245394E-2</v>
       </c>
       <c r="M6" s="4">
-        <v>5.4163015835221838E-2</v>
+        <v>7.6315789473684212E-2</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="P6" s="14">
         <v>45900</v>
@@ -3578,100 +3590,100 @@
     </row>
     <row r="7" spans="1:17">
       <c r="B7" s="11" t="s">
-        <v>247</v>
+        <v>168</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>248</v>
+        <v>169</v>
       </c>
       <c r="D7" s="2">
-        <v>13.48</v>
+        <v>2.12</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F7" s="15">
-        <v>0.13185476539875873</v>
+        <v>0.13244092382946393</v>
       </c>
       <c r="G7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$10</f>
-        <v>1.4454765398758729E-2</v>
+        <v>1.5040923829463926E-2</v>
       </c>
       <c r="H7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$11</f>
-        <v>9.735476539875873E-2</v>
+        <v>9.7940923829463927E-2</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>10.178161876153645</v>
+        <v>1.5997267456616144</v>
       </c>
       <c r="K7" s="2">
-        <v>16.701383951862589</v>
+        <v>2.6866937246321601</v>
       </c>
       <c r="L7" s="4">
-        <v>0.11391563292899698</v>
+        <v>3.8615512854405329E-2</v>
       </c>
       <c r="M7" s="4">
-        <v>6.1834673590504444E-2</v>
+        <v>5.4163015835221838E-2</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>249</v>
+        <v>170</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>251</v>
+        <v>171</v>
       </c>
       <c r="P7" s="14">
         <v>45900</v>
       </c>
       <c r="Q7" s="11" t="s">
-        <v>250</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="B8" s="11" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D8" s="2">
-        <v>59.9</v>
+        <v>13.48</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F8" s="15">
-        <v>0.12493740306462042</v>
+        <v>0.13185476539875873</v>
       </c>
       <c r="G8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$10</f>
-        <v>7.5374030646204182E-3</v>
+        <v>1.4454765398758729E-2</v>
       </c>
       <c r="H8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$11</f>
-        <v>9.043740306462042E-2</v>
+        <v>9.735476539875873E-2</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
       </c>
       <c r="J8" s="2">
-        <v>44.107282041660923</v>
+        <v>10.178161876153645</v>
       </c>
       <c r="K8" s="2">
-        <v>78.252775679635405</v>
+        <v>16.701383951862589</v>
       </c>
       <c r="L8" s="4">
-        <v>3.7429294343278158E-2</v>
+        <v>0.11391563292899698</v>
       </c>
       <c r="M8" s="4">
-        <v>3.456803769335158E-2</v>
+        <v>6.1834673590504444E-2</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>162</v>
+        <v>251</v>
       </c>
       <c r="P8" s="14">
         <v>45900</v>
@@ -3682,117 +3694,159 @@
     </row>
     <row r="9" spans="1:17">
       <c r="B9" s="11" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="D9" s="2">
-        <v>49.05</v>
+        <v>59.9</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F9" s="15">
-        <v>0.1151268191287802</v>
+        <v>0.12493740306462042</v>
       </c>
       <c r="G9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.2731808712198043E-3</v>
+        <v>7.5374030646204182E-3</v>
       </c>
       <c r="H9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$11</f>
-        <v>8.0626819128780197E-2</v>
+        <v>9.043740306462042E-2</v>
       </c>
       <c r="I9" s="15">
         <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>34.82424866299835</v>
+        <v>44.107282041660923</v>
       </c>
       <c r="K9" s="2">
-        <v>68.016110669918646</v>
+        <v>78.252775679635405</v>
       </c>
       <c r="L9" s="4">
-        <v>0.10720319069009697</v>
+        <v>3.7429294343278158E-2</v>
       </c>
       <c r="M9" s="4">
-        <v>0</v>
+        <v>3.456803769335158E-2</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="O9" s="11" t="s">
         <v>162</v>
       </c>
       <c r="P9" s="14">
-        <v>45808</v>
+        <v>45900</v>
       </c>
       <c r="Q9" s="11" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="B10" s="11" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D10" s="2">
-        <v>1.35</v>
+        <v>49.05</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F10" s="15">
-        <v>-0.26037178228763347</v>
+        <v>0.1151268191287802</v>
       </c>
       <c r="G10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$10</f>
-        <v>-0.37777178228763347</v>
+        <v>-2.2731808712198043E-3</v>
       </c>
       <c r="H10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$11</f>
-        <v>-0.29487178228763344</v>
+        <v>8.0626819128780197E-2</v>
       </c>
       <c r="I10" s="15">
         <v>0</v>
       </c>
       <c r="J10" s="2">
+        <v>34.82424866299835</v>
+      </c>
+      <c r="K10" s="2">
+        <v>68.016110669918646</v>
+      </c>
+      <c r="L10" s="4">
+        <v>0.10720319069009697</v>
+      </c>
+      <c r="M10" s="4">
+        <v>0</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="P10" s="14">
+        <v>45808</v>
+      </c>
+      <c r="Q10" s="11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="B11" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1.35</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="F11" s="15">
+        <v>-0.26037178228763347</v>
+      </c>
+      <c r="G11" s="15">
+        <f>F11 - Portfolio_Mgmt!$C$10</f>
+        <v>-0.37777178228763347</v>
+      </c>
+      <c r="H11" s="15">
+        <f>F11 - Portfolio_Mgmt!$C$11</f>
+        <v>-0.29487178228763344</v>
+      </c>
+      <c r="I11" s="15">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2">
         <v>0.28748108885958823</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K11" s="2">
         <v>0.52336150167888329</v>
       </c>
-      <c r="L10" s="4">
+      <c r="L11" s="4">
         <v>1.6563974747231462E-3</v>
       </c>
-      <c r="M10" s="4">
+      <c r="M11" s="4">
         <v>7.4074074074074068E-3</v>
       </c>
-      <c r="N10" s="16" t="s">
+      <c r="N11" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="O10" s="11" t="s">
+      <c r="O11" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="P10" s="14">
+      <c r="P11" s="14">
         <v>45900</v>
       </c>
-      <c r="Q10" s="11" t="s">
+      <c r="Q11" s="11" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="11" spans="1:17">
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="E11" s="12"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="14"/>
     </row>
     <row r="12" spans="1:17">
       <c r="B12" s="11"/>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B05B01-58F6-4DB6-90C6-82BF893C11D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E10F7A-7C19-4CD3-8964-255BE53EADD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="264">
   <si>
     <t>Name</t>
   </si>
@@ -1613,6 +1613,15 @@
   </si>
   <si>
     <t>TMT_05</t>
+  </si>
+  <si>
+    <t>KHC</t>
+  </si>
+  <si>
+    <t>The Kraft Heinz Company</t>
+  </si>
+  <si>
+    <t>CNS_01</t>
   </si>
 </sst>
 </file>
@@ -3798,65 +3807,107 @@
     </row>
     <row r="11" spans="1:17">
       <c r="B11" s="11" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="D11" s="2">
-        <v>1.35</v>
+        <v>28.81</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>160</v>
+        <v>259</v>
       </c>
       <c r="F11" s="15">
-        <v>-0.26037178228763347</v>
+        <v>9.408289080523935E-2</v>
       </c>
       <c r="G11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$10</f>
-        <v>-0.37777178228763347</v>
+        <v>-2.3317109194760655E-2</v>
       </c>
       <c r="H11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$11</f>
-        <v>-0.29487178228763344</v>
+        <v>5.9582890805239347E-2</v>
       </c>
       <c r="I11" s="15">
         <v>0</v>
       </c>
       <c r="J11" s="2">
-        <v>0.28748108885958823</v>
+        <v>19.745207945921621</v>
       </c>
       <c r="K11" s="2">
-        <v>0.52336150167888329</v>
+        <v>32.464859269378167</v>
       </c>
       <c r="L11" s="4">
-        <v>1.6563974747231462E-3</v>
+        <v>8.8134932571433455E-2</v>
       </c>
       <c r="M11" s="4">
-        <v>7.4074074074074068E-3</v>
+        <v>5.5536272127733433E-2</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="O11" s="11" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="P11" s="14">
         <v>45900</v>
       </c>
       <c r="Q11" s="11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="B12" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1.35</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="F12" s="15">
+        <v>-0.26037178228763347</v>
+      </c>
+      <c r="G12" s="15">
+        <f>F12 - Portfolio_Mgmt!$C$10</f>
+        <v>-0.37777178228763347</v>
+      </c>
+      <c r="H12" s="15">
+        <f>F12 - Portfolio_Mgmt!$C$11</f>
+        <v>-0.29487178228763344</v>
+      </c>
+      <c r="I12" s="15">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0.28748108885958823</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0.52336150167888329</v>
+      </c>
+      <c r="L12" s="4">
+        <v>1.6563974747231462E-3</v>
+      </c>
+      <c r="M12" s="4">
+        <v>7.4074074074074068E-3</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="O12" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="P12" s="14">
+        <v>45900</v>
+      </c>
+      <c r="Q12" s="11" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="12" spans="1:17">
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="E12" s="12"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="14"/>
     </row>
     <row r="13" spans="1:17">
       <c r="B13" s="11"/>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E10F7A-7C19-4CD3-8964-255BE53EADD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DAB014C-9B41-49C7-A05D-552F6F9F10C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="261">
   <si>
     <t>Name</t>
   </si>
@@ -1592,15 +1592,6 @@
   </si>
   <si>
     <t>偉易達</t>
-  </si>
-  <si>
-    <t>0806.HK</t>
-  </si>
-  <si>
-    <t>惠理集團</t>
-  </si>
-  <si>
-    <t>FIN_02</t>
   </si>
   <si>
     <t>SIRI</t>
@@ -3218,11 +3209,11 @@
         <v>176</v>
       </c>
       <c r="C112" s="44">
-        <v>0.1214850482523553</v>
+        <v>0.11210459565877447</v>
       </c>
       <c r="D112" s="62" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
-        <v/>
+        <v>Warning: Return is lower than the Benchmark.</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
@@ -3397,36 +3388,36 @@
         <v>239</v>
       </c>
       <c r="D3" s="2">
-        <v>5.65</v>
+        <v>5.82</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F3" s="15">
-        <v>0.18805346196285577</v>
+        <v>0.17654933116845006</v>
       </c>
       <c r="G3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$10</f>
-        <v>7.0653461962855768E-2</v>
+        <v>5.9149331168450059E-2</v>
       </c>
       <c r="H3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$11</f>
-        <v>0.15355346196285577</v>
+        <v>0.14204933116845006</v>
       </c>
       <c r="I3" s="15">
-        <v>0.22566415435542692</v>
+        <v>0.21185919740214007</v>
       </c>
       <c r="J3" s="2">
-        <v>4.8991357331780589</v>
+        <v>4.9100950691878094</v>
       </c>
       <c r="K3" s="2">
-        <v>7.8837300954481879</v>
+        <v>7.905135048592232</v>
       </c>
       <c r="L3" s="4">
-        <v>0.13554798122911768</v>
+        <v>0.13194594963823414</v>
       </c>
       <c r="M3" s="4">
-        <v>7.821938237238743E-2</v>
+        <v>7.5934623780754121E-2</v>
       </c>
       <c r="N3" s="13" t="s">
         <v>241</v>
@@ -3443,51 +3434,51 @@
     </row>
     <row r="4" spans="1:17">
       <c r="B4" s="11" t="s">
-        <v>158</v>
+        <v>254</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>159</v>
+        <v>255</v>
       </c>
       <c r="D4" s="2">
-        <v>15.3</v>
+        <v>20.079999999999998</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>160</v>
+        <v>256</v>
       </c>
       <c r="F4" s="15">
-        <v>0.18384675850766619</v>
+        <v>0.16060765378265396</v>
       </c>
       <c r="G4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$10</f>
-        <v>6.6446758507666182E-2</v>
+        <v>4.3207653782653954E-2</v>
       </c>
       <c r="H4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$11</f>
-        <v>0.14934675850766618</v>
+        <v>0.12610765378265396</v>
       </c>
       <c r="I4" s="15">
-        <v>0.22061611020919941</v>
+        <v>0.19272918453918475</v>
       </c>
       <c r="J4" s="2">
-        <v>13.155317996540354</v>
+        <v>16.165402289394244</v>
       </c>
       <c r="K4" s="2">
-        <v>20.508980461992877</v>
+        <v>29.309951346473134</v>
       </c>
       <c r="L4" s="4">
-        <v>0.11294026270389734</v>
+        <v>0.22703991769612522</v>
       </c>
       <c r="M4" s="4">
-        <v>8.8888888888888892E-2</v>
+        <v>2.956175298804781E-2</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>161</v>
+        <v>257</v>
       </c>
       <c r="O4" s="11" t="s">
         <v>162</v>
       </c>
       <c r="P4" s="14">
-        <v>45808</v>
+        <v>45900</v>
       </c>
       <c r="Q4" s="11" t="s">
         <v>163</v>
@@ -3495,51 +3486,51 @@
     </row>
     <row r="5" spans="1:17">
       <c r="B5" s="11" t="s">
-        <v>257</v>
+        <v>158</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>258</v>
+        <v>159</v>
       </c>
       <c r="D5" s="2">
-        <v>20.079999999999998</v>
+        <v>16.420000000000002</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>259</v>
+        <v>160</v>
       </c>
       <c r="F5" s="15">
-        <v>0.16060765378265396</v>
+        <v>0.15425024630514339</v>
       </c>
       <c r="G5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$10</f>
-        <v>4.3207653782653954E-2</v>
+        <v>3.6850246305143386E-2</v>
       </c>
       <c r="H5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$11</f>
-        <v>0.12610765378265396</v>
+        <v>0.11975024630514339</v>
       </c>
       <c r="I5" s="15">
-        <v>0.15371973543537365</v>
+        <v>0.18510029556617205</v>
       </c>
       <c r="J5" s="2">
-        <v>16.165402289394244</v>
+        <v>13.155317996540354</v>
       </c>
       <c r="K5" s="2">
-        <v>29.309951346473134</v>
+        <v>20.508980461992877</v>
       </c>
       <c r="L5" s="4">
-        <v>0.22703991769612522</v>
+        <v>0.1052366637862137</v>
       </c>
       <c r="M5" s="4">
-        <v>2.956175298804781E-2</v>
+        <v>8.282582216808769E-2</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>260</v>
+        <v>161</v>
       </c>
       <c r="O5" s="11" t="s">
         <v>162</v>
       </c>
       <c r="P5" s="14">
-        <v>45900</v>
+        <v>45808</v>
       </c>
       <c r="Q5" s="11" t="s">
         <v>163</v>
@@ -3547,100 +3538,100 @@
     </row>
     <row r="6" spans="1:17">
       <c r="B6" s="11" t="s">
-        <v>164</v>
+        <v>242</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>165</v>
+        <v>243</v>
       </c>
       <c r="D6" s="2">
-        <v>7.6</v>
+        <v>58.45</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F6" s="15">
-        <v>0.13405026456260738</v>
+        <v>0.13533159592642741</v>
       </c>
       <c r="G6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$10</f>
-        <v>1.6650264562607375E-2</v>
+        <v>1.7931595926427402E-2</v>
       </c>
       <c r="H6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$11</f>
-        <v>9.9550264562607377E-2</v>
+        <v>0.1008315959264274</v>
       </c>
       <c r="I6" s="15">
-        <v>0</v>
+        <v>1.0311322492503106E-2</v>
       </c>
       <c r="J6" s="2">
-        <v>5.7917118707600084</v>
+        <v>44.205240144973352</v>
       </c>
       <c r="K6" s="2">
-        <v>9.1006872475781417</v>
+        <v>78.465475605444368</v>
       </c>
       <c r="L6" s="4">
-        <v>4.0644522629245394E-2</v>
+        <v>3.8461528914527629E-2</v>
       </c>
       <c r="M6" s="4">
-        <v>7.6315789473684212E-2</v>
+        <v>3.5329662411002084E-2</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>166</v>
+        <v>244</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="P6" s="14">
         <v>45900</v>
       </c>
       <c r="Q6" s="11" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="B7" s="11" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D7" s="2">
-        <v>2.12</v>
+        <v>7.81</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F7" s="15">
-        <v>0.13244092382946393</v>
+        <v>0.12309347362957457</v>
       </c>
       <c r="G7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$10</f>
-        <v>1.5040923829463926E-2</v>
+        <v>5.6934736295745636E-3</v>
       </c>
       <c r="H7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$11</f>
-        <v>9.7940923829463927E-2</v>
+        <v>8.8593473629574565E-2</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>1.5997267456616144</v>
+        <v>5.7917118707600084</v>
       </c>
       <c r="K7" s="2">
-        <v>2.6866937246321601</v>
+        <v>9.1006872475781417</v>
       </c>
       <c r="L7" s="4">
-        <v>3.8615512854405329E-2</v>
+        <v>3.9551648141135085E-2</v>
       </c>
       <c r="M7" s="4">
-        <v>5.4163015835221838E-2</v>
+        <v>7.4263764404609467E-2</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="P7" s="14">
         <v>45900</v>
@@ -3651,100 +3642,100 @@
     </row>
     <row r="8" spans="1:17">
       <c r="B8" s="11" t="s">
-        <v>247</v>
+        <v>168</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>248</v>
+        <v>169</v>
       </c>
       <c r="D8" s="2">
-        <v>13.48</v>
+        <v>2.21</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F8" s="15">
-        <v>0.13185476539875873</v>
+        <v>0.11692472124626607</v>
       </c>
       <c r="G8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$10</f>
-        <v>1.4454765398758729E-2</v>
+        <v>-4.7527875373393202E-4</v>
       </c>
       <c r="H8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$11</f>
-        <v>9.735476539875873E-2</v>
+        <v>8.2424721246266069E-2</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
       </c>
       <c r="J8" s="2">
-        <v>10.178161876153645</v>
+        <v>1.6029152090321055</v>
       </c>
       <c r="K8" s="2">
-        <v>16.701383951862589</v>
+        <v>2.6941065610816408</v>
       </c>
       <c r="L8" s="4">
-        <v>0.11391563292899698</v>
+        <v>3.7141818309151198E-2</v>
       </c>
       <c r="M8" s="4">
-        <v>6.1834673590504444E-2</v>
+        <v>5.1816595986551785E-2</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>249</v>
+        <v>170</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>251</v>
+        <v>171</v>
       </c>
       <c r="P8" s="14">
         <v>45900</v>
       </c>
       <c r="Q8" s="11" t="s">
-        <v>250</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="B9" s="11" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D9" s="2">
-        <v>59.9</v>
+        <v>14.24</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F9" s="15">
-        <v>0.12493740306462042</v>
+        <v>0.11016267230709409</v>
       </c>
       <c r="G9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$10</f>
-        <v>7.5374030646204182E-3</v>
+        <v>-7.2373276929059149E-3</v>
       </c>
       <c r="H9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$11</f>
-        <v>9.043740306462042E-2</v>
+        <v>7.5662672307094087E-2</v>
       </c>
       <c r="I9" s="15">
         <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>44.107282041660923</v>
+        <v>10.176104857461148</v>
       </c>
       <c r="K9" s="2">
-        <v>78.252775679635405</v>
+        <v>16.698021477228806</v>
       </c>
       <c r="L9" s="4">
-        <v>3.7429294343278158E-2</v>
+        <v>0.10781351698346985</v>
       </c>
       <c r="M9" s="4">
-        <v>3.456803769335158E-2</v>
+        <v>5.8522441011235951E-2</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>162</v>
+        <v>251</v>
       </c>
       <c r="P9" s="14">
         <v>45900</v>
@@ -3761,33 +3752,33 @@
         <v>253</v>
       </c>
       <c r="D10" s="2">
-        <v>49.05</v>
+        <v>50.7</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F10" s="15">
-        <v>0.1151268191287802</v>
+        <v>0.10282033117906053</v>
       </c>
       <c r="G10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.2731808712198043E-3</v>
+        <v>-1.4579668820939473E-2</v>
       </c>
       <c r="H10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$11</f>
-        <v>8.0626819128780197E-2</v>
+        <v>6.8320331179060528E-2</v>
       </c>
       <c r="I10" s="15">
         <v>0</v>
       </c>
       <c r="J10" s="2">
-        <v>34.82424866299835</v>
+        <v>34.81706933071375</v>
       </c>
       <c r="K10" s="2">
-        <v>68.016110669918646</v>
+        <v>68.002088536550289</v>
       </c>
       <c r="L10" s="4">
-        <v>0.10720319069009697</v>
+        <v>0.10369294781216104</v>
       </c>
       <c r="M10" s="4">
         <v>0</v>
@@ -3807,16 +3798,16 @@
     </row>
     <row r="11" spans="1:17">
       <c r="B11" s="11" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D11" s="2">
         <v>28.81</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F11" s="15">
         <v>9.408289080523935E-2</v>
@@ -3845,7 +3836,7 @@
         <v>5.5536272127733433E-2</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="O11" s="11" t="s">
         <v>162</v>
@@ -3858,56 +3849,14 @@
       </c>
     </row>
     <row r="12" spans="1:17">
-      <c r="B12" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="D12" s="2">
-        <v>1.35</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="F12" s="15">
-        <v>-0.26037178228763347</v>
-      </c>
-      <c r="G12" s="15">
-        <f>F12 - Portfolio_Mgmt!$C$10</f>
-        <v>-0.37777178228763347</v>
-      </c>
-      <c r="H12" s="15">
-        <f>F12 - Portfolio_Mgmt!$C$11</f>
-        <v>-0.29487178228763344</v>
-      </c>
-      <c r="I12" s="15">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2">
-        <v>0.28748108885958823</v>
-      </c>
-      <c r="K12" s="2">
-        <v>0.52336150167888329</v>
-      </c>
-      <c r="L12" s="4">
-        <v>1.6563974747231462E-3</v>
-      </c>
-      <c r="M12" s="4">
-        <v>7.4074074074074068E-3</v>
-      </c>
-      <c r="N12" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="O12" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="P12" s="14">
-        <v>45900</v>
-      </c>
-      <c r="Q12" s="11" t="s">
-        <v>250</v>
-      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="E12" s="12"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="14"/>
     </row>
     <row r="13" spans="1:17">
       <c r="B13" s="11"/>
@@ -6041,14 +5990,14 @@
         <v>22</v>
       </c>
       <c r="C4" s="34">
-        <v>4.3499999999999997E-2</v>
+        <v>4.4199999999999996E-2</v>
       </c>
       <c r="D4" s="34">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="E4" s="35">
         <f>D4-C4</f>
-        <v>3.15E-2</v>
+        <v>3.0800000000000001E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DAB014C-9B41-49C7-A05D-552F6F9F10C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68EF0CA-81A3-4714-B5C2-2DA75A4C6A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="263">
   <si>
     <t>Name</t>
   </si>
@@ -1613,6 +1613,12 @@
   </si>
   <si>
     <t>CNS_01</t>
+  </si>
+  <si>
+    <t>2331.HK</t>
+  </si>
+  <si>
+    <t>李宁</t>
   </si>
 </sst>
 </file>
@@ -3209,11 +3215,11 @@
         <v>176</v>
       </c>
       <c r="C112" s="44">
-        <v>0.11210459565877447</v>
+        <v>0.12628169356729124</v>
       </c>
       <c r="D112" s="62" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
-        <v>Warning: Return is lower than the Benchmark.</v>
+        <v/>
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
@@ -3382,48 +3388,48 @@
     </row>
     <row r="3" spans="1:17">
       <c r="B3" s="11" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="D3" s="2">
-        <v>5.82</v>
+        <v>14.96</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F3" s="15">
-        <v>0.17654933116845006</v>
+        <v>0.21093739792614596</v>
       </c>
       <c r="G3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$10</f>
-        <v>5.9149331168450059E-2</v>
+        <v>9.353739792614596E-2</v>
       </c>
       <c r="H3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$11</f>
-        <v>0.14204933116845006</v>
+        <v>0.17643739792614596</v>
       </c>
       <c r="I3" s="15">
-        <v>0.21185919740214007</v>
+        <v>0.25312487751137513</v>
       </c>
       <c r="J3" s="2">
-        <v>4.9100950691878094</v>
+        <v>13.639056095083927</v>
       </c>
       <c r="K3" s="2">
-        <v>7.905135048592232</v>
+        <v>24.535432379107018</v>
       </c>
       <c r="L3" s="4">
-        <v>0.13194594963823414</v>
+        <v>7.7204543835549769E-2</v>
       </c>
       <c r="M3" s="4">
-        <v>7.5934623780754121E-2</v>
+        <v>3.687821612349914E-2</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>240</v>
+        <v>162</v>
       </c>
       <c r="P3" s="14">
         <v>45900</v>
@@ -3434,48 +3440,48 @@
     </row>
     <row r="4" spans="1:17">
       <c r="B4" s="11" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="D4" s="2">
-        <v>20.079999999999998</v>
+        <v>5.82</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>256</v>
+        <v>160</v>
       </c>
       <c r="F4" s="15">
-        <v>0.16060765378265396</v>
+        <v>0.17654933116845006</v>
       </c>
       <c r="G4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$10</f>
-        <v>4.3207653782653954E-2</v>
+        <v>5.9149331168450059E-2</v>
       </c>
       <c r="H4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$11</f>
-        <v>0.12610765378265396</v>
+        <v>0.14204933116845006</v>
       </c>
       <c r="I4" s="15">
-        <v>0.19272918453918475</v>
+        <v>0.21185919740214007</v>
       </c>
       <c r="J4" s="2">
-        <v>16.165402289394244</v>
+        <v>4.9100950691878094</v>
       </c>
       <c r="K4" s="2">
-        <v>29.309951346473134</v>
+        <v>7.905135048592232</v>
       </c>
       <c r="L4" s="4">
-        <v>0.22703991769612522</v>
+        <v>0.13194594963823414</v>
       </c>
       <c r="M4" s="4">
-        <v>2.956175298804781E-2</v>
+        <v>7.5934623780754121E-2</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>162</v>
+        <v>240</v>
       </c>
       <c r="P4" s="14">
         <v>45900</v>
@@ -3486,51 +3492,51 @@
     </row>
     <row r="5" spans="1:17">
       <c r="B5" s="11" t="s">
-        <v>158</v>
+        <v>254</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>159</v>
+        <v>255</v>
       </c>
       <c r="D5" s="2">
-        <v>16.420000000000002</v>
+        <v>20.079999999999998</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>160</v>
+        <v>256</v>
       </c>
       <c r="F5" s="15">
-        <v>0.15425024630514339</v>
+        <v>0.16060765378265396</v>
       </c>
       <c r="G5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$10</f>
-        <v>3.6850246305143386E-2</v>
+        <v>4.3207653782653954E-2</v>
       </c>
       <c r="H5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$11</f>
-        <v>0.11975024630514339</v>
+        <v>0.12610765378265396</v>
       </c>
       <c r="I5" s="15">
-        <v>0.18510029556617205</v>
+        <v>0.13501592508648474</v>
       </c>
       <c r="J5" s="2">
-        <v>13.155317996540354</v>
+        <v>16.165402289394244</v>
       </c>
       <c r="K5" s="2">
-        <v>20.508980461992877</v>
+        <v>29.309951346473134</v>
       </c>
       <c r="L5" s="4">
-        <v>0.1052366637862137</v>
+        <v>0.22703991769612522</v>
       </c>
       <c r="M5" s="4">
-        <v>8.282582216808769E-2</v>
+        <v>2.956175298804781E-2</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>161</v>
+        <v>257</v>
       </c>
       <c r="O5" s="11" t="s">
         <v>162</v>
       </c>
       <c r="P5" s="14">
-        <v>45808</v>
+        <v>45900</v>
       </c>
       <c r="Q5" s="11" t="s">
         <v>163</v>
@@ -3538,152 +3544,152 @@
     </row>
     <row r="6" spans="1:17">
       <c r="B6" s="11" t="s">
-        <v>242</v>
+        <v>158</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>243</v>
+        <v>159</v>
       </c>
       <c r="D6" s="2">
-        <v>58.45</v>
+        <v>16.420000000000002</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F6" s="15">
-        <v>0.13533159592642741</v>
+        <v>0.15425024630514339</v>
       </c>
       <c r="G6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$10</f>
-        <v>1.7931595926427402E-2</v>
+        <v>3.6850246305143386E-2</v>
       </c>
       <c r="H6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$11</f>
-        <v>0.1008315959264274</v>
+        <v>0.11975024630514339</v>
       </c>
       <c r="I6" s="15">
-        <v>1.0311322492503106E-2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>44.205240144973352</v>
+        <v>13.155317996540354</v>
       </c>
       <c r="K6" s="2">
-        <v>78.465475605444368</v>
+        <v>20.508980461992877</v>
       </c>
       <c r="L6" s="4">
-        <v>3.8461528914527629E-2</v>
+        <v>0.1052366637862137</v>
       </c>
       <c r="M6" s="4">
-        <v>3.5329662411002084E-2</v>
+        <v>8.282582216808769E-2</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>244</v>
+        <v>161</v>
       </c>
       <c r="O6" s="11" t="s">
         <v>162</v>
       </c>
       <c r="P6" s="14">
-        <v>45900</v>
+        <v>45808</v>
       </c>
       <c r="Q6" s="11" t="s">
-        <v>250</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="B7" s="11" t="s">
-        <v>164</v>
+        <v>242</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>165</v>
+        <v>243</v>
       </c>
       <c r="D7" s="2">
-        <v>7.81</v>
+        <v>58.45</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F7" s="15">
-        <v>0.12309347362957457</v>
+        <v>0.13533159592642741</v>
       </c>
       <c r="G7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$10</f>
-        <v>5.6934736295745636E-3</v>
+        <v>1.7931595926427402E-2</v>
       </c>
       <c r="H7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$11</f>
-        <v>8.8593473629574565E-2</v>
+        <v>0.1008315959264274</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>5.7917118707600084</v>
+        <v>44.205240144973352</v>
       </c>
       <c r="K7" s="2">
-        <v>9.1006872475781417</v>
+        <v>78.465475605444368</v>
       </c>
       <c r="L7" s="4">
-        <v>3.9551648141135085E-2</v>
+        <v>3.8461528914527629E-2</v>
       </c>
       <c r="M7" s="4">
-        <v>7.4263764404609467E-2</v>
+        <v>3.5329662411002084E-2</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>166</v>
+        <v>244</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="P7" s="14">
         <v>45900</v>
       </c>
       <c r="Q7" s="11" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="B8" s="11" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D8" s="2">
-        <v>2.21</v>
+        <v>7.81</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F8" s="15">
-        <v>0.11692472124626607</v>
+        <v>0.12309347362957457</v>
       </c>
       <c r="G8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$10</f>
-        <v>-4.7527875373393202E-4</v>
+        <v>5.6934736295745636E-3</v>
       </c>
       <c r="H8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$11</f>
-        <v>8.2424721246266069E-2</v>
+        <v>8.8593473629574565E-2</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
       </c>
       <c r="J8" s="2">
-        <v>1.6029152090321055</v>
+        <v>5.7917118707600084</v>
       </c>
       <c r="K8" s="2">
-        <v>2.6941065610816408</v>
+        <v>9.1006872475781417</v>
       </c>
       <c r="L8" s="4">
-        <v>3.7141818309151198E-2</v>
+        <v>3.9551648141135085E-2</v>
       </c>
       <c r="M8" s="4">
-        <v>5.1816595986551785E-2</v>
+        <v>7.4263764404609467E-2</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="P8" s="14">
         <v>45900</v>
@@ -3694,169 +3700,211 @@
     </row>
     <row r="9" spans="1:17">
       <c r="B9" s="11" t="s">
-        <v>247</v>
+        <v>168</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>248</v>
+        <v>169</v>
       </c>
       <c r="D9" s="2">
-        <v>14.24</v>
+        <v>2.21</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F9" s="15">
-        <v>0.11016267230709409</v>
+        <v>0.11692472124626607</v>
       </c>
       <c r="G9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$10</f>
-        <v>-7.2373276929059149E-3</v>
+        <v>-4.7527875373393202E-4</v>
       </c>
       <c r="H9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$11</f>
-        <v>7.5662672307094087E-2</v>
+        <v>8.2424721246266069E-2</v>
       </c>
       <c r="I9" s="15">
         <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>10.176104857461148</v>
+        <v>1.6029152090321055</v>
       </c>
       <c r="K9" s="2">
-        <v>16.698021477228806</v>
+        <v>2.6941065610816408</v>
       </c>
       <c r="L9" s="4">
-        <v>0.10781351698346985</v>
+        <v>3.7141818309151198E-2</v>
       </c>
       <c r="M9" s="4">
-        <v>5.8522441011235951E-2</v>
+        <v>5.1816595986551785E-2</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>249</v>
+        <v>170</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>251</v>
+        <v>171</v>
       </c>
       <c r="P9" s="14">
         <v>45900</v>
       </c>
       <c r="Q9" s="11" t="s">
-        <v>250</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="B10" s="11" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D10" s="2">
-        <v>50.7</v>
+        <v>14.24</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F10" s="15">
-        <v>0.10282033117906053</v>
+        <v>0.11016267230709409</v>
       </c>
       <c r="G10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$10</f>
-        <v>-1.4579668820939473E-2</v>
+        <v>-7.2373276929059149E-3</v>
       </c>
       <c r="H10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$11</f>
-        <v>6.8320331179060528E-2</v>
+        <v>7.5662672307094087E-2</v>
       </c>
       <c r="I10" s="15">
         <v>0</v>
       </c>
       <c r="J10" s="2">
-        <v>34.81706933071375</v>
+        <v>10.176104857461148</v>
       </c>
       <c r="K10" s="2">
-        <v>68.002088536550289</v>
+        <v>16.698021477228806</v>
       </c>
       <c r="L10" s="4">
-        <v>0.10369294781216104</v>
+        <v>0.10781351698346985</v>
       </c>
       <c r="M10" s="4">
-        <v>0</v>
+        <v>5.8522441011235951E-2</v>
       </c>
       <c r="N10" s="16" t="s">
         <v>249</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>162</v>
+        <v>251</v>
       </c>
       <c r="P10" s="14">
-        <v>45808</v>
+        <v>45900</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="B11" s="11" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D11" s="2">
-        <v>28.81</v>
+        <v>50.7</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>256</v>
+        <v>160</v>
       </c>
       <c r="F11" s="15">
-        <v>9.408289080523935E-2</v>
+        <v>0.10282033117906053</v>
       </c>
       <c r="G11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.3317109194760655E-2</v>
+        <v>-1.4579668820939473E-2</v>
       </c>
       <c r="H11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$11</f>
-        <v>5.9582890805239347E-2</v>
+        <v>6.8320331179060528E-2</v>
       </c>
       <c r="I11" s="15">
         <v>0</v>
       </c>
       <c r="J11" s="2">
-        <v>19.745207945921621</v>
+        <v>34.81706933071375</v>
       </c>
       <c r="K11" s="2">
-        <v>32.464859269378167</v>
+        <v>68.002088536550289</v>
       </c>
       <c r="L11" s="4">
-        <v>8.8134932571433455E-2</v>
+        <v>0.10369294781216104</v>
       </c>
       <c r="M11" s="4">
-        <v>5.5536272127733433E-2</v>
+        <v>0</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="O11" s="11" t="s">
         <v>162</v>
       </c>
       <c r="P11" s="14">
-        <v>45900</v>
+        <v>45808</v>
       </c>
       <c r="Q11" s="11" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:17">
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="E12" s="12"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="14"/>
+      <c r="B12" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="D12" s="2">
+        <v>28.81</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="F12" s="15">
+        <v>9.408289080523935E-2</v>
+      </c>
+      <c r="G12" s="15">
+        <f>F12 - Portfolio_Mgmt!$C$10</f>
+        <v>-2.3317109194760655E-2</v>
+      </c>
+      <c r="H12" s="15">
+        <f>F12 - Portfolio_Mgmt!$C$11</f>
+        <v>5.9582890805239347E-2</v>
+      </c>
+      <c r="I12" s="15">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2">
+        <v>19.745207945921621</v>
+      </c>
+      <c r="K12" s="2">
+        <v>32.464859269378167</v>
+      </c>
+      <c r="L12" s="4">
+        <v>8.8134932571433455E-2</v>
+      </c>
+      <c r="M12" s="4">
+        <v>5.5536272127733433E-2</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="O12" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="P12" s="14">
+        <v>45900</v>
+      </c>
+      <c r="Q12" s="11" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="13" spans="1:17">
       <c r="B13" s="11"/>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68EF0CA-81A3-4714-B5C2-2DA75A4C6A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4BC036-5925-4ED1-B215-6D3B640CF8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3215,7 +3215,7 @@
         <v>176</v>
       </c>
       <c r="C112" s="44">
-        <v>0.12628169356729124</v>
+        <v>0.12368197076027623</v>
       </c>
       <c r="D112" s="62" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
@@ -3400,24 +3400,24 @@
         <v>160</v>
       </c>
       <c r="F3" s="15">
-        <v>0.21093739792614596</v>
+        <v>0.20236403420229543</v>
       </c>
       <c r="G3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$10</f>
-        <v>9.353739792614596E-2</v>
+        <v>8.4964034202295424E-2</v>
       </c>
       <c r="H3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$11</f>
-        <v>0.17643739792614596</v>
+        <v>0.16786403420229543</v>
       </c>
       <c r="I3" s="15">
-        <v>0.25312487751137513</v>
+        <v>0.24283684104275449</v>
       </c>
       <c r="J3" s="2">
-        <v>13.639056095083927</v>
+        <v>13.36048258046131</v>
       </c>
       <c r="K3" s="2">
-        <v>24.535432379107018</v>
+        <v>23.991343483359721</v>
       </c>
       <c r="L3" s="4">
         <v>7.7204543835549769E-2</v>
@@ -3515,7 +3515,7 @@
         <v>0.12610765378265396</v>
       </c>
       <c r="I5" s="15">
-        <v>0.13501592508648474</v>
+        <v>0.14530396155510539</v>
       </c>
       <c r="J5" s="2">
         <v>16.165402289394244</v>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4BC036-5925-4ED1-B215-6D3B640CF8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C984EBAD-9828-492B-BEEA-71EFF069398A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="267">
   <si>
     <t>Name</t>
   </si>
@@ -1504,10 +1504,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Cash in HK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>nm</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1620,6 +1616,26 @@
   <si>
     <t>李宁</t>
   </si>
+  <si>
+    <t>2331.HK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Planning</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Beg. Cash Balance</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>End. Cash Balance</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Projected Holdings</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1632,7 +1648,7 @@
     <numFmt numFmtId="179" formatCode="#,##0.00_);\(#,##0.00\)"/>
     <numFmt numFmtId="180" formatCode="#,##0_);\(#,##0\)"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1852,6 +1868,11 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -1971,7 +1992,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2135,13 +2156,44 @@
     <xf numFmtId="180" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="180" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="180" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="30" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="180" fontId="31" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="179" fontId="31" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2587,12 +2639,12 @@
       <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B4" s="76" t="s">
+      <c r="B4" s="87" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="20" t="s">
@@ -2604,12 +2656,12 @@
       <c r="C6" s="62"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="87" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="76"/>
-      <c r="D7" s="76"/>
-      <c r="E7" s="76"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="23" t="s">
@@ -2698,12 +2750,12 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
-      <c r="B24" s="76" t="s">
+      <c r="B24" s="87" t="s">
         <v>220</v>
       </c>
-      <c r="C24" s="76"/>
-      <c r="D24" s="76"/>
-      <c r="E24" s="76"/>
+      <c r="C24" s="87"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="87"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
@@ -2797,20 +2849,20 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="B39" s="76" t="s">
+      <c r="B39" s="87" t="s">
         <v>156</v>
       </c>
-      <c r="C39" s="76"/>
-      <c r="D39" s="76"/>
-      <c r="E39" s="76"/>
+      <c r="C39" s="87"/>
+      <c r="D39" s="87"/>
+      <c r="E39" s="87"/>
     </row>
     <row r="40" spans="1:5" ht="46.6" customHeight="1">
-      <c r="B40" s="76" t="s">
-        <v>237</v>
-      </c>
-      <c r="C40" s="76"/>
-      <c r="D40" s="76"/>
-      <c r="E40" s="76"/>
+      <c r="B40" s="87" t="s">
+        <v>236</v>
+      </c>
+      <c r="C40" s="87"/>
+      <c r="D40" s="87"/>
+      <c r="E40" s="87"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="21" t="s">
@@ -2822,12 +2874,12 @@
       <c r="E42" s="21"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="B44" s="76" t="s">
+      <c r="B44" s="87" t="s">
         <v>208</v>
       </c>
-      <c r="C44" s="76"/>
-      <c r="D44" s="76"/>
-      <c r="E44" s="76"/>
+      <c r="C44" s="87"/>
+      <c r="D44" s="87"/>
+      <c r="E44" s="87"/>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="23" t="s">
@@ -3012,12 +3064,12 @@
       <c r="E69" s="21"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="B71" s="76" t="s">
+      <c r="B71" s="87" t="s">
         <v>196</v>
       </c>
-      <c r="C71" s="76"/>
-      <c r="D71" s="76"/>
-      <c r="E71" s="76"/>
+      <c r="C71" s="87"/>
+      <c r="D71" s="87"/>
+      <c r="E71" s="87"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="28" t="s">
@@ -3079,36 +3131,36 @@
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="B85" s="79" t="s">
+      <c r="B85" s="90" t="s">
         <v>192</v>
       </c>
-      <c r="C85" s="79"/>
-      <c r="D85" s="79"/>
-      <c r="E85" s="79"/>
+      <c r="C85" s="90"/>
+      <c r="D85" s="90"/>
+      <c r="E85" s="90"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="B86" s="78" t="s">
+      <c r="B86" s="89" t="s">
         <v>190</v>
       </c>
-      <c r="C86" s="78"/>
-      <c r="D86" s="78"/>
-      <c r="E86" s="78"/>
+      <c r="C86" s="89"/>
+      <c r="D86" s="89"/>
+      <c r="E86" s="89"/>
     </row>
     <row r="87" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B87" s="76" t="s">
+      <c r="B87" s="87" t="s">
         <v>189</v>
       </c>
-      <c r="C87" s="76"/>
-      <c r="D87" s="76"/>
-      <c r="E87" s="76"/>
+      <c r="C87" s="87"/>
+      <c r="D87" s="87"/>
+      <c r="E87" s="87"/>
     </row>
     <row r="88" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B88" s="76" t="s">
+      <c r="B88" s="87" t="s">
         <v>225</v>
       </c>
-      <c r="C88" s="76"/>
-      <c r="D88" s="76"/>
-      <c r="E88" s="76"/>
+      <c r="C88" s="87"/>
+      <c r="D88" s="87"/>
+      <c r="E88" s="87"/>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="24" t="s">
@@ -3141,12 +3193,12 @@
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="B97" s="77" t="s">
+      <c r="B97" s="88" t="s">
         <v>211</v>
       </c>
-      <c r="C97" s="77"/>
-      <c r="D97" s="77"/>
-      <c r="E97" s="77"/>
+      <c r="C97" s="88"/>
+      <c r="D97" s="88"/>
+      <c r="E97" s="88"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
@@ -3154,20 +3206,20 @@
       </c>
     </row>
     <row r="100" spans="1:5" ht="12.4">
-      <c r="B100" s="77" t="s">
+      <c r="B100" s="88" t="s">
         <v>212</v>
       </c>
-      <c r="C100" s="77"/>
-      <c r="D100" s="77"/>
-      <c r="E100" s="77"/>
+      <c r="C100" s="88"/>
+      <c r="D100" s="88"/>
+      <c r="E100" s="88"/>
     </row>
     <row r="101" spans="1:5" ht="58.5" customHeight="1">
-      <c r="B101" s="76" t="s">
+      <c r="B101" s="87" t="s">
         <v>219</v>
       </c>
-      <c r="C101" s="76"/>
-      <c r="D101" s="76"/>
-      <c r="E101" s="76"/>
+      <c r="C101" s="87"/>
+      <c r="D101" s="87"/>
+      <c r="E101" s="87"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="28" t="s">
@@ -3215,7 +3267,7 @@
         <v>176</v>
       </c>
       <c r="C112" s="44">
-        <v>0.12368197076027623</v>
+        <v>0.13078963304662303</v>
       </c>
       <c r="D112" s="62" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
@@ -3223,12 +3275,12 @@
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B114" s="76" t="s">
+      <c r="B114" s="87" t="s">
         <v>217</v>
       </c>
-      <c r="C114" s="76"/>
-      <c r="D114" s="76"/>
-      <c r="E114" s="76"/>
+      <c r="C114" s="87"/>
+      <c r="D114" s="87"/>
+      <c r="E114" s="87"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="21" t="s">
@@ -3311,30 +3363,30 @@
       <c r="B1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="83" t="s">
+      <c r="D1" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="84" t="s">
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="80" t="s">
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="80"/>
-      <c r="L1" s="81" t="s">
+      <c r="K1" s="91"/>
+      <c r="L1" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="81"/>
-      <c r="N1" s="82" t="s">
+      <c r="M1" s="92"/>
+      <c r="N1" s="93" t="s">
         <v>53</v>
       </c>
-      <c r="O1" s="82"/>
-      <c r="P1" s="82"/>
-      <c r="Q1" s="82"/>
+      <c r="O1" s="93"/>
+      <c r="P1" s="93"/>
+      <c r="Q1" s="93"/>
     </row>
     <row r="2" spans="1:17" ht="26" customHeight="1">
       <c r="B2" s="7" t="s">
@@ -3388,45 +3440,45 @@
     </row>
     <row r="3" spans="1:17">
       <c r="B3" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>262</v>
-      </c>
       <c r="D3" s="2">
-        <v>14.96</v>
+        <v>14.62</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F3" s="15">
-        <v>0.20236403420229543</v>
+        <v>0.22170440631904209</v>
       </c>
       <c r="G3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$10</f>
-        <v>8.4964034202295424E-2</v>
+        <v>0.10430440631904209</v>
       </c>
       <c r="H3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$11</f>
-        <v>0.16786403420229543</v>
+        <v>0.18720440631904209</v>
       </c>
       <c r="I3" s="15">
-        <v>0.24283684104275449</v>
+        <v>0.26604528758285051</v>
       </c>
       <c r="J3" s="2">
-        <v>13.36048258046131</v>
+        <v>13.677042438413379</v>
       </c>
       <c r="K3" s="2">
-        <v>23.991343483359721</v>
+        <v>24.622857747833486</v>
       </c>
       <c r="L3" s="4">
-        <v>7.7204543835549769E-2</v>
+        <v>6.4508135967563232E-2</v>
       </c>
       <c r="M3" s="4">
-        <v>3.687821612349914E-2</v>
+        <v>3.749843268269646E-2</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O3" s="11" t="s">
         <v>162</v>
@@ -3440,48 +3492,48 @@
     </row>
     <row r="4" spans="1:17">
       <c r="B4" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>239</v>
-      </c>
       <c r="D4" s="2">
-        <v>5.82</v>
+        <v>5.8</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F4" s="15">
-        <v>0.17654933116845006</v>
+        <v>0.1784289263913903</v>
       </c>
       <c r="G4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$10</f>
-        <v>5.9149331168450059E-2</v>
+        <v>6.1028926391390292E-2</v>
       </c>
       <c r="H4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$11</f>
-        <v>0.14204933116845006</v>
+        <v>0.14392892639139029</v>
       </c>
       <c r="I4" s="15">
-        <v>0.21185919740214007</v>
+        <v>0.21411471166966836</v>
       </c>
       <c r="J4" s="2">
-        <v>4.9100950691878094</v>
+        <v>4.91520725037517</v>
       </c>
       <c r="K4" s="2">
-        <v>7.905135048592232</v>
+        <v>7.9151197774737954</v>
       </c>
       <c r="L4" s="4">
-        <v>0.13194594963823414</v>
+        <v>0.13256816715305939</v>
       </c>
       <c r="M4" s="4">
-        <v>7.5934623780754121E-2</v>
+        <v>7.6196467311032592E-2</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P4" s="14">
         <v>45900</v>
@@ -3492,45 +3544,45 @@
     </row>
     <row r="5" spans="1:17">
       <c r="B5" s="11" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="D5" s="2">
-        <v>20.079999999999998</v>
+        <v>54.25</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>256</v>
+        <v>160</v>
       </c>
       <c r="F5" s="15">
-        <v>0.16060765378265396</v>
+        <v>0.16523666770490664</v>
       </c>
       <c r="G5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$10</f>
-        <v>4.3207653782653954E-2</v>
+        <v>4.7836667704906632E-2</v>
       </c>
       <c r="H5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$11</f>
-        <v>0.12610765378265396</v>
+        <v>0.13073666770490663</v>
       </c>
       <c r="I5" s="15">
-        <v>0.14530396155510539</v>
+        <v>0.11984000074748113</v>
       </c>
       <c r="J5" s="2">
-        <v>16.165402289394244</v>
+        <v>44.250954726078248</v>
       </c>
       <c r="K5" s="2">
-        <v>29.309951346473134</v>
+        <v>78.564693346218675</v>
       </c>
       <c r="L5" s="4">
-        <v>0.22703991769612522</v>
+        <v>4.1491316575080379E-2</v>
       </c>
       <c r="M5" s="4">
-        <v>2.956175298804781E-2</v>
+        <v>3.8016844194438813E-2</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="O5" s="11" t="s">
         <v>162</v>
@@ -3539,56 +3591,56 @@
         <v>45900</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>163</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="B6" s="11" t="s">
-        <v>158</v>
+        <v>253</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>159</v>
+        <v>254</v>
       </c>
       <c r="D6" s="2">
-        <v>16.420000000000002</v>
+        <v>20.079999999999998</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>160</v>
+        <v>255</v>
       </c>
       <c r="F6" s="15">
-        <v>0.15425024630514339</v>
+        <v>0.16060765378265396</v>
       </c>
       <c r="G6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$10</f>
-        <v>3.6850246305143386E-2</v>
+        <v>4.3207653782653954E-2</v>
       </c>
       <c r="H6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$11</f>
-        <v>0.11975024630514339</v>
+        <v>0.12610765378265396</v>
       </c>
       <c r="I6" s="15">
         <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>13.155317996540354</v>
+        <v>16.165402289394244</v>
       </c>
       <c r="K6" s="2">
-        <v>20.508980461992877</v>
+        <v>29.309951346473134</v>
       </c>
       <c r="L6" s="4">
-        <v>0.1052366637862137</v>
+        <v>0.22703991769612522</v>
       </c>
       <c r="M6" s="4">
-        <v>8.282582216808769E-2</v>
+        <v>2.956175298804781E-2</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>161</v>
+        <v>256</v>
       </c>
       <c r="O6" s="11" t="s">
         <v>162</v>
       </c>
       <c r="P6" s="14">
-        <v>45808</v>
+        <v>45900</v>
       </c>
       <c r="Q6" s="11" t="s">
         <v>163</v>
@@ -3596,54 +3648,54 @@
     </row>
     <row r="7" spans="1:17">
       <c r="B7" s="11" t="s">
-        <v>242</v>
+        <v>158</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>243</v>
+        <v>159</v>
       </c>
       <c r="D7" s="2">
-        <v>58.45</v>
+        <v>16.440000000000001</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F7" s="15">
-        <v>0.13533159592642741</v>
+        <v>0.15374754303551685</v>
       </c>
       <c r="G7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$10</f>
-        <v>1.7931595926427402E-2</v>
+        <v>3.6347543035516849E-2</v>
       </c>
       <c r="H7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$11</f>
-        <v>0.1008315959264274</v>
+        <v>0.11924754303551685</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>44.205240144973352</v>
+        <v>13.155317996540354</v>
       </c>
       <c r="K7" s="2">
-        <v>78.465475605444368</v>
+        <v>20.508980461992877</v>
       </c>
       <c r="L7" s="4">
-        <v>3.8461528914527629E-2</v>
+        <v>0.10510863864778767</v>
       </c>
       <c r="M7" s="4">
-        <v>3.5329662411002084E-2</v>
+        <v>8.2725060827250604E-2</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>244</v>
+        <v>161</v>
       </c>
       <c r="O7" s="11" t="s">
         <v>162</v>
       </c>
       <c r="P7" s="14">
-        <v>45900</v>
+        <v>45808</v>
       </c>
       <c r="Q7" s="11" t="s">
-        <v>250</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -3654,21 +3706,21 @@
         <v>165</v>
       </c>
       <c r="D8" s="2">
-        <v>7.81</v>
+        <v>7.85</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F8" s="15">
-        <v>0.12309347362957457</v>
+        <v>0.12105292184429062</v>
       </c>
       <c r="G8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$10</f>
-        <v>5.6934736295745636E-3</v>
+        <v>3.6529218442906131E-3</v>
       </c>
       <c r="H8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$11</f>
-        <v>8.8593473629574565E-2</v>
+        <v>8.6552921844290615E-2</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
@@ -3680,10 +3732,10 @@
         <v>9.1006872475781417</v>
       </c>
       <c r="L8" s="4">
-        <v>3.9551648141135085E-2</v>
+        <v>3.9350111080543315E-2</v>
       </c>
       <c r="M8" s="4">
-        <v>7.4263764404609467E-2</v>
+        <v>7.3885350318471335E-2</v>
       </c>
       <c r="N8" s="13" t="s">
         <v>166</v>
@@ -3700,155 +3752,155 @@
     </row>
     <row r="9" spans="1:17">
       <c r="B9" s="11" t="s">
-        <v>168</v>
+        <v>246</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>169</v>
+        <v>247</v>
       </c>
       <c r="D9" s="2">
-        <v>2.21</v>
+        <v>14.26</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F9" s="15">
-        <v>0.11692472124626607</v>
+        <v>0.10954171828338932</v>
       </c>
       <c r="G9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$10</f>
-        <v>-4.7527875373393202E-4</v>
+        <v>-7.8582817166106822E-3</v>
       </c>
       <c r="H9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$11</f>
-        <v>8.2424721246266069E-2</v>
+        <v>7.5041718283389319E-2</v>
       </c>
       <c r="I9" s="15">
         <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>1.6029152090321055</v>
+        <v>10.174176386967826</v>
       </c>
       <c r="K9" s="2">
-        <v>2.6941065610816408</v>
+        <v>16.694869127046534</v>
       </c>
       <c r="L9" s="4">
-        <v>3.7141818309151198E-2</v>
+        <v>0.10764138310388582</v>
       </c>
       <c r="M9" s="4">
-        <v>5.1816595986551785E-2</v>
+        <v>5.8429064516129031E-2</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>170</v>
+        <v>248</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>171</v>
+        <v>250</v>
       </c>
       <c r="P9" s="14">
         <v>45900</v>
       </c>
       <c r="Q9" s="11" t="s">
-        <v>163</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="B10" s="11" t="s">
-        <v>247</v>
+        <v>168</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>248</v>
+        <v>169</v>
       </c>
       <c r="D10" s="2">
-        <v>14.24</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F10" s="15">
-        <v>0.11016267230709409</v>
+        <v>0.10185445179346719</v>
       </c>
       <c r="G10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$10</f>
-        <v>-7.2373276929059149E-3</v>
+        <v>-1.5545548206532811E-2</v>
       </c>
       <c r="H10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$11</f>
-        <v>7.5662672307094087E-2</v>
+        <v>6.735445179346719E-2</v>
       </c>
       <c r="I10" s="15">
         <v>0</v>
       </c>
       <c r="J10" s="2">
-        <v>10.176104857461148</v>
+        <v>1.6044036483689859</v>
       </c>
       <c r="K10" s="2">
-        <v>16.698021477228806</v>
+        <v>2.6975644131821959</v>
       </c>
       <c r="L10" s="4">
-        <v>0.10781351698346985</v>
+        <v>3.5732763614444767E-2</v>
       </c>
       <c r="M10" s="4">
-        <v>5.8522441011235951E-2</v>
+        <v>4.972618247053226E-2</v>
       </c>
       <c r="N10" s="16" t="s">
-        <v>249</v>
+        <v>170</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>251</v>
+        <v>171</v>
       </c>
       <c r="P10" s="14">
         <v>45900</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>250</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="B11" s="11" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="D11" s="2">
-        <v>50.7</v>
+        <v>28.81</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>160</v>
+        <v>255</v>
       </c>
       <c r="F11" s="15">
-        <v>0.10282033117906053</v>
+        <v>9.408289080523935E-2</v>
       </c>
       <c r="G11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$10</f>
-        <v>-1.4579668820939473E-2</v>
+        <v>-2.3317109194760655E-2</v>
       </c>
       <c r="H11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$11</f>
-        <v>6.8320331179060528E-2</v>
+        <v>5.9582890805239347E-2</v>
       </c>
       <c r="I11" s="15">
         <v>0</v>
       </c>
       <c r="J11" s="2">
-        <v>34.81706933071375</v>
+        <v>19.745207945921621</v>
       </c>
       <c r="K11" s="2">
-        <v>68.002088536550289</v>
+        <v>32.464859269378167</v>
       </c>
       <c r="L11" s="4">
-        <v>0.10369294781216104</v>
+        <v>8.8134932571433455E-2</v>
       </c>
       <c r="M11" s="4">
-        <v>0</v>
+        <v>5.5536272127733433E-2</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="O11" s="11" t="s">
         <v>162</v>
       </c>
       <c r="P11" s="14">
-        <v>45808</v>
+        <v>45900</v>
       </c>
       <c r="Q11" s="11" t="s">
         <v>163</v>
@@ -3856,51 +3908,51 @@
     </row>
     <row r="12" spans="1:17">
       <c r="B12" s="11" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D12" s="2">
-        <v>28.81</v>
+        <v>52.2</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>256</v>
+        <v>160</v>
       </c>
       <c r="F12" s="15">
-        <v>9.408289080523935E-2</v>
+        <v>9.2083708290373378E-2</v>
       </c>
       <c r="G12" s="15">
         <f>F12 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.3317109194760655E-2</v>
+        <v>-2.5316291709626626E-2</v>
       </c>
       <c r="H12" s="15">
         <f>F12 - Portfolio_Mgmt!$C$11</f>
-        <v>5.9582890805239347E-2</v>
+        <v>5.7583708290373375E-2</v>
       </c>
       <c r="I12" s="15">
         <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>19.745207945921621</v>
+        <v>34.810338706696939</v>
       </c>
       <c r="K12" s="2">
-        <v>32.464859269378167</v>
+        <v>67.988942786517455</v>
       </c>
       <c r="L12" s="4">
-        <v>8.8134932571433455E-2</v>
+        <v>0.10069379612803481</v>
       </c>
       <c r="M12" s="4">
-        <v>5.5536272127733433E-2</v>
+        <v>0</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="O12" s="11" t="s">
         <v>162</v>
       </c>
       <c r="P12" s="14">
-        <v>45900</v>
+        <v>45808</v>
       </c>
       <c r="Q12" s="11" t="s">
         <v>163</v>
@@ -5988,7 +6040,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.75" customHeight="1" zeroHeight="1"/>
   <cols>
-    <col min="1" max="16384" width="9.06640625" style="74"/>
+    <col min="1" max="16384" width="9.06640625" style="73"/>
   </cols>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -6038,14 +6090,14 @@
         <v>22</v>
       </c>
       <c r="C4" s="34">
-        <v>4.4199999999999996E-2</v>
+        <v>4.2900000000000001E-2</v>
       </c>
       <c r="D4" s="34">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="E4" s="35">
         <f>D4-C4</f>
-        <v>3.0800000000000001E-2</v>
+        <v>3.2099999999999997E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6290,39 +6342,39 @@
         <v>227</v>
       </c>
       <c r="F2" s="67" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G2" s="67" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="78" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="76" t="s">
         <v>233</v>
       </c>
-      <c r="C3" s="71" t="s">
-        <v>234</v>
-      </c>
-      <c r="D3" s="68" t="s">
+      <c r="D3" s="75" t="s">
         <v>230</v>
       </c>
-      <c r="E3" s="72" t="s">
-        <v>234</v>
+      <c r="E3" s="77" t="s">
+        <v>233</v>
       </c>
       <c r="F3" s="72">
-        <v>395673.88</v>
-      </c>
-      <c r="G3" s="75">
-        <f>F3/$F$8</f>
-        <v>0.50576089073376196</v>
+        <v>351395.62</v>
+      </c>
+      <c r="G3" s="74">
+        <f>F3/$F$9</f>
+        <v>0.43175061871716075</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="79" t="s">
         <v>232</v>
       </c>
       <c r="C4" s="71">
-        <v>14.2</v>
+        <v>16.54</v>
       </c>
       <c r="D4" s="68" t="s">
         <v>230</v>
@@ -6330,17 +6382,17 @@
       <c r="E4" s="72">
         <v>10000</v>
       </c>
-      <c r="F4" s="72">
+      <c r="F4" s="77">
         <f>C4*E4</f>
-        <v>142000</v>
-      </c>
-      <c r="G4" s="75">
-        <f t="shared" ref="G4:G6" si="0">F4/$F$8</f>
-        <v>0.18150818164745722</v>
+        <v>165400</v>
+      </c>
+      <c r="G4" s="74">
+        <f>F4/$F$9</f>
+        <v>0.2032226592232948</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="79" t="s">
         <v>231</v>
       </c>
       <c r="C5" s="71">
@@ -6352,18 +6404,18 @@
       <c r="E5" s="72">
         <v>20000</v>
       </c>
-      <c r="F5" s="72">
+      <c r="F5" s="77">
         <f>E5*C5</f>
         <v>148000</v>
       </c>
-      <c r="G5" s="75">
-        <f t="shared" si="0"/>
-        <v>0.18917754143537796</v>
+      <c r="G5" s="74">
+        <f>F5/$F$9</f>
+        <v>0.18184373376691432</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="B6" s="68" t="s">
-        <v>245</v>
+      <c r="B6" s="79" t="s">
+        <v>244</v>
       </c>
       <c r="C6" s="71">
         <v>5.37</v>
@@ -6374,38 +6426,58 @@
       <c r="E6" s="72">
         <v>18000</v>
       </c>
-      <c r="F6" s="72">
+      <c r="F6" s="77">
         <f>E6*C6</f>
         <v>96660</v>
       </c>
-      <c r="G6" s="75">
-        <f t="shared" si="0"/>
-        <v>0.12355338618340292</v>
+      <c r="G6" s="74">
+        <f>F6/$F$9</f>
+        <v>0.11876361693182391</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="B7" s="68"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="68"/>
-    </row>
-    <row r="8" spans="1:7" ht="13.15">
+      <c r="B7" s="79" t="s">
+        <v>260</v>
+      </c>
+      <c r="C7" s="71">
+        <v>14.98</v>
+      </c>
+      <c r="D7" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="E7" s="72">
+        <f>500*7</f>
+        <v>3500</v>
+      </c>
+      <c r="F7" s="77">
+        <f>C7*E7</f>
+        <v>52430</v>
+      </c>
+      <c r="G7" s="74">
+        <f>F7/$F$9</f>
+        <v>6.4419371360806207E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="B8" s="68"/>
       <c r="C8" s="71"/>
       <c r="D8" s="68"/>
-      <c r="E8" s="73" t="s">
-        <v>235</v>
-      </c>
-      <c r="F8" s="73">
+    </row>
+    <row r="9" spans="1:7" ht="13.15">
+      <c r="B9" s="80"/>
+      <c r="C9" s="81"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="82" t="s">
+        <v>234</v>
+      </c>
+      <c r="F9" s="82">
         <f>SUM(F3:F7)</f>
-        <v>782333.88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="B9" s="68"/>
-      <c r="C9" s="71"/>
-      <c r="D9" s="68"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
+        <v>813885.62</v>
+      </c>
+      <c r="G9" s="83">
+        <f>SUM(G3:G7)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:7">
       <c r="B10" s="68"/>
@@ -6414,40 +6486,87 @@
       <c r="E10" s="72"/>
       <c r="F10" s="72"/>
     </row>
-    <row r="11" spans="1:7">
-      <c r="B11" s="68"/>
+    <row r="11" spans="1:7" ht="13.15">
+      <c r="A11" s="64"/>
+      <c r="B11" s="65" t="s">
+        <v>263</v>
+      </c>
       <c r="C11" s="71"/>
       <c r="D11" s="68"/>
       <c r="E11" s="72"/>
       <c r="F11" s="72"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="B12" s="68"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="68"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
+      <c r="B12" s="78" t="s">
+        <v>264</v>
+      </c>
+      <c r="C12" s="76" t="s">
+        <v>233</v>
+      </c>
+      <c r="D12" s="75" t="s">
+        <v>160</v>
+      </c>
+      <c r="E12" s="76" t="s">
+        <v>233</v>
+      </c>
+      <c r="F12" s="77">
+        <f>F3</f>
+        <v>351395.62</v>
+      </c>
+      <c r="G12" s="74">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="B13" s="68"/>
-      <c r="C13" s="71"/>
-      <c r="D13" s="68"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
+      <c r="B13" s="79" t="s">
+        <v>260</v>
+      </c>
+      <c r="C13" s="71">
+        <v>14.9</v>
+      </c>
+      <c r="D13" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="E13" s="72">
+        <v>8000</v>
+      </c>
+      <c r="F13" s="77">
+        <f>C13*E13</f>
+        <v>119200</v>
+      </c>
+      <c r="G13" s="74">
+        <f>F13/$F$12</f>
+        <v>0.3392187984585579</v>
+      </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="B14" s="68"/>
+      <c r="B14" s="79"/>
       <c r="C14" s="71"/>
       <c r="D14" s="68"/>
       <c r="E14" s="72"/>
       <c r="F14" s="72"/>
     </row>
-    <row r="15" spans="1:7">
-      <c r="B15" s="68"/>
-      <c r="C15" s="71"/>
-      <c r="D15" s="68"/>
-      <c r="E15" s="72"/>
-      <c r="F15" s="72"/>
+    <row r="15" spans="1:7" ht="13.15">
+      <c r="B15" s="84" t="s">
+        <v>265</v>
+      </c>
+      <c r="C15" s="85" t="s">
+        <v>233</v>
+      </c>
+      <c r="D15" s="86" t="s">
+        <v>160</v>
+      </c>
+      <c r="E15" s="85" t="s">
+        <v>233</v>
+      </c>
+      <c r="F15" s="82">
+        <f>F12-F13</f>
+        <v>232195.62</v>
+      </c>
+      <c r="G15" s="83">
+        <f>F15/$F$12</f>
+        <v>0.66078120154144204</v>
+      </c>
     </row>
     <row r="16" spans="1:7">
       <c r="B16" s="68"/>
@@ -6456,105 +6575,200 @@
       <c r="E16" s="72"/>
       <c r="F16" s="72"/>
     </row>
-    <row r="17" spans="2:6">
-      <c r="B17" s="68"/>
-      <c r="C17" s="71"/>
-      <c r="D17" s="68"/>
-      <c r="E17" s="72"/>
-      <c r="F17" s="72"/>
-    </row>
-    <row r="18" spans="2:6">
-      <c r="B18" s="68"/>
-      <c r="C18" s="71"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="72"/>
-    </row>
-    <row r="19" spans="2:6">
-      <c r="B19" s="68"/>
-      <c r="C19" s="71"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="72"/>
-    </row>
-    <row r="20" spans="2:6">
-      <c r="B20" s="68"/>
-      <c r="C20" s="71"/>
-      <c r="D20" s="68"/>
-      <c r="E20" s="72"/>
-      <c r="F20" s="72"/>
-    </row>
-    <row r="21" spans="2:6">
-      <c r="B21" s="68"/>
-      <c r="C21" s="71"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="72"/>
-      <c r="F21" s="72"/>
-    </row>
-    <row r="22" spans="2:6">
-      <c r="B22" s="68"/>
-      <c r="C22" s="71"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="72"/>
-    </row>
-    <row r="23" spans="2:6">
-      <c r="B23" s="68"/>
-      <c r="C23" s="71"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="72"/>
-      <c r="F23" s="72"/>
-    </row>
-    <row r="24" spans="2:6">
+    <row r="17" spans="1:7" ht="13.15">
+      <c r="A17" s="64"/>
+      <c r="B17" s="65" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="26.25">
+      <c r="B18" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="67" t="s">
+        <v>229</v>
+      </c>
+      <c r="D18" s="67" t="s">
+        <v>228</v>
+      </c>
+      <c r="E18" s="67" t="s">
+        <v>227</v>
+      </c>
+      <c r="F18" s="67" t="s">
+        <v>235</v>
+      </c>
+      <c r="G18" s="67" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="B19" s="78" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="76" t="s">
+        <v>233</v>
+      </c>
+      <c r="D19" s="75" t="s">
+        <v>230</v>
+      </c>
+      <c r="E19" s="77" t="s">
+        <v>233</v>
+      </c>
+      <c r="F19" s="77">
+        <f>F15</f>
+        <v>232195.62</v>
+      </c>
+      <c r="G19" s="74">
+        <f>F19/$F$9</f>
+        <v>0.28529269260218654</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="B20" s="79" t="s">
+        <v>232</v>
+      </c>
+      <c r="C20" s="71">
+        <v>16.54</v>
+      </c>
+      <c r="D20" s="68" t="s">
+        <v>230</v>
+      </c>
+      <c r="E20" s="72">
+        <v>10000</v>
+      </c>
+      <c r="F20" s="77">
+        <f>C20*E20</f>
+        <v>165400</v>
+      </c>
+      <c r="G20" s="74">
+        <f t="shared" ref="G20:G23" si="0">F20/$F$9</f>
+        <v>0.2032226592232948</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="B21" s="79" t="s">
+        <v>231</v>
+      </c>
+      <c r="C21" s="71">
+        <v>7.4</v>
+      </c>
+      <c r="D21" s="68" t="s">
+        <v>230</v>
+      </c>
+      <c r="E21" s="72">
+        <v>20000</v>
+      </c>
+      <c r="F21" s="77">
+        <f>E21*C21</f>
+        <v>148000</v>
+      </c>
+      <c r="G21" s="74">
+        <f t="shared" si="0"/>
+        <v>0.18184373376691432</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="B22" s="79" t="s">
+        <v>244</v>
+      </c>
+      <c r="C22" s="71">
+        <v>5.37</v>
+      </c>
+      <c r="D22" s="68" t="s">
+        <v>230</v>
+      </c>
+      <c r="E22" s="72">
+        <v>18000</v>
+      </c>
+      <c r="F22" s="77">
+        <f>E22*C22</f>
+        <v>96660</v>
+      </c>
+      <c r="G22" s="74">
+        <f t="shared" si="0"/>
+        <v>0.11876361693182391</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="B23" s="79" t="s">
+        <v>262</v>
+      </c>
+      <c r="C23" s="71">
+        <v>14.9</v>
+      </c>
+      <c r="D23" s="68" t="s">
+        <v>230</v>
+      </c>
+      <c r="E23" s="72">
+        <f>E7+E13</f>
+        <v>11500</v>
+      </c>
+      <c r="F23" s="77">
+        <f>E23*C23</f>
+        <v>171350</v>
+      </c>
+      <c r="G23" s="74">
+        <f t="shared" si="0"/>
+        <v>0.21053326879027548</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="B24" s="68"/>
       <c r="C24" s="71"/>
       <c r="D24" s="68"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="72"/>
-    </row>
-    <row r="25" spans="2:6">
-      <c r="B25" s="68"/>
-      <c r="C25" s="71"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="72"/>
-      <c r="F25" s="72"/>
-    </row>
-    <row r="26" spans="2:6">
+    </row>
+    <row r="25" spans="1:7" ht="13.15">
+      <c r="B25" s="80"/>
+      <c r="C25" s="81"/>
+      <c r="D25" s="80"/>
+      <c r="E25" s="82" t="s">
+        <v>234</v>
+      </c>
+      <c r="F25" s="82">
+        <f>SUM(F19:F23)</f>
+        <v>813605.62</v>
+      </c>
+      <c r="G25" s="83">
+        <f>SUM(G19:G23)</f>
+        <v>0.99965597131449502</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="B26" s="68"/>
       <c r="C26" s="71"/>
       <c r="D26" s="68"/>
       <c r="E26" s="72"/>
       <c r="F26" s="72"/>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="1:7">
       <c r="B27" s="68"/>
       <c r="C27" s="71"/>
       <c r="D27" s="68"/>
       <c r="E27" s="72"/>
       <c r="F27" s="72"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="1:7">
       <c r="B28" s="68"/>
       <c r="C28" s="71"/>
       <c r="D28" s="68"/>
       <c r="E28" s="72"/>
       <c r="F28" s="72"/>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="1:7">
       <c r="B29" s="68"/>
       <c r="C29" s="71"/>
       <c r="D29" s="68"/>
       <c r="E29" s="72"/>
       <c r="F29" s="72"/>
     </row>
-    <row r="30" spans="2:6">
+    <row r="30" spans="1:7">
       <c r="B30" s="68"/>
       <c r="C30" s="71"/>
       <c r="D30" s="68"/>
       <c r="E30" s="72"/>
       <c r="F30" s="72"/>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="1:7">
       <c r="B31" s="68"/>
       <c r="C31" s="69"/>
       <c r="D31" s="68"/>
@@ -6592,25 +6806,25 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="B3" s="85" t="s">
+      <c r="B3" s="96" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="B5" s="86" t="s">
+      <c r="B5" s="97" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="88"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="97" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="77"/>
-      <c r="D6" s="77"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="88"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">
@@ -6624,18 +6838,18 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="85" t="s">
+      <c r="B11" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="C11" s="85"/>
-      <c r="D11" s="85"/>
+      <c r="C11" s="96"/>
+      <c r="D11" s="96"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="B12" s="85" t="s">
+      <c r="B12" s="96" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="85"/>
-      <c r="D12" s="85"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="96"/>
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="23" t="s">
@@ -6729,18 +6943,18 @@
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="B28" s="85" t="s">
+      <c r="B28" s="96" t="s">
         <v>122</v>
       </c>
-      <c r="C28" s="85"/>
-      <c r="D28" s="85"/>
+      <c r="C28" s="96"/>
+      <c r="D28" s="96"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="B29" s="85" t="s">
+      <c r="B29" s="96" t="s">
         <v>123</v>
       </c>
-      <c r="C29" s="85"/>
-      <c r="D29" s="85"/>
+      <c r="C29" s="96"/>
+      <c r="D29" s="96"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="5"/>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C984EBAD-9828-492B-BEEA-71EFF069398A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE16CB6-A1EE-468B-B087-A67C98BA3B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -2194,17 +2194,17 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2639,12 +2639,12 @@
       <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="88" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="87"/>
-      <c r="D4" s="87"/>
-      <c r="E4" s="87"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="20" t="s">
@@ -2656,12 +2656,12 @@
       <c r="C6" s="62"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" s="87" t="s">
+      <c r="B7" s="88" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="87"/>
-      <c r="D7" s="87"/>
-      <c r="E7" s="87"/>
+      <c r="C7" s="88"/>
+      <c r="D7" s="88"/>
+      <c r="E7" s="88"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="23" t="s">
@@ -2750,12 +2750,12 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
-      <c r="B24" s="87" t="s">
+      <c r="B24" s="88" t="s">
         <v>220</v>
       </c>
-      <c r="C24" s="87"/>
-      <c r="D24" s="87"/>
-      <c r="E24" s="87"/>
+      <c r="C24" s="88"/>
+      <c r="D24" s="88"/>
+      <c r="E24" s="88"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
@@ -2849,20 +2849,20 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="B39" s="87" t="s">
+      <c r="B39" s="88" t="s">
         <v>156</v>
       </c>
-      <c r="C39" s="87"/>
-      <c r="D39" s="87"/>
-      <c r="E39" s="87"/>
+      <c r="C39" s="88"/>
+      <c r="D39" s="88"/>
+      <c r="E39" s="88"/>
     </row>
     <row r="40" spans="1:5" ht="46.6" customHeight="1">
-      <c r="B40" s="87" t="s">
+      <c r="B40" s="88" t="s">
         <v>236</v>
       </c>
-      <c r="C40" s="87"/>
-      <c r="D40" s="87"/>
-      <c r="E40" s="87"/>
+      <c r="C40" s="88"/>
+      <c r="D40" s="88"/>
+      <c r="E40" s="88"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="21" t="s">
@@ -2874,12 +2874,12 @@
       <c r="E42" s="21"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="B44" s="87" t="s">
+      <c r="B44" s="88" t="s">
         <v>208</v>
       </c>
-      <c r="C44" s="87"/>
-      <c r="D44" s="87"/>
-      <c r="E44" s="87"/>
+      <c r="C44" s="88"/>
+      <c r="D44" s="88"/>
+      <c r="E44" s="88"/>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="23" t="s">
@@ -3064,12 +3064,12 @@
       <c r="E69" s="21"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="B71" s="87" t="s">
+      <c r="B71" s="88" t="s">
         <v>196</v>
       </c>
-      <c r="C71" s="87"/>
-      <c r="D71" s="87"/>
-      <c r="E71" s="87"/>
+      <c r="C71" s="88"/>
+      <c r="D71" s="88"/>
+      <c r="E71" s="88"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="28" t="s">
@@ -3131,36 +3131,36 @@
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="B85" s="90" t="s">
+      <c r="B85" s="89" t="s">
         <v>192</v>
       </c>
-      <c r="C85" s="90"/>
-      <c r="D85" s="90"/>
-      <c r="E85" s="90"/>
+      <c r="C85" s="89"/>
+      <c r="D85" s="89"/>
+      <c r="E85" s="89"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="B86" s="89" t="s">
+      <c r="B86" s="87" t="s">
         <v>190</v>
       </c>
-      <c r="C86" s="89"/>
-      <c r="D86" s="89"/>
-      <c r="E86" s="89"/>
+      <c r="C86" s="87"/>
+      <c r="D86" s="87"/>
+      <c r="E86" s="87"/>
     </row>
     <row r="87" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B87" s="87" t="s">
+      <c r="B87" s="88" t="s">
         <v>189</v>
       </c>
-      <c r="C87" s="87"/>
-      <c r="D87" s="87"/>
-      <c r="E87" s="87"/>
+      <c r="C87" s="88"/>
+      <c r="D87" s="88"/>
+      <c r="E87" s="88"/>
     </row>
     <row r="88" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B88" s="87" t="s">
+      <c r="B88" s="88" t="s">
         <v>225</v>
       </c>
-      <c r="C88" s="87"/>
-      <c r="D88" s="87"/>
-      <c r="E88" s="87"/>
+      <c r="C88" s="88"/>
+      <c r="D88" s="88"/>
+      <c r="E88" s="88"/>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="24" t="s">
@@ -3193,12 +3193,12 @@
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="B97" s="88" t="s">
+      <c r="B97" s="90" t="s">
         <v>211</v>
       </c>
-      <c r="C97" s="88"/>
-      <c r="D97" s="88"/>
-      <c r="E97" s="88"/>
+      <c r="C97" s="90"/>
+      <c r="D97" s="90"/>
+      <c r="E97" s="90"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
@@ -3206,20 +3206,20 @@
       </c>
     </row>
     <row r="100" spans="1:5" ht="12.4">
-      <c r="B100" s="88" t="s">
+      <c r="B100" s="90" t="s">
         <v>212</v>
       </c>
-      <c r="C100" s="88"/>
-      <c r="D100" s="88"/>
-      <c r="E100" s="88"/>
+      <c r="C100" s="90"/>
+      <c r="D100" s="90"/>
+      <c r="E100" s="90"/>
     </row>
     <row r="101" spans="1:5" ht="58.5" customHeight="1">
-      <c r="B101" s="87" t="s">
+      <c r="B101" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="C101" s="87"/>
-      <c r="D101" s="87"/>
-      <c r="E101" s="87"/>
+      <c r="C101" s="88"/>
+      <c r="D101" s="88"/>
+      <c r="E101" s="88"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="28" t="s">
@@ -3275,12 +3275,12 @@
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B114" s="87" t="s">
+      <c r="B114" s="88" t="s">
         <v>217</v>
       </c>
-      <c r="C114" s="87"/>
-      <c r="D114" s="87"/>
-      <c r="E114" s="87"/>
+      <c r="C114" s="88"/>
+      <c r="D114" s="88"/>
+      <c r="E114" s="88"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="21" t="s">
@@ -3313,6 +3313,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
     <mergeCell ref="B86:E86"/>
     <mergeCell ref="B71:E71"/>
     <mergeCell ref="B85:E85"/>
@@ -3322,12 +3328,6 @@
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6816,15 +6816,15 @@
       <c r="B5" s="97" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="88"/>
-      <c r="D5" s="88"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="97" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="88"/>
-      <c r="D6" s="88"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE16CB6-A1EE-468B-B087-A67C98BA3B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF7E1463-6930-41A3-9209-A42D29C452A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="269">
   <si>
     <t>Name</t>
   </si>
@@ -1634,6 +1634,14 @@
   </si>
   <si>
     <t>Projected Holdings</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Price</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1992,7 +2000,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2193,6 +2201,12 @@
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -2639,12 +2653,12 @@
       <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B4" s="88" t="s">
+      <c r="B4" s="90" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="20" t="s">
@@ -2656,12 +2670,12 @@
       <c r="C6" s="62"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" s="88" t="s">
+      <c r="B7" s="90" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="88"/>
-      <c r="D7" s="88"/>
-      <c r="E7" s="88"/>
+      <c r="C7" s="90"/>
+      <c r="D7" s="90"/>
+      <c r="E7" s="90"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="23" t="s">
@@ -2750,12 +2764,12 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
-      <c r="B24" s="88" t="s">
+      <c r="B24" s="90" t="s">
         <v>220</v>
       </c>
-      <c r="C24" s="88"/>
-      <c r="D24" s="88"/>
-      <c r="E24" s="88"/>
+      <c r="C24" s="90"/>
+      <c r="D24" s="90"/>
+      <c r="E24" s="90"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
@@ -2849,20 +2863,20 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="B39" s="88" t="s">
+      <c r="B39" s="90" t="s">
         <v>156</v>
       </c>
-      <c r="C39" s="88"/>
-      <c r="D39" s="88"/>
-      <c r="E39" s="88"/>
+      <c r="C39" s="90"/>
+      <c r="D39" s="90"/>
+      <c r="E39" s="90"/>
     </row>
     <row r="40" spans="1:5" ht="46.6" customHeight="1">
-      <c r="B40" s="88" t="s">
+      <c r="B40" s="90" t="s">
         <v>236</v>
       </c>
-      <c r="C40" s="88"/>
-      <c r="D40" s="88"/>
-      <c r="E40" s="88"/>
+      <c r="C40" s="90"/>
+      <c r="D40" s="90"/>
+      <c r="E40" s="90"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="21" t="s">
@@ -2874,12 +2888,12 @@
       <c r="E42" s="21"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="B44" s="88" t="s">
+      <c r="B44" s="90" t="s">
         <v>208</v>
       </c>
-      <c r="C44" s="88"/>
-      <c r="D44" s="88"/>
-      <c r="E44" s="88"/>
+      <c r="C44" s="90"/>
+      <c r="D44" s="90"/>
+      <c r="E44" s="90"/>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="23" t="s">
@@ -3064,12 +3078,12 @@
       <c r="E69" s="21"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="B71" s="88" t="s">
+      <c r="B71" s="90" t="s">
         <v>196</v>
       </c>
-      <c r="C71" s="88"/>
-      <c r="D71" s="88"/>
-      <c r="E71" s="88"/>
+      <c r="C71" s="90"/>
+      <c r="D71" s="90"/>
+      <c r="E71" s="90"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="28" t="s">
@@ -3131,36 +3145,36 @@
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="B85" s="89" t="s">
+      <c r="B85" s="91" t="s">
         <v>192</v>
       </c>
-      <c r="C85" s="89"/>
-      <c r="D85" s="89"/>
-      <c r="E85" s="89"/>
+      <c r="C85" s="91"/>
+      <c r="D85" s="91"/>
+      <c r="E85" s="91"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="B86" s="87" t="s">
+      <c r="B86" s="89" t="s">
         <v>190</v>
       </c>
-      <c r="C86" s="87"/>
-      <c r="D86" s="87"/>
-      <c r="E86" s="87"/>
+      <c r="C86" s="89"/>
+      <c r="D86" s="89"/>
+      <c r="E86" s="89"/>
     </row>
     <row r="87" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B87" s="88" t="s">
+      <c r="B87" s="90" t="s">
         <v>189</v>
       </c>
-      <c r="C87" s="88"/>
-      <c r="D87" s="88"/>
-      <c r="E87" s="88"/>
+      <c r="C87" s="90"/>
+      <c r="D87" s="90"/>
+      <c r="E87" s="90"/>
     </row>
     <row r="88" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B88" s="88" t="s">
+      <c r="B88" s="90" t="s">
         <v>225</v>
       </c>
-      <c r="C88" s="88"/>
-      <c r="D88" s="88"/>
-      <c r="E88" s="88"/>
+      <c r="C88" s="90"/>
+      <c r="D88" s="90"/>
+      <c r="E88" s="90"/>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="24" t="s">
@@ -3193,12 +3207,12 @@
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="B97" s="90" t="s">
+      <c r="B97" s="92" t="s">
         <v>211</v>
       </c>
-      <c r="C97" s="90"/>
-      <c r="D97" s="90"/>
-      <c r="E97" s="90"/>
+      <c r="C97" s="92"/>
+      <c r="D97" s="92"/>
+      <c r="E97" s="92"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
@@ -3206,20 +3220,20 @@
       </c>
     </row>
     <row r="100" spans="1:5" ht="12.4">
-      <c r="B100" s="90" t="s">
+      <c r="B100" s="92" t="s">
         <v>212</v>
       </c>
-      <c r="C100" s="90"/>
-      <c r="D100" s="90"/>
-      <c r="E100" s="90"/>
+      <c r="C100" s="92"/>
+      <c r="D100" s="92"/>
+      <c r="E100" s="92"/>
     </row>
     <row r="101" spans="1:5" ht="58.5" customHeight="1">
-      <c r="B101" s="88" t="s">
+      <c r="B101" s="90" t="s">
         <v>219</v>
       </c>
-      <c r="C101" s="88"/>
-      <c r="D101" s="88"/>
-      <c r="E101" s="88"/>
+      <c r="C101" s="90"/>
+      <c r="D101" s="90"/>
+      <c r="E101" s="90"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="28" t="s">
@@ -3267,7 +3281,7 @@
         <v>176</v>
       </c>
       <c r="C112" s="44">
-        <v>0.13078963304662303</v>
+        <v>0.13023489201472013</v>
       </c>
       <c r="D112" s="62" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
@@ -3275,12 +3289,12 @@
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B114" s="88" t="s">
+      <c r="B114" s="90" t="s">
         <v>217</v>
       </c>
-      <c r="C114" s="88"/>
-      <c r="D114" s="88"/>
-      <c r="E114" s="88"/>
+      <c r="C114" s="90"/>
+      <c r="D114" s="90"/>
+      <c r="E114" s="90"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="21" t="s">
@@ -3340,7 +3354,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q358"/>
+  <dimension ref="A1:R358"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.46484375" style="1" customWidth="1"/>
@@ -3354,41 +3368,44 @@
     <col min="15" max="15" width="22.73046875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.796875" style="3" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="8.796875" style="11"/>
-    <col min="18" max="18" width="16.3984375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="8.796875" style="88"/>
     <col min="19" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" s="5"/>
       <c r="B1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="94" t="s">
+      <c r="D1" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="95" t="s">
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="97" t="s">
         <v>101</v>
       </c>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="91" t="s">
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="93" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="91"/>
-      <c r="L1" s="92" t="s">
+      <c r="K1" s="93"/>
+      <c r="L1" s="94" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="92"/>
-      <c r="N1" s="93" t="s">
+      <c r="M1" s="94"/>
+      <c r="N1" s="95" t="s">
         <v>53</v>
       </c>
-      <c r="O1" s="93"/>
-      <c r="P1" s="93"/>
-      <c r="Q1" s="93"/>
-    </row>
-    <row r="2" spans="1:17" ht="26" customHeight="1">
+      <c r="O1" s="95"/>
+      <c r="P1" s="95"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="87" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="26" customHeight="1">
       <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
@@ -3437,8 +3454,11 @@
       <c r="Q2" s="10" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" s="8" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="B3" s="11" t="s">
         <v>260</v>
       </c>
@@ -3452,30 +3472,30 @@
         <v>160</v>
       </c>
       <c r="F3" s="15">
-        <v>0.22170440631904209</v>
+        <v>0.22170440631904187</v>
       </c>
       <c r="G3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$10</f>
-        <v>0.10430440631904209</v>
+        <v>0.10430440631904186</v>
       </c>
       <c r="H3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$11</f>
-        <v>0.18720440631904209</v>
+        <v>0.18720440631904187</v>
       </c>
       <c r="I3" s="15">
-        <v>0.26604528758285051</v>
+        <v>0.26604528758285023</v>
       </c>
       <c r="J3" s="2">
-        <v>13.677042438413379</v>
+        <v>13.677042438413375</v>
       </c>
       <c r="K3" s="2">
-        <v>24.622857747833486</v>
+        <v>24.622857747833478</v>
       </c>
       <c r="L3" s="4">
-        <v>6.4508135967563232E-2</v>
+        <v>6.4508135967563204E-2</v>
       </c>
       <c r="M3" s="4">
-        <v>3.749843268269646E-2</v>
+        <v>3.7498432682696467E-2</v>
       </c>
       <c r="N3" s="13" t="s">
         <v>248</v>
@@ -3489,8 +3509,11 @@
       <c r="Q3" s="11" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" s="88">
+        <v>23.77802559054318</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="B4" s="11" t="s">
         <v>237</v>
       </c>
@@ -3504,27 +3527,27 @@
         <v>160</v>
       </c>
       <c r="F4" s="15">
-        <v>0.1784289263913903</v>
+        <v>0.17842892639139052</v>
       </c>
       <c r="G4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$10</f>
-        <v>6.1028926391390292E-2</v>
+        <v>6.1028926391390514E-2</v>
       </c>
       <c r="H4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$11</f>
-        <v>0.14392892639139029</v>
+        <v>0.14392892639139052</v>
       </c>
       <c r="I4" s="15">
-        <v>0.21411471166966836</v>
+        <v>0.21411471166966861</v>
       </c>
       <c r="J4" s="2">
-        <v>4.91520725037517</v>
+        <v>4.9152072503751691</v>
       </c>
       <c r="K4" s="2">
-        <v>7.9151197774737954</v>
+        <v>7.9151197774737936</v>
       </c>
       <c r="L4" s="4">
-        <v>0.13256816715305939</v>
+        <v>0.13256816715305936</v>
       </c>
       <c r="M4" s="4">
         <v>7.6196467311032592E-2</v>
@@ -3541,48 +3564,51 @@
       <c r="Q4" s="11" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="R4" s="88">
+        <v>8.3886784986115117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="B5" s="11" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D5" s="2">
-        <v>54.25</v>
+        <v>20.079999999999998</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>160</v>
+        <v>255</v>
       </c>
       <c r="F5" s="15">
-        <v>0.16523666770490664</v>
+        <v>0.16060765378265396</v>
       </c>
       <c r="G5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$10</f>
-        <v>4.7836667704906632E-2</v>
+        <v>4.3207653782653954E-2</v>
       </c>
       <c r="H5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$11</f>
-        <v>0.13073666770490663</v>
+        <v>0.12610765378265396</v>
       </c>
       <c r="I5" s="15">
         <v>0.11984000074748113</v>
       </c>
       <c r="J5" s="2">
-        <v>44.250954726078248</v>
+        <v>16.165402289394244</v>
       </c>
       <c r="K5" s="2">
-        <v>78.564693346218675</v>
+        <v>29.309951346473134</v>
       </c>
       <c r="L5" s="4">
-        <v>4.1491316575080379E-2</v>
+        <v>0.22703991769612522</v>
       </c>
       <c r="M5" s="4">
-        <v>3.8016844194438813E-2</v>
+        <v>2.956175298804781E-2</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="O5" s="11" t="s">
         <v>162</v>
@@ -3591,209 +3617,221 @@
         <v>45900</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
+        <v>163</v>
+      </c>
+      <c r="R5" s="88">
+        <v>28.138888137115678</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="B6" s="11" t="s">
-        <v>253</v>
+        <v>158</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>254</v>
+        <v>159</v>
       </c>
       <c r="D6" s="2">
-        <v>20.079999999999998</v>
+        <v>16.440000000000001</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F6" s="15">
-        <v>0.16060765378265396</v>
+        <v>0.15374754303551685</v>
       </c>
       <c r="G6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$10</f>
-        <v>4.3207653782653954E-2</v>
+        <v>3.6347543035516849E-2</v>
       </c>
       <c r="H6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$11</f>
-        <v>0.12610765378265396</v>
+        <v>0.11924754303551685</v>
       </c>
       <c r="I6" s="15">
         <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>16.165402289394244</v>
+        <v>13.155317996540354</v>
       </c>
       <c r="K6" s="2">
-        <v>29.309951346473134</v>
+        <v>20.508980461992877</v>
       </c>
       <c r="L6" s="4">
-        <v>0.22703991769612522</v>
+        <v>0.10510863864778767</v>
       </c>
       <c r="M6" s="4">
-        <v>2.956175298804781E-2</v>
+        <v>8.2725060827250604E-2</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>256</v>
+        <v>161</v>
       </c>
       <c r="O6" s="11" t="s">
         <v>162</v>
       </c>
       <c r="P6" s="14">
-        <v>45900</v>
+        <v>45808</v>
       </c>
       <c r="Q6" s="11" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="R6" s="88">
+        <v>22.338628219506891</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="B7" s="11" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D7" s="2">
-        <v>16.440000000000001</v>
+        <v>7.85</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F7" s="15">
-        <v>0.15374754303551685</v>
+        <v>0.12328963999428066</v>
       </c>
       <c r="G7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$10</f>
-        <v>3.6347543035516849E-2</v>
+        <v>5.8896399942806599E-3</v>
       </c>
       <c r="H7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$11</f>
-        <v>0.11924754303551685</v>
+        <v>8.8789639994280661E-2</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>13.155317996540354</v>
+        <v>5.8235187175367322</v>
       </c>
       <c r="K7" s="2">
-        <v>20.508980461992877</v>
+        <v>9.1628099951889297</v>
       </c>
       <c r="L7" s="4">
-        <v>0.10510863864778767</v>
+        <v>3.9350111080543315E-2</v>
       </c>
       <c r="M7" s="4">
-        <v>8.2725060827250604E-2</v>
+        <v>7.3885350318471335E-2</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="P7" s="14">
-        <v>45808</v>
+        <v>45900</v>
       </c>
       <c r="Q7" s="11" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="R7" s="88">
+        <v>9.9028212013122712</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="B8" s="11" t="s">
-        <v>164</v>
+        <v>246</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>165</v>
+        <v>247</v>
       </c>
       <c r="D8" s="2">
-        <v>7.85</v>
+        <v>14.26</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F8" s="15">
-        <v>0.12105292184429062</v>
+        <v>0.10954171828338932</v>
       </c>
       <c r="G8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$10</f>
-        <v>3.6529218442906131E-3</v>
+        <v>-7.8582817166106822E-3</v>
       </c>
       <c r="H8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$11</f>
-        <v>8.6552921844290615E-2</v>
+        <v>7.5041718283389319E-2</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
       </c>
       <c r="J8" s="2">
-        <v>5.7917118707600084</v>
+        <v>10.174176386967826</v>
       </c>
       <c r="K8" s="2">
-        <v>9.1006872475781417</v>
+        <v>16.694869127046534</v>
       </c>
       <c r="L8" s="4">
-        <v>3.9350111080543315E-2</v>
+        <v>0.10764138310388582</v>
       </c>
       <c r="M8" s="4">
-        <v>7.3885350318471335E-2</v>
+        <v>5.8429064516129031E-2</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>166</v>
+        <v>248</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>167</v>
+        <v>250</v>
       </c>
       <c r="P8" s="14">
         <v>45900</v>
       </c>
       <c r="Q8" s="11" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17">
+        <v>249</v>
+      </c>
+      <c r="R8" s="88">
+        <v>17.416210381668485</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="B9" s="11" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D9" s="2">
-        <v>14.26</v>
+        <v>54.25</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F9" s="15">
-        <v>0.10954171828338932</v>
+        <v>0.10804060157997641</v>
       </c>
       <c r="G9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$10</f>
-        <v>-7.8582817166106822E-3</v>
+        <v>-9.3593984200235902E-3</v>
       </c>
       <c r="H9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$11</f>
-        <v>7.5041718283389319E-2</v>
+        <v>7.3540601579976411E-2</v>
       </c>
       <c r="I9" s="15">
         <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>10.174176386967826</v>
+        <v>38.289885084736952</v>
       </c>
       <c r="K9" s="2">
-        <v>16.694869127046534</v>
+        <v>66.921979202973944</v>
       </c>
       <c r="L9" s="4">
-        <v>0.10764138310388582</v>
+        <v>4.1491316575080373E-2</v>
       </c>
       <c r="M9" s="4">
-        <v>5.8429064516129031E-2</v>
+        <v>3.801684419443882E-2</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>250</v>
+        <v>162</v>
       </c>
       <c r="P9" s="14">
         <v>45900</v>
@@ -3801,8 +3839,11 @@
       <c r="Q9" s="11" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="10" spans="1:17">
+      <c r="R9" s="88">
+        <v>66.231011456376947</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="B10" s="11" t="s">
         <v>168</v>
       </c>
@@ -3816,30 +3857,30 @@
         <v>160</v>
       </c>
       <c r="F10" s="15">
-        <v>0.10185445179346719</v>
+        <v>0.10185445179346697</v>
       </c>
       <c r="G10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$10</f>
-        <v>-1.5545548206532811E-2</v>
+        <v>-1.5545548206533033E-2</v>
       </c>
       <c r="H10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$11</f>
-        <v>6.735445179346719E-2</v>
+        <v>6.7354451793466968E-2</v>
       </c>
       <c r="I10" s="15">
         <v>0</v>
       </c>
       <c r="J10" s="2">
-        <v>1.6044036483689859</v>
+        <v>1.6044036483689856</v>
       </c>
       <c r="K10" s="2">
-        <v>2.6975644131821959</v>
+        <v>2.697564413182195</v>
       </c>
       <c r="L10" s="4">
-        <v>3.5732763614444767E-2</v>
+        <v>3.573276361444476E-2</v>
       </c>
       <c r="M10" s="4">
-        <v>4.972618247053226E-2</v>
+        <v>4.9726182470532274E-2</v>
       </c>
       <c r="N10" s="16" t="s">
         <v>170</v>
@@ -3853,8 +3894,11 @@
       <c r="Q10" s="11" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="R10" s="88">
+        <v>2.7573082335059835</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="B11" s="11" t="s">
         <v>257</v>
       </c>
@@ -3905,8 +3949,11 @@
       <c r="Q11" s="11" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="12" spans="1:17">
+      <c r="R11" s="88">
+        <v>33.810824894744755</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="B12" s="11" t="s">
         <v>251</v>
       </c>
@@ -3957,8 +4004,11 @@
       <c r="Q12" s="11" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="R12" s="88">
+        <v>61.41108960250569</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
       <c r="E13" s="12"/>
@@ -3968,7 +4018,7 @@
       <c r="O13" s="11"/>
       <c r="P13" s="14"/>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:18">
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
       <c r="E14" s="12"/>
@@ -3978,7 +4028,7 @@
       <c r="O14" s="11"/>
       <c r="P14" s="14"/>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:18">
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
       <c r="E15" s="12"/>
@@ -3988,7 +4038,7 @@
       <c r="O15" s="11"/>
       <c r="P15" s="14"/>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:18">
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
       <c r="E16" s="12"/>
@@ -6806,25 +6856,25 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="B3" s="96" t="s">
+      <c r="B3" s="98" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="96"/>
-      <c r="D3" s="96"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="B5" s="97" t="s">
+      <c r="B5" s="99" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="90"/>
-      <c r="D5" s="90"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="B6" s="97" t="s">
+      <c r="B6" s="99" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="90"/>
-      <c r="D6" s="90"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="92"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">
@@ -6838,18 +6888,18 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="96" t="s">
+      <c r="B11" s="98" t="s">
         <v>109</v>
       </c>
-      <c r="C11" s="96"/>
-      <c r="D11" s="96"/>
+      <c r="C11" s="98"/>
+      <c r="D11" s="98"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="B12" s="96" t="s">
+      <c r="B12" s="98" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="96"/>
-      <c r="D12" s="96"/>
+      <c r="C12" s="98"/>
+      <c r="D12" s="98"/>
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="23" t="s">
@@ -6943,18 +6993,18 @@
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="B28" s="96" t="s">
+      <c r="B28" s="98" t="s">
         <v>122</v>
       </c>
-      <c r="C28" s="96"/>
-      <c r="D28" s="96"/>
+      <c r="C28" s="98"/>
+      <c r="D28" s="98"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="B29" s="96" t="s">
+      <c r="B29" s="98" t="s">
         <v>123</v>
       </c>
-      <c r="C29" s="96"/>
-      <c r="D29" s="96"/>
+      <c r="C29" s="98"/>
+      <c r="D29" s="98"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="5"/>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF7E1463-6930-41A3-9209-A42D29C452A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8CC7BF-2AC5-41C3-9D59-DD3D42228909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -20,74 +20,20 @@
     <sheet name="Holdings" sheetId="7" r:id="rId5"/>
     <sheet name="Comp_Group" sheetId="6" r:id="rId6"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Opportunities!$B$2:$Q$2</definedName>
-    <definedName name="AddInfoCommentBox1">#REF!</definedName>
-    <definedName name="AddInfoName1">#REF!</definedName>
-    <definedName name="AddInfoTextBox1">#REF!</definedName>
-    <definedName name="AURABOOKMARK4">#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Opportunities!$B$2:$V$2</definedName>
     <definedName name="AuraStyleDefaultsReset" hidden="1">#N/A</definedName>
-    <definedName name="AvgRate202109">#REF!</definedName>
-    <definedName name="AvgRate2022">#REF!</definedName>
-    <definedName name="AvgRate202409">#REF!</definedName>
     <definedName name="benchmark">Portfolio_Mgmt!$C$10</definedName>
     <definedName name="Cash_Yield">Portfolio_Mgmt!$C$11</definedName>
-    <definedName name="CDC">#REF!</definedName>
-    <definedName name="Chinese_Client_Name">#REF!</definedName>
-    <definedName name="Client_Name">#REF!</definedName>
-    <definedName name="ClosingRate202109">#REF!</definedName>
-    <definedName name="ClosingRate2022">#REF!</definedName>
-    <definedName name="ClosingRate202403">#REF!</definedName>
-    <definedName name="ClosingRate202409">#REF!</definedName>
-    <definedName name="CommentBox1a">#REF!</definedName>
-    <definedName name="Currency">#REF!</definedName>
-    <definedName name="CY">#REF!</definedName>
-    <definedName name="exchange_rate">[1]白银数据!$F$2</definedName>
-    <definedName name="GMV">#REF!</definedName>
-    <definedName name="Long_term_loans">#REF!</definedName>
-    <definedName name="Name10c">#REF!</definedName>
-    <definedName name="Name1a">#REF!</definedName>
-    <definedName name="Name1b">#REF!</definedName>
-    <definedName name="Name1c">#REF!</definedName>
-    <definedName name="Name1d">#REF!</definedName>
-    <definedName name="Name1e">#REF!</definedName>
-    <definedName name="Name1f">#REF!</definedName>
-    <definedName name="Name2a">#REF!</definedName>
-    <definedName name="Name2b">#REF!</definedName>
-    <definedName name="Name3a">#REF!</definedName>
-    <definedName name="Name3b">#REF!</definedName>
-    <definedName name="Name3c">#REF!</definedName>
-    <definedName name="Name4a">#REF!</definedName>
-    <definedName name="Name4b">#REF!</definedName>
-    <definedName name="NSProjectionMethodIndex">#REF!</definedName>
-    <definedName name="NSRequiredLevelOfEvidenceItems">#REF!</definedName>
-    <definedName name="NSTargetedTestingItems">#REF!</definedName>
-    <definedName name="PDC">#REF!</definedName>
-    <definedName name="Period_Ended">#REF!</definedName>
-    <definedName name="PIE">#REF!</definedName>
-    <definedName name="PY">#REF!</definedName>
-    <definedName name="Scenario_Copy">#REF!</definedName>
-    <definedName name="Scenario_Count">#REF!</definedName>
-    <definedName name="Scenario_Paste">#REF!</definedName>
-    <definedName name="Scenario_Switch">#REF!</definedName>
-    <definedName name="TextBox1a">#REF!</definedName>
-    <definedName name="TTDesiredLevelOfEvidenceItems">#REF!</definedName>
-    <definedName name="TwoStepMisstatementIdentified">#REF!</definedName>
-    <definedName name="TwoStepTolerableEstMisstmtCalc">#REF!</definedName>
     <definedName name="WW3f877d8e32714ec8a8180854ed7f8276_634328481945590045" hidden="1">#REF!</definedName>
     <definedName name="WW3f877d8e32714ec8a8180854ed7f8276_634328482352282765" hidden="1">#REF!</definedName>
-    <definedName name="Year">#REF!</definedName>
-    <definedName name="黄色">#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="270">
   <si>
     <t>Name</t>
   </si>
@@ -1508,10 +1454,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Total</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Market Value (HKD)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1565,10 +1507,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>1910.HK</t>
   </si>
   <si>
@@ -1617,31 +1555,45 @@
     <t>李宁</t>
   </si>
   <si>
-    <t>2331.HK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Planning</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Beg. Cash Balance</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>End. Cash Balance</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Projected Holdings</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Sell Price</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Sell</t>
+    <t>Total Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Actual %</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Debt/
+Equity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Liabilities/
+Equity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Realizable Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Debt/EBIT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Balance Sheet Strength</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1649,12 +1601,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="177" formatCode="[$-13C09]d\ mmm\ yyyy;@"/>
     <numFmt numFmtId="178" formatCode="0&quot; yrs&quot;"/>
     <numFmt numFmtId="179" formatCode="#,##0.00_);\(#,##0.00\)"/>
     <numFmt numFmtId="180" formatCode="#,##0_);\(#,##0\)"/>
+    <numFmt numFmtId="181" formatCode="0.0\x"/>
   </numFmts>
   <fonts count="34">
     <font>
@@ -2000,7 +1953,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2202,37 +2155,49 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="28" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="4" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2266,66 +2231,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="财务预测&gt;"/>
-      <sheetName val="数商时代"/>
-      <sheetName val="PSP计划"/>
-      <sheetName val="PSP相关费用"/>
-      <sheetName val="财务分析&gt;"/>
-      <sheetName val="审计数据"/>
-      <sheetName val="白银数据"/>
-      <sheetName val="PSP分析"/>
-      <sheetName val="原始数据&gt;"/>
-      <sheetName val="CK12_PL 20240930"/>
-      <sheetName val="白银智勤 TB 20240930"/>
-      <sheetName val="白银智勤审计数据"/>
-      <sheetName val="智勤商城数据"/>
-      <sheetName val="智勤优品数据"/>
-      <sheetName val="2024年3月31日年度(12個月)"/>
-      <sheetName val="2023年3月31日年度(12個月)"/>
-      <sheetName val="2024年4月至12月(9個月)"/>
-      <sheetName val="利润表2024年9期"/>
-      <sheetName val="链嬴"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6">
-        <row r="2">
-          <cell r="F2">
-            <v>0.92</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2653,12 +2558,12 @@
       <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B4" s="90" t="s">
+      <c r="B4" s="94" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="20" t="s">
@@ -2670,12 +2575,12 @@
       <c r="C6" s="62"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" s="90" t="s">
+      <c r="B7" s="94" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="90"/>
-      <c r="D7" s="90"/>
-      <c r="E7" s="90"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="94"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="23" t="s">
@@ -2764,12 +2669,12 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
-      <c r="B24" s="90" t="s">
+      <c r="B24" s="94" t="s">
         <v>220</v>
       </c>
-      <c r="C24" s="90"/>
-      <c r="D24" s="90"/>
-      <c r="E24" s="90"/>
+      <c r="C24" s="94"/>
+      <c r="D24" s="94"/>
+      <c r="E24" s="94"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
@@ -2863,20 +2768,20 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="B39" s="90" t="s">
+      <c r="B39" s="94" t="s">
         <v>156</v>
       </c>
-      <c r="C39" s="90"/>
-      <c r="D39" s="90"/>
-      <c r="E39" s="90"/>
+      <c r="C39" s="94"/>
+      <c r="D39" s="94"/>
+      <c r="E39" s="94"/>
     </row>
     <row r="40" spans="1:5" ht="46.6" customHeight="1">
-      <c r="B40" s="90" t="s">
-        <v>236</v>
-      </c>
-      <c r="C40" s="90"/>
-      <c r="D40" s="90"/>
-      <c r="E40" s="90"/>
+      <c r="B40" s="94" t="s">
+        <v>235</v>
+      </c>
+      <c r="C40" s="94"/>
+      <c r="D40" s="94"/>
+      <c r="E40" s="94"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="21" t="s">
@@ -2888,12 +2793,12 @@
       <c r="E42" s="21"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="B44" s="90" t="s">
+      <c r="B44" s="94" t="s">
         <v>208</v>
       </c>
-      <c r="C44" s="90"/>
-      <c r="D44" s="90"/>
-      <c r="E44" s="90"/>
+      <c r="C44" s="94"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="23" t="s">
@@ -3078,12 +2983,12 @@
       <c r="E69" s="21"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="B71" s="90" t="s">
+      <c r="B71" s="94" t="s">
         <v>196</v>
       </c>
-      <c r="C71" s="90"/>
-      <c r="D71" s="90"/>
-      <c r="E71" s="90"/>
+      <c r="C71" s="94"/>
+      <c r="D71" s="94"/>
+      <c r="E71" s="94"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="28" t="s">
@@ -3145,36 +3050,36 @@
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="B85" s="91" t="s">
+      <c r="B85" s="97" t="s">
         <v>192</v>
       </c>
-      <c r="C85" s="91"/>
-      <c r="D85" s="91"/>
-      <c r="E85" s="91"/>
+      <c r="C85" s="97"/>
+      <c r="D85" s="97"/>
+      <c r="E85" s="97"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="B86" s="89" t="s">
+      <c r="B86" s="96" t="s">
         <v>190</v>
       </c>
-      <c r="C86" s="89"/>
-      <c r="D86" s="89"/>
-      <c r="E86" s="89"/>
+      <c r="C86" s="96"/>
+      <c r="D86" s="96"/>
+      <c r="E86" s="96"/>
     </row>
     <row r="87" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B87" s="90" t="s">
+      <c r="B87" s="94" t="s">
         <v>189</v>
       </c>
-      <c r="C87" s="90"/>
-      <c r="D87" s="90"/>
-      <c r="E87" s="90"/>
+      <c r="C87" s="94"/>
+      <c r="D87" s="94"/>
+      <c r="E87" s="94"/>
     </row>
     <row r="88" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B88" s="90" t="s">
+      <c r="B88" s="94" t="s">
         <v>225</v>
       </c>
-      <c r="C88" s="90"/>
-      <c r="D88" s="90"/>
-      <c r="E88" s="90"/>
+      <c r="C88" s="94"/>
+      <c r="D88" s="94"/>
+      <c r="E88" s="94"/>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="24" t="s">
@@ -3207,12 +3112,12 @@
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="B97" s="92" t="s">
+      <c r="B97" s="95" t="s">
         <v>211</v>
       </c>
-      <c r="C97" s="92"/>
-      <c r="D97" s="92"/>
-      <c r="E97" s="92"/>
+      <c r="C97" s="95"/>
+      <c r="D97" s="95"/>
+      <c r="E97" s="95"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
@@ -3220,20 +3125,20 @@
       </c>
     </row>
     <row r="100" spans="1:5" ht="12.4">
-      <c r="B100" s="92" t="s">
+      <c r="B100" s="95" t="s">
         <v>212</v>
       </c>
-      <c r="C100" s="92"/>
-      <c r="D100" s="92"/>
-      <c r="E100" s="92"/>
+      <c r="C100" s="95"/>
+      <c r="D100" s="95"/>
+      <c r="E100" s="95"/>
     </row>
     <row r="101" spans="1:5" ht="58.5" customHeight="1">
-      <c r="B101" s="90" t="s">
+      <c r="B101" s="94" t="s">
         <v>219</v>
       </c>
-      <c r="C101" s="90"/>
-      <c r="D101" s="90"/>
-      <c r="E101" s="90"/>
+      <c r="C101" s="94"/>
+      <c r="D101" s="94"/>
+      <c r="E101" s="94"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="28" t="s">
@@ -3289,12 +3194,12 @@
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B114" s="90" t="s">
+      <c r="B114" s="94" t="s">
         <v>217</v>
       </c>
-      <c r="C114" s="90"/>
-      <c r="D114" s="90"/>
-      <c r="E114" s="90"/>
+      <c r="C114" s="94"/>
+      <c r="D114" s="94"/>
+      <c r="E114" s="94"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="21" t="s">
@@ -3327,12 +3232,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
     <mergeCell ref="B86:E86"/>
     <mergeCell ref="B71:E71"/>
     <mergeCell ref="B85:E85"/>
@@ -3342,6 +3241,12 @@
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3354,7 +3259,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R358"/>
+  <dimension ref="A1:V358"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.46484375" style="1" customWidth="1"/>
@@ -3363,49 +3268,57 @@
     <col min="4" max="4" width="8.6640625" style="2" customWidth="1"/>
     <col min="5" max="5" width="10.33203125" style="1" customWidth="1"/>
     <col min="6" max="9" width="10.33203125" style="15" customWidth="1"/>
-    <col min="10" max="11" width="8.6640625" style="2" customWidth="1"/>
-    <col min="12" max="14" width="8.6640625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="22.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.796875" style="11"/>
-    <col min="18" max="18" width="8.796875" style="88"/>
-    <col min="19" max="16384" width="8.796875" style="1"/>
+    <col min="10" max="12" width="8.6640625" style="2" customWidth="1"/>
+    <col min="13" max="14" width="8.6640625" style="1" customWidth="1"/>
+    <col min="15" max="16" width="8.6640625" style="15" customWidth="1"/>
+    <col min="17" max="17" width="8.6640625" style="93" customWidth="1"/>
+    <col min="18" max="18" width="8.6640625" style="87" customWidth="1"/>
+    <col min="19" max="19" width="8.6640625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="22.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.796875" style="11"/>
+    <col min="23" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:22">
       <c r="A1" s="5"/>
       <c r="B1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="96" t="s">
+      <c r="C1" s="88"/>
+      <c r="D1" s="100" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="97" t="s">
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="101" t="s">
         <v>101</v>
       </c>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="93" t="s">
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="93"/>
-      <c r="L1" s="94" t="s">
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="94"/>
-      <c r="N1" s="95" t="s">
+      <c r="N1" s="98"/>
+      <c r="O1" s="103" t="s">
+        <v>269</v>
+      </c>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="99" t="s">
         <v>53</v>
       </c>
-      <c r="O1" s="95"/>
-      <c r="P1" s="95"/>
-      <c r="Q1" s="95"/>
-      <c r="R1" s="87" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" ht="26" customHeight="1">
+      <c r="T1" s="99"/>
+      <c r="U1" s="99"/>
+      <c r="V1" s="99"/>
+    </row>
+    <row r="2" spans="1:22" ht="26" customHeight="1">
       <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
@@ -3436,34 +3349,46 @@
       <c r="K2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="M2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="N2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="O2" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="S2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="T2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="U2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="Q2" s="10" t="s">
+      <c r="V2" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="R2" s="8" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
+    </row>
+    <row r="3" spans="1:22">
       <c r="B3" s="11" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D3" s="2">
         <v>14.62</v>
@@ -3491,34 +3416,46 @@
       <c r="K3" s="2">
         <v>24.622857747833478</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="87">
+        <v>22.308475032950721</v>
+      </c>
+      <c r="M3" s="4">
         <v>6.4508135967563204E-2</v>
       </c>
-      <c r="M3" s="4">
+      <c r="N3" s="4">
         <v>3.7498432682696467E-2</v>
       </c>
-      <c r="N3" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="O3" s="11" t="s">
+      <c r="O3" s="15">
+        <v>0.36794481423679237</v>
+      </c>
+      <c r="P3" s="15">
+        <v>7.4171010848313429E-2</v>
+      </c>
+      <c r="Q3" s="93">
+        <v>0.60402076709908736</v>
+      </c>
+      <c r="R3" s="87">
+        <v>4.4970487317420522</v>
+      </c>
+      <c r="S3" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="T3" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="P3" s="14">
+      <c r="U3" s="14">
         <v>45900</v>
       </c>
-      <c r="Q3" s="11" t="s">
+      <c r="V3" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="R3" s="88">
-        <v>23.77802559054318</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
+    </row>
+    <row r="4" spans="1:22">
       <c r="B4" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>237</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>238</v>
       </c>
       <c r="D4" s="2">
         <v>5.8</v>
@@ -3546,40 +3483,52 @@
       <c r="K4" s="2">
         <v>7.9151197774737936</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="87">
+        <v>7.8850261201801173</v>
+      </c>
+      <c r="M4" s="4">
         <v>0.13256816715305936</v>
       </c>
-      <c r="M4" s="4">
+      <c r="N4" s="4">
         <v>7.6196467311032592E-2</v>
       </c>
-      <c r="N4" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="15">
+        <v>0.61007460831657279</v>
+      </c>
+      <c r="P4" s="15">
+        <v>0.16360901428944893</v>
+      </c>
+      <c r="Q4" s="93">
+        <v>1.1309485990394448</v>
+      </c>
+      <c r="R4" s="87">
+        <v>-3.7849818877411923</v>
+      </c>
+      <c r="S4" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="P4" s="14">
+      <c r="T4" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="U4" s="14">
         <v>45900</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="V4" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="R4" s="88">
-        <v>8.3886784986115117</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
+    </row>
+    <row r="5" spans="1:22">
       <c r="B5" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D5" s="2">
         <v>20.079999999999998</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F5" s="15">
         <v>0.16060765378265396</v>
@@ -3601,29 +3550,41 @@
       <c r="K5" s="2">
         <v>29.309951346473134</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="87">
+        <v>26.396539978799055</v>
+      </c>
+      <c r="M5" s="4">
         <v>0.22703991769612522</v>
       </c>
-      <c r="M5" s="4">
+      <c r="N5" s="4">
         <v>2.956175298804781E-2</v>
       </c>
-      <c r="N5" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="O5" s="11" t="s">
+      <c r="O5" s="15">
+        <v>1.4851905363915479</v>
+      </c>
+      <c r="P5" s="15">
+        <v>0.95241105291674188</v>
+      </c>
+      <c r="Q5" s="93">
+        <v>4.0148803043206254</v>
+      </c>
+      <c r="R5" s="87">
+        <v>-38.360607814419353</v>
+      </c>
+      <c r="S5" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="T5" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="P5" s="14">
+      <c r="U5" s="14">
         <v>45900</v>
       </c>
-      <c r="Q5" s="11" t="s">
+      <c r="V5" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="R5" s="88">
-        <v>28.138888137115678</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
+    </row>
+    <row r="6" spans="1:22">
       <c r="B6" s="11" t="s">
         <v>158</v>
       </c>
@@ -3656,29 +3617,41 @@
       <c r="K6" s="2">
         <v>20.508980461992877</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="87">
+        <v>21.008327387940341</v>
+      </c>
+      <c r="M6" s="4">
         <v>0.10510863864778767</v>
       </c>
-      <c r="M6" s="4">
+      <c r="N6" s="4">
         <v>8.2725060827250604E-2</v>
       </c>
-      <c r="N6" s="13" t="s">
+      <c r="O6" s="15">
+        <v>0.31018327415220487</v>
+      </c>
+      <c r="P6" s="15">
+        <v>0.15818859882129041</v>
+      </c>
+      <c r="Q6" s="93">
+        <v>1.4550387206421544</v>
+      </c>
+      <c r="R6" s="87">
+        <v>5.8696003638854428</v>
+      </c>
+      <c r="S6" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="T6" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="P6" s="14">
+      <c r="U6" s="14">
         <v>45808</v>
       </c>
-      <c r="Q6" s="11" t="s">
+      <c r="V6" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="R6" s="88">
-        <v>22.338628219506891</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
+    </row>
+    <row r="7" spans="1:22">
       <c r="B7" s="11" t="s">
         <v>164</v>
       </c>
@@ -3711,34 +3684,46 @@
       <c r="K7" s="2">
         <v>9.1628099951889297</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7" s="87">
+        <v>9.3117298015925627</v>
+      </c>
+      <c r="M7" s="4">
         <v>3.9350111080543315E-2</v>
       </c>
-      <c r="M7" s="4">
+      <c r="N7" s="4">
         <v>7.3885350318471335E-2</v>
       </c>
-      <c r="N7" s="13" t="s">
+      <c r="O7" s="15">
+        <v>8.3114411724224596E-2</v>
+      </c>
+      <c r="P7" s="15">
+        <v>1.8509098960546238E-2</v>
+      </c>
+      <c r="Q7" s="93">
+        <v>1.1933697905849452</v>
+      </c>
+      <c r="R7" s="87">
+        <v>11.511512740854835</v>
+      </c>
+      <c r="S7" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="T7" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="P7" s="14">
+      <c r="U7" s="14">
         <v>45900</v>
       </c>
-      <c r="Q7" s="11" t="s">
+      <c r="V7" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="R7" s="88">
-        <v>9.9028212013122712</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
+    </row>
+    <row r="8" spans="1:22">
       <c r="B8" s="11" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D8" s="2">
         <v>14.26</v>
@@ -3766,34 +3751,46 @@
       <c r="K8" s="2">
         <v>16.694869127046534</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8" s="87">
+        <v>16.365529532356156</v>
+      </c>
+      <c r="M8" s="4">
         <v>0.10764138310388582</v>
       </c>
-      <c r="M8" s="4">
+      <c r="N8" s="4">
         <v>5.8429064516129031E-2</v>
       </c>
-      <c r="N8" s="13" t="s">
+      <c r="O8" s="15">
+        <v>2.2875080906148866</v>
+      </c>
+      <c r="P8" s="15">
+        <v>1.5035598705501618</v>
+      </c>
+      <c r="Q8" s="93">
+        <v>4.1998196571663646</v>
+      </c>
+      <c r="R8" s="87">
+        <v>-12.13407231254085</v>
+      </c>
+      <c r="S8" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="T8" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="O8" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="P8" s="14">
+      <c r="U8" s="14">
         <v>45900</v>
       </c>
-      <c r="Q8" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="R8" s="88">
-        <v>17.416210381668485</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
+      <c r="V8" s="11" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
       <c r="B9" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>241</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>242</v>
       </c>
       <c r="D9" s="2">
         <v>54.25</v>
@@ -3821,29 +3818,41 @@
       <c r="K9" s="2">
         <v>66.921979202973944</v>
       </c>
-      <c r="L9" s="4">
+      <c r="L9" s="87">
+        <v>62.169609540564053</v>
+      </c>
+      <c r="M9" s="4">
         <v>4.1491316575080373E-2</v>
       </c>
-      <c r="M9" s="4">
+      <c r="N9" s="4">
         <v>3.801684419443882E-2</v>
       </c>
-      <c r="N9" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="O9" s="11" t="s">
+      <c r="O9" s="15">
+        <v>0.72207550313588764</v>
+      </c>
+      <c r="P9" s="15">
+        <v>9.5579625064196368E-3</v>
+      </c>
+      <c r="Q9" s="93">
+        <v>7.3592411949940734E-2</v>
+      </c>
+      <c r="R9" s="87">
+        <v>1.3258162597677496</v>
+      </c>
+      <c r="S9" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="T9" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="P9" s="14">
+      <c r="U9" s="14">
         <v>45900</v>
       </c>
-      <c r="Q9" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="R9" s="88">
-        <v>66.231011456376947</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
+      <c r="V9" s="11" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
       <c r="B10" s="11" t="s">
         <v>168</v>
       </c>
@@ -3876,40 +3885,52 @@
       <c r="K10" s="2">
         <v>2.697564413182195</v>
       </c>
-      <c r="L10" s="4">
+      <c r="L10" s="87">
+        <v>2.5899220352770942</v>
+      </c>
+      <c r="M10" s="4">
         <v>3.573276361444476E-2</v>
       </c>
-      <c r="M10" s="4">
+      <c r="N10" s="4">
         <v>4.9726182470532274E-2</v>
       </c>
-      <c r="N10" s="16" t="s">
+      <c r="O10" s="15">
+        <v>0.20351769929714394</v>
+      </c>
+      <c r="P10" s="15">
+        <v>1.0763175939415467E-2</v>
+      </c>
+      <c r="Q10" s="93">
+        <v>0.29882156160837919</v>
+      </c>
+      <c r="R10" s="87">
+        <v>1.8653456492018881</v>
+      </c>
+      <c r="S10" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="O10" s="11" t="s">
+      <c r="T10" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="P10" s="14">
+      <c r="U10" s="14">
         <v>45900</v>
       </c>
-      <c r="Q10" s="11" t="s">
+      <c r="V10" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="R10" s="88">
-        <v>2.7573082335059835</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
+    </row>
+    <row r="11" spans="1:22">
       <c r="B11" s="11" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D11" s="2">
         <v>28.81</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F11" s="15">
         <v>9.408289080523935E-2</v>
@@ -3931,34 +3952,46 @@
       <c r="K11" s="2">
         <v>32.464859269378167</v>
       </c>
-      <c r="L11" s="4">
+      <c r="L11" s="87">
+        <v>31.770050813856095</v>
+      </c>
+      <c r="M11" s="4">
         <v>8.8134932571433455E-2</v>
       </c>
-      <c r="M11" s="4">
+      <c r="N11" s="4">
         <v>5.5536272127733433E-2</v>
       </c>
-      <c r="N11" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="O11" s="11" t="s">
+      <c r="O11" s="15">
+        <v>0.78990369994931575</v>
+      </c>
+      <c r="P11" s="15">
+        <v>0.40281804358844397</v>
+      </c>
+      <c r="Q11" s="93">
+        <v>3.955391512509995</v>
+      </c>
+      <c r="R11" s="87">
+        <v>-26.938493611476797</v>
+      </c>
+      <c r="S11" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="T11" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="P11" s="14">
+      <c r="U11" s="14">
         <v>45900</v>
       </c>
-      <c r="Q11" s="11" t="s">
+      <c r="V11" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="R11" s="88">
-        <v>33.810824894744755</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
+    </row>
+    <row r="12" spans="1:22">
       <c r="B12" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D12" s="2">
         <v>52.2</v>
@@ -3986,2095 +4019,2108 @@
       <c r="K12" s="2">
         <v>67.988942786517455</v>
       </c>
-      <c r="L12" s="4">
+      <c r="L12" s="87">
+        <v>57.531434982190753</v>
+      </c>
+      <c r="M12" s="4">
         <v>0.10069379612803481</v>
       </c>
-      <c r="M12" s="4">
+      <c r="N12" s="4">
         <v>0</v>
       </c>
-      <c r="N12" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="O12" s="11" t="s">
+      <c r="O12" s="15">
+        <v>1.2907496012759174</v>
+      </c>
+      <c r="P12" s="15">
+        <v>0.24768740031897937</v>
+      </c>
+      <c r="Q12" s="93">
+        <v>0.73855199466278643</v>
+      </c>
+      <c r="R12" s="87">
+        <v>-2.643445053008028</v>
+      </c>
+      <c r="S12" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="T12" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="P12" s="14">
+      <c r="U12" s="14">
         <v>45808</v>
       </c>
-      <c r="Q12" s="11" t="s">
+      <c r="V12" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="R12" s="88">
-        <v>61.41108960250569</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
+    </row>
+    <row r="13" spans="1:22">
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
       <c r="E13" s="12"/>
-      <c r="L13" s="4"/>
       <c r="M13" s="4"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="14"/>
-    </row>
-    <row r="14" spans="1:18">
+      <c r="N13" s="4"/>
+      <c r="S13" s="13"/>
+      <c r="T13" s="11"/>
+      <c r="U13" s="14"/>
+    </row>
+    <row r="14" spans="1:22">
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
       <c r="E14" s="12"/>
-      <c r="L14" s="4"/>
       <c r="M14" s="4"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="14"/>
-    </row>
-    <row r="15" spans="1:18">
+      <c r="N14" s="4"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="14"/>
+    </row>
+    <row r="15" spans="1:22">
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
       <c r="E15" s="12"/>
-      <c r="L15" s="4"/>
       <c r="M15" s="4"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="14"/>
-    </row>
-    <row r="16" spans="1:18">
+      <c r="N15" s="4"/>
+      <c r="S15" s="13"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="14"/>
+    </row>
+    <row r="16" spans="1:22">
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
       <c r="E16" s="12"/>
-      <c r="L16" s="4"/>
       <c r="M16" s="4"/>
-      <c r="N16" s="13"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="14"/>
-    </row>
-    <row r="17" spans="2:16">
+      <c r="N16" s="4"/>
+      <c r="S16" s="13"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="14"/>
+    </row>
+    <row r="17" spans="2:21">
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="E17" s="12"/>
-      <c r="L17" s="4"/>
       <c r="M17" s="4"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="14"/>
-    </row>
-    <row r="18" spans="2:16">
+      <c r="N17" s="4"/>
+      <c r="S17" s="13"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="14"/>
+    </row>
+    <row r="18" spans="2:21">
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
       <c r="E18" s="12"/>
-      <c r="L18" s="4"/>
       <c r="M18" s="4"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="14"/>
-    </row>
-    <row r="19" spans="2:16">
+      <c r="N18" s="4"/>
+      <c r="S18" s="13"/>
+      <c r="T18" s="11"/>
+      <c r="U18" s="14"/>
+    </row>
+    <row r="19" spans="2:21">
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
       <c r="E19" s="12"/>
-      <c r="L19" s="4"/>
       <c r="M19" s="4"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="14"/>
-    </row>
-    <row r="20" spans="2:16">
+      <c r="N19" s="4"/>
+      <c r="S19" s="13"/>
+      <c r="T19" s="11"/>
+      <c r="U19" s="14"/>
+    </row>
+    <row r="20" spans="2:21">
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
       <c r="E20" s="12"/>
-      <c r="L20" s="4"/>
       <c r="M20" s="4"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="14"/>
-    </row>
-    <row r="21" spans="2:16">
+      <c r="N20" s="4"/>
+      <c r="S20" s="13"/>
+      <c r="T20" s="11"/>
+      <c r="U20" s="14"/>
+    </row>
+    <row r="21" spans="2:21">
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
       <c r="E21" s="12"/>
-      <c r="L21" s="4"/>
       <c r="M21" s="4"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="14"/>
-    </row>
-    <row r="22" spans="2:16">
+      <c r="N21" s="4"/>
+      <c r="S21" s="13"/>
+      <c r="T21" s="11"/>
+      <c r="U21" s="14"/>
+    </row>
+    <row r="22" spans="2:21">
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="E22" s="12"/>
-      <c r="L22" s="4"/>
       <c r="M22" s="4"/>
-      <c r="N22" s="13"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="14"/>
-    </row>
-    <row r="23" spans="2:16">
+      <c r="N22" s="4"/>
+      <c r="S22" s="13"/>
+      <c r="T22" s="11"/>
+      <c r="U22" s="14"/>
+    </row>
+    <row r="23" spans="2:21">
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="E23" s="12"/>
-      <c r="L23" s="4"/>
       <c r="M23" s="4"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="14"/>
-    </row>
-    <row r="24" spans="2:16">
+      <c r="N23" s="4"/>
+      <c r="S23" s="13"/>
+      <c r="T23" s="11"/>
+      <c r="U23" s="14"/>
+    </row>
+    <row r="24" spans="2:21">
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="E24" s="12"/>
-      <c r="L24" s="4"/>
       <c r="M24" s="4"/>
-      <c r="N24" s="13"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="14"/>
-    </row>
-    <row r="25" spans="2:16">
+      <c r="N24" s="4"/>
+      <c r="S24" s="13"/>
+      <c r="T24" s="11"/>
+      <c r="U24" s="14"/>
+    </row>
+    <row r="25" spans="2:21">
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="E25" s="12"/>
-      <c r="L25" s="4"/>
       <c r="M25" s="4"/>
-      <c r="N25" s="13"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="14"/>
-    </row>
-    <row r="26" spans="2:16">
+      <c r="N25" s="4"/>
+      <c r="S25" s="13"/>
+      <c r="T25" s="11"/>
+      <c r="U25" s="14"/>
+    </row>
+    <row r="26" spans="2:21">
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="E26" s="12"/>
-      <c r="L26" s="4"/>
       <c r="M26" s="4"/>
-      <c r="N26" s="13"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="14"/>
-    </row>
-    <row r="27" spans="2:16">
+      <c r="N26" s="4"/>
+      <c r="S26" s="13"/>
+      <c r="T26" s="11"/>
+      <c r="U26" s="14"/>
+    </row>
+    <row r="27" spans="2:21">
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="E27" s="12"/>
-      <c r="L27" s="4"/>
       <c r="M27" s="4"/>
-      <c r="N27" s="13"/>
-      <c r="O27" s="11"/>
-      <c r="P27" s="14"/>
-    </row>
-    <row r="28" spans="2:16">
+      <c r="N27" s="4"/>
+      <c r="S27" s="13"/>
+      <c r="T27" s="11"/>
+      <c r="U27" s="14"/>
+    </row>
+    <row r="28" spans="2:21">
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="E28" s="12"/>
-      <c r="L28" s="4"/>
       <c r="M28" s="4"/>
-      <c r="N28" s="13"/>
-      <c r="O28" s="11"/>
-      <c r="P28" s="14"/>
-    </row>
-    <row r="29" spans="2:16">
+      <c r="N28" s="4"/>
+      <c r="S28" s="13"/>
+      <c r="T28" s="11"/>
+      <c r="U28" s="14"/>
+    </row>
+    <row r="29" spans="2:21">
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
       <c r="E29" s="12"/>
-      <c r="L29" s="4"/>
       <c r="M29" s="4"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="11"/>
-      <c r="P29" s="14"/>
-    </row>
-    <row r="30" spans="2:16">
+      <c r="N29" s="4"/>
+      <c r="S29" s="13"/>
+      <c r="T29" s="11"/>
+      <c r="U29" s="14"/>
+    </row>
+    <row r="30" spans="2:21">
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="E30" s="12"/>
-      <c r="L30" s="4"/>
       <c r="M30" s="4"/>
-      <c r="N30" s="13"/>
-      <c r="O30" s="11"/>
-      <c r="P30" s="14"/>
-    </row>
-    <row r="31" spans="2:16">
+      <c r="N30" s="4"/>
+      <c r="S30" s="13"/>
+      <c r="T30" s="11"/>
+      <c r="U30" s="14"/>
+    </row>
+    <row r="31" spans="2:21">
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="E31" s="12"/>
-      <c r="L31" s="4"/>
       <c r="M31" s="4"/>
-      <c r="N31" s="16"/>
-      <c r="O31" s="11"/>
-      <c r="P31" s="14"/>
-    </row>
-    <row r="32" spans="2:16">
+      <c r="N31" s="4"/>
+      <c r="S31" s="16"/>
+      <c r="T31" s="11"/>
+      <c r="U31" s="14"/>
+    </row>
+    <row r="32" spans="2:21">
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
       <c r="E32" s="12"/>
-      <c r="L32" s="4"/>
       <c r="M32" s="4"/>
-      <c r="N32" s="13"/>
-      <c r="O32" s="11"/>
-      <c r="P32" s="14"/>
-    </row>
-    <row r="33" spans="2:16">
+      <c r="N32" s="4"/>
+      <c r="S32" s="13"/>
+      <c r="T32" s="11"/>
+      <c r="U32" s="14"/>
+    </row>
+    <row r="33" spans="2:21">
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
       <c r="E33" s="12"/>
-      <c r="L33" s="4"/>
       <c r="M33" s="4"/>
-      <c r="N33" s="13"/>
-      <c r="O33" s="11"/>
-      <c r="P33" s="14"/>
-    </row>
-    <row r="34" spans="2:16">
+      <c r="N33" s="4"/>
+      <c r="S33" s="13"/>
+      <c r="T33" s="11"/>
+      <c r="U33" s="14"/>
+    </row>
+    <row r="34" spans="2:21">
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="E34" s="12"/>
-      <c r="L34" s="4"/>
       <c r="M34" s="4"/>
-      <c r="N34" s="16"/>
-      <c r="O34" s="11"/>
-      <c r="P34" s="14"/>
-    </row>
-    <row r="35" spans="2:16">
+      <c r="N34" s="4"/>
+      <c r="S34" s="16"/>
+      <c r="T34" s="11"/>
+      <c r="U34" s="14"/>
+    </row>
+    <row r="35" spans="2:21">
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
       <c r="E35" s="12"/>
-      <c r="L35" s="4"/>
       <c r="M35" s="4"/>
-      <c r="N35" s="13"/>
-      <c r="O35" s="11"/>
-      <c r="P35" s="14"/>
-    </row>
-    <row r="36" spans="2:16">
+      <c r="N35" s="4"/>
+      <c r="S35" s="13"/>
+      <c r="T35" s="11"/>
+      <c r="U35" s="14"/>
+    </row>
+    <row r="36" spans="2:21">
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
       <c r="E36" s="12"/>
-      <c r="L36" s="4"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="13"/>
-      <c r="O36" s="11"/>
-      <c r="P36" s="14"/>
-    </row>
-    <row r="37" spans="2:16">
+      <c r="N36" s="4"/>
+      <c r="S36" s="13"/>
+      <c r="T36" s="11"/>
+      <c r="U36" s="14"/>
+    </row>
+    <row r="37" spans="2:21">
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
       <c r="E37" s="12"/>
-      <c r="L37" s="4"/>
       <c r="M37" s="4"/>
-      <c r="N37" s="13"/>
-      <c r="O37" s="11"/>
-      <c r="P37" s="14"/>
-    </row>
-    <row r="38" spans="2:16">
+      <c r="N37" s="4"/>
+      <c r="S37" s="13"/>
+      <c r="T37" s="11"/>
+      <c r="U37" s="14"/>
+    </row>
+    <row r="38" spans="2:21">
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
       <c r="E38" s="12"/>
-      <c r="L38" s="4"/>
       <c r="M38" s="4"/>
-      <c r="N38" s="13"/>
-      <c r="O38" s="11"/>
-      <c r="P38" s="14"/>
-    </row>
-    <row r="39" spans="2:16">
+      <c r="N38" s="4"/>
+      <c r="S38" s="13"/>
+      <c r="T38" s="11"/>
+      <c r="U38" s="14"/>
+    </row>
+    <row r="39" spans="2:21">
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
       <c r="E39" s="12"/>
-      <c r="L39" s="4"/>
       <c r="M39" s="4"/>
-      <c r="N39" s="13"/>
-      <c r="O39" s="11"/>
-      <c r="P39" s="14"/>
-    </row>
-    <row r="40" spans="2:16">
+      <c r="N39" s="4"/>
+      <c r="S39" s="13"/>
+      <c r="T39" s="11"/>
+      <c r="U39" s="14"/>
+    </row>
+    <row r="40" spans="2:21">
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
       <c r="E40" s="12"/>
-      <c r="L40" s="4"/>
       <c r="M40" s="4"/>
-      <c r="N40" s="13"/>
-      <c r="O40" s="11"/>
-      <c r="P40" s="14"/>
-    </row>
-    <row r="41" spans="2:16">
+      <c r="N40" s="4"/>
+      <c r="S40" s="13"/>
+      <c r="T40" s="11"/>
+      <c r="U40" s="14"/>
+    </row>
+    <row r="41" spans="2:21">
       <c r="B41" s="11"/>
       <c r="C41" s="11"/>
       <c r="E41" s="12"/>
-      <c r="L41" s="4"/>
       <c r="M41" s="4"/>
-      <c r="N41" s="13"/>
-      <c r="O41" s="11"/>
-      <c r="P41" s="14"/>
-    </row>
-    <row r="42" spans="2:16">
+      <c r="N41" s="4"/>
+      <c r="S41" s="13"/>
+      <c r="T41" s="11"/>
+      <c r="U41" s="14"/>
+    </row>
+    <row r="42" spans="2:21">
       <c r="B42" s="11"/>
       <c r="C42" s="11"/>
       <c r="E42" s="12"/>
-      <c r="L42" s="4"/>
       <c r="M42" s="4"/>
-      <c r="N42" s="13"/>
-      <c r="O42" s="11"/>
-      <c r="P42" s="14"/>
-    </row>
-    <row r="43" spans="2:16">
+      <c r="N42" s="4"/>
+      <c r="S42" s="13"/>
+      <c r="T42" s="11"/>
+      <c r="U42" s="14"/>
+    </row>
+    <row r="43" spans="2:21">
       <c r="B43" s="11"/>
       <c r="C43" s="11"/>
       <c r="E43" s="12"/>
-      <c r="L43" s="4"/>
       <c r="M43" s="4"/>
-      <c r="N43" s="13"/>
-      <c r="O43" s="11"/>
-      <c r="P43" s="14"/>
-    </row>
-    <row r="44" spans="2:16">
+      <c r="N43" s="4"/>
+      <c r="S43" s="13"/>
+      <c r="T43" s="11"/>
+      <c r="U43" s="14"/>
+    </row>
+    <row r="44" spans="2:21">
       <c r="B44" s="11"/>
       <c r="C44" s="11"/>
       <c r="E44" s="12"/>
-      <c r="L44" s="4"/>
       <c r="M44" s="4"/>
-      <c r="N44" s="13"/>
-      <c r="O44" s="11"/>
-      <c r="P44" s="14"/>
-    </row>
-    <row r="45" spans="2:16">
+      <c r="N44" s="4"/>
+      <c r="S44" s="13"/>
+      <c r="T44" s="11"/>
+      <c r="U44" s="14"/>
+    </row>
+    <row r="45" spans="2:21">
       <c r="B45" s="11"/>
       <c r="C45" s="11"/>
       <c r="E45" s="12"/>
-      <c r="L45" s="4"/>
       <c r="M45" s="4"/>
-      <c r="N45" s="13"/>
-      <c r="O45" s="11"/>
-      <c r="P45" s="14"/>
-    </row>
-    <row r="46" spans="2:16">
+      <c r="N45" s="4"/>
+      <c r="S45" s="13"/>
+      <c r="T45" s="11"/>
+      <c r="U45" s="14"/>
+    </row>
+    <row r="46" spans="2:21">
       <c r="B46" s="11"/>
       <c r="C46" s="11"/>
       <c r="E46" s="12"/>
-      <c r="L46" s="4"/>
       <c r="M46" s="4"/>
-      <c r="N46" s="13"/>
-      <c r="O46" s="11"/>
-      <c r="P46" s="14"/>
-    </row>
-    <row r="47" spans="2:16">
+      <c r="N46" s="4"/>
+      <c r="S46" s="13"/>
+      <c r="T46" s="11"/>
+      <c r="U46" s="14"/>
+    </row>
+    <row r="47" spans="2:21">
       <c r="B47" s="11"/>
       <c r="C47" s="11"/>
       <c r="E47" s="12"/>
-      <c r="L47" s="4"/>
       <c r="M47" s="4"/>
-      <c r="N47" s="13"/>
-      <c r="O47" s="11"/>
-      <c r="P47" s="14"/>
-    </row>
-    <row r="48" spans="2:16">
+      <c r="N47" s="4"/>
+      <c r="S47" s="13"/>
+      <c r="T47" s="11"/>
+      <c r="U47" s="14"/>
+    </row>
+    <row r="48" spans="2:21">
       <c r="B48" s="11"/>
       <c r="C48" s="11"/>
       <c r="E48" s="12"/>
-      <c r="L48" s="4"/>
       <c r="M48" s="4"/>
-      <c r="N48" s="13"/>
-      <c r="O48" s="11"/>
-      <c r="P48" s="14"/>
-    </row>
-    <row r="49" spans="2:16">
+      <c r="N48" s="4"/>
+      <c r="S48" s="13"/>
+      <c r="T48" s="11"/>
+      <c r="U48" s="14"/>
+    </row>
+    <row r="49" spans="2:21">
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
       <c r="E49" s="12"/>
-      <c r="L49" s="4"/>
       <c r="M49" s="4"/>
-      <c r="N49" s="13"/>
-      <c r="O49" s="11"/>
-      <c r="P49" s="14"/>
-    </row>
-    <row r="50" spans="2:16">
+      <c r="N49" s="4"/>
+      <c r="S49" s="13"/>
+      <c r="T49" s="11"/>
+      <c r="U49" s="14"/>
+    </row>
+    <row r="50" spans="2:21">
       <c r="B50" s="11"/>
       <c r="C50" s="11"/>
       <c r="E50" s="12"/>
-      <c r="L50" s="4"/>
       <c r="M50" s="4"/>
-      <c r="N50" s="13"/>
-      <c r="O50" s="11"/>
-      <c r="P50" s="14"/>
-    </row>
-    <row r="51" spans="2:16">
+      <c r="N50" s="4"/>
+      <c r="S50" s="13"/>
+      <c r="T50" s="11"/>
+      <c r="U50" s="14"/>
+    </row>
+    <row r="51" spans="2:21">
       <c r="B51" s="11"/>
       <c r="C51" s="11"/>
       <c r="E51" s="12"/>
-      <c r="L51" s="4"/>
       <c r="M51" s="4"/>
-      <c r="N51" s="13"/>
-      <c r="O51" s="11"/>
-      <c r="P51" s="14"/>
-    </row>
-    <row r="52" spans="2:16">
+      <c r="N51" s="4"/>
+      <c r="S51" s="13"/>
+      <c r="T51" s="11"/>
+      <c r="U51" s="14"/>
+    </row>
+    <row r="52" spans="2:21">
       <c r="B52" s="11"/>
       <c r="C52" s="11"/>
       <c r="E52" s="12"/>
-      <c r="L52" s="4"/>
       <c r="M52" s="4"/>
-      <c r="N52" s="13"/>
-      <c r="O52" s="11"/>
-      <c r="P52" s="14"/>
-    </row>
-    <row r="53" spans="2:16">
+      <c r="N52" s="4"/>
+      <c r="S52" s="13"/>
+      <c r="T52" s="11"/>
+      <c r="U52" s="14"/>
+    </row>
+    <row r="53" spans="2:21">
       <c r="B53" s="11"/>
       <c r="C53" s="11"/>
       <c r="E53" s="12"/>
-      <c r="L53" s="4"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="13"/>
-      <c r="O53" s="11"/>
-      <c r="P53" s="14"/>
-    </row>
-    <row r="54" spans="2:16">
+      <c r="N53" s="4"/>
+      <c r="S53" s="13"/>
+      <c r="T53" s="11"/>
+      <c r="U53" s="14"/>
+    </row>
+    <row r="54" spans="2:21">
       <c r="B54" s="11"/>
       <c r="C54" s="11"/>
       <c r="E54" s="12"/>
-      <c r="L54" s="4"/>
       <c r="M54" s="4"/>
-      <c r="N54" s="13"/>
-      <c r="O54" s="11"/>
-      <c r="P54" s="14"/>
-    </row>
-    <row r="55" spans="2:16">
+      <c r="N54" s="4"/>
+      <c r="S54" s="13"/>
+      <c r="T54" s="11"/>
+      <c r="U54" s="14"/>
+    </row>
+    <row r="55" spans="2:21">
       <c r="B55" s="11"/>
       <c r="C55" s="11"/>
       <c r="E55" s="12"/>
-      <c r="L55" s="4"/>
       <c r="M55" s="4"/>
-      <c r="N55" s="13"/>
-      <c r="O55" s="11"/>
-      <c r="P55" s="14"/>
-    </row>
-    <row r="56" spans="2:16">
+      <c r="N55" s="4"/>
+      <c r="S55" s="13"/>
+      <c r="T55" s="11"/>
+      <c r="U55" s="14"/>
+    </row>
+    <row r="56" spans="2:21">
       <c r="B56" s="11"/>
       <c r="C56" s="11"/>
       <c r="E56" s="12"/>
-      <c r="L56" s="4"/>
       <c r="M56" s="4"/>
-      <c r="N56" s="13"/>
-      <c r="O56" s="11"/>
-      <c r="P56" s="14"/>
-    </row>
-    <row r="57" spans="2:16">
+      <c r="N56" s="4"/>
+      <c r="S56" s="13"/>
+      <c r="T56" s="11"/>
+      <c r="U56" s="14"/>
+    </row>
+    <row r="57" spans="2:21">
       <c r="B57" s="11"/>
       <c r="C57" s="11"/>
       <c r="E57" s="12"/>
-      <c r="L57" s="4"/>
       <c r="M57" s="4"/>
-      <c r="N57" s="13"/>
-      <c r="O57" s="11"/>
-      <c r="P57" s="14"/>
-    </row>
-    <row r="58" spans="2:16">
+      <c r="N57" s="4"/>
+      <c r="S57" s="13"/>
+      <c r="T57" s="11"/>
+      <c r="U57" s="14"/>
+    </row>
+    <row r="58" spans="2:21">
       <c r="B58" s="11"/>
       <c r="C58" s="11"/>
       <c r="E58" s="12"/>
-      <c r="L58" s="4"/>
       <c r="M58" s="4"/>
-      <c r="N58" s="13"/>
-      <c r="O58" s="11"/>
-      <c r="P58" s="14"/>
-    </row>
-    <row r="59" spans="2:16">
+      <c r="N58" s="4"/>
+      <c r="S58" s="13"/>
+      <c r="T58" s="11"/>
+      <c r="U58" s="14"/>
+    </row>
+    <row r="59" spans="2:21">
       <c r="B59" s="11"/>
       <c r="C59" s="11"/>
       <c r="E59" s="12"/>
-      <c r="L59" s="4"/>
       <c r="M59" s="4"/>
-      <c r="N59" s="13"/>
-      <c r="O59" s="11"/>
-      <c r="P59" s="14"/>
-    </row>
-    <row r="60" spans="2:16">
+      <c r="N59" s="4"/>
+      <c r="S59" s="13"/>
+      <c r="T59" s="11"/>
+      <c r="U59" s="14"/>
+    </row>
+    <row r="60" spans="2:21">
       <c r="B60" s="11"/>
       <c r="C60" s="11"/>
       <c r="E60" s="12"/>
-      <c r="L60" s="4"/>
       <c r="M60" s="4"/>
-      <c r="N60" s="13"/>
-      <c r="O60" s="11"/>
-      <c r="P60" s="14"/>
-    </row>
-    <row r="61" spans="2:16">
+      <c r="N60" s="4"/>
+      <c r="S60" s="13"/>
+      <c r="T60" s="11"/>
+      <c r="U60" s="14"/>
+    </row>
+    <row r="61" spans="2:21">
       <c r="B61" s="11"/>
       <c r="C61" s="11"/>
       <c r="E61" s="12"/>
-      <c r="L61" s="4"/>
       <c r="M61" s="4"/>
-      <c r="N61" s="13"/>
-      <c r="O61" s="11"/>
-      <c r="P61" s="14"/>
-    </row>
-    <row r="62" spans="2:16">
+      <c r="N61" s="4"/>
+      <c r="S61" s="13"/>
+      <c r="T61" s="11"/>
+      <c r="U61" s="14"/>
+    </row>
+    <row r="62" spans="2:21">
       <c r="B62" s="11"/>
       <c r="C62" s="11"/>
       <c r="E62" s="12"/>
-      <c r="L62" s="4"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="13"/>
-      <c r="O62" s="11"/>
-      <c r="P62" s="14"/>
-    </row>
-    <row r="63" spans="2:16">
+      <c r="N62" s="4"/>
+      <c r="S62" s="13"/>
+      <c r="T62" s="11"/>
+      <c r="U62" s="14"/>
+    </row>
+    <row r="63" spans="2:21">
       <c r="B63" s="11"/>
       <c r="C63" s="11"/>
       <c r="E63" s="12"/>
-      <c r="L63" s="4"/>
       <c r="M63" s="4"/>
-      <c r="N63" s="13"/>
-      <c r="O63" s="11"/>
-      <c r="P63" s="14"/>
-    </row>
-    <row r="64" spans="2:16">
+      <c r="N63" s="4"/>
+      <c r="S63" s="13"/>
+      <c r="T63" s="11"/>
+      <c r="U63" s="14"/>
+    </row>
+    <row r="64" spans="2:21">
       <c r="B64" s="11"/>
       <c r="C64" s="11"/>
       <c r="E64" s="12"/>
-      <c r="L64" s="4"/>
       <c r="M64" s="4"/>
-      <c r="N64" s="13"/>
-      <c r="O64" s="11"/>
-      <c r="P64" s="14"/>
-    </row>
-    <row r="65" spans="2:16">
+      <c r="N64" s="4"/>
+      <c r="S64" s="13"/>
+      <c r="T64" s="11"/>
+      <c r="U64" s="14"/>
+    </row>
+    <row r="65" spans="2:21">
       <c r="B65" s="11"/>
       <c r="C65" s="11"/>
       <c r="E65" s="12"/>
-      <c r="L65" s="4"/>
       <c r="M65" s="4"/>
-      <c r="N65" s="13"/>
-      <c r="O65" s="11"/>
-      <c r="P65" s="14"/>
-    </row>
-    <row r="66" spans="2:16">
+      <c r="N65" s="4"/>
+      <c r="S65" s="13"/>
+      <c r="T65" s="11"/>
+      <c r="U65" s="14"/>
+    </row>
+    <row r="66" spans="2:21">
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
       <c r="E66" s="12"/>
-      <c r="L66" s="4"/>
       <c r="M66" s="4"/>
-      <c r="N66" s="13"/>
-      <c r="O66" s="11"/>
-      <c r="P66" s="14"/>
-    </row>
-    <row r="67" spans="2:16">
+      <c r="N66" s="4"/>
+      <c r="S66" s="13"/>
+      <c r="T66" s="11"/>
+      <c r="U66" s="14"/>
+    </row>
+    <row r="67" spans="2:21">
       <c r="B67" s="11"/>
       <c r="C67" s="11"/>
       <c r="E67" s="12"/>
-      <c r="L67" s="4"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="13"/>
-      <c r="O67" s="11"/>
-      <c r="P67" s="14"/>
-    </row>
-    <row r="68" spans="2:16">
+      <c r="N67" s="4"/>
+      <c r="S67" s="13"/>
+      <c r="T67" s="11"/>
+      <c r="U67" s="14"/>
+    </row>
+    <row r="68" spans="2:21">
       <c r="B68" s="11"/>
       <c r="C68" s="11"/>
       <c r="E68" s="12"/>
-      <c r="L68" s="4"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="13"/>
-      <c r="O68" s="11"/>
-      <c r="P68" s="14"/>
-    </row>
-    <row r="69" spans="2:16">
+      <c r="N68" s="4"/>
+      <c r="S68" s="13"/>
+      <c r="T68" s="11"/>
+      <c r="U68" s="14"/>
+    </row>
+    <row r="69" spans="2:21">
       <c r="B69" s="11"/>
       <c r="C69" s="11"/>
       <c r="E69" s="12"/>
-      <c r="L69" s="4"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="13"/>
-      <c r="O69" s="11"/>
-      <c r="P69" s="14"/>
-    </row>
-    <row r="70" spans="2:16">
+      <c r="N69" s="4"/>
+      <c r="S69" s="13"/>
+      <c r="T69" s="11"/>
+      <c r="U69" s="14"/>
+    </row>
+    <row r="70" spans="2:21">
       <c r="B70" s="11"/>
       <c r="C70" s="11"/>
       <c r="E70" s="12"/>
-      <c r="L70" s="4"/>
       <c r="M70" s="4"/>
-      <c r="N70" s="13"/>
-      <c r="O70" s="11"/>
-      <c r="P70" s="14"/>
-    </row>
-    <row r="71" spans="2:16">
+      <c r="N70" s="4"/>
+      <c r="S70" s="13"/>
+      <c r="T70" s="11"/>
+      <c r="U70" s="14"/>
+    </row>
+    <row r="71" spans="2:21">
       <c r="B71" s="11"/>
       <c r="C71" s="11"/>
       <c r="E71" s="12"/>
-      <c r="L71" s="4"/>
       <c r="M71" s="4"/>
-      <c r="N71" s="13"/>
-      <c r="O71" s="11"/>
-      <c r="P71" s="14"/>
-    </row>
-    <row r="72" spans="2:16">
+      <c r="N71" s="4"/>
+      <c r="S71" s="13"/>
+      <c r="T71" s="11"/>
+      <c r="U71" s="14"/>
+    </row>
+    <row r="72" spans="2:21">
       <c r="B72" s="11"/>
       <c r="C72" s="11"/>
       <c r="E72" s="12"/>
-      <c r="L72" s="4"/>
       <c r="M72" s="4"/>
-      <c r="N72" s="13"/>
-      <c r="O72" s="11"/>
-      <c r="P72" s="14"/>
-    </row>
-    <row r="73" spans="2:16">
+      <c r="N72" s="4"/>
+      <c r="S72" s="13"/>
+      <c r="T72" s="11"/>
+      <c r="U72" s="14"/>
+    </row>
+    <row r="73" spans="2:21">
       <c r="B73" s="11"/>
       <c r="C73" s="11"/>
       <c r="E73" s="12"/>
-      <c r="L73" s="4"/>
       <c r="M73" s="4"/>
-      <c r="N73" s="13"/>
-      <c r="O73" s="11"/>
-      <c r="P73" s="14"/>
-    </row>
-    <row r="74" spans="2:16">
+      <c r="N73" s="4"/>
+      <c r="S73" s="13"/>
+      <c r="T73" s="11"/>
+      <c r="U73" s="14"/>
+    </row>
+    <row r="74" spans="2:21">
       <c r="B74" s="11"/>
       <c r="C74" s="11"/>
       <c r="E74" s="12"/>
-      <c r="L74" s="4"/>
       <c r="M74" s="4"/>
-      <c r="N74" s="13"/>
-      <c r="O74" s="11"/>
-      <c r="P74" s="14"/>
-    </row>
-    <row r="75" spans="2:16">
+      <c r="N74" s="4"/>
+      <c r="S74" s="13"/>
+      <c r="T74" s="11"/>
+      <c r="U74" s="14"/>
+    </row>
+    <row r="75" spans="2:21">
       <c r="B75" s="11"/>
       <c r="C75" s="11"/>
       <c r="E75" s="12"/>
-      <c r="L75" s="4"/>
       <c r="M75" s="4"/>
-      <c r="N75" s="13"/>
-      <c r="O75" s="11"/>
-      <c r="P75" s="14"/>
-    </row>
-    <row r="76" spans="2:16">
+      <c r="N75" s="4"/>
+      <c r="S75" s="13"/>
+      <c r="T75" s="11"/>
+      <c r="U75" s="14"/>
+    </row>
+    <row r="76" spans="2:21">
       <c r="B76" s="11"/>
       <c r="C76" s="11"/>
       <c r="E76" s="12"/>
-      <c r="L76" s="4"/>
       <c r="M76" s="4"/>
-      <c r="N76" s="13"/>
-      <c r="O76" s="11"/>
-      <c r="P76" s="14"/>
-    </row>
-    <row r="77" spans="2:16">
+      <c r="N76" s="4"/>
+      <c r="S76" s="13"/>
+      <c r="T76" s="11"/>
+      <c r="U76" s="14"/>
+    </row>
+    <row r="77" spans="2:21">
       <c r="B77" s="11"/>
       <c r="C77" s="11"/>
       <c r="E77" s="12"/>
-      <c r="L77" s="4"/>
       <c r="M77" s="4"/>
-      <c r="N77" s="13"/>
-      <c r="O77" s="11"/>
-      <c r="P77" s="14"/>
-    </row>
-    <row r="78" spans="2:16">
+      <c r="N77" s="4"/>
+      <c r="S77" s="13"/>
+      <c r="T77" s="11"/>
+      <c r="U77" s="14"/>
+    </row>
+    <row r="78" spans="2:21">
       <c r="B78" s="11"/>
       <c r="C78" s="11"/>
       <c r="E78" s="12"/>
-      <c r="L78" s="4"/>
       <c r="M78" s="4"/>
-      <c r="N78" s="13"/>
-      <c r="O78" s="11"/>
-      <c r="P78" s="14"/>
-    </row>
-    <row r="79" spans="2:16">
+      <c r="N78" s="4"/>
+      <c r="S78" s="13"/>
+      <c r="T78" s="11"/>
+      <c r="U78" s="14"/>
+    </row>
+    <row r="79" spans="2:21">
       <c r="B79" s="11"/>
       <c r="C79" s="11"/>
       <c r="E79" s="12"/>
-      <c r="L79" s="4"/>
       <c r="M79" s="4"/>
-      <c r="N79" s="13"/>
-      <c r="O79" s="11"/>
-      <c r="P79" s="14"/>
-    </row>
-    <row r="80" spans="2:16">
+      <c r="N79" s="4"/>
+      <c r="S79" s="13"/>
+      <c r="T79" s="11"/>
+      <c r="U79" s="14"/>
+    </row>
+    <row r="80" spans="2:21">
       <c r="B80" s="11"/>
       <c r="C80" s="11"/>
       <c r="E80" s="12"/>
-      <c r="L80" s="4"/>
       <c r="M80" s="4"/>
-      <c r="N80" s="13"/>
-      <c r="O80" s="11"/>
-      <c r="P80" s="14"/>
-    </row>
-    <row r="81" spans="2:16">
+      <c r="N80" s="4"/>
+      <c r="S80" s="13"/>
+      <c r="T80" s="11"/>
+      <c r="U80" s="14"/>
+    </row>
+    <row r="81" spans="2:21">
       <c r="B81" s="11"/>
       <c r="C81" s="11"/>
       <c r="E81" s="12"/>
-      <c r="L81" s="4"/>
       <c r="M81" s="4"/>
-      <c r="N81" s="13"/>
-      <c r="O81" s="11"/>
-      <c r="P81" s="14"/>
-    </row>
-    <row r="82" spans="2:16">
+      <c r="N81" s="4"/>
+      <c r="S81" s="13"/>
+      <c r="T81" s="11"/>
+      <c r="U81" s="14"/>
+    </row>
+    <row r="82" spans="2:21">
       <c r="B82" s="11"/>
       <c r="C82" s="11"/>
       <c r="E82" s="12"/>
-      <c r="L82" s="4"/>
       <c r="M82" s="4"/>
-      <c r="N82" s="13"/>
-      <c r="O82" s="11"/>
-      <c r="P82" s="14"/>
-    </row>
-    <row r="83" spans="2:16">
+      <c r="N82" s="4"/>
+      <c r="S82" s="13"/>
+      <c r="T82" s="11"/>
+      <c r="U82" s="14"/>
+    </row>
+    <row r="83" spans="2:21">
       <c r="B83" s="11"/>
       <c r="C83" s="11"/>
       <c r="E83" s="12"/>
-      <c r="L83" s="4"/>
       <c r="M83" s="4"/>
-      <c r="N83" s="13"/>
-      <c r="O83" s="11"/>
-      <c r="P83" s="14"/>
-    </row>
-    <row r="84" spans="2:16">
+      <c r="N83" s="4"/>
+      <c r="S83" s="13"/>
+      <c r="T83" s="11"/>
+      <c r="U83" s="14"/>
+    </row>
+    <row r="84" spans="2:21">
       <c r="B84" s="11"/>
       <c r="C84" s="11"/>
       <c r="E84" s="12"/>
-      <c r="L84" s="4"/>
       <c r="M84" s="4"/>
-      <c r="N84" s="13"/>
-      <c r="O84" s="11"/>
-      <c r="P84" s="14"/>
-    </row>
-    <row r="85" spans="2:16">
+      <c r="N84" s="4"/>
+      <c r="S84" s="13"/>
+      <c r="T84" s="11"/>
+      <c r="U84" s="14"/>
+    </row>
+    <row r="85" spans="2:21">
       <c r="B85" s="11"/>
       <c r="C85" s="11"/>
       <c r="E85" s="12"/>
-      <c r="L85" s="4"/>
       <c r="M85" s="4"/>
-      <c r="N85" s="13"/>
-      <c r="O85" s="11"/>
-      <c r="P85" s="14"/>
-    </row>
-    <row r="86" spans="2:16">
+      <c r="N85" s="4"/>
+      <c r="S85" s="13"/>
+      <c r="T85" s="11"/>
+      <c r="U85" s="14"/>
+    </row>
+    <row r="86" spans="2:21">
       <c r="B86" s="11"/>
       <c r="C86" s="11"/>
       <c r="E86" s="12"/>
-      <c r="L86" s="4"/>
       <c r="M86" s="4"/>
-      <c r="N86" s="13"/>
-      <c r="O86" s="11"/>
-      <c r="P86" s="14"/>
-    </row>
-    <row r="87" spans="2:16">
+      <c r="N86" s="4"/>
+      <c r="S86" s="13"/>
+      <c r="T86" s="11"/>
+      <c r="U86" s="14"/>
+    </row>
+    <row r="87" spans="2:21">
       <c r="B87" s="11"/>
       <c r="C87" s="11"/>
       <c r="E87" s="12"/>
-      <c r="L87" s="4"/>
       <c r="M87" s="4"/>
-      <c r="N87" s="13"/>
-      <c r="O87" s="11"/>
-      <c r="P87" s="14"/>
-    </row>
-    <row r="88" spans="2:16">
+      <c r="N87" s="4"/>
+      <c r="S87" s="13"/>
+      <c r="T87" s="11"/>
+      <c r="U87" s="14"/>
+    </row>
+    <row r="88" spans="2:21">
       <c r="B88" s="11"/>
       <c r="C88" s="11"/>
       <c r="E88" s="12"/>
-      <c r="L88" s="4"/>
       <c r="M88" s="4"/>
-      <c r="N88" s="13"/>
-      <c r="O88" s="11"/>
-      <c r="P88" s="14"/>
-    </row>
-    <row r="89" spans="2:16">
+      <c r="N88" s="4"/>
+      <c r="S88" s="13"/>
+      <c r="T88" s="11"/>
+      <c r="U88" s="14"/>
+    </row>
+    <row r="89" spans="2:21">
       <c r="B89" s="11"/>
       <c r="C89" s="11"/>
       <c r="E89" s="12"/>
-      <c r="L89" s="4"/>
       <c r="M89" s="4"/>
-      <c r="N89" s="13"/>
-      <c r="O89" s="11"/>
-      <c r="P89" s="14"/>
-    </row>
-    <row r="90" spans="2:16">
+      <c r="N89" s="4"/>
+      <c r="S89" s="13"/>
+      <c r="T89" s="11"/>
+      <c r="U89" s="14"/>
+    </row>
+    <row r="90" spans="2:21">
       <c r="B90" s="11"/>
       <c r="C90" s="11"/>
       <c r="E90" s="12"/>
-      <c r="L90" s="4"/>
       <c r="M90" s="4"/>
-      <c r="N90" s="13"/>
-      <c r="O90" s="11"/>
-      <c r="P90" s="14"/>
-    </row>
-    <row r="91" spans="2:16">
+      <c r="N90" s="4"/>
+      <c r="S90" s="13"/>
+      <c r="T90" s="11"/>
+      <c r="U90" s="14"/>
+    </row>
+    <row r="91" spans="2:21">
       <c r="B91" s="11"/>
       <c r="C91" s="11"/>
       <c r="E91" s="12"/>
-      <c r="L91" s="4"/>
       <c r="M91" s="4"/>
-      <c r="N91" s="13"/>
-      <c r="O91" s="11"/>
-      <c r="P91" s="14"/>
-    </row>
-    <row r="92" spans="2:16">
+      <c r="N91" s="4"/>
+      <c r="S91" s="13"/>
+      <c r="T91" s="11"/>
+      <c r="U91" s="14"/>
+    </row>
+    <row r="92" spans="2:21">
       <c r="B92" s="11"/>
       <c r="C92" s="11"/>
       <c r="E92" s="12"/>
-      <c r="L92" s="4"/>
       <c r="M92" s="4"/>
-      <c r="N92" s="13"/>
-      <c r="O92" s="11"/>
-      <c r="P92" s="14"/>
-    </row>
-    <row r="93" spans="2:16">
+      <c r="N92" s="4"/>
+      <c r="S92" s="13"/>
+      <c r="T92" s="11"/>
+      <c r="U92" s="14"/>
+    </row>
+    <row r="93" spans="2:21">
       <c r="B93" s="11"/>
       <c r="C93" s="11"/>
       <c r="E93" s="12"/>
-      <c r="L93" s="4"/>
       <c r="M93" s="4"/>
-      <c r="N93" s="13"/>
-      <c r="O93" s="11"/>
-      <c r="P93" s="14"/>
-    </row>
-    <row r="94" spans="2:16">
+      <c r="N93" s="4"/>
+      <c r="S93" s="13"/>
+      <c r="T93" s="11"/>
+      <c r="U93" s="14"/>
+    </row>
+    <row r="94" spans="2:21">
       <c r="B94" s="11"/>
       <c r="C94" s="11"/>
       <c r="E94" s="12"/>
-      <c r="L94" s="4"/>
       <c r="M94" s="4"/>
-      <c r="N94" s="13"/>
-      <c r="O94" s="11"/>
-      <c r="P94" s="14"/>
-    </row>
-    <row r="95" spans="2:16">
+      <c r="N94" s="4"/>
+      <c r="S94" s="13"/>
+      <c r="T94" s="11"/>
+      <c r="U94" s="14"/>
+    </row>
+    <row r="95" spans="2:21">
       <c r="B95" s="11"/>
       <c r="C95" s="11"/>
       <c r="E95" s="12"/>
-      <c r="L95" s="4"/>
       <c r="M95" s="4"/>
-      <c r="N95" s="13"/>
-      <c r="O95" s="11"/>
-      <c r="P95" s="14"/>
-    </row>
-    <row r="96" spans="2:16">
+      <c r="N95" s="4"/>
+      <c r="S95" s="13"/>
+      <c r="T95" s="11"/>
+      <c r="U95" s="14"/>
+    </row>
+    <row r="96" spans="2:21">
       <c r="B96" s="11"/>
       <c r="C96" s="11"/>
       <c r="E96" s="12"/>
-      <c r="L96" s="4"/>
       <c r="M96" s="4"/>
-      <c r="N96" s="13"/>
-      <c r="O96" s="11"/>
-      <c r="P96" s="14"/>
-    </row>
-    <row r="97" spans="2:16">
+      <c r="N96" s="4"/>
+      <c r="S96" s="13"/>
+      <c r="T96" s="11"/>
+      <c r="U96" s="14"/>
+    </row>
+    <row r="97" spans="2:21">
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
       <c r="E97" s="12"/>
-      <c r="L97" s="4"/>
       <c r="M97" s="4"/>
-      <c r="N97" s="13"/>
-      <c r="O97" s="11"/>
-      <c r="P97" s="14"/>
-    </row>
-    <row r="98" spans="2:16">
+      <c r="N97" s="4"/>
+      <c r="S97" s="13"/>
+      <c r="T97" s="11"/>
+      <c r="U97" s="14"/>
+    </row>
+    <row r="98" spans="2:21">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
       <c r="E98" s="12"/>
-      <c r="L98" s="4"/>
       <c r="M98" s="4"/>
-      <c r="N98" s="13"/>
-      <c r="O98" s="11"/>
-      <c r="P98" s="14"/>
-    </row>
-    <row r="99" spans="2:16">
+      <c r="N98" s="4"/>
+      <c r="S98" s="13"/>
+      <c r="T98" s="11"/>
+      <c r="U98" s="14"/>
+    </row>
+    <row r="99" spans="2:21">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
       <c r="E99" s="12"/>
-      <c r="L99" s="4"/>
       <c r="M99" s="4"/>
-      <c r="N99" s="13"/>
-      <c r="O99" s="11"/>
-      <c r="P99" s="14"/>
-    </row>
-    <row r="100" spans="2:16">
+      <c r="N99" s="4"/>
+      <c r="S99" s="13"/>
+      <c r="T99" s="11"/>
+      <c r="U99" s="14"/>
+    </row>
+    <row r="100" spans="2:21">
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="E100" s="12"/>
-      <c r="L100" s="4"/>
       <c r="M100" s="4"/>
-      <c r="N100" s="13"/>
-      <c r="O100" s="11"/>
-      <c r="P100" s="14"/>
-    </row>
-    <row r="101" spans="2:16">
+      <c r="N100" s="4"/>
+      <c r="S100" s="13"/>
+      <c r="T100" s="11"/>
+      <c r="U100" s="14"/>
+    </row>
+    <row r="101" spans="2:21">
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="E101" s="12"/>
-      <c r="L101" s="4"/>
       <c r="M101" s="4"/>
-      <c r="N101" s="13"/>
-      <c r="O101" s="11"/>
-      <c r="P101" s="14"/>
-    </row>
-    <row r="102" spans="2:16">
+      <c r="N101" s="4"/>
+      <c r="S101" s="13"/>
+      <c r="T101" s="11"/>
+      <c r="U101" s="14"/>
+    </row>
+    <row r="102" spans="2:21">
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="E102" s="12"/>
-      <c r="L102" s="4"/>
       <c r="M102" s="4"/>
-      <c r="N102" s="13"/>
-      <c r="O102" s="11"/>
-      <c r="P102" s="14"/>
-    </row>
-    <row r="103" spans="2:16">
+      <c r="N102" s="4"/>
+      <c r="S102" s="13"/>
+      <c r="T102" s="11"/>
+      <c r="U102" s="14"/>
+    </row>
+    <row r="103" spans="2:21">
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="E103" s="12"/>
-      <c r="L103" s="4"/>
       <c r="M103" s="4"/>
-      <c r="N103" s="13"/>
-      <c r="O103" s="11"/>
-      <c r="P103" s="14"/>
-    </row>
-    <row r="104" spans="2:16">
+      <c r="N103" s="4"/>
+      <c r="S103" s="13"/>
+      <c r="T103" s="11"/>
+      <c r="U103" s="14"/>
+    </row>
+    <row r="104" spans="2:21">
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="E104" s="12"/>
-      <c r="L104" s="4"/>
       <c r="M104" s="4"/>
-      <c r="N104" s="13"/>
-      <c r="O104" s="11"/>
-      <c r="P104" s="14"/>
-    </row>
-    <row r="105" spans="2:16">
+      <c r="N104" s="4"/>
+      <c r="S104" s="13"/>
+      <c r="T104" s="11"/>
+      <c r="U104" s="14"/>
+    </row>
+    <row r="105" spans="2:21">
       <c r="B105" s="11"/>
       <c r="C105" s="11"/>
       <c r="E105" s="12"/>
-      <c r="L105" s="4"/>
       <c r="M105" s="4"/>
-      <c r="N105" s="13"/>
-      <c r="O105" s="11"/>
-      <c r="P105" s="14"/>
-    </row>
-    <row r="106" spans="2:16">
+      <c r="N105" s="4"/>
+      <c r="S105" s="13"/>
+      <c r="T105" s="11"/>
+      <c r="U105" s="14"/>
+    </row>
+    <row r="106" spans="2:21">
       <c r="B106" s="11"/>
       <c r="C106" s="11"/>
       <c r="E106" s="12"/>
-      <c r="L106" s="4"/>
       <c r="M106" s="4"/>
-      <c r="N106" s="13"/>
-      <c r="O106" s="11"/>
-      <c r="P106" s="14"/>
-    </row>
-    <row r="107" spans="2:16">
+      <c r="N106" s="4"/>
+      <c r="S106" s="13"/>
+      <c r="T106" s="11"/>
+      <c r="U106" s="14"/>
+    </row>
+    <row r="107" spans="2:21">
       <c r="B107" s="11"/>
       <c r="C107" s="11"/>
       <c r="E107" s="12"/>
-      <c r="L107" s="4"/>
       <c r="M107" s="4"/>
-      <c r="N107" s="13"/>
-      <c r="O107" s="11"/>
-      <c r="P107" s="14"/>
-    </row>
-    <row r="108" spans="2:16">
+      <c r="N107" s="4"/>
+      <c r="S107" s="13"/>
+      <c r="T107" s="11"/>
+      <c r="U107" s="14"/>
+    </row>
+    <row r="108" spans="2:21">
       <c r="B108" s="11"/>
       <c r="C108" s="11"/>
       <c r="E108" s="12"/>
-      <c r="L108" s="4"/>
       <c r="M108" s="4"/>
-      <c r="N108" s="13"/>
-      <c r="O108" s="11"/>
-      <c r="P108" s="14"/>
-    </row>
-    <row r="109" spans="2:16">
+      <c r="N108" s="4"/>
+      <c r="S108" s="13"/>
+      <c r="T108" s="11"/>
+      <c r="U108" s="14"/>
+    </row>
+    <row r="109" spans="2:21">
       <c r="B109" s="11"/>
       <c r="C109" s="11"/>
       <c r="E109" s="12"/>
-      <c r="L109" s="4"/>
       <c r="M109" s="4"/>
-      <c r="N109" s="13"/>
-      <c r="O109" s="11"/>
-      <c r="P109" s="14"/>
-    </row>
-    <row r="110" spans="2:16">
+      <c r="N109" s="4"/>
+      <c r="S109" s="13"/>
+      <c r="T109" s="11"/>
+      <c r="U109" s="14"/>
+    </row>
+    <row r="110" spans="2:21">
       <c r="B110" s="11"/>
       <c r="C110" s="11"/>
       <c r="E110" s="12"/>
-      <c r="L110" s="4"/>
       <c r="M110" s="4"/>
-      <c r="N110" s="13"/>
-      <c r="O110" s="11"/>
-      <c r="P110" s="14"/>
-    </row>
-    <row r="111" spans="2:16">
+      <c r="N110" s="4"/>
+      <c r="S110" s="13"/>
+      <c r="T110" s="11"/>
+      <c r="U110" s="14"/>
+    </row>
+    <row r="111" spans="2:21">
       <c r="B111" s="11"/>
       <c r="C111" s="11"/>
       <c r="E111" s="12"/>
-      <c r="L111" s="4"/>
       <c r="M111" s="4"/>
-      <c r="N111" s="13"/>
-      <c r="O111" s="11"/>
-      <c r="P111" s="14"/>
-    </row>
-    <row r="112" spans="2:16">
+      <c r="N111" s="4"/>
+      <c r="S111" s="13"/>
+      <c r="T111" s="11"/>
+      <c r="U111" s="14"/>
+    </row>
+    <row r="112" spans="2:21">
       <c r="B112" s="11"/>
       <c r="C112" s="11"/>
       <c r="E112" s="12"/>
-      <c r="L112" s="4"/>
       <c r="M112" s="4"/>
-      <c r="N112" s="13"/>
-      <c r="O112" s="11"/>
-      <c r="P112" s="14"/>
-    </row>
-    <row r="113" spans="2:16">
+      <c r="N112" s="4"/>
+      <c r="S112" s="13"/>
+      <c r="T112" s="11"/>
+      <c r="U112" s="14"/>
+    </row>
+    <row r="113" spans="2:21">
       <c r="B113" s="11"/>
       <c r="C113" s="11"/>
       <c r="E113" s="12"/>
-      <c r="L113" s="4"/>
       <c r="M113" s="4"/>
-      <c r="N113" s="13"/>
-      <c r="O113" s="11"/>
-      <c r="P113" s="14"/>
-    </row>
-    <row r="114" spans="2:16">
+      <c r="N113" s="4"/>
+      <c r="S113" s="13"/>
+      <c r="T113" s="11"/>
+      <c r="U113" s="14"/>
+    </row>
+    <row r="114" spans="2:21">
       <c r="B114" s="11"/>
       <c r="C114" s="11"/>
       <c r="E114" s="12"/>
-      <c r="L114" s="4"/>
       <c r="M114" s="4"/>
-      <c r="N114" s="13"/>
-      <c r="O114" s="11"/>
-      <c r="P114" s="14"/>
-    </row>
-    <row r="115" spans="2:16">
+      <c r="N114" s="4"/>
+      <c r="S114" s="13"/>
+      <c r="T114" s="11"/>
+      <c r="U114" s="14"/>
+    </row>
+    <row r="115" spans="2:21">
       <c r="B115" s="11"/>
       <c r="C115" s="11"/>
       <c r="E115" s="12"/>
-      <c r="L115" s="4"/>
       <c r="M115" s="4"/>
-      <c r="N115" s="13"/>
-      <c r="O115" s="11"/>
-      <c r="P115" s="14"/>
-    </row>
-    <row r="116" spans="2:16">
+      <c r="N115" s="4"/>
+      <c r="S115" s="13"/>
+      <c r="T115" s="11"/>
+      <c r="U115" s="14"/>
+    </row>
+    <row r="116" spans="2:21">
       <c r="B116" s="11"/>
       <c r="C116" s="11"/>
       <c r="E116" s="12"/>
-      <c r="L116" s="4"/>
       <c r="M116" s="4"/>
-      <c r="N116" s="13"/>
-      <c r="O116" s="11"/>
-      <c r="P116" s="14"/>
-    </row>
-    <row r="117" spans="2:16">
+      <c r="N116" s="4"/>
+      <c r="S116" s="13"/>
+      <c r="T116" s="11"/>
+      <c r="U116" s="14"/>
+    </row>
+    <row r="117" spans="2:21">
       <c r="B117" s="11"/>
       <c r="C117" s="11"/>
       <c r="E117" s="12"/>
-      <c r="L117" s="4"/>
       <c r="M117" s="4"/>
-      <c r="N117" s="13"/>
-      <c r="O117" s="11"/>
-      <c r="P117" s="14"/>
-    </row>
-    <row r="118" spans="2:16">
+      <c r="N117" s="4"/>
+      <c r="S117" s="13"/>
+      <c r="T117" s="11"/>
+      <c r="U117" s="14"/>
+    </row>
+    <row r="118" spans="2:21">
       <c r="B118" s="11"/>
       <c r="C118" s="11"/>
       <c r="E118" s="12"/>
-      <c r="L118" s="4"/>
       <c r="M118" s="4"/>
-      <c r="N118" s="13"/>
-      <c r="O118" s="11"/>
-      <c r="P118" s="14"/>
-    </row>
-    <row r="119" spans="2:16">
+      <c r="N118" s="4"/>
+      <c r="S118" s="13"/>
+      <c r="T118" s="11"/>
+      <c r="U118" s="14"/>
+    </row>
+    <row r="119" spans="2:21">
       <c r="B119" s="11"/>
       <c r="C119" s="11"/>
       <c r="E119" s="12"/>
-      <c r="L119" s="4"/>
       <c r="M119" s="4"/>
-      <c r="N119" s="13"/>
-      <c r="O119" s="11"/>
-      <c r="P119" s="14"/>
-    </row>
-    <row r="120" spans="2:16">
+      <c r="N119" s="4"/>
+      <c r="S119" s="13"/>
+      <c r="T119" s="11"/>
+      <c r="U119" s="14"/>
+    </row>
+    <row r="120" spans="2:21">
       <c r="B120" s="11"/>
       <c r="C120" s="11"/>
       <c r="E120" s="12"/>
-      <c r="L120" s="4"/>
       <c r="M120" s="4"/>
-      <c r="N120" s="13"/>
-      <c r="O120" s="11"/>
-      <c r="P120" s="14"/>
-    </row>
-    <row r="121" spans="2:16">
+      <c r="N120" s="4"/>
+      <c r="S120" s="13"/>
+      <c r="T120" s="11"/>
+      <c r="U120" s="14"/>
+    </row>
+    <row r="121" spans="2:21">
       <c r="B121" s="11"/>
       <c r="C121" s="11"/>
       <c r="E121" s="12"/>
-      <c r="L121" s="4"/>
       <c r="M121" s="4"/>
-      <c r="N121" s="13"/>
-      <c r="O121" s="11"/>
-      <c r="P121" s="14"/>
-    </row>
-    <row r="122" spans="2:16">
+      <c r="N121" s="4"/>
+      <c r="S121" s="13"/>
+      <c r="T121" s="11"/>
+      <c r="U121" s="14"/>
+    </row>
+    <row r="122" spans="2:21">
       <c r="B122" s="11"/>
       <c r="C122" s="11"/>
       <c r="E122" s="12"/>
-      <c r="L122" s="4"/>
       <c r="M122" s="4"/>
-      <c r="N122" s="13"/>
-      <c r="O122" s="11"/>
-      <c r="P122" s="14"/>
-    </row>
-    <row r="123" spans="2:16">
+      <c r="N122" s="4"/>
+      <c r="S122" s="13"/>
+      <c r="T122" s="11"/>
+      <c r="U122" s="14"/>
+    </row>
+    <row r="123" spans="2:21">
       <c r="B123" s="11"/>
       <c r="C123" s="11"/>
       <c r="E123" s="12"/>
-      <c r="L123" s="4"/>
       <c r="M123" s="4"/>
-      <c r="N123" s="13"/>
-      <c r="O123" s="11"/>
-      <c r="P123" s="14"/>
-    </row>
-    <row r="124" spans="2:16">
+      <c r="N123" s="4"/>
+      <c r="S123" s="13"/>
+      <c r="T123" s="11"/>
+      <c r="U123" s="14"/>
+    </row>
+    <row r="124" spans="2:21">
       <c r="B124" s="11"/>
       <c r="C124" s="11"/>
       <c r="E124" s="12"/>
-      <c r="L124" s="4"/>
       <c r="M124" s="4"/>
-      <c r="N124" s="13"/>
-      <c r="O124" s="11"/>
-      <c r="P124" s="14"/>
-    </row>
-    <row r="125" spans="2:16">
+      <c r="N124" s="4"/>
+      <c r="S124" s="13"/>
+      <c r="T124" s="11"/>
+      <c r="U124" s="14"/>
+    </row>
+    <row r="125" spans="2:21">
       <c r="B125" s="11"/>
       <c r="C125" s="11"/>
       <c r="E125" s="12"/>
-      <c r="L125" s="4"/>
       <c r="M125" s="4"/>
-      <c r="N125" s="13"/>
-      <c r="O125" s="11"/>
-      <c r="P125" s="14"/>
-    </row>
-    <row r="126" spans="2:16">
+      <c r="N125" s="4"/>
+      <c r="S125" s="13"/>
+      <c r="T125" s="11"/>
+      <c r="U125" s="14"/>
+    </row>
+    <row r="126" spans="2:21">
       <c r="B126" s="11"/>
       <c r="C126" s="11"/>
       <c r="E126" s="12"/>
-      <c r="L126" s="4"/>
       <c r="M126" s="4"/>
-      <c r="N126" s="13"/>
-      <c r="O126" s="11"/>
-      <c r="P126" s="14"/>
-    </row>
-    <row r="127" spans="2:16">
+      <c r="N126" s="4"/>
+      <c r="S126" s="13"/>
+      <c r="T126" s="11"/>
+      <c r="U126" s="14"/>
+    </row>
+    <row r="127" spans="2:21">
       <c r="B127" s="11"/>
       <c r="C127" s="11"/>
       <c r="E127" s="12"/>
-      <c r="L127" s="4"/>
       <c r="M127" s="4"/>
-      <c r="N127" s="13"/>
-      <c r="O127" s="11"/>
-      <c r="P127" s="14"/>
-    </row>
-    <row r="128" spans="2:16">
+      <c r="N127" s="4"/>
+      <c r="S127" s="13"/>
+      <c r="T127" s="11"/>
+      <c r="U127" s="14"/>
+    </row>
+    <row r="128" spans="2:21">
       <c r="B128" s="11"/>
       <c r="C128" s="11"/>
       <c r="E128" s="12"/>
-      <c r="L128" s="4"/>
       <c r="M128" s="4"/>
-      <c r="N128" s="13"/>
-      <c r="O128" s="11"/>
-      <c r="P128" s="14"/>
-    </row>
-    <row r="129" spans="2:16">
+      <c r="N128" s="4"/>
+      <c r="S128" s="13"/>
+      <c r="T128" s="11"/>
+      <c r="U128" s="14"/>
+    </row>
+    <row r="129" spans="2:21">
       <c r="B129" s="11"/>
       <c r="C129" s="11"/>
       <c r="E129" s="12"/>
-      <c r="L129" s="4"/>
       <c r="M129" s="4"/>
-      <c r="N129" s="13"/>
-      <c r="O129" s="11"/>
-      <c r="P129" s="14"/>
-    </row>
-    <row r="130" spans="2:16">
+      <c r="N129" s="4"/>
+      <c r="S129" s="13"/>
+      <c r="T129" s="11"/>
+      <c r="U129" s="14"/>
+    </row>
+    <row r="130" spans="2:21">
       <c r="B130" s="11"/>
       <c r="C130" s="11"/>
       <c r="E130" s="12"/>
-      <c r="L130" s="4"/>
       <c r="M130" s="4"/>
-      <c r="N130" s="13"/>
-      <c r="O130" s="11"/>
-      <c r="P130" s="14"/>
-    </row>
-    <row r="131" spans="2:16">
+      <c r="N130" s="4"/>
+      <c r="S130" s="13"/>
+      <c r="T130" s="11"/>
+      <c r="U130" s="14"/>
+    </row>
+    <row r="131" spans="2:21">
       <c r="B131" s="11"/>
       <c r="C131" s="11"/>
       <c r="E131" s="12"/>
-      <c r="L131" s="4"/>
       <c r="M131" s="4"/>
-      <c r="N131" s="13"/>
-      <c r="O131" s="11"/>
-      <c r="P131" s="14"/>
-    </row>
-    <row r="132" spans="2:16">
+      <c r="N131" s="4"/>
+      <c r="S131" s="13"/>
+      <c r="T131" s="11"/>
+      <c r="U131" s="14"/>
+    </row>
+    <row r="132" spans="2:21">
       <c r="B132" s="11"/>
       <c r="C132" s="11"/>
       <c r="E132" s="12"/>
-      <c r="L132" s="4"/>
       <c r="M132" s="4"/>
-      <c r="N132" s="13"/>
-      <c r="O132" s="11"/>
-      <c r="P132" s="14"/>
-    </row>
-    <row r="133" spans="2:16">
+      <c r="N132" s="4"/>
+      <c r="S132" s="13"/>
+      <c r="T132" s="11"/>
+      <c r="U132" s="14"/>
+    </row>
+    <row r="133" spans="2:21">
       <c r="B133" s="11"/>
       <c r="C133" s="11"/>
       <c r="E133" s="12"/>
-      <c r="L133" s="4"/>
       <c r="M133" s="4"/>
-      <c r="N133" s="13"/>
-      <c r="O133" s="11"/>
-      <c r="P133" s="14"/>
-    </row>
-    <row r="134" spans="2:16">
+      <c r="N133" s="4"/>
+      <c r="S133" s="13"/>
+      <c r="T133" s="11"/>
+      <c r="U133" s="14"/>
+    </row>
+    <row r="134" spans="2:21">
       <c r="B134" s="11"/>
       <c r="C134" s="11"/>
       <c r="E134" s="12"/>
-      <c r="L134" s="4"/>
       <c r="M134" s="4"/>
-      <c r="N134" s="13"/>
-      <c r="O134" s="11"/>
-      <c r="P134" s="14"/>
-    </row>
-    <row r="135" spans="2:16">
+      <c r="N134" s="4"/>
+      <c r="S134" s="13"/>
+      <c r="T134" s="11"/>
+      <c r="U134" s="14"/>
+    </row>
+    <row r="135" spans="2:21">
       <c r="B135" s="11"/>
       <c r="C135" s="11"/>
       <c r="E135" s="12"/>
-      <c r="L135" s="4"/>
       <c r="M135" s="4"/>
-      <c r="N135" s="13"/>
-      <c r="O135" s="11"/>
-      <c r="P135" s="14"/>
-    </row>
-    <row r="136" spans="2:16">
+      <c r="N135" s="4"/>
+      <c r="S135" s="13"/>
+      <c r="T135" s="11"/>
+      <c r="U135" s="14"/>
+    </row>
+    <row r="136" spans="2:21">
       <c r="B136" s="11"/>
       <c r="C136" s="11"/>
       <c r="E136" s="12"/>
-      <c r="L136" s="4"/>
       <c r="M136" s="4"/>
-      <c r="N136" s="13"/>
-      <c r="O136" s="11"/>
-      <c r="P136" s="14"/>
-    </row>
-    <row r="137" spans="2:16">
+      <c r="N136" s="4"/>
+      <c r="S136" s="13"/>
+      <c r="T136" s="11"/>
+      <c r="U136" s="14"/>
+    </row>
+    <row r="137" spans="2:21">
       <c r="B137" s="11"/>
       <c r="C137" s="11"/>
       <c r="E137" s="12"/>
-      <c r="L137" s="4"/>
       <c r="M137" s="4"/>
-      <c r="N137" s="13"/>
-      <c r="O137" s="11"/>
-      <c r="P137" s="14"/>
-    </row>
-    <row r="138" spans="2:16">
+      <c r="N137" s="4"/>
+      <c r="S137" s="13"/>
+      <c r="T137" s="11"/>
+      <c r="U137" s="14"/>
+    </row>
+    <row r="138" spans="2:21">
       <c r="B138" s="11"/>
       <c r="C138" s="11"/>
       <c r="E138" s="12"/>
-      <c r="L138" s="4"/>
       <c r="M138" s="4"/>
-      <c r="N138" s="13"/>
-      <c r="O138" s="11"/>
-      <c r="P138" s="14"/>
-    </row>
-    <row r="139" spans="2:16">
+      <c r="N138" s="4"/>
+      <c r="S138" s="13"/>
+      <c r="T138" s="11"/>
+      <c r="U138" s="14"/>
+    </row>
+    <row r="139" spans="2:21">
       <c r="B139" s="11"/>
       <c r="C139" s="11"/>
       <c r="E139" s="12"/>
-      <c r="L139" s="4"/>
       <c r="M139" s="4"/>
-      <c r="N139" s="13"/>
-      <c r="O139" s="11"/>
-      <c r="P139" s="14"/>
-    </row>
-    <row r="140" spans="2:16">
+      <c r="N139" s="4"/>
+      <c r="S139" s="13"/>
+      <c r="T139" s="11"/>
+      <c r="U139" s="14"/>
+    </row>
+    <row r="140" spans="2:21">
       <c r="B140" s="11"/>
       <c r="C140" s="11"/>
       <c r="E140" s="12"/>
-      <c r="L140" s="4"/>
       <c r="M140" s="4"/>
-      <c r="N140" s="13"/>
-      <c r="O140" s="11"/>
-      <c r="P140" s="14"/>
-    </row>
-    <row r="141" spans="2:16">
+      <c r="N140" s="4"/>
+      <c r="S140" s="13"/>
+      <c r="T140" s="11"/>
+      <c r="U140" s="14"/>
+    </row>
+    <row r="141" spans="2:21">
       <c r="B141" s="11"/>
       <c r="C141" s="11"/>
       <c r="E141" s="12"/>
-      <c r="L141" s="4"/>
       <c r="M141" s="4"/>
-      <c r="N141" s="13"/>
-      <c r="O141" s="11"/>
-      <c r="P141" s="14"/>
-    </row>
-    <row r="142" spans="2:16">
+      <c r="N141" s="4"/>
+      <c r="S141" s="13"/>
+      <c r="T141" s="11"/>
+      <c r="U141" s="14"/>
+    </row>
+    <row r="142" spans="2:21">
       <c r="B142" s="11"/>
       <c r="C142" s="11"/>
       <c r="E142" s="12"/>
-      <c r="L142" s="4"/>
       <c r="M142" s="4"/>
-      <c r="N142" s="13"/>
-      <c r="O142" s="11"/>
-      <c r="P142" s="14"/>
-    </row>
-    <row r="143" spans="2:16">
+      <c r="N142" s="4"/>
+      <c r="S142" s="13"/>
+      <c r="T142" s="11"/>
+      <c r="U142" s="14"/>
+    </row>
+    <row r="143" spans="2:21">
       <c r="B143" s="11"/>
       <c r="C143" s="11"/>
       <c r="E143" s="12"/>
-      <c r="L143" s="4"/>
       <c r="M143" s="4"/>
-      <c r="N143" s="13"/>
-      <c r="O143" s="11"/>
-      <c r="P143" s="14"/>
-    </row>
-    <row r="144" spans="2:16">
+      <c r="N143" s="4"/>
+      <c r="S143" s="13"/>
+      <c r="T143" s="11"/>
+      <c r="U143" s="14"/>
+    </row>
+    <row r="144" spans="2:21">
       <c r="B144" s="11"/>
       <c r="C144" s="11"/>
       <c r="E144" s="12"/>
-      <c r="L144" s="4"/>
       <c r="M144" s="4"/>
-      <c r="N144" s="13"/>
-      <c r="O144" s="11"/>
-      <c r="P144" s="14"/>
-    </row>
-    <row r="145" spans="2:16">
+      <c r="N144" s="4"/>
+      <c r="S144" s="13"/>
+      <c r="T144" s="11"/>
+      <c r="U144" s="14"/>
+    </row>
+    <row r="145" spans="2:21">
       <c r="B145" s="11"/>
       <c r="C145" s="11"/>
       <c r="E145" s="12"/>
-      <c r="L145" s="4"/>
       <c r="M145" s="4"/>
-      <c r="N145" s="13"/>
-      <c r="O145" s="11"/>
-      <c r="P145" s="14"/>
-    </row>
-    <row r="146" spans="2:16">
+      <c r="N145" s="4"/>
+      <c r="S145" s="13"/>
+      <c r="T145" s="11"/>
+      <c r="U145" s="14"/>
+    </row>
+    <row r="146" spans="2:21">
       <c r="B146" s="11"/>
       <c r="C146" s="11"/>
       <c r="E146" s="12"/>
-      <c r="L146" s="4"/>
       <c r="M146" s="4"/>
-      <c r="N146" s="13"/>
-      <c r="O146" s="11"/>
-      <c r="P146" s="14"/>
-    </row>
-    <row r="147" spans="2:16">
+      <c r="N146" s="4"/>
+      <c r="S146" s="13"/>
+      <c r="T146" s="11"/>
+      <c r="U146" s="14"/>
+    </row>
+    <row r="147" spans="2:21">
       <c r="B147" s="11"/>
       <c r="C147" s="11"/>
       <c r="E147" s="12"/>
-      <c r="L147" s="4"/>
       <c r="M147" s="4"/>
-      <c r="N147" s="13"/>
-      <c r="O147" s="11"/>
-      <c r="P147" s="14"/>
-    </row>
-    <row r="148" spans="2:16">
+      <c r="N147" s="4"/>
+      <c r="S147" s="13"/>
+      <c r="T147" s="11"/>
+      <c r="U147" s="14"/>
+    </row>
+    <row r="148" spans="2:21">
       <c r="B148" s="11"/>
       <c r="C148" s="11"/>
       <c r="E148" s="12"/>
-      <c r="L148" s="4"/>
       <c r="M148" s="4"/>
-      <c r="N148" s="13"/>
-      <c r="O148" s="11"/>
-      <c r="P148" s="14"/>
-    </row>
-    <row r="149" spans="2:16">
+      <c r="N148" s="4"/>
+      <c r="S148" s="13"/>
+      <c r="T148" s="11"/>
+      <c r="U148" s="14"/>
+    </row>
+    <row r="149" spans="2:21">
       <c r="B149" s="11"/>
       <c r="C149" s="11"/>
       <c r="E149" s="12"/>
-      <c r="L149" s="4"/>
       <c r="M149" s="4"/>
-      <c r="N149" s="13"/>
-      <c r="O149" s="11"/>
-      <c r="P149" s="14"/>
-    </row>
-    <row r="150" spans="2:16">
+      <c r="N149" s="4"/>
+      <c r="S149" s="13"/>
+      <c r="T149" s="11"/>
+      <c r="U149" s="14"/>
+    </row>
+    <row r="150" spans="2:21">
       <c r="B150" s="11"/>
       <c r="C150" s="11"/>
       <c r="E150" s="12"/>
-      <c r="L150" s="4"/>
       <c r="M150" s="4"/>
-      <c r="N150" s="13"/>
-      <c r="O150" s="11"/>
-      <c r="P150" s="14"/>
-    </row>
-    <row r="151" spans="2:16">
+      <c r="N150" s="4"/>
+      <c r="S150" s="13"/>
+      <c r="T150" s="11"/>
+      <c r="U150" s="14"/>
+    </row>
+    <row r="151" spans="2:21">
       <c r="B151" s="11"/>
       <c r="C151" s="11"/>
       <c r="E151" s="12"/>
-      <c r="L151" s="4"/>
       <c r="M151" s="4"/>
-      <c r="N151" s="13"/>
-      <c r="O151" s="11"/>
-      <c r="P151" s="14"/>
-    </row>
-    <row r="152" spans="2:16">
+      <c r="N151" s="4"/>
+      <c r="S151" s="13"/>
+      <c r="T151" s="11"/>
+      <c r="U151" s="14"/>
+    </row>
+    <row r="152" spans="2:21">
       <c r="B152" s="11"/>
       <c r="C152" s="11"/>
       <c r="E152" s="12"/>
-      <c r="L152" s="4"/>
       <c r="M152" s="4"/>
-      <c r="N152" s="13"/>
-      <c r="O152" s="11"/>
-      <c r="P152" s="14"/>
-    </row>
-    <row r="153" spans="2:16">
+      <c r="N152" s="4"/>
+      <c r="S152" s="13"/>
+      <c r="T152" s="11"/>
+      <c r="U152" s="14"/>
+    </row>
+    <row r="153" spans="2:21">
       <c r="B153" s="11"/>
       <c r="C153" s="11"/>
       <c r="E153" s="12"/>
-      <c r="L153" s="4"/>
       <c r="M153" s="4"/>
-      <c r="N153" s="13"/>
-      <c r="O153" s="11"/>
-      <c r="P153" s="14"/>
-    </row>
-    <row r="154" spans="2:16">
+      <c r="N153" s="4"/>
+      <c r="S153" s="13"/>
+      <c r="T153" s="11"/>
+      <c r="U153" s="14"/>
+    </row>
+    <row r="154" spans="2:21">
       <c r="B154" s="11"/>
       <c r="C154" s="11"/>
       <c r="E154" s="12"/>
-      <c r="L154" s="4"/>
       <c r="M154" s="4"/>
-      <c r="N154" s="13"/>
-      <c r="O154" s="11"/>
-      <c r="P154" s="14"/>
-    </row>
-    <row r="155" spans="2:16">
+      <c r="N154" s="4"/>
+      <c r="S154" s="13"/>
+      <c r="T154" s="11"/>
+      <c r="U154" s="14"/>
+    </row>
+    <row r="155" spans="2:21">
       <c r="B155" s="11"/>
       <c r="C155" s="11"/>
       <c r="E155" s="12"/>
-      <c r="L155" s="4"/>
       <c r="M155" s="4"/>
-      <c r="N155" s="13"/>
-      <c r="O155" s="11"/>
-      <c r="P155" s="14"/>
-    </row>
-    <row r="156" spans="2:16">
+      <c r="N155" s="4"/>
+      <c r="S155" s="13"/>
+      <c r="T155" s="11"/>
+      <c r="U155" s="14"/>
+    </row>
+    <row r="156" spans="2:21">
       <c r="B156" s="11"/>
       <c r="C156" s="11"/>
       <c r="E156" s="12"/>
-      <c r="L156" s="4"/>
       <c r="M156" s="4"/>
-      <c r="N156" s="13"/>
-      <c r="O156" s="11"/>
-      <c r="P156" s="14"/>
-    </row>
-    <row r="157" spans="2:16">
+      <c r="N156" s="4"/>
+      <c r="S156" s="13"/>
+      <c r="T156" s="11"/>
+      <c r="U156" s="14"/>
+    </row>
+    <row r="157" spans="2:21">
       <c r="B157" s="11"/>
       <c r="C157" s="11"/>
       <c r="E157" s="12"/>
-      <c r="L157" s="4"/>
       <c r="M157" s="4"/>
-      <c r="N157" s="13"/>
-      <c r="O157" s="11"/>
-      <c r="P157" s="14"/>
-    </row>
-    <row r="158" spans="2:16">
+      <c r="N157" s="4"/>
+      <c r="S157" s="13"/>
+      <c r="T157" s="11"/>
+      <c r="U157" s="14"/>
+    </row>
+    <row r="158" spans="2:21">
       <c r="B158" s="11"/>
       <c r="C158" s="11"/>
       <c r="E158" s="12"/>
-      <c r="L158" s="4"/>
       <c r="M158" s="4"/>
-      <c r="N158" s="13"/>
-      <c r="O158" s="11"/>
-      <c r="P158" s="14"/>
-    </row>
-    <row r="159" spans="2:16">
-      <c r="N159" s="17"/>
-    </row>
-    <row r="160" spans="2:16">
-      <c r="N160" s="17"/>
-    </row>
-    <row r="161" spans="14:14">
-      <c r="N161" s="17"/>
-    </row>
-    <row r="162" spans="14:14">
-      <c r="N162" s="17"/>
-    </row>
-    <row r="163" spans="14:14">
-      <c r="N163" s="17"/>
-    </row>
-    <row r="164" spans="14:14">
-      <c r="N164" s="17"/>
-    </row>
-    <row r="165" spans="14:14">
-      <c r="N165" s="17"/>
-    </row>
-    <row r="166" spans="14:14">
-      <c r="N166" s="17"/>
-    </row>
-    <row r="167" spans="14:14">
-      <c r="N167" s="17"/>
-    </row>
-    <row r="168" spans="14:14">
-      <c r="N168" s="17"/>
-    </row>
-    <row r="169" spans="14:14">
-      <c r="N169" s="17"/>
-    </row>
-    <row r="170" spans="14:14">
-      <c r="N170" s="17"/>
-    </row>
-    <row r="171" spans="14:14">
-      <c r="N171" s="17"/>
-    </row>
-    <row r="172" spans="14:14">
-      <c r="N172" s="17"/>
-    </row>
-    <row r="173" spans="14:14">
-      <c r="N173" s="17"/>
-    </row>
-    <row r="174" spans="14:14">
-      <c r="N174" s="17"/>
-    </row>
-    <row r="175" spans="14:14">
-      <c r="N175" s="17"/>
-    </row>
-    <row r="176" spans="14:14">
-      <c r="N176" s="17"/>
-    </row>
-    <row r="177" spans="14:14">
-      <c r="N177" s="17"/>
-    </row>
-    <row r="178" spans="14:14">
-      <c r="N178" s="17"/>
-    </row>
-    <row r="179" spans="14:14">
-      <c r="N179" s="17"/>
-    </row>
-    <row r="180" spans="14:14">
-      <c r="N180" s="17"/>
-    </row>
-    <row r="181" spans="14:14">
-      <c r="N181" s="17"/>
-    </row>
-    <row r="182" spans="14:14">
-      <c r="N182" s="17"/>
-    </row>
-    <row r="183" spans="14:14">
-      <c r="N183" s="17"/>
-    </row>
-    <row r="184" spans="14:14">
-      <c r="N184" s="17"/>
-    </row>
-    <row r="185" spans="14:14">
-      <c r="N185" s="17"/>
-    </row>
-    <row r="186" spans="14:14">
-      <c r="N186" s="17"/>
-    </row>
-    <row r="187" spans="14:14">
-      <c r="N187" s="17"/>
-    </row>
-    <row r="188" spans="14:14">
-      <c r="N188" s="17"/>
-    </row>
-    <row r="189" spans="14:14">
-      <c r="N189" s="17"/>
-    </row>
-    <row r="190" spans="14:14">
-      <c r="N190" s="17"/>
-    </row>
-    <row r="191" spans="14:14">
-      <c r="N191" s="17"/>
-    </row>
-    <row r="192" spans="14:14">
-      <c r="N192" s="17"/>
-    </row>
-    <row r="193" spans="14:14">
-      <c r="N193" s="17"/>
-    </row>
-    <row r="194" spans="14:14">
-      <c r="N194" s="17"/>
-    </row>
-    <row r="195" spans="14:14">
-      <c r="N195" s="17"/>
-    </row>
-    <row r="196" spans="14:14">
-      <c r="N196" s="17"/>
-    </row>
-    <row r="197" spans="14:14">
-      <c r="N197" s="17"/>
-    </row>
-    <row r="198" spans="14:14">
-      <c r="N198" s="17"/>
-    </row>
-    <row r="199" spans="14:14">
-      <c r="N199" s="17"/>
-    </row>
-    <row r="200" spans="14:14">
-      <c r="N200" s="17"/>
-    </row>
-    <row r="201" spans="14:14">
-      <c r="N201" s="17"/>
-    </row>
-    <row r="202" spans="14:14">
-      <c r="N202" s="17"/>
-    </row>
-    <row r="203" spans="14:14">
-      <c r="N203" s="17"/>
-    </row>
-    <row r="204" spans="14:14">
-      <c r="N204" s="17"/>
-    </row>
-    <row r="205" spans="14:14">
-      <c r="N205" s="17"/>
-    </row>
-    <row r="206" spans="14:14">
-      <c r="N206" s="17"/>
-    </row>
-    <row r="207" spans="14:14">
-      <c r="N207" s="17"/>
-    </row>
-    <row r="208" spans="14:14">
-      <c r="N208" s="17"/>
-    </row>
-    <row r="209" spans="14:14">
-      <c r="N209" s="17"/>
-    </row>
-    <row r="210" spans="14:14">
-      <c r="N210" s="17"/>
-    </row>
-    <row r="211" spans="14:14">
-      <c r="N211" s="17"/>
-    </row>
-    <row r="212" spans="14:14">
-      <c r="N212" s="17"/>
-    </row>
-    <row r="213" spans="14:14">
-      <c r="N213" s="17"/>
-    </row>
-    <row r="214" spans="14:14">
-      <c r="N214" s="17"/>
-    </row>
-    <row r="215" spans="14:14">
-      <c r="N215" s="17"/>
-    </row>
-    <row r="216" spans="14:14">
-      <c r="N216" s="17"/>
-    </row>
-    <row r="217" spans="14:14">
-      <c r="N217" s="17"/>
-    </row>
-    <row r="218" spans="14:14">
-      <c r="N218" s="17"/>
-    </row>
-    <row r="219" spans="14:14">
-      <c r="N219" s="17"/>
-    </row>
-    <row r="220" spans="14:14">
-      <c r="N220" s="17"/>
-    </row>
-    <row r="221" spans="14:14">
-      <c r="N221" s="17"/>
-    </row>
-    <row r="222" spans="14:14">
-      <c r="N222" s="17"/>
-    </row>
-    <row r="223" spans="14:14">
-      <c r="N223" s="17"/>
-    </row>
-    <row r="224" spans="14:14">
-      <c r="N224" s="17"/>
-    </row>
-    <row r="225" spans="14:14">
-      <c r="N225" s="17"/>
-    </row>
-    <row r="226" spans="14:14">
-      <c r="N226" s="17"/>
-    </row>
-    <row r="227" spans="14:14">
-      <c r="N227" s="17"/>
-    </row>
-    <row r="228" spans="14:14">
-      <c r="N228" s="17"/>
-    </row>
-    <row r="229" spans="14:14">
-      <c r="N229" s="17"/>
-    </row>
-    <row r="230" spans="14:14">
-      <c r="N230" s="17"/>
-    </row>
-    <row r="231" spans="14:14">
-      <c r="N231" s="17"/>
-    </row>
-    <row r="232" spans="14:14">
-      <c r="N232" s="17"/>
-    </row>
-    <row r="233" spans="14:14">
-      <c r="N233" s="17"/>
-    </row>
-    <row r="234" spans="14:14">
-      <c r="N234" s="17"/>
-    </row>
-    <row r="235" spans="14:14">
-      <c r="N235" s="17"/>
-    </row>
-    <row r="236" spans="14:14">
-      <c r="N236" s="17"/>
-    </row>
-    <row r="237" spans="14:14">
-      <c r="N237" s="17"/>
-    </row>
-    <row r="238" spans="14:14">
-      <c r="N238" s="17"/>
-    </row>
-    <row r="239" spans="14:14">
-      <c r="N239" s="17"/>
-    </row>
-    <row r="240" spans="14:14">
-      <c r="N240" s="17"/>
-    </row>
-    <row r="241" spans="14:14">
-      <c r="N241" s="17"/>
-    </row>
-    <row r="242" spans="14:14">
-      <c r="N242" s="17"/>
-    </row>
-    <row r="243" spans="14:14">
-      <c r="N243" s="17"/>
-    </row>
-    <row r="244" spans="14:14">
-      <c r="N244" s="17"/>
-    </row>
-    <row r="245" spans="14:14">
-      <c r="N245" s="17"/>
-    </row>
-    <row r="246" spans="14:14">
-      <c r="N246" s="17"/>
-    </row>
-    <row r="247" spans="14:14">
-      <c r="N247" s="17"/>
-    </row>
-    <row r="248" spans="14:14">
-      <c r="N248" s="17"/>
-    </row>
-    <row r="249" spans="14:14">
-      <c r="N249" s="17"/>
-    </row>
-    <row r="250" spans="14:14">
-      <c r="N250" s="17"/>
-    </row>
-    <row r="251" spans="14:14">
-      <c r="N251" s="17"/>
-    </row>
-    <row r="252" spans="14:14">
-      <c r="N252" s="17"/>
-    </row>
-    <row r="253" spans="14:14">
-      <c r="N253" s="17"/>
-    </row>
-    <row r="254" spans="14:14">
-      <c r="N254" s="17"/>
-    </row>
-    <row r="255" spans="14:14">
-      <c r="N255" s="17"/>
-    </row>
-    <row r="256" spans="14:14">
-      <c r="N256" s="17"/>
-    </row>
-    <row r="257" spans="14:14">
-      <c r="N257" s="17"/>
-    </row>
-    <row r="258" spans="14:14">
-      <c r="N258" s="17"/>
-    </row>
-    <row r="259" spans="14:14">
-      <c r="N259" s="17"/>
-    </row>
-    <row r="260" spans="14:14">
-      <c r="N260" s="17"/>
-    </row>
-    <row r="261" spans="14:14">
-      <c r="N261" s="17"/>
-    </row>
-    <row r="262" spans="14:14">
-      <c r="N262" s="17"/>
-    </row>
-    <row r="263" spans="14:14">
-      <c r="N263" s="17"/>
-    </row>
-    <row r="264" spans="14:14">
-      <c r="N264" s="17"/>
-    </row>
-    <row r="265" spans="14:14">
-      <c r="N265" s="17"/>
-    </row>
-    <row r="266" spans="14:14">
-      <c r="N266" s="17"/>
-    </row>
-    <row r="267" spans="14:14">
-      <c r="N267" s="17"/>
-    </row>
-    <row r="268" spans="14:14">
-      <c r="N268" s="17"/>
-    </row>
-    <row r="269" spans="14:14">
-      <c r="N269" s="17"/>
-    </row>
-    <row r="270" spans="14:14">
-      <c r="N270" s="17"/>
-    </row>
-    <row r="271" spans="14:14">
-      <c r="N271" s="17"/>
-    </row>
-    <row r="272" spans="14:14">
-      <c r="N272" s="17"/>
-    </row>
-    <row r="273" spans="14:14">
-      <c r="N273" s="17"/>
-    </row>
-    <row r="274" spans="14:14">
-      <c r="N274" s="17"/>
-    </row>
-    <row r="275" spans="14:14">
-      <c r="N275" s="17"/>
-    </row>
-    <row r="276" spans="14:14">
-      <c r="N276" s="17"/>
-    </row>
-    <row r="277" spans="14:14">
-      <c r="N277" s="17"/>
-    </row>
-    <row r="278" spans="14:14">
-      <c r="N278" s="17"/>
-    </row>
-    <row r="279" spans="14:14">
-      <c r="N279" s="17"/>
-    </row>
-    <row r="280" spans="14:14">
-      <c r="N280" s="17"/>
-    </row>
-    <row r="281" spans="14:14">
-      <c r="N281" s="17"/>
-    </row>
-    <row r="282" spans="14:14">
-      <c r="N282" s="17"/>
-    </row>
-    <row r="283" spans="14:14">
-      <c r="N283" s="17"/>
-    </row>
-    <row r="284" spans="14:14">
-      <c r="N284" s="17"/>
-    </row>
-    <row r="285" spans="14:14">
-      <c r="N285" s="17"/>
-    </row>
-    <row r="286" spans="14:14">
-      <c r="N286" s="17"/>
-    </row>
-    <row r="287" spans="14:14">
-      <c r="N287" s="17"/>
-    </row>
-    <row r="288" spans="14:14">
-      <c r="N288" s="17"/>
-    </row>
-    <row r="289" spans="14:14">
-      <c r="N289" s="17"/>
-    </row>
-    <row r="290" spans="14:14">
-      <c r="N290" s="17"/>
-    </row>
-    <row r="291" spans="14:14">
-      <c r="N291" s="17"/>
-    </row>
-    <row r="292" spans="14:14">
-      <c r="N292" s="17"/>
-    </row>
-    <row r="293" spans="14:14">
-      <c r="N293" s="17"/>
-    </row>
-    <row r="294" spans="14:14">
-      <c r="N294" s="17"/>
-    </row>
-    <row r="295" spans="14:14">
-      <c r="N295" s="17"/>
-    </row>
-    <row r="296" spans="14:14">
-      <c r="N296" s="17"/>
-    </row>
-    <row r="297" spans="14:14">
-      <c r="N297" s="17"/>
-    </row>
-    <row r="298" spans="14:14">
-      <c r="N298" s="17"/>
-    </row>
-    <row r="299" spans="14:14">
-      <c r="N299" s="17"/>
-    </row>
-    <row r="300" spans="14:14">
-      <c r="N300" s="17"/>
-    </row>
-    <row r="301" spans="14:14">
-      <c r="N301" s="17"/>
-    </row>
-    <row r="302" spans="14:14">
-      <c r="N302" s="17"/>
-    </row>
-    <row r="303" spans="14:14">
-      <c r="N303" s="17"/>
-    </row>
-    <row r="304" spans="14:14">
-      <c r="N304" s="17"/>
-    </row>
-    <row r="305" spans="14:14">
-      <c r="N305" s="17"/>
-    </row>
-    <row r="306" spans="14:14">
-      <c r="N306" s="17"/>
-    </row>
-    <row r="307" spans="14:14">
-      <c r="N307" s="17"/>
-    </row>
-    <row r="308" spans="14:14">
-      <c r="N308" s="17"/>
-    </row>
-    <row r="309" spans="14:14">
-      <c r="N309" s="17"/>
-    </row>
-    <row r="310" spans="14:14">
-      <c r="N310" s="17"/>
-    </row>
-    <row r="311" spans="14:14">
-      <c r="N311" s="17"/>
-    </row>
-    <row r="312" spans="14:14">
-      <c r="N312" s="17"/>
-    </row>
-    <row r="313" spans="14:14">
-      <c r="N313" s="17"/>
-    </row>
-    <row r="314" spans="14:14">
-      <c r="N314" s="17"/>
-    </row>
-    <row r="315" spans="14:14">
-      <c r="N315" s="17"/>
-    </row>
-    <row r="316" spans="14:14">
-      <c r="N316" s="17"/>
-    </row>
-    <row r="317" spans="14:14">
-      <c r="N317" s="17"/>
-    </row>
-    <row r="318" spans="14:14">
-      <c r="N318" s="17"/>
-    </row>
-    <row r="319" spans="14:14">
-      <c r="N319" s="17"/>
-    </row>
-    <row r="320" spans="14:14">
-      <c r="N320" s="17"/>
-    </row>
-    <row r="321" spans="14:14">
-      <c r="N321" s="17"/>
-    </row>
-    <row r="322" spans="14:14">
-      <c r="N322" s="17"/>
-    </row>
-    <row r="323" spans="14:14">
-      <c r="N323" s="17"/>
-    </row>
-    <row r="324" spans="14:14">
-      <c r="N324" s="17"/>
-    </row>
-    <row r="325" spans="14:14">
-      <c r="N325" s="17"/>
-    </row>
-    <row r="326" spans="14:14">
-      <c r="N326" s="17"/>
-    </row>
-    <row r="327" spans="14:14">
-      <c r="N327" s="17"/>
-    </row>
-    <row r="328" spans="14:14">
-      <c r="N328" s="17"/>
-    </row>
-    <row r="329" spans="14:14">
-      <c r="N329" s="17"/>
-    </row>
-    <row r="330" spans="14:14">
-      <c r="N330" s="17"/>
-    </row>
-    <row r="331" spans="14:14">
-      <c r="N331" s="17"/>
-    </row>
-    <row r="332" spans="14:14">
-      <c r="N332" s="17"/>
-    </row>
-    <row r="333" spans="14:14">
-      <c r="N333" s="17"/>
-    </row>
-    <row r="334" spans="14:14">
-      <c r="N334" s="17"/>
-    </row>
-    <row r="335" spans="14:14">
-      <c r="N335" s="17"/>
-    </row>
-    <row r="336" spans="14:14">
-      <c r="N336" s="17"/>
-    </row>
-    <row r="337" spans="14:14">
-      <c r="N337" s="17"/>
-    </row>
-    <row r="338" spans="14:14">
-      <c r="N338" s="17"/>
-    </row>
-    <row r="339" spans="14:14">
-      <c r="N339" s="17"/>
-    </row>
-    <row r="340" spans="14:14">
-      <c r="N340" s="17"/>
-    </row>
-    <row r="341" spans="14:14">
-      <c r="N341" s="17"/>
-    </row>
-    <row r="342" spans="14:14">
-      <c r="N342" s="17"/>
-    </row>
-    <row r="343" spans="14:14">
-      <c r="N343" s="17"/>
-    </row>
-    <row r="344" spans="14:14">
-      <c r="N344" s="17"/>
-    </row>
-    <row r="345" spans="14:14">
-      <c r="N345" s="17"/>
-    </row>
-    <row r="346" spans="14:14">
-      <c r="N346" s="17"/>
-    </row>
-    <row r="347" spans="14:14">
-      <c r="N347" s="17"/>
-    </row>
-    <row r="348" spans="14:14">
-      <c r="N348" s="17"/>
-    </row>
-    <row r="349" spans="14:14">
-      <c r="N349" s="17"/>
-    </row>
-    <row r="350" spans="14:14">
-      <c r="N350" s="17"/>
-    </row>
-    <row r="351" spans="14:14">
-      <c r="N351" s="17"/>
-    </row>
-    <row r="352" spans="14:14">
-      <c r="N352" s="17"/>
-    </row>
-    <row r="353" spans="14:14">
-      <c r="N353" s="17"/>
-    </row>
-    <row r="354" spans="14:14">
-      <c r="N354" s="17"/>
-    </row>
-    <row r="355" spans="14:14">
-      <c r="N355" s="17"/>
-    </row>
-    <row r="356" spans="14:14">
-      <c r="N356" s="17"/>
-    </row>
-    <row r="357" spans="14:14">
-      <c r="N357" s="17"/>
-    </row>
-    <row r="358" spans="14:14">
-      <c r="N358" s="17"/>
+      <c r="N158" s="4"/>
+      <c r="S158" s="13"/>
+      <c r="T158" s="11"/>
+      <c r="U158" s="14"/>
+    </row>
+    <row r="159" spans="2:21">
+      <c r="S159" s="17"/>
+    </row>
+    <row r="160" spans="2:21">
+      <c r="S160" s="17"/>
+    </row>
+    <row r="161" spans="19:19">
+      <c r="S161" s="17"/>
+    </row>
+    <row r="162" spans="19:19">
+      <c r="S162" s="17"/>
+    </row>
+    <row r="163" spans="19:19">
+      <c r="S163" s="17"/>
+    </row>
+    <row r="164" spans="19:19">
+      <c r="S164" s="17"/>
+    </row>
+    <row r="165" spans="19:19">
+      <c r="S165" s="17"/>
+    </row>
+    <row r="166" spans="19:19">
+      <c r="S166" s="17"/>
+    </row>
+    <row r="167" spans="19:19">
+      <c r="S167" s="17"/>
+    </row>
+    <row r="168" spans="19:19">
+      <c r="S168" s="17"/>
+    </row>
+    <row r="169" spans="19:19">
+      <c r="S169" s="17"/>
+    </row>
+    <row r="170" spans="19:19">
+      <c r="S170" s="17"/>
+    </row>
+    <row r="171" spans="19:19">
+      <c r="S171" s="17"/>
+    </row>
+    <row r="172" spans="19:19">
+      <c r="S172" s="17"/>
+    </row>
+    <row r="173" spans="19:19">
+      <c r="S173" s="17"/>
+    </row>
+    <row r="174" spans="19:19">
+      <c r="S174" s="17"/>
+    </row>
+    <row r="175" spans="19:19">
+      <c r="S175" s="17"/>
+    </row>
+    <row r="176" spans="19:19">
+      <c r="S176" s="17"/>
+    </row>
+    <row r="177" spans="19:19">
+      <c r="S177" s="17"/>
+    </row>
+    <row r="178" spans="19:19">
+      <c r="S178" s="17"/>
+    </row>
+    <row r="179" spans="19:19">
+      <c r="S179" s="17"/>
+    </row>
+    <row r="180" spans="19:19">
+      <c r="S180" s="17"/>
+    </row>
+    <row r="181" spans="19:19">
+      <c r="S181" s="17"/>
+    </row>
+    <row r="182" spans="19:19">
+      <c r="S182" s="17"/>
+    </row>
+    <row r="183" spans="19:19">
+      <c r="S183" s="17"/>
+    </row>
+    <row r="184" spans="19:19">
+      <c r="S184" s="17"/>
+    </row>
+    <row r="185" spans="19:19">
+      <c r="S185" s="17"/>
+    </row>
+    <row r="186" spans="19:19">
+      <c r="S186" s="17"/>
+    </row>
+    <row r="187" spans="19:19">
+      <c r="S187" s="17"/>
+    </row>
+    <row r="188" spans="19:19">
+      <c r="S188" s="17"/>
+    </row>
+    <row r="189" spans="19:19">
+      <c r="S189" s="17"/>
+    </row>
+    <row r="190" spans="19:19">
+      <c r="S190" s="17"/>
+    </row>
+    <row r="191" spans="19:19">
+      <c r="S191" s="17"/>
+    </row>
+    <row r="192" spans="19:19">
+      <c r="S192" s="17"/>
+    </row>
+    <row r="193" spans="19:19">
+      <c r="S193" s="17"/>
+    </row>
+    <row r="194" spans="19:19">
+      <c r="S194" s="17"/>
+    </row>
+    <row r="195" spans="19:19">
+      <c r="S195" s="17"/>
+    </row>
+    <row r="196" spans="19:19">
+      <c r="S196" s="17"/>
+    </row>
+    <row r="197" spans="19:19">
+      <c r="S197" s="17"/>
+    </row>
+    <row r="198" spans="19:19">
+      <c r="S198" s="17"/>
+    </row>
+    <row r="199" spans="19:19">
+      <c r="S199" s="17"/>
+    </row>
+    <row r="200" spans="19:19">
+      <c r="S200" s="17"/>
+    </row>
+    <row r="201" spans="19:19">
+      <c r="S201" s="17"/>
+    </row>
+    <row r="202" spans="19:19">
+      <c r="S202" s="17"/>
+    </row>
+    <row r="203" spans="19:19">
+      <c r="S203" s="17"/>
+    </row>
+    <row r="204" spans="19:19">
+      <c r="S204" s="17"/>
+    </row>
+    <row r="205" spans="19:19">
+      <c r="S205" s="17"/>
+    </row>
+    <row r="206" spans="19:19">
+      <c r="S206" s="17"/>
+    </row>
+    <row r="207" spans="19:19">
+      <c r="S207" s="17"/>
+    </row>
+    <row r="208" spans="19:19">
+      <c r="S208" s="17"/>
+    </row>
+    <row r="209" spans="19:19">
+      <c r="S209" s="17"/>
+    </row>
+    <row r="210" spans="19:19">
+      <c r="S210" s="17"/>
+    </row>
+    <row r="211" spans="19:19">
+      <c r="S211" s="17"/>
+    </row>
+    <row r="212" spans="19:19">
+      <c r="S212" s="17"/>
+    </row>
+    <row r="213" spans="19:19">
+      <c r="S213" s="17"/>
+    </row>
+    <row r="214" spans="19:19">
+      <c r="S214" s="17"/>
+    </row>
+    <row r="215" spans="19:19">
+      <c r="S215" s="17"/>
+    </row>
+    <row r="216" spans="19:19">
+      <c r="S216" s="17"/>
+    </row>
+    <row r="217" spans="19:19">
+      <c r="S217" s="17"/>
+    </row>
+    <row r="218" spans="19:19">
+      <c r="S218" s="17"/>
+    </row>
+    <row r="219" spans="19:19">
+      <c r="S219" s="17"/>
+    </row>
+    <row r="220" spans="19:19">
+      <c r="S220" s="17"/>
+    </row>
+    <row r="221" spans="19:19">
+      <c r="S221" s="17"/>
+    </row>
+    <row r="222" spans="19:19">
+      <c r="S222" s="17"/>
+    </row>
+    <row r="223" spans="19:19">
+      <c r="S223" s="17"/>
+    </row>
+    <row r="224" spans="19:19">
+      <c r="S224" s="17"/>
+    </row>
+    <row r="225" spans="19:19">
+      <c r="S225" s="17"/>
+    </row>
+    <row r="226" spans="19:19">
+      <c r="S226" s="17"/>
+    </row>
+    <row r="227" spans="19:19">
+      <c r="S227" s="17"/>
+    </row>
+    <row r="228" spans="19:19">
+      <c r="S228" s="17"/>
+    </row>
+    <row r="229" spans="19:19">
+      <c r="S229" s="17"/>
+    </row>
+    <row r="230" spans="19:19">
+      <c r="S230" s="17"/>
+    </row>
+    <row r="231" spans="19:19">
+      <c r="S231" s="17"/>
+    </row>
+    <row r="232" spans="19:19">
+      <c r="S232" s="17"/>
+    </row>
+    <row r="233" spans="19:19">
+      <c r="S233" s="17"/>
+    </row>
+    <row r="234" spans="19:19">
+      <c r="S234" s="17"/>
+    </row>
+    <row r="235" spans="19:19">
+      <c r="S235" s="17"/>
+    </row>
+    <row r="236" spans="19:19">
+      <c r="S236" s="17"/>
+    </row>
+    <row r="237" spans="19:19">
+      <c r="S237" s="17"/>
+    </row>
+    <row r="238" spans="19:19">
+      <c r="S238" s="17"/>
+    </row>
+    <row r="239" spans="19:19">
+      <c r="S239" s="17"/>
+    </row>
+    <row r="240" spans="19:19">
+      <c r="S240" s="17"/>
+    </row>
+    <row r="241" spans="19:19">
+      <c r="S241" s="17"/>
+    </row>
+    <row r="242" spans="19:19">
+      <c r="S242" s="17"/>
+    </row>
+    <row r="243" spans="19:19">
+      <c r="S243" s="17"/>
+    </row>
+    <row r="244" spans="19:19">
+      <c r="S244" s="17"/>
+    </row>
+    <row r="245" spans="19:19">
+      <c r="S245" s="17"/>
+    </row>
+    <row r="246" spans="19:19">
+      <c r="S246" s="17"/>
+    </row>
+    <row r="247" spans="19:19">
+      <c r="S247" s="17"/>
+    </row>
+    <row r="248" spans="19:19">
+      <c r="S248" s="17"/>
+    </row>
+    <row r="249" spans="19:19">
+      <c r="S249" s="17"/>
+    </row>
+    <row r="250" spans="19:19">
+      <c r="S250" s="17"/>
+    </row>
+    <row r="251" spans="19:19">
+      <c r="S251" s="17"/>
+    </row>
+    <row r="252" spans="19:19">
+      <c r="S252" s="17"/>
+    </row>
+    <row r="253" spans="19:19">
+      <c r="S253" s="17"/>
+    </row>
+    <row r="254" spans="19:19">
+      <c r="S254" s="17"/>
+    </row>
+    <row r="255" spans="19:19">
+      <c r="S255" s="17"/>
+    </row>
+    <row r="256" spans="19:19">
+      <c r="S256" s="17"/>
+    </row>
+    <row r="257" spans="19:19">
+      <c r="S257" s="17"/>
+    </row>
+    <row r="258" spans="19:19">
+      <c r="S258" s="17"/>
+    </row>
+    <row r="259" spans="19:19">
+      <c r="S259" s="17"/>
+    </row>
+    <row r="260" spans="19:19">
+      <c r="S260" s="17"/>
+    </row>
+    <row r="261" spans="19:19">
+      <c r="S261" s="17"/>
+    </row>
+    <row r="262" spans="19:19">
+      <c r="S262" s="17"/>
+    </row>
+    <row r="263" spans="19:19">
+      <c r="S263" s="17"/>
+    </row>
+    <row r="264" spans="19:19">
+      <c r="S264" s="17"/>
+    </row>
+    <row r="265" spans="19:19">
+      <c r="S265" s="17"/>
+    </row>
+    <row r="266" spans="19:19">
+      <c r="S266" s="17"/>
+    </row>
+    <row r="267" spans="19:19">
+      <c r="S267" s="17"/>
+    </row>
+    <row r="268" spans="19:19">
+      <c r="S268" s="17"/>
+    </row>
+    <row r="269" spans="19:19">
+      <c r="S269" s="17"/>
+    </row>
+    <row r="270" spans="19:19">
+      <c r="S270" s="17"/>
+    </row>
+    <row r="271" spans="19:19">
+      <c r="S271" s="17"/>
+    </row>
+    <row r="272" spans="19:19">
+      <c r="S272" s="17"/>
+    </row>
+    <row r="273" spans="19:19">
+      <c r="S273" s="17"/>
+    </row>
+    <row r="274" spans="19:19">
+      <c r="S274" s="17"/>
+    </row>
+    <row r="275" spans="19:19">
+      <c r="S275" s="17"/>
+    </row>
+    <row r="276" spans="19:19">
+      <c r="S276" s="17"/>
+    </row>
+    <row r="277" spans="19:19">
+      <c r="S277" s="17"/>
+    </row>
+    <row r="278" spans="19:19">
+      <c r="S278" s="17"/>
+    </row>
+    <row r="279" spans="19:19">
+      <c r="S279" s="17"/>
+    </row>
+    <row r="280" spans="19:19">
+      <c r="S280" s="17"/>
+    </row>
+    <row r="281" spans="19:19">
+      <c r="S281" s="17"/>
+    </row>
+    <row r="282" spans="19:19">
+      <c r="S282" s="17"/>
+    </row>
+    <row r="283" spans="19:19">
+      <c r="S283" s="17"/>
+    </row>
+    <row r="284" spans="19:19">
+      <c r="S284" s="17"/>
+    </row>
+    <row r="285" spans="19:19">
+      <c r="S285" s="17"/>
+    </row>
+    <row r="286" spans="19:19">
+      <c r="S286" s="17"/>
+    </row>
+    <row r="287" spans="19:19">
+      <c r="S287" s="17"/>
+    </row>
+    <row r="288" spans="19:19">
+      <c r="S288" s="17"/>
+    </row>
+    <row r="289" spans="19:19">
+      <c r="S289" s="17"/>
+    </row>
+    <row r="290" spans="19:19">
+      <c r="S290" s="17"/>
+    </row>
+    <row r="291" spans="19:19">
+      <c r="S291" s="17"/>
+    </row>
+    <row r="292" spans="19:19">
+      <c r="S292" s="17"/>
+    </row>
+    <row r="293" spans="19:19">
+      <c r="S293" s="17"/>
+    </row>
+    <row r="294" spans="19:19">
+      <c r="S294" s="17"/>
+    </row>
+    <row r="295" spans="19:19">
+      <c r="S295" s="17"/>
+    </row>
+    <row r="296" spans="19:19">
+      <c r="S296" s="17"/>
+    </row>
+    <row r="297" spans="19:19">
+      <c r="S297" s="17"/>
+    </row>
+    <row r="298" spans="19:19">
+      <c r="S298" s="17"/>
+    </row>
+    <row r="299" spans="19:19">
+      <c r="S299" s="17"/>
+    </row>
+    <row r="300" spans="19:19">
+      <c r="S300" s="17"/>
+    </row>
+    <row r="301" spans="19:19">
+      <c r="S301" s="17"/>
+    </row>
+    <row r="302" spans="19:19">
+      <c r="S302" s="17"/>
+    </row>
+    <row r="303" spans="19:19">
+      <c r="S303" s="17"/>
+    </row>
+    <row r="304" spans="19:19">
+      <c r="S304" s="17"/>
+    </row>
+    <row r="305" spans="19:19">
+      <c r="S305" s="17"/>
+    </row>
+    <row r="306" spans="19:19">
+      <c r="S306" s="17"/>
+    </row>
+    <row r="307" spans="19:19">
+      <c r="S307" s="17"/>
+    </row>
+    <row r="308" spans="19:19">
+      <c r="S308" s="17"/>
+    </row>
+    <row r="309" spans="19:19">
+      <c r="S309" s="17"/>
+    </row>
+    <row r="310" spans="19:19">
+      <c r="S310" s="17"/>
+    </row>
+    <row r="311" spans="19:19">
+      <c r="S311" s="17"/>
+    </row>
+    <row r="312" spans="19:19">
+      <c r="S312" s="17"/>
+    </row>
+    <row r="313" spans="19:19">
+      <c r="S313" s="17"/>
+    </row>
+    <row r="314" spans="19:19">
+      <c r="S314" s="17"/>
+    </row>
+    <row r="315" spans="19:19">
+      <c r="S315" s="17"/>
+    </row>
+    <row r="316" spans="19:19">
+      <c r="S316" s="17"/>
+    </row>
+    <row r="317" spans="19:19">
+      <c r="S317" s="17"/>
+    </row>
+    <row r="318" spans="19:19">
+      <c r="S318" s="17"/>
+    </row>
+    <row r="319" spans="19:19">
+      <c r="S319" s="17"/>
+    </row>
+    <row r="320" spans="19:19">
+      <c r="S320" s="17"/>
+    </row>
+    <row r="321" spans="19:19">
+      <c r="S321" s="17"/>
+    </row>
+    <row r="322" spans="19:19">
+      <c r="S322" s="17"/>
+    </row>
+    <row r="323" spans="19:19">
+      <c r="S323" s="17"/>
+    </row>
+    <row r="324" spans="19:19">
+      <c r="S324" s="17"/>
+    </row>
+    <row r="325" spans="19:19">
+      <c r="S325" s="17"/>
+    </row>
+    <row r="326" spans="19:19">
+      <c r="S326" s="17"/>
+    </row>
+    <row r="327" spans="19:19">
+      <c r="S327" s="17"/>
+    </row>
+    <row r="328" spans="19:19">
+      <c r="S328" s="17"/>
+    </row>
+    <row r="329" spans="19:19">
+      <c r="S329" s="17"/>
+    </row>
+    <row r="330" spans="19:19">
+      <c r="S330" s="17"/>
+    </row>
+    <row r="331" spans="19:19">
+      <c r="S331" s="17"/>
+    </row>
+    <row r="332" spans="19:19">
+      <c r="S332" s="17"/>
+    </row>
+    <row r="333" spans="19:19">
+      <c r="S333" s="17"/>
+    </row>
+    <row r="334" spans="19:19">
+      <c r="S334" s="17"/>
+    </row>
+    <row r="335" spans="19:19">
+      <c r="S335" s="17"/>
+    </row>
+    <row r="336" spans="19:19">
+      <c r="S336" s="17"/>
+    </row>
+    <row r="337" spans="19:19">
+      <c r="S337" s="17"/>
+    </row>
+    <row r="338" spans="19:19">
+      <c r="S338" s="17"/>
+    </row>
+    <row r="339" spans="19:19">
+      <c r="S339" s="17"/>
+    </row>
+    <row r="340" spans="19:19">
+      <c r="S340" s="17"/>
+    </row>
+    <row r="341" spans="19:19">
+      <c r="S341" s="17"/>
+    </row>
+    <row r="342" spans="19:19">
+      <c r="S342" s="17"/>
+    </row>
+    <row r="343" spans="19:19">
+      <c r="S343" s="17"/>
+    </row>
+    <row r="344" spans="19:19">
+      <c r="S344" s="17"/>
+    </row>
+    <row r="345" spans="19:19">
+      <c r="S345" s="17"/>
+    </row>
+    <row r="346" spans="19:19">
+      <c r="S346" s="17"/>
+    </row>
+    <row r="347" spans="19:19">
+      <c r="S347" s="17"/>
+    </row>
+    <row r="348" spans="19:19">
+      <c r="S348" s="17"/>
+    </row>
+    <row r="349" spans="19:19">
+      <c r="S349" s="17"/>
+    </row>
+    <row r="350" spans="19:19">
+      <c r="S350" s="17"/>
+    </row>
+    <row r="351" spans="19:19">
+      <c r="S351" s="17"/>
+    </row>
+    <row r="352" spans="19:19">
+      <c r="S352" s="17"/>
+    </row>
+    <row r="353" spans="19:19">
+      <c r="S353" s="17"/>
+    </row>
+    <row r="354" spans="19:19">
+      <c r="S354" s="17"/>
+    </row>
+    <row r="355" spans="19:19">
+      <c r="S355" s="17"/>
+    </row>
+    <row r="356" spans="19:19">
+      <c r="S356" s="17"/>
+    </row>
+    <row r="357" spans="19:19">
+      <c r="S357" s="17"/>
+    </row>
+    <row r="358" spans="19:19">
+      <c r="S358" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="N1:Q1"/>
+  <mergeCells count="6">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="S1:V1"/>
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="G1:I1"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="O1:R1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6361,24 +6407,24 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D81F047E-EC38-4C3A-BA81-E6C9549453D6}">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.59765625" style="66" customWidth="1"/>
     <col min="2" max="2" width="16.59765625" style="66" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9.06640625" style="66"/>
     <col min="5" max="6" width="15.59765625" style="66" customWidth="1"/>
-    <col min="7" max="7" width="9.9296875" style="66" customWidth="1"/>
-    <col min="8" max="16384" width="9.06640625" style="66"/>
+    <col min="7" max="8" width="9.9296875" style="66" customWidth="1"/>
+    <col min="9" max="16384" width="9.06640625" style="66"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13.15">
+    <row r="1" spans="1:8" ht="13.15">
       <c r="A1" s="64"/>
       <c r="B1" s="65" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="29.65" customHeight="1">
+    <row r="2" spans="1:8" ht="29.65" customHeight="1">
       <c r="B2" s="67" t="s">
         <v>3</v>
       </c>
@@ -6392,13 +6438,16 @@
         <v>227</v>
       </c>
       <c r="F2" s="67" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G2" s="67" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>264</v>
+      </c>
+      <c r="H2" s="67" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="B3" s="78" t="s">
         <v>30</v>
       </c>
@@ -6416,409 +6465,264 @@
       </c>
       <c r="G3" s="74">
         <f>F3/$F$9</f>
-        <v>0.43175061871716075</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>0.40627734298520357</v>
+      </c>
+      <c r="H3" s="92" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="B4" s="79" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="71">
-        <v>16.54</v>
-      </c>
-      <c r="D4" s="68" t="s">
-        <v>230</v>
+      <c r="C4" s="76">
+        <f>VLOOKUP(B4,Opportunities!B$3:E$12,3,FALSE)</f>
+        <v>16.440000000000001</v>
+      </c>
+      <c r="D4" s="75" t="str">
+        <f>VLOOKUP(B4,Opportunities!B$3:E$12,4,FALSE)</f>
+        <v>HKD</v>
       </c>
       <c r="E4" s="72">
         <v>10000</v>
       </c>
       <c r="F4" s="77">
         <f>C4*E4</f>
-        <v>165400</v>
+        <v>164400</v>
       </c>
       <c r="G4" s="74">
         <f>F4/$F$9</f>
-        <v>0.2032226592232948</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>0.19007634525088124</v>
+      </c>
+      <c r="H4" s="74">
+        <f>VLOOKUP(B4,Opportunities!B$3:I$12,8,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="B5" s="79" t="s">
         <v>231</v>
       </c>
-      <c r="C5" s="71">
-        <v>7.4</v>
-      </c>
-      <c r="D5" s="68" t="s">
-        <v>230</v>
+      <c r="C5" s="76">
+        <f>VLOOKUP(B5,Opportunities!B$3:E$12,3,FALSE)</f>
+        <v>7.85</v>
+      </c>
+      <c r="D5" s="75" t="str">
+        <f>VLOOKUP(B5,Opportunities!B$3:E$12,4,FALSE)</f>
+        <v>HKD</v>
       </c>
       <c r="E5" s="72">
         <v>20000</v>
       </c>
       <c r="F5" s="77">
         <f>E5*C5</f>
-        <v>148000</v>
+        <v>157000</v>
       </c>
       <c r="G5" s="74">
         <f>F5/$F$9</f>
-        <v>0.18184373376691432</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>0.18152059735029413</v>
+      </c>
+      <c r="H5" s="74">
+        <f>VLOOKUP(B5,Opportunities!B$3:I$12,8,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="B6" s="79" t="s">
-        <v>244</v>
-      </c>
-      <c r="C6" s="71">
-        <v>5.37</v>
-      </c>
-      <c r="D6" s="68" t="s">
-        <v>230</v>
+        <v>243</v>
+      </c>
+      <c r="C6" s="76">
+        <f>VLOOKUP(B6,Opportunities!B$3:E$12,3,FALSE)</f>
+        <v>5.8</v>
+      </c>
+      <c r="D6" s="75" t="str">
+        <f>VLOOKUP(B6,Opportunities!B$3:E$12,4,FALSE)</f>
+        <v>HKD</v>
       </c>
       <c r="E6" s="72">
         <v>18000</v>
       </c>
       <c r="F6" s="77">
         <f>E6*C6</f>
-        <v>96660</v>
+        <v>104400</v>
       </c>
       <c r="G6" s="74">
         <f>F6/$F$9</f>
-        <v>0.11876361693182391</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>0.12070541632720196</v>
+      </c>
+      <c r="H6" s="74">
+        <f>VLOOKUP(B6,Opportunities!B$3:I$12,8,FALSE)</f>
+        <v>0.21411471166966861</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="B7" s="79" t="s">
-        <v>260</v>
-      </c>
-      <c r="C7" s="71">
-        <v>14.98</v>
-      </c>
-      <c r="D7" s="68" t="s">
-        <v>160</v>
+        <v>258</v>
+      </c>
+      <c r="C7" s="76">
+        <f>VLOOKUP(B7,Opportunities!B$3:E$12,3,FALSE)</f>
+        <v>14.62</v>
+      </c>
+      <c r="D7" s="75" t="str">
+        <f>VLOOKUP(B7,Opportunities!B$3:E$12,4,FALSE)</f>
+        <v>HKD</v>
       </c>
       <c r="E7" s="72">
-        <f>500*7</f>
-        <v>3500</v>
+        <v>6000</v>
       </c>
       <c r="F7" s="77">
         <f>C7*E7</f>
-        <v>52430</v>
+        <v>87720</v>
       </c>
       <c r="G7" s="74">
         <f>F7/$F$9</f>
-        <v>6.4419371360806207E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>0.10142029808641911</v>
+      </c>
+      <c r="H7" s="74">
+        <f>VLOOKUP(B7,Opportunities!B$3:I$12,8,FALSE)</f>
+        <v>0.26604528758285023</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="B8" s="68"/>
       <c r="C8" s="71"/>
       <c r="D8" s="68"/>
-    </row>
-    <row r="9" spans="1:7" ht="13.15">
+      <c r="H8" s="91"/>
+    </row>
+    <row r="9" spans="1:8" ht="13.15">
       <c r="B9" s="80"/>
       <c r="C9" s="81"/>
       <c r="D9" s="80"/>
       <c r="E9" s="82" t="s">
-        <v>234</v>
+        <v>263</v>
       </c>
       <c r="F9" s="82">
         <f>SUM(F3:F7)</f>
-        <v>813885.62</v>
+        <v>864915.62</v>
       </c>
       <c r="G9" s="83">
         <f>SUM(G3:G7)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="H9" s="90">
+        <f>SUM(H4:H7)</f>
+        <v>0.48015999925251884</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="B10" s="68"/>
       <c r="C10" s="71"/>
       <c r="D10" s="68"/>
       <c r="E10" s="72"/>
       <c r="F10" s="72"/>
     </row>
-    <row r="11" spans="1:7" ht="13.15">
+    <row r="11" spans="1:8" ht="13.15">
       <c r="A11" s="64"/>
       <c r="B11" s="65" t="s">
-        <v>263</v>
-      </c>
-      <c r="C11" s="71"/>
-      <c r="D11" s="68"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="B12" s="78" t="s">
-        <v>264</v>
-      </c>
-      <c r="C12" s="76" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="B12" s="79" t="s">
+        <v>258</v>
+      </c>
+      <c r="C12" s="76">
+        <f>VLOOKUP(B12,Opportunities!B$3:E$12,3,FALSE)</f>
+        <v>14.62</v>
+      </c>
+      <c r="D12" s="75" t="str">
+        <f>VLOOKUP(B12,Opportunities!B$3:E$12,4,FALSE)</f>
+        <v>HKD</v>
+      </c>
+      <c r="E12" s="72">
+        <v>4000</v>
+      </c>
+      <c r="F12" s="77">
+        <f>C12*E12</f>
+        <v>58480</v>
+      </c>
+      <c r="G12" s="74">
+        <f>F12/$F$9</f>
+        <v>6.7613532057612738E-2</v>
+      </c>
+      <c r="H12" s="74">
+        <f>VLOOKUP(B12,Opportunities!B$3:I$12,8,FALSE)</f>
+        <v>0.26604528758285023</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="G13" s="89"/>
+      <c r="H13" s="89"/>
+    </row>
+    <row r="14" spans="1:8" ht="13.15">
+      <c r="B14" s="84" t="s">
+        <v>261</v>
+      </c>
+      <c r="C14" s="85" t="s">
         <v>233</v>
       </c>
-      <c r="D12" s="75" t="s">
+      <c r="D14" s="86" t="s">
         <v>160</v>
       </c>
-      <c r="E12" s="76" t="s">
+      <c r="E14" s="85" t="s">
         <v>233</v>
       </c>
-      <c r="F12" s="77">
-        <f>F3</f>
-        <v>351395.62</v>
-      </c>
-      <c r="G12" s="74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="B13" s="79" t="s">
-        <v>260</v>
-      </c>
-      <c r="C13" s="71">
-        <v>14.9</v>
-      </c>
-      <c r="D13" s="68" t="s">
-        <v>160</v>
-      </c>
-      <c r="E13" s="72">
-        <v>8000</v>
-      </c>
-      <c r="F13" s="77">
-        <f>C13*E13</f>
-        <v>119200</v>
-      </c>
-      <c r="G13" s="74">
-        <f>F13/$F$12</f>
-        <v>0.3392187984585579</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="B14" s="79"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="68"/>
-      <c r="E14" s="72"/>
-      <c r="F14" s="72"/>
-    </row>
-    <row r="15" spans="1:7" ht="13.15">
-      <c r="B15" s="84" t="s">
-        <v>265</v>
-      </c>
-      <c r="C15" s="85" t="s">
-        <v>233</v>
-      </c>
-      <c r="D15" s="86" t="s">
-        <v>160</v>
-      </c>
-      <c r="E15" s="85" t="s">
-        <v>233</v>
-      </c>
-      <c r="F15" s="82">
-        <f>F12-F13</f>
-        <v>232195.62</v>
-      </c>
-      <c r="G15" s="83">
-        <f>F15/$F$12</f>
-        <v>0.66078120154144204</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="F14" s="82">
+        <f>F3-F12</f>
+        <v>292915.62</v>
+      </c>
+      <c r="G14" s="90">
+        <f t="shared" ref="G14" si="0">F14/$F$9</f>
+        <v>0.33866381092759085</v>
+      </c>
+      <c r="H14" s="90">
+        <f>Portfolio_Mgmt!E61</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="B16" s="68"/>
       <c r="C16" s="71"/>
       <c r="D16" s="68"/>
       <c r="E16" s="72"/>
       <c r="F16" s="72"/>
     </row>
-    <row r="17" spans="1:7" ht="13.15">
-      <c r="A17" s="64"/>
-      <c r="B17" s="65" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="26.25">
-      <c r="B18" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="67" t="s">
-        <v>229</v>
-      </c>
-      <c r="D18" s="67" t="s">
-        <v>228</v>
-      </c>
-      <c r="E18" s="67" t="s">
-        <v>227</v>
-      </c>
-      <c r="F18" s="67" t="s">
-        <v>235</v>
-      </c>
-      <c r="G18" s="67" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="B19" s="78" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="76" t="s">
-        <v>233</v>
-      </c>
-      <c r="D19" s="75" t="s">
-        <v>230</v>
-      </c>
-      <c r="E19" s="77" t="s">
-        <v>233</v>
-      </c>
-      <c r="F19" s="77">
-        <f>F15</f>
-        <v>232195.62</v>
-      </c>
-      <c r="G19" s="74">
-        <f>F19/$F$9</f>
-        <v>0.28529269260218654</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="B20" s="79" t="s">
-        <v>232</v>
-      </c>
-      <c r="C20" s="71">
-        <v>16.54</v>
-      </c>
-      <c r="D20" s="68" t="s">
-        <v>230</v>
-      </c>
-      <c r="E20" s="72">
-        <v>10000</v>
-      </c>
-      <c r="F20" s="77">
-        <f>C20*E20</f>
-        <v>165400</v>
-      </c>
-      <c r="G20" s="74">
-        <f t="shared" ref="G20:G23" si="0">F20/$F$9</f>
-        <v>0.2032226592232948</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="B21" s="79" t="s">
-        <v>231</v>
-      </c>
-      <c r="C21" s="71">
-        <v>7.4</v>
-      </c>
-      <c r="D21" s="68" t="s">
-        <v>230</v>
-      </c>
-      <c r="E21" s="72">
-        <v>20000</v>
-      </c>
-      <c r="F21" s="77">
-        <f>E21*C21</f>
-        <v>148000</v>
-      </c>
-      <c r="G21" s="74">
-        <f t="shared" si="0"/>
-        <v>0.18184373376691432</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="B22" s="79" t="s">
-        <v>244</v>
-      </c>
-      <c r="C22" s="71">
-        <v>5.37</v>
-      </c>
-      <c r="D22" s="68" t="s">
-        <v>230</v>
-      </c>
-      <c r="E22" s="72">
-        <v>18000</v>
-      </c>
-      <c r="F22" s="77">
-        <f>E22*C22</f>
-        <v>96660</v>
-      </c>
-      <c r="G22" s="74">
-        <f t="shared" si="0"/>
-        <v>0.11876361693182391</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="B23" s="79" t="s">
-        <v>262</v>
-      </c>
-      <c r="C23" s="71">
-        <v>14.9</v>
-      </c>
-      <c r="D23" s="68" t="s">
-        <v>230</v>
-      </c>
-      <c r="E23" s="72">
-        <f>E7+E13</f>
-        <v>11500</v>
-      </c>
-      <c r="F23" s="77">
-        <f>E23*C23</f>
-        <v>171350</v>
-      </c>
-      <c r="G23" s="74">
-        <f t="shared" si="0"/>
-        <v>0.21053326879027548</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="B24" s="68"/>
-      <c r="C24" s="71"/>
-      <c r="D24" s="68"/>
-    </row>
-    <row r="25" spans="1:7" ht="13.15">
-      <c r="B25" s="80"/>
-      <c r="C25" s="81"/>
-      <c r="D25" s="80"/>
-      <c r="E25" s="82" t="s">
-        <v>234</v>
-      </c>
-      <c r="F25" s="82">
-        <f>SUM(F19:F23)</f>
-        <v>813605.62</v>
-      </c>
-      <c r="G25" s="83">
-        <f>SUM(G19:G23)</f>
-        <v>0.99965597131449502</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="2:6">
       <c r="B26" s="68"/>
       <c r="C26" s="71"/>
       <c r="D26" s="68"/>
       <c r="E26" s="72"/>
       <c r="F26" s="72"/>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="2:6">
       <c r="B27" s="68"/>
       <c r="C27" s="71"/>
       <c r="D27" s="68"/>
       <c r="E27" s="72"/>
       <c r="F27" s="72"/>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="2:6">
       <c r="B28" s="68"/>
       <c r="C28" s="71"/>
       <c r="D28" s="68"/>
       <c r="E28" s="72"/>
       <c r="F28" s="72"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="2:6">
       <c r="B29" s="68"/>
       <c r="C29" s="71"/>
       <c r="D29" s="68"/>
       <c r="E29" s="72"/>
       <c r="F29" s="72"/>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="2:6">
       <c r="B30" s="68"/>
       <c r="C30" s="71"/>
       <c r="D30" s="68"/>
       <c r="E30" s="72"/>
       <c r="F30" s="72"/>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="2:6">
       <c r="B31" s="68"/>
       <c r="C31" s="69"/>
       <c r="D31" s="68"/>
@@ -6856,25 +6760,25 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="B3" s="98" t="s">
+      <c r="B3" s="104" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="B5" s="99" t="s">
+      <c r="B5" s="105" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="92"/>
-      <c r="D5" s="92"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="95"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="B6" s="99" t="s">
+      <c r="B6" s="105" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="92"/>
-      <c r="D6" s="92"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">
@@ -6888,18 +6792,18 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="98" t="s">
+      <c r="B11" s="104" t="s">
         <v>109</v>
       </c>
-      <c r="C11" s="98"/>
-      <c r="D11" s="98"/>
+      <c r="C11" s="104"/>
+      <c r="D11" s="104"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="B12" s="98" t="s">
+      <c r="B12" s="104" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="98"/>
-      <c r="D12" s="98"/>
+      <c r="C12" s="104"/>
+      <c r="D12" s="104"/>
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="23" t="s">
@@ -6993,18 +6897,18 @@
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="B28" s="98" t="s">
+      <c r="B28" s="104" t="s">
         <v>122</v>
       </c>
-      <c r="C28" s="98"/>
-      <c r="D28" s="98"/>
+      <c r="C28" s="104"/>
+      <c r="D28" s="104"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="B29" s="98" t="s">
+      <c r="B29" s="104" t="s">
         <v>123</v>
       </c>
-      <c r="C29" s="98"/>
-      <c r="D29" s="98"/>
+      <c r="C29" s="104"/>
+      <c r="D29" s="104"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="5"/>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8CC7BF-2AC5-41C3-9D59-DD3D42228909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F02716-0C67-4A18-8B98-D105E3C3C862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -3186,7 +3186,7 @@
         <v>176</v>
       </c>
       <c r="C112" s="44">
-        <v>0.13023489201472013</v>
+        <v>0.12941277633765541</v>
       </c>
       <c r="D112" s="62" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
@@ -3542,7 +3542,7 @@
         <v>0.12610765378265396</v>
       </c>
       <c r="I5" s="15">
-        <v>0.11984000074748113</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2">
         <v>16.165402289394244</v>
@@ -3581,7 +3581,7 @@
         <v>45900</v>
       </c>
       <c r="V5" s="11" t="s">
-        <v>163</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3609,7 +3609,7 @@
         <v>0.11924754303551685</v>
       </c>
       <c r="I6" s="15">
-        <v>0</v>
+        <v>0.11984000074748113</v>
       </c>
       <c r="J6" s="2">
         <v>13.155317996540354</v>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="H4" s="74">
         <f>VLOOKUP(B4,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0</v>
+        <v>0.11984000074748113</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="H9" s="90">
         <f>SUM(H4:H7)</f>
-        <v>0.48015999925251884</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="10" spans="1:8">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F02716-0C67-4A18-8B98-D105E3C3C862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F306A4-887F-4A52-93C3-E0CED764DA87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -1602,31 +1602,31 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="177" formatCode="[$-13C09]d\ mmm\ yyyy;@"/>
-    <numFmt numFmtId="178" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="179" formatCode="#,##0.00_);\(#,##0.00\)"/>
-    <numFmt numFmtId="180" formatCode="#,##0_);\(#,##0\)"/>
-    <numFmt numFmtId="181" formatCode="0.0\x"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-13C09]d\ mmm\ yyyy;@"/>
+    <numFmt numFmtId="166" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00_);\(#,##0.00\)"/>
+    <numFmt numFmtId="168" formatCode="#,##0_);\(#,##0\)"/>
+    <numFmt numFmtId="169" formatCode="0.0\x"/>
   </numFmts>
   <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1661,7 +1661,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1957,7 +1957,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1969,7 +1969,7 @@
     <xf numFmtId="4" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1981,10 +1981,10 @@
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1993,7 +1993,7 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2060,7 +2060,7 @@
     <xf numFmtId="10" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2080,18 +2080,18 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="180" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="179" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
@@ -2105,16 +2105,16 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="180" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="3">
@@ -2124,10 +2124,10 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="180" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2139,23 +2139,23 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="30" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="30" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="180" fontId="31" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="31" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="179" fontId="31" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2167,7 +2167,7 @@
     <xf numFmtId="10" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3186,7 +3186,7 @@
         <v>176</v>
       </c>
       <c r="C112" s="44">
-        <v>0.12941277633765541</v>
+        <v>0.13547956846156287</v>
       </c>
       <c r="D112" s="62" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
@@ -3397,30 +3397,30 @@
         <v>160</v>
       </c>
       <c r="F3" s="15">
-        <v>0.22170440631904187</v>
+        <v>0.23821680012512947</v>
       </c>
       <c r="G3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$10</f>
-        <v>0.10430440631904186</v>
+        <v>0.12081680012512946</v>
       </c>
       <c r="H3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$11</f>
-        <v>0.18720440631904187</v>
+        <v>0.20371680012512947</v>
       </c>
       <c r="I3" s="15">
-        <v>0.26604528758285023</v>
+        <v>0.28586016015015536</v>
       </c>
       <c r="J3" s="2">
-        <v>13.677042438413375</v>
+        <v>14.221973350893821</v>
       </c>
       <c r="K3" s="2">
-        <v>24.622857747833478</v>
+        <v>25.687175936271849</v>
       </c>
       <c r="L3" s="87">
-        <v>22.308475032950721</v>
+        <v>23.032865794155285</v>
       </c>
       <c r="M3" s="4">
-        <v>6.4508135967563204E-2</v>
+        <v>6.8306347295356576E-2</v>
       </c>
       <c r="N3" s="4">
         <v>3.7498432682696467E-2</v>
@@ -3484,7 +3484,7 @@
         <v>7.9151197774737936</v>
       </c>
       <c r="L4" s="87">
-        <v>7.8850261201801173</v>
+        <v>7.8269967849264273</v>
       </c>
       <c r="M4" s="4">
         <v>0.13256816715305936</v>
@@ -3551,7 +3551,7 @@
         <v>29.309951346473134</v>
       </c>
       <c r="L5" s="87">
-        <v>26.396539978799055</v>
+        <v>26.195900228437846</v>
       </c>
       <c r="M5" s="4">
         <v>0.22703991769612522</v>
@@ -3609,7 +3609,7 @@
         <v>0.11924754303551685</v>
       </c>
       <c r="I6" s="15">
-        <v>0.11984000074748113</v>
+        <v>0.100025128180176</v>
       </c>
       <c r="J6" s="2">
         <v>13.155317996540354</v>
@@ -3618,7 +3618,7 @@
         <v>20.508980461992877</v>
       </c>
       <c r="L6" s="87">
-        <v>21.008327387940341</v>
+        <v>20.855031722489773</v>
       </c>
       <c r="M6" s="4">
         <v>0.10510863864778767</v>
@@ -3685,7 +3685,7 @@
         <v>9.1628099951889297</v>
       </c>
       <c r="L7" s="87">
-        <v>9.3117298015925627</v>
+        <v>9.2436188894094862</v>
       </c>
       <c r="M7" s="4">
         <v>3.9350111080543315E-2</v>
@@ -3752,7 +3752,7 @@
         <v>16.694869127046534</v>
       </c>
       <c r="L8" s="87">
-        <v>16.365529532356156</v>
+        <v>16.244483486621952</v>
       </c>
       <c r="M8" s="4">
         <v>0.10764138310388582</v>
@@ -3819,7 +3819,7 @@
         <v>66.921979202973944</v>
       </c>
       <c r="L9" s="87">
-        <v>62.169609540564053</v>
+        <v>61.70184092308476</v>
       </c>
       <c r="M9" s="4">
         <v>4.1491316575080373E-2</v>
@@ -3886,7 +3886,7 @@
         <v>2.697564413182195</v>
       </c>
       <c r="L10" s="87">
-        <v>2.5899220352770942</v>
+        <v>2.570640062402624</v>
       </c>
       <c r="M10" s="4">
         <v>3.573276361444476E-2</v>
@@ -3953,7 +3953,7 @@
         <v>32.464859269378167</v>
       </c>
       <c r="L11" s="87">
-        <v>31.770050813856095</v>
+        <v>31.534940982638489</v>
       </c>
       <c r="M11" s="4">
         <v>8.8134932571433455E-2</v>
@@ -4020,7 +4020,7 @@
         <v>67.988942786517455</v>
       </c>
       <c r="L12" s="87">
-        <v>57.531434982190753</v>
+        <v>57.084827396539964</v>
       </c>
       <c r="M12" s="4">
         <v>0.10069379612803481</v>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="H4" s="74">
         <f>VLOOKUP(B4,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.11984000074748113</v>
+        <v>0.100025128180176</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="H7" s="74">
         <f>VLOOKUP(B7,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.26604528758285023</v>
+        <v>0.28586016015015536</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="H12" s="74">
         <f>VLOOKUP(B12,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.26604528758285023</v>
+        <v>0.28586016015015536</v>
       </c>
     </row>
     <row r="13" spans="1:8">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F306A4-887F-4A52-93C3-E0CED764DA87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE27D8ED-A57D-416E-8D64-F5C79A1CE5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -6635,15 +6635,15 @@
         <v>HKD</v>
       </c>
       <c r="E12" s="72">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="F12" s="77">
         <f>C12*E12</f>
-        <v>58480</v>
+        <v>87720</v>
       </c>
       <c r="G12" s="74">
         <f>F12/$F$9</f>
-        <v>6.7613532057612738E-2</v>
+        <v>0.10142029808641911</v>
       </c>
       <c r="H12" s="74">
         <f>VLOOKUP(B12,Opportunities!B$3:I$12,8,FALSE)</f>
@@ -6669,11 +6669,11 @@
       </c>
       <c r="F14" s="82">
         <f>F3-F12</f>
-        <v>292915.62</v>
+        <v>263675.62</v>
       </c>
       <c r="G14" s="90">
         <f t="shared" ref="G14" si="0">F14/$F$9</f>
-        <v>0.33866381092759085</v>
+        <v>0.30485704489878446</v>
       </c>
       <c r="H14" s="90">
         <f>Portfolio_Mgmt!E61</f>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE27D8ED-A57D-416E-8D64-F5C79A1CE5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD2AB94-C53D-4179-B1D1-39EB4DF40E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3417,7 +3417,7 @@
         <v>25.687175936271849</v>
       </c>
       <c r="L3" s="87">
-        <v>23.032865794155285</v>
+        <v>21.804142810167097</v>
       </c>
       <c r="M3" s="4">
         <v>6.8306347295356576E-2</v>
@@ -3484,7 +3484,7 @@
         <v>7.9151197774737936</v>
       </c>
       <c r="L4" s="87">
-        <v>7.8269967849264273</v>
+        <v>7.4221982517030112</v>
       </c>
       <c r="M4" s="4">
         <v>0.13256816715305936</v>
@@ -3551,7 +3551,7 @@
         <v>29.309951346473134</v>
       </c>
       <c r="L5" s="87">
-        <v>26.195900228437846</v>
+        <v>24.796949133193245</v>
       </c>
       <c r="M5" s="4">
         <v>0.22703991769612522</v>
@@ -3618,7 +3618,7 @@
         <v>20.508980461992877</v>
       </c>
       <c r="L6" s="87">
-        <v>20.855031722489773</v>
+        <v>19.785541823839793</v>
       </c>
       <c r="M6" s="4">
         <v>0.10510863864778767</v>
@@ -3685,7 +3685,7 @@
         <v>9.1628099951889297</v>
       </c>
       <c r="L7" s="87">
-        <v>9.2436188894094862</v>
+        <v>8.7684502451266084</v>
       </c>
       <c r="M7" s="4">
         <v>3.9350111080543315E-2</v>
@@ -3752,7 +3752,7 @@
         <v>16.694869127046534</v>
       </c>
       <c r="L8" s="87">
-        <v>16.244483486621952</v>
+        <v>15.400158613707365</v>
       </c>
       <c r="M8" s="4">
         <v>0.10764138310388582</v>
@@ -3819,7 +3819,7 @@
         <v>66.921979202973944</v>
       </c>
       <c r="L9" s="87">
-        <v>61.70184092308476</v>
+        <v>58.439865108322181</v>
       </c>
       <c r="M9" s="4">
         <v>4.1491316575080373E-2</v>
@@ -3886,7 +3886,7 @@
         <v>2.697564413182195</v>
       </c>
       <c r="L10" s="87">
-        <v>2.570640062402624</v>
+        <v>2.4361567519866192</v>
       </c>
       <c r="M10" s="4">
         <v>3.573276361444476E-2</v>
@@ -3953,7 +3953,7 @@
         <v>32.464859269378167</v>
       </c>
       <c r="L11" s="87">
-        <v>31.534940982638489</v>
+        <v>29.895007167811503</v>
       </c>
       <c r="M11" s="4">
         <v>8.8134932571433455E-2</v>
@@ -4020,7 +4020,7 @@
         <v>67.988942786517455</v>
       </c>
       <c r="L12" s="87">
-        <v>57.084827396539964</v>
+        <v>53.971814816813243</v>
       </c>
       <c r="M12" s="4">
         <v>0.10069379612803481</v>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD2AB94-C53D-4179-B1D1-39EB4DF40E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A8239B-F695-4A37-AF78-D60A417D9716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="271">
   <si>
     <t>Name</t>
   </si>
@@ -1595,6 +1595,9 @@
   <si>
     <t>Balance Sheet Strength</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yield to open a position at</t>
   </si>
 </sst>
 </file>
@@ -2060,9 +2063,6 @@
     <xf numFmtId="10" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2168,6 +2168,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2572,7 +2575,7 @@
       <c r="B6" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="C6" s="62"/>
+      <c r="C6" s="61"/>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="94" t="s">
@@ -2665,7 +2668,7 @@
       <c r="B23" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="C23" s="62"/>
+      <c r="C23" s="61"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
@@ -2681,10 +2684,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="18"/>
-      <c r="B26" s="51" t="s">
+      <c r="B26" s="50" t="s">
         <v>154</v>
       </c>
-      <c r="C26" s="51" t="s">
+      <c r="C26" s="50" t="s">
         <v>148</v>
       </c>
     </row>
@@ -2692,7 +2695,7 @@
       <c r="B27" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="C27" s="52">
+      <c r="C27" s="51">
         <v>6</v>
       </c>
     </row>
@@ -2700,15 +2703,15 @@
       <c r="B28" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C28" s="53">
+      <c r="C28" s="52">
         <v>0.3</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="B30" s="51" t="s">
+      <c r="B30" s="50" t="s">
         <v>155</v>
       </c>
-      <c r="C30" s="51" t="s">
+      <c r="C30" s="50" t="s">
         <v>148</v>
       </c>
     </row>
@@ -2716,7 +2719,7 @@
       <c r="B31" s="26" t="s">
         <v>149</v>
       </c>
-      <c r="C31" s="60">
+      <c r="C31" s="59">
         <f>C27-C32</f>
         <v>5</v>
       </c>
@@ -2725,7 +2728,7 @@
       <c r="B32" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="C32" s="59">
+      <c r="C32" s="58">
         <v>1</v>
       </c>
     </row>
@@ -2736,7 +2739,7 @@
       <c r="B34" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C34" s="62"/>
+      <c r="C34" s="61"/>
       <c r="D34" s="22"/>
     </row>
     <row r="35" spans="1:5">
@@ -2744,12 +2747,12 @@
         <v>16</v>
       </c>
       <c r="C35" s="48">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D35" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="E35" s="50">
+      <c r="E35" s="93">
         <v>3</v>
       </c>
     </row>
@@ -2760,6 +2763,12 @@
       <c r="C36" s="49">
         <f>MAX(8%,Market_Yield!C4:D6)</f>
         <v>0.08</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E36" s="48">
+        <v>0.2</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2806,14 +2815,14 @@
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="B48" s="51" t="s">
+      <c r="B48" s="50" t="s">
         <v>93</v>
       </c>
-      <c r="C48" s="51" t="s">
+      <c r="C48" s="50" t="s">
         <v>199</v>
       </c>
-      <c r="D48" s="57"/>
-      <c r="E48" s="57"/>
+      <c r="D48" s="56"/>
+      <c r="E48" s="56"/>
     </row>
     <row r="49" spans="2:5">
       <c r="B49" s="26" t="s">
@@ -2822,8 +2831,8 @@
       <c r="C49" s="29">
         <v>0.6</v>
       </c>
-      <c r="D49" s="58"/>
-      <c r="E49" s="56"/>
+      <c r="D49" s="57"/>
+      <c r="E49" s="55"/>
     </row>
     <row r="50" spans="2:5">
       <c r="B50" s="26" t="s">
@@ -2832,8 +2841,8 @@
       <c r="C50" s="29">
         <v>0.4</v>
       </c>
-      <c r="D50" s="58"/>
-      <c r="E50" s="56"/>
+      <c r="D50" s="57"/>
+      <c r="E50" s="55"/>
     </row>
     <row r="51" spans="2:5">
       <c r="B51" s="26" t="s">
@@ -2842,10 +2851,10 @@
       <c r="C51" s="29">
         <v>0.3</v>
       </c>
-      <c r="D51" s="63" t="s">
+      <c r="D51" s="62" t="s">
         <v>222</v>
       </c>
-      <c r="E51" s="56"/>
+      <c r="E51" s="55"/>
     </row>
     <row r="53" spans="2:5">
       <c r="B53" s="23" t="s">
@@ -2853,16 +2862,16 @@
       </c>
     </row>
     <row r="55" spans="2:5">
-      <c r="B55" s="51" t="s">
+      <c r="B55" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="C55" s="51" t="s">
+      <c r="C55" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="D55" s="51" t="s">
+      <c r="D55" s="50" t="s">
         <v>96</v>
       </c>
-      <c r="E55" s="51" t="s">
+      <c r="E55" s="50" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2947,21 +2956,21 @@
       </c>
     </row>
     <row r="64" spans="2:5">
-      <c r="B64" s="54" t="s">
+      <c r="B64" s="53" t="s">
         <v>173</v>
       </c>
-      <c r="C64" s="55">
+      <c r="C64" s="54">
         <f>-E61*(C35-Cash_Yield)</f>
-        <v>-8.6199999999999999E-2</v>
+        <v>-0.10619999999999999</v>
       </c>
     </row>
     <row r="65" spans="1:5">
-      <c r="B65" s="54" t="s">
+      <c r="B65" s="53" t="s">
         <v>174</v>
       </c>
-      <c r="C65" s="55">
+      <c r="C65" s="54">
         <f>C35+C64</f>
-        <v>0.1638</v>
+        <v>0.1938</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3092,7 +3101,7 @@
       </c>
     </row>
     <row r="92" spans="1:5">
-      <c r="B92" s="61" t="s">
+      <c r="B92" s="60" t="s">
         <v>182</v>
       </c>
     </row>
@@ -3186,9 +3195,9 @@
         <v>176</v>
       </c>
       <c r="C112" s="44">
-        <v>0.13547956846156287</v>
-      </c>
-      <c r="D112" s="62" t="str">
+        <v>0.12967263576283533</v>
+      </c>
+      <c r="D112" s="61" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
         <v/>
       </c>
@@ -3271,8 +3280,8 @@
     <col min="10" max="12" width="8.6640625" style="2" customWidth="1"/>
     <col min="13" max="14" width="8.6640625" style="1" customWidth="1"/>
     <col min="15" max="16" width="8.6640625" style="15" customWidth="1"/>
-    <col min="17" max="17" width="8.6640625" style="93" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" style="87" customWidth="1"/>
+    <col min="17" max="17" width="8.6640625" style="92" customWidth="1"/>
+    <col min="18" max="18" width="8.6640625" style="86" customWidth="1"/>
     <col min="19" max="19" width="8.6640625" style="1" customWidth="1"/>
     <col min="20" max="20" width="22.73046875" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.796875" style="3" bestFit="1" customWidth="1"/>
@@ -3285,7 +3294,7 @@
       <c r="B1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="88"/>
+      <c r="C1" s="87"/>
       <c r="D1" s="100" t="s">
         <v>1</v>
       </c>
@@ -3408,7 +3417,7 @@
         <v>0.20371680012512947</v>
       </c>
       <c r="I3" s="15">
-        <v>0.28586016015015536</v>
+        <v>0.23821680012512947</v>
       </c>
       <c r="J3" s="2">
         <v>14.221973350893821</v>
@@ -3416,7 +3425,7 @@
       <c r="K3" s="2">
         <v>25.687175936271849</v>
       </c>
-      <c r="L3" s="87">
+      <c r="L3" s="86">
         <v>21.804142810167097</v>
       </c>
       <c r="M3" s="4">
@@ -3431,10 +3440,10 @@
       <c r="P3" s="15">
         <v>7.4171010848313429E-2</v>
       </c>
-      <c r="Q3" s="93">
+      <c r="Q3" s="92">
         <v>0.60402076709908736</v>
       </c>
-      <c r="R3" s="87">
+      <c r="R3" s="86">
         <v>4.4970487317420522</v>
       </c>
       <c r="S3" s="13" t="s">
@@ -3475,7 +3484,7 @@
         <v>0.14392892639139052</v>
       </c>
       <c r="I4" s="15">
-        <v>0.21411471166966861</v>
+        <v>0.17842892639139052</v>
       </c>
       <c r="J4" s="2">
         <v>4.9152072503751691</v>
@@ -3483,7 +3492,7 @@
       <c r="K4" s="2">
         <v>7.9151197774737936</v>
       </c>
-      <c r="L4" s="87">
+      <c r="L4" s="86">
         <v>7.4221982517030112</v>
       </c>
       <c r="M4" s="4">
@@ -3498,10 +3507,10 @@
       <c r="P4" s="15">
         <v>0.16360901428944893</v>
       </c>
-      <c r="Q4" s="93">
+      <c r="Q4" s="92">
         <v>1.1309485990394448</v>
       </c>
-      <c r="R4" s="87">
+      <c r="R4" s="86">
         <v>-3.7849818877411923</v>
       </c>
       <c r="S4" s="13" t="s">
@@ -3550,7 +3559,7 @@
       <c r="K5" s="2">
         <v>29.309951346473134</v>
       </c>
-      <c r="L5" s="87">
+      <c r="L5" s="86">
         <v>24.796949133193245</v>
       </c>
       <c r="M5" s="4">
@@ -3565,10 +3574,10 @@
       <c r="P5" s="15">
         <v>0.95241105291674188</v>
       </c>
-      <c r="Q5" s="93">
+      <c r="Q5" s="92">
         <v>4.0148803043206254</v>
       </c>
-      <c r="R5" s="87">
+      <c r="R5" s="86">
         <v>-38.360607814419353</v>
       </c>
       <c r="S5" s="13" t="s">
@@ -3609,7 +3618,7 @@
         <v>0.11924754303551685</v>
       </c>
       <c r="I6" s="15">
-        <v>0.100025128180176</v>
+        <v>0.15374754303551685</v>
       </c>
       <c r="J6" s="2">
         <v>13.155317996540354</v>
@@ -3617,7 +3626,7 @@
       <c r="K6" s="2">
         <v>20.508980461992877</v>
       </c>
-      <c r="L6" s="87">
+      <c r="L6" s="86">
         <v>19.785541823839793</v>
       </c>
       <c r="M6" s="4">
@@ -3632,10 +3641,10 @@
       <c r="P6" s="15">
         <v>0.15818859882129041</v>
       </c>
-      <c r="Q6" s="93">
+      <c r="Q6" s="92">
         <v>1.4550387206421544</v>
       </c>
-      <c r="R6" s="87">
+      <c r="R6" s="86">
         <v>5.8696003638854428</v>
       </c>
       <c r="S6" s="13" t="s">
@@ -3676,7 +3685,7 @@
         <v>8.8789639994280661E-2</v>
       </c>
       <c r="I7" s="15">
-        <v>0</v>
+        <v>2.9606730447963137E-2</v>
       </c>
       <c r="J7" s="2">
         <v>5.8235187175367322</v>
@@ -3684,7 +3693,7 @@
       <c r="K7" s="2">
         <v>9.1628099951889297</v>
       </c>
-      <c r="L7" s="87">
+      <c r="L7" s="86">
         <v>8.7684502451266084</v>
       </c>
       <c r="M7" s="4">
@@ -3699,10 +3708,10 @@
       <c r="P7" s="15">
         <v>1.8509098960546238E-2</v>
       </c>
-      <c r="Q7" s="93">
+      <c r="Q7" s="92">
         <v>1.1933697905849452</v>
       </c>
-      <c r="R7" s="87">
+      <c r="R7" s="86">
         <v>11.511512740854835</v>
       </c>
       <c r="S7" s="13" t="s">
@@ -3751,7 +3760,7 @@
       <c r="K8" s="2">
         <v>16.694869127046534</v>
       </c>
-      <c r="L8" s="87">
+      <c r="L8" s="86">
         <v>15.400158613707365</v>
       </c>
       <c r="M8" s="4">
@@ -3766,10 +3775,10 @@
       <c r="P8" s="15">
         <v>1.5035598705501618</v>
       </c>
-      <c r="Q8" s="93">
+      <c r="Q8" s="92">
         <v>4.1998196571663646</v>
       </c>
-      <c r="R8" s="87">
+      <c r="R8" s="86">
         <v>-12.13407231254085</v>
       </c>
       <c r="S8" s="13" t="s">
@@ -3818,7 +3827,7 @@
       <c r="K9" s="2">
         <v>66.921979202973944</v>
       </c>
-      <c r="L9" s="87">
+      <c r="L9" s="86">
         <v>58.439865108322181</v>
       </c>
       <c r="M9" s="4">
@@ -3833,10 +3842,10 @@
       <c r="P9" s="15">
         <v>9.5579625064196368E-3</v>
       </c>
-      <c r="Q9" s="93">
+      <c r="Q9" s="92">
         <v>7.3592411949940734E-2</v>
       </c>
-      <c r="R9" s="87">
+      <c r="R9" s="86">
         <v>1.3258162597677496</v>
       </c>
       <c r="S9" s="13" t="s">
@@ -3885,7 +3894,7 @@
       <c r="K10" s="2">
         <v>2.697564413182195</v>
       </c>
-      <c r="L10" s="87">
+      <c r="L10" s="86">
         <v>2.4361567519866192</v>
       </c>
       <c r="M10" s="4">
@@ -3900,10 +3909,10 @@
       <c r="P10" s="15">
         <v>1.0763175939415467E-2</v>
       </c>
-      <c r="Q10" s="93">
+      <c r="Q10" s="92">
         <v>0.29882156160837919</v>
       </c>
-      <c r="R10" s="87">
+      <c r="R10" s="86">
         <v>1.8653456492018881</v>
       </c>
       <c r="S10" s="16" t="s">
@@ -3952,7 +3961,7 @@
       <c r="K11" s="2">
         <v>32.464859269378167</v>
       </c>
-      <c r="L11" s="87">
+      <c r="L11" s="86">
         <v>29.895007167811503</v>
       </c>
       <c r="M11" s="4">
@@ -3967,10 +3976,10 @@
       <c r="P11" s="15">
         <v>0.40281804358844397</v>
       </c>
-      <c r="Q11" s="93">
+      <c r="Q11" s="92">
         <v>3.955391512509995</v>
       </c>
-      <c r="R11" s="87">
+      <c r="R11" s="86">
         <v>-26.938493611476797</v>
       </c>
       <c r="S11" s="13" t="s">
@@ -4019,7 +4028,7 @@
       <c r="K12" s="2">
         <v>67.988942786517455</v>
       </c>
-      <c r="L12" s="87">
+      <c r="L12" s="86">
         <v>53.971814816813243</v>
       </c>
       <c r="M12" s="4">
@@ -4034,10 +4043,10 @@
       <c r="P12" s="15">
         <v>0.24768740031897937</v>
       </c>
-      <c r="Q12" s="93">
+      <c r="Q12" s="92">
         <v>0.73855199466278643</v>
       </c>
-      <c r="R12" s="87">
+      <c r="R12" s="86">
         <v>-2.643445053008028</v>
       </c>
       <c r="S12" s="13" t="s">
@@ -6136,7 +6145,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.75" customHeight="1" zeroHeight="1"/>
   <cols>
-    <col min="1" max="16384" width="9.06640625" style="73"/>
+    <col min="1" max="16384" width="9.06640625" style="72"/>
   </cols>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -6186,14 +6195,14 @@
         <v>22</v>
       </c>
       <c r="C4" s="34">
-        <v>4.2900000000000001E-2</v>
+        <v>4.1700000000000001E-2</v>
       </c>
       <c r="D4" s="34">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="E4" s="35">
         <f>D4-C4</f>
-        <v>3.2099999999999997E-2</v>
+        <v>3.3299999999999996E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6410,324 +6419,324 @@
   <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="66" customWidth="1"/>
-    <col min="2" max="2" width="16.59765625" style="66" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.06640625" style="66"/>
-    <col min="5" max="6" width="15.59765625" style="66" customWidth="1"/>
-    <col min="7" max="8" width="9.9296875" style="66" customWidth="1"/>
-    <col min="9" max="16384" width="9.06640625" style="66"/>
+    <col min="1" max="1" width="2.59765625" style="65" customWidth="1"/>
+    <col min="2" max="2" width="16.59765625" style="65" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.06640625" style="65"/>
+    <col min="5" max="6" width="15.59765625" style="65" customWidth="1"/>
+    <col min="7" max="8" width="9.9296875" style="65" customWidth="1"/>
+    <col min="9" max="16384" width="9.06640625" style="65"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="13.15">
-      <c r="A1" s="64"/>
-      <c r="B1" s="65" t="s">
+      <c r="A1" s="63"/>
+      <c r="B1" s="64" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="29.65" customHeight="1">
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="66" t="s">
         <v>229</v>
       </c>
-      <c r="D2" s="67" t="s">
+      <c r="D2" s="66" t="s">
         <v>228</v>
       </c>
-      <c r="E2" s="67" t="s">
+      <c r="E2" s="66" t="s">
         <v>227</v>
       </c>
-      <c r="F2" s="67" t="s">
+      <c r="F2" s="66" t="s">
         <v>234</v>
       </c>
-      <c r="G2" s="67" t="s">
+      <c r="G2" s="66" t="s">
         <v>264</v>
       </c>
-      <c r="H2" s="67" t="s">
+      <c r="H2" s="66" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="B3" s="78" t="s">
+      <c r="B3" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="76" t="s">
+      <c r="C3" s="75" t="s">
         <v>233</v>
       </c>
-      <c r="D3" s="75" t="s">
+      <c r="D3" s="74" t="s">
         <v>230</v>
       </c>
-      <c r="E3" s="77" t="s">
+      <c r="E3" s="76" t="s">
         <v>233</v>
       </c>
-      <c r="F3" s="72">
+      <c r="F3" s="71">
         <v>351395.62</v>
       </c>
-      <c r="G3" s="74">
+      <c r="G3" s="73">
         <f>F3/$F$9</f>
         <v>0.40627734298520357</v>
       </c>
-      <c r="H3" s="92" t="s">
+      <c r="H3" s="91" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="B4" s="79" t="s">
+      <c r="B4" s="78" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="76">
+      <c r="C4" s="75">
         <f>VLOOKUP(B4,Opportunities!B$3:E$12,3,FALSE)</f>
         <v>16.440000000000001</v>
       </c>
-      <c r="D4" s="75" t="str">
+      <c r="D4" s="74" t="str">
         <f>VLOOKUP(B4,Opportunities!B$3:E$12,4,FALSE)</f>
         <v>HKD</v>
       </c>
-      <c r="E4" s="72">
+      <c r="E4" s="71">
         <v>10000</v>
       </c>
-      <c r="F4" s="77">
+      <c r="F4" s="76">
         <f>C4*E4</f>
         <v>164400</v>
       </c>
-      <c r="G4" s="74">
+      <c r="G4" s="73">
         <f>F4/$F$9</f>
         <v>0.19007634525088124</v>
       </c>
-      <c r="H4" s="74">
+      <c r="H4" s="73">
         <f>VLOOKUP(B4,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.100025128180176</v>
+        <v>0.15374754303551685</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="B5" s="79" t="s">
+      <c r="B5" s="78" t="s">
         <v>231</v>
       </c>
-      <c r="C5" s="76">
+      <c r="C5" s="75">
         <f>VLOOKUP(B5,Opportunities!B$3:E$12,3,FALSE)</f>
         <v>7.85</v>
       </c>
-      <c r="D5" s="75" t="str">
+      <c r="D5" s="74" t="str">
         <f>VLOOKUP(B5,Opportunities!B$3:E$12,4,FALSE)</f>
         <v>HKD</v>
       </c>
-      <c r="E5" s="72">
+      <c r="E5" s="71">
         <v>20000</v>
       </c>
-      <c r="F5" s="77">
+      <c r="F5" s="76">
         <f>E5*C5</f>
         <v>157000</v>
       </c>
-      <c r="G5" s="74">
+      <c r="G5" s="73">
         <f>F5/$F$9</f>
         <v>0.18152059735029413</v>
       </c>
-      <c r="H5" s="74">
+      <c r="H5" s="73">
         <f>VLOOKUP(B5,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0</v>
+        <v>2.9606730447963137E-2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="B6" s="79" t="s">
+      <c r="B6" s="78" t="s">
         <v>243</v>
       </c>
-      <c r="C6" s="76">
+      <c r="C6" s="75">
         <f>VLOOKUP(B6,Opportunities!B$3:E$12,3,FALSE)</f>
         <v>5.8</v>
       </c>
-      <c r="D6" s="75" t="str">
+      <c r="D6" s="74" t="str">
         <f>VLOOKUP(B6,Opportunities!B$3:E$12,4,FALSE)</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="72">
+      <c r="E6" s="71">
         <v>18000</v>
       </c>
-      <c r="F6" s="77">
+      <c r="F6" s="76">
         <f>E6*C6</f>
         <v>104400</v>
       </c>
-      <c r="G6" s="74">
+      <c r="G6" s="73">
         <f>F6/$F$9</f>
         <v>0.12070541632720196</v>
       </c>
-      <c r="H6" s="74">
+      <c r="H6" s="73">
         <f>VLOOKUP(B6,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.21411471166966861</v>
+        <v>0.17842892639139052</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="78" t="s">
         <v>258</v>
       </c>
-      <c r="C7" s="76">
+      <c r="C7" s="75">
         <f>VLOOKUP(B7,Opportunities!B$3:E$12,3,FALSE)</f>
         <v>14.62</v>
       </c>
-      <c r="D7" s="75" t="str">
+      <c r="D7" s="74" t="str">
         <f>VLOOKUP(B7,Opportunities!B$3:E$12,4,FALSE)</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="72">
+      <c r="E7" s="71">
         <v>6000</v>
       </c>
-      <c r="F7" s="77">
+      <c r="F7" s="76">
         <f>C7*E7</f>
         <v>87720</v>
       </c>
-      <c r="G7" s="74">
+      <c r="G7" s="73">
         <f>F7/$F$9</f>
         <v>0.10142029808641911</v>
       </c>
-      <c r="H7" s="74">
+      <c r="H7" s="73">
         <f>VLOOKUP(B7,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.28586016015015536</v>
+        <v>0.23821680012512947</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="B8" s="68"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="68"/>
-      <c r="H8" s="91"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="67"/>
+      <c r="H8" s="90"/>
     </row>
     <row r="9" spans="1:8" ht="13.15">
-      <c r="B9" s="80"/>
-      <c r="C9" s="81"/>
-      <c r="D9" s="80"/>
-      <c r="E9" s="82" t="s">
+      <c r="B9" s="79"/>
+      <c r="C9" s="80"/>
+      <c r="D9" s="79"/>
+      <c r="E9" s="81" t="s">
         <v>263</v>
       </c>
-      <c r="F9" s="82">
+      <c r="F9" s="81">
         <f>SUM(F3:F7)</f>
         <v>864915.62</v>
       </c>
-      <c r="G9" s="83">
+      <c r="G9" s="82">
         <f>SUM(G3:G7)</f>
         <v>1</v>
       </c>
-      <c r="H9" s="90">
+      <c r="H9" s="89">
         <f>SUM(H4:H7)</f>
         <v>0.6</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="B10" s="68"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
     </row>
     <row r="11" spans="1:8" ht="13.15">
-      <c r="A11" s="64"/>
-      <c r="B11" s="65" t="s">
+      <c r="A11" s="63"/>
+      <c r="B11" s="64" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="B12" s="79" t="s">
+      <c r="B12" s="78" t="s">
         <v>258</v>
       </c>
-      <c r="C12" s="76">
+      <c r="C12" s="75">
         <f>VLOOKUP(B12,Opportunities!B$3:E$12,3,FALSE)</f>
         <v>14.62</v>
       </c>
-      <c r="D12" s="75" t="str">
+      <c r="D12" s="74" t="str">
         <f>VLOOKUP(B12,Opportunities!B$3:E$12,4,FALSE)</f>
         <v>HKD</v>
       </c>
-      <c r="E12" s="72">
+      <c r="E12" s="71">
         <v>6000</v>
       </c>
-      <c r="F12" s="77">
+      <c r="F12" s="76">
         <f>C12*E12</f>
         <v>87720</v>
       </c>
-      <c r="G12" s="74">
+      <c r="G12" s="73">
         <f>F12/$F$9</f>
         <v>0.10142029808641911</v>
       </c>
-      <c r="H12" s="74">
+      <c r="H12" s="73">
         <f>VLOOKUP(B12,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.28586016015015536</v>
+        <v>0.23821680012512947</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="G13" s="89"/>
-      <c r="H13" s="89"/>
+      <c r="G13" s="88"/>
+      <c r="H13" s="88"/>
     </row>
     <row r="14" spans="1:8" ht="13.15">
-      <c r="B14" s="84" t="s">
+      <c r="B14" s="83" t="s">
         <v>261</v>
       </c>
-      <c r="C14" s="85" t="s">
+      <c r="C14" s="84" t="s">
         <v>233</v>
       </c>
-      <c r="D14" s="86" t="s">
+      <c r="D14" s="85" t="s">
         <v>160</v>
       </c>
-      <c r="E14" s="85" t="s">
+      <c r="E14" s="84" t="s">
         <v>233</v>
       </c>
-      <c r="F14" s="82">
+      <c r="F14" s="81">
         <f>F3-F12</f>
         <v>263675.62</v>
       </c>
-      <c r="G14" s="90">
+      <c r="G14" s="89">
         <f t="shared" ref="G14" si="0">F14/$F$9</f>
         <v>0.30485704489878446</v>
       </c>
-      <c r="H14" s="90">
+      <c r="H14" s="89">
         <f>Portfolio_Mgmt!E61</f>
         <v>0.4</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="B16" s="68"/>
-      <c r="C16" s="71"/>
-      <c r="D16" s="68"/>
-      <c r="E16" s="72"/>
-      <c r="F16" s="72"/>
+      <c r="B16" s="67"/>
+      <c r="C16" s="70"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
     </row>
     <row r="26" spans="2:6">
-      <c r="B26" s="68"/>
-      <c r="C26" s="71"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="72"/>
-      <c r="F26" s="72"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="70"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="68"/>
-      <c r="C27" s="71"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="72"/>
-      <c r="F27" s="72"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="B28" s="68"/>
-      <c r="C28" s="71"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="72"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="70"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="B29" s="68"/>
-      <c r="C29" s="71"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="72"/>
-      <c r="F29" s="72"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="70"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="B30" s="68"/>
-      <c r="C30" s="71"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="72"/>
-      <c r="F30" s="72"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="70"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="B31" s="68"/>
-      <c r="C31" s="69"/>
-      <c r="D31" s="68"/>
-      <c r="E31" s="70"/>
-      <c r="F31" s="70"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="68"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="69"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A8239B-F695-4A37-AF78-D60A417D9716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FEB76F2-A99D-4B3C-B2ED-D335BBEF5017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Comp_Group" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Opportunities!$B$2:$V$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Opportunities!$B$2:$W$2</definedName>
     <definedName name="AuraStyleDefaultsReset" hidden="1">#N/A</definedName>
     <definedName name="benchmark">Portfolio_Mgmt!$C$10</definedName>
     <definedName name="Cash_Yield">Portfolio_Mgmt!$C$11</definedName>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="272">
   <si>
     <t>Name</t>
   </si>
@@ -1597,7 +1597,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Yield to open a position at</t>
+    <t>open a position at a yield of</t>
+  </si>
+  <si>
+    <t>Open Position</t>
   </si>
 </sst>
 </file>
@@ -3195,7 +3198,7 @@
         <v>176</v>
       </c>
       <c r="C112" s="44">
-        <v>0.12967263576283533</v>
+        <v>0.12974936050286673</v>
       </c>
       <c r="D112" s="61" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
@@ -3268,7 +3271,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V358"/>
+  <dimension ref="A1:W358"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.46484375" style="1" customWidth="1"/>
@@ -3277,19 +3280,19 @@
     <col min="4" max="4" width="8.6640625" style="2" customWidth="1"/>
     <col min="5" max="5" width="10.33203125" style="1" customWidth="1"/>
     <col min="6" max="9" width="10.33203125" style="15" customWidth="1"/>
-    <col min="10" max="12" width="8.6640625" style="2" customWidth="1"/>
-    <col min="13" max="14" width="8.6640625" style="1" customWidth="1"/>
-    <col min="15" max="16" width="8.6640625" style="15" customWidth="1"/>
-    <col min="17" max="17" width="8.6640625" style="92" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" style="86" customWidth="1"/>
-    <col min="19" max="19" width="8.6640625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="22.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.796875" style="11"/>
-    <col min="23" max="16384" width="8.796875" style="1"/>
+    <col min="10" max="13" width="8.6640625" style="2" customWidth="1"/>
+    <col min="14" max="15" width="8.6640625" style="1" customWidth="1"/>
+    <col min="16" max="17" width="8.6640625" style="15" customWidth="1"/>
+    <col min="18" max="18" width="8.6640625" style="92" customWidth="1"/>
+    <col min="19" max="19" width="8.6640625" style="86" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="22.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.796875" style="11"/>
+    <col min="24" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:23">
       <c r="A1" s="5"/>
       <c r="B1" s="6" t="s">
         <v>4</v>
@@ -3310,24 +3313,25 @@
       </c>
       <c r="K1" s="102"/>
       <c r="L1" s="102"/>
-      <c r="M1" s="98" t="s">
+      <c r="M1" s="102"/>
+      <c r="N1" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="98"/>
-      <c r="O1" s="103" t="s">
+      <c r="O1" s="98"/>
+      <c r="P1" s="103" t="s">
         <v>269</v>
       </c>
-      <c r="P1" s="103"/>
       <c r="Q1" s="103"/>
       <c r="R1" s="103"/>
-      <c r="S1" s="99" t="s">
+      <c r="S1" s="103"/>
+      <c r="T1" s="99" t="s">
         <v>53</v>
       </c>
-      <c r="T1" s="99"/>
       <c r="U1" s="99"/>
       <c r="V1" s="99"/>
-    </row>
-    <row r="2" spans="1:22" ht="26" customHeight="1">
+      <c r="W1" s="99"/>
+    </row>
+    <row r="2" spans="1:23" ht="26" customHeight="1">
       <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
@@ -3359,40 +3363,43 @@
         <v>12</v>
       </c>
       <c r="L2" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="M2" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="N2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="O2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="P2" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="Q2" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="R2" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="S2" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="S2" s="7" t="s">
+      <c r="T2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="7" t="s">
+      <c r="U2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="U2" s="9" t="s">
+      <c r="V2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="V2" s="10" t="s">
+      <c r="W2" s="10" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:23">
       <c r="B3" s="11" t="s">
         <v>258</v>
       </c>
@@ -3406,60 +3413,60 @@
         <v>160</v>
       </c>
       <c r="F3" s="15">
-        <v>0.23821680012512947</v>
+        <v>0.23834947369112891</v>
       </c>
       <c r="G3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$10</f>
-        <v>0.12081680012512946</v>
+        <v>0.12094947369112891</v>
       </c>
       <c r="H3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$11</f>
-        <v>0.20371680012512947</v>
+        <v>0.20384947369112891</v>
       </c>
       <c r="I3" s="15">
-        <v>0.23821680012512947</v>
+        <v>0.23834947369112891</v>
       </c>
       <c r="J3" s="2">
-        <v>14.221973350893821</v>
+        <v>12.691501140813982</v>
       </c>
       <c r="K3" s="2">
-        <v>25.687175936271849</v>
-      </c>
-      <c r="L3" s="86">
-        <v>21.804142810167097</v>
-      </c>
-      <c r="M3" s="4">
-        <v>6.8306347295356576E-2</v>
+        <v>25.696602430940541</v>
+      </c>
+      <c r="M3" s="86">
+        <v>21.811108833373932</v>
       </c>
       <c r="N3" s="4">
-        <v>3.7498432682696467E-2</v>
-      </c>
-      <c r="O3" s="15">
+        <v>6.8331310133345272E-2</v>
+      </c>
+      <c r="O3" s="4">
+        <v>3.7484709986796393E-2</v>
+      </c>
+      <c r="P3" s="15">
         <v>0.36794481423679237</v>
       </c>
-      <c r="P3" s="15">
+      <c r="Q3" s="15">
         <v>7.4171010848313429E-2</v>
       </c>
-      <c r="Q3" s="92">
+      <c r="R3" s="92">
         <v>0.60402076709908736</v>
       </c>
-      <c r="R3" s="86">
-        <v>4.4970487317420522</v>
-      </c>
-      <c r="S3" s="13" t="s">
+      <c r="S3" s="86">
+        <v>4.4986950465252065</v>
+      </c>
+      <c r="T3" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="T3" s="11" t="s">
+      <c r="U3" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U3" s="14">
+      <c r="V3" s="14">
         <v>45900</v>
       </c>
-      <c r="V3" s="11" t="s">
+      <c r="W3" s="11" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:23">
       <c r="B4" s="11" t="s">
         <v>236</v>
       </c>
@@ -3473,60 +3480,60 @@
         <v>160</v>
       </c>
       <c r="F4" s="15">
-        <v>0.17842892639139052</v>
+        <v>0.17855667472343195</v>
       </c>
       <c r="G4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$10</f>
-        <v>6.1028926391390514E-2</v>
+        <v>6.1156674723431947E-2</v>
       </c>
       <c r="H4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$11</f>
-        <v>0.14392892639139052</v>
+        <v>0.14405667472343195</v>
       </c>
       <c r="I4" s="15">
-        <v>0.17842892639139052</v>
+        <v>0.17855667472343195</v>
       </c>
       <c r="J4" s="2">
-        <v>4.9152072503751691</v>
+        <v>4.4066254223755825</v>
       </c>
       <c r="K4" s="2">
-        <v>7.9151197774737936</v>
-      </c>
-      <c r="L4" s="86">
-        <v>7.4221982517030112</v>
-      </c>
-      <c r="M4" s="4">
-        <v>0.13256816715305936</v>
+        <v>7.9180174064472393</v>
+      </c>
+      <c r="M4" s="86">
+        <v>7.4244984830046468</v>
       </c>
       <c r="N4" s="4">
+        <v>0.13261669874486073</v>
+      </c>
+      <c r="O4" s="4">
         <v>7.6196467311032592E-2</v>
       </c>
-      <c r="O4" s="15">
+      <c r="P4" s="15">
         <v>0.61007460831657279</v>
       </c>
-      <c r="P4" s="15">
+      <c r="Q4" s="15">
         <v>0.16360901428944893</v>
       </c>
-      <c r="Q4" s="92">
+      <c r="R4" s="92">
         <v>1.1309485990394448</v>
       </c>
-      <c r="R4" s="86">
-        <v>-3.7849818877411923</v>
-      </c>
-      <c r="S4" s="13" t="s">
+      <c r="S4" s="86">
+        <v>-3.7863675235231167</v>
+      </c>
+      <c r="T4" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="T4" s="11" t="s">
+      <c r="U4" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="U4" s="14">
+      <c r="V4" s="14">
         <v>45900</v>
       </c>
-      <c r="V4" s="11" t="s">
+      <c r="W4" s="11" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:23">
       <c r="B5" s="11" t="s">
         <v>251</v>
       </c>
@@ -3554,46 +3561,46 @@
         <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>16.165402289394244</v>
+        <v>14.418941896437474</v>
       </c>
       <c r="K5" s="2">
         <v>29.309951346473134</v>
       </c>
-      <c r="L5" s="86">
+      <c r="M5" s="86">
         <v>24.796949133193245</v>
       </c>
-      <c r="M5" s="4">
+      <c r="N5" s="4">
         <v>0.22703991769612522</v>
       </c>
-      <c r="N5" s="4">
+      <c r="O5" s="4">
         <v>2.956175298804781E-2</v>
       </c>
-      <c r="O5" s="15">
+      <c r="P5" s="15">
         <v>1.4851905363915479</v>
       </c>
-      <c r="P5" s="15">
+      <c r="Q5" s="15">
         <v>0.95241105291674188</v>
       </c>
-      <c r="Q5" s="92">
+      <c r="R5" s="92">
         <v>4.0148803043206254</v>
       </c>
-      <c r="R5" s="86">
+      <c r="S5" s="86">
         <v>-38.360607814419353</v>
       </c>
-      <c r="S5" s="13" t="s">
+      <c r="T5" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="T5" s="11" t="s">
+      <c r="U5" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U5" s="14">
+      <c r="V5" s="14">
         <v>45900</v>
       </c>
-      <c r="V5" s="11" t="s">
+      <c r="W5" s="11" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:23">
       <c r="B6" s="11" t="s">
         <v>158</v>
       </c>
@@ -3621,46 +3628,46 @@
         <v>0.15374754303551685</v>
       </c>
       <c r="J6" s="2">
-        <v>13.155317996540354</v>
+        <v>11.804906901225705</v>
       </c>
       <c r="K6" s="2">
         <v>20.508980461992877</v>
       </c>
-      <c r="L6" s="86">
+      <c r="M6" s="86">
         <v>19.785541823839793</v>
       </c>
-      <c r="M6" s="4">
+      <c r="N6" s="4">
         <v>0.10510863864778767</v>
       </c>
-      <c r="N6" s="4">
+      <c r="O6" s="4">
         <v>8.2725060827250604E-2</v>
       </c>
-      <c r="O6" s="15">
+      <c r="P6" s="15">
         <v>0.31018327415220487</v>
       </c>
-      <c r="P6" s="15">
+      <c r="Q6" s="15">
         <v>0.15818859882129041</v>
       </c>
-      <c r="Q6" s="92">
+      <c r="R6" s="92">
         <v>1.4550387206421544</v>
       </c>
-      <c r="R6" s="86">
+      <c r="S6" s="86">
         <v>5.8696003638854428</v>
       </c>
-      <c r="S6" s="13" t="s">
+      <c r="T6" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="T6" s="11" t="s">
+      <c r="U6" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U6" s="14">
+      <c r="V6" s="14">
         <v>45808</v>
       </c>
-      <c r="V6" s="11" t="s">
+      <c r="W6" s="11" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:23">
       <c r="B7" s="11" t="s">
         <v>164</v>
       </c>
@@ -3685,49 +3692,49 @@
         <v>8.8789639994280661E-2</v>
       </c>
       <c r="I7" s="15">
-        <v>2.9606730447963137E-2</v>
+        <v>2.9346308549922262E-2</v>
       </c>
       <c r="J7" s="2">
-        <v>5.8235187175367322</v>
+        <v>5.2239462882061574</v>
       </c>
       <c r="K7" s="2">
         <v>9.1628099951889297</v>
       </c>
-      <c r="L7" s="86">
+      <c r="M7" s="86">
         <v>8.7684502451266084</v>
       </c>
-      <c r="M7" s="4">
+      <c r="N7" s="4">
         <v>3.9350111080543315E-2</v>
       </c>
-      <c r="N7" s="4">
+      <c r="O7" s="4">
         <v>7.3885350318471335E-2</v>
       </c>
-      <c r="O7" s="15">
+      <c r="P7" s="15">
         <v>8.3114411724224596E-2</v>
       </c>
-      <c r="P7" s="15">
+      <c r="Q7" s="15">
         <v>1.8509098960546238E-2</v>
       </c>
-      <c r="Q7" s="92">
+      <c r="R7" s="92">
         <v>1.1933697905849452</v>
       </c>
-      <c r="R7" s="86">
+      <c r="S7" s="86">
         <v>11.511512740854835</v>
       </c>
-      <c r="S7" s="13" t="s">
+      <c r="T7" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="T7" s="11" t="s">
+      <c r="U7" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="U7" s="14">
+      <c r="V7" s="14">
         <v>45900</v>
       </c>
-      <c r="V7" s="11" t="s">
+      <c r="W7" s="11" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:23">
       <c r="B8" s="11" t="s">
         <v>244</v>
       </c>
@@ -3741,60 +3748,60 @@
         <v>160</v>
       </c>
       <c r="F8" s="15">
-        <v>0.10954171828338932</v>
+        <v>0.10940387682956731</v>
       </c>
       <c r="G8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$10</f>
-        <v>-7.8582817166106822E-3</v>
+        <v>-7.9961231704326896E-3</v>
       </c>
       <c r="H8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$11</f>
-        <v>7.5041718283389319E-2</v>
+        <v>7.4903876829567312E-2</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
       </c>
       <c r="J8" s="2">
-        <v>10.174176386967826</v>
+        <v>9.1088969706010197</v>
       </c>
       <c r="K8" s="2">
-        <v>16.694869127046534</v>
-      </c>
-      <c r="L8" s="86">
-        <v>15.400158613707365</v>
-      </c>
-      <c r="M8" s="4">
-        <v>0.10764138310388582</v>
+        <v>16.688984661810444</v>
+      </c>
+      <c r="M8" s="86">
+        <v>15.394712350875789</v>
       </c>
       <c r="N8" s="4">
-        <v>5.8429064516129031E-2</v>
-      </c>
-      <c r="O8" s="15">
+        <v>0.1076023273696578</v>
+      </c>
+      <c r="O8" s="4">
+        <v>5.8407976157082743E-2</v>
+      </c>
+      <c r="P8" s="15">
         <v>2.2875080906148866</v>
       </c>
-      <c r="P8" s="15">
+      <c r="Q8" s="15">
         <v>1.5035598705501618</v>
       </c>
-      <c r="Q8" s="92">
+      <c r="R8" s="92">
         <v>4.1998196571663646</v>
       </c>
-      <c r="R8" s="86">
-        <v>-12.13407231254085</v>
-      </c>
-      <c r="S8" s="13" t="s">
+      <c r="S8" s="86">
+        <v>-12.129692853863228</v>
+      </c>
+      <c r="T8" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="T8" s="11" t="s">
+      <c r="U8" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="U8" s="14">
+      <c r="V8" s="14">
         <v>45900</v>
       </c>
-      <c r="V8" s="11" t="s">
+      <c r="W8" s="11" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:23">
       <c r="B9" s="11" t="s">
         <v>240</v>
       </c>
@@ -3808,60 +3815,60 @@
         <v>160</v>
       </c>
       <c r="F9" s="15">
-        <v>0.10804060157997641</v>
+        <v>0.10815463230293121</v>
       </c>
       <c r="G9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$10</f>
-        <v>-9.3593984200235902E-3</v>
+        <v>-9.2453676970687959E-3</v>
       </c>
       <c r="H9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$11</f>
-        <v>7.3540601579976411E-2</v>
+        <v>7.3654632302931206E-2</v>
       </c>
       <c r="I9" s="15">
         <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>38.289885084736952</v>
+        <v>34.215998183334875</v>
       </c>
       <c r="K9" s="2">
-        <v>66.921979202973944</v>
-      </c>
-      <c r="L9" s="86">
-        <v>58.439865108322181</v>
-      </c>
-      <c r="M9" s="4">
-        <v>4.1491316575080373E-2</v>
+        <v>66.946528402184271</v>
+      </c>
+      <c r="M9" s="86">
+        <v>58.457407994642217</v>
       </c>
       <c r="N9" s="4">
-        <v>3.801684419443882E-2</v>
-      </c>
-      <c r="O9" s="15">
+        <v>4.1506442378573941E-2</v>
+      </c>
+      <c r="O9" s="4">
+        <v>3.8002931783848878E-2</v>
+      </c>
+      <c r="P9" s="15">
         <v>0.72207550313588764</v>
       </c>
-      <c r="P9" s="15">
+      <c r="Q9" s="15">
         <v>9.5579625064196368E-3</v>
       </c>
-      <c r="Q9" s="92">
+      <c r="R9" s="92">
         <v>7.3592411949940734E-2</v>
       </c>
-      <c r="R9" s="86">
-        <v>1.3258162597677496</v>
-      </c>
-      <c r="S9" s="13" t="s">
+      <c r="S9" s="86">
+        <v>1.3263016249568782</v>
+      </c>
+      <c r="T9" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="T9" s="11" t="s">
+      <c r="U9" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U9" s="14">
+      <c r="V9" s="14">
         <v>45900</v>
       </c>
-      <c r="V9" s="11" t="s">
+      <c r="W9" s="11" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:23">
       <c r="B10" s="11" t="s">
         <v>168</v>
       </c>
@@ -3875,60 +3882,60 @@
         <v>160</v>
       </c>
       <c r="F10" s="15">
-        <v>0.10185445179346697</v>
+        <v>0.10196238180241868</v>
       </c>
       <c r="G10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$10</f>
-        <v>-1.5545548206533033E-2</v>
+        <v>-1.5437618197581326E-2</v>
       </c>
       <c r="H10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$11</f>
-        <v>6.7354451793466968E-2</v>
+        <v>6.7462381802418675E-2</v>
       </c>
       <c r="I10" s="15">
         <v>0</v>
       </c>
       <c r="J10" s="2">
-        <v>1.6044036483689856</v>
+        <v>1.435929941306664</v>
       </c>
       <c r="K10" s="2">
-        <v>2.697564413182195</v>
-      </c>
-      <c r="L10" s="86">
-        <v>2.4361567519866192</v>
-      </c>
-      <c r="M10" s="4">
-        <v>3.573276361444476E-2</v>
+        <v>2.6985679028664227</v>
+      </c>
+      <c r="M10" s="86">
+        <v>2.4368454920607938</v>
       </c>
       <c r="N10" s="4">
-        <v>4.9726182470532274E-2</v>
-      </c>
-      <c r="O10" s="15">
+        <v>3.5745625781092097E-2</v>
+      </c>
+      <c r="O10" s="4">
+        <v>4.9707984982490863E-2</v>
+      </c>
+      <c r="P10" s="15">
         <v>0.20351769929714394</v>
       </c>
-      <c r="P10" s="15">
+      <c r="Q10" s="15">
         <v>1.0763175939415467E-2</v>
       </c>
-      <c r="Q10" s="92">
+      <c r="R10" s="92">
         <v>0.29882156160837919</v>
       </c>
-      <c r="R10" s="86">
-        <v>1.8653456492018881</v>
-      </c>
-      <c r="S10" s="16" t="s">
+      <c r="S10" s="86">
+        <v>1.866028529531002</v>
+      </c>
+      <c r="T10" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="T10" s="11" t="s">
+      <c r="U10" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="U10" s="14">
+      <c r="V10" s="14">
         <v>45900</v>
       </c>
-      <c r="V10" s="11" t="s">
+      <c r="W10" s="11" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:23">
       <c r="B11" s="11" t="s">
         <v>255</v>
       </c>
@@ -3956,46 +3963,46 @@
         <v>0</v>
       </c>
       <c r="J11" s="2">
-        <v>19.745207945921621</v>
+        <v>17.682685147645955</v>
       </c>
       <c r="K11" s="2">
         <v>32.464859269378167</v>
       </c>
-      <c r="L11" s="86">
+      <c r="M11" s="86">
         <v>29.895007167811503</v>
       </c>
-      <c r="M11" s="4">
+      <c r="N11" s="4">
         <v>8.8134932571433455E-2</v>
       </c>
-      <c r="N11" s="4">
+      <c r="O11" s="4">
         <v>5.5536272127733433E-2</v>
       </c>
-      <c r="O11" s="15">
+      <c r="P11" s="15">
         <v>0.78990369994931575</v>
       </c>
-      <c r="P11" s="15">
+      <c r="Q11" s="15">
         <v>0.40281804358844397</v>
       </c>
-      <c r="Q11" s="92">
+      <c r="R11" s="92">
         <v>3.955391512509995</v>
       </c>
-      <c r="R11" s="86">
+      <c r="S11" s="86">
         <v>-26.938493611476797</v>
       </c>
-      <c r="S11" s="13" t="s">
+      <c r="T11" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="T11" s="11" t="s">
+      <c r="U11" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U11" s="14">
+      <c r="V11" s="14">
         <v>45900</v>
       </c>
-      <c r="V11" s="11" t="s">
+      <c r="W11" s="11" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:23">
       <c r="B12" s="11" t="s">
         <v>249</v>
       </c>
@@ -4009,2127 +4016,2127 @@
         <v>160</v>
       </c>
       <c r="F12" s="15">
-        <v>9.2083708290373378E-2</v>
+        <v>9.195230665086962E-2</v>
       </c>
       <c r="G12" s="15">
         <f>F12 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.5316291709626626E-2</v>
+        <v>-2.5447693349130385E-2</v>
       </c>
       <c r="H12" s="15">
         <f>F12 - Portfolio_Mgmt!$C$11</f>
-        <v>5.7583708290373375E-2</v>
+        <v>5.7452306650869617E-2</v>
       </c>
       <c r="I12" s="15">
         <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>34.810338706696939</v>
+        <v>30.935095153902036</v>
       </c>
       <c r="K12" s="2">
-        <v>67.988942786517455</v>
-      </c>
-      <c r="L12" s="86">
-        <v>53.971814816813243</v>
-      </c>
-      <c r="M12" s="4">
-        <v>0.10069379612803481</v>
+        <v>67.964404053122792</v>
+      </c>
+      <c r="M12" s="86">
+        <v>53.95233517909076</v>
       </c>
       <c r="N12" s="4">
+        <v>0.10065745348000395</v>
+      </c>
+      <c r="O12" s="4">
         <v>0</v>
       </c>
-      <c r="O12" s="15">
+      <c r="P12" s="15">
         <v>1.2907496012759174</v>
       </c>
-      <c r="P12" s="15">
+      <c r="Q12" s="15">
         <v>0.24768740031897937</v>
       </c>
-      <c r="Q12" s="92">
+      <c r="R12" s="92">
         <v>0.73855199466278643</v>
       </c>
-      <c r="R12" s="86">
-        <v>-2.643445053008028</v>
-      </c>
-      <c r="S12" s="13" t="s">
+      <c r="S12" s="86">
+        <v>-2.6424909744367104</v>
+      </c>
+      <c r="T12" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="T12" s="11" t="s">
+      <c r="U12" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U12" s="14">
+      <c r="V12" s="14">
         <v>45808</v>
       </c>
-      <c r="V12" s="11" t="s">
+      <c r="W12" s="11" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:23">
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
       <c r="E13" s="12"/>
-      <c r="M13" s="4"/>
       <c r="N13" s="4"/>
-      <c r="S13" s="13"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="14"/>
-    </row>
-    <row r="14" spans="1:22">
+      <c r="O13" s="4"/>
+      <c r="T13" s="13"/>
+      <c r="U13" s="11"/>
+      <c r="V13" s="14"/>
+    </row>
+    <row r="14" spans="1:23">
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
       <c r="E14" s="12"/>
-      <c r="M14" s="4"/>
       <c r="N14" s="4"/>
-      <c r="S14" s="13"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="14"/>
-    </row>
-    <row r="15" spans="1:22">
+      <c r="O14" s="4"/>
+      <c r="T14" s="13"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="14"/>
+    </row>
+    <row r="15" spans="1:23">
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
       <c r="E15" s="12"/>
-      <c r="M15" s="4"/>
       <c r="N15" s="4"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="14"/>
-    </row>
-    <row r="16" spans="1:22">
+      <c r="O15" s="4"/>
+      <c r="T15" s="13"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="14"/>
+    </row>
+    <row r="16" spans="1:23">
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
       <c r="E16" s="12"/>
-      <c r="M16" s="4"/>
       <c r="N16" s="4"/>
-      <c r="S16" s="13"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="14"/>
-    </row>
-    <row r="17" spans="2:21">
+      <c r="O16" s="4"/>
+      <c r="T16" s="13"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="14"/>
+    </row>
+    <row r="17" spans="2:22">
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="E17" s="12"/>
-      <c r="M17" s="4"/>
       <c r="N17" s="4"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="14"/>
-    </row>
-    <row r="18" spans="2:21">
+      <c r="O17" s="4"/>
+      <c r="T17" s="13"/>
+      <c r="U17" s="11"/>
+      <c r="V17" s="14"/>
+    </row>
+    <row r="18" spans="2:22">
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
       <c r="E18" s="12"/>
-      <c r="M18" s="4"/>
       <c r="N18" s="4"/>
-      <c r="S18" s="13"/>
-      <c r="T18" s="11"/>
-      <c r="U18" s="14"/>
-    </row>
-    <row r="19" spans="2:21">
+      <c r="O18" s="4"/>
+      <c r="T18" s="13"/>
+      <c r="U18" s="11"/>
+      <c r="V18" s="14"/>
+    </row>
+    <row r="19" spans="2:22">
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
       <c r="E19" s="12"/>
-      <c r="M19" s="4"/>
       <c r="N19" s="4"/>
-      <c r="S19" s="13"/>
-      <c r="T19" s="11"/>
-      <c r="U19" s="14"/>
-    </row>
-    <row r="20" spans="2:21">
+      <c r="O19" s="4"/>
+      <c r="T19" s="13"/>
+      <c r="U19" s="11"/>
+      <c r="V19" s="14"/>
+    </row>
+    <row r="20" spans="2:22">
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
       <c r="E20" s="12"/>
-      <c r="M20" s="4"/>
       <c r="N20" s="4"/>
-      <c r="S20" s="13"/>
-      <c r="T20" s="11"/>
-      <c r="U20" s="14"/>
-    </row>
-    <row r="21" spans="2:21">
+      <c r="O20" s="4"/>
+      <c r="T20" s="13"/>
+      <c r="U20" s="11"/>
+      <c r="V20" s="14"/>
+    </row>
+    <row r="21" spans="2:22">
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
       <c r="E21" s="12"/>
-      <c r="M21" s="4"/>
       <c r="N21" s="4"/>
-      <c r="S21" s="13"/>
-      <c r="T21" s="11"/>
-      <c r="U21" s="14"/>
-    </row>
-    <row r="22" spans="2:21">
+      <c r="O21" s="4"/>
+      <c r="T21" s="13"/>
+      <c r="U21" s="11"/>
+      <c r="V21" s="14"/>
+    </row>
+    <row r="22" spans="2:22">
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="E22" s="12"/>
-      <c r="M22" s="4"/>
       <c r="N22" s="4"/>
-      <c r="S22" s="13"/>
-      <c r="T22" s="11"/>
-      <c r="U22" s="14"/>
-    </row>
-    <row r="23" spans="2:21">
+      <c r="O22" s="4"/>
+      <c r="T22" s="13"/>
+      <c r="U22" s="11"/>
+      <c r="V22" s="14"/>
+    </row>
+    <row r="23" spans="2:22">
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="E23" s="12"/>
-      <c r="M23" s="4"/>
       <c r="N23" s="4"/>
-      <c r="S23" s="13"/>
-      <c r="T23" s="11"/>
-      <c r="U23" s="14"/>
-    </row>
-    <row r="24" spans="2:21">
+      <c r="O23" s="4"/>
+      <c r="T23" s="13"/>
+      <c r="U23" s="11"/>
+      <c r="V23" s="14"/>
+    </row>
+    <row r="24" spans="2:22">
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="E24" s="12"/>
-      <c r="M24" s="4"/>
       <c r="N24" s="4"/>
-      <c r="S24" s="13"/>
-      <c r="T24" s="11"/>
-      <c r="U24" s="14"/>
-    </row>
-    <row r="25" spans="2:21">
+      <c r="O24" s="4"/>
+      <c r="T24" s="13"/>
+      <c r="U24" s="11"/>
+      <c r="V24" s="14"/>
+    </row>
+    <row r="25" spans="2:22">
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="E25" s="12"/>
-      <c r="M25" s="4"/>
       <c r="N25" s="4"/>
-      <c r="S25" s="13"/>
-      <c r="T25" s="11"/>
-      <c r="U25" s="14"/>
-    </row>
-    <row r="26" spans="2:21">
+      <c r="O25" s="4"/>
+      <c r="T25" s="13"/>
+      <c r="U25" s="11"/>
+      <c r="V25" s="14"/>
+    </row>
+    <row r="26" spans="2:22">
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="E26" s="12"/>
-      <c r="M26" s="4"/>
       <c r="N26" s="4"/>
-      <c r="S26" s="13"/>
-      <c r="T26" s="11"/>
-      <c r="U26" s="14"/>
-    </row>
-    <row r="27" spans="2:21">
+      <c r="O26" s="4"/>
+      <c r="T26" s="13"/>
+      <c r="U26" s="11"/>
+      <c r="V26" s="14"/>
+    </row>
+    <row r="27" spans="2:22">
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="E27" s="12"/>
-      <c r="M27" s="4"/>
       <c r="N27" s="4"/>
-      <c r="S27" s="13"/>
-      <c r="T27" s="11"/>
-      <c r="U27" s="14"/>
-    </row>
-    <row r="28" spans="2:21">
+      <c r="O27" s="4"/>
+      <c r="T27" s="13"/>
+      <c r="U27" s="11"/>
+      <c r="V27" s="14"/>
+    </row>
+    <row r="28" spans="2:22">
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="E28" s="12"/>
-      <c r="M28" s="4"/>
       <c r="N28" s="4"/>
-      <c r="S28" s="13"/>
-      <c r="T28" s="11"/>
-      <c r="U28" s="14"/>
-    </row>
-    <row r="29" spans="2:21">
+      <c r="O28" s="4"/>
+      <c r="T28" s="13"/>
+      <c r="U28" s="11"/>
+      <c r="V28" s="14"/>
+    </row>
+    <row r="29" spans="2:22">
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
       <c r="E29" s="12"/>
-      <c r="M29" s="4"/>
       <c r="N29" s="4"/>
-      <c r="S29" s="13"/>
-      <c r="T29" s="11"/>
-      <c r="U29" s="14"/>
-    </row>
-    <row r="30" spans="2:21">
+      <c r="O29" s="4"/>
+      <c r="T29" s="13"/>
+      <c r="U29" s="11"/>
+      <c r="V29" s="14"/>
+    </row>
+    <row r="30" spans="2:22">
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="E30" s="12"/>
-      <c r="M30" s="4"/>
       <c r="N30" s="4"/>
-      <c r="S30" s="13"/>
-      <c r="T30" s="11"/>
-      <c r="U30" s="14"/>
-    </row>
-    <row r="31" spans="2:21">
+      <c r="O30" s="4"/>
+      <c r="T30" s="13"/>
+      <c r="U30" s="11"/>
+      <c r="V30" s="14"/>
+    </row>
+    <row r="31" spans="2:22">
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="E31" s="12"/>
-      <c r="M31" s="4"/>
       <c r="N31" s="4"/>
-      <c r="S31" s="16"/>
-      <c r="T31" s="11"/>
-      <c r="U31" s="14"/>
-    </row>
-    <row r="32" spans="2:21">
+      <c r="O31" s="4"/>
+      <c r="T31" s="16"/>
+      <c r="U31" s="11"/>
+      <c r="V31" s="14"/>
+    </row>
+    <row r="32" spans="2:22">
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
       <c r="E32" s="12"/>
-      <c r="M32" s="4"/>
       <c r="N32" s="4"/>
-      <c r="S32" s="13"/>
-      <c r="T32" s="11"/>
-      <c r="U32" s="14"/>
-    </row>
-    <row r="33" spans="2:21">
+      <c r="O32" s="4"/>
+      <c r="T32" s="13"/>
+      <c r="U32" s="11"/>
+      <c r="V32" s="14"/>
+    </row>
+    <row r="33" spans="2:22">
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
       <c r="E33" s="12"/>
-      <c r="M33" s="4"/>
       <c r="N33" s="4"/>
-      <c r="S33" s="13"/>
-      <c r="T33" s="11"/>
-      <c r="U33" s="14"/>
-    </row>
-    <row r="34" spans="2:21">
+      <c r="O33" s="4"/>
+      <c r="T33" s="13"/>
+      <c r="U33" s="11"/>
+      <c r="V33" s="14"/>
+    </row>
+    <row r="34" spans="2:22">
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="E34" s="12"/>
-      <c r="M34" s="4"/>
       <c r="N34" s="4"/>
-      <c r="S34" s="16"/>
-      <c r="T34" s="11"/>
-      <c r="U34" s="14"/>
-    </row>
-    <row r="35" spans="2:21">
+      <c r="O34" s="4"/>
+      <c r="T34" s="16"/>
+      <c r="U34" s="11"/>
+      <c r="V34" s="14"/>
+    </row>
+    <row r="35" spans="2:22">
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
       <c r="E35" s="12"/>
-      <c r="M35" s="4"/>
       <c r="N35" s="4"/>
-      <c r="S35" s="13"/>
-      <c r="T35" s="11"/>
-      <c r="U35" s="14"/>
-    </row>
-    <row r="36" spans="2:21">
+      <c r="O35" s="4"/>
+      <c r="T35" s="13"/>
+      <c r="U35" s="11"/>
+      <c r="V35" s="14"/>
+    </row>
+    <row r="36" spans="2:22">
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
       <c r="E36" s="12"/>
-      <c r="M36" s="4"/>
       <c r="N36" s="4"/>
-      <c r="S36" s="13"/>
-      <c r="T36" s="11"/>
-      <c r="U36" s="14"/>
-    </row>
-    <row r="37" spans="2:21">
+      <c r="O36" s="4"/>
+      <c r="T36" s="13"/>
+      <c r="U36" s="11"/>
+      <c r="V36" s="14"/>
+    </row>
+    <row r="37" spans="2:22">
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
       <c r="E37" s="12"/>
-      <c r="M37" s="4"/>
       <c r="N37" s="4"/>
-      <c r="S37" s="13"/>
-      <c r="T37" s="11"/>
-      <c r="U37" s="14"/>
-    </row>
-    <row r="38" spans="2:21">
+      <c r="O37" s="4"/>
+      <c r="T37" s="13"/>
+      <c r="U37" s="11"/>
+      <c r="V37" s="14"/>
+    </row>
+    <row r="38" spans="2:22">
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
       <c r="E38" s="12"/>
-      <c r="M38" s="4"/>
       <c r="N38" s="4"/>
-      <c r="S38" s="13"/>
-      <c r="T38" s="11"/>
-      <c r="U38" s="14"/>
-    </row>
-    <row r="39" spans="2:21">
+      <c r="O38" s="4"/>
+      <c r="T38" s="13"/>
+      <c r="U38" s="11"/>
+      <c r="V38" s="14"/>
+    </row>
+    <row r="39" spans="2:22">
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
       <c r="E39" s="12"/>
-      <c r="M39" s="4"/>
       <c r="N39" s="4"/>
-      <c r="S39" s="13"/>
-      <c r="T39" s="11"/>
-      <c r="U39" s="14"/>
-    </row>
-    <row r="40" spans="2:21">
+      <c r="O39" s="4"/>
+      <c r="T39" s="13"/>
+      <c r="U39" s="11"/>
+      <c r="V39" s="14"/>
+    </row>
+    <row r="40" spans="2:22">
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
       <c r="E40" s="12"/>
-      <c r="M40" s="4"/>
       <c r="N40" s="4"/>
-      <c r="S40" s="13"/>
-      <c r="T40" s="11"/>
-      <c r="U40" s="14"/>
-    </row>
-    <row r="41" spans="2:21">
+      <c r="O40" s="4"/>
+      <c r="T40" s="13"/>
+      <c r="U40" s="11"/>
+      <c r="V40" s="14"/>
+    </row>
+    <row r="41" spans="2:22">
       <c r="B41" s="11"/>
       <c r="C41" s="11"/>
       <c r="E41" s="12"/>
-      <c r="M41" s="4"/>
       <c r="N41" s="4"/>
-      <c r="S41" s="13"/>
-      <c r="T41" s="11"/>
-      <c r="U41" s="14"/>
-    </row>
-    <row r="42" spans="2:21">
+      <c r="O41" s="4"/>
+      <c r="T41" s="13"/>
+      <c r="U41" s="11"/>
+      <c r="V41" s="14"/>
+    </row>
+    <row r="42" spans="2:22">
       <c r="B42" s="11"/>
       <c r="C42" s="11"/>
       <c r="E42" s="12"/>
-      <c r="M42" s="4"/>
       <c r="N42" s="4"/>
-      <c r="S42" s="13"/>
-      <c r="T42" s="11"/>
-      <c r="U42" s="14"/>
-    </row>
-    <row r="43" spans="2:21">
+      <c r="O42" s="4"/>
+      <c r="T42" s="13"/>
+      <c r="U42" s="11"/>
+      <c r="V42" s="14"/>
+    </row>
+    <row r="43" spans="2:22">
       <c r="B43" s="11"/>
       <c r="C43" s="11"/>
       <c r="E43" s="12"/>
-      <c r="M43" s="4"/>
       <c r="N43" s="4"/>
-      <c r="S43" s="13"/>
-      <c r="T43" s="11"/>
-      <c r="U43" s="14"/>
-    </row>
-    <row r="44" spans="2:21">
+      <c r="O43" s="4"/>
+      <c r="T43" s="13"/>
+      <c r="U43" s="11"/>
+      <c r="V43" s="14"/>
+    </row>
+    <row r="44" spans="2:22">
       <c r="B44" s="11"/>
       <c r="C44" s="11"/>
       <c r="E44" s="12"/>
-      <c r="M44" s="4"/>
       <c r="N44" s="4"/>
-      <c r="S44" s="13"/>
-      <c r="T44" s="11"/>
-      <c r="U44" s="14"/>
-    </row>
-    <row r="45" spans="2:21">
+      <c r="O44" s="4"/>
+      <c r="T44" s="13"/>
+      <c r="U44" s="11"/>
+      <c r="V44" s="14"/>
+    </row>
+    <row r="45" spans="2:22">
       <c r="B45" s="11"/>
       <c r="C45" s="11"/>
       <c r="E45" s="12"/>
-      <c r="M45" s="4"/>
       <c r="N45" s="4"/>
-      <c r="S45" s="13"/>
-      <c r="T45" s="11"/>
-      <c r="U45" s="14"/>
-    </row>
-    <row r="46" spans="2:21">
+      <c r="O45" s="4"/>
+      <c r="T45" s="13"/>
+      <c r="U45" s="11"/>
+      <c r="V45" s="14"/>
+    </row>
+    <row r="46" spans="2:22">
       <c r="B46" s="11"/>
       <c r="C46" s="11"/>
       <c r="E46" s="12"/>
-      <c r="M46" s="4"/>
       <c r="N46" s="4"/>
-      <c r="S46" s="13"/>
-      <c r="T46" s="11"/>
-      <c r="U46" s="14"/>
-    </row>
-    <row r="47" spans="2:21">
+      <c r="O46" s="4"/>
+      <c r="T46" s="13"/>
+      <c r="U46" s="11"/>
+      <c r="V46" s="14"/>
+    </row>
+    <row r="47" spans="2:22">
       <c r="B47" s="11"/>
       <c r="C47" s="11"/>
       <c r="E47" s="12"/>
-      <c r="M47" s="4"/>
       <c r="N47" s="4"/>
-      <c r="S47" s="13"/>
-      <c r="T47" s="11"/>
-      <c r="U47" s="14"/>
-    </row>
-    <row r="48" spans="2:21">
+      <c r="O47" s="4"/>
+      <c r="T47" s="13"/>
+      <c r="U47" s="11"/>
+      <c r="V47" s="14"/>
+    </row>
+    <row r="48" spans="2:22">
       <c r="B48" s="11"/>
       <c r="C48" s="11"/>
       <c r="E48" s="12"/>
-      <c r="M48" s="4"/>
       <c r="N48" s="4"/>
-      <c r="S48" s="13"/>
-      <c r="T48" s="11"/>
-      <c r="U48" s="14"/>
-    </row>
-    <row r="49" spans="2:21">
+      <c r="O48" s="4"/>
+      <c r="T48" s="13"/>
+      <c r="U48" s="11"/>
+      <c r="V48" s="14"/>
+    </row>
+    <row r="49" spans="2:22">
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
       <c r="E49" s="12"/>
-      <c r="M49" s="4"/>
       <c r="N49" s="4"/>
-      <c r="S49" s="13"/>
-      <c r="T49" s="11"/>
-      <c r="U49" s="14"/>
-    </row>
-    <row r="50" spans="2:21">
+      <c r="O49" s="4"/>
+      <c r="T49" s="13"/>
+      <c r="U49" s="11"/>
+      <c r="V49" s="14"/>
+    </row>
+    <row r="50" spans="2:22">
       <c r="B50" s="11"/>
       <c r="C50" s="11"/>
       <c r="E50" s="12"/>
-      <c r="M50" s="4"/>
       <c r="N50" s="4"/>
-      <c r="S50" s="13"/>
-      <c r="T50" s="11"/>
-      <c r="U50" s="14"/>
-    </row>
-    <row r="51" spans="2:21">
+      <c r="O50" s="4"/>
+      <c r="T50" s="13"/>
+      <c r="U50" s="11"/>
+      <c r="V50" s="14"/>
+    </row>
+    <row r="51" spans="2:22">
       <c r="B51" s="11"/>
       <c r="C51" s="11"/>
       <c r="E51" s="12"/>
-      <c r="M51" s="4"/>
       <c r="N51" s="4"/>
-      <c r="S51" s="13"/>
-      <c r="T51" s="11"/>
-      <c r="U51" s="14"/>
-    </row>
-    <row r="52" spans="2:21">
+      <c r="O51" s="4"/>
+      <c r="T51" s="13"/>
+      <c r="U51" s="11"/>
+      <c r="V51" s="14"/>
+    </row>
+    <row r="52" spans="2:22">
       <c r="B52" s="11"/>
       <c r="C52" s="11"/>
       <c r="E52" s="12"/>
-      <c r="M52" s="4"/>
       <c r="N52" s="4"/>
-      <c r="S52" s="13"/>
-      <c r="T52" s="11"/>
-      <c r="U52" s="14"/>
-    </row>
-    <row r="53" spans="2:21">
+      <c r="O52" s="4"/>
+      <c r="T52" s="13"/>
+      <c r="U52" s="11"/>
+      <c r="V52" s="14"/>
+    </row>
+    <row r="53" spans="2:22">
       <c r="B53" s="11"/>
       <c r="C53" s="11"/>
       <c r="E53" s="12"/>
-      <c r="M53" s="4"/>
       <c r="N53" s="4"/>
-      <c r="S53" s="13"/>
-      <c r="T53" s="11"/>
-      <c r="U53" s="14"/>
-    </row>
-    <row r="54" spans="2:21">
+      <c r="O53" s="4"/>
+      <c r="T53" s="13"/>
+      <c r="U53" s="11"/>
+      <c r="V53" s="14"/>
+    </row>
+    <row r="54" spans="2:22">
       <c r="B54" s="11"/>
       <c r="C54" s="11"/>
       <c r="E54" s="12"/>
-      <c r="M54" s="4"/>
       <c r="N54" s="4"/>
-      <c r="S54" s="13"/>
-      <c r="T54" s="11"/>
-      <c r="U54" s="14"/>
-    </row>
-    <row r="55" spans="2:21">
+      <c r="O54" s="4"/>
+      <c r="T54" s="13"/>
+      <c r="U54" s="11"/>
+      <c r="V54" s="14"/>
+    </row>
+    <row r="55" spans="2:22">
       <c r="B55" s="11"/>
       <c r="C55" s="11"/>
       <c r="E55" s="12"/>
-      <c r="M55" s="4"/>
       <c r="N55" s="4"/>
-      <c r="S55" s="13"/>
-      <c r="T55" s="11"/>
-      <c r="U55" s="14"/>
-    </row>
-    <row r="56" spans="2:21">
+      <c r="O55" s="4"/>
+      <c r="T55" s="13"/>
+      <c r="U55" s="11"/>
+      <c r="V55" s="14"/>
+    </row>
+    <row r="56" spans="2:22">
       <c r="B56" s="11"/>
       <c r="C56" s="11"/>
       <c r="E56" s="12"/>
-      <c r="M56" s="4"/>
       <c r="N56" s="4"/>
-      <c r="S56" s="13"/>
-      <c r="T56" s="11"/>
-      <c r="U56" s="14"/>
-    </row>
-    <row r="57" spans="2:21">
+      <c r="O56" s="4"/>
+      <c r="T56" s="13"/>
+      <c r="U56" s="11"/>
+      <c r="V56" s="14"/>
+    </row>
+    <row r="57" spans="2:22">
       <c r="B57" s="11"/>
       <c r="C57" s="11"/>
       <c r="E57" s="12"/>
-      <c r="M57" s="4"/>
       <c r="N57" s="4"/>
-      <c r="S57" s="13"/>
-      <c r="T57" s="11"/>
-      <c r="U57" s="14"/>
-    </row>
-    <row r="58" spans="2:21">
+      <c r="O57" s="4"/>
+      <c r="T57" s="13"/>
+      <c r="U57" s="11"/>
+      <c r="V57" s="14"/>
+    </row>
+    <row r="58" spans="2:22">
       <c r="B58" s="11"/>
       <c r="C58" s="11"/>
       <c r="E58" s="12"/>
-      <c r="M58" s="4"/>
       <c r="N58" s="4"/>
-      <c r="S58" s="13"/>
-      <c r="T58" s="11"/>
-      <c r="U58" s="14"/>
-    </row>
-    <row r="59" spans="2:21">
+      <c r="O58" s="4"/>
+      <c r="T58" s="13"/>
+      <c r="U58" s="11"/>
+      <c r="V58" s="14"/>
+    </row>
+    <row r="59" spans="2:22">
       <c r="B59" s="11"/>
       <c r="C59" s="11"/>
       <c r="E59" s="12"/>
-      <c r="M59" s="4"/>
       <c r="N59" s="4"/>
-      <c r="S59" s="13"/>
-      <c r="T59" s="11"/>
-      <c r="U59" s="14"/>
-    </row>
-    <row r="60" spans="2:21">
+      <c r="O59" s="4"/>
+      <c r="T59" s="13"/>
+      <c r="U59" s="11"/>
+      <c r="V59" s="14"/>
+    </row>
+    <row r="60" spans="2:22">
       <c r="B60" s="11"/>
       <c r="C60" s="11"/>
       <c r="E60" s="12"/>
-      <c r="M60" s="4"/>
       <c r="N60" s="4"/>
-      <c r="S60" s="13"/>
-      <c r="T60" s="11"/>
-      <c r="U60" s="14"/>
-    </row>
-    <row r="61" spans="2:21">
+      <c r="O60" s="4"/>
+      <c r="T60" s="13"/>
+      <c r="U60" s="11"/>
+      <c r="V60" s="14"/>
+    </row>
+    <row r="61" spans="2:22">
       <c r="B61" s="11"/>
       <c r="C61" s="11"/>
       <c r="E61" s="12"/>
-      <c r="M61" s="4"/>
       <c r="N61" s="4"/>
-      <c r="S61" s="13"/>
-      <c r="T61" s="11"/>
-      <c r="U61" s="14"/>
-    </row>
-    <row r="62" spans="2:21">
+      <c r="O61" s="4"/>
+      <c r="T61" s="13"/>
+      <c r="U61" s="11"/>
+      <c r="V61" s="14"/>
+    </row>
+    <row r="62" spans="2:22">
       <c r="B62" s="11"/>
       <c r="C62" s="11"/>
       <c r="E62" s="12"/>
-      <c r="M62" s="4"/>
       <c r="N62" s="4"/>
-      <c r="S62" s="13"/>
-      <c r="T62" s="11"/>
-      <c r="U62" s="14"/>
-    </row>
-    <row r="63" spans="2:21">
+      <c r="O62" s="4"/>
+      <c r="T62" s="13"/>
+      <c r="U62" s="11"/>
+      <c r="V62" s="14"/>
+    </row>
+    <row r="63" spans="2:22">
       <c r="B63" s="11"/>
       <c r="C63" s="11"/>
       <c r="E63" s="12"/>
-      <c r="M63" s="4"/>
       <c r="N63" s="4"/>
-      <c r="S63" s="13"/>
-      <c r="T63" s="11"/>
-      <c r="U63" s="14"/>
-    </row>
-    <row r="64" spans="2:21">
+      <c r="O63" s="4"/>
+      <c r="T63" s="13"/>
+      <c r="U63" s="11"/>
+      <c r="V63" s="14"/>
+    </row>
+    <row r="64" spans="2:22">
       <c r="B64" s="11"/>
       <c r="C64" s="11"/>
       <c r="E64" s="12"/>
-      <c r="M64" s="4"/>
       <c r="N64" s="4"/>
-      <c r="S64" s="13"/>
-      <c r="T64" s="11"/>
-      <c r="U64" s="14"/>
-    </row>
-    <row r="65" spans="2:21">
+      <c r="O64" s="4"/>
+      <c r="T64" s="13"/>
+      <c r="U64" s="11"/>
+      <c r="V64" s="14"/>
+    </row>
+    <row r="65" spans="2:22">
       <c r="B65" s="11"/>
       <c r="C65" s="11"/>
       <c r="E65" s="12"/>
-      <c r="M65" s="4"/>
       <c r="N65" s="4"/>
-      <c r="S65" s="13"/>
-      <c r="T65" s="11"/>
-      <c r="U65" s="14"/>
-    </row>
-    <row r="66" spans="2:21">
+      <c r="O65" s="4"/>
+      <c r="T65" s="13"/>
+      <c r="U65" s="11"/>
+      <c r="V65" s="14"/>
+    </row>
+    <row r="66" spans="2:22">
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
       <c r="E66" s="12"/>
-      <c r="M66" s="4"/>
       <c r="N66" s="4"/>
-      <c r="S66" s="13"/>
-      <c r="T66" s="11"/>
-      <c r="U66" s="14"/>
-    </row>
-    <row r="67" spans="2:21">
+      <c r="O66" s="4"/>
+      <c r="T66" s="13"/>
+      <c r="U66" s="11"/>
+      <c r="V66" s="14"/>
+    </row>
+    <row r="67" spans="2:22">
       <c r="B67" s="11"/>
       <c r="C67" s="11"/>
       <c r="E67" s="12"/>
-      <c r="M67" s="4"/>
       <c r="N67" s="4"/>
-      <c r="S67" s="13"/>
-      <c r="T67" s="11"/>
-      <c r="U67" s="14"/>
-    </row>
-    <row r="68" spans="2:21">
+      <c r="O67" s="4"/>
+      <c r="T67" s="13"/>
+      <c r="U67" s="11"/>
+      <c r="V67" s="14"/>
+    </row>
+    <row r="68" spans="2:22">
       <c r="B68" s="11"/>
       <c r="C68" s="11"/>
       <c r="E68" s="12"/>
-      <c r="M68" s="4"/>
       <c r="N68" s="4"/>
-      <c r="S68" s="13"/>
-      <c r="T68" s="11"/>
-      <c r="U68" s="14"/>
-    </row>
-    <row r="69" spans="2:21">
+      <c r="O68" s="4"/>
+      <c r="T68" s="13"/>
+      <c r="U68" s="11"/>
+      <c r="V68" s="14"/>
+    </row>
+    <row r="69" spans="2:22">
       <c r="B69" s="11"/>
       <c r="C69" s="11"/>
       <c r="E69" s="12"/>
-      <c r="M69" s="4"/>
       <c r="N69" s="4"/>
-      <c r="S69" s="13"/>
-      <c r="T69" s="11"/>
-      <c r="U69" s="14"/>
-    </row>
-    <row r="70" spans="2:21">
+      <c r="O69" s="4"/>
+      <c r="T69" s="13"/>
+      <c r="U69" s="11"/>
+      <c r="V69" s="14"/>
+    </row>
+    <row r="70" spans="2:22">
       <c r="B70" s="11"/>
       <c r="C70" s="11"/>
       <c r="E70" s="12"/>
-      <c r="M70" s="4"/>
       <c r="N70" s="4"/>
-      <c r="S70" s="13"/>
-      <c r="T70" s="11"/>
-      <c r="U70" s="14"/>
-    </row>
-    <row r="71" spans="2:21">
+      <c r="O70" s="4"/>
+      <c r="T70" s="13"/>
+      <c r="U70" s="11"/>
+      <c r="V70" s="14"/>
+    </row>
+    <row r="71" spans="2:22">
       <c r="B71" s="11"/>
       <c r="C71" s="11"/>
       <c r="E71" s="12"/>
-      <c r="M71" s="4"/>
       <c r="N71" s="4"/>
-      <c r="S71" s="13"/>
-      <c r="T71" s="11"/>
-      <c r="U71" s="14"/>
-    </row>
-    <row r="72" spans="2:21">
+      <c r="O71" s="4"/>
+      <c r="T71" s="13"/>
+      <c r="U71" s="11"/>
+      <c r="V71" s="14"/>
+    </row>
+    <row r="72" spans="2:22">
       <c r="B72" s="11"/>
       <c r="C72" s="11"/>
       <c r="E72" s="12"/>
-      <c r="M72" s="4"/>
       <c r="N72" s="4"/>
-      <c r="S72" s="13"/>
-      <c r="T72" s="11"/>
-      <c r="U72" s="14"/>
-    </row>
-    <row r="73" spans="2:21">
+      <c r="O72" s="4"/>
+      <c r="T72" s="13"/>
+      <c r="U72" s="11"/>
+      <c r="V72" s="14"/>
+    </row>
+    <row r="73" spans="2:22">
       <c r="B73" s="11"/>
       <c r="C73" s="11"/>
       <c r="E73" s="12"/>
-      <c r="M73" s="4"/>
       <c r="N73" s="4"/>
-      <c r="S73" s="13"/>
-      <c r="T73" s="11"/>
-      <c r="U73" s="14"/>
-    </row>
-    <row r="74" spans="2:21">
+      <c r="O73" s="4"/>
+      <c r="T73" s="13"/>
+      <c r="U73" s="11"/>
+      <c r="V73" s="14"/>
+    </row>
+    <row r="74" spans="2:22">
       <c r="B74" s="11"/>
       <c r="C74" s="11"/>
       <c r="E74" s="12"/>
-      <c r="M74" s="4"/>
       <c r="N74" s="4"/>
-      <c r="S74" s="13"/>
-      <c r="T74" s="11"/>
-      <c r="U74" s="14"/>
-    </row>
-    <row r="75" spans="2:21">
+      <c r="O74" s="4"/>
+      <c r="T74" s="13"/>
+      <c r="U74" s="11"/>
+      <c r="V74" s="14"/>
+    </row>
+    <row r="75" spans="2:22">
       <c r="B75" s="11"/>
       <c r="C75" s="11"/>
       <c r="E75" s="12"/>
-      <c r="M75" s="4"/>
       <c r="N75" s="4"/>
-      <c r="S75" s="13"/>
-      <c r="T75" s="11"/>
-      <c r="U75" s="14"/>
-    </row>
-    <row r="76" spans="2:21">
+      <c r="O75" s="4"/>
+      <c r="T75" s="13"/>
+      <c r="U75" s="11"/>
+      <c r="V75" s="14"/>
+    </row>
+    <row r="76" spans="2:22">
       <c r="B76" s="11"/>
       <c r="C76" s="11"/>
       <c r="E76" s="12"/>
-      <c r="M76" s="4"/>
       <c r="N76" s="4"/>
-      <c r="S76" s="13"/>
-      <c r="T76" s="11"/>
-      <c r="U76" s="14"/>
-    </row>
-    <row r="77" spans="2:21">
+      <c r="O76" s="4"/>
+      <c r="T76" s="13"/>
+      <c r="U76" s="11"/>
+      <c r="V76" s="14"/>
+    </row>
+    <row r="77" spans="2:22">
       <c r="B77" s="11"/>
       <c r="C77" s="11"/>
       <c r="E77" s="12"/>
-      <c r="M77" s="4"/>
       <c r="N77" s="4"/>
-      <c r="S77" s="13"/>
-      <c r="T77" s="11"/>
-      <c r="U77" s="14"/>
-    </row>
-    <row r="78" spans="2:21">
+      <c r="O77" s="4"/>
+      <c r="T77" s="13"/>
+      <c r="U77" s="11"/>
+      <c r="V77" s="14"/>
+    </row>
+    <row r="78" spans="2:22">
       <c r="B78" s="11"/>
       <c r="C78" s="11"/>
       <c r="E78" s="12"/>
-      <c r="M78" s="4"/>
       <c r="N78" s="4"/>
-      <c r="S78" s="13"/>
-      <c r="T78" s="11"/>
-      <c r="U78" s="14"/>
-    </row>
-    <row r="79" spans="2:21">
+      <c r="O78" s="4"/>
+      <c r="T78" s="13"/>
+      <c r="U78" s="11"/>
+      <c r="V78" s="14"/>
+    </row>
+    <row r="79" spans="2:22">
       <c r="B79" s="11"/>
       <c r="C79" s="11"/>
       <c r="E79" s="12"/>
-      <c r="M79" s="4"/>
       <c r="N79" s="4"/>
-      <c r="S79" s="13"/>
-      <c r="T79" s="11"/>
-      <c r="U79" s="14"/>
-    </row>
-    <row r="80" spans="2:21">
+      <c r="O79" s="4"/>
+      <c r="T79" s="13"/>
+      <c r="U79" s="11"/>
+      <c r="V79" s="14"/>
+    </row>
+    <row r="80" spans="2:22">
       <c r="B80" s="11"/>
       <c r="C80" s="11"/>
       <c r="E80" s="12"/>
-      <c r="M80" s="4"/>
       <c r="N80" s="4"/>
-      <c r="S80" s="13"/>
-      <c r="T80" s="11"/>
-      <c r="U80" s="14"/>
-    </row>
-    <row r="81" spans="2:21">
+      <c r="O80" s="4"/>
+      <c r="T80" s="13"/>
+      <c r="U80" s="11"/>
+      <c r="V80" s="14"/>
+    </row>
+    <row r="81" spans="2:22">
       <c r="B81" s="11"/>
       <c r="C81" s="11"/>
       <c r="E81" s="12"/>
-      <c r="M81" s="4"/>
       <c r="N81" s="4"/>
-      <c r="S81" s="13"/>
-      <c r="T81" s="11"/>
-      <c r="U81" s="14"/>
-    </row>
-    <row r="82" spans="2:21">
+      <c r="O81" s="4"/>
+      <c r="T81" s="13"/>
+      <c r="U81" s="11"/>
+      <c r="V81" s="14"/>
+    </row>
+    <row r="82" spans="2:22">
       <c r="B82" s="11"/>
       <c r="C82" s="11"/>
       <c r="E82" s="12"/>
-      <c r="M82" s="4"/>
       <c r="N82" s="4"/>
-      <c r="S82" s="13"/>
-      <c r="T82" s="11"/>
-      <c r="U82" s="14"/>
-    </row>
-    <row r="83" spans="2:21">
+      <c r="O82" s="4"/>
+      <c r="T82" s="13"/>
+      <c r="U82" s="11"/>
+      <c r="V82" s="14"/>
+    </row>
+    <row r="83" spans="2:22">
       <c r="B83" s="11"/>
       <c r="C83" s="11"/>
       <c r="E83" s="12"/>
-      <c r="M83" s="4"/>
       <c r="N83" s="4"/>
-      <c r="S83" s="13"/>
-      <c r="T83" s="11"/>
-      <c r="U83" s="14"/>
-    </row>
-    <row r="84" spans="2:21">
+      <c r="O83" s="4"/>
+      <c r="T83" s="13"/>
+      <c r="U83" s="11"/>
+      <c r="V83" s="14"/>
+    </row>
+    <row r="84" spans="2:22">
       <c r="B84" s="11"/>
       <c r="C84" s="11"/>
       <c r="E84" s="12"/>
-      <c r="M84" s="4"/>
       <c r="N84" s="4"/>
-      <c r="S84" s="13"/>
-      <c r="T84" s="11"/>
-      <c r="U84" s="14"/>
-    </row>
-    <row r="85" spans="2:21">
+      <c r="O84" s="4"/>
+      <c r="T84" s="13"/>
+      <c r="U84" s="11"/>
+      <c r="V84" s="14"/>
+    </row>
+    <row r="85" spans="2:22">
       <c r="B85" s="11"/>
       <c r="C85" s="11"/>
       <c r="E85" s="12"/>
-      <c r="M85" s="4"/>
       <c r="N85" s="4"/>
-      <c r="S85" s="13"/>
-      <c r="T85" s="11"/>
-      <c r="U85" s="14"/>
-    </row>
-    <row r="86" spans="2:21">
+      <c r="O85" s="4"/>
+      <c r="T85" s="13"/>
+      <c r="U85" s="11"/>
+      <c r="V85" s="14"/>
+    </row>
+    <row r="86" spans="2:22">
       <c r="B86" s="11"/>
       <c r="C86" s="11"/>
       <c r="E86" s="12"/>
-      <c r="M86" s="4"/>
       <c r="N86" s="4"/>
-      <c r="S86" s="13"/>
-      <c r="T86" s="11"/>
-      <c r="U86" s="14"/>
-    </row>
-    <row r="87" spans="2:21">
+      <c r="O86" s="4"/>
+      <c r="T86" s="13"/>
+      <c r="U86" s="11"/>
+      <c r="V86" s="14"/>
+    </row>
+    <row r="87" spans="2:22">
       <c r="B87" s="11"/>
       <c r="C87" s="11"/>
       <c r="E87" s="12"/>
-      <c r="M87" s="4"/>
       <c r="N87" s="4"/>
-      <c r="S87" s="13"/>
-      <c r="T87" s="11"/>
-      <c r="U87" s="14"/>
-    </row>
-    <row r="88" spans="2:21">
+      <c r="O87" s="4"/>
+      <c r="T87" s="13"/>
+      <c r="U87" s="11"/>
+      <c r="V87" s="14"/>
+    </row>
+    <row r="88" spans="2:22">
       <c r="B88" s="11"/>
       <c r="C88" s="11"/>
       <c r="E88" s="12"/>
-      <c r="M88" s="4"/>
       <c r="N88" s="4"/>
-      <c r="S88" s="13"/>
-      <c r="T88" s="11"/>
-      <c r="U88" s="14"/>
-    </row>
-    <row r="89" spans="2:21">
+      <c r="O88" s="4"/>
+      <c r="T88" s="13"/>
+      <c r="U88" s="11"/>
+      <c r="V88" s="14"/>
+    </row>
+    <row r="89" spans="2:22">
       <c r="B89" s="11"/>
       <c r="C89" s="11"/>
       <c r="E89" s="12"/>
-      <c r="M89" s="4"/>
       <c r="N89" s="4"/>
-      <c r="S89" s="13"/>
-      <c r="T89" s="11"/>
-      <c r="U89" s="14"/>
-    </row>
-    <row r="90" spans="2:21">
+      <c r="O89" s="4"/>
+      <c r="T89" s="13"/>
+      <c r="U89" s="11"/>
+      <c r="V89" s="14"/>
+    </row>
+    <row r="90" spans="2:22">
       <c r="B90" s="11"/>
       <c r="C90" s="11"/>
       <c r="E90" s="12"/>
-      <c r="M90" s="4"/>
       <c r="N90" s="4"/>
-      <c r="S90" s="13"/>
-      <c r="T90" s="11"/>
-      <c r="U90" s="14"/>
-    </row>
-    <row r="91" spans="2:21">
+      <c r="O90" s="4"/>
+      <c r="T90" s="13"/>
+      <c r="U90" s="11"/>
+      <c r="V90" s="14"/>
+    </row>
+    <row r="91" spans="2:22">
       <c r="B91" s="11"/>
       <c r="C91" s="11"/>
       <c r="E91" s="12"/>
-      <c r="M91" s="4"/>
       <c r="N91" s="4"/>
-      <c r="S91" s="13"/>
-      <c r="T91" s="11"/>
-      <c r="U91" s="14"/>
-    </row>
-    <row r="92" spans="2:21">
+      <c r="O91" s="4"/>
+      <c r="T91" s="13"/>
+      <c r="U91" s="11"/>
+      <c r="V91" s="14"/>
+    </row>
+    <row r="92" spans="2:22">
       <c r="B92" s="11"/>
       <c r="C92" s="11"/>
       <c r="E92" s="12"/>
-      <c r="M92" s="4"/>
       <c r="N92" s="4"/>
-      <c r="S92" s="13"/>
-      <c r="T92" s="11"/>
-      <c r="U92" s="14"/>
-    </row>
-    <row r="93" spans="2:21">
+      <c r="O92" s="4"/>
+      <c r="T92" s="13"/>
+      <c r="U92" s="11"/>
+      <c r="V92" s="14"/>
+    </row>
+    <row r="93" spans="2:22">
       <c r="B93" s="11"/>
       <c r="C93" s="11"/>
       <c r="E93" s="12"/>
-      <c r="M93" s="4"/>
       <c r="N93" s="4"/>
-      <c r="S93" s="13"/>
-      <c r="T93" s="11"/>
-      <c r="U93" s="14"/>
-    </row>
-    <row r="94" spans="2:21">
+      <c r="O93" s="4"/>
+      <c r="T93" s="13"/>
+      <c r="U93" s="11"/>
+      <c r="V93" s="14"/>
+    </row>
+    <row r="94" spans="2:22">
       <c r="B94" s="11"/>
       <c r="C94" s="11"/>
       <c r="E94" s="12"/>
-      <c r="M94" s="4"/>
       <c r="N94" s="4"/>
-      <c r="S94" s="13"/>
-      <c r="T94" s="11"/>
-      <c r="U94" s="14"/>
-    </row>
-    <row r="95" spans="2:21">
+      <c r="O94" s="4"/>
+      <c r="T94" s="13"/>
+      <c r="U94" s="11"/>
+      <c r="V94" s="14"/>
+    </row>
+    <row r="95" spans="2:22">
       <c r="B95" s="11"/>
       <c r="C95" s="11"/>
       <c r="E95" s="12"/>
-      <c r="M95" s="4"/>
       <c r="N95" s="4"/>
-      <c r="S95" s="13"/>
-      <c r="T95" s="11"/>
-      <c r="U95" s="14"/>
-    </row>
-    <row r="96" spans="2:21">
+      <c r="O95" s="4"/>
+      <c r="T95" s="13"/>
+      <c r="U95" s="11"/>
+      <c r="V95" s="14"/>
+    </row>
+    <row r="96" spans="2:22">
       <c r="B96" s="11"/>
       <c r="C96" s="11"/>
       <c r="E96" s="12"/>
-      <c r="M96" s="4"/>
       <c r="N96" s="4"/>
-      <c r="S96" s="13"/>
-      <c r="T96" s="11"/>
-      <c r="U96" s="14"/>
-    </row>
-    <row r="97" spans="2:21">
+      <c r="O96" s="4"/>
+      <c r="T96" s="13"/>
+      <c r="U96" s="11"/>
+      <c r="V96" s="14"/>
+    </row>
+    <row r="97" spans="2:22">
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
       <c r="E97" s="12"/>
-      <c r="M97" s="4"/>
       <c r="N97" s="4"/>
-      <c r="S97" s="13"/>
-      <c r="T97" s="11"/>
-      <c r="U97" s="14"/>
-    </row>
-    <row r="98" spans="2:21">
+      <c r="O97" s="4"/>
+      <c r="T97" s="13"/>
+      <c r="U97" s="11"/>
+      <c r="V97" s="14"/>
+    </row>
+    <row r="98" spans="2:22">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
       <c r="E98" s="12"/>
-      <c r="M98" s="4"/>
       <c r="N98" s="4"/>
-      <c r="S98" s="13"/>
-      <c r="T98" s="11"/>
-      <c r="U98" s="14"/>
-    </row>
-    <row r="99" spans="2:21">
+      <c r="O98" s="4"/>
+      <c r="T98" s="13"/>
+      <c r="U98" s="11"/>
+      <c r="V98" s="14"/>
+    </row>
+    <row r="99" spans="2:22">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
       <c r="E99" s="12"/>
-      <c r="M99" s="4"/>
       <c r="N99" s="4"/>
-      <c r="S99" s="13"/>
-      <c r="T99" s="11"/>
-      <c r="U99" s="14"/>
-    </row>
-    <row r="100" spans="2:21">
+      <c r="O99" s="4"/>
+      <c r="T99" s="13"/>
+      <c r="U99" s="11"/>
+      <c r="V99" s="14"/>
+    </row>
+    <row r="100" spans="2:22">
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="E100" s="12"/>
-      <c r="M100" s="4"/>
       <c r="N100" s="4"/>
-      <c r="S100" s="13"/>
-      <c r="T100" s="11"/>
-      <c r="U100" s="14"/>
-    </row>
-    <row r="101" spans="2:21">
+      <c r="O100" s="4"/>
+      <c r="T100" s="13"/>
+      <c r="U100" s="11"/>
+      <c r="V100" s="14"/>
+    </row>
+    <row r="101" spans="2:22">
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="E101" s="12"/>
-      <c r="M101" s="4"/>
       <c r="N101" s="4"/>
-      <c r="S101" s="13"/>
-      <c r="T101" s="11"/>
-      <c r="U101" s="14"/>
-    </row>
-    <row r="102" spans="2:21">
+      <c r="O101" s="4"/>
+      <c r="T101" s="13"/>
+      <c r="U101" s="11"/>
+      <c r="V101" s="14"/>
+    </row>
+    <row r="102" spans="2:22">
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="E102" s="12"/>
-      <c r="M102" s="4"/>
       <c r="N102" s="4"/>
-      <c r="S102" s="13"/>
-      <c r="T102" s="11"/>
-      <c r="U102" s="14"/>
-    </row>
-    <row r="103" spans="2:21">
+      <c r="O102" s="4"/>
+      <c r="T102" s="13"/>
+      <c r="U102" s="11"/>
+      <c r="V102" s="14"/>
+    </row>
+    <row r="103" spans="2:22">
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="E103" s="12"/>
-      <c r="M103" s="4"/>
       <c r="N103" s="4"/>
-      <c r="S103" s="13"/>
-      <c r="T103" s="11"/>
-      <c r="U103" s="14"/>
-    </row>
-    <row r="104" spans="2:21">
+      <c r="O103" s="4"/>
+      <c r="T103" s="13"/>
+      <c r="U103" s="11"/>
+      <c r="V103" s="14"/>
+    </row>
+    <row r="104" spans="2:22">
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="E104" s="12"/>
-      <c r="M104" s="4"/>
       <c r="N104" s="4"/>
-      <c r="S104" s="13"/>
-      <c r="T104" s="11"/>
-      <c r="U104" s="14"/>
-    </row>
-    <row r="105" spans="2:21">
+      <c r="O104" s="4"/>
+      <c r="T104" s="13"/>
+      <c r="U104" s="11"/>
+      <c r="V104" s="14"/>
+    </row>
+    <row r="105" spans="2:22">
       <c r="B105" s="11"/>
       <c r="C105" s="11"/>
       <c r="E105" s="12"/>
-      <c r="M105" s="4"/>
       <c r="N105" s="4"/>
-      <c r="S105" s="13"/>
-      <c r="T105" s="11"/>
-      <c r="U105" s="14"/>
-    </row>
-    <row r="106" spans="2:21">
+      <c r="O105" s="4"/>
+      <c r="T105" s="13"/>
+      <c r="U105" s="11"/>
+      <c r="V105" s="14"/>
+    </row>
+    <row r="106" spans="2:22">
       <c r="B106" s="11"/>
       <c r="C106" s="11"/>
       <c r="E106" s="12"/>
-      <c r="M106" s="4"/>
       <c r="N106" s="4"/>
-      <c r="S106" s="13"/>
-      <c r="T106" s="11"/>
-      <c r="U106" s="14"/>
-    </row>
-    <row r="107" spans="2:21">
+      <c r="O106" s="4"/>
+      <c r="T106" s="13"/>
+      <c r="U106" s="11"/>
+      <c r="V106" s="14"/>
+    </row>
+    <row r="107" spans="2:22">
       <c r="B107" s="11"/>
       <c r="C107" s="11"/>
       <c r="E107" s="12"/>
-      <c r="M107" s="4"/>
       <c r="N107" s="4"/>
-      <c r="S107" s="13"/>
-      <c r="T107" s="11"/>
-      <c r="U107" s="14"/>
-    </row>
-    <row r="108" spans="2:21">
+      <c r="O107" s="4"/>
+      <c r="T107" s="13"/>
+      <c r="U107" s="11"/>
+      <c r="V107" s="14"/>
+    </row>
+    <row r="108" spans="2:22">
       <c r="B108" s="11"/>
       <c r="C108" s="11"/>
       <c r="E108" s="12"/>
-      <c r="M108" s="4"/>
       <c r="N108" s="4"/>
-      <c r="S108" s="13"/>
-      <c r="T108" s="11"/>
-      <c r="U108" s="14"/>
-    </row>
-    <row r="109" spans="2:21">
+      <c r="O108" s="4"/>
+      <c r="T108" s="13"/>
+      <c r="U108" s="11"/>
+      <c r="V108" s="14"/>
+    </row>
+    <row r="109" spans="2:22">
       <c r="B109" s="11"/>
       <c r="C109" s="11"/>
       <c r="E109" s="12"/>
-      <c r="M109" s="4"/>
       <c r="N109" s="4"/>
-      <c r="S109" s="13"/>
-      <c r="T109" s="11"/>
-      <c r="U109" s="14"/>
-    </row>
-    <row r="110" spans="2:21">
+      <c r="O109" s="4"/>
+      <c r="T109" s="13"/>
+      <c r="U109" s="11"/>
+      <c r="V109" s="14"/>
+    </row>
+    <row r="110" spans="2:22">
       <c r="B110" s="11"/>
       <c r="C110" s="11"/>
       <c r="E110" s="12"/>
-      <c r="M110" s="4"/>
       <c r="N110" s="4"/>
-      <c r="S110" s="13"/>
-      <c r="T110" s="11"/>
-      <c r="U110" s="14"/>
-    </row>
-    <row r="111" spans="2:21">
+      <c r="O110" s="4"/>
+      <c r="T110" s="13"/>
+      <c r="U110" s="11"/>
+      <c r="V110" s="14"/>
+    </row>
+    <row r="111" spans="2:22">
       <c r="B111" s="11"/>
       <c r="C111" s="11"/>
       <c r="E111" s="12"/>
-      <c r="M111" s="4"/>
       <c r="N111" s="4"/>
-      <c r="S111" s="13"/>
-      <c r="T111" s="11"/>
-      <c r="U111" s="14"/>
-    </row>
-    <row r="112" spans="2:21">
+      <c r="O111" s="4"/>
+      <c r="T111" s="13"/>
+      <c r="U111" s="11"/>
+      <c r="V111" s="14"/>
+    </row>
+    <row r="112" spans="2:22">
       <c r="B112" s="11"/>
       <c r="C112" s="11"/>
       <c r="E112" s="12"/>
-      <c r="M112" s="4"/>
       <c r="N112" s="4"/>
-      <c r="S112" s="13"/>
-      <c r="T112" s="11"/>
-      <c r="U112" s="14"/>
-    </row>
-    <row r="113" spans="2:21">
+      <c r="O112" s="4"/>
+      <c r="T112" s="13"/>
+      <c r="U112" s="11"/>
+      <c r="V112" s="14"/>
+    </row>
+    <row r="113" spans="2:22">
       <c r="B113" s="11"/>
       <c r="C113" s="11"/>
       <c r="E113" s="12"/>
-      <c r="M113" s="4"/>
       <c r="N113" s="4"/>
-      <c r="S113" s="13"/>
-      <c r="T113" s="11"/>
-      <c r="U113" s="14"/>
-    </row>
-    <row r="114" spans="2:21">
+      <c r="O113" s="4"/>
+      <c r="T113" s="13"/>
+      <c r="U113" s="11"/>
+      <c r="V113" s="14"/>
+    </row>
+    <row r="114" spans="2:22">
       <c r="B114" s="11"/>
       <c r="C114" s="11"/>
       <c r="E114" s="12"/>
-      <c r="M114" s="4"/>
       <c r="N114" s="4"/>
-      <c r="S114" s="13"/>
-      <c r="T114" s="11"/>
-      <c r="U114" s="14"/>
-    </row>
-    <row r="115" spans="2:21">
+      <c r="O114" s="4"/>
+      <c r="T114" s="13"/>
+      <c r="U114" s="11"/>
+      <c r="V114" s="14"/>
+    </row>
+    <row r="115" spans="2:22">
       <c r="B115" s="11"/>
       <c r="C115" s="11"/>
       <c r="E115" s="12"/>
-      <c r="M115" s="4"/>
       <c r="N115" s="4"/>
-      <c r="S115" s="13"/>
-      <c r="T115" s="11"/>
-      <c r="U115" s="14"/>
-    </row>
-    <row r="116" spans="2:21">
+      <c r="O115" s="4"/>
+      <c r="T115" s="13"/>
+      <c r="U115" s="11"/>
+      <c r="V115" s="14"/>
+    </row>
+    <row r="116" spans="2:22">
       <c r="B116" s="11"/>
       <c r="C116" s="11"/>
       <c r="E116" s="12"/>
-      <c r="M116" s="4"/>
       <c r="N116" s="4"/>
-      <c r="S116" s="13"/>
-      <c r="T116" s="11"/>
-      <c r="U116" s="14"/>
-    </row>
-    <row r="117" spans="2:21">
+      <c r="O116" s="4"/>
+      <c r="T116" s="13"/>
+      <c r="U116" s="11"/>
+      <c r="V116" s="14"/>
+    </row>
+    <row r="117" spans="2:22">
       <c r="B117" s="11"/>
       <c r="C117" s="11"/>
       <c r="E117" s="12"/>
-      <c r="M117" s="4"/>
       <c r="N117" s="4"/>
-      <c r="S117" s="13"/>
-      <c r="T117" s="11"/>
-      <c r="U117" s="14"/>
-    </row>
-    <row r="118" spans="2:21">
+      <c r="O117" s="4"/>
+      <c r="T117" s="13"/>
+      <c r="U117" s="11"/>
+      <c r="V117" s="14"/>
+    </row>
+    <row r="118" spans="2:22">
       <c r="B118" s="11"/>
       <c r="C118" s="11"/>
       <c r="E118" s="12"/>
-      <c r="M118" s="4"/>
       <c r="N118" s="4"/>
-      <c r="S118" s="13"/>
-      <c r="T118" s="11"/>
-      <c r="U118" s="14"/>
-    </row>
-    <row r="119" spans="2:21">
+      <c r="O118" s="4"/>
+      <c r="T118" s="13"/>
+      <c r="U118" s="11"/>
+      <c r="V118" s="14"/>
+    </row>
+    <row r="119" spans="2:22">
       <c r="B119" s="11"/>
       <c r="C119" s="11"/>
       <c r="E119" s="12"/>
-      <c r="M119" s="4"/>
       <c r="N119" s="4"/>
-      <c r="S119" s="13"/>
-      <c r="T119" s="11"/>
-      <c r="U119" s="14"/>
-    </row>
-    <row r="120" spans="2:21">
+      <c r="O119" s="4"/>
+      <c r="T119" s="13"/>
+      <c r="U119" s="11"/>
+      <c r="V119" s="14"/>
+    </row>
+    <row r="120" spans="2:22">
       <c r="B120" s="11"/>
       <c r="C120" s="11"/>
       <c r="E120" s="12"/>
-      <c r="M120" s="4"/>
       <c r="N120" s="4"/>
-      <c r="S120" s="13"/>
-      <c r="T120" s="11"/>
-      <c r="U120" s="14"/>
-    </row>
-    <row r="121" spans="2:21">
+      <c r="O120" s="4"/>
+      <c r="T120" s="13"/>
+      <c r="U120" s="11"/>
+      <c r="V120" s="14"/>
+    </row>
+    <row r="121" spans="2:22">
       <c r="B121" s="11"/>
       <c r="C121" s="11"/>
       <c r="E121" s="12"/>
-      <c r="M121" s="4"/>
       <c r="N121" s="4"/>
-      <c r="S121" s="13"/>
-      <c r="T121" s="11"/>
-      <c r="U121" s="14"/>
-    </row>
-    <row r="122" spans="2:21">
+      <c r="O121" s="4"/>
+      <c r="T121" s="13"/>
+      <c r="U121" s="11"/>
+      <c r="V121" s="14"/>
+    </row>
+    <row r="122" spans="2:22">
       <c r="B122" s="11"/>
       <c r="C122" s="11"/>
       <c r="E122" s="12"/>
-      <c r="M122" s="4"/>
       <c r="N122" s="4"/>
-      <c r="S122" s="13"/>
-      <c r="T122" s="11"/>
-      <c r="U122" s="14"/>
-    </row>
-    <row r="123" spans="2:21">
+      <c r="O122" s="4"/>
+      <c r="T122" s="13"/>
+      <c r="U122" s="11"/>
+      <c r="V122" s="14"/>
+    </row>
+    <row r="123" spans="2:22">
       <c r="B123" s="11"/>
       <c r="C123" s="11"/>
       <c r="E123" s="12"/>
-      <c r="M123" s="4"/>
       <c r="N123" s="4"/>
-      <c r="S123" s="13"/>
-      <c r="T123" s="11"/>
-      <c r="U123" s="14"/>
-    </row>
-    <row r="124" spans="2:21">
+      <c r="O123" s="4"/>
+      <c r="T123" s="13"/>
+      <c r="U123" s="11"/>
+      <c r="V123" s="14"/>
+    </row>
+    <row r="124" spans="2:22">
       <c r="B124" s="11"/>
       <c r="C124" s="11"/>
       <c r="E124" s="12"/>
-      <c r="M124" s="4"/>
       <c r="N124" s="4"/>
-      <c r="S124" s="13"/>
-      <c r="T124" s="11"/>
-      <c r="U124" s="14"/>
-    </row>
-    <row r="125" spans="2:21">
+      <c r="O124" s="4"/>
+      <c r="T124" s="13"/>
+      <c r="U124" s="11"/>
+      <c r="V124" s="14"/>
+    </row>
+    <row r="125" spans="2:22">
       <c r="B125" s="11"/>
       <c r="C125" s="11"/>
       <c r="E125" s="12"/>
-      <c r="M125" s="4"/>
       <c r="N125" s="4"/>
-      <c r="S125" s="13"/>
-      <c r="T125" s="11"/>
-      <c r="U125" s="14"/>
-    </row>
-    <row r="126" spans="2:21">
+      <c r="O125" s="4"/>
+      <c r="T125" s="13"/>
+      <c r="U125" s="11"/>
+      <c r="V125" s="14"/>
+    </row>
+    <row r="126" spans="2:22">
       <c r="B126" s="11"/>
       <c r="C126" s="11"/>
       <c r="E126" s="12"/>
-      <c r="M126" s="4"/>
       <c r="N126" s="4"/>
-      <c r="S126" s="13"/>
-      <c r="T126" s="11"/>
-      <c r="U126" s="14"/>
-    </row>
-    <row r="127" spans="2:21">
+      <c r="O126" s="4"/>
+      <c r="T126" s="13"/>
+      <c r="U126" s="11"/>
+      <c r="V126" s="14"/>
+    </row>
+    <row r="127" spans="2:22">
       <c r="B127" s="11"/>
       <c r="C127" s="11"/>
       <c r="E127" s="12"/>
-      <c r="M127" s="4"/>
       <c r="N127" s="4"/>
-      <c r="S127" s="13"/>
-      <c r="T127" s="11"/>
-      <c r="U127" s="14"/>
-    </row>
-    <row r="128" spans="2:21">
+      <c r="O127" s="4"/>
+      <c r="T127" s="13"/>
+      <c r="U127" s="11"/>
+      <c r="V127" s="14"/>
+    </row>
+    <row r="128" spans="2:22">
       <c r="B128" s="11"/>
       <c r="C128" s="11"/>
       <c r="E128" s="12"/>
-      <c r="M128" s="4"/>
       <c r="N128" s="4"/>
-      <c r="S128" s="13"/>
-      <c r="T128" s="11"/>
-      <c r="U128" s="14"/>
-    </row>
-    <row r="129" spans="2:21">
+      <c r="O128" s="4"/>
+      <c r="T128" s="13"/>
+      <c r="U128" s="11"/>
+      <c r="V128" s="14"/>
+    </row>
+    <row r="129" spans="2:22">
       <c r="B129" s="11"/>
       <c r="C129" s="11"/>
       <c r="E129" s="12"/>
-      <c r="M129" s="4"/>
       <c r="N129" s="4"/>
-      <c r="S129" s="13"/>
-      <c r="T129" s="11"/>
-      <c r="U129" s="14"/>
-    </row>
-    <row r="130" spans="2:21">
+      <c r="O129" s="4"/>
+      <c r="T129" s="13"/>
+      <c r="U129" s="11"/>
+      <c r="V129" s="14"/>
+    </row>
+    <row r="130" spans="2:22">
       <c r="B130" s="11"/>
       <c r="C130" s="11"/>
       <c r="E130" s="12"/>
-      <c r="M130" s="4"/>
       <c r="N130" s="4"/>
-      <c r="S130" s="13"/>
-      <c r="T130" s="11"/>
-      <c r="U130" s="14"/>
-    </row>
-    <row r="131" spans="2:21">
+      <c r="O130" s="4"/>
+      <c r="T130" s="13"/>
+      <c r="U130" s="11"/>
+      <c r="V130" s="14"/>
+    </row>
+    <row r="131" spans="2:22">
       <c r="B131" s="11"/>
       <c r="C131" s="11"/>
       <c r="E131" s="12"/>
-      <c r="M131" s="4"/>
       <c r="N131" s="4"/>
-      <c r="S131" s="13"/>
-      <c r="T131" s="11"/>
-      <c r="U131" s="14"/>
-    </row>
-    <row r="132" spans="2:21">
+      <c r="O131" s="4"/>
+      <c r="T131" s="13"/>
+      <c r="U131" s="11"/>
+      <c r="V131" s="14"/>
+    </row>
+    <row r="132" spans="2:22">
       <c r="B132" s="11"/>
       <c r="C132" s="11"/>
       <c r="E132" s="12"/>
-      <c r="M132" s="4"/>
       <c r="N132" s="4"/>
-      <c r="S132" s="13"/>
-      <c r="T132" s="11"/>
-      <c r="U132" s="14"/>
-    </row>
-    <row r="133" spans="2:21">
+      <c r="O132" s="4"/>
+      <c r="T132" s="13"/>
+      <c r="U132" s="11"/>
+      <c r="V132" s="14"/>
+    </row>
+    <row r="133" spans="2:22">
       <c r="B133" s="11"/>
       <c r="C133" s="11"/>
       <c r="E133" s="12"/>
-      <c r="M133" s="4"/>
       <c r="N133" s="4"/>
-      <c r="S133" s="13"/>
-      <c r="T133" s="11"/>
-      <c r="U133" s="14"/>
-    </row>
-    <row r="134" spans="2:21">
+      <c r="O133" s="4"/>
+      <c r="T133" s="13"/>
+      <c r="U133" s="11"/>
+      <c r="V133" s="14"/>
+    </row>
+    <row r="134" spans="2:22">
       <c r="B134" s="11"/>
       <c r="C134" s="11"/>
       <c r="E134" s="12"/>
-      <c r="M134" s="4"/>
       <c r="N134" s="4"/>
-      <c r="S134" s="13"/>
-      <c r="T134" s="11"/>
-      <c r="U134" s="14"/>
-    </row>
-    <row r="135" spans="2:21">
+      <c r="O134" s="4"/>
+      <c r="T134" s="13"/>
+      <c r="U134" s="11"/>
+      <c r="V134" s="14"/>
+    </row>
+    <row r="135" spans="2:22">
       <c r="B135" s="11"/>
       <c r="C135" s="11"/>
       <c r="E135" s="12"/>
-      <c r="M135" s="4"/>
       <c r="N135" s="4"/>
-      <c r="S135" s="13"/>
-      <c r="T135" s="11"/>
-      <c r="U135" s="14"/>
-    </row>
-    <row r="136" spans="2:21">
+      <c r="O135" s="4"/>
+      <c r="T135" s="13"/>
+      <c r="U135" s="11"/>
+      <c r="V135" s="14"/>
+    </row>
+    <row r="136" spans="2:22">
       <c r="B136" s="11"/>
       <c r="C136" s="11"/>
       <c r="E136" s="12"/>
-      <c r="M136" s="4"/>
       <c r="N136" s="4"/>
-      <c r="S136" s="13"/>
-      <c r="T136" s="11"/>
-      <c r="U136" s="14"/>
-    </row>
-    <row r="137" spans="2:21">
+      <c r="O136" s="4"/>
+      <c r="T136" s="13"/>
+      <c r="U136" s="11"/>
+      <c r="V136" s="14"/>
+    </row>
+    <row r="137" spans="2:22">
       <c r="B137" s="11"/>
       <c r="C137" s="11"/>
       <c r="E137" s="12"/>
-      <c r="M137" s="4"/>
       <c r="N137" s="4"/>
-      <c r="S137" s="13"/>
-      <c r="T137" s="11"/>
-      <c r="U137" s="14"/>
-    </row>
-    <row r="138" spans="2:21">
+      <c r="O137" s="4"/>
+      <c r="T137" s="13"/>
+      <c r="U137" s="11"/>
+      <c r="V137" s="14"/>
+    </row>
+    <row r="138" spans="2:22">
       <c r="B138" s="11"/>
       <c r="C138" s="11"/>
       <c r="E138" s="12"/>
-      <c r="M138" s="4"/>
       <c r="N138" s="4"/>
-      <c r="S138" s="13"/>
-      <c r="T138" s="11"/>
-      <c r="U138" s="14"/>
-    </row>
-    <row r="139" spans="2:21">
+      <c r="O138" s="4"/>
+      <c r="T138" s="13"/>
+      <c r="U138" s="11"/>
+      <c r="V138" s="14"/>
+    </row>
+    <row r="139" spans="2:22">
       <c r="B139" s="11"/>
       <c r="C139" s="11"/>
       <c r="E139" s="12"/>
-      <c r="M139" s="4"/>
       <c r="N139" s="4"/>
-      <c r="S139" s="13"/>
-      <c r="T139" s="11"/>
-      <c r="U139" s="14"/>
-    </row>
-    <row r="140" spans="2:21">
+      <c r="O139" s="4"/>
+      <c r="T139" s="13"/>
+      <c r="U139" s="11"/>
+      <c r="V139" s="14"/>
+    </row>
+    <row r="140" spans="2:22">
       <c r="B140" s="11"/>
       <c r="C140" s="11"/>
       <c r="E140" s="12"/>
-      <c r="M140" s="4"/>
       <c r="N140" s="4"/>
-      <c r="S140" s="13"/>
-      <c r="T140" s="11"/>
-      <c r="U140" s="14"/>
-    </row>
-    <row r="141" spans="2:21">
+      <c r="O140" s="4"/>
+      <c r="T140" s="13"/>
+      <c r="U140" s="11"/>
+      <c r="V140" s="14"/>
+    </row>
+    <row r="141" spans="2:22">
       <c r="B141" s="11"/>
       <c r="C141" s="11"/>
       <c r="E141" s="12"/>
-      <c r="M141" s="4"/>
       <c r="N141" s="4"/>
-      <c r="S141" s="13"/>
-      <c r="T141" s="11"/>
-      <c r="U141" s="14"/>
-    </row>
-    <row r="142" spans="2:21">
+      <c r="O141" s="4"/>
+      <c r="T141" s="13"/>
+      <c r="U141" s="11"/>
+      <c r="V141" s="14"/>
+    </row>
+    <row r="142" spans="2:22">
       <c r="B142" s="11"/>
       <c r="C142" s="11"/>
       <c r="E142" s="12"/>
-      <c r="M142" s="4"/>
       <c r="N142" s="4"/>
-      <c r="S142" s="13"/>
-      <c r="T142" s="11"/>
-      <c r="U142" s="14"/>
-    </row>
-    <row r="143" spans="2:21">
+      <c r="O142" s="4"/>
+      <c r="T142" s="13"/>
+      <c r="U142" s="11"/>
+      <c r="V142" s="14"/>
+    </row>
+    <row r="143" spans="2:22">
       <c r="B143" s="11"/>
       <c r="C143" s="11"/>
       <c r="E143" s="12"/>
-      <c r="M143" s="4"/>
       <c r="N143" s="4"/>
-      <c r="S143" s="13"/>
-      <c r="T143" s="11"/>
-      <c r="U143" s="14"/>
-    </row>
-    <row r="144" spans="2:21">
+      <c r="O143" s="4"/>
+      <c r="T143" s="13"/>
+      <c r="U143" s="11"/>
+      <c r="V143" s="14"/>
+    </row>
+    <row r="144" spans="2:22">
       <c r="B144" s="11"/>
       <c r="C144" s="11"/>
       <c r="E144" s="12"/>
-      <c r="M144" s="4"/>
       <c r="N144" s="4"/>
-      <c r="S144" s="13"/>
-      <c r="T144" s="11"/>
-      <c r="U144" s="14"/>
-    </row>
-    <row r="145" spans="2:21">
+      <c r="O144" s="4"/>
+      <c r="T144" s="13"/>
+      <c r="U144" s="11"/>
+      <c r="V144" s="14"/>
+    </row>
+    <row r="145" spans="2:22">
       <c r="B145" s="11"/>
       <c r="C145" s="11"/>
       <c r="E145" s="12"/>
-      <c r="M145" s="4"/>
       <c r="N145" s="4"/>
-      <c r="S145" s="13"/>
-      <c r="T145" s="11"/>
-      <c r="U145" s="14"/>
-    </row>
-    <row r="146" spans="2:21">
+      <c r="O145" s="4"/>
+      <c r="T145" s="13"/>
+      <c r="U145" s="11"/>
+      <c r="V145" s="14"/>
+    </row>
+    <row r="146" spans="2:22">
       <c r="B146" s="11"/>
       <c r="C146" s="11"/>
       <c r="E146" s="12"/>
-      <c r="M146" s="4"/>
       <c r="N146" s="4"/>
-      <c r="S146" s="13"/>
-      <c r="T146" s="11"/>
-      <c r="U146" s="14"/>
-    </row>
-    <row r="147" spans="2:21">
+      <c r="O146" s="4"/>
+      <c r="T146" s="13"/>
+      <c r="U146" s="11"/>
+      <c r="V146" s="14"/>
+    </row>
+    <row r="147" spans="2:22">
       <c r="B147" s="11"/>
       <c r="C147" s="11"/>
       <c r="E147" s="12"/>
-      <c r="M147" s="4"/>
       <c r="N147" s="4"/>
-      <c r="S147" s="13"/>
-      <c r="T147" s="11"/>
-      <c r="U147" s="14"/>
-    </row>
-    <row r="148" spans="2:21">
+      <c r="O147" s="4"/>
+      <c r="T147" s="13"/>
+      <c r="U147" s="11"/>
+      <c r="V147" s="14"/>
+    </row>
+    <row r="148" spans="2:22">
       <c r="B148" s="11"/>
       <c r="C148" s="11"/>
       <c r="E148" s="12"/>
-      <c r="M148" s="4"/>
       <c r="N148" s="4"/>
-      <c r="S148" s="13"/>
-      <c r="T148" s="11"/>
-      <c r="U148" s="14"/>
-    </row>
-    <row r="149" spans="2:21">
+      <c r="O148" s="4"/>
+      <c r="T148" s="13"/>
+      <c r="U148" s="11"/>
+      <c r="V148" s="14"/>
+    </row>
+    <row r="149" spans="2:22">
       <c r="B149" s="11"/>
       <c r="C149" s="11"/>
       <c r="E149" s="12"/>
-      <c r="M149" s="4"/>
       <c r="N149" s="4"/>
-      <c r="S149" s="13"/>
-      <c r="T149" s="11"/>
-      <c r="U149" s="14"/>
-    </row>
-    <row r="150" spans="2:21">
+      <c r="O149" s="4"/>
+      <c r="T149" s="13"/>
+      <c r="U149" s="11"/>
+      <c r="V149" s="14"/>
+    </row>
+    <row r="150" spans="2:22">
       <c r="B150" s="11"/>
       <c r="C150" s="11"/>
       <c r="E150" s="12"/>
-      <c r="M150" s="4"/>
       <c r="N150" s="4"/>
-      <c r="S150" s="13"/>
-      <c r="T150" s="11"/>
-      <c r="U150" s="14"/>
-    </row>
-    <row r="151" spans="2:21">
+      <c r="O150" s="4"/>
+      <c r="T150" s="13"/>
+      <c r="U150" s="11"/>
+      <c r="V150" s="14"/>
+    </row>
+    <row r="151" spans="2:22">
       <c r="B151" s="11"/>
       <c r="C151" s="11"/>
       <c r="E151" s="12"/>
-      <c r="M151" s="4"/>
       <c r="N151" s="4"/>
-      <c r="S151" s="13"/>
-      <c r="T151" s="11"/>
-      <c r="U151" s="14"/>
-    </row>
-    <row r="152" spans="2:21">
+      <c r="O151" s="4"/>
+      <c r="T151" s="13"/>
+      <c r="U151" s="11"/>
+      <c r="V151" s="14"/>
+    </row>
+    <row r="152" spans="2:22">
       <c r="B152" s="11"/>
       <c r="C152" s="11"/>
       <c r="E152" s="12"/>
-      <c r="M152" s="4"/>
       <c r="N152" s="4"/>
-      <c r="S152" s="13"/>
-      <c r="T152" s="11"/>
-      <c r="U152" s="14"/>
-    </row>
-    <row r="153" spans="2:21">
+      <c r="O152" s="4"/>
+      <c r="T152" s="13"/>
+      <c r="U152" s="11"/>
+      <c r="V152" s="14"/>
+    </row>
+    <row r="153" spans="2:22">
       <c r="B153" s="11"/>
       <c r="C153" s="11"/>
       <c r="E153" s="12"/>
-      <c r="M153" s="4"/>
       <c r="N153" s="4"/>
-      <c r="S153" s="13"/>
-      <c r="T153" s="11"/>
-      <c r="U153" s="14"/>
-    </row>
-    <row r="154" spans="2:21">
+      <c r="O153" s="4"/>
+      <c r="T153" s="13"/>
+      <c r="U153" s="11"/>
+      <c r="V153" s="14"/>
+    </row>
+    <row r="154" spans="2:22">
       <c r="B154" s="11"/>
       <c r="C154" s="11"/>
       <c r="E154" s="12"/>
-      <c r="M154" s="4"/>
       <c r="N154" s="4"/>
-      <c r="S154" s="13"/>
-      <c r="T154" s="11"/>
-      <c r="U154" s="14"/>
-    </row>
-    <row r="155" spans="2:21">
+      <c r="O154" s="4"/>
+      <c r="T154" s="13"/>
+      <c r="U154" s="11"/>
+      <c r="V154" s="14"/>
+    </row>
+    <row r="155" spans="2:22">
       <c r="B155" s="11"/>
       <c r="C155" s="11"/>
       <c r="E155" s="12"/>
-      <c r="M155" s="4"/>
       <c r="N155" s="4"/>
-      <c r="S155" s="13"/>
-      <c r="T155" s="11"/>
-      <c r="U155" s="14"/>
-    </row>
-    <row r="156" spans="2:21">
+      <c r="O155" s="4"/>
+      <c r="T155" s="13"/>
+      <c r="U155" s="11"/>
+      <c r="V155" s="14"/>
+    </row>
+    <row r="156" spans="2:22">
       <c r="B156" s="11"/>
       <c r="C156" s="11"/>
       <c r="E156" s="12"/>
-      <c r="M156" s="4"/>
       <c r="N156" s="4"/>
-      <c r="S156" s="13"/>
-      <c r="T156" s="11"/>
-      <c r="U156" s="14"/>
-    </row>
-    <row r="157" spans="2:21">
+      <c r="O156" s="4"/>
+      <c r="T156" s="13"/>
+      <c r="U156" s="11"/>
+      <c r="V156" s="14"/>
+    </row>
+    <row r="157" spans="2:22">
       <c r="B157" s="11"/>
       <c r="C157" s="11"/>
       <c r="E157" s="12"/>
-      <c r="M157" s="4"/>
       <c r="N157" s="4"/>
-      <c r="S157" s="13"/>
-      <c r="T157" s="11"/>
-      <c r="U157" s="14"/>
-    </row>
-    <row r="158" spans="2:21">
+      <c r="O157" s="4"/>
+      <c r="T157" s="13"/>
+      <c r="U157" s="11"/>
+      <c r="V157" s="14"/>
+    </row>
+    <row r="158" spans="2:22">
       <c r="B158" s="11"/>
       <c r="C158" s="11"/>
       <c r="E158" s="12"/>
-      <c r="M158" s="4"/>
       <c r="N158" s="4"/>
-      <c r="S158" s="13"/>
-      <c r="T158" s="11"/>
-      <c r="U158" s="14"/>
-    </row>
-    <row r="159" spans="2:21">
-      <c r="S159" s="17"/>
-    </row>
-    <row r="160" spans="2:21">
-      <c r="S160" s="17"/>
-    </row>
-    <row r="161" spans="19:19">
-      <c r="S161" s="17"/>
-    </row>
-    <row r="162" spans="19:19">
-      <c r="S162" s="17"/>
-    </row>
-    <row r="163" spans="19:19">
-      <c r="S163" s="17"/>
-    </row>
-    <row r="164" spans="19:19">
-      <c r="S164" s="17"/>
-    </row>
-    <row r="165" spans="19:19">
-      <c r="S165" s="17"/>
-    </row>
-    <row r="166" spans="19:19">
-      <c r="S166" s="17"/>
-    </row>
-    <row r="167" spans="19:19">
-      <c r="S167" s="17"/>
-    </row>
-    <row r="168" spans="19:19">
-      <c r="S168" s="17"/>
-    </row>
-    <row r="169" spans="19:19">
-      <c r="S169" s="17"/>
-    </row>
-    <row r="170" spans="19:19">
-      <c r="S170" s="17"/>
-    </row>
-    <row r="171" spans="19:19">
-      <c r="S171" s="17"/>
-    </row>
-    <row r="172" spans="19:19">
-      <c r="S172" s="17"/>
-    </row>
-    <row r="173" spans="19:19">
-      <c r="S173" s="17"/>
-    </row>
-    <row r="174" spans="19:19">
-      <c r="S174" s="17"/>
-    </row>
-    <row r="175" spans="19:19">
-      <c r="S175" s="17"/>
-    </row>
-    <row r="176" spans="19:19">
-      <c r="S176" s="17"/>
-    </row>
-    <row r="177" spans="19:19">
-      <c r="S177" s="17"/>
-    </row>
-    <row r="178" spans="19:19">
-      <c r="S178" s="17"/>
-    </row>
-    <row r="179" spans="19:19">
-      <c r="S179" s="17"/>
-    </row>
-    <row r="180" spans="19:19">
-      <c r="S180" s="17"/>
-    </row>
-    <row r="181" spans="19:19">
-      <c r="S181" s="17"/>
-    </row>
-    <row r="182" spans="19:19">
-      <c r="S182" s="17"/>
-    </row>
-    <row r="183" spans="19:19">
-      <c r="S183" s="17"/>
-    </row>
-    <row r="184" spans="19:19">
-      <c r="S184" s="17"/>
-    </row>
-    <row r="185" spans="19:19">
-      <c r="S185" s="17"/>
-    </row>
-    <row r="186" spans="19:19">
-      <c r="S186" s="17"/>
-    </row>
-    <row r="187" spans="19:19">
-      <c r="S187" s="17"/>
-    </row>
-    <row r="188" spans="19:19">
-      <c r="S188" s="17"/>
-    </row>
-    <row r="189" spans="19:19">
-      <c r="S189" s="17"/>
-    </row>
-    <row r="190" spans="19:19">
-      <c r="S190" s="17"/>
-    </row>
-    <row r="191" spans="19:19">
-      <c r="S191" s="17"/>
-    </row>
-    <row r="192" spans="19:19">
-      <c r="S192" s="17"/>
-    </row>
-    <row r="193" spans="19:19">
-      <c r="S193" s="17"/>
-    </row>
-    <row r="194" spans="19:19">
-      <c r="S194" s="17"/>
-    </row>
-    <row r="195" spans="19:19">
-      <c r="S195" s="17"/>
-    </row>
-    <row r="196" spans="19:19">
-      <c r="S196" s="17"/>
-    </row>
-    <row r="197" spans="19:19">
-      <c r="S197" s="17"/>
-    </row>
-    <row r="198" spans="19:19">
-      <c r="S198" s="17"/>
-    </row>
-    <row r="199" spans="19:19">
-      <c r="S199" s="17"/>
-    </row>
-    <row r="200" spans="19:19">
-      <c r="S200" s="17"/>
-    </row>
-    <row r="201" spans="19:19">
-      <c r="S201" s="17"/>
-    </row>
-    <row r="202" spans="19:19">
-      <c r="S202" s="17"/>
-    </row>
-    <row r="203" spans="19:19">
-      <c r="S203" s="17"/>
-    </row>
-    <row r="204" spans="19:19">
-      <c r="S204" s="17"/>
-    </row>
-    <row r="205" spans="19:19">
-      <c r="S205" s="17"/>
-    </row>
-    <row r="206" spans="19:19">
-      <c r="S206" s="17"/>
-    </row>
-    <row r="207" spans="19:19">
-      <c r="S207" s="17"/>
-    </row>
-    <row r="208" spans="19:19">
-      <c r="S208" s="17"/>
-    </row>
-    <row r="209" spans="19:19">
-      <c r="S209" s="17"/>
-    </row>
-    <row r="210" spans="19:19">
-      <c r="S210" s="17"/>
-    </row>
-    <row r="211" spans="19:19">
-      <c r="S211" s="17"/>
-    </row>
-    <row r="212" spans="19:19">
-      <c r="S212" s="17"/>
-    </row>
-    <row r="213" spans="19:19">
-      <c r="S213" s="17"/>
-    </row>
-    <row r="214" spans="19:19">
-      <c r="S214" s="17"/>
-    </row>
-    <row r="215" spans="19:19">
-      <c r="S215" s="17"/>
-    </row>
-    <row r="216" spans="19:19">
-      <c r="S216" s="17"/>
-    </row>
-    <row r="217" spans="19:19">
-      <c r="S217" s="17"/>
-    </row>
-    <row r="218" spans="19:19">
-      <c r="S218" s="17"/>
-    </row>
-    <row r="219" spans="19:19">
-      <c r="S219" s="17"/>
-    </row>
-    <row r="220" spans="19:19">
-      <c r="S220" s="17"/>
-    </row>
-    <row r="221" spans="19:19">
-      <c r="S221" s="17"/>
-    </row>
-    <row r="222" spans="19:19">
-      <c r="S222" s="17"/>
-    </row>
-    <row r="223" spans="19:19">
-      <c r="S223" s="17"/>
-    </row>
-    <row r="224" spans="19:19">
-      <c r="S224" s="17"/>
-    </row>
-    <row r="225" spans="19:19">
-      <c r="S225" s="17"/>
-    </row>
-    <row r="226" spans="19:19">
-      <c r="S226" s="17"/>
-    </row>
-    <row r="227" spans="19:19">
-      <c r="S227" s="17"/>
-    </row>
-    <row r="228" spans="19:19">
-      <c r="S228" s="17"/>
-    </row>
-    <row r="229" spans="19:19">
-      <c r="S229" s="17"/>
-    </row>
-    <row r="230" spans="19:19">
-      <c r="S230" s="17"/>
-    </row>
-    <row r="231" spans="19:19">
-      <c r="S231" s="17"/>
-    </row>
-    <row r="232" spans="19:19">
-      <c r="S232" s="17"/>
-    </row>
-    <row r="233" spans="19:19">
-      <c r="S233" s="17"/>
-    </row>
-    <row r="234" spans="19:19">
-      <c r="S234" s="17"/>
-    </row>
-    <row r="235" spans="19:19">
-      <c r="S235" s="17"/>
-    </row>
-    <row r="236" spans="19:19">
-      <c r="S236" s="17"/>
-    </row>
-    <row r="237" spans="19:19">
-      <c r="S237" s="17"/>
-    </row>
-    <row r="238" spans="19:19">
-      <c r="S238" s="17"/>
-    </row>
-    <row r="239" spans="19:19">
-      <c r="S239" s="17"/>
-    </row>
-    <row r="240" spans="19:19">
-      <c r="S240" s="17"/>
-    </row>
-    <row r="241" spans="19:19">
-      <c r="S241" s="17"/>
-    </row>
-    <row r="242" spans="19:19">
-      <c r="S242" s="17"/>
-    </row>
-    <row r="243" spans="19:19">
-      <c r="S243" s="17"/>
-    </row>
-    <row r="244" spans="19:19">
-      <c r="S244" s="17"/>
-    </row>
-    <row r="245" spans="19:19">
-      <c r="S245" s="17"/>
-    </row>
-    <row r="246" spans="19:19">
-      <c r="S246" s="17"/>
-    </row>
-    <row r="247" spans="19:19">
-      <c r="S247" s="17"/>
-    </row>
-    <row r="248" spans="19:19">
-      <c r="S248" s="17"/>
-    </row>
-    <row r="249" spans="19:19">
-      <c r="S249" s="17"/>
-    </row>
-    <row r="250" spans="19:19">
-      <c r="S250" s="17"/>
-    </row>
-    <row r="251" spans="19:19">
-      <c r="S251" s="17"/>
-    </row>
-    <row r="252" spans="19:19">
-      <c r="S252" s="17"/>
-    </row>
-    <row r="253" spans="19:19">
-      <c r="S253" s="17"/>
-    </row>
-    <row r="254" spans="19:19">
-      <c r="S254" s="17"/>
-    </row>
-    <row r="255" spans="19:19">
-      <c r="S255" s="17"/>
-    </row>
-    <row r="256" spans="19:19">
-      <c r="S256" s="17"/>
-    </row>
-    <row r="257" spans="19:19">
-      <c r="S257" s="17"/>
-    </row>
-    <row r="258" spans="19:19">
-      <c r="S258" s="17"/>
-    </row>
-    <row r="259" spans="19:19">
-      <c r="S259" s="17"/>
-    </row>
-    <row r="260" spans="19:19">
-      <c r="S260" s="17"/>
-    </row>
-    <row r="261" spans="19:19">
-      <c r="S261" s="17"/>
-    </row>
-    <row r="262" spans="19:19">
-      <c r="S262" s="17"/>
-    </row>
-    <row r="263" spans="19:19">
-      <c r="S263" s="17"/>
-    </row>
-    <row r="264" spans="19:19">
-      <c r="S264" s="17"/>
-    </row>
-    <row r="265" spans="19:19">
-      <c r="S265" s="17"/>
-    </row>
-    <row r="266" spans="19:19">
-      <c r="S266" s="17"/>
-    </row>
-    <row r="267" spans="19:19">
-      <c r="S267" s="17"/>
-    </row>
-    <row r="268" spans="19:19">
-      <c r="S268" s="17"/>
-    </row>
-    <row r="269" spans="19:19">
-      <c r="S269" s="17"/>
-    </row>
-    <row r="270" spans="19:19">
-      <c r="S270" s="17"/>
-    </row>
-    <row r="271" spans="19:19">
-      <c r="S271" s="17"/>
-    </row>
-    <row r="272" spans="19:19">
-      <c r="S272" s="17"/>
-    </row>
-    <row r="273" spans="19:19">
-      <c r="S273" s="17"/>
-    </row>
-    <row r="274" spans="19:19">
-      <c r="S274" s="17"/>
-    </row>
-    <row r="275" spans="19:19">
-      <c r="S275" s="17"/>
-    </row>
-    <row r="276" spans="19:19">
-      <c r="S276" s="17"/>
-    </row>
-    <row r="277" spans="19:19">
-      <c r="S277" s="17"/>
-    </row>
-    <row r="278" spans="19:19">
-      <c r="S278" s="17"/>
-    </row>
-    <row r="279" spans="19:19">
-      <c r="S279" s="17"/>
-    </row>
-    <row r="280" spans="19:19">
-      <c r="S280" s="17"/>
-    </row>
-    <row r="281" spans="19:19">
-      <c r="S281" s="17"/>
-    </row>
-    <row r="282" spans="19:19">
-      <c r="S282" s="17"/>
-    </row>
-    <row r="283" spans="19:19">
-      <c r="S283" s="17"/>
-    </row>
-    <row r="284" spans="19:19">
-      <c r="S284" s="17"/>
-    </row>
-    <row r="285" spans="19:19">
-      <c r="S285" s="17"/>
-    </row>
-    <row r="286" spans="19:19">
-      <c r="S286" s="17"/>
-    </row>
-    <row r="287" spans="19:19">
-      <c r="S287" s="17"/>
-    </row>
-    <row r="288" spans="19:19">
-      <c r="S288" s="17"/>
-    </row>
-    <row r="289" spans="19:19">
-      <c r="S289" s="17"/>
-    </row>
-    <row r="290" spans="19:19">
-      <c r="S290" s="17"/>
-    </row>
-    <row r="291" spans="19:19">
-      <c r="S291" s="17"/>
-    </row>
-    <row r="292" spans="19:19">
-      <c r="S292" s="17"/>
-    </row>
-    <row r="293" spans="19:19">
-      <c r="S293" s="17"/>
-    </row>
-    <row r="294" spans="19:19">
-      <c r="S294" s="17"/>
-    </row>
-    <row r="295" spans="19:19">
-      <c r="S295" s="17"/>
-    </row>
-    <row r="296" spans="19:19">
-      <c r="S296" s="17"/>
-    </row>
-    <row r="297" spans="19:19">
-      <c r="S297" s="17"/>
-    </row>
-    <row r="298" spans="19:19">
-      <c r="S298" s="17"/>
-    </row>
-    <row r="299" spans="19:19">
-      <c r="S299" s="17"/>
-    </row>
-    <row r="300" spans="19:19">
-      <c r="S300" s="17"/>
-    </row>
-    <row r="301" spans="19:19">
-      <c r="S301" s="17"/>
-    </row>
-    <row r="302" spans="19:19">
-      <c r="S302" s="17"/>
-    </row>
-    <row r="303" spans="19:19">
-      <c r="S303" s="17"/>
-    </row>
-    <row r="304" spans="19:19">
-      <c r="S304" s="17"/>
-    </row>
-    <row r="305" spans="19:19">
-      <c r="S305" s="17"/>
-    </row>
-    <row r="306" spans="19:19">
-      <c r="S306" s="17"/>
-    </row>
-    <row r="307" spans="19:19">
-      <c r="S307" s="17"/>
-    </row>
-    <row r="308" spans="19:19">
-      <c r="S308" s="17"/>
-    </row>
-    <row r="309" spans="19:19">
-      <c r="S309" s="17"/>
-    </row>
-    <row r="310" spans="19:19">
-      <c r="S310" s="17"/>
-    </row>
-    <row r="311" spans="19:19">
-      <c r="S311" s="17"/>
-    </row>
-    <row r="312" spans="19:19">
-      <c r="S312" s="17"/>
-    </row>
-    <row r="313" spans="19:19">
-      <c r="S313" s="17"/>
-    </row>
-    <row r="314" spans="19:19">
-      <c r="S314" s="17"/>
-    </row>
-    <row r="315" spans="19:19">
-      <c r="S315" s="17"/>
-    </row>
-    <row r="316" spans="19:19">
-      <c r="S316" s="17"/>
-    </row>
-    <row r="317" spans="19:19">
-      <c r="S317" s="17"/>
-    </row>
-    <row r="318" spans="19:19">
-      <c r="S318" s="17"/>
-    </row>
-    <row r="319" spans="19:19">
-      <c r="S319" s="17"/>
-    </row>
-    <row r="320" spans="19:19">
-      <c r="S320" s="17"/>
-    </row>
-    <row r="321" spans="19:19">
-      <c r="S321" s="17"/>
-    </row>
-    <row r="322" spans="19:19">
-      <c r="S322" s="17"/>
-    </row>
-    <row r="323" spans="19:19">
-      <c r="S323" s="17"/>
-    </row>
-    <row r="324" spans="19:19">
-      <c r="S324" s="17"/>
-    </row>
-    <row r="325" spans="19:19">
-      <c r="S325" s="17"/>
-    </row>
-    <row r="326" spans="19:19">
-      <c r="S326" s="17"/>
-    </row>
-    <row r="327" spans="19:19">
-      <c r="S327" s="17"/>
-    </row>
-    <row r="328" spans="19:19">
-      <c r="S328" s="17"/>
-    </row>
-    <row r="329" spans="19:19">
-      <c r="S329" s="17"/>
-    </row>
-    <row r="330" spans="19:19">
-      <c r="S330" s="17"/>
-    </row>
-    <row r="331" spans="19:19">
-      <c r="S331" s="17"/>
-    </row>
-    <row r="332" spans="19:19">
-      <c r="S332" s="17"/>
-    </row>
-    <row r="333" spans="19:19">
-      <c r="S333" s="17"/>
-    </row>
-    <row r="334" spans="19:19">
-      <c r="S334" s="17"/>
-    </row>
-    <row r="335" spans="19:19">
-      <c r="S335" s="17"/>
-    </row>
-    <row r="336" spans="19:19">
-      <c r="S336" s="17"/>
-    </row>
-    <row r="337" spans="19:19">
-      <c r="S337" s="17"/>
-    </row>
-    <row r="338" spans="19:19">
-      <c r="S338" s="17"/>
-    </row>
-    <row r="339" spans="19:19">
-      <c r="S339" s="17"/>
-    </row>
-    <row r="340" spans="19:19">
-      <c r="S340" s="17"/>
-    </row>
-    <row r="341" spans="19:19">
-      <c r="S341" s="17"/>
-    </row>
-    <row r="342" spans="19:19">
-      <c r="S342" s="17"/>
-    </row>
-    <row r="343" spans="19:19">
-      <c r="S343" s="17"/>
-    </row>
-    <row r="344" spans="19:19">
-      <c r="S344" s="17"/>
-    </row>
-    <row r="345" spans="19:19">
-      <c r="S345" s="17"/>
-    </row>
-    <row r="346" spans="19:19">
-      <c r="S346" s="17"/>
-    </row>
-    <row r="347" spans="19:19">
-      <c r="S347" s="17"/>
-    </row>
-    <row r="348" spans="19:19">
-      <c r="S348" s="17"/>
-    </row>
-    <row r="349" spans="19:19">
-      <c r="S349" s="17"/>
-    </row>
-    <row r="350" spans="19:19">
-      <c r="S350" s="17"/>
-    </row>
-    <row r="351" spans="19:19">
-      <c r="S351" s="17"/>
-    </row>
-    <row r="352" spans="19:19">
-      <c r="S352" s="17"/>
-    </row>
-    <row r="353" spans="19:19">
-      <c r="S353" s="17"/>
-    </row>
-    <row r="354" spans="19:19">
-      <c r="S354" s="17"/>
-    </row>
-    <row r="355" spans="19:19">
-      <c r="S355" s="17"/>
-    </row>
-    <row r="356" spans="19:19">
-      <c r="S356" s="17"/>
-    </row>
-    <row r="357" spans="19:19">
-      <c r="S357" s="17"/>
-    </row>
-    <row r="358" spans="19:19">
-      <c r="S358" s="17"/>
+      <c r="O158" s="4"/>
+      <c r="T158" s="13"/>
+      <c r="U158" s="11"/>
+      <c r="V158" s="14"/>
+    </row>
+    <row r="159" spans="2:22">
+      <c r="T159" s="17"/>
+    </row>
+    <row r="160" spans="2:22">
+      <c r="T160" s="17"/>
+    </row>
+    <row r="161" spans="20:20">
+      <c r="T161" s="17"/>
+    </row>
+    <row r="162" spans="20:20">
+      <c r="T162" s="17"/>
+    </row>
+    <row r="163" spans="20:20">
+      <c r="T163" s="17"/>
+    </row>
+    <row r="164" spans="20:20">
+      <c r="T164" s="17"/>
+    </row>
+    <row r="165" spans="20:20">
+      <c r="T165" s="17"/>
+    </row>
+    <row r="166" spans="20:20">
+      <c r="T166" s="17"/>
+    </row>
+    <row r="167" spans="20:20">
+      <c r="T167" s="17"/>
+    </row>
+    <row r="168" spans="20:20">
+      <c r="T168" s="17"/>
+    </row>
+    <row r="169" spans="20:20">
+      <c r="T169" s="17"/>
+    </row>
+    <row r="170" spans="20:20">
+      <c r="T170" s="17"/>
+    </row>
+    <row r="171" spans="20:20">
+      <c r="T171" s="17"/>
+    </row>
+    <row r="172" spans="20:20">
+      <c r="T172" s="17"/>
+    </row>
+    <row r="173" spans="20:20">
+      <c r="T173" s="17"/>
+    </row>
+    <row r="174" spans="20:20">
+      <c r="T174" s="17"/>
+    </row>
+    <row r="175" spans="20:20">
+      <c r="T175" s="17"/>
+    </row>
+    <row r="176" spans="20:20">
+      <c r="T176" s="17"/>
+    </row>
+    <row r="177" spans="20:20">
+      <c r="T177" s="17"/>
+    </row>
+    <row r="178" spans="20:20">
+      <c r="T178" s="17"/>
+    </row>
+    <row r="179" spans="20:20">
+      <c r="T179" s="17"/>
+    </row>
+    <row r="180" spans="20:20">
+      <c r="T180" s="17"/>
+    </row>
+    <row r="181" spans="20:20">
+      <c r="T181" s="17"/>
+    </row>
+    <row r="182" spans="20:20">
+      <c r="T182" s="17"/>
+    </row>
+    <row r="183" spans="20:20">
+      <c r="T183" s="17"/>
+    </row>
+    <row r="184" spans="20:20">
+      <c r="T184" s="17"/>
+    </row>
+    <row r="185" spans="20:20">
+      <c r="T185" s="17"/>
+    </row>
+    <row r="186" spans="20:20">
+      <c r="T186" s="17"/>
+    </row>
+    <row r="187" spans="20:20">
+      <c r="T187" s="17"/>
+    </row>
+    <row r="188" spans="20:20">
+      <c r="T188" s="17"/>
+    </row>
+    <row r="189" spans="20:20">
+      <c r="T189" s="17"/>
+    </row>
+    <row r="190" spans="20:20">
+      <c r="T190" s="17"/>
+    </row>
+    <row r="191" spans="20:20">
+      <c r="T191" s="17"/>
+    </row>
+    <row r="192" spans="20:20">
+      <c r="T192" s="17"/>
+    </row>
+    <row r="193" spans="20:20">
+      <c r="T193" s="17"/>
+    </row>
+    <row r="194" spans="20:20">
+      <c r="T194" s="17"/>
+    </row>
+    <row r="195" spans="20:20">
+      <c r="T195" s="17"/>
+    </row>
+    <row r="196" spans="20:20">
+      <c r="T196" s="17"/>
+    </row>
+    <row r="197" spans="20:20">
+      <c r="T197" s="17"/>
+    </row>
+    <row r="198" spans="20:20">
+      <c r="T198" s="17"/>
+    </row>
+    <row r="199" spans="20:20">
+      <c r="T199" s="17"/>
+    </row>
+    <row r="200" spans="20:20">
+      <c r="T200" s="17"/>
+    </row>
+    <row r="201" spans="20:20">
+      <c r="T201" s="17"/>
+    </row>
+    <row r="202" spans="20:20">
+      <c r="T202" s="17"/>
+    </row>
+    <row r="203" spans="20:20">
+      <c r="T203" s="17"/>
+    </row>
+    <row r="204" spans="20:20">
+      <c r="T204" s="17"/>
+    </row>
+    <row r="205" spans="20:20">
+      <c r="T205" s="17"/>
+    </row>
+    <row r="206" spans="20:20">
+      <c r="T206" s="17"/>
+    </row>
+    <row r="207" spans="20:20">
+      <c r="T207" s="17"/>
+    </row>
+    <row r="208" spans="20:20">
+      <c r="T208" s="17"/>
+    </row>
+    <row r="209" spans="20:20">
+      <c r="T209" s="17"/>
+    </row>
+    <row r="210" spans="20:20">
+      <c r="T210" s="17"/>
+    </row>
+    <row r="211" spans="20:20">
+      <c r="T211" s="17"/>
+    </row>
+    <row r="212" spans="20:20">
+      <c r="T212" s="17"/>
+    </row>
+    <row r="213" spans="20:20">
+      <c r="T213" s="17"/>
+    </row>
+    <row r="214" spans="20:20">
+      <c r="T214" s="17"/>
+    </row>
+    <row r="215" spans="20:20">
+      <c r="T215" s="17"/>
+    </row>
+    <row r="216" spans="20:20">
+      <c r="T216" s="17"/>
+    </row>
+    <row r="217" spans="20:20">
+      <c r="T217" s="17"/>
+    </row>
+    <row r="218" spans="20:20">
+      <c r="T218" s="17"/>
+    </row>
+    <row r="219" spans="20:20">
+      <c r="T219" s="17"/>
+    </row>
+    <row r="220" spans="20:20">
+      <c r="T220" s="17"/>
+    </row>
+    <row r="221" spans="20:20">
+      <c r="T221" s="17"/>
+    </row>
+    <row r="222" spans="20:20">
+      <c r="T222" s="17"/>
+    </row>
+    <row r="223" spans="20:20">
+      <c r="T223" s="17"/>
+    </row>
+    <row r="224" spans="20:20">
+      <c r="T224" s="17"/>
+    </row>
+    <row r="225" spans="20:20">
+      <c r="T225" s="17"/>
+    </row>
+    <row r="226" spans="20:20">
+      <c r="T226" s="17"/>
+    </row>
+    <row r="227" spans="20:20">
+      <c r="T227" s="17"/>
+    </row>
+    <row r="228" spans="20:20">
+      <c r="T228" s="17"/>
+    </row>
+    <row r="229" spans="20:20">
+      <c r="T229" s="17"/>
+    </row>
+    <row r="230" spans="20:20">
+      <c r="T230" s="17"/>
+    </row>
+    <row r="231" spans="20:20">
+      <c r="T231" s="17"/>
+    </row>
+    <row r="232" spans="20:20">
+      <c r="T232" s="17"/>
+    </row>
+    <row r="233" spans="20:20">
+      <c r="T233" s="17"/>
+    </row>
+    <row r="234" spans="20:20">
+      <c r="T234" s="17"/>
+    </row>
+    <row r="235" spans="20:20">
+      <c r="T235" s="17"/>
+    </row>
+    <row r="236" spans="20:20">
+      <c r="T236" s="17"/>
+    </row>
+    <row r="237" spans="20:20">
+      <c r="T237" s="17"/>
+    </row>
+    <row r="238" spans="20:20">
+      <c r="T238" s="17"/>
+    </row>
+    <row r="239" spans="20:20">
+      <c r="T239" s="17"/>
+    </row>
+    <row r="240" spans="20:20">
+      <c r="T240" s="17"/>
+    </row>
+    <row r="241" spans="20:20">
+      <c r="T241" s="17"/>
+    </row>
+    <row r="242" spans="20:20">
+      <c r="T242" s="17"/>
+    </row>
+    <row r="243" spans="20:20">
+      <c r="T243" s="17"/>
+    </row>
+    <row r="244" spans="20:20">
+      <c r="T244" s="17"/>
+    </row>
+    <row r="245" spans="20:20">
+      <c r="T245" s="17"/>
+    </row>
+    <row r="246" spans="20:20">
+      <c r="T246" s="17"/>
+    </row>
+    <row r="247" spans="20:20">
+      <c r="T247" s="17"/>
+    </row>
+    <row r="248" spans="20:20">
+      <c r="T248" s="17"/>
+    </row>
+    <row r="249" spans="20:20">
+      <c r="T249" s="17"/>
+    </row>
+    <row r="250" spans="20:20">
+      <c r="T250" s="17"/>
+    </row>
+    <row r="251" spans="20:20">
+      <c r="T251" s="17"/>
+    </row>
+    <row r="252" spans="20:20">
+      <c r="T252" s="17"/>
+    </row>
+    <row r="253" spans="20:20">
+      <c r="T253" s="17"/>
+    </row>
+    <row r="254" spans="20:20">
+      <c r="T254" s="17"/>
+    </row>
+    <row r="255" spans="20:20">
+      <c r="T255" s="17"/>
+    </row>
+    <row r="256" spans="20:20">
+      <c r="T256" s="17"/>
+    </row>
+    <row r="257" spans="20:20">
+      <c r="T257" s="17"/>
+    </row>
+    <row r="258" spans="20:20">
+      <c r="T258" s="17"/>
+    </row>
+    <row r="259" spans="20:20">
+      <c r="T259" s="17"/>
+    </row>
+    <row r="260" spans="20:20">
+      <c r="T260" s="17"/>
+    </row>
+    <row r="261" spans="20:20">
+      <c r="T261" s="17"/>
+    </row>
+    <row r="262" spans="20:20">
+      <c r="T262" s="17"/>
+    </row>
+    <row r="263" spans="20:20">
+      <c r="T263" s="17"/>
+    </row>
+    <row r="264" spans="20:20">
+      <c r="T264" s="17"/>
+    </row>
+    <row r="265" spans="20:20">
+      <c r="T265" s="17"/>
+    </row>
+    <row r="266" spans="20:20">
+      <c r="T266" s="17"/>
+    </row>
+    <row r="267" spans="20:20">
+      <c r="T267" s="17"/>
+    </row>
+    <row r="268" spans="20:20">
+      <c r="T268" s="17"/>
+    </row>
+    <row r="269" spans="20:20">
+      <c r="T269" s="17"/>
+    </row>
+    <row r="270" spans="20:20">
+      <c r="T270" s="17"/>
+    </row>
+    <row r="271" spans="20:20">
+      <c r="T271" s="17"/>
+    </row>
+    <row r="272" spans="20:20">
+      <c r="T272" s="17"/>
+    </row>
+    <row r="273" spans="20:20">
+      <c r="T273" s="17"/>
+    </row>
+    <row r="274" spans="20:20">
+      <c r="T274" s="17"/>
+    </row>
+    <row r="275" spans="20:20">
+      <c r="T275" s="17"/>
+    </row>
+    <row r="276" spans="20:20">
+      <c r="T276" s="17"/>
+    </row>
+    <row r="277" spans="20:20">
+      <c r="T277" s="17"/>
+    </row>
+    <row r="278" spans="20:20">
+      <c r="T278" s="17"/>
+    </row>
+    <row r="279" spans="20:20">
+      <c r="T279" s="17"/>
+    </row>
+    <row r="280" spans="20:20">
+      <c r="T280" s="17"/>
+    </row>
+    <row r="281" spans="20:20">
+      <c r="T281" s="17"/>
+    </row>
+    <row r="282" spans="20:20">
+      <c r="T282" s="17"/>
+    </row>
+    <row r="283" spans="20:20">
+      <c r="T283" s="17"/>
+    </row>
+    <row r="284" spans="20:20">
+      <c r="T284" s="17"/>
+    </row>
+    <row r="285" spans="20:20">
+      <c r="T285" s="17"/>
+    </row>
+    <row r="286" spans="20:20">
+      <c r="T286" s="17"/>
+    </row>
+    <row r="287" spans="20:20">
+      <c r="T287" s="17"/>
+    </row>
+    <row r="288" spans="20:20">
+      <c r="T288" s="17"/>
+    </row>
+    <row r="289" spans="20:20">
+      <c r="T289" s="17"/>
+    </row>
+    <row r="290" spans="20:20">
+      <c r="T290" s="17"/>
+    </row>
+    <row r="291" spans="20:20">
+      <c r="T291" s="17"/>
+    </row>
+    <row r="292" spans="20:20">
+      <c r="T292" s="17"/>
+    </row>
+    <row r="293" spans="20:20">
+      <c r="T293" s="17"/>
+    </row>
+    <row r="294" spans="20:20">
+      <c r="T294" s="17"/>
+    </row>
+    <row r="295" spans="20:20">
+      <c r="T295" s="17"/>
+    </row>
+    <row r="296" spans="20:20">
+      <c r="T296" s="17"/>
+    </row>
+    <row r="297" spans="20:20">
+      <c r="T297" s="17"/>
+    </row>
+    <row r="298" spans="20:20">
+      <c r="T298" s="17"/>
+    </row>
+    <row r="299" spans="20:20">
+      <c r="T299" s="17"/>
+    </row>
+    <row r="300" spans="20:20">
+      <c r="T300" s="17"/>
+    </row>
+    <row r="301" spans="20:20">
+      <c r="T301" s="17"/>
+    </row>
+    <row r="302" spans="20:20">
+      <c r="T302" s="17"/>
+    </row>
+    <row r="303" spans="20:20">
+      <c r="T303" s="17"/>
+    </row>
+    <row r="304" spans="20:20">
+      <c r="T304" s="17"/>
+    </row>
+    <row r="305" spans="20:20">
+      <c r="T305" s="17"/>
+    </row>
+    <row r="306" spans="20:20">
+      <c r="T306" s="17"/>
+    </row>
+    <row r="307" spans="20:20">
+      <c r="T307" s="17"/>
+    </row>
+    <row r="308" spans="20:20">
+      <c r="T308" s="17"/>
+    </row>
+    <row r="309" spans="20:20">
+      <c r="T309" s="17"/>
+    </row>
+    <row r="310" spans="20:20">
+      <c r="T310" s="17"/>
+    </row>
+    <row r="311" spans="20:20">
+      <c r="T311" s="17"/>
+    </row>
+    <row r="312" spans="20:20">
+      <c r="T312" s="17"/>
+    </row>
+    <row r="313" spans="20:20">
+      <c r="T313" s="17"/>
+    </row>
+    <row r="314" spans="20:20">
+      <c r="T314" s="17"/>
+    </row>
+    <row r="315" spans="20:20">
+      <c r="T315" s="17"/>
+    </row>
+    <row r="316" spans="20:20">
+      <c r="T316" s="17"/>
+    </row>
+    <row r="317" spans="20:20">
+      <c r="T317" s="17"/>
+    </row>
+    <row r="318" spans="20:20">
+      <c r="T318" s="17"/>
+    </row>
+    <row r="319" spans="20:20">
+      <c r="T319" s="17"/>
+    </row>
+    <row r="320" spans="20:20">
+      <c r="T320" s="17"/>
+    </row>
+    <row r="321" spans="20:20">
+      <c r="T321" s="17"/>
+    </row>
+    <row r="322" spans="20:20">
+      <c r="T322" s="17"/>
+    </row>
+    <row r="323" spans="20:20">
+      <c r="T323" s="17"/>
+    </row>
+    <row r="324" spans="20:20">
+      <c r="T324" s="17"/>
+    </row>
+    <row r="325" spans="20:20">
+      <c r="T325" s="17"/>
+    </row>
+    <row r="326" spans="20:20">
+      <c r="T326" s="17"/>
+    </row>
+    <row r="327" spans="20:20">
+      <c r="T327" s="17"/>
+    </row>
+    <row r="328" spans="20:20">
+      <c r="T328" s="17"/>
+    </row>
+    <row r="329" spans="20:20">
+      <c r="T329" s="17"/>
+    </row>
+    <row r="330" spans="20:20">
+      <c r="T330" s="17"/>
+    </row>
+    <row r="331" spans="20:20">
+      <c r="T331" s="17"/>
+    </row>
+    <row r="332" spans="20:20">
+      <c r="T332" s="17"/>
+    </row>
+    <row r="333" spans="20:20">
+      <c r="T333" s="17"/>
+    </row>
+    <row r="334" spans="20:20">
+      <c r="T334" s="17"/>
+    </row>
+    <row r="335" spans="20:20">
+      <c r="T335" s="17"/>
+    </row>
+    <row r="336" spans="20:20">
+      <c r="T336" s="17"/>
+    </row>
+    <row r="337" spans="20:20">
+      <c r="T337" s="17"/>
+    </row>
+    <row r="338" spans="20:20">
+      <c r="T338" s="17"/>
+    </row>
+    <row r="339" spans="20:20">
+      <c r="T339" s="17"/>
+    </row>
+    <row r="340" spans="20:20">
+      <c r="T340" s="17"/>
+    </row>
+    <row r="341" spans="20:20">
+      <c r="T341" s="17"/>
+    </row>
+    <row r="342" spans="20:20">
+      <c r="T342" s="17"/>
+    </row>
+    <row r="343" spans="20:20">
+      <c r="T343" s="17"/>
+    </row>
+    <row r="344" spans="20:20">
+      <c r="T344" s="17"/>
+    </row>
+    <row r="345" spans="20:20">
+      <c r="T345" s="17"/>
+    </row>
+    <row r="346" spans="20:20">
+      <c r="T346" s="17"/>
+    </row>
+    <row r="347" spans="20:20">
+      <c r="T347" s="17"/>
+    </row>
+    <row r="348" spans="20:20">
+      <c r="T348" s="17"/>
+    </row>
+    <row r="349" spans="20:20">
+      <c r="T349" s="17"/>
+    </row>
+    <row r="350" spans="20:20">
+      <c r="T350" s="17"/>
+    </row>
+    <row r="351" spans="20:20">
+      <c r="T351" s="17"/>
+    </row>
+    <row r="352" spans="20:20">
+      <c r="T352" s="17"/>
+    </row>
+    <row r="353" spans="20:20">
+      <c r="T353" s="17"/>
+    </row>
+    <row r="354" spans="20:20">
+      <c r="T354" s="17"/>
+    </row>
+    <row r="355" spans="20:20">
+      <c r="T355" s="17"/>
+    </row>
+    <row r="356" spans="20:20">
+      <c r="T356" s="17"/>
+    </row>
+    <row r="357" spans="20:20">
+      <c r="T357" s="17"/>
+    </row>
+    <row r="358" spans="20:20">
+      <c r="T358" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="S1:V1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="T1:W1"/>
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="G1:I1"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="P1:S1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6533,7 +6540,7 @@
       </c>
       <c r="H5" s="73">
         <f>VLOOKUP(B5,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>2.9606730447963137E-2</v>
+        <v>2.9346308549922262E-2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -6561,7 +6568,7 @@
       </c>
       <c r="H6" s="73">
         <f>VLOOKUP(B6,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.17842892639139052</v>
+        <v>0.17855667472343195</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -6589,7 +6596,7 @@
       </c>
       <c r="H7" s="73">
         <f>VLOOKUP(B7,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.23821680012512947</v>
+        <v>0.23834947369112891</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -6656,7 +6663,7 @@
       </c>
       <c r="H12" s="73">
         <f>VLOOKUP(B12,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.23821680012512947</v>
+        <v>0.23834947369112891</v>
       </c>
     </row>
     <row r="13" spans="1:8">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FEB76F2-A99D-4B3C-B2ED-D335BBEF5017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3680A6A-F52D-4D09-B2E4-B4D7B2015D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="273">
   <si>
     <t>Name</t>
   </si>
@@ -1600,7 +1600,10 @@
     <t>open a position at a yield of</t>
   </si>
   <si>
-    <t>Open Position</t>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Execution</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1962,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2176,18 +2179,18 @@
     <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2200,10 +2203,13 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="4" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2564,12 +2570,12 @@
       <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="95" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="94"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="20" t="s">
@@ -2581,12 +2587,12 @@
       <c r="C6" s="61"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" s="94" t="s">
+      <c r="B7" s="95" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="23" t="s">
@@ -2675,12 +2681,12 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
-      <c r="B24" s="94" t="s">
+      <c r="B24" s="95" t="s">
         <v>220</v>
       </c>
-      <c r="C24" s="94"/>
-      <c r="D24" s="94"/>
-      <c r="E24" s="94"/>
+      <c r="C24" s="95"/>
+      <c r="D24" s="95"/>
+      <c r="E24" s="95"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
@@ -2780,20 +2786,20 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="B39" s="94" t="s">
+      <c r="B39" s="95" t="s">
         <v>156</v>
       </c>
-      <c r="C39" s="94"/>
-      <c r="D39" s="94"/>
-      <c r="E39" s="94"/>
+      <c r="C39" s="95"/>
+      <c r="D39" s="95"/>
+      <c r="E39" s="95"/>
     </row>
     <row r="40" spans="1:5" ht="46.6" customHeight="1">
-      <c r="B40" s="94" t="s">
+      <c r="B40" s="95" t="s">
         <v>235</v>
       </c>
-      <c r="C40" s="94"/>
-      <c r="D40" s="94"/>
-      <c r="E40" s="94"/>
+      <c r="C40" s="95"/>
+      <c r="D40" s="95"/>
+      <c r="E40" s="95"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="21" t="s">
@@ -2805,12 +2811,12 @@
       <c r="E42" s="21"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="B44" s="94" t="s">
+      <c r="B44" s="95" t="s">
         <v>208</v>
       </c>
-      <c r="C44" s="94"/>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="23" t="s">
@@ -2995,12 +3001,12 @@
       <c r="E69" s="21"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="B71" s="94" t="s">
+      <c r="B71" s="95" t="s">
         <v>196</v>
       </c>
-      <c r="C71" s="94"/>
-      <c r="D71" s="94"/>
-      <c r="E71" s="94"/>
+      <c r="C71" s="95"/>
+      <c r="D71" s="95"/>
+      <c r="E71" s="95"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="28" t="s">
@@ -3062,36 +3068,36 @@
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="B85" s="97" t="s">
+      <c r="B85" s="96" t="s">
         <v>192</v>
       </c>
-      <c r="C85" s="97"/>
-      <c r="D85" s="97"/>
-      <c r="E85" s="97"/>
+      <c r="C85" s="96"/>
+      <c r="D85" s="96"/>
+      <c r="E85" s="96"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="B86" s="96" t="s">
+      <c r="B86" s="94" t="s">
         <v>190</v>
       </c>
-      <c r="C86" s="96"/>
-      <c r="D86" s="96"/>
-      <c r="E86" s="96"/>
+      <c r="C86" s="94"/>
+      <c r="D86" s="94"/>
+      <c r="E86" s="94"/>
     </row>
     <row r="87" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B87" s="94" t="s">
+      <c r="B87" s="95" t="s">
         <v>189</v>
       </c>
-      <c r="C87" s="94"/>
-      <c r="D87" s="94"/>
-      <c r="E87" s="94"/>
+      <c r="C87" s="95"/>
+      <c r="D87" s="95"/>
+      <c r="E87" s="95"/>
     </row>
     <row r="88" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B88" s="94" t="s">
+      <c r="B88" s="95" t="s">
         <v>225</v>
       </c>
-      <c r="C88" s="94"/>
-      <c r="D88" s="94"/>
-      <c r="E88" s="94"/>
+      <c r="C88" s="95"/>
+      <c r="D88" s="95"/>
+      <c r="E88" s="95"/>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="24" t="s">
@@ -3124,12 +3130,12 @@
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="B97" s="95" t="s">
+      <c r="B97" s="97" t="s">
         <v>211</v>
       </c>
-      <c r="C97" s="95"/>
-      <c r="D97" s="95"/>
-      <c r="E97" s="95"/>
+      <c r="C97" s="97"/>
+      <c r="D97" s="97"/>
+      <c r="E97" s="97"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
@@ -3137,20 +3143,20 @@
       </c>
     </row>
     <row r="100" spans="1:5" ht="12.4">
-      <c r="B100" s="95" t="s">
+      <c r="B100" s="97" t="s">
         <v>212</v>
       </c>
-      <c r="C100" s="95"/>
-      <c r="D100" s="95"/>
-      <c r="E100" s="95"/>
+      <c r="C100" s="97"/>
+      <c r="D100" s="97"/>
+      <c r="E100" s="97"/>
     </row>
     <row r="101" spans="1:5" ht="58.5" customHeight="1">
-      <c r="B101" s="94" t="s">
+      <c r="B101" s="95" t="s">
         <v>219</v>
       </c>
-      <c r="C101" s="94"/>
-      <c r="D101" s="94"/>
-      <c r="E101" s="94"/>
+      <c r="C101" s="95"/>
+      <c r="D101" s="95"/>
+      <c r="E101" s="95"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="28" t="s">
@@ -3198,7 +3204,7 @@
         <v>176</v>
       </c>
       <c r="C112" s="44">
-        <v>0.12974936050286673</v>
+        <v>0.12974395182995507</v>
       </c>
       <c r="D112" s="61" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
@@ -3206,12 +3212,12 @@
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B114" s="94" t="s">
+      <c r="B114" s="95" t="s">
         <v>217</v>
       </c>
-      <c r="C114" s="94"/>
-      <c r="D114" s="94"/>
-      <c r="E114" s="94"/>
+      <c r="C114" s="95"/>
+      <c r="D114" s="95"/>
+      <c r="E114" s="95"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="21" t="s">
@@ -3244,6 +3250,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
     <mergeCell ref="B86:E86"/>
     <mergeCell ref="B71:E71"/>
     <mergeCell ref="B85:E85"/>
@@ -3253,12 +3265,6 @@
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3308,22 +3314,24 @@
       </c>
       <c r="H1" s="101"/>
       <c r="I1" s="101"/>
-      <c r="J1" s="102" t="s">
+      <c r="J1" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="104" t="s">
+        <v>272</v>
+      </c>
+      <c r="M1" s="104"/>
       <c r="N1" s="98" t="s">
         <v>9</v>
       </c>
       <c r="O1" s="98"/>
-      <c r="P1" s="103" t="s">
+      <c r="P1" s="102" t="s">
         <v>269</v>
       </c>
-      <c r="Q1" s="103"/>
-      <c r="R1" s="103"/>
-      <c r="S1" s="103"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
       <c r="T1" s="99" t="s">
         <v>53</v>
       </c>
@@ -3413,33 +3421,36 @@
         <v>160</v>
       </c>
       <c r="F3" s="15">
-        <v>0.23834947369112891</v>
+        <v>0.23834012469037225</v>
       </c>
       <c r="G3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$10</f>
-        <v>0.12094947369112891</v>
+        <v>0.12094012469037224</v>
       </c>
       <c r="H3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$11</f>
-        <v>0.20384947369112891</v>
+        <v>0.20384012469037224</v>
       </c>
       <c r="I3" s="15">
-        <v>0.23834947369112891</v>
+        <v>0.23834012469037225</v>
       </c>
       <c r="J3" s="2">
-        <v>12.691501140813982</v>
+        <v>12.691224440750165</v>
       </c>
       <c r="K3" s="2">
-        <v>25.696602430940541</v>
+        <v>25.695938127508406</v>
+      </c>
+      <c r="L3" s="2">
+        <v>16.024771926236642</v>
       </c>
       <c r="M3" s="86">
-        <v>21.811108833373932</v>
+        <v>21.810617911761469</v>
       </c>
       <c r="N3" s="4">
-        <v>6.8331310133345272E-2</v>
+        <v>6.8329550953551019E-2</v>
       </c>
       <c r="O3" s="4">
-        <v>3.7484709986796393E-2</v>
+        <v>3.7485676722924174E-2</v>
       </c>
       <c r="P3" s="15">
         <v>0.36794481423679237</v>
@@ -3451,7 +3462,7 @@
         <v>0.60402076709908736</v>
       </c>
       <c r="S3" s="86">
-        <v>4.4986950465252065</v>
+        <v>4.4985790275171595</v>
       </c>
       <c r="T3" s="13" t="s">
         <v>246</v>
@@ -3480,30 +3491,33 @@
         <v>160</v>
       </c>
       <c r="F4" s="15">
-        <v>0.17855667472343195</v>
+        <v>0.17854767299529528</v>
       </c>
       <c r="G4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$10</f>
-        <v>6.1156674723431947E-2</v>
+        <v>6.1147672995295277E-2</v>
       </c>
       <c r="H4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$11</f>
-        <v>0.14405667472343195</v>
+        <v>0.14404767299529528</v>
       </c>
       <c r="I4" s="15">
-        <v>0.17855667472343195</v>
+        <v>0.17854767299529528</v>
       </c>
       <c r="J4" s="2">
-        <v>4.4066254223755825</v>
+        <v>4.4065324767427771</v>
       </c>
       <c r="K4" s="2">
-        <v>7.9180174064472393</v>
+        <v>7.9178132048919672</v>
+      </c>
+      <c r="L4" s="2">
+        <v>5.5130052215060692</v>
       </c>
       <c r="M4" s="86">
-        <v>7.4244984830046468</v>
+        <v>7.4243363812264054</v>
       </c>
       <c r="N4" s="4">
-        <v>0.13261669874486073</v>
+        <v>0.1326132786290983</v>
       </c>
       <c r="O4" s="4">
         <v>7.6196467311032592E-2</v>
@@ -3518,7 +3532,7 @@
         <v>1.1309485990394448</v>
       </c>
       <c r="S4" s="86">
-        <v>-3.7863675235231167</v>
+        <v>-3.7862698750718136</v>
       </c>
       <c r="T4" s="13" t="s">
         <v>239</v>
@@ -3566,6 +3580,9 @@
       <c r="K5" s="2">
         <v>29.309951346473134</v>
       </c>
+      <c r="L5" s="2">
+        <v>18.21218480698677</v>
+      </c>
       <c r="M5" s="86">
         <v>24.796949133193245</v>
       </c>
@@ -3633,6 +3650,9 @@
       <c r="K6" s="2">
         <v>20.508980461992877</v>
       </c>
+      <c r="L6" s="2">
+        <v>14.733437767356989</v>
+      </c>
       <c r="M6" s="86">
         <v>19.785541823839793</v>
       </c>
@@ -3692,13 +3712,16 @@
         <v>8.8789639994280661E-2</v>
       </c>
       <c r="I7" s="15">
-        <v>2.9346308549922262E-2</v>
+        <v>2.9364659278815597E-2</v>
       </c>
       <c r="J7" s="2">
         <v>5.2239462882061574</v>
       </c>
       <c r="K7" s="2">
         <v>9.1628099951889297</v>
+      </c>
+      <c r="L7" s="2">
+        <v>6.5243113398084081</v>
       </c>
       <c r="M7" s="86">
         <v>8.7684502451266084</v>
@@ -3748,33 +3771,36 @@
         <v>160</v>
       </c>
       <c r="F8" s="15">
-        <v>0.10940387682956731</v>
+        <v>0.10939402978090751</v>
       </c>
       <c r="G8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$10</f>
-        <v>-7.9961231704326896E-3</v>
+        <v>-8.0059702190924953E-3</v>
       </c>
       <c r="H8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$11</f>
-        <v>7.4903876829567312E-2</v>
+        <v>7.4894029780907506E-2</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
       </c>
       <c r="J8" s="2">
-        <v>9.1088969706010197</v>
+        <v>9.1086666437717536</v>
       </c>
       <c r="K8" s="2">
-        <v>16.688984661810444</v>
+        <v>16.688564338966547</v>
+      </c>
+      <c r="L8" s="2">
+        <v>11.412172410513048</v>
       </c>
       <c r="M8" s="86">
-        <v>15.394712350875789</v>
+        <v>15.394323329007381</v>
       </c>
       <c r="N8" s="4">
-        <v>0.1076023273696578</v>
+        <v>0.10759953768003538</v>
       </c>
       <c r="O8" s="4">
-        <v>5.8407976157082743E-2</v>
+        <v>5.8406469845722293E-2</v>
       </c>
       <c r="P8" s="15">
         <v>2.2875080906148866</v>
@@ -3786,7 +3812,7 @@
         <v>4.1998196571663646</v>
       </c>
       <c r="S8" s="86">
-        <v>-12.129692853863228</v>
+        <v>-12.129380035386257</v>
       </c>
       <c r="T8" s="13" t="s">
         <v>246</v>
@@ -3815,33 +3841,36 @@
         <v>160</v>
       </c>
       <c r="F9" s="15">
-        <v>0.10815463230293121</v>
+        <v>0.1081465969032307</v>
       </c>
       <c r="G9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$10</f>
-        <v>-9.2453676970687959E-3</v>
+        <v>-9.2534030967693082E-3</v>
       </c>
       <c r="H9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$11</f>
-        <v>7.3654632302931206E-2</v>
+        <v>7.3646596903230693E-2</v>
       </c>
       <c r="I9" s="15">
         <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>34.215998183334875</v>
+        <v>34.215307295933449</v>
       </c>
       <c r="K9" s="2">
-        <v>66.946528402184271</v>
+        <v>66.944798372320093</v>
+      </c>
+      <c r="L9" s="2">
+        <v>43.084161372829577</v>
       </c>
       <c r="M9" s="86">
-        <v>58.457407994642217</v>
+        <v>58.456171666660033</v>
       </c>
       <c r="N9" s="4">
-        <v>4.1506442378573941E-2</v>
+        <v>4.1505376433752697E-2</v>
       </c>
       <c r="O9" s="4">
-        <v>3.8002931783848878E-2</v>
+        <v>3.8003911884992247E-2</v>
       </c>
       <c r="P9" s="15">
         <v>0.72207550313588764</v>
@@ -3853,7 +3882,7 @@
         <v>7.3592411949940734E-2</v>
       </c>
       <c r="S9" s="86">
-        <v>1.3263016249568782</v>
+        <v>1.3262674203270228</v>
       </c>
       <c r="T9" s="13" t="s">
         <v>242</v>
@@ -3882,33 +3911,36 @@
         <v>160</v>
       </c>
       <c r="F10" s="15">
-        <v>0.10196238180241868</v>
+        <v>0.10195477618081239</v>
       </c>
       <c r="G10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$10</f>
-        <v>-1.5437618197581326E-2</v>
+        <v>-1.5445223819187615E-2</v>
       </c>
       <c r="H10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$11</f>
-        <v>6.7462381802418675E-2</v>
+        <v>6.7454776180812387E-2</v>
       </c>
       <c r="I10" s="15">
         <v>0</v>
       </c>
       <c r="J10" s="2">
-        <v>1.435929941306664</v>
+        <v>1.4359031078171438</v>
       </c>
       <c r="K10" s="2">
-        <v>2.6985679028664227</v>
+        <v>2.6984971849946402</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1.8024671110952224</v>
       </c>
       <c r="M10" s="86">
-        <v>2.4368454920607938</v>
+        <v>2.4367969526210818</v>
       </c>
       <c r="N10" s="4">
-        <v>3.5745625781092097E-2</v>
+        <v>3.5744719359166593E-2</v>
       </c>
       <c r="O10" s="4">
-        <v>4.9707984982490863E-2</v>
+        <v>4.970926695866032E-2</v>
       </c>
       <c r="P10" s="15">
         <v>0.20351769929714394</v>
@@ -3920,7 +3952,7 @@
         <v>0.29882156160837919</v>
       </c>
       <c r="S10" s="86">
-        <v>1.866028529531002</v>
+        <v>1.8659804056246816</v>
       </c>
       <c r="T10" s="16" t="s">
         <v>170</v>
@@ -3968,6 +4000,9 @@
       <c r="K11" s="2">
         <v>32.464859269378167</v>
       </c>
+      <c r="L11" s="2">
+        <v>22.157904669779033</v>
+      </c>
       <c r="M11" s="86">
         <v>29.895007167811503</v>
       </c>
@@ -4016,30 +4051,33 @@
         <v>160</v>
       </c>
       <c r="F12" s="15">
-        <v>9.195230665086962E-2</v>
+        <v>9.1942919609277585E-2</v>
       </c>
       <c r="G12" s="15">
         <f>F12 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.5447693349130385E-2</v>
+        <v>-2.545708039072242E-2</v>
       </c>
       <c r="H12" s="15">
         <f>F12 - Portfolio_Mgmt!$C$11</f>
-        <v>5.7452306650869617E-2</v>
+        <v>5.7442919609277582E-2</v>
       </c>
       <c r="I12" s="15">
         <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>30.935095153902036</v>
+        <v>30.934297353869699</v>
       </c>
       <c r="K12" s="2">
-        <v>67.964404053122792</v>
+        <v>67.962651286451745</v>
+      </c>
+      <c r="L12" s="2">
+        <v>39.330238012992908</v>
       </c>
       <c r="M12" s="86">
-        <v>53.95233517909076</v>
+        <v>53.950943776396301</v>
       </c>
       <c r="N12" s="4">
-        <v>0.10065745348000395</v>
+        <v>0.10065485757657319</v>
       </c>
       <c r="O12" s="4">
         <v>0</v>
@@ -4054,7 +4092,7 @@
         <v>0.73855199466278643</v>
       </c>
       <c r="S12" s="86">
-        <v>-2.6424909744367104</v>
+        <v>-2.6424228259673308</v>
       </c>
       <c r="T12" s="13" t="s">
         <v>246</v>
@@ -6130,13 +6168,14 @@
       <c r="T358" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="T1:W1"/>
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="G1:I1"/>
-    <mergeCell ref="J1:M1"/>
     <mergeCell ref="P1:S1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6540,7 +6579,7 @@
       </c>
       <c r="H5" s="73">
         <f>VLOOKUP(B5,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>2.9346308549922262E-2</v>
+        <v>2.9364659278815597E-2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -6568,7 +6607,7 @@
       </c>
       <c r="H6" s="73">
         <f>VLOOKUP(B6,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.17855667472343195</v>
+        <v>0.17854767299529528</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -6596,7 +6635,7 @@
       </c>
       <c r="H7" s="73">
         <f>VLOOKUP(B7,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.23834947369112891</v>
+        <v>0.23834012469037225</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -6663,7 +6702,7 @@
       </c>
       <c r="H12" s="73">
         <f>VLOOKUP(B12,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.23834947369112891</v>
+        <v>0.23834012469037225</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -6776,25 +6815,25 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="B3" s="104" t="s">
+      <c r="B3" s="105" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="105"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="B5" s="105" t="s">
+      <c r="B5" s="106" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="95"/>
-      <c r="D5" s="95"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="97"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="B6" s="105" t="s">
+      <c r="B6" s="106" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="97"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">
@@ -6808,18 +6847,18 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="104" t="s">
+      <c r="B11" s="105" t="s">
         <v>109</v>
       </c>
-      <c r="C11" s="104"/>
-      <c r="D11" s="104"/>
+      <c r="C11" s="105"/>
+      <c r="D11" s="105"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="B12" s="104" t="s">
+      <c r="B12" s="105" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
+      <c r="C12" s="105"/>
+      <c r="D12" s="105"/>
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="23" t="s">
@@ -6913,18 +6952,18 @@
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="B28" s="104" t="s">
+      <c r="B28" s="105" t="s">
         <v>122</v>
       </c>
-      <c r="C28" s="104"/>
-      <c r="D28" s="104"/>
+      <c r="C28" s="105"/>
+      <c r="D28" s="105"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="B29" s="104" t="s">
+      <c r="B29" s="105" t="s">
         <v>123</v>
       </c>
-      <c r="C29" s="104"/>
-      <c r="D29" s="104"/>
+      <c r="C29" s="105"/>
+      <c r="D29" s="105"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="5"/>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3680A6A-F52D-4D09-B2E4-B4D7B2015D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27358B8F-CBD8-44A6-A566-0631C599AD60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3204,7 +3204,7 @@
         <v>176</v>
       </c>
       <c r="C112" s="44">
-        <v>0.12974395182995507</v>
+        <v>0.11749874685956269</v>
       </c>
       <c r="D112" s="61" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
@@ -3415,24 +3415,24 @@
         <v>259</v>
       </c>
       <c r="D3" s="2">
-        <v>14.62</v>
+        <v>15.26</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F3" s="15">
-        <v>0.23834012469037225</v>
+        <v>0.2202784312360544</v>
       </c>
       <c r="G3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$10</f>
-        <v>0.12094012469037224</v>
+        <v>0.10287843123605439</v>
       </c>
       <c r="H3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$11</f>
-        <v>0.20384012469037224</v>
+        <v>0.18577843123605439</v>
       </c>
       <c r="I3" s="15">
-        <v>0.23834012469037225</v>
+        <v>0.2202784312360544</v>
       </c>
       <c r="J3" s="2">
         <v>12.691224440750165</v>
@@ -3447,10 +3447,10 @@
         <v>21.810617911761469</v>
       </c>
       <c r="N3" s="4">
-        <v>6.8329550953551019E-2</v>
+        <v>6.5463829288395545E-2</v>
       </c>
       <c r="O3" s="4">
-        <v>3.7485676722924174E-2</v>
+        <v>3.5913538249616732E-2</v>
       </c>
       <c r="P3" s="15">
         <v>0.36794481423679237</v>
@@ -3485,24 +3485,24 @@
         <v>237</v>
       </c>
       <c r="D4" s="2">
-        <v>5.8</v>
+        <v>5.94</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F4" s="15">
-        <v>0.17854767299529528</v>
+        <v>0.1686112219828888</v>
       </c>
       <c r="G4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$10</f>
-        <v>6.1147672995295277E-2</v>
+        <v>5.1211221982888799E-2</v>
       </c>
       <c r="H4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$11</f>
-        <v>0.14404767299529528</v>
+        <v>0.1341112219828888</v>
       </c>
       <c r="I4" s="15">
-        <v>0.17854767299529528</v>
+        <v>0.16861122198288883</v>
       </c>
       <c r="J4" s="2">
         <v>4.4065324767427771</v>
@@ -3517,10 +3517,10 @@
         <v>7.4243363812264054</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1326132786290983</v>
+        <v>0.12948771313952359</v>
       </c>
       <c r="O4" s="4">
-        <v>7.6196467311032592E-2</v>
+        <v>7.4400590977102513E-2</v>
       </c>
       <c r="P4" s="15">
         <v>0.61007460831657279</v>
@@ -3625,24 +3625,24 @@
         <v>159</v>
       </c>
       <c r="D6" s="2">
-        <v>16.440000000000001</v>
+        <v>17.36</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F6" s="15">
-        <v>0.15374754303551685</v>
+        <v>0.13150710314103176</v>
       </c>
       <c r="G6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$10</f>
-        <v>3.6347543035516849E-2</v>
+        <v>1.4107103141031752E-2</v>
       </c>
       <c r="H6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$11</f>
-        <v>0.11924754303551685</v>
+        <v>9.7007103141031753E-2</v>
       </c>
       <c r="I6" s="15">
-        <v>0.15374754303551685</v>
+        <v>0.13150710314103176</v>
       </c>
       <c r="J6" s="2">
         <v>11.804906901225705</v>
@@ -3657,10 +3657,10 @@
         <v>19.785541823839793</v>
       </c>
       <c r="N6" s="4">
-        <v>0.10510863864778767</v>
+        <v>9.9538365171061599E-2</v>
       </c>
       <c r="O6" s="4">
-        <v>8.2725060827250604E-2</v>
+        <v>7.83410138248848E-2</v>
       </c>
       <c r="P6" s="15">
         <v>0.31018327415220487</v>
@@ -3695,24 +3695,24 @@
         <v>165</v>
       </c>
       <c r="D7" s="2">
-        <v>7.85</v>
+        <v>7.94</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F7" s="15">
-        <v>0.12328963999428066</v>
+        <v>0.11874261404950959</v>
       </c>
       <c r="G7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$10</f>
-        <v>5.8896399942806599E-3</v>
+        <v>1.3426140495095829E-3</v>
       </c>
       <c r="H7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$11</f>
-        <v>8.8789639994280661E-2</v>
+        <v>8.4242614049509584E-2</v>
       </c>
       <c r="I7" s="15">
-        <v>2.9364659278815597E-2</v>
+        <v>7.9603243640025023E-2</v>
       </c>
       <c r="J7" s="2">
         <v>5.2239462882061574</v>
@@ -3727,10 +3727,10 @@
         <v>8.7684502451266084</v>
       </c>
       <c r="N7" s="4">
-        <v>3.9350111080543315E-2</v>
+        <v>3.8904077075852014E-2</v>
       </c>
       <c r="O7" s="4">
-        <v>7.3885350318471335E-2</v>
+        <v>7.3047858942065488E-2</v>
       </c>
       <c r="P7" s="15">
         <v>8.3114411724224596E-2</v>
@@ -3765,21 +3765,21 @@
         <v>245</v>
       </c>
       <c r="D8" s="2">
-        <v>14.26</v>
+        <v>14.64</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F8" s="15">
-        <v>0.10939402978090751</v>
+        <v>9.919795200818049E-2</v>
       </c>
       <c r="G8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$10</f>
-        <v>-8.0059702190924953E-3</v>
+        <v>-1.8202047991819514E-2</v>
       </c>
       <c r="H8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$11</f>
-        <v>7.4894029780907506E-2</v>
+        <v>6.4697952008180487E-2</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
@@ -3797,10 +3797,10 @@
         <v>15.394323329007381</v>
       </c>
       <c r="N8" s="4">
-        <v>0.10759953768003538</v>
+        <v>0.10480665350528036</v>
       </c>
       <c r="O8" s="4">
-        <v>5.8406469845722293E-2</v>
+        <v>5.6890454918032782E-2</v>
       </c>
       <c r="P8" s="15">
         <v>2.2875080906148866</v>
@@ -3829,63 +3829,63 @@
     </row>
     <row r="9" spans="1:23">
       <c r="B9" s="11" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="D9" s="2">
-        <v>54.25</v>
+        <v>28.81</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>160</v>
+        <v>253</v>
       </c>
       <c r="F9" s="15">
-        <v>0.1081465969032307</v>
+        <v>9.408289080523935E-2</v>
       </c>
       <c r="G9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$10</f>
-        <v>-9.2534030967693082E-3</v>
+        <v>-2.3317109194760655E-2</v>
       </c>
       <c r="H9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$11</f>
-        <v>7.3646596903230693E-2</v>
+        <v>5.9582890805239347E-2</v>
       </c>
       <c r="I9" s="15">
         <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>34.215307295933449</v>
+        <v>17.682685147645955</v>
       </c>
       <c r="K9" s="2">
-        <v>66.944798372320093</v>
+        <v>32.464859269378167</v>
       </c>
       <c r="L9" s="2">
-        <v>43.084161372829577</v>
+        <v>22.157904669779033</v>
       </c>
       <c r="M9" s="86">
-        <v>58.456171666660033</v>
+        <v>29.895007167811503</v>
       </c>
       <c r="N9" s="4">
-        <v>4.1505376433752697E-2</v>
+        <v>8.8134932571433455E-2</v>
       </c>
       <c r="O9" s="4">
-        <v>3.8003911884992247E-2</v>
+        <v>5.5536272127733433E-2</v>
       </c>
       <c r="P9" s="15">
-        <v>0.72207550313588764</v>
+        <v>0.78990369994931575</v>
       </c>
       <c r="Q9" s="15">
-        <v>9.5579625064196368E-3</v>
+        <v>0.40281804358844397</v>
       </c>
       <c r="R9" s="92">
-        <v>7.3592411949940734E-2</v>
+        <v>3.955391512509995</v>
       </c>
       <c r="S9" s="86">
-        <v>1.3262674203270228</v>
+        <v>-26.938493611476797</v>
       </c>
       <c r="T9" s="13" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="U9" s="11" t="s">
         <v>162</v>
@@ -3894,144 +3894,144 @@
         <v>45900</v>
       </c>
       <c r="W9" s="11" t="s">
-        <v>247</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:23">
       <c r="B10" s="11" t="s">
-        <v>168</v>
+        <v>240</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>169</v>
+        <v>241</v>
       </c>
       <c r="D10" s="2">
-        <v>2.2999999999999998</v>
+        <v>56.45</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F10" s="15">
-        <v>0.10195477618081239</v>
+        <v>9.3068045296727409E-2</v>
       </c>
       <c r="G10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$10</f>
-        <v>-1.5445223819187615E-2</v>
+        <v>-2.4331954703272596E-2</v>
       </c>
       <c r="H10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$11</f>
-        <v>6.7454776180812387E-2</v>
+        <v>5.8568045296727406E-2</v>
       </c>
       <c r="I10" s="15">
         <v>0</v>
       </c>
       <c r="J10" s="2">
-        <v>1.4359031078171438</v>
+        <v>34.215307295933449</v>
       </c>
       <c r="K10" s="2">
-        <v>2.6984971849946402</v>
+        <v>66.944798372320093</v>
       </c>
       <c r="L10" s="2">
-        <v>1.8024671110952224</v>
+        <v>43.084161372829577</v>
       </c>
       <c r="M10" s="86">
-        <v>2.4367969526210818</v>
+        <v>58.456171666660033</v>
       </c>
       <c r="N10" s="4">
-        <v>3.5744719359166593E-2</v>
+        <v>3.9887806404447897E-2</v>
       </c>
       <c r="O10" s="4">
-        <v>4.970926695866032E-2</v>
+        <v>3.652280283012984E-2</v>
       </c>
       <c r="P10" s="15">
-        <v>0.20351769929714394</v>
+        <v>0.72207550313588764</v>
       </c>
       <c r="Q10" s="15">
-        <v>1.0763175939415467E-2</v>
+        <v>9.5579625064196368E-3</v>
       </c>
       <c r="R10" s="92">
-        <v>0.29882156160837919</v>
+        <v>7.3592411949940734E-2</v>
       </c>
       <c r="S10" s="86">
-        <v>1.8659804056246816</v>
+        <v>1.3262674203270228</v>
       </c>
       <c r="T10" s="16" t="s">
-        <v>170</v>
+        <v>242</v>
       </c>
       <c r="U10" s="11" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="V10" s="14">
         <v>45900</v>
       </c>
       <c r="W10" s="11" t="s">
-        <v>163</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="1:23">
       <c r="B11" s="11" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="D11" s="2">
-        <v>28.81</v>
+        <v>53.85</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>253</v>
+        <v>160</v>
       </c>
       <c r="F11" s="15">
-        <v>9.408289080523935E-2</v>
+        <v>8.0674411817778235E-2</v>
       </c>
       <c r="G11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.3317109194760655E-2</v>
+        <v>-3.6725588182221769E-2</v>
       </c>
       <c r="H11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$11</f>
-        <v>5.9582890805239347E-2</v>
+        <v>4.6174411817778233E-2</v>
       </c>
       <c r="I11" s="15">
         <v>0</v>
       </c>
       <c r="J11" s="2">
-        <v>17.682685147645955</v>
+        <v>30.934297353869699</v>
       </c>
       <c r="K11" s="2">
-        <v>32.464859269378167</v>
+        <v>67.962651286451745</v>
       </c>
       <c r="L11" s="2">
-        <v>22.157904669779033</v>
+        <v>39.330238012992908</v>
       </c>
       <c r="M11" s="86">
-        <v>29.895007167811503</v>
+        <v>53.950943776396301</v>
       </c>
       <c r="N11" s="4">
-        <v>8.8134932571433455E-2</v>
+        <v>9.7570725450271498E-2</v>
       </c>
       <c r="O11" s="4">
-        <v>5.5536272127733433E-2</v>
+        <v>0</v>
       </c>
       <c r="P11" s="15">
-        <v>0.78990369994931575</v>
+        <v>1.2907496012759174</v>
       </c>
       <c r="Q11" s="15">
-        <v>0.40281804358844397</v>
+        <v>0.24768740031897937</v>
       </c>
       <c r="R11" s="92">
-        <v>3.955391512509995</v>
+        <v>0.73855199466278643</v>
       </c>
       <c r="S11" s="86">
-        <v>-26.938493611476797</v>
+        <v>-2.6424228259673308</v>
       </c>
       <c r="T11" s="13" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="U11" s="11" t="s">
         <v>162</v>
       </c>
       <c r="V11" s="14">
-        <v>45900</v>
+        <v>45808</v>
       </c>
       <c r="W11" s="11" t="s">
         <v>163</v>
@@ -4039,69 +4039,69 @@
     </row>
     <row r="12" spans="1:23">
       <c r="B12" s="11" t="s">
-        <v>249</v>
+        <v>168</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>250</v>
+        <v>169</v>
       </c>
       <c r="D12" s="2">
-        <v>52.2</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F12" s="15">
-        <v>9.1942919609277585E-2</v>
+        <v>6.8934165996179741E-2</v>
       </c>
       <c r="G12" s="15">
         <f>F12 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.545708039072242E-2</v>
+        <v>-4.8465834003820263E-2</v>
       </c>
       <c r="H12" s="15">
         <f>F12 - Portfolio_Mgmt!$C$11</f>
-        <v>5.7442919609277582E-2</v>
+        <v>3.4434165996179739E-2</v>
       </c>
       <c r="I12" s="15">
         <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>30.934297353869699</v>
+        <v>1.4359031078171438</v>
       </c>
       <c r="K12" s="2">
-        <v>67.962651286451745</v>
+        <v>2.6984971849946402</v>
       </c>
       <c r="L12" s="2">
-        <v>39.330238012992908</v>
+        <v>1.8024671110952224</v>
       </c>
       <c r="M12" s="86">
-        <v>53.950943776396301</v>
+        <v>2.4367969526210818</v>
       </c>
       <c r="N12" s="4">
-        <v>0.10065485757657319</v>
+        <v>3.2754125309196483E-2</v>
       </c>
       <c r="O12" s="4">
-        <v>0</v>
+        <v>4.55503243047485E-2</v>
       </c>
       <c r="P12" s="15">
-        <v>1.2907496012759174</v>
+        <v>0.20351769929714394</v>
       </c>
       <c r="Q12" s="15">
-        <v>0.24768740031897937</v>
+        <v>1.0763175939415467E-2</v>
       </c>
       <c r="R12" s="92">
-        <v>0.73855199466278643</v>
+        <v>0.29882156160837919</v>
       </c>
       <c r="S12" s="86">
-        <v>-2.6424228259673308</v>
+        <v>1.8659804056246816</v>
       </c>
       <c r="T12" s="13" t="s">
-        <v>246</v>
+        <v>170</v>
       </c>
       <c r="U12" s="11" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="V12" s="14">
-        <v>45808</v>
+        <v>45900</v>
       </c>
       <c r="W12" s="11" t="s">
         <v>163</v>
@@ -6520,7 +6520,7 @@
       </c>
       <c r="G3" s="73">
         <f>F3/$F$9</f>
-        <v>0.40627734298520357</v>
+        <v>0.39828327116190743</v>
       </c>
       <c r="H3" s="91" t="s">
         <v>233</v>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="C4" s="75">
         <f>VLOOKUP(B4,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>16.440000000000001</v>
+        <v>17.36</v>
       </c>
       <c r="D4" s="74" t="str">
         <f>VLOOKUP(B4,Opportunities!B$3:E$12,4,FALSE)</f>
@@ -6543,15 +6543,15 @@
       </c>
       <c r="F4" s="76">
         <f>C4*E4</f>
-        <v>164400</v>
+        <v>173600</v>
       </c>
       <c r="G4" s="73">
         <f>F4/$F$9</f>
-        <v>0.19007634525088124</v>
+        <v>0.1967639092192075</v>
       </c>
       <c r="H4" s="73">
         <f>VLOOKUP(B4,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.15374754303551685</v>
+        <v>0.13150710314103176</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="C5" s="75">
         <f>VLOOKUP(B5,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>7.85</v>
+        <v>7.94</v>
       </c>
       <c r="D5" s="74" t="str">
         <f>VLOOKUP(B5,Opportunities!B$3:E$12,4,FALSE)</f>
@@ -6571,15 +6571,15 @@
       </c>
       <c r="F5" s="76">
         <f>E5*C5</f>
-        <v>157000</v>
+        <v>158800</v>
       </c>
       <c r="G5" s="73">
         <f>F5/$F$9</f>
-        <v>0.18152059735029413</v>
+        <v>0.17998910589867598</v>
       </c>
       <c r="H5" s="73">
         <f>VLOOKUP(B5,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>2.9364659278815597E-2</v>
+        <v>7.9603243640025023E-2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="C6" s="75">
         <f>VLOOKUP(B6,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>5.8</v>
+        <v>5.94</v>
       </c>
       <c r="D6" s="74" t="str">
         <f>VLOOKUP(B6,Opportunities!B$3:E$12,4,FALSE)</f>
@@ -6599,15 +6599,15 @@
       </c>
       <c r="F6" s="76">
         <f>E6*C6</f>
-        <v>104400</v>
+        <v>106920</v>
       </c>
       <c r="G6" s="73">
         <f>F6/$F$9</f>
-        <v>0.12070541632720196</v>
+        <v>0.12118661966427226</v>
       </c>
       <c r="H6" s="73">
         <f>VLOOKUP(B6,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.17854767299529528</v>
+        <v>0.16861122198288883</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="C7" s="75">
         <f>VLOOKUP(B7,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>14.62</v>
+        <v>15.26</v>
       </c>
       <c r="D7" s="74" t="str">
         <f>VLOOKUP(B7,Opportunities!B$3:E$12,4,FALSE)</f>
@@ -6627,15 +6627,15 @@
       </c>
       <c r="F7" s="76">
         <f>C7*E7</f>
-        <v>87720</v>
+        <v>91560</v>
       </c>
       <c r="G7" s="73">
         <f>F7/$F$9</f>
-        <v>0.10142029808641911</v>
+        <v>0.10377709405593685</v>
       </c>
       <c r="H7" s="73">
         <f>VLOOKUP(B7,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.23834012469037225</v>
+        <v>0.2202784312360544</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="F9" s="81">
         <f>SUM(F3:F7)</f>
-        <v>864915.62</v>
+        <v>882275.62</v>
       </c>
       <c r="G9" s="82">
         <f>SUM(G3:G7)</f>
@@ -6683,7 +6683,7 @@
       </c>
       <c r="C12" s="75">
         <f>VLOOKUP(B12,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>14.62</v>
+        <v>15.26</v>
       </c>
       <c r="D12" s="74" t="str">
         <f>VLOOKUP(B12,Opportunities!B$3:E$12,4,FALSE)</f>
@@ -6694,15 +6694,15 @@
       </c>
       <c r="F12" s="76">
         <f>C12*E12</f>
-        <v>87720</v>
+        <v>91560</v>
       </c>
       <c r="G12" s="73">
         <f>F12/$F$9</f>
-        <v>0.10142029808641911</v>
+        <v>0.10377709405593685</v>
       </c>
       <c r="H12" s="73">
         <f>VLOOKUP(B12,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.23834012469037225</v>
+        <v>0.2202784312360544</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -6724,11 +6724,11 @@
       </c>
       <c r="F14" s="81">
         <f>F3-F12</f>
-        <v>263675.62</v>
+        <v>259835.62</v>
       </c>
       <c r="G14" s="89">
         <f t="shared" ref="G14" si="0">F14/$F$9</f>
-        <v>0.30485704489878446</v>
+        <v>0.2945061771059706</v>
       </c>
       <c r="H14" s="89">
         <f>Portfolio_Mgmt!E61</f>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27358B8F-CBD8-44A6-A566-0631C599AD60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D57FEE5-3CCE-4688-A49E-F2CE4FB8236F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3204,7 +3204,7 @@
         <v>176</v>
       </c>
       <c r="C112" s="44">
-        <v>0.11749874685956269</v>
+        <v>0.12155581855631381</v>
       </c>
       <c r="D112" s="61" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
@@ -3619,63 +3619,63 @@
     </row>
     <row r="6" spans="1:23">
       <c r="B6" s="11" t="s">
-        <v>158</v>
+        <v>249</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>159</v>
+        <v>250</v>
       </c>
       <c r="D6" s="2">
-        <v>17.36</v>
+        <v>53.85</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F6" s="15">
-        <v>0.13150710314103176</v>
+        <v>0.15157025452393125</v>
       </c>
       <c r="G6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$10</f>
-        <v>1.4107103141031752E-2</v>
+        <v>3.4170254523931243E-2</v>
       </c>
       <c r="H6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$11</f>
-        <v>9.7007103141031753E-2</v>
+        <v>0.11707025452393124</v>
       </c>
       <c r="I6" s="15">
-        <v>0.13150710314103176</v>
+        <v>0.15157025452393125</v>
       </c>
       <c r="J6" s="2">
-        <v>11.804906901225705</v>
+        <v>38.606046318120192</v>
       </c>
       <c r="K6" s="2">
-        <v>20.508980461992877</v>
+        <v>64.705150610910081</v>
       </c>
       <c r="L6" s="2">
-        <v>14.733437767356989</v>
+        <v>48.063219913721113</v>
       </c>
       <c r="M6" s="86">
-        <v>19.785541823839793</v>
+        <v>64.355368842171927</v>
       </c>
       <c r="N6" s="4">
-        <v>9.9538365171061599E-2</v>
+        <v>9.7570725450271498E-2</v>
       </c>
       <c r="O6" s="4">
-        <v>7.83410138248848E-2</v>
+        <v>9.3606035283194056E-2</v>
       </c>
       <c r="P6" s="15">
-        <v>0.31018327415220487</v>
+        <v>1.2907496012759174</v>
       </c>
       <c r="Q6" s="15">
-        <v>0.15818859882129041</v>
+        <v>0.24768740031897937</v>
       </c>
       <c r="R6" s="92">
-        <v>1.4550387206421544</v>
+        <v>0.73855199466278643</v>
       </c>
       <c r="S6" s="86">
-        <v>5.8696003638854428</v>
+        <v>-2.6424228259673308</v>
       </c>
       <c r="T6" s="13" t="s">
-        <v>161</v>
+        <v>246</v>
       </c>
       <c r="U6" s="11" t="s">
         <v>162</v>
@@ -3689,69 +3689,69 @@
     </row>
     <row r="7" spans="1:23">
       <c r="B7" s="11" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D7" s="2">
-        <v>7.94</v>
+        <v>17.36</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F7" s="15">
-        <v>0.11874261404950959</v>
+        <v>0.13150710314103176</v>
       </c>
       <c r="G7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$10</f>
-        <v>1.3426140495095829E-3</v>
+        <v>1.4107103141031752E-2</v>
       </c>
       <c r="H7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$11</f>
-        <v>8.4242614049509584E-2</v>
+        <v>9.7007103141031753E-2</v>
       </c>
       <c r="I7" s="15">
-        <v>7.9603243640025023E-2</v>
+        <v>5.9540092257125532E-2</v>
       </c>
       <c r="J7" s="2">
-        <v>5.2239462882061574</v>
+        <v>11.804906901225705</v>
       </c>
       <c r="K7" s="2">
-        <v>9.1628099951889297</v>
+        <v>20.508980461992877</v>
       </c>
       <c r="L7" s="2">
-        <v>6.5243113398084081</v>
+        <v>14.733437767356989</v>
       </c>
       <c r="M7" s="86">
-        <v>8.7684502451266084</v>
+        <v>19.785541823839793</v>
       </c>
       <c r="N7" s="4">
-        <v>3.8904077075852014E-2</v>
+        <v>9.9538365171061599E-2</v>
       </c>
       <c r="O7" s="4">
-        <v>7.3047858942065488E-2</v>
+        <v>7.83410138248848E-2</v>
       </c>
       <c r="P7" s="15">
-        <v>8.3114411724224596E-2</v>
+        <v>0.31018327415220487</v>
       </c>
       <c r="Q7" s="15">
-        <v>1.8509098960546238E-2</v>
+        <v>0.15818859882129041</v>
       </c>
       <c r="R7" s="92">
-        <v>1.1933697905849452</v>
+        <v>1.4550387206421544</v>
       </c>
       <c r="S7" s="86">
-        <v>11.511512740854835</v>
+        <v>5.8696003638854428</v>
       </c>
       <c r="T7" s="13" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="U7" s="11" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="V7" s="14">
-        <v>45900</v>
+        <v>45808</v>
       </c>
       <c r="W7" s="11" t="s">
         <v>163</v>
@@ -3759,203 +3759,203 @@
     </row>
     <row r="8" spans="1:23">
       <c r="B8" s="11" t="s">
-        <v>244</v>
+        <v>164</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>245</v>
+        <v>165</v>
       </c>
       <c r="D8" s="2">
-        <v>14.64</v>
+        <v>7.94</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F8" s="15">
-        <v>9.919795200818049E-2</v>
+        <v>0.11874261404950959</v>
       </c>
       <c r="G8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$10</f>
-        <v>-1.8202047991819514E-2</v>
+        <v>1.3426140495095829E-3</v>
       </c>
       <c r="H8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$11</f>
-        <v>6.4697952008180487E-2</v>
+        <v>8.4242614049509584E-2</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
       </c>
       <c r="J8" s="2">
-        <v>9.1086666437717536</v>
+        <v>5.2239462882061574</v>
       </c>
       <c r="K8" s="2">
-        <v>16.688564338966547</v>
+        <v>9.1628099951889297</v>
       </c>
       <c r="L8" s="2">
-        <v>11.412172410513048</v>
+        <v>6.5243113398084081</v>
       </c>
       <c r="M8" s="86">
-        <v>15.394323329007381</v>
+        <v>8.7684502451266084</v>
       </c>
       <c r="N8" s="4">
-        <v>0.10480665350528036</v>
+        <v>3.8904077075852014E-2</v>
       </c>
       <c r="O8" s="4">
-        <v>5.6890454918032782E-2</v>
+        <v>7.3047858942065488E-2</v>
       </c>
       <c r="P8" s="15">
-        <v>2.2875080906148866</v>
+        <v>8.3114411724224596E-2</v>
       </c>
       <c r="Q8" s="15">
-        <v>1.5035598705501618</v>
+        <v>1.8509098960546238E-2</v>
       </c>
       <c r="R8" s="92">
-        <v>4.1998196571663646</v>
+        <v>1.1933697905849452</v>
       </c>
       <c r="S8" s="86">
-        <v>-12.129380035386257</v>
+        <v>11.511512740854835</v>
       </c>
       <c r="T8" s="13" t="s">
-        <v>246</v>
+        <v>166</v>
       </c>
       <c r="U8" s="11" t="s">
-        <v>248</v>
+        <v>167</v>
       </c>
       <c r="V8" s="14">
         <v>45900</v>
       </c>
       <c r="W8" s="11" t="s">
-        <v>247</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:23">
       <c r="B9" s="11" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="D9" s="2">
-        <v>28.81</v>
+        <v>14.64</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>253</v>
+        <v>160</v>
       </c>
       <c r="F9" s="15">
-        <v>9.408289080523935E-2</v>
+        <v>9.919795200818049E-2</v>
       </c>
       <c r="G9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.3317109194760655E-2</v>
+        <v>-1.8202047991819514E-2</v>
       </c>
       <c r="H9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$11</f>
-        <v>5.9582890805239347E-2</v>
+        <v>6.4697952008180487E-2</v>
       </c>
       <c r="I9" s="15">
         <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>17.682685147645955</v>
+        <v>9.1086666437717536</v>
       </c>
       <c r="K9" s="2">
-        <v>32.464859269378167</v>
+        <v>16.688564338966547</v>
       </c>
       <c r="L9" s="2">
-        <v>22.157904669779033</v>
+        <v>11.412172410513048</v>
       </c>
       <c r="M9" s="86">
-        <v>29.895007167811503</v>
+        <v>15.394323329007381</v>
       </c>
       <c r="N9" s="4">
-        <v>8.8134932571433455E-2</v>
+        <v>0.10480665350528036</v>
       </c>
       <c r="O9" s="4">
-        <v>5.5536272127733433E-2</v>
+        <v>5.6890454918032782E-2</v>
       </c>
       <c r="P9" s="15">
-        <v>0.78990369994931575</v>
+        <v>2.2875080906148866</v>
       </c>
       <c r="Q9" s="15">
-        <v>0.40281804358844397</v>
+        <v>1.5035598705501618</v>
       </c>
       <c r="R9" s="92">
-        <v>3.955391512509995</v>
+        <v>4.1998196571663646</v>
       </c>
       <c r="S9" s="86">
-        <v>-26.938493611476797</v>
+        <v>-12.129380035386257</v>
       </c>
       <c r="T9" s="13" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="U9" s="11" t="s">
-        <v>162</v>
+        <v>248</v>
       </c>
       <c r="V9" s="14">
         <v>45900</v>
       </c>
       <c r="W9" s="11" t="s">
-        <v>163</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:23">
       <c r="B10" s="11" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="D10" s="2">
-        <v>56.45</v>
+        <v>28.81</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>160</v>
+        <v>253</v>
       </c>
       <c r="F10" s="15">
-        <v>9.3068045296727409E-2</v>
+        <v>9.408289080523935E-2</v>
       </c>
       <c r="G10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.4331954703272596E-2</v>
+        <v>-2.3317109194760655E-2</v>
       </c>
       <c r="H10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$11</f>
-        <v>5.8568045296727406E-2</v>
+        <v>5.9582890805239347E-2</v>
       </c>
       <c r="I10" s="15">
         <v>0</v>
       </c>
       <c r="J10" s="2">
-        <v>34.215307295933449</v>
+        <v>17.682685147645955</v>
       </c>
       <c r="K10" s="2">
-        <v>66.944798372320093</v>
+        <v>32.464859269378167</v>
       </c>
       <c r="L10" s="2">
-        <v>43.084161372829577</v>
+        <v>22.157904669779033</v>
       </c>
       <c r="M10" s="86">
-        <v>58.456171666660033</v>
+        <v>29.895007167811503</v>
       </c>
       <c r="N10" s="4">
-        <v>3.9887806404447897E-2</v>
+        <v>8.8134932571433455E-2</v>
       </c>
       <c r="O10" s="4">
-        <v>3.652280283012984E-2</v>
+        <v>5.5536272127733433E-2</v>
       </c>
       <c r="P10" s="15">
-        <v>0.72207550313588764</v>
+        <v>0.78990369994931575</v>
       </c>
       <c r="Q10" s="15">
-        <v>9.5579625064196368E-3</v>
+        <v>0.40281804358844397</v>
       </c>
       <c r="R10" s="92">
-        <v>7.3592411949940734E-2</v>
+        <v>3.955391512509995</v>
       </c>
       <c r="S10" s="86">
-        <v>1.3262674203270228</v>
+        <v>-26.938493611476797</v>
       </c>
       <c r="T10" s="16" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="U10" s="11" t="s">
         <v>162</v>
@@ -3964,77 +3964,77 @@
         <v>45900</v>
       </c>
       <c r="W10" s="11" t="s">
-        <v>247</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:23">
       <c r="B11" s="11" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D11" s="2">
-        <v>53.85</v>
+        <v>56.45</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F11" s="15">
-        <v>8.0674411817778235E-2</v>
+        <v>9.3068045296727409E-2</v>
       </c>
       <c r="G11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$10</f>
-        <v>-3.6725588182221769E-2</v>
+        <v>-2.4331954703272596E-2</v>
       </c>
       <c r="H11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$11</f>
-        <v>4.6174411817778233E-2</v>
+        <v>5.8568045296727406E-2</v>
       </c>
       <c r="I11" s="15">
         <v>0</v>
       </c>
       <c r="J11" s="2">
-        <v>30.934297353869699</v>
+        <v>34.215307295933449</v>
       </c>
       <c r="K11" s="2">
-        <v>67.962651286451745</v>
+        <v>66.944798372320093</v>
       </c>
       <c r="L11" s="2">
-        <v>39.330238012992908</v>
+        <v>43.084161372829577</v>
       </c>
       <c r="M11" s="86">
-        <v>53.950943776396301</v>
+        <v>58.456171666660033</v>
       </c>
       <c r="N11" s="4">
-        <v>9.7570725450271498E-2</v>
+        <v>3.9887806404447897E-2</v>
       </c>
       <c r="O11" s="4">
-        <v>0</v>
+        <v>3.652280283012984E-2</v>
       </c>
       <c r="P11" s="15">
-        <v>1.2907496012759174</v>
+        <v>0.72207550313588764</v>
       </c>
       <c r="Q11" s="15">
-        <v>0.24768740031897937</v>
+        <v>9.5579625064196368E-3</v>
       </c>
       <c r="R11" s="92">
-        <v>0.73855199466278643</v>
+        <v>7.3592411949940734E-2</v>
       </c>
       <c r="S11" s="86">
-        <v>-2.6424228259673308</v>
+        <v>1.3262674203270228</v>
       </c>
       <c r="T11" s="13" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="U11" s="11" t="s">
         <v>162</v>
       </c>
       <c r="V11" s="14">
-        <v>45808</v>
+        <v>45900</v>
       </c>
       <c r="W11" s="11" t="s">
-        <v>163</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" spans="1:23">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="H4" s="73">
         <f>VLOOKUP(B4,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.13150710314103176</v>
+        <v>5.9540092257125532E-2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="H5" s="73">
         <f>VLOOKUP(B5,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>7.9603243640025023E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="H9" s="89">
         <f>SUM(H4:H7)</f>
-        <v>0.6</v>
+        <v>0.44842974547606873</v>
       </c>
     </row>
     <row r="10" spans="1:8">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D57FEE5-3CCE-4688-A49E-F2CE4FB8236F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EF0A24-B245-4A9E-BE31-DB0AF2842B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2179,17 +2179,17 @@
     <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2570,12 +2570,12 @@
       <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B4" s="95" t="s">
+      <c r="B4" s="94" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="20" t="s">
@@ -2587,12 +2587,12 @@
       <c r="C6" s="61"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" s="95" t="s">
+      <c r="B7" s="94" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="95"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="94"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="23" t="s">
@@ -2681,12 +2681,12 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
-      <c r="B24" s="95" t="s">
+      <c r="B24" s="94" t="s">
         <v>220</v>
       </c>
-      <c r="C24" s="95"/>
-      <c r="D24" s="95"/>
-      <c r="E24" s="95"/>
+      <c r="C24" s="94"/>
+      <c r="D24" s="94"/>
+      <c r="E24" s="94"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
@@ -2786,20 +2786,20 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="B39" s="95" t="s">
+      <c r="B39" s="94" t="s">
         <v>156</v>
       </c>
-      <c r="C39" s="95"/>
-      <c r="D39" s="95"/>
-      <c r="E39" s="95"/>
+      <c r="C39" s="94"/>
+      <c r="D39" s="94"/>
+      <c r="E39" s="94"/>
     </row>
     <row r="40" spans="1:5" ht="46.6" customHeight="1">
-      <c r="B40" s="95" t="s">
+      <c r="B40" s="94" t="s">
         <v>235</v>
       </c>
-      <c r="C40" s="95"/>
-      <c r="D40" s="95"/>
-      <c r="E40" s="95"/>
+      <c r="C40" s="94"/>
+      <c r="D40" s="94"/>
+      <c r="E40" s="94"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="21" t="s">
@@ -2811,12 +2811,12 @@
       <c r="E42" s="21"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="B44" s="95" t="s">
+      <c r="B44" s="94" t="s">
         <v>208</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="94"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="23" t="s">
@@ -3001,12 +3001,12 @@
       <c r="E69" s="21"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="B71" s="95" t="s">
+      <c r="B71" s="94" t="s">
         <v>196</v>
       </c>
-      <c r="C71" s="95"/>
-      <c r="D71" s="95"/>
-      <c r="E71" s="95"/>
+      <c r="C71" s="94"/>
+      <c r="D71" s="94"/>
+      <c r="E71" s="94"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="28" t="s">
@@ -3068,36 +3068,36 @@
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="B85" s="96" t="s">
+      <c r="B85" s="97" t="s">
         <v>192</v>
       </c>
-      <c r="C85" s="96"/>
-      <c r="D85" s="96"/>
-      <c r="E85" s="96"/>
+      <c r="C85" s="97"/>
+      <c r="D85" s="97"/>
+      <c r="E85" s="97"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="B86" s="94" t="s">
+      <c r="B86" s="96" t="s">
         <v>190</v>
       </c>
-      <c r="C86" s="94"/>
-      <c r="D86" s="94"/>
-      <c r="E86" s="94"/>
+      <c r="C86" s="96"/>
+      <c r="D86" s="96"/>
+      <c r="E86" s="96"/>
     </row>
     <row r="87" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B87" s="95" t="s">
+      <c r="B87" s="94" t="s">
         <v>189</v>
       </c>
-      <c r="C87" s="95"/>
-      <c r="D87" s="95"/>
-      <c r="E87" s="95"/>
+      <c r="C87" s="94"/>
+      <c r="D87" s="94"/>
+      <c r="E87" s="94"/>
     </row>
     <row r="88" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B88" s="95" t="s">
+      <c r="B88" s="94" t="s">
         <v>225</v>
       </c>
-      <c r="C88" s="95"/>
-      <c r="D88" s="95"/>
-      <c r="E88" s="95"/>
+      <c r="C88" s="94"/>
+      <c r="D88" s="94"/>
+      <c r="E88" s="94"/>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="24" t="s">
@@ -3130,12 +3130,12 @@
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="B97" s="97" t="s">
+      <c r="B97" s="95" t="s">
         <v>211</v>
       </c>
-      <c r="C97" s="97"/>
-      <c r="D97" s="97"/>
-      <c r="E97" s="97"/>
+      <c r="C97" s="95"/>
+      <c r="D97" s="95"/>
+      <c r="E97" s="95"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
@@ -3143,20 +3143,20 @@
       </c>
     </row>
     <row r="100" spans="1:5" ht="12.4">
-      <c r="B100" s="97" t="s">
+      <c r="B100" s="95" t="s">
         <v>212</v>
       </c>
-      <c r="C100" s="97"/>
-      <c r="D100" s="97"/>
-      <c r="E100" s="97"/>
+      <c r="C100" s="95"/>
+      <c r="D100" s="95"/>
+      <c r="E100" s="95"/>
     </row>
     <row r="101" spans="1:5" ht="58.5" customHeight="1">
-      <c r="B101" s="95" t="s">
+      <c r="B101" s="94" t="s">
         <v>219</v>
       </c>
-      <c r="C101" s="95"/>
-      <c r="D101" s="95"/>
-      <c r="E101" s="95"/>
+      <c r="C101" s="94"/>
+      <c r="D101" s="94"/>
+      <c r="E101" s="94"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="28" t="s">
@@ -3212,12 +3212,12 @@
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B114" s="95" t="s">
+      <c r="B114" s="94" t="s">
         <v>217</v>
       </c>
-      <c r="C114" s="95"/>
-      <c r="D114" s="95"/>
-      <c r="E114" s="95"/>
+      <c r="C114" s="94"/>
+      <c r="D114" s="94"/>
+      <c r="E114" s="94"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="21" t="s">
@@ -3250,12 +3250,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
     <mergeCell ref="B86:E86"/>
     <mergeCell ref="B71:E71"/>
     <mergeCell ref="B85:E85"/>
@@ -3265,6 +3259,12 @@
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3964,7 +3964,7 @@
         <v>45900</v>
       </c>
       <c r="W10" s="11" t="s">
-        <v>163</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="1:23">
@@ -6825,15 +6825,15 @@
       <c r="B5" s="106" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="95"/>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="106" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="97"/>
-      <c r="D6" s="97"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EF0A24-B245-4A9E-BE31-DB0AF2842B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7EDCE2-EEF5-451D-A8A7-DCEE4302B6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="278">
   <si>
     <t>Name</t>
   </si>
@@ -1604,6 +1604,21 @@
   </si>
   <si>
     <t>Execution</t>
+  </si>
+  <si>
+    <t>600132.SS</t>
+  </si>
+  <si>
+    <t>重庆啤酒</t>
+  </si>
+  <si>
+    <t>CNY</t>
+  </si>
+  <si>
+    <t>002304.SZ</t>
+  </si>
+  <si>
+    <t>洋河股份</t>
   </si>
 </sst>
 </file>
@@ -2179,17 +2194,17 @@
     <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2570,12 +2585,12 @@
       <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="95" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="94"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="20" t="s">
@@ -2587,12 +2602,12 @@
       <c r="C6" s="61"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" s="94" t="s">
+      <c r="B7" s="95" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="23" t="s">
@@ -2681,12 +2696,12 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
-      <c r="B24" s="94" t="s">
+      <c r="B24" s="95" t="s">
         <v>220</v>
       </c>
-      <c r="C24" s="94"/>
-      <c r="D24" s="94"/>
-      <c r="E24" s="94"/>
+      <c r="C24" s="95"/>
+      <c r="D24" s="95"/>
+      <c r="E24" s="95"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
@@ -2786,20 +2801,20 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="B39" s="94" t="s">
+      <c r="B39" s="95" t="s">
         <v>156</v>
       </c>
-      <c r="C39" s="94"/>
-      <c r="D39" s="94"/>
-      <c r="E39" s="94"/>
+      <c r="C39" s="95"/>
+      <c r="D39" s="95"/>
+      <c r="E39" s="95"/>
     </row>
     <row r="40" spans="1:5" ht="46.6" customHeight="1">
-      <c r="B40" s="94" t="s">
+      <c r="B40" s="95" t="s">
         <v>235</v>
       </c>
-      <c r="C40" s="94"/>
-      <c r="D40" s="94"/>
-      <c r="E40" s="94"/>
+      <c r="C40" s="95"/>
+      <c r="D40" s="95"/>
+      <c r="E40" s="95"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="21" t="s">
@@ -2811,12 +2826,12 @@
       <c r="E42" s="21"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="B44" s="94" t="s">
+      <c r="B44" s="95" t="s">
         <v>208</v>
       </c>
-      <c r="C44" s="94"/>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="23" t="s">
@@ -3001,12 +3016,12 @@
       <c r="E69" s="21"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="B71" s="94" t="s">
+      <c r="B71" s="95" t="s">
         <v>196</v>
       </c>
-      <c r="C71" s="94"/>
-      <c r="D71" s="94"/>
-      <c r="E71" s="94"/>
+      <c r="C71" s="95"/>
+      <c r="D71" s="95"/>
+      <c r="E71" s="95"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="28" t="s">
@@ -3068,36 +3083,36 @@
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="B85" s="97" t="s">
+      <c r="B85" s="96" t="s">
         <v>192</v>
       </c>
-      <c r="C85" s="97"/>
-      <c r="D85" s="97"/>
-      <c r="E85" s="97"/>
+      <c r="C85" s="96"/>
+      <c r="D85" s="96"/>
+      <c r="E85" s="96"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="B86" s="96" t="s">
+      <c r="B86" s="94" t="s">
         <v>190</v>
       </c>
-      <c r="C86" s="96"/>
-      <c r="D86" s="96"/>
-      <c r="E86" s="96"/>
+      <c r="C86" s="94"/>
+      <c r="D86" s="94"/>
+      <c r="E86" s="94"/>
     </row>
     <row r="87" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B87" s="94" t="s">
+      <c r="B87" s="95" t="s">
         <v>189</v>
       </c>
-      <c r="C87" s="94"/>
-      <c r="D87" s="94"/>
-      <c r="E87" s="94"/>
+      <c r="C87" s="95"/>
+      <c r="D87" s="95"/>
+      <c r="E87" s="95"/>
     </row>
     <row r="88" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B88" s="94" t="s">
+      <c r="B88" s="95" t="s">
         <v>225</v>
       </c>
-      <c r="C88" s="94"/>
-      <c r="D88" s="94"/>
-      <c r="E88" s="94"/>
+      <c r="C88" s="95"/>
+      <c r="D88" s="95"/>
+      <c r="E88" s="95"/>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="24" t="s">
@@ -3130,12 +3145,12 @@
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="B97" s="95" t="s">
+      <c r="B97" s="97" t="s">
         <v>211</v>
       </c>
-      <c r="C97" s="95"/>
-      <c r="D97" s="95"/>
-      <c r="E97" s="95"/>
+      <c r="C97" s="97"/>
+      <c r="D97" s="97"/>
+      <c r="E97" s="97"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
@@ -3143,20 +3158,20 @@
       </c>
     </row>
     <row r="100" spans="1:5" ht="12.4">
-      <c r="B100" s="95" t="s">
+      <c r="B100" s="97" t="s">
         <v>212</v>
       </c>
-      <c r="C100" s="95"/>
-      <c r="D100" s="95"/>
-      <c r="E100" s="95"/>
+      <c r="C100" s="97"/>
+      <c r="D100" s="97"/>
+      <c r="E100" s="97"/>
     </row>
     <row r="101" spans="1:5" ht="58.5" customHeight="1">
-      <c r="B101" s="94" t="s">
+      <c r="B101" s="95" t="s">
         <v>219</v>
       </c>
-      <c r="C101" s="94"/>
-      <c r="D101" s="94"/>
-      <c r="E101" s="94"/>
+      <c r="C101" s="95"/>
+      <c r="D101" s="95"/>
+      <c r="E101" s="95"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="28" t="s">
@@ -3212,12 +3227,12 @@
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B114" s="94" t="s">
+      <c r="B114" s="95" t="s">
         <v>217</v>
       </c>
-      <c r="C114" s="94"/>
-      <c r="D114" s="94"/>
-      <c r="E114" s="94"/>
+      <c r="C114" s="95"/>
+      <c r="D114" s="95"/>
+      <c r="E114" s="95"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="21" t="s">
@@ -3250,6 +3265,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
     <mergeCell ref="B86:E86"/>
     <mergeCell ref="B71:E71"/>
     <mergeCell ref="B85:E85"/>
@@ -3259,12 +3280,6 @@
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3619,133 +3634,133 @@
     </row>
     <row r="6" spans="1:23">
       <c r="B6" s="11" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="D6" s="2">
-        <v>53.85</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>160</v>
+        <v>275</v>
       </c>
       <c r="F6" s="15">
-        <v>0.15157025452393125</v>
+        <v>0.15986601836174463</v>
       </c>
       <c r="G6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$10</f>
-        <v>3.4170254523931243E-2</v>
+        <v>4.2466018361744629E-2</v>
       </c>
       <c r="H6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$11</f>
-        <v>0.11707025452393124</v>
+        <v>0.12536601836174463</v>
       </c>
       <c r="I6" s="15">
-        <v>0.15157025452393125</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>38.606046318120192</v>
+        <v>49.746673136282389</v>
       </c>
       <c r="K6" s="2">
-        <v>64.705150610910081</v>
+        <v>90.751910880412424</v>
       </c>
       <c r="L6" s="2">
-        <v>48.063219913721113</v>
+        <v>62.307286389127562</v>
       </c>
       <c r="M6" s="86">
-        <v>64.355368842171927</v>
+        <v>84.017562490801396</v>
       </c>
       <c r="N6" s="4">
-        <v>9.7570725450271498E-2</v>
+        <v>7.6967954245883027E-2</v>
       </c>
       <c r="O6" s="4">
-        <v>9.3606035283194056E-2</v>
+        <v>6.7740524781341113E-2</v>
       </c>
       <c r="P6" s="15">
-        <v>1.2907496012759174</v>
+        <v>0.30279158651211824</v>
       </c>
       <c r="Q6" s="15">
-        <v>0.24768740031897937</v>
+        <v>7.7640983998987034E-4</v>
       </c>
       <c r="R6" s="92">
-        <v>0.73855199466278643</v>
+        <v>3.8209153156820415E-3</v>
       </c>
       <c r="S6" s="86">
-        <v>-2.6424228259673308</v>
+        <v>15.284602440692964</v>
       </c>
       <c r="T6" s="13" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="U6" s="11" t="s">
         <v>162</v>
       </c>
       <c r="V6" s="14">
-        <v>45808</v>
+        <v>45900</v>
       </c>
       <c r="W6" s="11" t="s">
-        <v>163</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" spans="1:23">
       <c r="B7" s="11" t="s">
-        <v>158</v>
+        <v>249</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>159</v>
+        <v>250</v>
       </c>
       <c r="D7" s="2">
-        <v>17.36</v>
+        <v>53.85</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F7" s="15">
-        <v>0.13150710314103176</v>
+        <v>0.15157025452393125</v>
       </c>
       <c r="G7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$10</f>
-        <v>1.4107103141031752E-2</v>
+        <v>3.4170254523931243E-2</v>
       </c>
       <c r="H7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$11</f>
-        <v>9.7007103141031753E-2</v>
+        <v>0.11707025452393124</v>
       </c>
       <c r="I7" s="15">
-        <v>5.9540092257125532E-2</v>
+        <v>0.15157025452393125</v>
       </c>
       <c r="J7" s="2">
-        <v>11.804906901225705</v>
+        <v>38.606046318120192</v>
       </c>
       <c r="K7" s="2">
-        <v>20.508980461992877</v>
+        <v>64.705150610910081</v>
       </c>
       <c r="L7" s="2">
-        <v>14.733437767356989</v>
+        <v>48.063219913721113</v>
       </c>
       <c r="M7" s="86">
-        <v>19.785541823839793</v>
+        <v>64.355368842171927</v>
       </c>
       <c r="N7" s="4">
-        <v>9.9538365171061599E-2</v>
+        <v>9.7570725450271498E-2</v>
       </c>
       <c r="O7" s="4">
-        <v>7.83410138248848E-2</v>
+        <v>9.3606035283194056E-2</v>
       </c>
       <c r="P7" s="15">
-        <v>0.31018327415220487</v>
+        <v>1.2907496012759174</v>
       </c>
       <c r="Q7" s="15">
-        <v>0.15818859882129041</v>
+        <v>0.24768740031897937</v>
       </c>
       <c r="R7" s="92">
-        <v>1.4550387206421544</v>
+        <v>0.73855199466278643</v>
       </c>
       <c r="S7" s="86">
-        <v>5.8696003638854428</v>
+        <v>-2.6424228259673308</v>
       </c>
       <c r="T7" s="13" t="s">
-        <v>161</v>
+        <v>246</v>
       </c>
       <c r="U7" s="11" t="s">
         <v>162</v>
@@ -3759,69 +3774,69 @@
     </row>
     <row r="8" spans="1:23">
       <c r="B8" s="11" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D8" s="2">
-        <v>7.94</v>
+        <v>17.36</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F8" s="15">
-        <v>0.11874261404950959</v>
+        <v>0.13150710314103176</v>
       </c>
       <c r="G8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$10</f>
-        <v>1.3426140495095829E-3</v>
+        <v>1.4107103141031752E-2</v>
       </c>
       <c r="H8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$11</f>
-        <v>8.4242614049509584E-2</v>
+        <v>9.7007103141031753E-2</v>
       </c>
       <c r="I8" s="15">
-        <v>0</v>
+        <v>5.9540092257125532E-2</v>
       </c>
       <c r="J8" s="2">
-        <v>5.2239462882061574</v>
+        <v>11.804906901225705</v>
       </c>
       <c r="K8" s="2">
-        <v>9.1628099951889297</v>
+        <v>20.508980461992877</v>
       </c>
       <c r="L8" s="2">
-        <v>6.5243113398084081</v>
+        <v>14.733437767356989</v>
       </c>
       <c r="M8" s="86">
-        <v>8.7684502451266084</v>
+        <v>19.785541823839793</v>
       </c>
       <c r="N8" s="4">
-        <v>3.8904077075852014E-2</v>
+        <v>9.9538365171061599E-2</v>
       </c>
       <c r="O8" s="4">
-        <v>7.3047858942065488E-2</v>
+        <v>7.83410138248848E-2</v>
       </c>
       <c r="P8" s="15">
-        <v>8.3114411724224596E-2</v>
+        <v>0.31018327415220487</v>
       </c>
       <c r="Q8" s="15">
-        <v>1.8509098960546238E-2</v>
+        <v>0.15818859882129041</v>
       </c>
       <c r="R8" s="92">
-        <v>1.1933697905849452</v>
+        <v>1.4550387206421544</v>
       </c>
       <c r="S8" s="86">
-        <v>11.511512740854835</v>
+        <v>5.8696003638854428</v>
       </c>
       <c r="T8" s="13" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="U8" s="11" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="V8" s="14">
-        <v>45900</v>
+        <v>45808</v>
       </c>
       <c r="W8" s="11" t="s">
         <v>163</v>
@@ -3829,136 +3844,136 @@
     </row>
     <row r="9" spans="1:23">
       <c r="B9" s="11" t="s">
-        <v>244</v>
+        <v>164</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>245</v>
+        <v>165</v>
       </c>
       <c r="D9" s="2">
-        <v>14.64</v>
+        <v>7.94</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F9" s="15">
-        <v>9.919795200818049E-2</v>
+        <v>0.11874261404950959</v>
       </c>
       <c r="G9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$10</f>
-        <v>-1.8202047991819514E-2</v>
+        <v>1.3426140495095829E-3</v>
       </c>
       <c r="H9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$11</f>
-        <v>6.4697952008180487E-2</v>
+        <v>8.4242614049509584E-2</v>
       </c>
       <c r="I9" s="15">
         <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>9.1086666437717536</v>
+        <v>5.2239462882061574</v>
       </c>
       <c r="K9" s="2">
-        <v>16.688564338966547</v>
+        <v>9.1628099951889297</v>
       </c>
       <c r="L9" s="2">
-        <v>11.412172410513048</v>
+        <v>6.5243113398084081</v>
       </c>
       <c r="M9" s="86">
-        <v>15.394323329007381</v>
+        <v>8.7684502451266084</v>
       </c>
       <c r="N9" s="4">
-        <v>0.10480665350528036</v>
+        <v>3.8904077075852014E-2</v>
       </c>
       <c r="O9" s="4">
-        <v>5.6890454918032782E-2</v>
+        <v>7.3047858942065488E-2</v>
       </c>
       <c r="P9" s="15">
-        <v>2.2875080906148866</v>
+        <v>8.3114411724224596E-2</v>
       </c>
       <c r="Q9" s="15">
-        <v>1.5035598705501618</v>
+        <v>1.8509098960546238E-2</v>
       </c>
       <c r="R9" s="92">
-        <v>4.1998196571663646</v>
+        <v>1.1933697905849452</v>
       </c>
       <c r="S9" s="86">
-        <v>-12.129380035386257</v>
+        <v>11.511512740854835</v>
       </c>
       <c r="T9" s="13" t="s">
-        <v>246</v>
+        <v>166</v>
       </c>
       <c r="U9" s="11" t="s">
-        <v>248</v>
+        <v>167</v>
       </c>
       <c r="V9" s="14">
         <v>45900</v>
       </c>
       <c r="W9" s="11" t="s">
-        <v>247</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:23">
       <c r="B10" s="11" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="D10" s="2">
-        <v>28.81</v>
+        <v>14.64</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>253</v>
+        <v>160</v>
       </c>
       <c r="F10" s="15">
-        <v>9.408289080523935E-2</v>
+        <v>9.919795200818049E-2</v>
       </c>
       <c r="G10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.3317109194760655E-2</v>
+        <v>-1.8202047991819514E-2</v>
       </c>
       <c r="H10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$11</f>
-        <v>5.9582890805239347E-2</v>
+        <v>6.4697952008180487E-2</v>
       </c>
       <c r="I10" s="15">
         <v>0</v>
       </c>
       <c r="J10" s="2">
-        <v>17.682685147645955</v>
+        <v>9.1086666437717536</v>
       </c>
       <c r="K10" s="2">
-        <v>32.464859269378167</v>
+        <v>16.688564338966547</v>
       </c>
       <c r="L10" s="2">
-        <v>22.157904669779033</v>
+        <v>11.412172410513048</v>
       </c>
       <c r="M10" s="86">
-        <v>29.895007167811503</v>
+        <v>15.394323329007381</v>
       </c>
       <c r="N10" s="4">
-        <v>8.8134932571433455E-2</v>
+        <v>0.10480665350528036</v>
       </c>
       <c r="O10" s="4">
-        <v>5.5536272127733433E-2</v>
+        <v>5.6890454918032782E-2</v>
       </c>
       <c r="P10" s="15">
-        <v>0.78990369994931575</v>
+        <v>2.2875080906148866</v>
       </c>
       <c r="Q10" s="15">
-        <v>0.40281804358844397</v>
+        <v>1.5035598705501618</v>
       </c>
       <c r="R10" s="92">
-        <v>3.955391512509995</v>
+        <v>4.1998196571663646</v>
       </c>
       <c r="S10" s="86">
-        <v>-26.938493611476797</v>
+        <v>-12.129380035386257</v>
       </c>
       <c r="T10" s="16" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="U10" s="11" t="s">
-        <v>162</v>
+        <v>248</v>
       </c>
       <c r="V10" s="14">
         <v>45900</v>
@@ -3969,63 +3984,63 @@
     </row>
     <row r="11" spans="1:23">
       <c r="B11" s="11" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="D11" s="2">
-        <v>56.45</v>
+        <v>28.81</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>160</v>
+        <v>253</v>
       </c>
       <c r="F11" s="15">
-        <v>9.3068045296727409E-2</v>
+        <v>9.408289080523935E-2</v>
       </c>
       <c r="G11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.4331954703272596E-2</v>
+        <v>-2.3317109194760655E-2</v>
       </c>
       <c r="H11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$11</f>
-        <v>5.8568045296727406E-2</v>
+        <v>5.9582890805239347E-2</v>
       </c>
       <c r="I11" s="15">
         <v>0</v>
       </c>
       <c r="J11" s="2">
-        <v>34.215307295933449</v>
+        <v>17.682685147645955</v>
       </c>
       <c r="K11" s="2">
-        <v>66.944798372320093</v>
+        <v>32.464859269378167</v>
       </c>
       <c r="L11" s="2">
-        <v>43.084161372829577</v>
+        <v>22.157904669779033</v>
       </c>
       <c r="M11" s="86">
-        <v>58.456171666660033</v>
+        <v>29.895007167811503</v>
       </c>
       <c r="N11" s="4">
-        <v>3.9887806404447897E-2</v>
+        <v>8.8134932571433455E-2</v>
       </c>
       <c r="O11" s="4">
-        <v>3.652280283012984E-2</v>
+        <v>5.5536272127733433E-2</v>
       </c>
       <c r="P11" s="15">
-        <v>0.72207550313588764</v>
+        <v>0.78990369994931575</v>
       </c>
       <c r="Q11" s="15">
-        <v>9.5579625064196368E-3</v>
+        <v>0.40281804358844397</v>
       </c>
       <c r="R11" s="92">
-        <v>7.3592411949940734E-2</v>
+        <v>3.955391512509995</v>
       </c>
       <c r="S11" s="86">
-        <v>1.3262674203270228</v>
+        <v>-26.938493611476797</v>
       </c>
       <c r="T11" s="13" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="U11" s="11" t="s">
         <v>162</v>
@@ -4039,93 +4054,213 @@
     </row>
     <row r="12" spans="1:23">
       <c r="B12" s="11" t="s">
-        <v>168</v>
+        <v>240</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>169</v>
+        <v>241</v>
       </c>
       <c r="D12" s="2">
-        <v>2.5099999999999998</v>
+        <v>56.45</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F12" s="15">
-        <v>6.8934165996179741E-2</v>
+        <v>9.3068045296727409E-2</v>
       </c>
       <c r="G12" s="15">
         <f>F12 - Portfolio_Mgmt!$C$10</f>
-        <v>-4.8465834003820263E-2</v>
+        <v>-2.4331954703272596E-2</v>
       </c>
       <c r="H12" s="15">
         <f>F12 - Portfolio_Mgmt!$C$11</f>
-        <v>3.4434165996179739E-2</v>
+        <v>5.8568045296727406E-2</v>
       </c>
       <c r="I12" s="15">
         <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>1.4359031078171438</v>
+        <v>34.215307295933449</v>
       </c>
       <c r="K12" s="2">
-        <v>2.6984971849946402</v>
+        <v>66.944798372320093</v>
       </c>
       <c r="L12" s="2">
-        <v>1.8024671110952224</v>
+        <v>43.084161372829577</v>
       </c>
       <c r="M12" s="86">
-        <v>2.4367969526210818</v>
+        <v>58.456171666660033</v>
       </c>
       <c r="N12" s="4">
-        <v>3.2754125309196483E-2</v>
+        <v>3.9887806404447897E-2</v>
       </c>
       <c r="O12" s="4">
-        <v>4.55503243047485E-2</v>
+        <v>3.652280283012984E-2</v>
       </c>
       <c r="P12" s="15">
-        <v>0.20351769929714394</v>
+        <v>0.72207550313588764</v>
       </c>
       <c r="Q12" s="15">
-        <v>1.0763175939415467E-2</v>
+        <v>9.5579625064196368E-3</v>
       </c>
       <c r="R12" s="92">
-        <v>0.29882156160837919</v>
+        <v>7.3592411949940734E-2</v>
       </c>
       <c r="S12" s="86">
-        <v>1.8659804056246816</v>
+        <v>1.3262674203270228</v>
       </c>
       <c r="T12" s="13" t="s">
-        <v>170</v>
+        <v>242</v>
       </c>
       <c r="U12" s="11" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="V12" s="14">
         <v>45900</v>
       </c>
       <c r="W12" s="11" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
+      <c r="B13" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="D13" s="2">
+        <v>57.77</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="F13" s="15">
+        <v>8.8211113876756064E-2</v>
+      </c>
+      <c r="G13" s="15">
+        <f>F13 - Portfolio_Mgmt!$C$10</f>
+        <v>-2.918888612324394E-2</v>
+      </c>
+      <c r="H13" s="15">
+        <f>F13 - Portfolio_Mgmt!$C$11</f>
+        <v>5.3711113876756061E-2</v>
+      </c>
+      <c r="I13" s="15">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2">
+        <v>34.669224296258527</v>
+      </c>
+      <c r="K13" s="2">
+        <v>66.592285778879997</v>
+      </c>
+      <c r="L13" s="2">
+        <v>43.592757973888887</v>
+      </c>
+      <c r="M13" s="2">
+        <v>59.048136223898794</v>
+      </c>
+      <c r="N13" s="4">
+        <v>7.9541392420431456E-2</v>
+      </c>
+      <c r="O13" s="4">
+        <v>4.1544054007270202E-2</v>
+      </c>
+      <c r="P13" s="15">
+        <v>3.4701988818540461</v>
+      </c>
+      <c r="Q13" s="15">
+        <v>5.0341856510546588E-2</v>
+      </c>
+      <c r="R13" s="92">
+        <v>3.9546057100127742E-2</v>
+      </c>
+      <c r="S13" s="86">
+        <v>-13.312996389940134</v>
+      </c>
+      <c r="T13" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="U13" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="V13" s="14">
+        <v>45716</v>
+      </c>
+      <c r="W13" s="11" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
+      <c r="B14" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D14" s="2">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="F14" s="15">
+        <v>6.8934165996179741E-2</v>
+      </c>
+      <c r="G14" s="15">
+        <f>F14 - Portfolio_Mgmt!$C$10</f>
+        <v>-4.8465834003820263E-2</v>
+      </c>
+      <c r="H14" s="15">
+        <f>F14 - Portfolio_Mgmt!$C$11</f>
+        <v>3.4434165996179739E-2</v>
+      </c>
+      <c r="I14" s="15">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1.4359031078171438</v>
+      </c>
+      <c r="K14" s="2">
+        <v>2.6984971849946402</v>
+      </c>
+      <c r="L14" s="2">
+        <v>1.8024671110952224</v>
+      </c>
+      <c r="M14" s="2">
+        <v>2.4367969526210818</v>
+      </c>
+      <c r="N14" s="4">
+        <v>3.2754125309196483E-2</v>
+      </c>
+      <c r="O14" s="4">
+        <v>4.55503243047485E-2</v>
+      </c>
+      <c r="P14" s="15">
+        <v>0.20351769929714394</v>
+      </c>
+      <c r="Q14" s="15">
+        <v>1.0763175939415467E-2</v>
+      </c>
+      <c r="R14" s="92">
+        <v>0.29882156160837919</v>
+      </c>
+      <c r="S14" s="86">
+        <v>1.8659804056246816</v>
+      </c>
+      <c r="T14" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="U14" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="V14" s="14">
+        <v>45900</v>
+      </c>
+      <c r="W14" s="11" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="13" spans="1:23">
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="E13" s="12"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="T13" s="13"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="14"/>
-    </row>
-    <row r="14" spans="1:23">
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="E14" s="12"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="T14" s="13"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="14"/>
     </row>
     <row r="15" spans="1:23">
       <c r="B15" s="11"/>
@@ -6825,15 +6960,15 @@
       <c r="B5" s="106" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="95"/>
-      <c r="D5" s="95"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="97"/>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="106" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="97"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7EDCE2-EEF5-451D-A8A7-DCEE4302B6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF47764D-B7A4-4E2A-9646-59377A0122BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3219,7 +3219,7 @@
         <v>176</v>
       </c>
       <c r="C112" s="44">
-        <v>0.12155581855631381</v>
+        <v>0.11959137223365987</v>
       </c>
       <c r="D112" s="61" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
@@ -3430,42 +3430,42 @@
         <v>259</v>
       </c>
       <c r="D3" s="2">
-        <v>15.26</v>
+        <v>15.32</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F3" s="15">
-        <v>0.2202784312360544</v>
+        <v>0.22093639979403168</v>
       </c>
       <c r="G3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$10</f>
-        <v>0.10287843123605439</v>
+        <v>0.10353639979403167</v>
       </c>
       <c r="H3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$11</f>
-        <v>0.18577843123605439</v>
+        <v>0.18643639979403168</v>
       </c>
       <c r="I3" s="15">
-        <v>0.2202784312360544</v>
+        <v>0.22093639979403171</v>
       </c>
       <c r="J3" s="2">
-        <v>12.691224440750165</v>
+        <v>12.76034731937011</v>
       </c>
       <c r="K3" s="2">
-        <v>25.695938127508406</v>
+        <v>25.861790776733326</v>
       </c>
       <c r="L3" s="2">
-        <v>16.024771926236642</v>
+        <v>16.113365751277065</v>
       </c>
       <c r="M3" s="86">
-        <v>21.810617911761469</v>
+        <v>21.933241308816839</v>
       </c>
       <c r="N3" s="4">
-        <v>6.5463829288395545E-2</v>
+        <v>6.5626579329258014E-2</v>
       </c>
       <c r="O3" s="4">
-        <v>3.5913538249616732E-2</v>
+        <v>3.5544021344529921E-2</v>
       </c>
       <c r="P3" s="15">
         <v>0.36794481423679237</v>
@@ -3477,7 +3477,7 @@
         <v>0.60402076709908736</v>
       </c>
       <c r="S3" s="86">
-        <v>4.4985790275171595</v>
+        <v>4.5275447966435411</v>
       </c>
       <c r="T3" s="13" t="s">
         <v>246</v>
@@ -3500,42 +3500,42 @@
         <v>237</v>
       </c>
       <c r="D4" s="2">
-        <v>5.94</v>
+        <v>6.04</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F4" s="15">
-        <v>0.1686112219828888</v>
+        <v>0.16392445461154903</v>
       </c>
       <c r="G4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$10</f>
-        <v>5.1211221982888799E-2</v>
+        <v>4.6524454611549027E-2</v>
       </c>
       <c r="H4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$11</f>
-        <v>0.1341112219828888</v>
+        <v>0.12942445461154903</v>
       </c>
       <c r="I4" s="15">
-        <v>0.16861122198288883</v>
+        <v>0.16392445461154903</v>
       </c>
       <c r="J4" s="2">
-        <v>4.4065324767427771</v>
+        <v>4.4297376548118468</v>
       </c>
       <c r="K4" s="2">
-        <v>7.9178132048919672</v>
+        <v>7.9687949811097125</v>
       </c>
       <c r="L4" s="2">
-        <v>5.5130052215060692</v>
+        <v>5.5425085642246721</v>
       </c>
       <c r="M4" s="86">
-        <v>7.4243363812264054</v>
+        <v>7.4648073588925268</v>
       </c>
       <c r="N4" s="4">
-        <v>0.12948771313952359</v>
+        <v>0.12816382759890571</v>
       </c>
       <c r="O4" s="4">
-        <v>7.4400590977102513E-2</v>
+        <v>7.3168793113243216E-2</v>
       </c>
       <c r="P4" s="15">
         <v>0.61007460831657279</v>
@@ -3547,7 +3547,7 @@
         <v>1.1309485990394448</v>
       </c>
       <c r="S4" s="86">
-        <v>-3.7862698750718136</v>
+        <v>-3.8106491775983788</v>
       </c>
       <c r="T4" s="13" t="s">
         <v>239</v>
@@ -3564,63 +3564,63 @@
     </row>
     <row r="5" spans="1:23">
       <c r="B5" s="11" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="D5" s="2">
-        <v>20.079999999999998</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="F5" s="15">
-        <v>0.16060765378265396</v>
+        <v>0.15689676518236584</v>
       </c>
       <c r="G5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$10</f>
-        <v>4.3207653782653954E-2</v>
+        <v>3.9496765182365834E-2</v>
       </c>
       <c r="H5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$11</f>
-        <v>0.12610765378265396</v>
+        <v>0.12239676518236584</v>
       </c>
       <c r="I5" s="15">
         <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>14.418941896437474</v>
+        <v>49.746673136282389</v>
       </c>
       <c r="K5" s="2">
-        <v>29.309951346473134</v>
+        <v>90.751910880412424</v>
       </c>
       <c r="L5" s="2">
-        <v>18.21218480698677</v>
+        <v>62.307286389127562</v>
       </c>
       <c r="M5" s="86">
-        <v>24.796949133193245</v>
+        <v>84.017562490801396</v>
       </c>
       <c r="N5" s="4">
-        <v>0.22703991769612522</v>
+        <v>7.6411022594320921E-2</v>
       </c>
       <c r="O5" s="4">
-        <v>2.956175298804781E-2</v>
+        <v>6.7250361794500738E-2</v>
       </c>
       <c r="P5" s="15">
-        <v>1.4851905363915479</v>
+        <v>0.30279158651211824</v>
       </c>
       <c r="Q5" s="15">
-        <v>0.95241105291674188</v>
+        <v>7.7640983998987034E-4</v>
       </c>
       <c r="R5" s="92">
-        <v>4.0148803043206254</v>
+        <v>3.8209153156820415E-3</v>
       </c>
       <c r="S5" s="86">
-        <v>-38.360607814419353</v>
+        <v>15.284602440692964</v>
       </c>
       <c r="T5" s="13" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="U5" s="11" t="s">
         <v>162</v>
@@ -3634,142 +3634,142 @@
     </row>
     <row r="6" spans="1:23">
       <c r="B6" s="11" t="s">
-        <v>276</v>
+        <v>249</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>277</v>
+        <v>250</v>
       </c>
       <c r="D6" s="2">
-        <v>68.599999999999994</v>
+        <v>54.35</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>275</v>
+        <v>160</v>
       </c>
       <c r="F6" s="15">
-        <v>0.15986601836174463</v>
+        <v>0.14793773051313952</v>
       </c>
       <c r="G6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$10</f>
-        <v>4.2466018361744629E-2</v>
+        <v>3.0537730513139516E-2</v>
       </c>
       <c r="H6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$11</f>
-        <v>0.12536601836174463</v>
+        <v>0.11343773051313952</v>
       </c>
       <c r="I6" s="15">
-        <v>0</v>
+        <v>0.14793773051313952</v>
       </c>
       <c r="J6" s="2">
-        <v>49.746673136282389</v>
+        <v>38.625338845755344</v>
       </c>
       <c r="K6" s="2">
-        <v>90.751910880412424</v>
+        <v>64.73708395408849</v>
       </c>
       <c r="L6" s="2">
-        <v>62.307286389127562</v>
+        <v>48.087218068397867</v>
       </c>
       <c r="M6" s="86">
-        <v>84.017562490801396</v>
+        <v>64.387469610682459</v>
       </c>
       <c r="N6" s="4">
-        <v>7.6967954245883027E-2</v>
+        <v>9.67233515064677E-2</v>
       </c>
       <c r="O6" s="4">
-        <v>6.7740524781341113E-2</v>
+        <v>9.2793093543592248E-2</v>
       </c>
       <c r="P6" s="15">
-        <v>0.30279158651211824</v>
+        <v>1.2907496012759174</v>
       </c>
       <c r="Q6" s="15">
-        <v>7.7640983998987034E-4</v>
+        <v>0.24768740031897937</v>
       </c>
       <c r="R6" s="92">
-        <v>3.8209153156820415E-3</v>
+        <v>0.73855199466278643</v>
       </c>
       <c r="S6" s="86">
-        <v>15.284602440692964</v>
+        <v>-2.6437960879200806</v>
       </c>
       <c r="T6" s="13" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="U6" s="11" t="s">
         <v>162</v>
       </c>
       <c r="V6" s="14">
-        <v>45900</v>
+        <v>45808</v>
       </c>
       <c r="W6" s="11" t="s">
-        <v>247</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:23">
       <c r="B7" s="11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D7" s="2">
-        <v>53.85</v>
+        <v>21.47</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>160</v>
+        <v>253</v>
       </c>
       <c r="F7" s="15">
-        <v>0.15157025452393125</v>
+        <v>0.13438178033413717</v>
       </c>
       <c r="G7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$10</f>
-        <v>3.4170254523931243E-2</v>
+        <v>1.6981780334137164E-2</v>
       </c>
       <c r="H7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$11</f>
-        <v>0.11707025452393124</v>
+        <v>9.9881780334137166E-2</v>
       </c>
       <c r="I7" s="15">
-        <v>0.15157025452393125</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>38.606046318120192</v>
+        <v>14.418941896437474</v>
       </c>
       <c r="K7" s="2">
-        <v>64.705150610910081</v>
+        <v>29.309951346473134</v>
       </c>
       <c r="L7" s="2">
-        <v>48.063219913721113</v>
+        <v>18.21218480698677</v>
       </c>
       <c r="M7" s="86">
-        <v>64.355368842171927</v>
+        <v>24.796949133193245</v>
       </c>
       <c r="N7" s="4">
-        <v>9.7570725450271498E-2</v>
+        <v>0.21234101291747526</v>
       </c>
       <c r="O7" s="4">
-        <v>9.3606035283194056E-2</v>
+        <v>2.7647880763856547E-2</v>
       </c>
       <c r="P7" s="15">
-        <v>1.2907496012759174</v>
+        <v>1.4851905363915479</v>
       </c>
       <c r="Q7" s="15">
-        <v>0.24768740031897937</v>
+        <v>0.95241105291674188</v>
       </c>
       <c r="R7" s="92">
-        <v>0.73855199466278643</v>
+        <v>4.0148803043206254</v>
       </c>
       <c r="S7" s="86">
-        <v>-2.6424228259673308</v>
+        <v>-38.360607814419353</v>
       </c>
       <c r="T7" s="13" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="U7" s="11" t="s">
         <v>162</v>
       </c>
       <c r="V7" s="14">
-        <v>45808</v>
+        <v>45900</v>
       </c>
       <c r="W7" s="11" t="s">
-        <v>163</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -3780,24 +3780,24 @@
         <v>159</v>
       </c>
       <c r="D8" s="2">
-        <v>17.36</v>
+        <v>17.760000000000002</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F8" s="15">
-        <v>0.13150710314103176</v>
+        <v>0.12234386047816836</v>
       </c>
       <c r="G8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$10</f>
-        <v>1.4107103141031752E-2</v>
+        <v>4.9438604781683604E-3</v>
       </c>
       <c r="H8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$11</f>
-        <v>9.7007103141031753E-2</v>
+        <v>8.7843860478168362E-2</v>
       </c>
       <c r="I8" s="15">
-        <v>5.9540092257125532E-2</v>
+        <v>6.7201415081279747E-2</v>
       </c>
       <c r="J8" s="2">
         <v>11.804906901225705</v>
@@ -3812,10 +3812,10 @@
         <v>19.785541823839793</v>
       </c>
       <c r="N8" s="4">
-        <v>9.9538365171061599E-2</v>
+        <v>9.7296510099641298E-2</v>
       </c>
       <c r="O8" s="4">
-        <v>7.83410138248848E-2</v>
+        <v>7.6576576576576572E-2</v>
       </c>
       <c r="P8" s="15">
         <v>0.31018327415220487</v>
@@ -3844,142 +3844,142 @@
     </row>
     <row r="9" spans="1:23">
       <c r="B9" s="11" t="s">
-        <v>164</v>
+        <v>240</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>165</v>
+        <v>241</v>
       </c>
       <c r="D9" s="2">
-        <v>7.94</v>
+        <v>54.65</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F9" s="15">
-        <v>0.11874261404950959</v>
+        <v>0.10734290687447179</v>
       </c>
       <c r="G9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$10</f>
-        <v>1.3426140495095829E-3</v>
+        <v>-1.0057093125528216E-2</v>
       </c>
       <c r="H9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$11</f>
-        <v>8.4242614049509584E-2</v>
+        <v>7.2842906874471786E-2</v>
       </c>
       <c r="I9" s="15">
         <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>5.2239462882061574</v>
+        <v>34.387950625486518</v>
       </c>
       <c r="K9" s="2">
-        <v>9.1628099951889297</v>
+        <v>67.376724540900142</v>
       </c>
       <c r="L9" s="2">
-        <v>6.5243113398084081</v>
+        <v>43.306333799977494</v>
       </c>
       <c r="M9" s="86">
-        <v>8.7684502451266084</v>
+        <v>58.765056240717605</v>
       </c>
       <c r="N9" s="4">
-        <v>3.8904077075852014E-2</v>
+        <v>4.1465766109394828E-2</v>
       </c>
       <c r="O9" s="4">
-        <v>7.3047858942065488E-2</v>
+        <v>3.748439251511098E-2</v>
       </c>
       <c r="P9" s="15">
-        <v>8.3114411724224596E-2</v>
+        <v>0.72207550313588764</v>
       </c>
       <c r="Q9" s="15">
-        <v>1.8509098960546238E-2</v>
+        <v>9.5579625064196368E-3</v>
       </c>
       <c r="R9" s="92">
-        <v>1.1933697905849452</v>
+        <v>7.3592411949940734E-2</v>
       </c>
       <c r="S9" s="86">
-        <v>11.511512740854835</v>
+        <v>1.3348070848882203</v>
       </c>
       <c r="T9" s="13" t="s">
-        <v>166</v>
+        <v>242</v>
       </c>
       <c r="U9" s="11" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="V9" s="14">
         <v>45900</v>
       </c>
       <c r="W9" s="11" t="s">
-        <v>163</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:23">
       <c r="B10" s="11" t="s">
-        <v>244</v>
+        <v>164</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>245</v>
+        <v>165</v>
       </c>
       <c r="D10" s="2">
-        <v>14.64</v>
+        <v>8.2200000000000006</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F10" s="15">
-        <v>9.919795200818049E-2</v>
+        <v>0.10504291417240008</v>
       </c>
       <c r="G10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$10</f>
-        <v>-1.8202047991819514E-2</v>
+        <v>-1.2357085827599923E-2</v>
       </c>
       <c r="H10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$11</f>
-        <v>6.4697952008180487E-2</v>
+        <v>7.0542914172400079E-2</v>
       </c>
       <c r="I10" s="15">
         <v>0</v>
       </c>
       <c r="J10" s="2">
-        <v>9.1086666437717536</v>
+        <v>5.2239462882061574</v>
       </c>
       <c r="K10" s="2">
-        <v>16.688564338966547</v>
+        <v>9.1628099951889297</v>
       </c>
       <c r="L10" s="2">
-        <v>11.412172410513048</v>
+        <v>6.5243113398084081</v>
       </c>
       <c r="M10" s="86">
-        <v>15.394323329007381</v>
+        <v>8.7684502451266084</v>
       </c>
       <c r="N10" s="4">
-        <v>0.10480665350528036</v>
+        <v>3.7578877370105228E-2</v>
       </c>
       <c r="O10" s="4">
-        <v>5.6890454918032782E-2</v>
+        <v>7.055961070559609E-2</v>
       </c>
       <c r="P10" s="15">
-        <v>2.2875080906148866</v>
+        <v>8.3114411724224596E-2</v>
       </c>
       <c r="Q10" s="15">
-        <v>1.5035598705501618</v>
+        <v>1.8509098960546238E-2</v>
       </c>
       <c r="R10" s="92">
-        <v>4.1998196571663646</v>
+        <v>1.1933697905849452</v>
       </c>
       <c r="S10" s="86">
-        <v>-12.129380035386257</v>
+        <v>11.511512740854835</v>
       </c>
       <c r="T10" s="16" t="s">
-        <v>246</v>
+        <v>166</v>
       </c>
       <c r="U10" s="11" t="s">
-        <v>248</v>
+        <v>167</v>
       </c>
       <c r="V10" s="14">
         <v>45900</v>
       </c>
       <c r="W10" s="11" t="s">
-        <v>247</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:23">
@@ -3990,21 +3990,21 @@
         <v>256</v>
       </c>
       <c r="D11" s="2">
-        <v>28.81</v>
+        <v>28.4</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>253</v>
       </c>
       <c r="F11" s="15">
-        <v>9.408289080523935E-2</v>
+        <v>9.9596254590427646E-2</v>
       </c>
       <c r="G11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.3317109194760655E-2</v>
+        <v>-1.7803745409572358E-2</v>
       </c>
       <c r="H11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$11</f>
-        <v>5.9582890805239347E-2</v>
+        <v>6.5096254590427644E-2</v>
       </c>
       <c r="I11" s="15">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>29.895007167811503</v>
       </c>
       <c r="N11" s="4">
-        <v>8.8134932571433455E-2</v>
+        <v>8.9407303076866118E-2</v>
       </c>
       <c r="O11" s="4">
-        <v>5.5536272127733433E-2</v>
+        <v>5.6338028169014093E-2</v>
       </c>
       <c r="P11" s="15">
         <v>0.78990369994931575</v>
@@ -4054,66 +4054,66 @@
     </row>
     <row r="12" spans="1:23">
       <c r="B12" s="11" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D12" s="2">
-        <v>56.45</v>
+        <v>14.82</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F12" s="15">
-        <v>9.3068045296727409E-2</v>
+        <v>9.4690284991131524E-2</v>
       </c>
       <c r="G12" s="15">
         <f>F12 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.4331954703272596E-2</v>
+        <v>-2.2709715008868481E-2</v>
       </c>
       <c r="H12" s="15">
         <f>F12 - Portfolio_Mgmt!$C$11</f>
-        <v>5.8568045296727406E-2</v>
+        <v>6.0190284991131521E-2</v>
       </c>
       <c r="I12" s="15">
         <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>34.215307295933449</v>
+        <v>9.113307921310053</v>
       </c>
       <c r="K12" s="2">
-        <v>66.944798372320093</v>
+        <v>16.69703417753378</v>
       </c>
       <c r="L12" s="2">
-        <v>43.084161372829577</v>
+        <v>11.4179857156617</v>
       </c>
       <c r="M12" s="86">
-        <v>58.456171666660033</v>
+        <v>15.402162441309935</v>
       </c>
       <c r="N12" s="4">
-        <v>3.9887806404447897E-2</v>
+        <v>0.10358778927538839</v>
       </c>
       <c r="O12" s="4">
-        <v>3.652280283012984E-2</v>
+        <v>5.6228684490991498E-2</v>
       </c>
       <c r="P12" s="15">
-        <v>0.72207550313588764</v>
+        <v>2.2875080906148866</v>
       </c>
       <c r="Q12" s="15">
-        <v>9.5579625064196368E-3</v>
+        <v>1.5035598705501618</v>
       </c>
       <c r="R12" s="92">
-        <v>7.3592411949940734E-2</v>
+        <v>4.1998196571663646</v>
       </c>
       <c r="S12" s="86">
-        <v>1.3262674203270228</v>
+        <v>-12.135683650367685</v>
       </c>
       <c r="T12" s="13" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="U12" s="11" t="s">
-        <v>162</v>
+        <v>248</v>
       </c>
       <c r="V12" s="14">
         <v>45900</v>
@@ -4124,142 +4124,142 @@
     </row>
     <row r="13" spans="1:23">
       <c r="B13" s="11" t="s">
-        <v>273</v>
+        <v>168</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>274</v>
+        <v>169</v>
       </c>
       <c r="D13" s="2">
-        <v>57.77</v>
+        <v>2.38</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>275</v>
+        <v>160</v>
       </c>
       <c r="F13" s="15">
-        <v>8.8211113876756064E-2</v>
+        <v>9.0784414850680895E-2</v>
       </c>
       <c r="G13" s="15">
         <f>F13 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.918888612324394E-2</v>
+        <v>-2.661558514931911E-2</v>
       </c>
       <c r="H13" s="15">
         <f>F13 - Portfolio_Mgmt!$C$11</f>
-        <v>5.3711113876756061E-2</v>
+        <v>5.6284414850680892E-2</v>
       </c>
       <c r="I13" s="15">
         <v>0</v>
       </c>
       <c r="J13" s="2">
-        <v>34.669224296258527</v>
+        <v>1.4426109829749554</v>
       </c>
       <c r="K13" s="2">
-        <v>66.592285778879997</v>
+        <v>2.7161528914315056</v>
       </c>
       <c r="L13" s="2">
-        <v>43.592757973888887</v>
+        <v>1.8111437377776596</v>
       </c>
       <c r="M13" s="2">
-        <v>59.048136223898794</v>
+        <v>2.4489275916264743</v>
       </c>
       <c r="N13" s="4">
-        <v>7.9541392420431456E-2</v>
+        <v>3.4761910353543202E-2</v>
       </c>
       <c r="O13" s="4">
-        <v>4.1544054007270202E-2</v>
+        <v>4.7731033272727166E-2</v>
       </c>
       <c r="P13" s="15">
-        <v>3.4701988818540461</v>
+        <v>0.20351769929714394</v>
       </c>
       <c r="Q13" s="15">
-        <v>5.0341856510546588E-2</v>
+        <v>1.0763175939415467E-2</v>
       </c>
       <c r="R13" s="92">
-        <v>3.9546057100127742E-2</v>
+        <v>0.29882156160837919</v>
       </c>
       <c r="S13" s="86">
-        <v>-13.312996389940134</v>
+        <v>1.8779952123654464</v>
       </c>
       <c r="T13" s="13" t="s">
-        <v>242</v>
+        <v>170</v>
       </c>
       <c r="U13" s="11" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="V13" s="14">
-        <v>45716</v>
+        <v>45900</v>
       </c>
       <c r="W13" s="11" t="s">
-        <v>247</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:23">
       <c r="B14" s="11" t="s">
-        <v>168</v>
+        <v>273</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>169</v>
+        <v>274</v>
       </c>
       <c r="D14" s="2">
-        <v>2.5099999999999998</v>
+        <v>57.52</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>160</v>
+        <v>275</v>
       </c>
       <c r="F14" s="15">
-        <v>6.8934165996179741E-2</v>
+        <v>8.984625754804787E-2</v>
       </c>
       <c r="G14" s="15">
         <f>F14 - Portfolio_Mgmt!$C$10</f>
-        <v>-4.8465834003820263E-2</v>
+        <v>-2.7553742451952135E-2</v>
       </c>
       <c r="H14" s="15">
         <f>F14 - Portfolio_Mgmt!$C$11</f>
-        <v>3.4434165996179739E-2</v>
+        <v>5.5346257548047867E-2</v>
       </c>
       <c r="I14" s="15">
         <v>0</v>
       </c>
       <c r="J14" s="2">
-        <v>1.4359031078171438</v>
+        <v>34.669224296258527</v>
       </c>
       <c r="K14" s="2">
-        <v>2.6984971849946402</v>
+        <v>66.592285778879997</v>
       </c>
       <c r="L14" s="2">
-        <v>1.8024671110952224</v>
+        <v>43.592757973888887</v>
       </c>
       <c r="M14" s="2">
-        <v>2.4367969526210818</v>
+        <v>59.048136223898794</v>
       </c>
       <c r="N14" s="4">
-        <v>3.2754125309196483E-2</v>
+        <v>7.9887104313774771E-2</v>
       </c>
       <c r="O14" s="4">
-        <v>4.55503243047485E-2</v>
+        <v>4.1724617524339355E-2</v>
       </c>
       <c r="P14" s="15">
-        <v>0.20351769929714394</v>
+        <v>3.4701988818540461</v>
       </c>
       <c r="Q14" s="15">
-        <v>1.0763175939415467E-2</v>
+        <v>5.0341856510546588E-2</v>
       </c>
       <c r="R14" s="92">
-        <v>0.29882156160837919</v>
+        <v>3.9546057100127742E-2</v>
       </c>
       <c r="S14" s="86">
-        <v>1.8659804056246816</v>
+        <v>-13.312996389940134</v>
       </c>
       <c r="T14" s="13" t="s">
-        <v>170</v>
+        <v>242</v>
       </c>
       <c r="U14" s="11" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="V14" s="14">
-        <v>45900</v>
+        <v>45716</v>
       </c>
       <c r="W14" s="11" t="s">
-        <v>163</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" spans="1:23">
@@ -6376,14 +6376,14 @@
         <v>22</v>
       </c>
       <c r="C4" s="34">
-        <v>4.1700000000000001E-2</v>
+        <v>4.36E-2</v>
       </c>
       <c r="D4" s="34">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="E4" s="35">
         <f>D4-C4</f>
-        <v>3.3299999999999996E-2</v>
+        <v>3.1399999999999997E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="G3" s="73">
         <f>F3/$F$9</f>
-        <v>0.39828327116190743</v>
+        <v>0.39304431740650331</v>
       </c>
       <c r="H3" s="91" t="s">
         <v>233</v>
@@ -6667,7 +6667,7 @@
       </c>
       <c r="C4" s="75">
         <f>VLOOKUP(B4,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>17.36</v>
+        <v>17.760000000000002</v>
       </c>
       <c r="D4" s="74" t="str">
         <f>VLOOKUP(B4,Opportunities!B$3:E$12,4,FALSE)</f>
@@ -6678,15 +6678,15 @@
       </c>
       <c r="F4" s="76">
         <f>C4*E4</f>
-        <v>173600</v>
+        <v>177600.00000000003</v>
       </c>
       <c r="G4" s="73">
         <f>F4/$F$9</f>
-        <v>0.1967639092192075</v>
+        <v>0.19864980323714623</v>
       </c>
       <c r="H4" s="73">
         <f>VLOOKUP(B4,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>5.9540092257125532E-2</v>
+        <v>6.7201415081279747E-2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="C5" s="75">
         <f>VLOOKUP(B5,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>7.94</v>
+        <v>8.2200000000000006</v>
       </c>
       <c r="D5" s="74" t="str">
         <f>VLOOKUP(B5,Opportunities!B$3:E$12,4,FALSE)</f>
@@ -6706,11 +6706,11 @@
       </c>
       <c r="F5" s="76">
         <f>E5*C5</f>
-        <v>158800</v>
+        <v>164400</v>
       </c>
       <c r="G5" s="73">
         <f>F5/$F$9</f>
-        <v>0.17998910589867598</v>
+        <v>0.18388529083438532</v>
       </c>
       <c r="H5" s="73">
         <f>VLOOKUP(B5,Opportunities!B$3:I$12,8,FALSE)</f>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="C6" s="75">
         <f>VLOOKUP(B6,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>5.94</v>
+        <v>6.04</v>
       </c>
       <c r="D6" s="74" t="str">
         <f>VLOOKUP(B6,Opportunities!B$3:E$12,4,FALSE)</f>
@@ -6734,15 +6734,15 @@
       </c>
       <c r="F6" s="76">
         <f>E6*C6</f>
-        <v>106920</v>
+        <v>108720</v>
       </c>
       <c r="G6" s="73">
         <f>F6/$F$9</f>
-        <v>0.12118661966427226</v>
+        <v>0.12160589306273949</v>
       </c>
       <c r="H6" s="73">
         <f>VLOOKUP(B6,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.16861122198288883</v>
+        <v>0.16392445461154903</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="C7" s="75">
         <f>VLOOKUP(B7,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>15.26</v>
+        <v>15.32</v>
       </c>
       <c r="D7" s="74" t="str">
         <f>VLOOKUP(B7,Opportunities!B$3:E$12,4,FALSE)</f>
@@ -6762,15 +6762,15 @@
       </c>
       <c r="F7" s="76">
         <f>C7*E7</f>
-        <v>91560</v>
+        <v>91920</v>
       </c>
       <c r="G7" s="73">
         <f>F7/$F$9</f>
-        <v>0.10377709405593685</v>
+        <v>0.10281469545922567</v>
       </c>
       <c r="H7" s="73">
         <f>VLOOKUP(B7,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.2202784312360544</v>
+        <v>0.22093639979403171</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="F9" s="81">
         <f>SUM(F3:F7)</f>
-        <v>882275.62</v>
+        <v>894035.62</v>
       </c>
       <c r="G9" s="82">
         <f>SUM(G3:G7)</f>
@@ -6796,7 +6796,7 @@
       </c>
       <c r="H9" s="89">
         <f>SUM(H4:H7)</f>
-        <v>0.44842974547606873</v>
+        <v>0.45206226948686046</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="C12" s="75">
         <f>VLOOKUP(B12,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>15.26</v>
+        <v>15.32</v>
       </c>
       <c r="D12" s="74" t="str">
         <f>VLOOKUP(B12,Opportunities!B$3:E$12,4,FALSE)</f>
@@ -6829,15 +6829,15 @@
       </c>
       <c r="F12" s="76">
         <f>C12*E12</f>
-        <v>91560</v>
+        <v>91920</v>
       </c>
       <c r="G12" s="73">
         <f>F12/$F$9</f>
-        <v>0.10377709405593685</v>
+        <v>0.10281469545922567</v>
       </c>
       <c r="H12" s="73">
         <f>VLOOKUP(B12,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.2202784312360544</v>
+        <v>0.22093639979403171</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -6859,11 +6859,11 @@
       </c>
       <c r="F14" s="81">
         <f>F3-F12</f>
-        <v>259835.62</v>
+        <v>259475.62</v>
       </c>
       <c r="G14" s="89">
         <f t="shared" ref="G14" si="0">F14/$F$9</f>
-        <v>0.2945061771059706</v>
+        <v>0.29022962194727769</v>
       </c>
       <c r="H14" s="89">
         <f>Portfolio_Mgmt!E61</f>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF47764D-B7A4-4E2A-9646-59377A0122BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8000EF81-E224-4FB2-A7CC-204CC55A7F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -2194,17 +2194,17 @@
     <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2240,7 +2240,29 @@
     <cellStyle name="常规 2" xfId="3" xr:uid="{32ADA8AA-F280-4250-ABBF-7E6B9CB799DC}"/>
     <cellStyle name="超链接" xfId="2" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
@@ -2585,12 +2607,12 @@
       <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B4" s="95" t="s">
+      <c r="B4" s="94" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="20" t="s">
@@ -2602,12 +2624,12 @@
       <c r="C6" s="61"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" s="95" t="s">
+      <c r="B7" s="94" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="95"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="94"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="23" t="s">
@@ -2696,12 +2718,12 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
-      <c r="B24" s="95" t="s">
+      <c r="B24" s="94" t="s">
         <v>220</v>
       </c>
-      <c r="C24" s="95"/>
-      <c r="D24" s="95"/>
-      <c r="E24" s="95"/>
+      <c r="C24" s="94"/>
+      <c r="D24" s="94"/>
+      <c r="E24" s="94"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
@@ -2801,20 +2823,20 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="B39" s="95" t="s">
+      <c r="B39" s="94" t="s">
         <v>156</v>
       </c>
-      <c r="C39" s="95"/>
-      <c r="D39" s="95"/>
-      <c r="E39" s="95"/>
+      <c r="C39" s="94"/>
+      <c r="D39" s="94"/>
+      <c r="E39" s="94"/>
     </row>
     <row r="40" spans="1:5" ht="46.6" customHeight="1">
-      <c r="B40" s="95" t="s">
+      <c r="B40" s="94" t="s">
         <v>235</v>
       </c>
-      <c r="C40" s="95"/>
-      <c r="D40" s="95"/>
-      <c r="E40" s="95"/>
+      <c r="C40" s="94"/>
+      <c r="D40" s="94"/>
+      <c r="E40" s="94"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="21" t="s">
@@ -2826,12 +2848,12 @@
       <c r="E42" s="21"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="B44" s="95" t="s">
+      <c r="B44" s="94" t="s">
         <v>208</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="94"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="23" t="s">
@@ -3016,12 +3038,12 @@
       <c r="E69" s="21"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="B71" s="95" t="s">
+      <c r="B71" s="94" t="s">
         <v>196</v>
       </c>
-      <c r="C71" s="95"/>
-      <c r="D71" s="95"/>
-      <c r="E71" s="95"/>
+      <c r="C71" s="94"/>
+      <c r="D71" s="94"/>
+      <c r="E71" s="94"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="28" t="s">
@@ -3083,36 +3105,36 @@
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="B85" s="96" t="s">
+      <c r="B85" s="97" t="s">
         <v>192</v>
       </c>
-      <c r="C85" s="96"/>
-      <c r="D85" s="96"/>
-      <c r="E85" s="96"/>
+      <c r="C85" s="97"/>
+      <c r="D85" s="97"/>
+      <c r="E85" s="97"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="B86" s="94" t="s">
+      <c r="B86" s="96" t="s">
         <v>190</v>
       </c>
-      <c r="C86" s="94"/>
-      <c r="D86" s="94"/>
-      <c r="E86" s="94"/>
+      <c r="C86" s="96"/>
+      <c r="D86" s="96"/>
+      <c r="E86" s="96"/>
     </row>
     <row r="87" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B87" s="95" t="s">
+      <c r="B87" s="94" t="s">
         <v>189</v>
       </c>
-      <c r="C87" s="95"/>
-      <c r="D87" s="95"/>
-      <c r="E87" s="95"/>
+      <c r="C87" s="94"/>
+      <c r="D87" s="94"/>
+      <c r="E87" s="94"/>
     </row>
     <row r="88" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B88" s="95" t="s">
+      <c r="B88" s="94" t="s">
         <v>225</v>
       </c>
-      <c r="C88" s="95"/>
-      <c r="D88" s="95"/>
-      <c r="E88" s="95"/>
+      <c r="C88" s="94"/>
+      <c r="D88" s="94"/>
+      <c r="E88" s="94"/>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="24" t="s">
@@ -3145,12 +3167,12 @@
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="B97" s="97" t="s">
+      <c r="B97" s="95" t="s">
         <v>211</v>
       </c>
-      <c r="C97" s="97"/>
-      <c r="D97" s="97"/>
-      <c r="E97" s="97"/>
+      <c r="C97" s="95"/>
+      <c r="D97" s="95"/>
+      <c r="E97" s="95"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
@@ -3158,20 +3180,20 @@
       </c>
     </row>
     <row r="100" spans="1:5" ht="12.4">
-      <c r="B100" s="97" t="s">
+      <c r="B100" s="95" t="s">
         <v>212</v>
       </c>
-      <c r="C100" s="97"/>
-      <c r="D100" s="97"/>
-      <c r="E100" s="97"/>
+      <c r="C100" s="95"/>
+      <c r="D100" s="95"/>
+      <c r="E100" s="95"/>
     </row>
     <row r="101" spans="1:5" ht="58.5" customHeight="1">
-      <c r="B101" s="95" t="s">
+      <c r="B101" s="94" t="s">
         <v>219</v>
       </c>
-      <c r="C101" s="95"/>
-      <c r="D101" s="95"/>
-      <c r="E101" s="95"/>
+      <c r="C101" s="94"/>
+      <c r="D101" s="94"/>
+      <c r="E101" s="94"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="28" t="s">
@@ -3219,20 +3241,20 @@
         <v>176</v>
       </c>
       <c r="C112" s="44">
-        <v>0.11959137223365987</v>
+        <v>0.11082705639317539</v>
       </c>
       <c r="D112" s="61" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
-        <v/>
+        <v>Warning: Return is lower than the Benchmark.</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B114" s="95" t="s">
+      <c r="B114" s="94" t="s">
         <v>217</v>
       </c>
-      <c r="C114" s="95"/>
-      <c r="D114" s="95"/>
-      <c r="E114" s="95"/>
+      <c r="C114" s="94"/>
+      <c r="D114" s="94"/>
+      <c r="E114" s="94"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="21" t="s">
@@ -3265,12 +3287,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
     <mergeCell ref="B86:E86"/>
     <mergeCell ref="B71:E71"/>
     <mergeCell ref="B85:E85"/>
@@ -3280,6 +3296,12 @@
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3436,30 +3458,30 @@
         <v>160</v>
       </c>
       <c r="F3" s="15">
-        <v>0.22093639979403168</v>
+        <v>0.19063377748254529</v>
       </c>
       <c r="G3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$10</f>
-        <v>0.10353639979403167</v>
+        <v>7.3233777482545281E-2</v>
       </c>
       <c r="H3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$11</f>
-        <v>0.18643639979403168</v>
+        <v>0.15613377748254528</v>
       </c>
       <c r="I3" s="15">
-        <v>0.22093639979403171</v>
+        <v>0.19063377748254529</v>
       </c>
       <c r="J3" s="2">
-        <v>12.76034731937011</v>
+        <v>11.864263383794571</v>
       </c>
       <c r="K3" s="2">
-        <v>25.861790776733326</v>
+        <v>23.893094370273865</v>
       </c>
       <c r="L3" s="2">
-        <v>16.113365751277065</v>
+        <v>14.974073849390802</v>
       </c>
       <c r="M3" s="86">
-        <v>21.933241308816839</v>
+        <v>20.370426628588771</v>
       </c>
       <c r="N3" s="4">
         <v>6.5626579329258014E-2</v>
@@ -3797,7 +3819,7 @@
         <v>8.7843860478168362E-2</v>
       </c>
       <c r="I8" s="15">
-        <v>6.7201415081279747E-2</v>
+        <v>9.7504037392766141E-2</v>
       </c>
       <c r="J8" s="2">
         <v>11.804906901225705</v>
@@ -6313,6 +6335,21 @@
     <mergeCell ref="L1:M1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="J3:J1048576">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>J3&gt;D3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L3:L1048576">
+    <cfRule type="expression" dxfId="1" priority="4">
+      <formula>L3&gt;D3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M3:M1048576">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>D3&gt;M3</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="75" orientation="landscape" r:id="rId1"/>
 </worksheet>
@@ -6686,7 +6723,7 @@
       </c>
       <c r="H4" s="73">
         <f>VLOOKUP(B4,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>6.7201415081279747E-2</v>
+        <v>9.7504037392766141E-2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6770,7 +6807,7 @@
       </c>
       <c r="H7" s="73">
         <f>VLOOKUP(B7,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.22093639979403171</v>
+        <v>0.19063377748254529</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -6837,7 +6874,7 @@
       </c>
       <c r="H12" s="73">
         <f>VLOOKUP(B12,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.22093639979403171</v>
+        <v>0.19063377748254529</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -6960,15 +6997,15 @@
       <c r="B5" s="106" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="95"/>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="106" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="97"/>
-      <c r="D6" s="97"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8000EF81-E224-4FB2-A7CC-204CC55A7F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45782BCE-70CB-4A14-9FE2-FC4F92CAE26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -3241,7 +3241,7 @@
         <v>176</v>
       </c>
       <c r="C112" s="44">
-        <v>0.11082705639317539</v>
+        <v>0.10743889729487202</v>
       </c>
       <c r="D112" s="61" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
@@ -3452,42 +3452,42 @@
         <v>259</v>
       </c>
       <c r="D3" s="2">
-        <v>15.32</v>
+        <v>15.44</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F3" s="15">
-        <v>0.19063377748254529</v>
+        <v>0.18737363316325828</v>
       </c>
       <c r="G3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$10</f>
-        <v>7.3233777482545281E-2</v>
+        <v>6.9973633163258275E-2</v>
       </c>
       <c r="H3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$11</f>
-        <v>0.15613377748254528</v>
+        <v>0.15287363316325828</v>
       </c>
       <c r="I3" s="15">
-        <v>0.19063377748254529</v>
+        <v>0.18737363316325828</v>
       </c>
       <c r="J3" s="2">
-        <v>11.864263383794571</v>
+        <v>11.862033069653084</v>
       </c>
       <c r="K3" s="2">
-        <v>23.893094370273865</v>
+        <v>23.887705575274836</v>
       </c>
       <c r="L3" s="2">
-        <v>14.974073849390802</v>
+        <v>14.971213388216997</v>
       </c>
       <c r="M3" s="86">
-        <v>20.370426628588771</v>
+        <v>20.366464536567324</v>
       </c>
       <c r="N3" s="4">
-        <v>6.5626579329258014E-2</v>
+        <v>6.5101907277916274E-2</v>
       </c>
       <c r="O3" s="4">
-        <v>3.5544021344529921E-2</v>
+        <v>3.5275706733689696E-2</v>
       </c>
       <c r="P3" s="15">
         <v>0.36794481423679237</v>
@@ -3499,7 +3499,7 @@
         <v>0.60402076709908736</v>
       </c>
       <c r="S3" s="86">
-        <v>4.5275447966435411</v>
+        <v>4.5265264551387059</v>
       </c>
       <c r="T3" s="13" t="s">
         <v>246</v>
@@ -3522,42 +3522,42 @@
         <v>237</v>
       </c>
       <c r="D4" s="2">
-        <v>6.04</v>
+        <v>6.08</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F4" s="15">
-        <v>0.16392445461154903</v>
+        <v>0.16112633203079096</v>
       </c>
       <c r="G4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$10</f>
-        <v>4.6524454611549027E-2</v>
+        <v>4.372633203079096E-2</v>
       </c>
       <c r="H4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$11</f>
-        <v>0.12942445461154903</v>
+        <v>0.12662633203079096</v>
       </c>
       <c r="I4" s="15">
-        <v>0.16392445461154903</v>
+        <v>0.16112633203079096</v>
       </c>
       <c r="J4" s="2">
-        <v>4.4297376548118468</v>
+        <v>4.428921836807783</v>
       </c>
       <c r="K4" s="2">
-        <v>7.9687949811097125</v>
+        <v>7.9670026289547851</v>
       </c>
       <c r="L4" s="2">
-        <v>5.5425085642246721</v>
+        <v>5.5414713233942736</v>
       </c>
       <c r="M4" s="86">
-        <v>7.4648073588925268</v>
+        <v>7.4633845319646834</v>
       </c>
       <c r="N4" s="4">
-        <v>0.12816382759890571</v>
+        <v>0.12729200739087043</v>
       </c>
       <c r="O4" s="4">
-        <v>7.3168793113243216E-2</v>
+        <v>7.2687419474340292E-2</v>
       </c>
       <c r="P4" s="15">
         <v>0.61007460831657279</v>
@@ -3569,7 +3569,7 @@
         <v>1.1309485990394448</v>
       </c>
       <c r="S4" s="86">
-        <v>-3.8106491775983788</v>
+        <v>-3.8097920812266781</v>
       </c>
       <c r="T4" s="13" t="s">
         <v>239</v>
@@ -3592,21 +3592,21 @@
         <v>277</v>
       </c>
       <c r="D5" s="2">
-        <v>69.099999999999994</v>
+        <v>69.39</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>275</v>
       </c>
       <c r="F5" s="15">
-        <v>0.15689676518236584</v>
+        <v>0.15518819500348435</v>
       </c>
       <c r="G5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$10</f>
-        <v>3.9496765182365834E-2</v>
+        <v>3.7788195003484348E-2</v>
       </c>
       <c r="H5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$11</f>
-        <v>0.12239676518236584</v>
+        <v>0.12068819500348435</v>
       </c>
       <c r="I5" s="15">
         <v>0</v>
@@ -3624,10 +3624,10 @@
         <v>84.017562490801396</v>
       </c>
       <c r="N5" s="4">
-        <v>7.6411022594320921E-2</v>
+        <v>7.6091679799215661E-2</v>
       </c>
       <c r="O5" s="4">
-        <v>6.7250361794500738E-2</v>
+        <v>6.6969303934284477E-2</v>
       </c>
       <c r="P5" s="15">
         <v>0.30279158651211824</v>
@@ -3656,142 +3656,142 @@
     </row>
     <row r="6" spans="1:23">
       <c r="B6" s="11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D6" s="2">
-        <v>54.35</v>
+        <v>21.15</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>160</v>
+        <v>253</v>
       </c>
       <c r="F6" s="15">
-        <v>0.14793773051313952</v>
+        <v>0.14021163259405034</v>
       </c>
       <c r="G6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$10</f>
-        <v>3.0537730513139516E-2</v>
+        <v>2.2811632594050335E-2</v>
       </c>
       <c r="H6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$11</f>
-        <v>0.11343773051313952</v>
+        <v>0.10571163259405034</v>
       </c>
       <c r="I6" s="15">
-        <v>0.14793773051313952</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>38.625338845755344</v>
+        <v>14.418941896437474</v>
       </c>
       <c r="K6" s="2">
-        <v>64.73708395408849</v>
+        <v>29.309951346473134</v>
       </c>
       <c r="L6" s="2">
-        <v>48.087218068397867</v>
+        <v>18.21218480698677</v>
       </c>
       <c r="M6" s="86">
-        <v>64.387469610682459</v>
+        <v>24.796949133193245</v>
       </c>
       <c r="N6" s="4">
-        <v>9.67233515064677E-2</v>
+        <v>0.21555373746279879</v>
       </c>
       <c r="O6" s="4">
-        <v>9.2793093543592248E-2</v>
+        <v>2.8066193853427897E-2</v>
       </c>
       <c r="P6" s="15">
-        <v>1.2907496012759174</v>
+        <v>1.4851905363915479</v>
       </c>
       <c r="Q6" s="15">
-        <v>0.24768740031897937</v>
+        <v>0.95241105291674188</v>
       </c>
       <c r="R6" s="92">
-        <v>0.73855199466278643</v>
+        <v>4.0148803043206254</v>
       </c>
       <c r="S6" s="86">
-        <v>-2.6437960879200806</v>
+        <v>-38.360607814419353</v>
       </c>
       <c r="T6" s="13" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="U6" s="11" t="s">
         <v>162</v>
       </c>
       <c r="V6" s="14">
-        <v>45808</v>
+        <v>45900</v>
       </c>
       <c r="W6" s="11" t="s">
-        <v>163</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" spans="1:23">
       <c r="B7" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D7" s="2">
-        <v>21.47</v>
+        <v>55.75</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>253</v>
+        <v>160</v>
       </c>
       <c r="F7" s="15">
-        <v>0.13438178033413717</v>
+        <v>0.13796564912031539</v>
       </c>
       <c r="G7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$10</f>
-        <v>1.6981780334137164E-2</v>
+        <v>2.0565649120315388E-2</v>
       </c>
       <c r="H7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$11</f>
-        <v>9.9881780334137166E-2</v>
+        <v>0.10346564912031539</v>
       </c>
       <c r="I7" s="15">
-        <v>0</v>
+        <v>0.13796564912031539</v>
       </c>
       <c r="J7" s="2">
-        <v>14.418941896437474</v>
+        <v>38.67449654927848</v>
       </c>
       <c r="K7" s="2">
-        <v>29.309951346473134</v>
+        <v>64.818448718764827</v>
       </c>
       <c r="L7" s="2">
-        <v>18.21218480698677</v>
+        <v>48.148365693729644</v>
       </c>
       <c r="M7" s="86">
-        <v>24.796949133193245</v>
+        <v>64.469262649530066</v>
       </c>
       <c r="N7" s="4">
-        <v>0.21234101291747526</v>
+        <v>9.4419233289180268E-2</v>
       </c>
       <c r="O7" s="4">
-        <v>2.7647880763856547E-2</v>
+        <v>9.0582600896860987E-2</v>
       </c>
       <c r="P7" s="15">
-        <v>1.4851905363915479</v>
+        <v>1.2907496012759174</v>
       </c>
       <c r="Q7" s="15">
-        <v>0.95241105291674188</v>
+        <v>0.24768740031897937</v>
       </c>
       <c r="R7" s="92">
-        <v>4.0148803043206254</v>
+        <v>0.73855199466278643</v>
       </c>
       <c r="S7" s="86">
-        <v>-38.360607814419353</v>
+        <v>-2.6472954415279868</v>
       </c>
       <c r="T7" s="13" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="U7" s="11" t="s">
         <v>162</v>
       </c>
       <c r="V7" s="14">
-        <v>45900</v>
+        <v>45808</v>
       </c>
       <c r="W7" s="11" t="s">
-        <v>247</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -3802,24 +3802,24 @@
         <v>159</v>
       </c>
       <c r="D8" s="2">
-        <v>17.760000000000002</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F8" s="15">
-        <v>0.12234386047816836</v>
+        <v>0.11920444715894019</v>
       </c>
       <c r="G8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$10</f>
-        <v>4.9438604781683604E-3</v>
+        <v>1.8044471589401812E-3</v>
       </c>
       <c r="H8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$11</f>
-        <v>8.7843860478168362E-2</v>
+        <v>8.4704447158940183E-2</v>
       </c>
       <c r="I8" s="15">
-        <v>9.7504037392766141E-2</v>
+        <v>0.11353438568563534</v>
       </c>
       <c r="J8" s="2">
         <v>11.804906901225705</v>
@@ -3834,10 +3834,10 @@
         <v>19.785541823839793</v>
       </c>
       <c r="N8" s="4">
-        <v>9.7296510099641298E-2</v>
+        <v>9.6535531808359179E-2</v>
       </c>
       <c r="O8" s="4">
-        <v>7.6576576576576572E-2</v>
+        <v>7.5977653631284933E-2</v>
       </c>
       <c r="P8" s="15">
         <v>0.31018327415220487</v>
@@ -3872,42 +3872,42 @@
         <v>241</v>
       </c>
       <c r="D9" s="2">
-        <v>54.65</v>
+        <v>54</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F9" s="15">
-        <v>0.10734290687447179</v>
+        <v>0.11184849157270471</v>
       </c>
       <c r="G9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$10</f>
-        <v>-1.0057093125528216E-2</v>
+        <v>-5.551508427295293E-3</v>
       </c>
       <c r="H9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$11</f>
-        <v>7.2842906874471786E-2</v>
+        <v>7.7348491572704708E-2</v>
       </c>
       <c r="I9" s="15">
         <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>34.387950625486518</v>
+        <v>34.381875852171149</v>
       </c>
       <c r="K9" s="2">
-        <v>67.376724540900142</v>
+        <v>67.361539432485785</v>
       </c>
       <c r="L9" s="2">
-        <v>43.306333799977494</v>
+        <v>43.298516914573895</v>
       </c>
       <c r="M9" s="86">
-        <v>58.765056240717605</v>
+        <v>58.754189493018607</v>
       </c>
       <c r="N9" s="4">
-        <v>4.1465766109394828E-2</v>
+        <v>4.1955491566384277E-2</v>
       </c>
       <c r="O9" s="4">
-        <v>3.748439251511098E-2</v>
+        <v>3.7944127980758587E-2</v>
       </c>
       <c r="P9" s="15">
         <v>0.72207550313588764</v>
@@ -3919,7 +3919,7 @@
         <v>7.3592411949940734E-2</v>
       </c>
       <c r="S9" s="86">
-        <v>1.3348070848882203</v>
+        <v>1.334506858271689</v>
       </c>
       <c r="T9" s="13" t="s">
         <v>242</v>
@@ -3942,21 +3942,21 @@
         <v>165</v>
       </c>
       <c r="D10" s="2">
-        <v>8.2200000000000006</v>
+        <v>8.1</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F10" s="15">
-        <v>0.10504291417240008</v>
+        <v>0.11083350655450119</v>
       </c>
       <c r="G10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$10</f>
-        <v>-1.2357085827599923E-2</v>
+        <v>-6.5664934454988111E-3</v>
       </c>
       <c r="H10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$11</f>
-        <v>7.0542914172400079E-2</v>
+        <v>7.633350655450119E-2</v>
       </c>
       <c r="I10" s="15">
         <v>0</v>
@@ -3974,10 +3974,10 @@
         <v>8.7684502451266084</v>
       </c>
       <c r="N10" s="4">
-        <v>3.7578877370105228E-2</v>
+        <v>3.8135601479291979E-2</v>
       </c>
       <c r="O10" s="4">
-        <v>7.055961070559609E-2</v>
+        <v>7.160493827160494E-2</v>
       </c>
       <c r="P10" s="15">
         <v>8.3114411724224596E-2</v>
@@ -4006,66 +4006,66 @@
     </row>
     <row r="11" spans="1:23">
       <c r="B11" s="11" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="D11" s="2">
-        <v>28.4</v>
+        <v>14.3</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>253</v>
+        <v>160</v>
       </c>
       <c r="F11" s="15">
-        <v>9.9596254590427646E-2</v>
+        <v>0.1090060893695004</v>
       </c>
       <c r="G11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$10</f>
-        <v>-1.7803745409572358E-2</v>
+        <v>-8.3939106304996014E-3</v>
       </c>
       <c r="H11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$11</f>
-        <v>6.5096254590427644E-2</v>
+        <v>7.45060893695004E-2</v>
       </c>
       <c r="I11" s="15">
         <v>0</v>
       </c>
       <c r="J11" s="2">
-        <v>17.682685147645955</v>
+        <v>9.1251344157607761</v>
       </c>
       <c r="K11" s="2">
-        <v>32.464859269378167</v>
+        <v>16.718616112226428</v>
       </c>
       <c r="L11" s="2">
-        <v>22.157904669779033</v>
+        <v>11.432798659390293</v>
       </c>
       <c r="M11" s="86">
-        <v>29.895007167811503</v>
+        <v>15.422137352615858</v>
       </c>
       <c r="N11" s="4">
-        <v>8.9407303076866118E-2</v>
+        <v>0.10749746672561937</v>
       </c>
       <c r="O11" s="4">
-        <v>5.6338028169014093E-2</v>
+        <v>5.8350495104895095E-2</v>
       </c>
       <c r="P11" s="15">
-        <v>0.78990369994931575</v>
+        <v>2.2875080906148866</v>
       </c>
       <c r="Q11" s="15">
-        <v>0.40281804358844397</v>
+        <v>1.5035598705501618</v>
       </c>
       <c r="R11" s="92">
-        <v>3.955391512509995</v>
+        <v>4.1998196571663646</v>
       </c>
       <c r="S11" s="86">
-        <v>-26.938493611476797</v>
+        <v>-12.151746556489819</v>
       </c>
       <c r="T11" s="13" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="U11" s="11" t="s">
-        <v>162</v>
+        <v>248</v>
       </c>
       <c r="V11" s="14">
         <v>45900</v>
@@ -4076,66 +4076,66 @@
     </row>
     <row r="12" spans="1:23">
       <c r="B12" s="11" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="D12" s="2">
-        <v>14.82</v>
+        <v>28.23</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>160</v>
+        <v>253</v>
       </c>
       <c r="F12" s="15">
-        <v>9.4690284991131524E-2</v>
+        <v>0.10191457699731421</v>
       </c>
       <c r="G12" s="15">
         <f>F12 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.2709715008868481E-2</v>
+        <v>-1.5485423002685794E-2</v>
       </c>
       <c r="H12" s="15">
         <f>F12 - Portfolio_Mgmt!$C$11</f>
-        <v>6.0190284991131521E-2</v>
+        <v>6.7414576997314207E-2</v>
       </c>
       <c r="I12" s="15">
         <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>9.113307921310053</v>
+        <v>17.682685147645955</v>
       </c>
       <c r="K12" s="2">
-        <v>16.69703417753378</v>
+        <v>32.464859269378167</v>
       </c>
       <c r="L12" s="2">
-        <v>11.4179857156617</v>
+        <v>22.157904669779033</v>
       </c>
       <c r="M12" s="86">
-        <v>15.402162441309935</v>
+        <v>29.895007167811503</v>
       </c>
       <c r="N12" s="4">
-        <v>0.10358778927538839</v>
+        <v>8.9945710498866363E-2</v>
       </c>
       <c r="O12" s="4">
-        <v>5.6228684490991498E-2</v>
+        <v>5.6677293659227773E-2</v>
       </c>
       <c r="P12" s="15">
-        <v>2.2875080906148866</v>
+        <v>0.78990369994931575</v>
       </c>
       <c r="Q12" s="15">
-        <v>1.5035598705501618</v>
+        <v>0.40281804358844397</v>
       </c>
       <c r="R12" s="92">
-        <v>4.1998196571663646</v>
+        <v>3.955391512509995</v>
       </c>
       <c r="S12" s="86">
-        <v>-12.135683650367685</v>
+        <v>-26.938493611476797</v>
       </c>
       <c r="T12" s="13" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="U12" s="11" t="s">
-        <v>248</v>
+        <v>162</v>
       </c>
       <c r="V12" s="14">
         <v>45900</v>
@@ -4152,42 +4152,42 @@
         <v>169</v>
       </c>
       <c r="D13" s="2">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F13" s="15">
-        <v>9.0784414850680895E-2</v>
+        <v>9.5546776071535167E-2</v>
       </c>
       <c r="G13" s="15">
         <f>F13 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.661558514931911E-2</v>
+        <v>-2.1853223928464838E-2</v>
       </c>
       <c r="H13" s="15">
         <f>F13 - Portfolio_Mgmt!$C$11</f>
-        <v>5.6284414850680892E-2</v>
+        <v>6.1046776071535164E-2</v>
       </c>
       <c r="I13" s="15">
         <v>0</v>
       </c>
       <c r="J13" s="2">
-        <v>1.4426109829749554</v>
+        <v>1.442374867722968</v>
       </c>
       <c r="K13" s="2">
-        <v>2.7161528914315056</v>
+        <v>2.7155321746611896</v>
       </c>
       <c r="L13" s="2">
-        <v>1.8111437377776596</v>
+        <v>1.8108383615725383</v>
       </c>
       <c r="M13" s="2">
-        <v>2.4489275916264743</v>
+        <v>2.4485007089485338</v>
       </c>
       <c r="N13" s="4">
-        <v>3.4761910353543202E-2</v>
+        <v>3.5197892699834928E-2</v>
       </c>
       <c r="O13" s="4">
-        <v>4.7731033272727166E-2</v>
+        <v>4.8351240838924094E-2</v>
       </c>
       <c r="P13" s="15">
         <v>0.20351769929714394</v>
@@ -4199,7 +4199,7 @@
         <v>0.29882156160837919</v>
       </c>
       <c r="S13" s="86">
-        <v>1.8779952123654464</v>
+        <v>1.8775728111399408</v>
       </c>
       <c r="T13" s="13" t="s">
         <v>170</v>
@@ -4222,21 +4222,21 @@
         <v>274</v>
       </c>
       <c r="D14" s="2">
-        <v>57.52</v>
+        <v>57.4</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>275</v>
       </c>
       <c r="F14" s="15">
-        <v>8.984625754804787E-2</v>
+        <v>9.0634582120934004E-2</v>
       </c>
       <c r="G14" s="15">
         <f>F14 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.7553742451952135E-2</v>
+        <v>-2.6765417879066E-2</v>
       </c>
       <c r="H14" s="15">
         <f>F14 - Portfolio_Mgmt!$C$11</f>
-        <v>5.5346257548047867E-2</v>
+        <v>5.6134582120934001E-2</v>
       </c>
       <c r="I14" s="15">
         <v>0</v>
@@ -4254,10 +4254,10 @@
         <v>59.048136223898794</v>
       </c>
       <c r="N14" s="4">
-        <v>7.9887104313774771E-2</v>
+        <v>8.005411568167814E-2</v>
       </c>
       <c r="O14" s="4">
-        <v>4.1724617524339355E-2</v>
+        <v>4.1811846689895467E-2</v>
       </c>
       <c r="P14" s="15">
         <v>3.4701988818540461</v>
@@ -6413,14 +6413,14 @@
         <v>22</v>
       </c>
       <c r="C4" s="34">
-        <v>4.36E-2</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="D4" s="34">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="E4" s="35">
         <f>D4-C4</f>
-        <v>3.1399999999999997E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="G3" s="73">
         <f>F3/$F$9</f>
-        <v>0.39304431740650331</v>
+        <v>0.39285097563642929</v>
       </c>
       <c r="H3" s="91" t="s">
         <v>233</v>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="C4" s="75">
         <f>VLOOKUP(B4,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>17.760000000000002</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="D4" s="74" t="str">
         <f>VLOOKUP(B4,Opportunities!B$3:E$12,4,FALSE)</f>
@@ -6715,15 +6715,15 @@
       </c>
       <c r="F4" s="76">
         <f>C4*E4</f>
-        <v>177600.00000000003</v>
+        <v>179000</v>
       </c>
       <c r="G4" s="73">
         <f>F4/$F$9</f>
-        <v>0.19864980323714623</v>
+        <v>0.20011724858414812</v>
       </c>
       <c r="H4" s="73">
         <f>VLOOKUP(B4,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>9.7504037392766141E-2</v>
+        <v>0.11353438568563534</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="C5" s="75">
         <f>VLOOKUP(B5,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>8.2200000000000006</v>
+        <v>8.1</v>
       </c>
       <c r="D5" s="74" t="str">
         <f>VLOOKUP(B5,Opportunities!B$3:E$12,4,FALSE)</f>
@@ -6743,11 +6743,11 @@
       </c>
       <c r="F5" s="76">
         <f>E5*C5</f>
-        <v>164400</v>
+        <v>162000</v>
       </c>
       <c r="G5" s="73">
         <f>F5/$F$9</f>
-        <v>0.18388529083438532</v>
+        <v>0.18111169983593292</v>
       </c>
       <c r="H5" s="73">
         <f>VLOOKUP(B5,Opportunities!B$3:I$12,8,FALSE)</f>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="C6" s="75">
         <f>VLOOKUP(B6,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>6.04</v>
+        <v>6.08</v>
       </c>
       <c r="D6" s="74" t="str">
         <f>VLOOKUP(B6,Opportunities!B$3:E$12,4,FALSE)</f>
@@ -6771,15 +6771,15 @@
       </c>
       <c r="F6" s="76">
         <f>E6*C6</f>
-        <v>108720</v>
+        <v>109440</v>
       </c>
       <c r="G6" s="73">
         <f>F6/$F$9</f>
-        <v>0.12160589306273949</v>
+        <v>0.12235101500027469</v>
       </c>
       <c r="H6" s="73">
         <f>VLOOKUP(B6,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.16392445461154903</v>
+        <v>0.16112633203079096</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="C7" s="75">
         <f>VLOOKUP(B7,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>15.32</v>
+        <v>15.44</v>
       </c>
       <c r="D7" s="74" t="str">
         <f>VLOOKUP(B7,Opportunities!B$3:E$12,4,FALSE)</f>
@@ -6799,15 +6799,15 @@
       </c>
       <c r="F7" s="76">
         <f>C7*E7</f>
-        <v>91920</v>
+        <v>92640</v>
       </c>
       <c r="G7" s="73">
         <f>F7/$F$9</f>
-        <v>0.10281469545922567</v>
+        <v>0.10356906094321498</v>
       </c>
       <c r="H7" s="73">
         <f>VLOOKUP(B7,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.19063377748254529</v>
+        <v>0.18737363316325828</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -6825,15 +6825,15 @@
       </c>
       <c r="F9" s="81">
         <f>SUM(F3:F7)</f>
-        <v>894035.62</v>
+        <v>894475.62</v>
       </c>
       <c r="G9" s="82">
         <f>SUM(G3:G7)</f>
-        <v>1</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="H9" s="89">
         <f>SUM(H4:H7)</f>
-        <v>0.45206226948686046</v>
+        <v>0.46203435087968459</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="C12" s="75">
         <f>VLOOKUP(B12,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>15.32</v>
+        <v>15.44</v>
       </c>
       <c r="D12" s="74" t="str">
         <f>VLOOKUP(B12,Opportunities!B$3:E$12,4,FALSE)</f>
@@ -6866,15 +6866,15 @@
       </c>
       <c r="F12" s="76">
         <f>C12*E12</f>
-        <v>91920</v>
+        <v>92640</v>
       </c>
       <c r="G12" s="73">
         <f>F12/$F$9</f>
-        <v>0.10281469545922567</v>
+        <v>0.10356906094321498</v>
       </c>
       <c r="H12" s="73">
         <f>VLOOKUP(B12,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.19063377748254529</v>
+        <v>0.18737363316325828</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -6896,11 +6896,11 @@
       </c>
       <c r="F14" s="81">
         <f>F3-F12</f>
-        <v>259475.62</v>
+        <v>258755.62</v>
       </c>
       <c r="G14" s="89">
         <f t="shared" ref="G14" si="0">F14/$F$9</f>
-        <v>0.29022962194727769</v>
+        <v>0.28928191469321435</v>
       </c>
       <c r="H14" s="89">
         <f>Portfolio_Mgmt!E61</f>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45782BCE-70CB-4A14-9FE2-FC4F92CAE26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5CBE852-C440-45D2-9783-7F0B53670D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="281">
   <si>
     <t>Name</t>
   </si>
@@ -1619,6 +1619,15 @@
   </si>
   <si>
     <t>洋河股份</t>
+  </si>
+  <si>
+    <t>9959.HK</t>
+  </si>
+  <si>
+    <t>聯易融科技</t>
+  </si>
+  <si>
+    <t>FIN_03</t>
   </si>
 </sst>
 </file>
@@ -3241,11 +3250,11 @@
         <v>176</v>
       </c>
       <c r="C112" s="44">
-        <v>0.10743889729487202</v>
+        <v>0.12655471362938422</v>
       </c>
       <c r="D112" s="61" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
-        <v>Warning: Return is lower than the Benchmark.</v>
+        <v/>
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
@@ -3446,66 +3455,66 @@
     </row>
     <row r="3" spans="1:23">
       <c r="B3" s="11" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="D3" s="2">
-        <v>15.44</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F3" s="15">
-        <v>0.18737363316325828</v>
+        <v>0.21644266614219942</v>
       </c>
       <c r="G3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$10</f>
-        <v>6.9973633163258275E-2</v>
+        <v>9.904266614219942E-2</v>
       </c>
       <c r="H3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$11</f>
-        <v>0.15287363316325828</v>
+        <v>0.18194266614219942</v>
       </c>
       <c r="I3" s="15">
-        <v>0.18737363316325828</v>
+        <v>0.21644266614219942</v>
       </c>
       <c r="J3" s="2">
-        <v>11.862033069653084</v>
+        <v>0.9421991685622978</v>
       </c>
       <c r="K3" s="2">
-        <v>23.887705575274836</v>
+        <v>2.0700115733313686</v>
       </c>
       <c r="L3" s="2">
-        <v>14.971213388216997</v>
+        <v>1.197923364196394</v>
       </c>
       <c r="M3" s="86">
-        <v>20.366464536567324</v>
+        <v>1.6432419261953275</v>
       </c>
       <c r="N3" s="4">
-        <v>6.5101907277916274E-2</v>
+        <v>6.3476783162570317E-3</v>
       </c>
       <c r="O3" s="4">
-        <v>3.5275706733689696E-2</v>
+        <v>0</v>
       </c>
       <c r="P3" s="15">
-        <v>0.36794481423679237</v>
+        <v>9.7057481271370302E-2</v>
       </c>
       <c r="Q3" s="15">
-        <v>7.4171010848313429E-2</v>
+        <v>1.4790654865358754E-2</v>
       </c>
       <c r="R3" s="92">
-        <v>0.60402076709908736</v>
+        <v>3.4432102574884196</v>
       </c>
       <c r="S3" s="86">
-        <v>4.5265264551387059</v>
+        <v>2.0258239687205015</v>
       </c>
       <c r="T3" s="13" t="s">
-        <v>246</v>
+        <v>280</v>
       </c>
       <c r="U3" s="11" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="V3" s="14">
         <v>45900</v>
@@ -3516,66 +3525,66 @@
     </row>
     <row r="4" spans="1:23">
       <c r="B4" s="11" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="D4" s="2">
-        <v>6.08</v>
+        <v>15.44</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F4" s="15">
-        <v>0.16112633203079096</v>
+        <v>0.18737363316325828</v>
       </c>
       <c r="G4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$10</f>
-        <v>4.372633203079096E-2</v>
+        <v>6.9973633163258275E-2</v>
       </c>
       <c r="H4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$11</f>
-        <v>0.12662633203079096</v>
+        <v>0.15287363316325828</v>
       </c>
       <c r="I4" s="15">
-        <v>0.16112633203079096</v>
+        <v>0.18737363316325828</v>
       </c>
       <c r="J4" s="2">
-        <v>4.428921836807783</v>
+        <v>11.862033069653084</v>
       </c>
       <c r="K4" s="2">
-        <v>7.9670026289547851</v>
+        <v>23.887705575274836</v>
       </c>
       <c r="L4" s="2">
-        <v>5.5414713233942736</v>
+        <v>14.971213388216997</v>
       </c>
       <c r="M4" s="86">
-        <v>7.4633845319646834</v>
+        <v>20.366464536567324</v>
       </c>
       <c r="N4" s="4">
-        <v>0.12729200739087043</v>
+        <v>6.5101907277916274E-2</v>
       </c>
       <c r="O4" s="4">
-        <v>7.2687419474340292E-2</v>
+        <v>3.5275706733689696E-2</v>
       </c>
       <c r="P4" s="15">
-        <v>0.61007460831657279</v>
+        <v>0.36794481423679237</v>
       </c>
       <c r="Q4" s="15">
-        <v>0.16360901428944893</v>
+        <v>7.4171010848313429E-2</v>
       </c>
       <c r="R4" s="92">
-        <v>1.1309485990394448</v>
+        <v>0.60402076709908736</v>
       </c>
       <c r="S4" s="86">
-        <v>-3.8097920812266781</v>
+        <v>4.5265264551387059</v>
       </c>
       <c r="T4" s="13" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>238</v>
+        <v>162</v>
       </c>
       <c r="V4" s="14">
         <v>45900</v>
@@ -3586,133 +3595,133 @@
     </row>
     <row r="5" spans="1:23">
       <c r="B5" s="11" t="s">
-        <v>276</v>
+        <v>236</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>277</v>
+        <v>237</v>
       </c>
       <c r="D5" s="2">
-        <v>69.39</v>
+        <v>6.08</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>275</v>
+        <v>160</v>
       </c>
       <c r="F5" s="15">
-        <v>0.15518819500348435</v>
+        <v>0.16112633203079096</v>
       </c>
       <c r="G5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$10</f>
-        <v>3.7788195003484348E-2</v>
+        <v>4.372633203079096E-2</v>
       </c>
       <c r="H5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$11</f>
-        <v>0.12068819500348435</v>
+        <v>0.12662633203079096</v>
       </c>
       <c r="I5" s="15">
-        <v>0</v>
+        <v>0.16112633203079096</v>
       </c>
       <c r="J5" s="2">
-        <v>49.746673136282389</v>
+        <v>4.428921836807783</v>
       </c>
       <c r="K5" s="2">
-        <v>90.751910880412424</v>
+        <v>7.9670026289547851</v>
       </c>
       <c r="L5" s="2">
-        <v>62.307286389127562</v>
+        <v>5.5414713233942736</v>
       </c>
       <c r="M5" s="86">
-        <v>84.017562490801396</v>
+        <v>7.4633845319646834</v>
       </c>
       <c r="N5" s="4">
-        <v>7.6091679799215661E-2</v>
+        <v>0.12729200739087043</v>
       </c>
       <c r="O5" s="4">
-        <v>6.6969303934284477E-2</v>
+        <v>7.2687419474340292E-2</v>
       </c>
       <c r="P5" s="15">
-        <v>0.30279158651211824</v>
+        <v>0.61007460831657279</v>
       </c>
       <c r="Q5" s="15">
-        <v>7.7640983998987034E-4</v>
+        <v>0.16360901428944893</v>
       </c>
       <c r="R5" s="92">
-        <v>3.8209153156820415E-3</v>
+        <v>1.1309485990394448</v>
       </c>
       <c r="S5" s="86">
-        <v>15.284602440692964</v>
+        <v>-3.8097920812266781</v>
       </c>
       <c r="T5" s="13" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="U5" s="11" t="s">
-        <v>162</v>
+        <v>238</v>
       </c>
       <c r="V5" s="14">
         <v>45900</v>
       </c>
       <c r="W5" s="11" t="s">
-        <v>247</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:23">
       <c r="B6" s="11" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="D6" s="2">
-        <v>21.15</v>
+        <v>69.39</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="F6" s="15">
-        <v>0.14021163259405034</v>
+        <v>0.15518819500348435</v>
       </c>
       <c r="G6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$10</f>
-        <v>2.2811632594050335E-2</v>
+        <v>3.7788195003484348E-2</v>
       </c>
       <c r="H6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$11</f>
-        <v>0.10571163259405034</v>
+        <v>0.12068819500348435</v>
       </c>
       <c r="I6" s="15">
         <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>14.418941896437474</v>
+        <v>49.746673136282389</v>
       </c>
       <c r="K6" s="2">
-        <v>29.309951346473134</v>
+        <v>90.751910880412424</v>
       </c>
       <c r="L6" s="2">
-        <v>18.21218480698677</v>
+        <v>62.307286389127562</v>
       </c>
       <c r="M6" s="86">
-        <v>24.796949133193245</v>
+        <v>84.017562490801396</v>
       </c>
       <c r="N6" s="4">
-        <v>0.21555373746279879</v>
+        <v>7.6091679799215661E-2</v>
       </c>
       <c r="O6" s="4">
-        <v>2.8066193853427897E-2</v>
+        <v>6.6969303934284477E-2</v>
       </c>
       <c r="P6" s="15">
-        <v>1.4851905363915479</v>
+        <v>0.30279158651211824</v>
       </c>
       <c r="Q6" s="15">
-        <v>0.95241105291674188</v>
+        <v>7.7640983998987034E-4</v>
       </c>
       <c r="R6" s="92">
-        <v>4.0148803043206254</v>
+        <v>3.8209153156820415E-3</v>
       </c>
       <c r="S6" s="86">
-        <v>-38.360607814419353</v>
+        <v>15.284602440692964</v>
       </c>
       <c r="T6" s="13" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="U6" s="11" t="s">
         <v>162</v>
@@ -3726,133 +3735,133 @@
     </row>
     <row r="7" spans="1:23">
       <c r="B7" s="11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D7" s="2">
-        <v>55.75</v>
+        <v>21.15</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>160</v>
+        <v>253</v>
       </c>
       <c r="F7" s="15">
-        <v>0.13796564912031539</v>
+        <v>0.14021163259405034</v>
       </c>
       <c r="G7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$10</f>
-        <v>2.0565649120315388E-2</v>
+        <v>2.2811632594050335E-2</v>
       </c>
       <c r="H7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$11</f>
-        <v>0.10346564912031539</v>
+        <v>0.10571163259405034</v>
       </c>
       <c r="I7" s="15">
-        <v>0.13796564912031539</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>38.67449654927848</v>
+        <v>14.418941896437474</v>
       </c>
       <c r="K7" s="2">
-        <v>64.818448718764827</v>
+        <v>29.309951346473134</v>
       </c>
       <c r="L7" s="2">
-        <v>48.148365693729644</v>
+        <v>18.21218480698677</v>
       </c>
       <c r="M7" s="86">
-        <v>64.469262649530066</v>
+        <v>24.796949133193245</v>
       </c>
       <c r="N7" s="4">
-        <v>9.4419233289180268E-2</v>
+        <v>0.21555373746279879</v>
       </c>
       <c r="O7" s="4">
-        <v>9.0582600896860987E-2</v>
+        <v>2.8066193853427897E-2</v>
       </c>
       <c r="P7" s="15">
-        <v>1.2907496012759174</v>
+        <v>1.4851905363915479</v>
       </c>
       <c r="Q7" s="15">
-        <v>0.24768740031897937</v>
+        <v>0.95241105291674188</v>
       </c>
       <c r="R7" s="92">
-        <v>0.73855199466278643</v>
+        <v>4.0148803043206254</v>
       </c>
       <c r="S7" s="86">
-        <v>-2.6472954415279868</v>
+        <v>-38.360607814419353</v>
       </c>
       <c r="T7" s="13" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="U7" s="11" t="s">
         <v>162</v>
       </c>
       <c r="V7" s="14">
-        <v>45808</v>
+        <v>45900</v>
       </c>
       <c r="W7" s="11" t="s">
-        <v>163</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="1:23">
       <c r="B8" s="11" t="s">
-        <v>158</v>
+        <v>249</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>159</v>
+        <v>250</v>
       </c>
       <c r="D8" s="2">
-        <v>17.899999999999999</v>
+        <v>55.75</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F8" s="15">
-        <v>0.11920444715894019</v>
+        <v>0.13796564912031539</v>
       </c>
       <c r="G8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$10</f>
-        <v>1.8044471589401812E-3</v>
+        <v>2.0565649120315388E-2</v>
       </c>
       <c r="H8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$11</f>
-        <v>8.4704447158940183E-2</v>
+        <v>0.10346564912031539</v>
       </c>
       <c r="I8" s="15">
-        <v>0.11353438568563534</v>
+        <v>3.5057368663751309E-2</v>
       </c>
       <c r="J8" s="2">
-        <v>11.804906901225705</v>
+        <v>38.67449654927848</v>
       </c>
       <c r="K8" s="2">
-        <v>20.508980461992877</v>
+        <v>64.818448718764827</v>
       </c>
       <c r="L8" s="2">
-        <v>14.733437767356989</v>
+        <v>48.148365693729644</v>
       </c>
       <c r="M8" s="86">
-        <v>19.785541823839793</v>
+        <v>64.469262649530066</v>
       </c>
       <c r="N8" s="4">
-        <v>9.6535531808359179E-2</v>
+        <v>9.4419233289180268E-2</v>
       </c>
       <c r="O8" s="4">
-        <v>7.5977653631284933E-2</v>
+        <v>9.0582600896860987E-2</v>
       </c>
       <c r="P8" s="15">
-        <v>0.31018327415220487</v>
+        <v>1.2907496012759174</v>
       </c>
       <c r="Q8" s="15">
-        <v>0.15818859882129041</v>
+        <v>0.24768740031897937</v>
       </c>
       <c r="R8" s="92">
-        <v>1.4550387206421544</v>
+        <v>0.73855199466278643</v>
       </c>
       <c r="S8" s="86">
-        <v>5.8696003638854428</v>
+        <v>-2.6472954415279868</v>
       </c>
       <c r="T8" s="13" t="s">
-        <v>161</v>
+        <v>246</v>
       </c>
       <c r="U8" s="11" t="s">
         <v>162</v>
@@ -3866,276 +3875,276 @@
     </row>
     <row r="9" spans="1:23">
       <c r="B9" s="11" t="s">
-        <v>240</v>
+        <v>158</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>241</v>
+        <v>159</v>
       </c>
       <c r="D9" s="2">
-        <v>54</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F9" s="15">
-        <v>0.11184849157270471</v>
+        <v>0.11920444715894019</v>
       </c>
       <c r="G9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$10</f>
-        <v>-5.551508427295293E-3</v>
+        <v>1.8044471589401812E-3</v>
       </c>
       <c r="H9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$11</f>
-        <v>7.7348491572704708E-2</v>
+        <v>8.4704447158940183E-2</v>
       </c>
       <c r="I9" s="15">
         <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>34.381875852171149</v>
+        <v>11.804906901225705</v>
       </c>
       <c r="K9" s="2">
-        <v>67.361539432485785</v>
+        <v>20.508980461992877</v>
       </c>
       <c r="L9" s="2">
-        <v>43.298516914573895</v>
+        <v>14.733437767356989</v>
       </c>
       <c r="M9" s="86">
-        <v>58.754189493018607</v>
+        <v>19.785541823839793</v>
       </c>
       <c r="N9" s="4">
-        <v>4.1955491566384277E-2</v>
+        <v>9.6535531808359179E-2</v>
       </c>
       <c r="O9" s="4">
-        <v>3.7944127980758587E-2</v>
+        <v>7.5977653631284933E-2</v>
       </c>
       <c r="P9" s="15">
-        <v>0.72207550313588764</v>
+        <v>0.31018327415220487</v>
       </c>
       <c r="Q9" s="15">
-        <v>9.5579625064196368E-3</v>
+        <v>0.15818859882129041</v>
       </c>
       <c r="R9" s="92">
-        <v>7.3592411949940734E-2</v>
+        <v>1.4550387206421544</v>
       </c>
       <c r="S9" s="86">
-        <v>1.334506858271689</v>
+        <v>5.8696003638854428</v>
       </c>
       <c r="T9" s="13" t="s">
-        <v>242</v>
+        <v>161</v>
       </c>
       <c r="U9" s="11" t="s">
         <v>162</v>
       </c>
       <c r="V9" s="14">
-        <v>45900</v>
+        <v>45808</v>
       </c>
       <c r="W9" s="11" t="s">
-        <v>247</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:23">
       <c r="B10" s="11" t="s">
-        <v>164</v>
+        <v>240</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>165</v>
+        <v>241</v>
       </c>
       <c r="D10" s="2">
-        <v>8.1</v>
+        <v>54</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F10" s="15">
-        <v>0.11083350655450119</v>
+        <v>0.11184849157270471</v>
       </c>
       <c r="G10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$10</f>
-        <v>-6.5664934454988111E-3</v>
+        <v>-5.551508427295293E-3</v>
       </c>
       <c r="H10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$11</f>
-        <v>7.633350655450119E-2</v>
+        <v>7.7348491572704708E-2</v>
       </c>
       <c r="I10" s="15">
         <v>0</v>
       </c>
       <c r="J10" s="2">
-        <v>5.2239462882061574</v>
+        <v>34.381875852171149</v>
       </c>
       <c r="K10" s="2">
-        <v>9.1628099951889297</v>
+        <v>67.361539432485785</v>
       </c>
       <c r="L10" s="2">
-        <v>6.5243113398084081</v>
+        <v>43.298516914573895</v>
       </c>
       <c r="M10" s="86">
-        <v>8.7684502451266084</v>
+        <v>58.754189493018607</v>
       </c>
       <c r="N10" s="4">
-        <v>3.8135601479291979E-2</v>
+        <v>4.1955491566384277E-2</v>
       </c>
       <c r="O10" s="4">
-        <v>7.160493827160494E-2</v>
+        <v>3.7944127980758587E-2</v>
       </c>
       <c r="P10" s="15">
-        <v>8.3114411724224596E-2</v>
+        <v>0.72207550313588764</v>
       </c>
       <c r="Q10" s="15">
-        <v>1.8509098960546238E-2</v>
+        <v>9.5579625064196368E-3</v>
       </c>
       <c r="R10" s="92">
-        <v>1.1933697905849452</v>
+        <v>7.3592411949940734E-2</v>
       </c>
       <c r="S10" s="86">
-        <v>11.511512740854835</v>
+        <v>1.334506858271689</v>
       </c>
       <c r="T10" s="16" t="s">
-        <v>166</v>
+        <v>242</v>
       </c>
       <c r="U10" s="11" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="V10" s="14">
         <v>45900</v>
       </c>
       <c r="W10" s="11" t="s">
-        <v>163</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="1:23">
       <c r="B11" s="11" t="s">
-        <v>244</v>
+        <v>164</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>245</v>
+        <v>165</v>
       </c>
       <c r="D11" s="2">
-        <v>14.3</v>
+        <v>8.1</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F11" s="15">
-        <v>0.1090060893695004</v>
+        <v>0.11083350655450119</v>
       </c>
       <c r="G11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$10</f>
-        <v>-8.3939106304996014E-3</v>
+        <v>-6.5664934454988111E-3</v>
       </c>
       <c r="H11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$11</f>
-        <v>7.45060893695004E-2</v>
+        <v>7.633350655450119E-2</v>
       </c>
       <c r="I11" s="15">
         <v>0</v>
       </c>
       <c r="J11" s="2">
-        <v>9.1251344157607761</v>
+        <v>5.2239462882061574</v>
       </c>
       <c r="K11" s="2">
-        <v>16.718616112226428</v>
+        <v>9.1628099951889297</v>
       </c>
       <c r="L11" s="2">
-        <v>11.432798659390293</v>
+        <v>6.5243113398084081</v>
       </c>
       <c r="M11" s="86">
-        <v>15.422137352615858</v>
+        <v>8.7684502451266084</v>
       </c>
       <c r="N11" s="4">
-        <v>0.10749746672561937</v>
+        <v>3.8135601479291979E-2</v>
       </c>
       <c r="O11" s="4">
-        <v>5.8350495104895095E-2</v>
+        <v>7.160493827160494E-2</v>
       </c>
       <c r="P11" s="15">
-        <v>2.2875080906148866</v>
+        <v>8.3114411724224596E-2</v>
       </c>
       <c r="Q11" s="15">
-        <v>1.5035598705501618</v>
+        <v>1.8509098960546238E-2</v>
       </c>
       <c r="R11" s="92">
-        <v>4.1998196571663646</v>
+        <v>1.1933697905849452</v>
       </c>
       <c r="S11" s="86">
-        <v>-12.151746556489819</v>
+        <v>11.511512740854835</v>
       </c>
       <c r="T11" s="13" t="s">
-        <v>246</v>
+        <v>166</v>
       </c>
       <c r="U11" s="11" t="s">
-        <v>248</v>
+        <v>167</v>
       </c>
       <c r="V11" s="14">
         <v>45900</v>
       </c>
       <c r="W11" s="11" t="s">
-        <v>247</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:23">
       <c r="B12" s="11" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="D12" s="2">
-        <v>28.23</v>
+        <v>14.3</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>253</v>
+        <v>160</v>
       </c>
       <c r="F12" s="15">
-        <v>0.10191457699731421</v>
+        <v>0.1090060893695004</v>
       </c>
       <c r="G12" s="15">
         <f>F12 - Portfolio_Mgmt!$C$10</f>
-        <v>-1.5485423002685794E-2</v>
+        <v>-8.3939106304996014E-3</v>
       </c>
       <c r="H12" s="15">
         <f>F12 - Portfolio_Mgmt!$C$11</f>
-        <v>6.7414576997314207E-2</v>
+        <v>7.45060893695004E-2</v>
       </c>
       <c r="I12" s="15">
         <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>17.682685147645955</v>
+        <v>9.1251344157607761</v>
       </c>
       <c r="K12" s="2">
-        <v>32.464859269378167</v>
+        <v>16.718616112226428</v>
       </c>
       <c r="L12" s="2">
-        <v>22.157904669779033</v>
+        <v>11.432798659390293</v>
       </c>
       <c r="M12" s="86">
-        <v>29.895007167811503</v>
+        <v>15.422137352615858</v>
       </c>
       <c r="N12" s="4">
-        <v>8.9945710498866363E-2</v>
+        <v>0.10749746672561937</v>
       </c>
       <c r="O12" s="4">
-        <v>5.6677293659227773E-2</v>
+        <v>5.8350495104895095E-2</v>
       </c>
       <c r="P12" s="15">
-        <v>0.78990369994931575</v>
+        <v>2.2875080906148866</v>
       </c>
       <c r="Q12" s="15">
-        <v>0.40281804358844397</v>
+        <v>1.5035598705501618</v>
       </c>
       <c r="R12" s="92">
-        <v>3.955391512509995</v>
+        <v>4.1998196571663646</v>
       </c>
       <c r="S12" s="86">
-        <v>-26.938493611476797</v>
+        <v>-12.151746556489819</v>
       </c>
       <c r="T12" s="13" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="U12" s="11" t="s">
-        <v>162</v>
+        <v>248</v>
       </c>
       <c r="V12" s="14">
         <v>45900</v>
@@ -4146,153 +4155,213 @@
     </row>
     <row r="13" spans="1:23">
       <c r="B13" s="11" t="s">
-        <v>168</v>
+        <v>255</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>169</v>
+        <v>256</v>
       </c>
       <c r="D13" s="2">
-        <v>2.35</v>
+        <v>28.23</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>160</v>
+        <v>253</v>
       </c>
       <c r="F13" s="15">
-        <v>9.5546776071535167E-2</v>
+        <v>0.10191457699731421</v>
       </c>
       <c r="G13" s="15">
         <f>F13 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.1853223928464838E-2</v>
+        <v>-1.5485423002685794E-2</v>
       </c>
       <c r="H13" s="15">
         <f>F13 - Portfolio_Mgmt!$C$11</f>
-        <v>6.1046776071535164E-2</v>
+        <v>6.7414576997314207E-2</v>
       </c>
       <c r="I13" s="15">
         <v>0</v>
       </c>
       <c r="J13" s="2">
-        <v>1.442374867722968</v>
+        <v>17.682685147645955</v>
       </c>
       <c r="K13" s="2">
-        <v>2.7155321746611896</v>
+        <v>32.464859269378167</v>
       </c>
       <c r="L13" s="2">
-        <v>1.8108383615725383</v>
+        <v>22.157904669779033</v>
       </c>
       <c r="M13" s="2">
-        <v>2.4485007089485338</v>
+        <v>29.895007167811503</v>
       </c>
       <c r="N13" s="4">
-        <v>3.5197892699834928E-2</v>
+        <v>8.9945710498866363E-2</v>
       </c>
       <c r="O13" s="4">
-        <v>4.8351240838924094E-2</v>
+        <v>5.6677293659227773E-2</v>
       </c>
       <c r="P13" s="15">
-        <v>0.20351769929714394</v>
+        <v>0.78990369994931575</v>
       </c>
       <c r="Q13" s="15">
-        <v>1.0763175939415467E-2</v>
+        <v>0.40281804358844397</v>
       </c>
       <c r="R13" s="92">
-        <v>0.29882156160837919</v>
+        <v>3.955391512509995</v>
       </c>
       <c r="S13" s="86">
-        <v>1.8775728111399408</v>
+        <v>-26.938493611476797</v>
       </c>
       <c r="T13" s="13" t="s">
-        <v>170</v>
+        <v>257</v>
       </c>
       <c r="U13" s="11" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="V13" s="14">
         <v>45900</v>
       </c>
       <c r="W13" s="11" t="s">
-        <v>163</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14" spans="1:23">
       <c r="B14" s="11" t="s">
-        <v>273</v>
+        <v>168</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>274</v>
+        <v>169</v>
       </c>
       <c r="D14" s="2">
-        <v>57.4</v>
+        <v>2.35</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>275</v>
+        <v>160</v>
       </c>
       <c r="F14" s="15">
-        <v>9.0634582120934004E-2</v>
+        <v>9.5546776071535167E-2</v>
       </c>
       <c r="G14" s="15">
         <f>F14 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.6765417879066E-2</v>
+        <v>-2.1853223928464838E-2</v>
       </c>
       <c r="H14" s="15">
         <f>F14 - Portfolio_Mgmt!$C$11</f>
-        <v>5.6134582120934001E-2</v>
+        <v>6.1046776071535164E-2</v>
       </c>
       <c r="I14" s="15">
         <v>0</v>
       </c>
       <c r="J14" s="2">
+        <v>1.442374867722968</v>
+      </c>
+      <c r="K14" s="2">
+        <v>2.7155321746611896</v>
+      </c>
+      <c r="L14" s="2">
+        <v>1.8108383615725383</v>
+      </c>
+      <c r="M14" s="2">
+        <v>2.4485007089485338</v>
+      </c>
+      <c r="N14" s="4">
+        <v>3.5197892699834928E-2</v>
+      </c>
+      <c r="O14" s="4">
+        <v>4.8351240838924094E-2</v>
+      </c>
+      <c r="P14" s="15">
+        <v>0.20351769929714394</v>
+      </c>
+      <c r="Q14" s="15">
+        <v>1.0763175939415467E-2</v>
+      </c>
+      <c r="R14" s="92">
+        <v>0.29882156160837919</v>
+      </c>
+      <c r="S14" s="86">
+        <v>1.8775728111399408</v>
+      </c>
+      <c r="T14" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="U14" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="V14" s="14">
+        <v>45900</v>
+      </c>
+      <c r="W14" s="11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23">
+      <c r="B15" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="D15" s="2">
+        <v>57.4</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="F15" s="15">
+        <v>9.0634582120934004E-2</v>
+      </c>
+      <c r="G15" s="15">
+        <f>F15 - Portfolio_Mgmt!$C$10</f>
+        <v>-2.6765417879066E-2</v>
+      </c>
+      <c r="H15" s="15">
+        <f>F15 - Portfolio_Mgmt!$C$11</f>
+        <v>5.6134582120934001E-2</v>
+      </c>
+      <c r="I15" s="15">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
         <v>34.669224296258527</v>
       </c>
-      <c r="K14" s="2">
+      <c r="K15" s="2">
         <v>66.592285778879997</v>
       </c>
-      <c r="L14" s="2">
+      <c r="L15" s="2">
         <v>43.592757973888887</v>
       </c>
-      <c r="M14" s="2">
+      <c r="M15" s="2">
         <v>59.048136223898794</v>
       </c>
-      <c r="N14" s="4">
+      <c r="N15" s="4">
         <v>8.005411568167814E-2</v>
       </c>
-      <c r="O14" s="4">
+      <c r="O15" s="4">
         <v>4.1811846689895467E-2</v>
       </c>
-      <c r="P14" s="15">
+      <c r="P15" s="15">
         <v>3.4701988818540461</v>
       </c>
-      <c r="Q14" s="15">
+      <c r="Q15" s="15">
         <v>5.0341856510546588E-2</v>
       </c>
-      <c r="R14" s="92">
+      <c r="R15" s="92">
         <v>3.9546057100127742E-2</v>
       </c>
-      <c r="S14" s="86">
+      <c r="S15" s="86">
         <v>-13.312996389940134</v>
       </c>
-      <c r="T14" s="13" t="s">
+      <c r="T15" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="U14" s="11" t="s">
+      <c r="U15" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="V14" s="14">
+      <c r="V15" s="14">
         <v>45716</v>
       </c>
-      <c r="W14" s="11" t="s">
+      <c r="W15" s="11" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="15" spans="1:23">
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="E15" s="12"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="T15" s="13"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="14"/>
     </row>
     <row r="16" spans="1:23">
       <c r="B16" s="11"/>
@@ -6723,7 +6792,7 @@
       </c>
       <c r="H4" s="73">
         <f>VLOOKUP(B4,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.11353438568563534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6833,7 +6902,7 @@
       </c>
       <c r="H9" s="89">
         <f>SUM(H4:H7)</f>
-        <v>0.46203435087968459</v>
+        <v>0.34849996519404924</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -6851,30 +6920,31 @@
     </row>
     <row r="12" spans="1:8">
       <c r="B12" s="78" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="C12" s="75">
         <f>VLOOKUP(B12,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>15.44</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="D12" s="74" t="str">
         <f>VLOOKUP(B12,Opportunities!B$3:E$12,4,FALSE)</f>
         <v>HKD</v>
       </c>
       <c r="E12" s="71">
-        <v>6000</v>
+        <f>500*100</f>
+        <v>50000</v>
       </c>
       <c r="F12" s="76">
         <f>C12*E12</f>
-        <v>92640</v>
+        <v>57499.999999999993</v>
       </c>
       <c r="G12" s="73">
         <f>F12/$F$9</f>
-        <v>0.10356906094321498</v>
+        <v>6.4283473707198405E-2</v>
       </c>
       <c r="H12" s="73">
         <f>VLOOKUP(B12,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.18737363316325828</v>
+        <v>0.21644266614219942</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -6896,11 +6966,11 @@
       </c>
       <c r="F14" s="81">
         <f>F3-F12</f>
-        <v>258755.62</v>
+        <v>293895.62</v>
       </c>
       <c r="G14" s="89">
         <f t="shared" ref="G14" si="0">F14/$F$9</f>
-        <v>0.28928191469321435</v>
+        <v>0.3285675019292309</v>
       </c>
       <c r="H14" s="89">
         <f>Portfolio_Mgmt!E61</f>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5CBE852-C440-45D2-9783-7F0B53670D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EDBAFF2-9DFC-4E18-83E9-4C9259724A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="281">
   <si>
     <t>Name</t>
   </si>
@@ -2203,17 +2203,17 @@
     <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2616,12 +2616,12 @@
       <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="95" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="94"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="20" t="s">
@@ -2633,12 +2633,12 @@
       <c r="C6" s="61"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" s="94" t="s">
+      <c r="B7" s="95" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="23" t="s">
@@ -2727,12 +2727,12 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
-      <c r="B24" s="94" t="s">
+      <c r="B24" s="95" t="s">
         <v>220</v>
       </c>
-      <c r="C24" s="94"/>
-      <c r="D24" s="94"/>
-      <c r="E24" s="94"/>
+      <c r="C24" s="95"/>
+      <c r="D24" s="95"/>
+      <c r="E24" s="95"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
@@ -2832,20 +2832,20 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="B39" s="94" t="s">
+      <c r="B39" s="95" t="s">
         <v>156</v>
       </c>
-      <c r="C39" s="94"/>
-      <c r="D39" s="94"/>
-      <c r="E39" s="94"/>
+      <c r="C39" s="95"/>
+      <c r="D39" s="95"/>
+      <c r="E39" s="95"/>
     </row>
     <row r="40" spans="1:5" ht="46.6" customHeight="1">
-      <c r="B40" s="94" t="s">
+      <c r="B40" s="95" t="s">
         <v>235</v>
       </c>
-      <c r="C40" s="94"/>
-      <c r="D40" s="94"/>
-      <c r="E40" s="94"/>
+      <c r="C40" s="95"/>
+      <c r="D40" s="95"/>
+      <c r="E40" s="95"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="21" t="s">
@@ -2857,12 +2857,12 @@
       <c r="E42" s="21"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="B44" s="94" t="s">
+      <c r="B44" s="95" t="s">
         <v>208</v>
       </c>
-      <c r="C44" s="94"/>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="23" t="s">
@@ -3047,12 +3047,12 @@
       <c r="E69" s="21"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="B71" s="94" t="s">
+      <c r="B71" s="95" t="s">
         <v>196</v>
       </c>
-      <c r="C71" s="94"/>
-      <c r="D71" s="94"/>
-      <c r="E71" s="94"/>
+      <c r="C71" s="95"/>
+      <c r="D71" s="95"/>
+      <c r="E71" s="95"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="28" t="s">
@@ -3114,36 +3114,36 @@
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="B85" s="97" t="s">
+      <c r="B85" s="96" t="s">
         <v>192</v>
       </c>
-      <c r="C85" s="97"/>
-      <c r="D85" s="97"/>
-      <c r="E85" s="97"/>
+      <c r="C85" s="96"/>
+      <c r="D85" s="96"/>
+      <c r="E85" s="96"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="B86" s="96" t="s">
+      <c r="B86" s="94" t="s">
         <v>190</v>
       </c>
-      <c r="C86" s="96"/>
-      <c r="D86" s="96"/>
-      <c r="E86" s="96"/>
+      <c r="C86" s="94"/>
+      <c r="D86" s="94"/>
+      <c r="E86" s="94"/>
     </row>
     <row r="87" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B87" s="94" t="s">
+      <c r="B87" s="95" t="s">
         <v>189</v>
       </c>
-      <c r="C87" s="94"/>
-      <c r="D87" s="94"/>
-      <c r="E87" s="94"/>
+      <c r="C87" s="95"/>
+      <c r="D87" s="95"/>
+      <c r="E87" s="95"/>
     </row>
     <row r="88" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B88" s="94" t="s">
+      <c r="B88" s="95" t="s">
         <v>225</v>
       </c>
-      <c r="C88" s="94"/>
-      <c r="D88" s="94"/>
-      <c r="E88" s="94"/>
+      <c r="C88" s="95"/>
+      <c r="D88" s="95"/>
+      <c r="E88" s="95"/>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="24" t="s">
@@ -3176,12 +3176,12 @@
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="B97" s="95" t="s">
+      <c r="B97" s="97" t="s">
         <v>211</v>
       </c>
-      <c r="C97" s="95"/>
-      <c r="D97" s="95"/>
-      <c r="E97" s="95"/>
+      <c r="C97" s="97"/>
+      <c r="D97" s="97"/>
+      <c r="E97" s="97"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
@@ -3189,20 +3189,20 @@
       </c>
     </row>
     <row r="100" spans="1:5" ht="12.4">
-      <c r="B100" s="95" t="s">
+      <c r="B100" s="97" t="s">
         <v>212</v>
       </c>
-      <c r="C100" s="95"/>
-      <c r="D100" s="95"/>
-      <c r="E100" s="95"/>
+      <c r="C100" s="97"/>
+      <c r="D100" s="97"/>
+      <c r="E100" s="97"/>
     </row>
     <row r="101" spans="1:5" ht="58.5" customHeight="1">
-      <c r="B101" s="94" t="s">
+      <c r="B101" s="95" t="s">
         <v>219</v>
       </c>
-      <c r="C101" s="94"/>
-      <c r="D101" s="94"/>
-      <c r="E101" s="94"/>
+      <c r="C101" s="95"/>
+      <c r="D101" s="95"/>
+      <c r="E101" s="95"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="28" t="s">
@@ -3258,12 +3258,12 @@
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B114" s="94" t="s">
+      <c r="B114" s="95" t="s">
         <v>217</v>
       </c>
-      <c r="C114" s="94"/>
-      <c r="D114" s="94"/>
-      <c r="E114" s="94"/>
+      <c r="C114" s="95"/>
+      <c r="D114" s="95"/>
+      <c r="E114" s="95"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="21" t="s">
@@ -3296,6 +3296,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
     <mergeCell ref="B86:E86"/>
     <mergeCell ref="B71:E71"/>
     <mergeCell ref="B85:E85"/>
@@ -3305,12 +3311,6 @@
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6763,8 +6763,9 @@
         <f>F3/$F$9</f>
         <v>0.39285097563642929</v>
       </c>
-      <c r="H3" s="91" t="s">
-        <v>233</v>
+      <c r="H3" s="91">
+        <f>Portfolio_Mgmt!E61</f>
+        <v>0.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -7067,15 +7068,15 @@
       <c r="B5" s="106" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="95"/>
-      <c r="D5" s="95"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="97"/>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="106" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="97"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EDBAFF2-9DFC-4E18-83E9-4C9259724A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D2552F8-7997-4FC2-9034-B98FE0A0A36D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -2203,17 +2203,17 @@
     <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2249,7 +2249,140 @@
     <cellStyle name="常规 2" xfId="3" xr:uid="{32ADA8AA-F280-4250-ABBF-7E6B9CB799DC}"/>
     <cellStyle name="超链接" xfId="2" builtinId="8"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="22">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2616,12 +2749,12 @@
       <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B4" s="95" t="s">
+      <c r="B4" s="94" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="20" t="s">
@@ -2633,12 +2766,12 @@
       <c r="C6" s="61"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" s="95" t="s">
+      <c r="B7" s="94" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="95"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="94"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="23" t="s">
@@ -2727,12 +2860,12 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
-      <c r="B24" s="95" t="s">
+      <c r="B24" s="94" t="s">
         <v>220</v>
       </c>
-      <c r="C24" s="95"/>
-      <c r="D24" s="95"/>
-      <c r="E24" s="95"/>
+      <c r="C24" s="94"/>
+      <c r="D24" s="94"/>
+      <c r="E24" s="94"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
@@ -2832,20 +2965,20 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="B39" s="95" t="s">
+      <c r="B39" s="94" t="s">
         <v>156</v>
       </c>
-      <c r="C39" s="95"/>
-      <c r="D39" s="95"/>
-      <c r="E39" s="95"/>
+      <c r="C39" s="94"/>
+      <c r="D39" s="94"/>
+      <c r="E39" s="94"/>
     </row>
     <row r="40" spans="1:5" ht="46.6" customHeight="1">
-      <c r="B40" s="95" t="s">
+      <c r="B40" s="94" t="s">
         <v>235</v>
       </c>
-      <c r="C40" s="95"/>
-      <c r="D40" s="95"/>
-      <c r="E40" s="95"/>
+      <c r="C40" s="94"/>
+      <c r="D40" s="94"/>
+      <c r="E40" s="94"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="21" t="s">
@@ -2857,12 +2990,12 @@
       <c r="E42" s="21"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="B44" s="95" t="s">
+      <c r="B44" s="94" t="s">
         <v>208</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="94"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="23" t="s">
@@ -3047,12 +3180,12 @@
       <c r="E69" s="21"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="B71" s="95" t="s">
+      <c r="B71" s="94" t="s">
         <v>196</v>
       </c>
-      <c r="C71" s="95"/>
-      <c r="D71" s="95"/>
-      <c r="E71" s="95"/>
+      <c r="C71" s="94"/>
+      <c r="D71" s="94"/>
+      <c r="E71" s="94"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="28" t="s">
@@ -3114,36 +3247,36 @@
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="B85" s="96" t="s">
+      <c r="B85" s="97" t="s">
         <v>192</v>
       </c>
-      <c r="C85" s="96"/>
-      <c r="D85" s="96"/>
-      <c r="E85" s="96"/>
+      <c r="C85" s="97"/>
+      <c r="D85" s="97"/>
+      <c r="E85" s="97"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="B86" s="94" t="s">
+      <c r="B86" s="96" t="s">
         <v>190</v>
       </c>
-      <c r="C86" s="94"/>
-      <c r="D86" s="94"/>
-      <c r="E86" s="94"/>
+      <c r="C86" s="96"/>
+      <c r="D86" s="96"/>
+      <c r="E86" s="96"/>
     </row>
     <row r="87" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B87" s="95" t="s">
+      <c r="B87" s="94" t="s">
         <v>189</v>
       </c>
-      <c r="C87" s="95"/>
-      <c r="D87" s="95"/>
-      <c r="E87" s="95"/>
+      <c r="C87" s="94"/>
+      <c r="D87" s="94"/>
+      <c r="E87" s="94"/>
     </row>
     <row r="88" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B88" s="95" t="s">
+      <c r="B88" s="94" t="s">
         <v>225</v>
       </c>
-      <c r="C88" s="95"/>
-      <c r="D88" s="95"/>
-      <c r="E88" s="95"/>
+      <c r="C88" s="94"/>
+      <c r="D88" s="94"/>
+      <c r="E88" s="94"/>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="24" t="s">
@@ -3176,12 +3309,12 @@
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="B97" s="97" t="s">
+      <c r="B97" s="95" t="s">
         <v>211</v>
       </c>
-      <c r="C97" s="97"/>
-      <c r="D97" s="97"/>
-      <c r="E97" s="97"/>
+      <c r="C97" s="95"/>
+      <c r="D97" s="95"/>
+      <c r="E97" s="95"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
@@ -3189,20 +3322,20 @@
       </c>
     </row>
     <row r="100" spans="1:5" ht="12.4">
-      <c r="B100" s="97" t="s">
+      <c r="B100" s="95" t="s">
         <v>212</v>
       </c>
-      <c r="C100" s="97"/>
-      <c r="D100" s="97"/>
-      <c r="E100" s="97"/>
+      <c r="C100" s="95"/>
+      <c r="D100" s="95"/>
+      <c r="E100" s="95"/>
     </row>
     <row r="101" spans="1:5" ht="58.5" customHeight="1">
-      <c r="B101" s="95" t="s">
+      <c r="B101" s="94" t="s">
         <v>219</v>
       </c>
-      <c r="C101" s="95"/>
-      <c r="D101" s="95"/>
-      <c r="E101" s="95"/>
+      <c r="C101" s="94"/>
+      <c r="D101" s="94"/>
+      <c r="E101" s="94"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="28" t="s">
@@ -3258,12 +3391,12 @@
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B114" s="95" t="s">
+      <c r="B114" s="94" t="s">
         <v>217</v>
       </c>
-      <c r="C114" s="95"/>
-      <c r="D114" s="95"/>
-      <c r="E114" s="95"/>
+      <c r="C114" s="94"/>
+      <c r="D114" s="94"/>
+      <c r="E114" s="94"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="21" t="s">
@@ -3296,12 +3429,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
     <mergeCell ref="B86:E86"/>
     <mergeCell ref="B71:E71"/>
     <mergeCell ref="B85:E85"/>
@@ -3311,6 +3438,12 @@
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6405,22 +6538,27 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="J3:J1048576">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="10" priority="3">
       <formula>J3&gt;D3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3:L1048576">
-    <cfRule type="expression" dxfId="1" priority="4">
+    <cfRule type="expression" dxfId="9" priority="6">
       <formula>L3&gt;D3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3:M1048576">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="8" priority="4">
       <formula>D3&gt;M3</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="V3:V1048576">
+    <cfRule type="expression" dxfId="7" priority="1">
+      <formula>V3&lt;TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="75" orientation="landscape" r:id="rId1"/>
+  <pageSetup scale="56" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7068,15 +7206,15 @@
       <c r="B5" s="106" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="95"/>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="106" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="97"/>
-      <c r="D6" s="97"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D2552F8-7997-4FC2-9034-B98FE0A0A36D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D988B6F-DFBA-42AE-A1FC-24FAB067448A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="283">
   <si>
     <t>Name</t>
   </si>
@@ -1628,6 +1628,12 @@
   </si>
   <si>
     <t>FIN_03</t>
+  </si>
+  <si>
+    <t>0398.HK</t>
+  </si>
+  <si>
+    <t>東方表行集團</t>
   </si>
 </sst>
 </file>
@@ -2203,17 +2209,17 @@
     <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2249,137 +2255,11 @@
     <cellStyle name="常规 2" xfId="3" xr:uid="{32ADA8AA-F280-4250-ABBF-7E6B9CB799DC}"/>
     <cellStyle name="超链接" xfId="2" builtinId="8"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2749,12 +2629,12 @@
       <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="95" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="94"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="20" t="s">
@@ -2766,12 +2646,12 @@
       <c r="C6" s="61"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" s="94" t="s">
+      <c r="B7" s="95" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="23" t="s">
@@ -2860,12 +2740,12 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
-      <c r="B24" s="94" t="s">
+      <c r="B24" s="95" t="s">
         <v>220</v>
       </c>
-      <c r="C24" s="94"/>
-      <c r="D24" s="94"/>
-      <c r="E24" s="94"/>
+      <c r="C24" s="95"/>
+      <c r="D24" s="95"/>
+      <c r="E24" s="95"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
@@ -2965,20 +2845,20 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="B39" s="94" t="s">
+      <c r="B39" s="95" t="s">
         <v>156</v>
       </c>
-      <c r="C39" s="94"/>
-      <c r="D39" s="94"/>
-      <c r="E39" s="94"/>
+      <c r="C39" s="95"/>
+      <c r="D39" s="95"/>
+      <c r="E39" s="95"/>
     </row>
     <row r="40" spans="1:5" ht="46.6" customHeight="1">
-      <c r="B40" s="94" t="s">
+      <c r="B40" s="95" t="s">
         <v>235</v>
       </c>
-      <c r="C40" s="94"/>
-      <c r="D40" s="94"/>
-      <c r="E40" s="94"/>
+      <c r="C40" s="95"/>
+      <c r="D40" s="95"/>
+      <c r="E40" s="95"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="21" t="s">
@@ -2990,12 +2870,12 @@
       <c r="E42" s="21"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="B44" s="94" t="s">
+      <c r="B44" s="95" t="s">
         <v>208</v>
       </c>
-      <c r="C44" s="94"/>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="23" t="s">
@@ -3180,12 +3060,12 @@
       <c r="E69" s="21"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="B71" s="94" t="s">
+      <c r="B71" s="95" t="s">
         <v>196</v>
       </c>
-      <c r="C71" s="94"/>
-      <c r="D71" s="94"/>
-      <c r="E71" s="94"/>
+      <c r="C71" s="95"/>
+      <c r="D71" s="95"/>
+      <c r="E71" s="95"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="28" t="s">
@@ -3247,36 +3127,36 @@
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="B85" s="97" t="s">
+      <c r="B85" s="96" t="s">
         <v>192</v>
       </c>
-      <c r="C85" s="97"/>
-      <c r="D85" s="97"/>
-      <c r="E85" s="97"/>
+      <c r="C85" s="96"/>
+      <c r="D85" s="96"/>
+      <c r="E85" s="96"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="B86" s="96" t="s">
+      <c r="B86" s="94" t="s">
         <v>190</v>
       </c>
-      <c r="C86" s="96"/>
-      <c r="D86" s="96"/>
-      <c r="E86" s="96"/>
+      <c r="C86" s="94"/>
+      <c r="D86" s="94"/>
+      <c r="E86" s="94"/>
     </row>
     <row r="87" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B87" s="94" t="s">
+      <c r="B87" s="95" t="s">
         <v>189</v>
       </c>
-      <c r="C87" s="94"/>
-      <c r="D87" s="94"/>
-      <c r="E87" s="94"/>
+      <c r="C87" s="95"/>
+      <c r="D87" s="95"/>
+      <c r="E87" s="95"/>
     </row>
     <row r="88" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B88" s="94" t="s">
+      <c r="B88" s="95" t="s">
         <v>225</v>
       </c>
-      <c r="C88" s="94"/>
-      <c r="D88" s="94"/>
-      <c r="E88" s="94"/>
+      <c r="C88" s="95"/>
+      <c r="D88" s="95"/>
+      <c r="E88" s="95"/>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="24" t="s">
@@ -3309,12 +3189,12 @@
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="B97" s="95" t="s">
+      <c r="B97" s="97" t="s">
         <v>211</v>
       </c>
-      <c r="C97" s="95"/>
-      <c r="D97" s="95"/>
-      <c r="E97" s="95"/>
+      <c r="C97" s="97"/>
+      <c r="D97" s="97"/>
+      <c r="E97" s="97"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
@@ -3322,20 +3202,20 @@
       </c>
     </row>
     <row r="100" spans="1:5" ht="12.4">
-      <c r="B100" s="95" t="s">
+      <c r="B100" s="97" t="s">
         <v>212</v>
       </c>
-      <c r="C100" s="95"/>
-      <c r="D100" s="95"/>
-      <c r="E100" s="95"/>
+      <c r="C100" s="97"/>
+      <c r="D100" s="97"/>
+      <c r="E100" s="97"/>
     </row>
     <row r="101" spans="1:5" ht="58.5" customHeight="1">
-      <c r="B101" s="94" t="s">
+      <c r="B101" s="95" t="s">
         <v>219</v>
       </c>
-      <c r="C101" s="94"/>
-      <c r="D101" s="94"/>
-      <c r="E101" s="94"/>
+      <c r="C101" s="95"/>
+      <c r="D101" s="95"/>
+      <c r="E101" s="95"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="28" t="s">
@@ -3383,7 +3263,7 @@
         <v>176</v>
       </c>
       <c r="C112" s="44">
-        <v>0.12655471362938422</v>
+        <v>0.12601445728348953</v>
       </c>
       <c r="D112" s="61" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
@@ -3391,12 +3271,12 @@
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B114" s="94" t="s">
+      <c r="B114" s="95" t="s">
         <v>217</v>
       </c>
-      <c r="C114" s="94"/>
-      <c r="D114" s="94"/>
-      <c r="E114" s="94"/>
+      <c r="C114" s="95"/>
+      <c r="D114" s="95"/>
+      <c r="E114" s="95"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="21" t="s">
@@ -3429,6 +3309,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
     <mergeCell ref="B86:E86"/>
     <mergeCell ref="B71:E71"/>
     <mergeCell ref="B85:E85"/>
@@ -3438,12 +3324,6 @@
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3594,24 +3474,24 @@
         <v>279</v>
       </c>
       <c r="D3" s="2">
-        <v>1.1499999999999999</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F3" s="15">
-        <v>0.21644266614219942</v>
+        <v>0.21293704824312565</v>
       </c>
       <c r="G3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$10</f>
-        <v>9.904266614219942E-2</v>
+        <v>9.5537048243125644E-2</v>
       </c>
       <c r="H3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$11</f>
-        <v>0.18194266614219942</v>
+        <v>0.17843704824312565</v>
       </c>
       <c r="I3" s="15">
-        <v>0.21644266614219942</v>
+        <v>0.21293704824312568</v>
       </c>
       <c r="J3" s="2">
         <v>0.9421991685622978</v>
@@ -3626,7 +3506,7 @@
         <v>1.6432419261953275</v>
       </c>
       <c r="N3" s="4">
-        <v>6.3476783162570317E-3</v>
+        <v>6.2929569514617121E-3</v>
       </c>
       <c r="O3" s="4">
         <v>0</v>
@@ -3641,7 +3521,7 @@
         <v>3.4432102574884196</v>
       </c>
       <c r="S3" s="86">
-        <v>2.0258239687205015</v>
+        <v>1.9115679363188245</v>
       </c>
       <c r="T3" s="13" t="s">
         <v>280</v>
@@ -3664,42 +3544,42 @@
         <v>259</v>
       </c>
       <c r="D4" s="2">
-        <v>15.44</v>
+        <v>15.38</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F4" s="15">
-        <v>0.18737363316325828</v>
+        <v>0.18912881948046301</v>
       </c>
       <c r="G4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$10</f>
-        <v>6.9973633163258275E-2</v>
+        <v>7.1728819480463002E-2</v>
       </c>
       <c r="H4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$11</f>
-        <v>0.15287363316325828</v>
+        <v>0.154628819480463</v>
       </c>
       <c r="I4" s="15">
-        <v>0.18737363316325828</v>
+        <v>0.18912881948046303</v>
       </c>
       <c r="J4" s="2">
-        <v>11.862033069653084</v>
+        <v>11.866845734983505</v>
       </c>
       <c r="K4" s="2">
-        <v>23.887705575274836</v>
+        <v>23.899333440997744</v>
       </c>
       <c r="L4" s="2">
-        <v>14.971213388216997</v>
+        <v>14.977385795894701</v>
       </c>
       <c r="M4" s="86">
-        <v>20.366464536567324</v>
+        <v>20.375014060112886</v>
       </c>
       <c r="N4" s="4">
-        <v>6.5101907277916274E-2</v>
+        <v>6.5387552793081283E-2</v>
       </c>
       <c r="O4" s="4">
-        <v>3.5275706733689696E-2</v>
+        <v>3.5396140526234639E-2</v>
       </c>
       <c r="P4" s="15">
         <v>0.36794481423679237</v>
@@ -3711,7 +3591,7 @@
         <v>0.60402076709908736</v>
       </c>
       <c r="S4" s="86">
-        <v>4.5265264551387059</v>
+        <v>4.5287238180520148</v>
       </c>
       <c r="T4" s="13" t="s">
         <v>246</v>
@@ -3734,42 +3614,42 @@
         <v>237</v>
       </c>
       <c r="D5" s="2">
-        <v>6.08</v>
+        <v>6.11</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F5" s="15">
-        <v>0.16112633203079096</v>
+        <v>0.15926921829883645</v>
       </c>
       <c r="G5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$10</f>
-        <v>4.372633203079096E-2</v>
+        <v>4.1869218298836441E-2</v>
       </c>
       <c r="H5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$11</f>
-        <v>0.12662633203079096</v>
+        <v>0.12476921829883644</v>
       </c>
       <c r="I5" s="15">
-        <v>0.16112633203079096</v>
+        <v>0.15926921829883645</v>
       </c>
       <c r="J5" s="2">
-        <v>4.428921836807783</v>
+        <v>4.4306821973721187</v>
       </c>
       <c r="K5" s="2">
-        <v>7.9670026289547851</v>
+        <v>7.970870141114629</v>
       </c>
       <c r="L5" s="2">
-        <v>5.5414713233942736</v>
+        <v>5.5437094670052947</v>
       </c>
       <c r="M5" s="86">
-        <v>7.4633845319646834</v>
+        <v>7.4664546878097049</v>
       </c>
       <c r="N5" s="4">
-        <v>0.12729200739087043</v>
+        <v>0.12672849511458295</v>
       </c>
       <c r="O5" s="4">
-        <v>7.2687419474340292E-2</v>
+        <v>7.2330525434368076E-2</v>
       </c>
       <c r="P5" s="15">
         <v>0.61007460831657279</v>
@@ -3781,7 +3661,7 @@
         <v>1.1309485990394448</v>
       </c>
       <c r="S5" s="86">
-        <v>-3.8097920812266781</v>
+        <v>-3.8116415116695737</v>
       </c>
       <c r="T5" s="13" t="s">
         <v>239</v>
@@ -3804,21 +3684,21 @@
         <v>277</v>
       </c>
       <c r="D6" s="2">
-        <v>69.39</v>
+        <v>68.8</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>275</v>
       </c>
       <c r="F6" s="15">
-        <v>0.15518819500348435</v>
+        <v>0.15867473171661994</v>
       </c>
       <c r="G6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$10</f>
-        <v>3.7788195003484348E-2</v>
+        <v>4.1274731716619939E-2</v>
       </c>
       <c r="H6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$11</f>
-        <v>0.12068819500348435</v>
+        <v>0.12417473171661994</v>
       </c>
       <c r="I6" s="15">
         <v>0</v>
@@ -3836,10 +3716,10 @@
         <v>84.017562490801396</v>
       </c>
       <c r="N6" s="4">
-        <v>7.6091679799215661E-2</v>
+        <v>7.6744210192842666E-2</v>
       </c>
       <c r="O6" s="4">
-        <v>6.6969303934284477E-2</v>
+        <v>6.7543604651162797E-2</v>
       </c>
       <c r="P6" s="15">
         <v>0.30279158651211824</v>
@@ -3868,72 +3748,72 @@
     </row>
     <row r="7" spans="1:23">
       <c r="B7" s="11" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="D7" s="2">
-        <v>21.15</v>
+        <v>3.57</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>253</v>
+        <v>160</v>
       </c>
       <c r="F7" s="15">
-        <v>0.14021163259405034</v>
+        <v>0.14834835832623461</v>
       </c>
       <c r="G7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$10</f>
-        <v>2.2811632594050335E-2</v>
+        <v>3.0948358326234604E-2</v>
       </c>
       <c r="H7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$11</f>
-        <v>0.10571163259405034</v>
+        <v>0.11384835832623461</v>
       </c>
       <c r="I7" s="15">
-        <v>0</v>
+        <v>3.8664913977574877E-2</v>
       </c>
       <c r="J7" s="2">
-        <v>14.418941896437474</v>
+        <v>2.4911701525888064</v>
       </c>
       <c r="K7" s="2">
-        <v>29.309951346473134</v>
+        <v>4.9623808252376094</v>
       </c>
       <c r="L7" s="2">
-        <v>18.21218480698677</v>
+        <v>3.1413777923828756</v>
       </c>
       <c r="M7" s="86">
-        <v>24.796949133193245</v>
+        <v>4.2691663056616189</v>
       </c>
       <c r="N7" s="4">
-        <v>0.21555373746279879</v>
+        <v>7.9541327003833207E-2</v>
       </c>
       <c r="O7" s="4">
-        <v>2.8066193853427897E-2</v>
+        <v>3.5854341736694682E-2</v>
       </c>
       <c r="P7" s="15">
-        <v>1.4851905363915479</v>
+        <v>0.40000523965699897</v>
       </c>
       <c r="Q7" s="15">
-        <v>0.95241105291674188</v>
+        <v>0.10646655543311496</v>
       </c>
       <c r="R7" s="92">
-        <v>4.0148803043206254</v>
+        <v>0.9804830051022897</v>
       </c>
       <c r="S7" s="86">
-        <v>-38.360607814419353</v>
+        <v>1.6698226477450393</v>
       </c>
       <c r="T7" s="13" t="s">
-        <v>254</v>
+        <v>161</v>
       </c>
       <c r="U7" s="11" t="s">
         <v>162</v>
       </c>
       <c r="V7" s="14">
-        <v>45900</v>
+        <v>45808</v>
       </c>
       <c r="W7" s="11" t="s">
-        <v>247</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -3944,42 +3824,42 @@
         <v>250</v>
       </c>
       <c r="D8" s="2">
-        <v>55.75</v>
+        <v>55.65</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F8" s="15">
-        <v>0.13796564912031539</v>
+        <v>0.13918053194738822</v>
       </c>
       <c r="G8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$10</f>
-        <v>2.0565649120315388E-2</v>
+        <v>2.1780531947388215E-2</v>
       </c>
       <c r="H8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$11</f>
-        <v>0.10346564912031539</v>
+        <v>0.10468053194738822</v>
       </c>
       <c r="I8" s="15">
-        <v>3.5057368663751309E-2</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2">
-        <v>38.67449654927848</v>
+        <v>38.719486313520228</v>
       </c>
       <c r="K8" s="2">
-        <v>64.818448718764827</v>
+        <v>64.892912330803952</v>
       </c>
       <c r="L8" s="2">
-        <v>48.148365693729644</v>
+        <v>48.204328663659695</v>
       </c>
       <c r="M8" s="86">
-        <v>64.469262649530066</v>
+        <v>64.544120328141631</v>
       </c>
       <c r="N8" s="4">
-        <v>9.4419233289180268E-2</v>
+        <v>9.4703343132953519E-2</v>
       </c>
       <c r="O8" s="4">
-        <v>9.0582600896860987E-2</v>
+        <v>9.085516621743038E-2</v>
       </c>
       <c r="P8" s="15">
         <v>1.2907496012759174</v>
@@ -3991,7 +3871,7 @@
         <v>0.73855199466278643</v>
       </c>
       <c r="S8" s="86">
-        <v>-2.6472954415279868</v>
+        <v>-2.6504984195888377</v>
       </c>
       <c r="T8" s="13" t="s">
         <v>246</v>
@@ -4008,503 +3888,563 @@
     </row>
     <row r="9" spans="1:23">
       <c r="B9" s="11" t="s">
-        <v>158</v>
+        <v>251</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>159</v>
+        <v>252</v>
       </c>
       <c r="D9" s="2">
-        <v>17.899999999999999</v>
+        <v>21.72</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>160</v>
+        <v>253</v>
       </c>
       <c r="F9" s="15">
-        <v>0.11920444715894019</v>
+        <v>0.12990849663525528</v>
       </c>
       <c r="G9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$10</f>
-        <v>1.8044471589401812E-3</v>
+        <v>1.2508496635255273E-2</v>
       </c>
       <c r="H9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$11</f>
-        <v>8.4704447158940183E-2</v>
+        <v>9.5408496635255274E-2</v>
       </c>
       <c r="I9" s="15">
         <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>11.804906901225705</v>
+        <v>14.418941896437474</v>
       </c>
       <c r="K9" s="2">
-        <v>20.508980461992877</v>
+        <v>29.309951346473134</v>
       </c>
       <c r="L9" s="2">
-        <v>14.733437767356989</v>
+        <v>18.21218480698677</v>
       </c>
       <c r="M9" s="86">
-        <v>19.785541823839793</v>
+        <v>24.796949133193245</v>
       </c>
       <c r="N9" s="4">
-        <v>9.6535531808359179E-2</v>
+        <v>0.2098969404851839</v>
       </c>
       <c r="O9" s="4">
-        <v>7.5977653631284933E-2</v>
+        <v>2.7329650092081034E-2</v>
       </c>
       <c r="P9" s="15">
-        <v>0.31018327415220487</v>
+        <v>1.4851905363915479</v>
       </c>
       <c r="Q9" s="15">
-        <v>0.15818859882129041</v>
+        <v>0.95241105291674188</v>
       </c>
       <c r="R9" s="92">
-        <v>1.4550387206421544</v>
+        <v>4.0148803043206254</v>
       </c>
       <c r="S9" s="86">
-        <v>5.8696003638854428</v>
+        <v>-38.360607814419353</v>
       </c>
       <c r="T9" s="13" t="s">
-        <v>161</v>
+        <v>254</v>
       </c>
       <c r="U9" s="11" t="s">
         <v>162</v>
       </c>
       <c r="V9" s="14">
-        <v>45808</v>
+        <v>45900</v>
       </c>
       <c r="W9" s="11" t="s">
-        <v>163</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:23">
       <c r="B10" s="11" t="s">
-        <v>240</v>
+        <v>158</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>241</v>
+        <v>159</v>
       </c>
       <c r="D10" s="2">
-        <v>54</v>
+        <v>17.82</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F10" s="15">
-        <v>0.11184849157270471</v>
+        <v>0.1209941874823961</v>
       </c>
       <c r="G10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$10</f>
-        <v>-5.551508427295293E-3</v>
+        <v>3.594187482396094E-3</v>
       </c>
       <c r="H10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$11</f>
-        <v>7.7348491572704708E-2</v>
+        <v>8.6494187482396095E-2</v>
       </c>
       <c r="I10" s="15">
         <v>0</v>
       </c>
       <c r="J10" s="2">
-        <v>34.381875852171149</v>
+        <v>11.804906901225705</v>
       </c>
       <c r="K10" s="2">
-        <v>67.361539432485785</v>
+        <v>20.508980461992877</v>
       </c>
       <c r="L10" s="2">
-        <v>43.298516914573895</v>
+        <v>14.733437767356989</v>
       </c>
       <c r="M10" s="86">
-        <v>58.754189493018607</v>
+        <v>19.785541823839793</v>
       </c>
       <c r="N10" s="4">
-        <v>4.1955491566384277E-2</v>
+        <v>9.696891242253812E-2</v>
       </c>
       <c r="O10" s="4">
-        <v>3.7944127980758587E-2</v>
+        <v>7.6318742985409652E-2</v>
       </c>
       <c r="P10" s="15">
-        <v>0.72207550313588764</v>
+        <v>0.31018327415220487</v>
       </c>
       <c r="Q10" s="15">
-        <v>9.5579625064196368E-3</v>
+        <v>0.15818859882129041</v>
       </c>
       <c r="R10" s="92">
-        <v>7.3592411949940734E-2</v>
+        <v>1.4550387206421544</v>
       </c>
       <c r="S10" s="86">
-        <v>1.334506858271689</v>
+        <v>5.8696003638854428</v>
       </c>
       <c r="T10" s="16" t="s">
-        <v>242</v>
+        <v>161</v>
       </c>
       <c r="U10" s="11" t="s">
         <v>162</v>
       </c>
       <c r="V10" s="14">
-        <v>45900</v>
+        <v>45808</v>
       </c>
       <c r="W10" s="11" t="s">
-        <v>247</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:23">
       <c r="B11" s="11" t="s">
-        <v>164</v>
+        <v>240</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>165</v>
+        <v>241</v>
       </c>
       <c r="D11" s="2">
-        <v>8.1</v>
+        <v>53.55</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F11" s="15">
-        <v>0.11083350655450119</v>
+        <v>0.11521291318800975</v>
       </c>
       <c r="G11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$10</f>
-        <v>-6.5664934454988111E-3</v>
+        <v>-2.1870868119902576E-3</v>
       </c>
       <c r="H11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$11</f>
-        <v>7.633350655450119E-2</v>
+        <v>8.0712913188009744E-2</v>
       </c>
       <c r="I11" s="15">
         <v>0</v>
       </c>
       <c r="J11" s="2">
-        <v>5.2239462882061574</v>
+        <v>34.394984382396515</v>
       </c>
       <c r="K11" s="2">
-        <v>9.1628099951889297</v>
+        <v>67.394305644906538</v>
       </c>
       <c r="L11" s="2">
-        <v>6.5243113398084081</v>
+        <v>43.315384624827814</v>
       </c>
       <c r="M11" s="86">
-        <v>8.7684502451266084</v>
+        <v>58.777638274888893</v>
       </c>
       <c r="N11" s="4">
-        <v>3.8135601479291979E-2</v>
+        <v>4.2328511280438831E-2</v>
       </c>
       <c r="O11" s="4">
-        <v>7.160493827160494E-2</v>
+        <v>3.8244420777520896E-2</v>
       </c>
       <c r="P11" s="15">
-        <v>8.3114411724224596E-2</v>
+        <v>0.72207550313588764</v>
       </c>
       <c r="Q11" s="15">
-        <v>1.8509098960546238E-2</v>
+        <v>9.5579625064196368E-3</v>
       </c>
       <c r="R11" s="92">
-        <v>1.1933697905849452</v>
+        <v>7.3592411949940734E-2</v>
       </c>
       <c r="S11" s="86">
-        <v>11.511512740854835</v>
+        <v>1.3351546830236229</v>
       </c>
       <c r="T11" s="13" t="s">
-        <v>166</v>
+        <v>242</v>
       </c>
       <c r="U11" s="11" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="V11" s="14">
         <v>45900</v>
       </c>
       <c r="W11" s="11" t="s">
-        <v>163</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" spans="1:23">
       <c r="B12" s="11" t="s">
-        <v>244</v>
+        <v>164</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>245</v>
+        <v>165</v>
       </c>
       <c r="D12" s="2">
-        <v>14.3</v>
+        <v>8.15</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F12" s="15">
-        <v>0.1090060893695004</v>
+        <v>0.10840635294497614</v>
       </c>
       <c r="G12" s="15">
         <f>F12 - Portfolio_Mgmt!$C$10</f>
-        <v>-8.3939106304996014E-3</v>
+        <v>-8.9936470550238679E-3</v>
       </c>
       <c r="H12" s="15">
         <f>F12 - Portfolio_Mgmt!$C$11</f>
-        <v>7.45060893695004E-2</v>
+        <v>7.3906352944976134E-2</v>
       </c>
       <c r="I12" s="15">
         <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>9.1251344157607761</v>
+        <v>5.2239462882061574</v>
       </c>
       <c r="K12" s="2">
-        <v>16.718616112226428</v>
+        <v>9.1628099951889297</v>
       </c>
       <c r="L12" s="2">
-        <v>11.432798659390293</v>
+        <v>6.5243113398084081</v>
       </c>
       <c r="M12" s="86">
-        <v>15.422137352615858</v>
+        <v>8.7684502451266084</v>
       </c>
       <c r="N12" s="4">
-        <v>0.10749746672561937</v>
+        <v>3.7901640734020248E-2</v>
       </c>
       <c r="O12" s="4">
-        <v>5.8350495104895095E-2</v>
+        <v>7.1165644171779133E-2</v>
       </c>
       <c r="P12" s="15">
-        <v>2.2875080906148866</v>
+        <v>8.3114411724224596E-2</v>
       </c>
       <c r="Q12" s="15">
-        <v>1.5035598705501618</v>
+        <v>1.8509098960546238E-2</v>
       </c>
       <c r="R12" s="92">
-        <v>4.1998196571663646</v>
+        <v>1.1933697905849452</v>
       </c>
       <c r="S12" s="86">
-        <v>-12.151746556489819</v>
+        <v>11.511512740854835</v>
       </c>
       <c r="T12" s="13" t="s">
-        <v>246</v>
+        <v>166</v>
       </c>
       <c r="U12" s="11" t="s">
-        <v>248</v>
+        <v>167</v>
       </c>
       <c r="V12" s="14">
         <v>45900</v>
       </c>
       <c r="W12" s="11" t="s">
-        <v>247</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:23">
       <c r="B13" s="11" t="s">
-        <v>255</v>
+        <v>168</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>256</v>
+        <v>169</v>
       </c>
       <c r="D13" s="2">
-        <v>28.23</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>253</v>
+        <v>160</v>
       </c>
       <c r="F13" s="15">
-        <v>0.10191457699731421</v>
+        <v>0.10392879009854439</v>
       </c>
       <c r="G13" s="15">
         <f>F13 - Portfolio_Mgmt!$C$10</f>
-        <v>-1.5485423002685794E-2</v>
+        <v>-1.3471209901455616E-2</v>
       </c>
       <c r="H13" s="15">
         <f>F13 - Portfolio_Mgmt!$C$11</f>
-        <v>6.7414576997314207E-2</v>
+        <v>6.9428790098544385E-2</v>
       </c>
       <c r="I13" s="15">
         <v>0</v>
       </c>
       <c r="J13" s="2">
-        <v>17.682685147645955</v>
+        <v>1.4428843799519049</v>
       </c>
       <c r="K13" s="2">
-        <v>32.464859269378167</v>
+        <v>2.7168715485394852</v>
       </c>
       <c r="L13" s="2">
-        <v>22.157904669779033</v>
+        <v>1.8114973282765074</v>
       </c>
       <c r="M13" s="2">
-        <v>29.895007167811503</v>
+        <v>2.4494218673596402</v>
       </c>
       <c r="N13" s="4">
-        <v>8.9945710498866363E-2</v>
+        <v>3.5980231621691262E-2</v>
       </c>
       <c r="O13" s="4">
-        <v>5.6677293659227773E-2</v>
+        <v>4.9378384462771097E-2</v>
       </c>
       <c r="P13" s="15">
-        <v>0.78990369994931575</v>
+        <v>0.20351769929714394</v>
       </c>
       <c r="Q13" s="15">
-        <v>0.40281804358844397</v>
+        <v>1.0763175939415467E-2</v>
       </c>
       <c r="R13" s="92">
-        <v>3.955391512509995</v>
+        <v>0.29882156160837919</v>
       </c>
       <c r="S13" s="86">
-        <v>-26.938493611476797</v>
+        <v>1.8784842625371931</v>
       </c>
       <c r="T13" s="13" t="s">
-        <v>257</v>
+        <v>170</v>
       </c>
       <c r="U13" s="11" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="V13" s="14">
         <v>45900</v>
       </c>
       <c r="W13" s="11" t="s">
-        <v>247</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:23">
       <c r="B14" s="11" t="s">
-        <v>168</v>
+        <v>244</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>169</v>
+        <v>245</v>
       </c>
       <c r="D14" s="2">
-        <v>2.35</v>
+        <v>14.62</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F14" s="15">
-        <v>9.5546776071535167E-2</v>
+        <v>0.10088016442395631</v>
       </c>
       <c r="G14" s="15">
         <f>F14 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.1853223928464838E-2</v>
+        <v>-1.6519835576043695E-2</v>
       </c>
       <c r="H14" s="15">
         <f>F14 - Portfolio_Mgmt!$C$11</f>
-        <v>6.1046776071535164E-2</v>
+        <v>6.6380164423956306E-2</v>
       </c>
       <c r="I14" s="15">
         <v>0</v>
       </c>
       <c r="J14" s="2">
-        <v>1.442374867722968</v>
+        <v>9.1359587259076722</v>
       </c>
       <c r="K14" s="2">
-        <v>2.7155321746611896</v>
+        <v>16.73836897721916</v>
       </c>
       <c r="L14" s="2">
-        <v>1.8108383615725383</v>
+        <v>11.446356334964792</v>
       </c>
       <c r="M14" s="2">
-        <v>2.4485007089485338</v>
+        <v>15.440419547734052</v>
       </c>
       <c r="N14" s="4">
-        <v>3.5197892699834928E-2</v>
+        <v>0.10527247112980752</v>
       </c>
       <c r="O14" s="4">
-        <v>4.8351240838924094E-2</v>
+        <v>5.7142383036935702E-2</v>
       </c>
       <c r="P14" s="15">
-        <v>0.20351769929714394</v>
+        <v>2.2875080906148866</v>
       </c>
       <c r="Q14" s="15">
-        <v>1.0763175939415467E-2</v>
+        <v>1.5035598705501618</v>
       </c>
       <c r="R14" s="92">
-        <v>0.29882156160837919</v>
+        <v>4.1998196571663646</v>
       </c>
       <c r="S14" s="86">
-        <v>1.8775728111399408</v>
+        <v>-12.166449024907546</v>
       </c>
       <c r="T14" s="13" t="s">
-        <v>170</v>
+        <v>246</v>
       </c>
       <c r="U14" s="11" t="s">
-        <v>171</v>
+        <v>248</v>
       </c>
       <c r="V14" s="14">
         <v>45900</v>
       </c>
       <c r="W14" s="11" t="s">
-        <v>163</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" spans="1:23">
       <c r="B15" s="11" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="D15" s="2">
-        <v>57.4</v>
+        <v>28.49</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="F15" s="15">
-        <v>9.0634582120934004E-2</v>
+        <v>9.8376640230496193E-2</v>
       </c>
       <c r="G15" s="15">
         <f>F15 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.6765417879066E-2</v>
+        <v>-1.9023359769503811E-2</v>
       </c>
       <c r="H15" s="15">
         <f>F15 - Portfolio_Mgmt!$C$11</f>
-        <v>5.6134582120934001E-2</v>
+        <v>6.387664023049619E-2</v>
       </c>
       <c r="I15" s="15">
         <v>0</v>
       </c>
       <c r="J15" s="2">
-        <v>34.669224296258527</v>
+        <v>17.682685147645955</v>
       </c>
       <c r="K15" s="2">
-        <v>66.592285778879997</v>
+        <v>32.464859269378167</v>
       </c>
       <c r="L15" s="2">
-        <v>43.592757973888887</v>
+        <v>22.157904669779033</v>
       </c>
       <c r="M15" s="2">
-        <v>59.048136223898794</v>
+        <v>29.895007167811503</v>
       </c>
       <c r="N15" s="4">
-        <v>8.005411568167814E-2</v>
+        <v>8.9124865124008343E-2</v>
       </c>
       <c r="O15" s="4">
-        <v>4.1811846689895467E-2</v>
+        <v>5.616005616005617E-2</v>
       </c>
       <c r="P15" s="15">
-        <v>3.4701988818540461</v>
+        <v>0.78990369994931575</v>
       </c>
       <c r="Q15" s="15">
-        <v>5.0341856510546588E-2</v>
+        <v>0.40281804358844397</v>
       </c>
       <c r="R15" s="92">
-        <v>3.9546057100127742E-2</v>
+        <v>3.955391512509995</v>
       </c>
       <c r="S15" s="86">
-        <v>-13.312996389940134</v>
+        <v>-26.938493611476797</v>
       </c>
       <c r="T15" s="13" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="U15" s="11" t="s">
         <v>162</v>
       </c>
       <c r="V15" s="14">
-        <v>45716</v>
+        <v>45900</v>
       </c>
       <c r="W15" s="11" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="16" spans="1:23">
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="E16" s="12"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="T16" s="13"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="14"/>
+      <c r="B16" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="D16" s="2">
+        <v>57.21</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="F16" s="15">
+        <v>9.1887382418681218E-2</v>
+      </c>
+      <c r="G16" s="15">
+        <f>F16 - Portfolio_Mgmt!$C$10</f>
+        <v>-2.5512617581318786E-2</v>
+      </c>
+      <c r="H16" s="15">
+        <f>F16 - Portfolio_Mgmt!$C$11</f>
+        <v>5.7387382418681215E-2</v>
+      </c>
+      <c r="I16" s="15">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2">
+        <v>34.669224296258527</v>
+      </c>
+      <c r="K16" s="2">
+        <v>66.592285778879997</v>
+      </c>
+      <c r="L16" s="2">
+        <v>43.592757973888887</v>
+      </c>
+      <c r="M16" s="2">
+        <v>59.048136223898794</v>
+      </c>
+      <c r="N16" s="4">
+        <v>8.0319983221959892E-2</v>
+      </c>
+      <c r="O16" s="4">
+        <v>4.195070791819612E-2</v>
+      </c>
+      <c r="P16" s="15">
+        <v>3.4701988818540461</v>
+      </c>
+      <c r="Q16" s="15">
+        <v>5.0341856510546588E-2</v>
+      </c>
+      <c r="R16" s="92">
+        <v>3.9546057100127742E-2</v>
+      </c>
+      <c r="S16" s="86">
+        <v>-13.312996389940134</v>
+      </c>
+      <c r="T16" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="U16" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="V16" s="14">
+        <v>45716</v>
+      </c>
+      <c r="W16" s="11" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="17" spans="2:22">
       <c r="B17" s="11"/>
@@ -6538,22 +6478,22 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="J3:J1048576">
-    <cfRule type="expression" dxfId="10" priority="3">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>J3&gt;D3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3:L1048576">
-    <cfRule type="expression" dxfId="9" priority="6">
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>L3&gt;D3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3:M1048576">
-    <cfRule type="expression" dxfId="8" priority="4">
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>D3&gt;M3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V3:V1048576">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>V3&lt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6620,14 +6560,14 @@
         <v>22</v>
       </c>
       <c r="C4" s="34">
-        <v>4.2999999999999997E-2</v>
+        <v>4.2599999999999999E-2</v>
       </c>
       <c r="D4" s="34">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="E4" s="35">
         <f>D4-C4</f>
-        <v>3.2000000000000001E-2</v>
+        <v>3.2399999999999998E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6899,7 +6839,7 @@
       </c>
       <c r="G3" s="73">
         <f>F3/$F$9</f>
-        <v>0.39285097563642929</v>
+        <v>0.39268415166236537</v>
       </c>
       <c r="H3" s="91">
         <f>Portfolio_Mgmt!E61</f>
@@ -6912,7 +6852,7 @@
       </c>
       <c r="C4" s="75">
         <f>VLOOKUP(B4,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>17.899999999999999</v>
+        <v>17.82</v>
       </c>
       <c r="D4" s="74" t="str">
         <f>VLOOKUP(B4,Opportunities!B$3:E$12,4,FALSE)</f>
@@ -6923,11 +6863,11 @@
       </c>
       <c r="F4" s="76">
         <f>C4*E4</f>
-        <v>179000</v>
+        <v>178200</v>
       </c>
       <c r="G4" s="73">
         <f>F4/$F$9</f>
-        <v>0.20011724858414812</v>
+        <v>0.19913826992559985</v>
       </c>
       <c r="H4" s="73">
         <f>VLOOKUP(B4,Opportunities!B$3:I$12,8,FALSE)</f>
@@ -6940,7 +6880,7 @@
       </c>
       <c r="C5" s="75">
         <f>VLOOKUP(B5,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>8.1</v>
+        <v>8.15</v>
       </c>
       <c r="D5" s="74" t="str">
         <f>VLOOKUP(B5,Opportunities!B$3:E$12,4,FALSE)</f>
@@ -6951,11 +6891,11 @@
       </c>
       <c r="F5" s="76">
         <f>E5*C5</f>
-        <v>162000</v>
+        <v>163000</v>
       </c>
       <c r="G5" s="73">
         <f>F5/$F$9</f>
-        <v>0.18111169983593292</v>
+        <v>0.18215228955035226</v>
       </c>
       <c r="H5" s="73">
         <f>VLOOKUP(B5,Opportunities!B$3:I$12,8,FALSE)</f>
@@ -6968,7 +6908,7 @@
       </c>
       <c r="C6" s="75">
         <f>VLOOKUP(B6,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>6.08</v>
+        <v>6.11</v>
       </c>
       <c r="D6" s="74" t="str">
         <f>VLOOKUP(B6,Opportunities!B$3:E$12,4,FALSE)</f>
@@ -6979,15 +6919,15 @@
       </c>
       <c r="F6" s="76">
         <f>E6*C6</f>
-        <v>109440</v>
+        <v>109980</v>
       </c>
       <c r="G6" s="73">
         <f>F6/$F$9</f>
-        <v>0.12235101500027469</v>
+        <v>0.12290250800458738</v>
       </c>
       <c r="H6" s="73">
         <f>VLOOKUP(B6,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.16112633203079096</v>
+        <v>0.15926921829883645</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -6996,7 +6936,7 @@
       </c>
       <c r="C7" s="75">
         <f>VLOOKUP(B7,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>15.44</v>
+        <v>15.38</v>
       </c>
       <c r="D7" s="74" t="str">
         <f>VLOOKUP(B7,Opportunities!B$3:E$12,4,FALSE)</f>
@@ -7007,15 +6947,15 @@
       </c>
       <c r="F7" s="76">
         <f>C7*E7</f>
-        <v>92640</v>
+        <v>92280</v>
       </c>
       <c r="G7" s="73">
         <f>F7/$F$9</f>
-        <v>0.10356906094321498</v>
+        <v>0.10312278085709514</v>
       </c>
       <c r="H7" s="73">
         <f>VLOOKUP(B7,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.18737363316325828</v>
+        <v>0.18912881948046303</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -7033,15 +6973,15 @@
       </c>
       <c r="F9" s="81">
         <f>SUM(F3:F7)</f>
-        <v>894475.62</v>
+        <v>894855.62</v>
       </c>
       <c r="G9" s="82">
         <f>SUM(G3:G7)</f>
-        <v>0.99999999999999989</v>
+        <v>1</v>
       </c>
       <c r="H9" s="89">
         <f>SUM(H4:H7)</f>
-        <v>0.34849996519404924</v>
+        <v>0.34839803777929945</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -7063,7 +7003,7 @@
       </c>
       <c r="C12" s="75">
         <f>VLOOKUP(B12,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>1.1499999999999999</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="D12" s="74" t="str">
         <f>VLOOKUP(B12,Opportunities!B$3:E$12,4,FALSE)</f>
@@ -7075,15 +7015,15 @@
       </c>
       <c r="F12" s="76">
         <f>C12*E12</f>
-        <v>57499.999999999993</v>
+        <v>57999.999999999993</v>
       </c>
       <c r="G12" s="73">
         <f>F12/$F$9</f>
-        <v>6.4283473707198405E-2</v>
+        <v>6.4814925116076255E-2</v>
       </c>
       <c r="H12" s="73">
         <f>VLOOKUP(B12,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.21644266614219942</v>
+        <v>0.21293704824312568</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -7105,11 +7045,11 @@
       </c>
       <c r="F14" s="81">
         <f>F3-F12</f>
-        <v>293895.62</v>
+        <v>293395.62</v>
       </c>
       <c r="G14" s="89">
         <f t="shared" ref="G14" si="0">F14/$F$9</f>
-        <v>0.3285675019292309</v>
+        <v>0.32786922654628908</v>
       </c>
       <c r="H14" s="89">
         <f>Portfolio_Mgmt!E61</f>
@@ -7206,15 +7146,15 @@
       <c r="B5" s="106" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="95"/>
-      <c r="D5" s="95"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="97"/>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="106" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="97"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D988B6F-DFBA-42AE-A1FC-24FAB067448A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24EE2DD8-E7B4-4F28-B820-65A815E8153A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="283">
   <si>
     <t>Name</t>
   </si>
@@ -324,10 +324,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Recession expected</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Overly bullish	</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -341,10 +337,6 @@
   </si>
   <si>
     <t>Wide (above historical median)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Expansion expected</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1634,6 +1626,12 @@
   </si>
   <si>
     <t>東方表行集團</t>
+  </si>
+  <si>
+    <t>Expansion expected</t>
+  </si>
+  <si>
+    <t>Recession expected</t>
   </si>
 </sst>
 </file>
@@ -2209,17 +2207,17 @@
     <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2616,7 +2614,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="20" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2629,29 +2627,29 @@
       <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B4" s="95" t="s">
-        <v>221</v>
-      </c>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
+      <c r="B4" s="94" t="s">
+        <v>219</v>
+      </c>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="20" t="s">
         <v>66</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C6" s="61"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" s="95" t="s">
-        <v>209</v>
-      </c>
-      <c r="C7" s="95"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
+      <c r="B7" s="94" t="s">
+        <v>207</v>
+      </c>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="94"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="23" t="s">
@@ -2687,26 +2685,26 @@
     </row>
     <row r="14" spans="1:5">
       <c r="B14" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="B15" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="B16" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2716,17 +2714,17 @@
     </row>
     <row r="19" spans="1:5">
       <c r="B19" s="24" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="B20" s="24" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="B21" s="24" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2734,18 +2732,18 @@
         <v>67</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C23" s="61"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
-      <c r="B24" s="95" t="s">
-        <v>220</v>
-      </c>
-      <c r="C24" s="95"/>
-      <c r="D24" s="95"/>
-      <c r="E24" s="95"/>
+      <c r="B24" s="94" t="s">
+        <v>218</v>
+      </c>
+      <c r="C24" s="94"/>
+      <c r="D24" s="94"/>
+      <c r="E24" s="94"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
@@ -2753,15 +2751,15 @@
     <row r="26" spans="1:5">
       <c r="A26" s="18"/>
       <c r="B26" s="50" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="B27" s="26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C27" s="51">
         <v>6</v>
@@ -2777,15 +2775,15 @@
     </row>
     <row r="30" spans="1:5">
       <c r="B30" s="50" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="B31" s="26" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C31" s="59">
         <f>C27-C32</f>
@@ -2794,7 +2792,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="B32" s="26" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C32" s="58">
         <v>1</v>
@@ -2833,7 +2831,7 @@
         <v>0.08</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E36" s="48">
         <v>0.2</v>
@@ -2841,28 +2839,28 @@
     </row>
     <row r="38" spans="1:5">
       <c r="B38" s="20" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="B39" s="95" t="s">
-        <v>156</v>
-      </c>
-      <c r="C39" s="95"/>
-      <c r="D39" s="95"/>
-      <c r="E39" s="95"/>
+      <c r="B39" s="94" t="s">
+        <v>154</v>
+      </c>
+      <c r="C39" s="94"/>
+      <c r="D39" s="94"/>
+      <c r="E39" s="94"/>
     </row>
     <row r="40" spans="1:5" ht="46.6" customHeight="1">
-      <c r="B40" s="95" t="s">
-        <v>235</v>
-      </c>
-      <c r="C40" s="95"/>
-      <c r="D40" s="95"/>
-      <c r="E40" s="95"/>
+      <c r="B40" s="94" t="s">
+        <v>233</v>
+      </c>
+      <c r="C40" s="94"/>
+      <c r="D40" s="94"/>
+      <c r="E40" s="94"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="21" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B42" s="21"/>
       <c r="C42" s="21"/>
@@ -2870,31 +2868,31 @@
       <c r="E42" s="21"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="B44" s="95" t="s">
-        <v>208</v>
-      </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="B44" s="94" t="s">
+        <v>206</v>
+      </c>
+      <c r="C44" s="94"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="23" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="B48" s="50" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D48" s="56"/>
       <c r="E48" s="56"/>
     </row>
     <row r="49" spans="2:5">
       <c r="B49" s="26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C49" s="29">
         <v>0.6</v>
@@ -2904,7 +2902,7 @@
     </row>
     <row r="50" spans="2:5">
       <c r="B50" s="26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C50" s="29">
         <v>0.4</v>
@@ -2914,33 +2912,33 @@
     </row>
     <row r="51" spans="2:5">
       <c r="B51" s="26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C51" s="29">
         <v>0.3</v>
       </c>
       <c r="D51" s="62" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E51" s="55"/>
     </row>
     <row r="53" spans="2:5">
       <c r="B53" s="23" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55" spans="2:5">
       <c r="B55" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="C55" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="D55" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="C55" s="50" t="s">
+      <c r="E55" s="50" t="s">
         <v>95</v>
-      </c>
-      <c r="D55" s="50" t="s">
-        <v>96</v>
-      </c>
-      <c r="E55" s="50" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="56" spans="2:5">
@@ -2948,10 +2946,10 @@
         <v>69</v>
       </c>
       <c r="C56" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D56" s="26" t="s">
         <v>76</v>
-      </c>
-      <c r="D56" s="26" t="s">
-        <v>77</v>
       </c>
       <c r="E56" s="41">
         <v>1</v>
@@ -2965,7 +2963,7 @@
         <v>73</v>
       </c>
       <c r="D57" s="26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E57" s="41">
         <v>2</v>
@@ -2976,13 +2974,13 @@
         <v>71</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>74</v>
+        <v>281</v>
       </c>
       <c r="D58" s="26" t="s">
-        <v>79</v>
+        <v>282</v>
       </c>
       <c r="E58" s="41">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="2:5">
@@ -2990,10 +2988,10 @@
         <v>72</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D59" s="26" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E59" s="41">
         <v>1</v>
@@ -3001,44 +2999,44 @@
     </row>
     <row r="60" spans="2:5">
       <c r="D60" s="27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E60" s="40">
         <f>SUM(E56:E59)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="2:5" ht="12" thickBot="1">
       <c r="D61" s="42" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E61" s="43">
         <f>IF(E60&lt;=2,C49,IF(E60&gt;=6,C51,C50))</f>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="62" spans="2:5" ht="12" thickTop="1"/>
     <row r="63" spans="2:5">
       <c r="B63" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="64" spans="2:5">
       <c r="B64" s="53" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C64" s="54">
         <f>-E61*(C35-Cash_Yield)</f>
-        <v>-0.10619999999999999</v>
+        <v>-7.9649999999999985E-2</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="B65" s="53" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C65" s="54">
         <f>C35+C64</f>
-        <v>0.1938</v>
+        <v>0.22034999999999999</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3047,12 +3045,12 @@
     </row>
     <row r="67" spans="1:5">
       <c r="B67" s="39" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="21" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B69" s="21"/>
       <c r="C69" s="21"/>
@@ -3060,199 +3058,199 @@
       <c r="E69" s="21"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="B71" s="95" t="s">
-        <v>196</v>
-      </c>
-      <c r="C71" s="95"/>
-      <c r="D71" s="95"/>
-      <c r="E71" s="95"/>
+      <c r="B71" s="94" t="s">
+        <v>194</v>
+      </c>
+      <c r="C71" s="94"/>
+      <c r="D71" s="94"/>
+      <c r="E71" s="94"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="28" t="s">
         <v>66</v>
       </c>
       <c r="B73" s="20" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="B74" s="24" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="B75" s="24" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="28" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B77" s="20" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="B78" s="39" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="B79" s="24" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="B80" s="24" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="B81" s="24" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="28" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B83" s="20" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="B84" s="24" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="B85" s="96" t="s">
-        <v>192</v>
-      </c>
-      <c r="C85" s="96"/>
-      <c r="D85" s="96"/>
-      <c r="E85" s="96"/>
+      <c r="B85" s="97" t="s">
+        <v>190</v>
+      </c>
+      <c r="C85" s="97"/>
+      <c r="D85" s="97"/>
+      <c r="E85" s="97"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="B86" s="94" t="s">
-        <v>190</v>
-      </c>
-      <c r="C86" s="94"/>
-      <c r="D86" s="94"/>
-      <c r="E86" s="94"/>
+      <c r="B86" s="96" t="s">
+        <v>188</v>
+      </c>
+      <c r="C86" s="96"/>
+      <c r="D86" s="96"/>
+      <c r="E86" s="96"/>
     </row>
     <row r="87" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B87" s="95" t="s">
-        <v>189</v>
-      </c>
-      <c r="C87" s="95"/>
-      <c r="D87" s="95"/>
-      <c r="E87" s="95"/>
+      <c r="B87" s="94" t="s">
+        <v>187</v>
+      </c>
+      <c r="C87" s="94"/>
+      <c r="D87" s="94"/>
+      <c r="E87" s="94"/>
     </row>
     <row r="88" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B88" s="95" t="s">
-        <v>225</v>
-      </c>
-      <c r="C88" s="95"/>
-      <c r="D88" s="95"/>
-      <c r="E88" s="95"/>
+      <c r="B88" s="94" t="s">
+        <v>223</v>
+      </c>
+      <c r="C88" s="94"/>
+      <c r="D88" s="94"/>
+      <c r="E88" s="94"/>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="24" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="B91" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="B92" s="60" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="B93" s="24" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="B94" s="24" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="B96" s="24" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="B97" s="97" t="s">
-        <v>211</v>
-      </c>
-      <c r="C97" s="97"/>
-      <c r="D97" s="97"/>
-      <c r="E97" s="97"/>
+      <c r="B97" s="95" t="s">
+        <v>209</v>
+      </c>
+      <c r="C97" s="95"/>
+      <c r="D97" s="95"/>
+      <c r="E97" s="95"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="12.4">
-      <c r="B100" s="97" t="s">
-        <v>212</v>
-      </c>
-      <c r="C100" s="97"/>
-      <c r="D100" s="97"/>
-      <c r="E100" s="97"/>
+      <c r="B100" s="95" t="s">
+        <v>210</v>
+      </c>
+      <c r="C100" s="95"/>
+      <c r="D100" s="95"/>
+      <c r="E100" s="95"/>
     </row>
     <row r="101" spans="1:5" ht="58.5" customHeight="1">
-      <c r="B101" s="95" t="s">
-        <v>219</v>
-      </c>
-      <c r="C101" s="95"/>
-      <c r="D101" s="95"/>
-      <c r="E101" s="95"/>
+      <c r="B101" s="94" t="s">
+        <v>217</v>
+      </c>
+      <c r="C101" s="94"/>
+      <c r="D101" s="94"/>
+      <c r="E101" s="94"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="28" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B103" s="20" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="B104" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="B105" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="B107" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="B108" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="B110" s="23" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="B111" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C111" s="44">
         <v>0.4</v>
@@ -3260,7 +3258,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="B112" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C112" s="44">
         <v>0.12601445728348953</v>
@@ -3271,16 +3269,16 @@
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B114" s="95" t="s">
-        <v>217</v>
-      </c>
-      <c r="C114" s="95"/>
-      <c r="D114" s="95"/>
-      <c r="E114" s="95"/>
+      <c r="B114" s="94" t="s">
+        <v>215</v>
+      </c>
+      <c r="C114" s="94"/>
+      <c r="D114" s="94"/>
+      <c r="E114" s="94"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B116" s="21"/>
       <c r="C116" s="21"/>
@@ -3289,32 +3287,26 @@
     </row>
     <row r="118" spans="1:5">
       <c r="B118" s="20" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="B119" s="24" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="B120" s="24" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="B121" s="24" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
     <mergeCell ref="B86:E86"/>
     <mergeCell ref="B71:E71"/>
     <mergeCell ref="B85:E85"/>
@@ -3324,6 +3316,12 @@
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3369,7 +3367,7 @@
       <c r="E1" s="100"/>
       <c r="F1" s="100"/>
       <c r="G1" s="101" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H1" s="101"/>
       <c r="I1" s="101"/>
@@ -3378,7 +3376,7 @@
       </c>
       <c r="K1" s="103"/>
       <c r="L1" s="104" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M1" s="104"/>
       <c r="N1" s="98" t="s">
@@ -3386,7 +3384,7 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="102" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="Q1" s="102"/>
       <c r="R1" s="102"/>
@@ -3421,7 +3419,7 @@
         <v>62</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>8</v>
@@ -3430,10 +3428,10 @@
         <v>12</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N2" s="7" t="s">
         <v>13</v>
@@ -3442,16 +3440,16 @@
         <v>7</v>
       </c>
       <c r="P2" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="R2" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="S2" s="7" t="s">
         <v>265</v>
-      </c>
-      <c r="R2" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="S2" s="7" t="s">
-        <v>267</v>
       </c>
       <c r="T2" s="7" t="s">
         <v>6</v>
@@ -3468,16 +3466,16 @@
     </row>
     <row r="3" spans="1:23">
       <c r="B3" s="11" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D3" s="2">
         <v>1.1599999999999999</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F3" s="15">
         <v>0.21293704824312565</v>
@@ -3524,30 +3522,30 @@
         <v>1.9115679363188245</v>
       </c>
       <c r="T3" s="13" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="U3" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="V3" s="14">
         <v>45900</v>
       </c>
       <c r="W3" s="11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:23">
       <c r="B4" s="11" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D4" s="2">
         <v>15.38</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F4" s="15">
         <v>0.18912881948046301</v>
@@ -3594,30 +3592,30 @@
         <v>4.5287238180520148</v>
       </c>
       <c r="T4" s="13" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="V4" s="14">
         <v>45900</v>
       </c>
       <c r="W4" s="11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:23">
       <c r="B5" s="11" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D5" s="2">
         <v>6.11</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F5" s="15">
         <v>0.15926921829883645</v>
@@ -3664,30 +3662,30 @@
         <v>-3.8116415116695737</v>
       </c>
       <c r="T5" s="13" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="U5" s="11" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="V5" s="14">
         <v>45900</v>
       </c>
       <c r="W5" s="11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:23">
       <c r="B6" s="11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D6" s="2">
         <v>68.8</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F6" s="15">
         <v>0.15867473171661994</v>
@@ -3734,30 +3732,30 @@
         <v>15.284602440692964</v>
       </c>
       <c r="T6" s="13" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="U6" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="V6" s="14">
         <v>45900</v>
       </c>
       <c r="W6" s="11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="1:23">
       <c r="B7" s="11" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D7" s="2">
         <v>3.57</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F7" s="15">
         <v>0.14834835832623461</v>
@@ -3804,30 +3802,30 @@
         <v>1.6698226477450393</v>
       </c>
       <c r="T7" s="13" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="U7" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="V7" s="14">
         <v>45808</v>
       </c>
       <c r="W7" s="11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:23">
       <c r="B8" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D8" s="2">
         <v>55.65</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F8" s="15">
         <v>0.13918053194738822</v>
@@ -3874,30 +3872,30 @@
         <v>-2.6504984195888377</v>
       </c>
       <c r="T8" s="13" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="U8" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="V8" s="14">
         <v>45808</v>
       </c>
       <c r="W8" s="11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:23">
       <c r="B9" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D9" s="2">
         <v>21.72</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F9" s="15">
         <v>0.12990849663525528</v>
@@ -3944,30 +3942,30 @@
         <v>-38.360607814419353</v>
       </c>
       <c r="T9" s="13" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="U9" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="V9" s="14">
         <v>45900</v>
       </c>
       <c r="W9" s="11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" spans="1:23">
       <c r="B10" s="11" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D10" s="2">
         <v>17.82</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F10" s="15">
         <v>0.1209941874823961</v>
@@ -4014,30 +4012,30 @@
         <v>5.8696003638854428</v>
       </c>
       <c r="T10" s="16" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="U10" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="V10" s="14">
         <v>45808</v>
       </c>
       <c r="W10" s="11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11" spans="1:23">
       <c r="B11" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D11" s="2">
         <v>53.55</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F11" s="15">
         <v>0.11521291318800975</v>
@@ -4084,30 +4082,30 @@
         <v>1.3351546830236229</v>
       </c>
       <c r="T11" s="13" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="U11" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="V11" s="14">
         <v>45900</v>
       </c>
       <c r="W11" s="11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12" spans="1:23">
       <c r="B12" s="11" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D12" s="2">
         <v>8.15</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F12" s="15">
         <v>0.10840635294497614</v>
@@ -4154,30 +4152,30 @@
         <v>11.511512740854835</v>
       </c>
       <c r="T12" s="13" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="U12" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="V12" s="14">
         <v>45900</v>
       </c>
       <c r="W12" s="11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:23">
       <c r="B13" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D13" s="2">
         <v>2.2999999999999998</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F13" s="15">
         <v>0.10392879009854439</v>
@@ -4224,30 +4222,30 @@
         <v>1.8784842625371931</v>
       </c>
       <c r="T13" s="13" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U13" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="V13" s="14">
         <v>45900</v>
       </c>
       <c r="W13" s="11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:23">
       <c r="B14" s="11" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D14" s="2">
         <v>14.62</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F14" s="15">
         <v>0.10088016442395631</v>
@@ -4294,30 +4292,30 @@
         <v>-12.166449024907546</v>
       </c>
       <c r="T14" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="U14" s="11" t="s">
         <v>246</v>
-      </c>
-      <c r="U14" s="11" t="s">
-        <v>248</v>
       </c>
       <c r="V14" s="14">
         <v>45900</v>
       </c>
       <c r="W14" s="11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15" spans="1:23">
       <c r="B15" s="11" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D15" s="2">
         <v>28.49</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F15" s="15">
         <v>9.8376640230496193E-2</v>
@@ -4364,30 +4362,30 @@
         <v>-26.938493611476797</v>
       </c>
       <c r="T15" s="13" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="U15" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="V15" s="14">
         <v>45900</v>
       </c>
       <c r="W15" s="11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="16" spans="1:23">
       <c r="B16" s="11" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D16" s="2">
         <v>57.21</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F16" s="15">
         <v>9.1887382418681218E-2</v>
@@ -4434,16 +4432,16 @@
         <v>-13.312996389940134</v>
       </c>
       <c r="T16" s="13" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="U16" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="V16" s="14">
         <v>45716</v>
       </c>
       <c r="W16" s="11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="17" spans="2:22">
@@ -6532,7 +6530,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="20" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -6781,7 +6779,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D81F047E-EC38-4C3A-BA81-E6C9549453D6}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.59765625" style="65" customWidth="1"/>
@@ -6795,7 +6793,7 @@
     <row r="1" spans="1:8" ht="13.15">
       <c r="A1" s="63"/>
       <c r="B1" s="64" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="29.65" customHeight="1">
@@ -6803,22 +6801,22 @@
         <v>3</v>
       </c>
       <c r="C2" s="66" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D2" s="66" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E2" s="66" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G2" s="66" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H2" s="66" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6826,13 +6824,13 @@
         <v>30</v>
       </c>
       <c r="C3" s="75" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D3" s="74" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E3" s="76" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F3" s="71">
         <v>351395.62</v>
@@ -6843,12 +6841,12 @@
       </c>
       <c r="H3" s="91">
         <f>Portfolio_Mgmt!E61</f>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="B4" s="78" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C4" s="75">
         <f>VLOOKUP(B4,Opportunities!B$3:E$12,3,FALSE)</f>
@@ -6876,7 +6874,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="B5" s="78" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C5" s="75">
         <f>VLOOKUP(B5,Opportunities!B$3:E$12,3,FALSE)</f>
@@ -6887,6 +6885,7 @@
         <v>HKD</v>
       </c>
       <c r="E5" s="71">
+        <f>2000*10</f>
         <v>20000</v>
       </c>
       <c r="F5" s="76">
@@ -6904,7 +6903,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="B6" s="78" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C6" s="75">
         <f>VLOOKUP(B6,Opportunities!B$3:E$12,3,FALSE)</f>
@@ -6932,7 +6931,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="B7" s="78" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C7" s="75">
         <f>VLOOKUP(B7,Opportunities!B$3:E$12,3,FALSE)</f>
@@ -6969,7 +6968,7 @@
       <c r="C9" s="80"/>
       <c r="D9" s="79"/>
       <c r="E9" s="81" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F9" s="81">
         <f>SUM(F3:F7)</f>
@@ -6994,12 +6993,12 @@
     <row r="11" spans="1:8" ht="13.15">
       <c r="A11" s="63"/>
       <c r="B11" s="64" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="B12" s="78" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C12" s="75">
         <f>VLOOKUP(B12,Opportunities!B$3:E$12,3,FALSE)</f>
@@ -7010,16 +7009,16 @@
         <v>HKD</v>
       </c>
       <c r="E12" s="71">
-        <f>500*100</f>
-        <v>50000</v>
+        <f>500*140</f>
+        <v>70000</v>
       </c>
       <c r="F12" s="76">
-        <f>C12*E12</f>
-        <v>57999.999999999993</v>
+        <f>-C12*E12</f>
+        <v>-81200</v>
       </c>
       <c r="G12" s="73">
-        <f>F12/$F$9</f>
-        <v>6.4814925116076255E-2</v>
+        <f>-F12/$F$9</f>
+        <v>9.0740895162506774E-2</v>
       </c>
       <c r="H12" s="73">
         <f>VLOOKUP(B12,Opportunities!B$3:I$12,8,FALSE)</f>
@@ -7027,48 +7026,70 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="G13" s="88"/>
-      <c r="H13" s="88"/>
-    </row>
-    <row r="14" spans="1:8" ht="13.15">
-      <c r="B14" s="83" t="s">
-        <v>261</v>
-      </c>
-      <c r="C14" s="84" t="s">
-        <v>233</v>
-      </c>
-      <c r="D14" s="85" t="s">
-        <v>160</v>
-      </c>
-      <c r="E14" s="84" t="s">
-        <v>233</v>
-      </c>
-      <c r="F14" s="81">
-        <f>F3-F12</f>
-        <v>293395.62</v>
-      </c>
-      <c r="G14" s="89">
-        <f t="shared" ref="G14" si="0">F14/$F$9</f>
-        <v>0.32786922654628908</v>
-      </c>
-      <c r="H14" s="89">
+      <c r="B13" s="78" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" s="75">
+        <f>VLOOKUP(B13,Opportunities!B$3:E$12,3,FALSE)</f>
+        <v>8.15</v>
+      </c>
+      <c r="D13" s="74" t="str">
+        <f>VLOOKUP(B13,Opportunities!B$3:E$12,4,FALSE)</f>
+        <v>HKD</v>
+      </c>
+      <c r="E13" s="71">
+        <f>-2000*5</f>
+        <v>-10000</v>
+      </c>
+      <c r="F13" s="76">
+        <f>-C13*E13</f>
+        <v>81500</v>
+      </c>
+      <c r="G13" s="73">
+        <f>-F13/$F$9</f>
+        <v>-9.1076144775176129E-2</v>
+      </c>
+      <c r="H13" s="73">
+        <f>VLOOKUP(B13,Opportunities!B$3:I$12,8,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="G14" s="88"/>
+      <c r="H14" s="88"/>
+    </row>
+    <row r="15" spans="1:8" ht="13.15">
+      <c r="B15" s="83" t="s">
+        <v>259</v>
+      </c>
+      <c r="C15" s="84" t="s">
+        <v>231</v>
+      </c>
+      <c r="D15" s="85" t="s">
+        <v>158</v>
+      </c>
+      <c r="E15" s="84" t="s">
+        <v>231</v>
+      </c>
+      <c r="F15" s="81">
+        <f>F3+F12</f>
+        <v>270195.62</v>
+      </c>
+      <c r="G15" s="89">
+        <f t="shared" ref="G15" si="0">F15/$F$9</f>
+        <v>0.30194325649985859</v>
+      </c>
+      <c r="H15" s="89">
         <f>Portfolio_Mgmt!E61</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="B16" s="67"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="67"/>
-      <c r="E16" s="71"/>
-      <c r="F16" s="71"/>
-    </row>
-    <row r="26" spans="2:6">
-      <c r="B26" s="67"/>
-      <c r="C26" s="70"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="71"/>
-      <c r="F26" s="71"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="67"/>
+      <c r="C17" s="70"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="67"/>
@@ -7100,10 +7121,17 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="67"/>
-      <c r="C31" s="68"/>
+      <c r="C31" s="70"/>
       <c r="D31" s="67"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="67"/>
+      <c r="C32" s="68"/>
+      <c r="D32" s="67"/>
+      <c r="E32" s="69"/>
+      <c r="F32" s="69"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -7126,162 +7154,162 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="20" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="B3" s="105" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C3" s="105"/>
       <c r="D3" s="105"/>
     </row>
     <row r="5" spans="1:4">
       <c r="B5" s="106" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
+        <v>104</v>
+      </c>
+      <c r="C5" s="95"/>
+      <c r="D5" s="95"/>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="106" t="s">
-        <v>107</v>
-      </c>
-      <c r="C6" s="97"/>
-      <c r="D6" s="97"/>
+        <v>105</v>
+      </c>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5"/>
       <c r="B10" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="B11" s="105" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C11" s="105"/>
       <c r="D11" s="105"/>
     </row>
     <row r="12" spans="1:4">
       <c r="B12" s="105" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C12" s="105"/>
       <c r="D12" s="105"/>
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="12.4">
       <c r="B16" s="30" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C16" s="30" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="B17" s="26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="B18" s="26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="B19" s="26" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="B20" s="26" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="B21" s="26" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="B22" s="26" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="B23" s="26" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="B24" s="26" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="B25" s="26" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="5"/>
       <c r="B27" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="B28" s="105" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C28" s="105"/>
       <c r="D28" s="105"/>
     </row>
     <row r="29" spans="1:4">
       <c r="B29" s="105" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C29" s="105"/>
       <c r="D29" s="105"/>
@@ -7289,7 +7317,7 @@
     <row r="31" spans="1:4">
       <c r="A31" s="5"/>
       <c r="B31" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -7297,46 +7325,46 @@
         <v>66</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="B33" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="28" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="B36" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="5"/>
       <c r="B38" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="B39" s="24" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="B40" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="B41" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24EE2DD8-E7B4-4F28-B820-65A815E8153A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE10DE0-E295-4E54-ABDD-69DA49052A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="285">
   <si>
     <t>Name</t>
   </si>
@@ -1632,6 +1632,12 @@
   </si>
   <si>
     <t>Recession expected</t>
+  </si>
+  <si>
+    <t>3983.HK</t>
+  </si>
+  <si>
+    <t>中海石油化学</t>
   </si>
 </sst>
 </file>
@@ -2207,17 +2213,17 @@
     <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2627,12 +2633,12 @@
       <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="95" t="s">
         <v>219</v>
       </c>
-      <c r="C4" s="94"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="20" t="s">
@@ -2644,12 +2650,12 @@
       <c r="C6" s="61"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" s="94" t="s">
+      <c r="B7" s="95" t="s">
         <v>207</v>
       </c>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="23" t="s">
@@ -2738,12 +2744,12 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
-      <c r="B24" s="94" t="s">
+      <c r="B24" s="95" t="s">
         <v>218</v>
       </c>
-      <c r="C24" s="94"/>
-      <c r="D24" s="94"/>
-      <c r="E24" s="94"/>
+      <c r="C24" s="95"/>
+      <c r="D24" s="95"/>
+      <c r="E24" s="95"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
@@ -2843,20 +2849,20 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="B39" s="94" t="s">
+      <c r="B39" s="95" t="s">
         <v>154</v>
       </c>
-      <c r="C39" s="94"/>
-      <c r="D39" s="94"/>
-      <c r="E39" s="94"/>
+      <c r="C39" s="95"/>
+      <c r="D39" s="95"/>
+      <c r="E39" s="95"/>
     </row>
     <row r="40" spans="1:5" ht="46.6" customHeight="1">
-      <c r="B40" s="94" t="s">
+      <c r="B40" s="95" t="s">
         <v>233</v>
       </c>
-      <c r="C40" s="94"/>
-      <c r="D40" s="94"/>
-      <c r="E40" s="94"/>
+      <c r="C40" s="95"/>
+      <c r="D40" s="95"/>
+      <c r="E40" s="95"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="21" t="s">
@@ -2868,12 +2874,12 @@
       <c r="E42" s="21"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="B44" s="94" t="s">
+      <c r="B44" s="95" t="s">
         <v>206</v>
       </c>
-      <c r="C44" s="94"/>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="23" t="s">
@@ -3058,12 +3064,12 @@
       <c r="E69" s="21"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="B71" s="94" t="s">
+      <c r="B71" s="95" t="s">
         <v>194</v>
       </c>
-      <c r="C71" s="94"/>
-      <c r="D71" s="94"/>
-      <c r="E71" s="94"/>
+      <c r="C71" s="95"/>
+      <c r="D71" s="95"/>
+      <c r="E71" s="95"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="28" t="s">
@@ -3125,36 +3131,36 @@
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="B85" s="97" t="s">
+      <c r="B85" s="96" t="s">
         <v>190</v>
       </c>
-      <c r="C85" s="97"/>
-      <c r="D85" s="97"/>
-      <c r="E85" s="97"/>
+      <c r="C85" s="96"/>
+      <c r="D85" s="96"/>
+      <c r="E85" s="96"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="B86" s="96" t="s">
+      <c r="B86" s="94" t="s">
         <v>188</v>
       </c>
-      <c r="C86" s="96"/>
-      <c r="D86" s="96"/>
-      <c r="E86" s="96"/>
+      <c r="C86" s="94"/>
+      <c r="D86" s="94"/>
+      <c r="E86" s="94"/>
     </row>
     <row r="87" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B87" s="94" t="s">
+      <c r="B87" s="95" t="s">
         <v>187</v>
       </c>
-      <c r="C87" s="94"/>
-      <c r="D87" s="94"/>
-      <c r="E87" s="94"/>
+      <c r="C87" s="95"/>
+      <c r="D87" s="95"/>
+      <c r="E87" s="95"/>
     </row>
     <row r="88" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B88" s="94" t="s">
+      <c r="B88" s="95" t="s">
         <v>223</v>
       </c>
-      <c r="C88" s="94"/>
-      <c r="D88" s="94"/>
-      <c r="E88" s="94"/>
+      <c r="C88" s="95"/>
+      <c r="D88" s="95"/>
+      <c r="E88" s="95"/>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="24" t="s">
@@ -3187,12 +3193,12 @@
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="B97" s="95" t="s">
+      <c r="B97" s="97" t="s">
         <v>209</v>
       </c>
-      <c r="C97" s="95"/>
-      <c r="D97" s="95"/>
-      <c r="E97" s="95"/>
+      <c r="C97" s="97"/>
+      <c r="D97" s="97"/>
+      <c r="E97" s="97"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
@@ -3200,20 +3206,20 @@
       </c>
     </row>
     <row r="100" spans="1:5" ht="12.4">
-      <c r="B100" s="95" t="s">
+      <c r="B100" s="97" t="s">
         <v>210</v>
       </c>
-      <c r="C100" s="95"/>
-      <c r="D100" s="95"/>
-      <c r="E100" s="95"/>
+      <c r="C100" s="97"/>
+      <c r="D100" s="97"/>
+      <c r="E100" s="97"/>
     </row>
     <row r="101" spans="1:5" ht="58.5" customHeight="1">
-      <c r="B101" s="94" t="s">
+      <c r="B101" s="95" t="s">
         <v>217</v>
       </c>
-      <c r="C101" s="94"/>
-      <c r="D101" s="94"/>
-      <c r="E101" s="94"/>
+      <c r="C101" s="95"/>
+      <c r="D101" s="95"/>
+      <c r="E101" s="95"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="28" t="s">
@@ -3253,7 +3259,7 @@
         <v>173</v>
       </c>
       <c r="C111" s="44">
-        <v>0.4</v>
+        <v>0.30000000000000004</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -3261,7 +3267,7 @@
         <v>174</v>
       </c>
       <c r="C112" s="44">
-        <v>0.12601445728348953</v>
+        <v>0.14930888295373529</v>
       </c>
       <c r="D112" s="61" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
@@ -3269,12 +3275,12 @@
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B114" s="94" t="s">
+      <c r="B114" s="95" t="s">
         <v>215</v>
       </c>
-      <c r="C114" s="94"/>
-      <c r="D114" s="94"/>
-      <c r="E114" s="94"/>
+      <c r="C114" s="95"/>
+      <c r="D114" s="95"/>
+      <c r="E114" s="95"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="21" t="s">
@@ -3307,6 +3313,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
     <mergeCell ref="B86:E86"/>
     <mergeCell ref="B71:E71"/>
     <mergeCell ref="B85:E85"/>
@@ -3316,12 +3328,6 @@
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3478,33 +3484,33 @@
         <v>158</v>
       </c>
       <c r="F3" s="15">
-        <v>0.21293704824312565</v>
+        <v>0.21955254305698646</v>
       </c>
       <c r="G3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$10</f>
-        <v>9.5537048243125644E-2</v>
+        <v>0.10215254305698646</v>
       </c>
       <c r="H3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$11</f>
-        <v>0.17843704824312565</v>
+        <v>0.18505254305698646</v>
       </c>
       <c r="I3" s="15">
-        <v>0.21293704824312568</v>
+        <v>0.21955254305698646</v>
       </c>
       <c r="J3" s="2">
-        <v>0.9421991685622978</v>
+        <v>0.9576999852710768</v>
       </c>
       <c r="K3" s="2">
-        <v>2.0700115733313686</v>
+        <v>2.1040668676405563</v>
       </c>
       <c r="L3" s="2">
-        <v>1.197923364196394</v>
+        <v>1.2176312891438406</v>
       </c>
       <c r="M3" s="86">
-        <v>1.6432419261953275</v>
+        <v>1.6702761167953912</v>
       </c>
       <c r="N3" s="4">
-        <v>6.2929569514617121E-3</v>
+        <v>8.265220900462859E-3</v>
       </c>
       <c r="O3" s="4">
         <v>0</v>
@@ -3536,63 +3542,63 @@
     </row>
     <row r="4" spans="1:23">
       <c r="B4" s="11" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="D4" s="2">
-        <v>15.38</v>
+        <v>1.95</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>158</v>
       </c>
       <c r="F4" s="15">
-        <v>0.18912881948046301</v>
+        <v>0.20182066703946511</v>
       </c>
       <c r="G4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$10</f>
-        <v>7.1728819480463002E-2</v>
+        <v>8.4420667039465103E-2</v>
       </c>
       <c r="H4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$11</f>
-        <v>0.154628819480463</v>
+        <v>0.1673206670394651</v>
       </c>
       <c r="I4" s="15">
-        <v>0.18912881948046303</v>
+        <v>0.20182066703946511</v>
       </c>
       <c r="J4" s="2">
-        <v>11.866845734983505</v>
+        <v>1.5407194269481685</v>
       </c>
       <c r="K4" s="2">
-        <v>23.899333440997744</v>
+        <v>3.3849605810051271</v>
       </c>
       <c r="L4" s="2">
-        <v>14.977385795894701</v>
+        <v>1.9588892251187078</v>
       </c>
       <c r="M4" s="86">
-        <v>20.375014060112886</v>
+        <v>2.6870908437842354</v>
       </c>
       <c r="N4" s="4">
-        <v>6.5387552793081283E-2</v>
+        <v>6.0823671959654366E-2</v>
       </c>
       <c r="O4" s="4">
-        <v>3.5396140526234639E-2</v>
+        <v>0</v>
       </c>
       <c r="P4" s="15">
-        <v>0.36794481423679237</v>
+        <v>0.23422582328431374</v>
       </c>
       <c r="Q4" s="15">
-        <v>7.4171010848313429E-2</v>
+        <v>0.10863424600069688</v>
       </c>
       <c r="R4" s="92">
-        <v>0.60402076709908736</v>
+        <v>2.2824569622635926</v>
       </c>
       <c r="S4" s="86">
-        <v>4.5287238180520148</v>
+        <v>1.6893987527114966</v>
       </c>
       <c r="T4" s="13" t="s">
-        <v>244</v>
+        <v>159</v>
       </c>
       <c r="U4" s="11" t="s">
         <v>160</v>
@@ -3606,66 +3612,66 @@
     </row>
     <row r="5" spans="1:23">
       <c r="B5" s="11" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="D5" s="2">
-        <v>6.11</v>
+        <v>15.38</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>158</v>
       </c>
       <c r="F5" s="15">
-        <v>0.15926921829883645</v>
+        <v>0.18912881948046301</v>
       </c>
       <c r="G5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$10</f>
-        <v>4.1869218298836441E-2</v>
+        <v>7.1728819480463002E-2</v>
       </c>
       <c r="H5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$11</f>
-        <v>0.12476921829883644</v>
+        <v>0.154628819480463</v>
       </c>
       <c r="I5" s="15">
-        <v>0.15926921829883645</v>
+        <v>0.18912881948046303</v>
       </c>
       <c r="J5" s="2">
-        <v>4.4306821973721187</v>
+        <v>11.866845734983505</v>
       </c>
       <c r="K5" s="2">
-        <v>7.970870141114629</v>
+        <v>23.899333440997744</v>
       </c>
       <c r="L5" s="2">
-        <v>5.5437094670052947</v>
+        <v>14.977385795894701</v>
       </c>
       <c r="M5" s="86">
-        <v>7.4664546878097049</v>
+        <v>20.375014060112886</v>
       </c>
       <c r="N5" s="4">
-        <v>0.12672849511458295</v>
+        <v>6.5387552793081283E-2</v>
       </c>
       <c r="O5" s="4">
-        <v>7.2330525434368076E-2</v>
+        <v>3.5396140526234639E-2</v>
       </c>
       <c r="P5" s="15">
-        <v>0.61007460831657279</v>
+        <v>0.36794481423679237</v>
       </c>
       <c r="Q5" s="15">
-        <v>0.16360901428944893</v>
+        <v>7.4171010848313429E-2</v>
       </c>
       <c r="R5" s="92">
-        <v>1.1309485990394448</v>
+        <v>0.60402076709908736</v>
       </c>
       <c r="S5" s="86">
-        <v>-3.8116415116695737</v>
+        <v>4.5287238180520148</v>
       </c>
       <c r="T5" s="13" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="U5" s="11" t="s">
-        <v>236</v>
+        <v>160</v>
       </c>
       <c r="V5" s="14">
         <v>45900</v>
@@ -3676,203 +3682,203 @@
     </row>
     <row r="6" spans="1:23">
       <c r="B6" s="11" t="s">
-        <v>274</v>
+        <v>234</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>275</v>
+        <v>235</v>
       </c>
       <c r="D6" s="2">
-        <v>68.8</v>
+        <v>6.11</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>273</v>
+        <v>158</v>
       </c>
       <c r="F6" s="15">
-        <v>0.15867473171661994</v>
+        <v>0.15926921829883645</v>
       </c>
       <c r="G6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$10</f>
-        <v>4.1274731716619939E-2</v>
+        <v>4.1869218298836441E-2</v>
       </c>
       <c r="H6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$11</f>
-        <v>0.12417473171661994</v>
+        <v>0.12476921829883644</v>
       </c>
       <c r="I6" s="15">
-        <v>0</v>
+        <v>8.9497970423085382E-2</v>
       </c>
       <c r="J6" s="2">
-        <v>49.746673136282389</v>
+        <v>4.4306821973721187</v>
       </c>
       <c r="K6" s="2">
-        <v>90.751910880412424</v>
+        <v>7.970870141114629</v>
       </c>
       <c r="L6" s="2">
-        <v>62.307286389127562</v>
+        <v>5.5437094670052947</v>
       </c>
       <c r="M6" s="86">
-        <v>84.017562490801396</v>
+        <v>7.4664546878097049</v>
       </c>
       <c r="N6" s="4">
-        <v>7.6744210192842666E-2</v>
+        <v>0.12672849511458295</v>
       </c>
       <c r="O6" s="4">
-        <v>6.7543604651162797E-2</v>
+        <v>7.2330525434368076E-2</v>
       </c>
       <c r="P6" s="15">
-        <v>0.30279158651211824</v>
+        <v>0.61007460831657279</v>
       </c>
       <c r="Q6" s="15">
-        <v>7.7640983998987034E-4</v>
+        <v>0.16360901428944893</v>
       </c>
       <c r="R6" s="92">
-        <v>3.8209153156820415E-3</v>
+        <v>1.1309485990394448</v>
       </c>
       <c r="S6" s="86">
-        <v>15.284602440692964</v>
+        <v>-3.8116415116695737</v>
       </c>
       <c r="T6" s="13" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="U6" s="11" t="s">
-        <v>160</v>
+        <v>236</v>
       </c>
       <c r="V6" s="14">
         <v>45900</v>
       </c>
       <c r="W6" s="11" t="s">
-        <v>245</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:23">
       <c r="B7" s="11" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="D7" s="2">
-        <v>3.57</v>
+        <v>68.8</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>158</v>
+        <v>273</v>
       </c>
       <c r="F7" s="15">
-        <v>0.14834835832623461</v>
+        <v>0.15867473171661994</v>
       </c>
       <c r="G7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$10</f>
-        <v>3.0948358326234604E-2</v>
+        <v>4.1274731716619939E-2</v>
       </c>
       <c r="H7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$11</f>
-        <v>0.11384835832623461</v>
+        <v>0.12417473171661994</v>
       </c>
       <c r="I7" s="15">
-        <v>3.8664913977574877E-2</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>2.4911701525888064</v>
+        <v>49.746673136282389</v>
       </c>
       <c r="K7" s="2">
-        <v>4.9623808252376094</v>
+        <v>90.751910880412424</v>
       </c>
       <c r="L7" s="2">
-        <v>3.1413777923828756</v>
+        <v>62.307286389127562</v>
       </c>
       <c r="M7" s="86">
-        <v>4.2691663056616189</v>
+        <v>84.017562490801396</v>
       </c>
       <c r="N7" s="4">
-        <v>7.9541327003833207E-2</v>
+        <v>7.6744210192842666E-2</v>
       </c>
       <c r="O7" s="4">
-        <v>3.5854341736694682E-2</v>
+        <v>6.7543604651162797E-2</v>
       </c>
       <c r="P7" s="15">
-        <v>0.40000523965699897</v>
+        <v>0.30279158651211824</v>
       </c>
       <c r="Q7" s="15">
-        <v>0.10646655543311496</v>
+        <v>7.7640983998987034E-4</v>
       </c>
       <c r="R7" s="92">
-        <v>0.9804830051022897</v>
+        <v>3.8209153156820415E-3</v>
       </c>
       <c r="S7" s="86">
-        <v>1.6698226477450393</v>
+        <v>15.284602440692964</v>
       </c>
       <c r="T7" s="13" t="s">
-        <v>159</v>
+        <v>240</v>
       </c>
       <c r="U7" s="11" t="s">
         <v>160</v>
       </c>
       <c r="V7" s="14">
-        <v>45808</v>
+        <v>45900</v>
       </c>
       <c r="W7" s="11" t="s">
-        <v>161</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" spans="1:23">
       <c r="B8" s="11" t="s">
-        <v>247</v>
+        <v>279</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>248</v>
+        <v>280</v>
       </c>
       <c r="D8" s="2">
-        <v>55.65</v>
+        <v>3.57</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>158</v>
       </c>
       <c r="F8" s="15">
-        <v>0.13918053194738822</v>
+        <v>0.14834835832623461</v>
       </c>
       <c r="G8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$10</f>
-        <v>2.1780531947388215E-2</v>
+        <v>3.0948358326234604E-2</v>
       </c>
       <c r="H8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$11</f>
-        <v>0.10468053194738822</v>
+        <v>0.11384835832623461</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
       </c>
       <c r="J8" s="2">
-        <v>38.719486313520228</v>
+        <v>2.4911701525888064</v>
       </c>
       <c r="K8" s="2">
-        <v>64.892912330803952</v>
+        <v>4.9623808252376094</v>
       </c>
       <c r="L8" s="2">
-        <v>48.204328663659695</v>
+        <v>3.1413777923828756</v>
       </c>
       <c r="M8" s="86">
-        <v>64.544120328141631</v>
+        <v>4.2691663056616189</v>
       </c>
       <c r="N8" s="4">
-        <v>9.4703343132953519E-2</v>
+        <v>7.9541327003833207E-2</v>
       </c>
       <c r="O8" s="4">
-        <v>9.085516621743038E-2</v>
+        <v>3.5854341736694682E-2</v>
       </c>
       <c r="P8" s="15">
-        <v>1.2907496012759174</v>
+        <v>0.40000523965699897</v>
       </c>
       <c r="Q8" s="15">
-        <v>0.24768740031897937</v>
+        <v>0.10646655543311496</v>
       </c>
       <c r="R8" s="92">
-        <v>0.73855199466278643</v>
+        <v>0.9804830051022897</v>
       </c>
       <c r="S8" s="86">
-        <v>-2.6504984195888377</v>
+        <v>1.6698226477450393</v>
       </c>
       <c r="T8" s="13" t="s">
-        <v>244</v>
+        <v>159</v>
       </c>
       <c r="U8" s="11" t="s">
         <v>160</v>
@@ -3886,346 +3892,346 @@
     </row>
     <row r="9" spans="1:23">
       <c r="B9" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D9" s="2">
-        <v>21.72</v>
+        <v>55.65</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>251</v>
+        <v>158</v>
       </c>
       <c r="F9" s="15">
-        <v>0.12990849663525528</v>
+        <v>0.13918053194738822</v>
       </c>
       <c r="G9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$10</f>
-        <v>1.2508496635255273E-2</v>
+        <v>2.1780531947388215E-2</v>
       </c>
       <c r="H9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$11</f>
-        <v>9.5408496635255274E-2</v>
+        <v>0.10468053194738822</v>
       </c>
       <c r="I9" s="15">
         <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>14.418941896437474</v>
+        <v>38.719486313520228</v>
       </c>
       <c r="K9" s="2">
-        <v>29.309951346473134</v>
+        <v>64.892912330803952</v>
       </c>
       <c r="L9" s="2">
-        <v>18.21218480698677</v>
+        <v>48.204328663659695</v>
       </c>
       <c r="M9" s="86">
-        <v>24.796949133193245</v>
+        <v>64.544120328141631</v>
       </c>
       <c r="N9" s="4">
-        <v>0.2098969404851839</v>
+        <v>9.4703343132953519E-2</v>
       </c>
       <c r="O9" s="4">
-        <v>2.7329650092081034E-2</v>
+        <v>9.085516621743038E-2</v>
       </c>
       <c r="P9" s="15">
-        <v>1.4851905363915479</v>
+        <v>1.2907496012759174</v>
       </c>
       <c r="Q9" s="15">
-        <v>0.95241105291674188</v>
+        <v>0.24768740031897937</v>
       </c>
       <c r="R9" s="92">
-        <v>4.0148803043206254</v>
+        <v>0.73855199466278643</v>
       </c>
       <c r="S9" s="86">
-        <v>-38.360607814419353</v>
+        <v>-2.6504984195888377</v>
       </c>
       <c r="T9" s="13" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="U9" s="11" t="s">
         <v>160</v>
       </c>
       <c r="V9" s="14">
-        <v>45900</v>
+        <v>45808</v>
       </c>
       <c r="W9" s="11" t="s">
-        <v>245</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:23">
       <c r="B10" s="11" t="s">
-        <v>156</v>
+        <v>249</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>157</v>
+        <v>250</v>
       </c>
       <c r="D10" s="2">
-        <v>17.82</v>
+        <v>21.72</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>158</v>
+        <v>251</v>
       </c>
       <c r="F10" s="15">
-        <v>0.1209941874823961</v>
+        <v>0.12990849663525528</v>
       </c>
       <c r="G10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$10</f>
-        <v>3.594187482396094E-3</v>
+        <v>1.2508496635255273E-2</v>
       </c>
       <c r="H10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$11</f>
-        <v>8.6494187482396095E-2</v>
+        <v>9.5408496635255274E-2</v>
       </c>
       <c r="I10" s="15">
         <v>0</v>
       </c>
       <c r="J10" s="2">
-        <v>11.804906901225705</v>
+        <v>14.418941896437474</v>
       </c>
       <c r="K10" s="2">
-        <v>20.508980461992877</v>
+        <v>29.309951346473134</v>
       </c>
       <c r="L10" s="2">
-        <v>14.733437767356989</v>
+        <v>18.21218480698677</v>
       </c>
       <c r="M10" s="86">
-        <v>19.785541823839793</v>
+        <v>24.796949133193245</v>
       </c>
       <c r="N10" s="4">
-        <v>9.696891242253812E-2</v>
+        <v>0.2098969404851839</v>
       </c>
       <c r="O10" s="4">
-        <v>7.6318742985409652E-2</v>
+        <v>2.7329650092081034E-2</v>
       </c>
       <c r="P10" s="15">
-        <v>0.31018327415220487</v>
+        <v>1.4851905363915479</v>
       </c>
       <c r="Q10" s="15">
-        <v>0.15818859882129041</v>
+        <v>0.95241105291674188</v>
       </c>
       <c r="R10" s="92">
-        <v>1.4550387206421544</v>
+        <v>4.0148803043206254</v>
       </c>
       <c r="S10" s="86">
-        <v>5.8696003638854428</v>
+        <v>-38.360607814419353</v>
       </c>
       <c r="T10" s="16" t="s">
-        <v>159</v>
+        <v>252</v>
       </c>
       <c r="U10" s="11" t="s">
         <v>160</v>
       </c>
       <c r="V10" s="14">
-        <v>45808</v>
+        <v>45900</v>
       </c>
       <c r="W10" s="11" t="s">
-        <v>161</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" spans="1:23">
       <c r="B11" s="11" t="s">
-        <v>238</v>
+        <v>156</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>239</v>
+        <v>157</v>
       </c>
       <c r="D11" s="2">
-        <v>53.55</v>
+        <v>17.82</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>158</v>
       </c>
       <c r="F11" s="15">
-        <v>0.11521291318800975</v>
+        <v>0.1209941874823961</v>
       </c>
       <c r="G11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.1870868119902576E-3</v>
+        <v>3.594187482396094E-3</v>
       </c>
       <c r="H11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$11</f>
-        <v>8.0712913188009744E-2</v>
+        <v>8.6494187482396095E-2</v>
       </c>
       <c r="I11" s="15">
         <v>0</v>
       </c>
       <c r="J11" s="2">
-        <v>34.394984382396515</v>
+        <v>11.804906901225705</v>
       </c>
       <c r="K11" s="2">
-        <v>67.394305644906538</v>
+        <v>20.508980461992877</v>
       </c>
       <c r="L11" s="2">
-        <v>43.315384624827814</v>
+        <v>14.733437767356989</v>
       </c>
       <c r="M11" s="86">
-        <v>58.777638274888893</v>
+        <v>19.785541823839793</v>
       </c>
       <c r="N11" s="4">
-        <v>4.2328511280438831E-2</v>
+        <v>9.696891242253812E-2</v>
       </c>
       <c r="O11" s="4">
-        <v>3.8244420777520896E-2</v>
+        <v>7.6318742985409652E-2</v>
       </c>
       <c r="P11" s="15">
-        <v>0.72207550313588764</v>
+        <v>0.31018327415220487</v>
       </c>
       <c r="Q11" s="15">
-        <v>9.5579625064196368E-3</v>
+        <v>0.15818859882129041</v>
       </c>
       <c r="R11" s="92">
-        <v>7.3592411949940734E-2</v>
+        <v>1.4550387206421544</v>
       </c>
       <c r="S11" s="86">
-        <v>1.3351546830236229</v>
+        <v>5.8696003638854428</v>
       </c>
       <c r="T11" s="13" t="s">
-        <v>240</v>
+        <v>159</v>
       </c>
       <c r="U11" s="11" t="s">
         <v>160</v>
       </c>
       <c r="V11" s="14">
-        <v>45900</v>
+        <v>45808</v>
       </c>
       <c r="W11" s="11" t="s">
-        <v>245</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:23">
       <c r="B12" s="11" t="s">
-        <v>162</v>
+        <v>238</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>163</v>
+        <v>239</v>
       </c>
       <c r="D12" s="2">
-        <v>8.15</v>
+        <v>53.55</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>158</v>
       </c>
       <c r="F12" s="15">
-        <v>0.10840635294497614</v>
+        <v>0.11521291318800975</v>
       </c>
       <c r="G12" s="15">
         <f>F12 - Portfolio_Mgmt!$C$10</f>
-        <v>-8.9936470550238679E-3</v>
+        <v>-2.1870868119902576E-3</v>
       </c>
       <c r="H12" s="15">
         <f>F12 - Portfolio_Mgmt!$C$11</f>
-        <v>7.3906352944976134E-2</v>
+        <v>8.0712913188009744E-2</v>
       </c>
       <c r="I12" s="15">
         <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>5.2239462882061574</v>
+        <v>34.394984382396515</v>
       </c>
       <c r="K12" s="2">
-        <v>9.1628099951889297</v>
+        <v>67.394305644906538</v>
       </c>
       <c r="L12" s="2">
-        <v>6.5243113398084081</v>
+        <v>43.315384624827814</v>
       </c>
       <c r="M12" s="86">
-        <v>8.7684502451266084</v>
+        <v>58.777638274888893</v>
       </c>
       <c r="N12" s="4">
-        <v>3.7901640734020248E-2</v>
+        <v>4.2328511280438831E-2</v>
       </c>
       <c r="O12" s="4">
-        <v>7.1165644171779133E-2</v>
+        <v>3.8244420777520896E-2</v>
       </c>
       <c r="P12" s="15">
-        <v>8.3114411724224596E-2</v>
+        <v>0.72207550313588764</v>
       </c>
       <c r="Q12" s="15">
-        <v>1.8509098960546238E-2</v>
+        <v>9.5579625064196368E-3</v>
       </c>
       <c r="R12" s="92">
-        <v>1.1933697905849452</v>
+        <v>7.3592411949940734E-2</v>
       </c>
       <c r="S12" s="86">
-        <v>11.511512740854835</v>
+        <v>1.3351546830236229</v>
       </c>
       <c r="T12" s="13" t="s">
-        <v>164</v>
+        <v>240</v>
       </c>
       <c r="U12" s="11" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="V12" s="14">
         <v>45900</v>
       </c>
       <c r="W12" s="11" t="s">
-        <v>161</v>
+        <v>245</v>
       </c>
     </row>
     <row r="13" spans="1:23">
       <c r="B13" s="11" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D13" s="2">
-        <v>2.2999999999999998</v>
+        <v>8.15</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>158</v>
       </c>
       <c r="F13" s="15">
-        <v>0.10392879009854439</v>
+        <v>0.10840635294497614</v>
       </c>
       <c r="G13" s="15">
         <f>F13 - Portfolio_Mgmt!$C$10</f>
-        <v>-1.3471209901455616E-2</v>
+        <v>-8.9936470550238679E-3</v>
       </c>
       <c r="H13" s="15">
         <f>F13 - Portfolio_Mgmt!$C$11</f>
-        <v>6.9428790098544385E-2</v>
+        <v>7.3906352944976134E-2</v>
       </c>
       <c r="I13" s="15">
         <v>0</v>
       </c>
       <c r="J13" s="2">
-        <v>1.4428843799519049</v>
+        <v>5.2239462882061574</v>
       </c>
       <c r="K13" s="2">
-        <v>2.7168715485394852</v>
+        <v>9.1628099951889297</v>
       </c>
       <c r="L13" s="2">
-        <v>1.8114973282765074</v>
+        <v>6.5243113398084081</v>
       </c>
       <c r="M13" s="2">
-        <v>2.4494218673596402</v>
+        <v>8.7684502451266084</v>
       </c>
       <c r="N13" s="4">
-        <v>3.5980231621691262E-2</v>
+        <v>3.7901640734020248E-2</v>
       </c>
       <c r="O13" s="4">
-        <v>4.9378384462771097E-2</v>
+        <v>7.1165644171779133E-2</v>
       </c>
       <c r="P13" s="15">
-        <v>0.20351769929714394</v>
+        <v>8.3114411724224596E-2</v>
       </c>
       <c r="Q13" s="15">
-        <v>1.0763175939415467E-2</v>
+        <v>1.8509098960546238E-2</v>
       </c>
       <c r="R13" s="92">
-        <v>0.29882156160837919</v>
+        <v>1.1933697905849452</v>
       </c>
       <c r="S13" s="86">
-        <v>1.8784842625371931</v>
+        <v>11.511512740854835</v>
       </c>
       <c r="T13" s="13" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="U13" s="11" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="V13" s="14">
         <v>45900</v>
@@ -4236,136 +4242,136 @@
     </row>
     <row r="14" spans="1:23">
       <c r="B14" s="11" t="s">
-        <v>242</v>
+        <v>166</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>243</v>
+        <v>167</v>
       </c>
       <c r="D14" s="2">
-        <v>14.62</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>158</v>
       </c>
       <c r="F14" s="15">
-        <v>0.10088016442395631</v>
+        <v>0.10392879009854439</v>
       </c>
       <c r="G14" s="15">
         <f>F14 - Portfolio_Mgmt!$C$10</f>
-        <v>-1.6519835576043695E-2</v>
+        <v>-1.3471209901455616E-2</v>
       </c>
       <c r="H14" s="15">
         <f>F14 - Portfolio_Mgmt!$C$11</f>
-        <v>6.6380164423956306E-2</v>
+        <v>6.9428790098544385E-2</v>
       </c>
       <c r="I14" s="15">
         <v>0</v>
       </c>
       <c r="J14" s="2">
-        <v>9.1359587259076722</v>
+        <v>1.4428843799519049</v>
       </c>
       <c r="K14" s="2">
-        <v>16.73836897721916</v>
+        <v>2.7168715485394852</v>
       </c>
       <c r="L14" s="2">
-        <v>11.446356334964792</v>
+        <v>1.8114973282765074</v>
       </c>
       <c r="M14" s="2">
-        <v>15.440419547734052</v>
+        <v>2.4494218673596402</v>
       </c>
       <c r="N14" s="4">
-        <v>0.10527247112980752</v>
+        <v>3.5980231621691262E-2</v>
       </c>
       <c r="O14" s="4">
-        <v>5.7142383036935702E-2</v>
+        <v>4.9378384462771097E-2</v>
       </c>
       <c r="P14" s="15">
-        <v>2.2875080906148866</v>
+        <v>0.20351769929714394</v>
       </c>
       <c r="Q14" s="15">
-        <v>1.5035598705501618</v>
+        <v>1.0763175939415467E-2</v>
       </c>
       <c r="R14" s="92">
-        <v>4.1998196571663646</v>
+        <v>0.29882156160837919</v>
       </c>
       <c r="S14" s="86">
-        <v>-12.166449024907546</v>
+        <v>1.8784842625371931</v>
       </c>
       <c r="T14" s="13" t="s">
-        <v>244</v>
+        <v>168</v>
       </c>
       <c r="U14" s="11" t="s">
-        <v>246</v>
+        <v>169</v>
       </c>
       <c r="V14" s="14">
         <v>45900</v>
       </c>
       <c r="W14" s="11" t="s">
-        <v>245</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:23">
       <c r="B15" s="11" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="D15" s="2">
-        <v>28.49</v>
+        <v>14.62</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>251</v>
+        <v>158</v>
       </c>
       <c r="F15" s="15">
-        <v>9.8376640230496193E-2</v>
+        <v>0.10088016442395631</v>
       </c>
       <c r="G15" s="15">
         <f>F15 - Portfolio_Mgmt!$C$10</f>
-        <v>-1.9023359769503811E-2</v>
+        <v>-1.6519835576043695E-2</v>
       </c>
       <c r="H15" s="15">
         <f>F15 - Portfolio_Mgmt!$C$11</f>
-        <v>6.387664023049619E-2</v>
+        <v>6.6380164423956306E-2</v>
       </c>
       <c r="I15" s="15">
         <v>0</v>
       </c>
       <c r="J15" s="2">
-        <v>17.682685147645955</v>
+        <v>9.1359587259076722</v>
       </c>
       <c r="K15" s="2">
-        <v>32.464859269378167</v>
+        <v>16.73836897721916</v>
       </c>
       <c r="L15" s="2">
-        <v>22.157904669779033</v>
+        <v>11.446356334964792</v>
       </c>
       <c r="M15" s="2">
-        <v>29.895007167811503</v>
+        <v>15.440419547734052</v>
       </c>
       <c r="N15" s="4">
-        <v>8.9124865124008343E-2</v>
+        <v>0.10527247112980752</v>
       </c>
       <c r="O15" s="4">
-        <v>5.616005616005617E-2</v>
+        <v>5.7142383036935702E-2</v>
       </c>
       <c r="P15" s="15">
-        <v>0.78990369994931575</v>
+        <v>2.2875080906148866</v>
       </c>
       <c r="Q15" s="15">
-        <v>0.40281804358844397</v>
+        <v>1.5035598705501618</v>
       </c>
       <c r="R15" s="92">
-        <v>3.955391512509995</v>
+        <v>4.1998196571663646</v>
       </c>
       <c r="S15" s="86">
-        <v>-26.938493611476797</v>
+        <v>-12.166449024907546</v>
       </c>
       <c r="T15" s="13" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="U15" s="11" t="s">
-        <v>160</v>
+        <v>246</v>
       </c>
       <c r="V15" s="14">
         <v>45900</v>
@@ -4376,85 +4382,145 @@
     </row>
     <row r="16" spans="1:23">
       <c r="B16" s="11" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="D16" s="2">
-        <v>57.21</v>
+        <v>28.49</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="F16" s="15">
-        <v>9.1887382418681218E-2</v>
+        <v>9.8376640230496193E-2</v>
       </c>
       <c r="G16" s="15">
         <f>F16 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.5512617581318786E-2</v>
+        <v>-1.9023359769503811E-2</v>
       </c>
       <c r="H16" s="15">
         <f>F16 - Portfolio_Mgmt!$C$11</f>
-        <v>5.7387382418681215E-2</v>
+        <v>6.387664023049619E-2</v>
       </c>
       <c r="I16" s="15">
         <v>0</v>
       </c>
       <c r="J16" s="2">
-        <v>34.669224296258527</v>
+        <v>17.682685147645955</v>
       </c>
       <c r="K16" s="2">
-        <v>66.592285778879997</v>
+        <v>32.464859269378167</v>
       </c>
       <c r="L16" s="2">
-        <v>43.592757973888887</v>
+        <v>22.157904669779033</v>
       </c>
       <c r="M16" s="2">
-        <v>59.048136223898794</v>
+        <v>29.895007167811503</v>
       </c>
       <c r="N16" s="4">
-        <v>8.0319983221959892E-2</v>
+        <v>8.9124865124008343E-2</v>
       </c>
       <c r="O16" s="4">
-        <v>4.195070791819612E-2</v>
+        <v>5.616005616005617E-2</v>
       </c>
       <c r="P16" s="15">
-        <v>3.4701988818540461</v>
+        <v>0.78990369994931575</v>
       </c>
       <c r="Q16" s="15">
-        <v>5.0341856510546588E-2</v>
+        <v>0.40281804358844397</v>
       </c>
       <c r="R16" s="92">
-        <v>3.9546057100127742E-2</v>
+        <v>3.955391512509995</v>
       </c>
       <c r="S16" s="86">
-        <v>-13.312996389940134</v>
+        <v>-26.938493611476797</v>
       </c>
       <c r="T16" s="13" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="U16" s="11" t="s">
         <v>160</v>
       </c>
       <c r="V16" s="14">
-        <v>45716</v>
+        <v>45900</v>
       </c>
       <c r="W16" s="11" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="17" spans="2:22">
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="E17" s="12"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="T17" s="13"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="14"/>
-    </row>
-    <row r="18" spans="2:22">
+    <row r="17" spans="2:23">
+      <c r="B17" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="D17" s="2">
+        <v>57.21</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="F17" s="15">
+        <v>9.1887382418681218E-2</v>
+      </c>
+      <c r="G17" s="15">
+        <f>F17 - Portfolio_Mgmt!$C$10</f>
+        <v>-2.5512617581318786E-2</v>
+      </c>
+      <c r="H17" s="15">
+        <f>F17 - Portfolio_Mgmt!$C$11</f>
+        <v>5.7387382418681215E-2</v>
+      </c>
+      <c r="I17" s="15">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2">
+        <v>34.669224296258527</v>
+      </c>
+      <c r="K17" s="2">
+        <v>66.592285778879997</v>
+      </c>
+      <c r="L17" s="2">
+        <v>43.592757973888887</v>
+      </c>
+      <c r="M17" s="2">
+        <v>59.048136223898794</v>
+      </c>
+      <c r="N17" s="4">
+        <v>8.0319983221959892E-2</v>
+      </c>
+      <c r="O17" s="4">
+        <v>4.195070791819612E-2</v>
+      </c>
+      <c r="P17" s="15">
+        <v>3.4701988818540461</v>
+      </c>
+      <c r="Q17" s="15">
+        <v>5.0341856510546588E-2</v>
+      </c>
+      <c r="R17" s="92">
+        <v>3.9546057100127742E-2</v>
+      </c>
+      <c r="S17" s="86">
+        <v>-13.312996389940134</v>
+      </c>
+      <c r="T17" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="U17" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="V17" s="14">
+        <v>45716</v>
+      </c>
+      <c r="W17" s="11" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="18" spans="2:23">
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
       <c r="E18" s="12"/>
@@ -4464,7 +4530,7 @@
       <c r="U18" s="11"/>
       <c r="V18" s="14"/>
     </row>
-    <row r="19" spans="2:22">
+    <row r="19" spans="2:23">
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
       <c r="E19" s="12"/>
@@ -4474,7 +4540,7 @@
       <c r="U19" s="11"/>
       <c r="V19" s="14"/>
     </row>
-    <row r="20" spans="2:22">
+    <row r="20" spans="2:23">
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
       <c r="E20" s="12"/>
@@ -4484,7 +4550,7 @@
       <c r="U20" s="11"/>
       <c r="V20" s="14"/>
     </row>
-    <row r="21" spans="2:22">
+    <row r="21" spans="2:23">
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
       <c r="E21" s="12"/>
@@ -4494,7 +4560,7 @@
       <c r="U21" s="11"/>
       <c r="V21" s="14"/>
     </row>
-    <row r="22" spans="2:22">
+    <row r="22" spans="2:23">
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="E22" s="12"/>
@@ -4504,7 +4570,7 @@
       <c r="U22" s="11"/>
       <c r="V22" s="14"/>
     </row>
-    <row r="23" spans="2:22">
+    <row r="23" spans="2:23">
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="E23" s="12"/>
@@ -4514,7 +4580,7 @@
       <c r="U23" s="11"/>
       <c r="V23" s="14"/>
     </row>
-    <row r="24" spans="2:22">
+    <row r="24" spans="2:23">
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="E24" s="12"/>
@@ -4524,7 +4590,7 @@
       <c r="U24" s="11"/>
       <c r="V24" s="14"/>
     </row>
-    <row r="25" spans="2:22">
+    <row r="25" spans="2:23">
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="E25" s="12"/>
@@ -4534,7 +4600,7 @@
       <c r="U25" s="11"/>
       <c r="V25" s="14"/>
     </row>
-    <row r="26" spans="2:22">
+    <row r="26" spans="2:23">
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="E26" s="12"/>
@@ -4544,7 +4610,7 @@
       <c r="U26" s="11"/>
       <c r="V26" s="14"/>
     </row>
-    <row r="27" spans="2:22">
+    <row r="27" spans="2:23">
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="E27" s="12"/>
@@ -4554,7 +4620,7 @@
       <c r="U27" s="11"/>
       <c r="V27" s="14"/>
     </row>
-    <row r="28" spans="2:22">
+    <row r="28" spans="2:23">
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="E28" s="12"/>
@@ -4564,7 +4630,7 @@
       <c r="U28" s="11"/>
       <c r="V28" s="14"/>
     </row>
-    <row r="29" spans="2:22">
+    <row r="29" spans="2:23">
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
       <c r="E29" s="12"/>
@@ -4574,7 +4640,7 @@
       <c r="U29" s="11"/>
       <c r="V29" s="14"/>
     </row>
-    <row r="30" spans="2:22">
+    <row r="30" spans="2:23">
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="E30" s="12"/>
@@ -4584,7 +4650,7 @@
       <c r="U30" s="11"/>
       <c r="V30" s="14"/>
     </row>
-    <row r="31" spans="2:22">
+    <row r="31" spans="2:23">
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="E31" s="12"/>
@@ -4594,7 +4660,7 @@
       <c r="U31" s="11"/>
       <c r="V31" s="14"/>
     </row>
-    <row r="32" spans="2:22">
+    <row r="32" spans="2:23">
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
       <c r="E32" s="12"/>
@@ -6835,9 +6901,9 @@
       <c r="F3" s="71">
         <v>351395.62</v>
       </c>
-      <c r="G3" s="73">
+      <c r="G3" s="73" t="e">
         <f>F3/$F$9</f>
-        <v>0.39268415166236537</v>
+        <v>#N/A</v>
       </c>
       <c r="H3" s="91">
         <f>Portfolio_Mgmt!E61</f>
@@ -6863,9 +6929,9 @@
         <f>C4*E4</f>
         <v>178200</v>
       </c>
-      <c r="G4" s="73">
+      <c r="G4" s="73" t="e">
         <f>F4/$F$9</f>
-        <v>0.19913826992559985</v>
+        <v>#N/A</v>
       </c>
       <c r="H4" s="73">
         <f>VLOOKUP(B4,Opportunities!B$3:I$12,8,FALSE)</f>
@@ -6876,29 +6942,29 @@
       <c r="B5" s="78" t="s">
         <v>229</v>
       </c>
-      <c r="C5" s="75">
+      <c r="C5" s="75" t="e">
         <f>VLOOKUP(B5,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>8.15</v>
-      </c>
-      <c r="D5" s="74" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="D5" s="74" t="e">
         <f>VLOOKUP(B5,Opportunities!B$3:E$12,4,FALSE)</f>
-        <v>HKD</v>
+        <v>#N/A</v>
       </c>
       <c r="E5" s="71">
         <f>2000*10</f>
         <v>20000</v>
       </c>
-      <c r="F5" s="76">
+      <c r="F5" s="76" t="e">
         <f>E5*C5</f>
-        <v>163000</v>
-      </c>
-      <c r="G5" s="73">
+        <v>#N/A</v>
+      </c>
+      <c r="G5" s="73" t="e">
         <f>F5/$F$9</f>
-        <v>0.18215228955035226</v>
-      </c>
-      <c r="H5" s="73">
+        <v>#N/A</v>
+      </c>
+      <c r="H5" s="73" t="e">
         <f>VLOOKUP(B5,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -6920,13 +6986,13 @@
         <f>E6*C6</f>
         <v>109980</v>
       </c>
-      <c r="G6" s="73">
+      <c r="G6" s="73" t="e">
         <f>F6/$F$9</f>
-        <v>0.12290250800458738</v>
+        <v>#N/A</v>
       </c>
       <c r="H6" s="73">
         <f>VLOOKUP(B6,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.15926921829883645</v>
+        <v>8.9497970423085382E-2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -6948,9 +7014,9 @@
         <f>C7*E7</f>
         <v>92280</v>
       </c>
-      <c r="G7" s="73">
+      <c r="G7" s="73" t="e">
         <f>F7/$F$9</f>
-        <v>0.10312278085709514</v>
+        <v>#N/A</v>
       </c>
       <c r="H7" s="73">
         <f>VLOOKUP(B7,Opportunities!B$3:I$12,8,FALSE)</f>
@@ -6970,17 +7036,17 @@
       <c r="E9" s="81" t="s">
         <v>261</v>
       </c>
-      <c r="F9" s="81">
+      <c r="F9" s="81" t="e">
         <f>SUM(F3:F7)</f>
-        <v>894855.62</v>
-      </c>
-      <c r="G9" s="82">
+        <v>#N/A</v>
+      </c>
+      <c r="G9" s="82" t="e">
         <f>SUM(G3:G7)</f>
-        <v>1</v>
-      </c>
-      <c r="H9" s="89">
+        <v>#N/A</v>
+      </c>
+      <c r="H9" s="89" t="e">
         <f>SUM(H4:H7)</f>
-        <v>0.34839803777929945</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -7016,42 +7082,42 @@
         <f>-C12*E12</f>
         <v>-81200</v>
       </c>
-      <c r="G12" s="73">
+      <c r="G12" s="73" t="e">
         <f>-F12/$F$9</f>
-        <v>9.0740895162506774E-2</v>
+        <v>#N/A</v>
       </c>
       <c r="H12" s="73">
         <f>VLOOKUP(B12,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0.21293704824312568</v>
+        <v>0.21955254305698646</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="B13" s="78" t="s">
         <v>162</v>
       </c>
-      <c r="C13" s="75">
+      <c r="C13" s="75" t="e">
         <f>VLOOKUP(B13,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>8.15</v>
-      </c>
-      <c r="D13" s="74" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="D13" s="74" t="e">
         <f>VLOOKUP(B13,Opportunities!B$3:E$12,4,FALSE)</f>
-        <v>HKD</v>
+        <v>#N/A</v>
       </c>
       <c r="E13" s="71">
         <f>-2000*5</f>
         <v>-10000</v>
       </c>
-      <c r="F13" s="76">
+      <c r="F13" s="76" t="e">
         <f>-C13*E13</f>
-        <v>81500</v>
-      </c>
-      <c r="G13" s="73">
+        <v>#N/A</v>
+      </c>
+      <c r="G13" s="73" t="e">
         <f>-F13/$F$9</f>
-        <v>-9.1076144775176129E-2</v>
-      </c>
-      <c r="H13" s="73">
+        <v>#N/A</v>
+      </c>
+      <c r="H13" s="73" t="e">
         <f>VLOOKUP(B13,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -7075,9 +7141,9 @@
         <f>F3+F12</f>
         <v>270195.62</v>
       </c>
-      <c r="G15" s="89">
+      <c r="G15" s="89" t="e">
         <f t="shared" ref="G15" si="0">F15/$F$9</f>
-        <v>0.30194325649985859</v>
+        <v>#N/A</v>
       </c>
       <c r="H15" s="89">
         <f>Portfolio_Mgmt!E61</f>
@@ -7174,15 +7240,15 @@
       <c r="B5" s="106" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="95"/>
-      <c r="D5" s="95"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="97"/>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="106" t="s">
         <v>105</v>
       </c>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="97"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE10DE0-E295-4E54-ABDD-69DA49052A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4870E858-F297-49AF-8299-D23A5FF3BE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio_Mgmt" sheetId="5" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="286">
   <si>
     <t>Name</t>
   </si>
@@ -1638,6 +1638,9 @@
   </si>
   <si>
     <t>中海石油化学</t>
+  </si>
+  <si>
+    <t>ENG_02</t>
   </si>
 </sst>
 </file>
@@ -2213,17 +2216,17 @@
     <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2633,12 +2636,12 @@
       <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B4" s="95" t="s">
+      <c r="B4" s="94" t="s">
         <v>219</v>
       </c>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="20" t="s">
@@ -2650,12 +2653,12 @@
       <c r="C6" s="61"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" s="95" t="s">
+      <c r="B7" s="94" t="s">
         <v>207</v>
       </c>
-      <c r="C7" s="95"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="94"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="23" t="s">
@@ -2744,12 +2747,12 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
-      <c r="B24" s="95" t="s">
+      <c r="B24" s="94" t="s">
         <v>218</v>
       </c>
-      <c r="C24" s="95"/>
-      <c r="D24" s="95"/>
-      <c r="E24" s="95"/>
+      <c r="C24" s="94"/>
+      <c r="D24" s="94"/>
+      <c r="E24" s="94"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
@@ -2849,20 +2852,20 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="B39" s="95" t="s">
+      <c r="B39" s="94" t="s">
         <v>154</v>
       </c>
-      <c r="C39" s="95"/>
-      <c r="D39" s="95"/>
-      <c r="E39" s="95"/>
+      <c r="C39" s="94"/>
+      <c r="D39" s="94"/>
+      <c r="E39" s="94"/>
     </row>
     <row r="40" spans="1:5" ht="46.6" customHeight="1">
-      <c r="B40" s="95" t="s">
+      <c r="B40" s="94" t="s">
         <v>233</v>
       </c>
-      <c r="C40" s="95"/>
-      <c r="D40" s="95"/>
-      <c r="E40" s="95"/>
+      <c r="C40" s="94"/>
+      <c r="D40" s="94"/>
+      <c r="E40" s="94"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="21" t="s">
@@ -2874,12 +2877,12 @@
       <c r="E42" s="21"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="B44" s="95" t="s">
+      <c r="B44" s="94" t="s">
         <v>206</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="94"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="23" t="s">
@@ -3064,12 +3067,12 @@
       <c r="E69" s="21"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="B71" s="95" t="s">
+      <c r="B71" s="94" t="s">
         <v>194</v>
       </c>
-      <c r="C71" s="95"/>
-      <c r="D71" s="95"/>
-      <c r="E71" s="95"/>
+      <c r="C71" s="94"/>
+      <c r="D71" s="94"/>
+      <c r="E71" s="94"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="28" t="s">
@@ -3131,36 +3134,36 @@
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="B85" s="96" t="s">
+      <c r="B85" s="97" t="s">
         <v>190</v>
       </c>
-      <c r="C85" s="96"/>
-      <c r="D85" s="96"/>
-      <c r="E85" s="96"/>
+      <c r="C85" s="97"/>
+      <c r="D85" s="97"/>
+      <c r="E85" s="97"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="B86" s="94" t="s">
+      <c r="B86" s="96" t="s">
         <v>188</v>
       </c>
-      <c r="C86" s="94"/>
-      <c r="D86" s="94"/>
-      <c r="E86" s="94"/>
+      <c r="C86" s="96"/>
+      <c r="D86" s="96"/>
+      <c r="E86" s="96"/>
     </row>
     <row r="87" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B87" s="95" t="s">
+      <c r="B87" s="94" t="s">
         <v>187</v>
       </c>
-      <c r="C87" s="95"/>
-      <c r="D87" s="95"/>
-      <c r="E87" s="95"/>
+      <c r="C87" s="94"/>
+      <c r="D87" s="94"/>
+      <c r="E87" s="94"/>
     </row>
     <row r="88" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B88" s="95" t="s">
+      <c r="B88" s="94" t="s">
         <v>223</v>
       </c>
-      <c r="C88" s="95"/>
-      <c r="D88" s="95"/>
-      <c r="E88" s="95"/>
+      <c r="C88" s="94"/>
+      <c r="D88" s="94"/>
+      <c r="E88" s="94"/>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="24" t="s">
@@ -3193,12 +3196,12 @@
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="B97" s="97" t="s">
+      <c r="B97" s="95" t="s">
         <v>209</v>
       </c>
-      <c r="C97" s="97"/>
-      <c r="D97" s="97"/>
-      <c r="E97" s="97"/>
+      <c r="C97" s="95"/>
+      <c r="D97" s="95"/>
+      <c r="E97" s="95"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
@@ -3206,20 +3209,20 @@
       </c>
     </row>
     <row r="100" spans="1:5" ht="12.4">
-      <c r="B100" s="97" t="s">
+      <c r="B100" s="95" t="s">
         <v>210</v>
       </c>
-      <c r="C100" s="97"/>
-      <c r="D100" s="97"/>
-      <c r="E100" s="97"/>
+      <c r="C100" s="95"/>
+      <c r="D100" s="95"/>
+      <c r="E100" s="95"/>
     </row>
     <row r="101" spans="1:5" ht="58.5" customHeight="1">
-      <c r="B101" s="95" t="s">
+      <c r="B101" s="94" t="s">
         <v>217</v>
       </c>
-      <c r="C101" s="95"/>
-      <c r="D101" s="95"/>
-      <c r="E101" s="95"/>
+      <c r="C101" s="94"/>
+      <c r="D101" s="94"/>
+      <c r="E101" s="94"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="28" t="s">
@@ -3267,7 +3270,7 @@
         <v>174</v>
       </c>
       <c r="C112" s="44">
-        <v>0.14930888295373529</v>
+        <v>0.17371081123875481</v>
       </c>
       <c r="D112" s="61" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
@@ -3275,12 +3278,12 @@
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B114" s="95" t="s">
+      <c r="B114" s="94" t="s">
         <v>215</v>
       </c>
-      <c r="C114" s="95"/>
-      <c r="D114" s="95"/>
-      <c r="E114" s="95"/>
+      <c r="C114" s="94"/>
+      <c r="D114" s="94"/>
+      <c r="E114" s="94"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="21" t="s">
@@ -3313,12 +3316,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
     <mergeCell ref="B86:E86"/>
     <mergeCell ref="B71:E71"/>
     <mergeCell ref="B85:E85"/>
@@ -3328,6 +3325,12 @@
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3472,66 +3475,66 @@
     </row>
     <row r="3" spans="1:23">
       <c r="B3" s="11" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="D3" s="2">
-        <v>1.1599999999999999</v>
+        <v>1.95</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>158</v>
       </c>
       <c r="F3" s="15">
-        <v>0.21955254305698646</v>
+        <v>0.27795596712109361</v>
       </c>
       <c r="G3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$10</f>
-        <v>0.10215254305698646</v>
+        <v>0.1605559671210936</v>
       </c>
       <c r="H3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$11</f>
-        <v>0.18505254305698646</v>
+        <v>0.2434559671210936</v>
       </c>
       <c r="I3" s="15">
-        <v>0.21955254305698646</v>
+        <v>0.27795596712109361</v>
       </c>
       <c r="J3" s="2">
-        <v>0.9576999852710768</v>
+        <v>1.8570713816288429</v>
       </c>
       <c r="K3" s="2">
-        <v>2.1040668676405563</v>
+        <v>3.5690743054385683</v>
       </c>
       <c r="L3" s="2">
-        <v>1.2176312891438406</v>
+        <v>2.3351672600917639</v>
       </c>
       <c r="M3" s="86">
-        <v>1.6702761167953912</v>
+        <v>3.1632383692769204</v>
       </c>
       <c r="N3" s="4">
-        <v>8.265220900462859E-3</v>
+        <v>6.4603602738772095E-2</v>
       </c>
       <c r="O3" s="4">
-        <v>0</v>
+        <v>6.5665641025641042E-2</v>
       </c>
       <c r="P3" s="15">
-        <v>9.7057481271370302E-2</v>
+        <v>0.23422582328431374</v>
       </c>
       <c r="Q3" s="15">
-        <v>1.4790654865358754E-2</v>
+        <v>0.10863424600069688</v>
       </c>
       <c r="R3" s="92">
-        <v>3.4432102574884196</v>
+        <v>2.2824569622635926</v>
       </c>
       <c r="S3" s="86">
-        <v>1.9115679363188245</v>
+        <v>1.7907626778741865</v>
       </c>
       <c r="T3" s="13" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="U3" s="11" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="V3" s="14">
         <v>45900</v>
@@ -3542,66 +3545,66 @@
     </row>
     <row r="4" spans="1:23">
       <c r="B4" s="11" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="D4" s="2">
-        <v>1.95</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>158</v>
       </c>
       <c r="F4" s="15">
-        <v>0.20182066703946511</v>
+        <v>0.21955254305698646</v>
       </c>
       <c r="G4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$10</f>
-        <v>8.4420667039465103E-2</v>
+        <v>0.10215254305698646</v>
       </c>
       <c r="H4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$11</f>
-        <v>0.1673206670394651</v>
+        <v>0.18505254305698646</v>
       </c>
       <c r="I4" s="15">
-        <v>0.20182066703946511</v>
+        <v>0.21955254305698646</v>
       </c>
       <c r="J4" s="2">
-        <v>1.5407194269481685</v>
+        <v>0.9576999852710768</v>
       </c>
       <c r="K4" s="2">
-        <v>3.3849605810051271</v>
+        <v>2.1040668676405563</v>
       </c>
       <c r="L4" s="2">
-        <v>1.9588892251187078</v>
+        <v>1.2176312891438406</v>
       </c>
       <c r="M4" s="86">
-        <v>2.6870908437842354</v>
+        <v>1.6702761167953912</v>
       </c>
       <c r="N4" s="4">
-        <v>6.0823671959654366E-2</v>
+        <v>8.265220900462859E-3</v>
       </c>
       <c r="O4" s="4">
         <v>0</v>
       </c>
       <c r="P4" s="15">
-        <v>0.23422582328431374</v>
+        <v>9.7057481271370302E-2</v>
       </c>
       <c r="Q4" s="15">
-        <v>0.10863424600069688</v>
+        <v>1.4790654865358754E-2</v>
       </c>
       <c r="R4" s="92">
-        <v>2.2824569622635926</v>
+        <v>3.4432102574884196</v>
       </c>
       <c r="S4" s="86">
-        <v>1.6893987527114966</v>
+        <v>1.9115679363188245</v>
       </c>
       <c r="T4" s="13" t="s">
-        <v>159</v>
+        <v>278</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="V4" s="14">
         <v>45900</v>
@@ -3705,7 +3708,7 @@
         <v>0.12476921829883644</v>
       </c>
       <c r="I6" s="15">
-        <v>8.9497970423085382E-2</v>
+        <v>1.3362670341456884E-2</v>
       </c>
       <c r="J6" s="2">
         <v>4.4306821973721187</v>
@@ -6901,9 +6904,9 @@
       <c r="F3" s="71">
         <v>351395.62</v>
       </c>
-      <c r="G3" s="73" t="e">
+      <c r="G3" s="73">
         <f>F3/$F$9</f>
-        <v>#N/A</v>
+        <v>0.39268415166236537</v>
       </c>
       <c r="H3" s="91">
         <f>Portfolio_Mgmt!E61</f>
@@ -6915,11 +6918,11 @@
         <v>230</v>
       </c>
       <c r="C4" s="75">
-        <f>VLOOKUP(B4,Opportunities!B$3:E$12,3,FALSE)</f>
+        <f>VLOOKUP(B4,Opportunities!B$3:E$30,3,FALSE)</f>
         <v>17.82</v>
       </c>
       <c r="D4" s="74" t="str">
-        <f>VLOOKUP(B4,Opportunities!B$3:E$12,4,FALSE)</f>
+        <f>VLOOKUP(B4,Opportunities!B$3:E$30,4,FALSE)</f>
         <v>HKD</v>
       </c>
       <c r="E4" s="71">
@@ -6929,12 +6932,12 @@
         <f>C4*E4</f>
         <v>178200</v>
       </c>
-      <c r="G4" s="73" t="e">
+      <c r="G4" s="73">
         <f>F4/$F$9</f>
-        <v>#N/A</v>
+        <v>0.19913826992559985</v>
       </c>
       <c r="H4" s="73">
-        <f>VLOOKUP(B4,Opportunities!B$3:I$12,8,FALSE)</f>
+        <f>VLOOKUP(B4,Opportunities!B$3:I$30,8,FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -6942,29 +6945,29 @@
       <c r="B5" s="78" t="s">
         <v>229</v>
       </c>
-      <c r="C5" s="75" t="e">
-        <f>VLOOKUP(B5,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D5" s="74" t="e">
-        <f>VLOOKUP(B5,Opportunities!B$3:E$12,4,FALSE)</f>
-        <v>#N/A</v>
+      <c r="C5" s="75">
+        <f>VLOOKUP(B5,Opportunities!B$3:E$30,3,FALSE)</f>
+        <v>8.15</v>
+      </c>
+      <c r="D5" s="74" t="str">
+        <f>VLOOKUP(B5,Opportunities!B$3:E$30,4,FALSE)</f>
+        <v>HKD</v>
       </c>
       <c r="E5" s="71">
         <f>2000*10</f>
         <v>20000</v>
       </c>
-      <c r="F5" s="76" t="e">
+      <c r="F5" s="76">
         <f>E5*C5</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G5" s="73" t="e">
+        <v>163000</v>
+      </c>
+      <c r="G5" s="73">
         <f>F5/$F$9</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H5" s="73" t="e">
-        <f>VLOOKUP(B5,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>#N/A</v>
+        <v>0.18215228955035226</v>
+      </c>
+      <c r="H5" s="73">
+        <f>VLOOKUP(B5,Opportunities!B$3:I$30,8,FALSE)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -6972,11 +6975,11 @@
         <v>241</v>
       </c>
       <c r="C6" s="75">
-        <f>VLOOKUP(B6,Opportunities!B$3:E$12,3,FALSE)</f>
+        <f>VLOOKUP(B6,Opportunities!B$3:E$30,3,FALSE)</f>
         <v>6.11</v>
       </c>
       <c r="D6" s="74" t="str">
-        <f>VLOOKUP(B6,Opportunities!B$3:E$12,4,FALSE)</f>
+        <f>VLOOKUP(B6,Opportunities!B$3:E$30,4,FALSE)</f>
         <v>HKD</v>
       </c>
       <c r="E6" s="71">
@@ -6986,13 +6989,13 @@
         <f>E6*C6</f>
         <v>109980</v>
       </c>
-      <c r="G6" s="73" t="e">
+      <c r="G6" s="73">
         <f>F6/$F$9</f>
-        <v>#N/A</v>
+        <v>0.12290250800458738</v>
       </c>
       <c r="H6" s="73">
-        <f>VLOOKUP(B6,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>8.9497970423085382E-2</v>
+        <f>VLOOKUP(B6,Opportunities!B$3:I$30,8,FALSE)</f>
+        <v>1.3362670341456884E-2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -7000,11 +7003,11 @@
         <v>256</v>
       </c>
       <c r="C7" s="75">
-        <f>VLOOKUP(B7,Opportunities!B$3:E$12,3,FALSE)</f>
+        <f>VLOOKUP(B7,Opportunities!B$3:E$30,3,FALSE)</f>
         <v>15.38</v>
       </c>
       <c r="D7" s="74" t="str">
-        <f>VLOOKUP(B7,Opportunities!B$3:E$12,4,FALSE)</f>
+        <f>VLOOKUP(B7,Opportunities!B$3:E$30,4,FALSE)</f>
         <v>HKD</v>
       </c>
       <c r="E7" s="71">
@@ -7014,12 +7017,12 @@
         <f>C7*E7</f>
         <v>92280</v>
       </c>
-      <c r="G7" s="73" t="e">
+      <c r="G7" s="73">
         <f>F7/$F$9</f>
-        <v>#N/A</v>
+        <v>0.10312278085709514</v>
       </c>
       <c r="H7" s="73">
-        <f>VLOOKUP(B7,Opportunities!B$3:I$12,8,FALSE)</f>
+        <f>VLOOKUP(B7,Opportunities!B$3:I$30,8,FALSE)</f>
         <v>0.18912881948046303</v>
       </c>
     </row>
@@ -7036,17 +7039,17 @@
       <c r="E9" s="81" t="s">
         <v>261</v>
       </c>
-      <c r="F9" s="81" t="e">
+      <c r="F9" s="81">
         <f>SUM(F3:F7)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G9" s="82" t="e">
+        <v>894855.62</v>
+      </c>
+      <c r="G9" s="82">
         <f>SUM(G3:G7)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H9" s="89" t="e">
+        <v>1</v>
+      </c>
+      <c r="H9" s="89">
         <f>SUM(H4:H7)</f>
-        <v>#N/A</v>
+        <v>0.20249148982191992</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -7067,11 +7070,11 @@
         <v>276</v>
       </c>
       <c r="C12" s="75">
-        <f>VLOOKUP(B12,Opportunities!B$3:E$12,3,FALSE)</f>
+        <f>VLOOKUP(B12,Opportunities!B$3:E$30,3,FALSE)</f>
         <v>1.1599999999999999</v>
       </c>
       <c r="D12" s="74" t="str">
-        <f>VLOOKUP(B12,Opportunities!B$3:E$12,4,FALSE)</f>
+        <f>VLOOKUP(B12,Opportunities!B$3:E$30,4,FALSE)</f>
         <v>HKD</v>
       </c>
       <c r="E12" s="71">
@@ -7082,12 +7085,12 @@
         <f>-C12*E12</f>
         <v>-81200</v>
       </c>
-      <c r="G12" s="73" t="e">
+      <c r="G12" s="73">
         <f>-F12/$F$9</f>
-        <v>#N/A</v>
+        <v>9.0740895162506774E-2</v>
       </c>
       <c r="H12" s="73">
-        <f>VLOOKUP(B12,Opportunities!B$3:I$12,8,FALSE)</f>
+        <f>VLOOKUP(B12,Opportunities!B$3:I$30,8,FALSE)</f>
         <v>0.21955254305698646</v>
       </c>
     </row>
@@ -7095,29 +7098,29 @@
       <c r="B13" s="78" t="s">
         <v>162</v>
       </c>
-      <c r="C13" s="75" t="e">
-        <f>VLOOKUP(B13,Opportunities!B$3:E$12,3,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D13" s="74" t="e">
-        <f>VLOOKUP(B13,Opportunities!B$3:E$12,4,FALSE)</f>
-        <v>#N/A</v>
+      <c r="C13" s="75">
+        <f>VLOOKUP(B13,Opportunities!B$3:E$30,3,FALSE)</f>
+        <v>8.15</v>
+      </c>
+      <c r="D13" s="74" t="str">
+        <f>VLOOKUP(B13,Opportunities!B$3:E$30,4,FALSE)</f>
+        <v>HKD</v>
       </c>
       <c r="E13" s="71">
         <f>-2000*5</f>
         <v>-10000</v>
       </c>
-      <c r="F13" s="76" t="e">
+      <c r="F13" s="76">
         <f>-C13*E13</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G13" s="73" t="e">
+        <v>81500</v>
+      </c>
+      <c r="G13" s="73">
         <f>-F13/$F$9</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H13" s="73" t="e">
-        <f>VLOOKUP(B13,Opportunities!B$3:I$12,8,FALSE)</f>
-        <v>#N/A</v>
+        <v>-9.1076144775176129E-2</v>
+      </c>
+      <c r="H13" s="73">
+        <f>VLOOKUP(B13,Opportunities!B$3:I$30,8,FALSE)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -7141,9 +7144,9 @@
         <f>F3+F12</f>
         <v>270195.62</v>
       </c>
-      <c r="G15" s="89" t="e">
+      <c r="G15" s="89">
         <f t="shared" ref="G15" si="0">F15/$F$9</f>
-        <v>#N/A</v>
+        <v>0.30194325649985859</v>
       </c>
       <c r="H15" s="89">
         <f>Portfolio_Mgmt!E61</f>
@@ -7240,15 +7243,15 @@
       <c r="B5" s="106" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="95"/>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="106" t="s">
         <v>105</v>
       </c>
-      <c r="C6" s="97"/>
-      <c r="D6" s="97"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4870E858-F297-49AF-8299-D23A5FF3BE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E1F7D68-215A-4D99-B41D-F08B07232298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="288">
   <si>
     <t>Name</t>
   </si>
@@ -881,18 +881,9 @@
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t>0590.HK</t>
-  </si>
-  <si>
-    <t>六福珠宝</t>
-  </si>
-  <si>
     <t>HKD</t>
   </si>
   <si>
-    <t>CNS_05</t>
-  </si>
-  <si>
     <t xml:space="preserve">Low Growth </t>
   </si>
   <si>
@@ -900,27 +891,6 @@
   </si>
   <si>
     <t>0083.HK</t>
-  </si>
-  <si>
-    <t>SINO LAND</t>
-  </si>
-  <si>
-    <t>RES_01</t>
-  </si>
-  <si>
-    <t>Negative Growth Asset Play</t>
-  </si>
-  <si>
-    <t>6601.HK</t>
-  </si>
-  <si>
-    <t>朝云集团</t>
-  </si>
-  <si>
-    <t>CNS_04</t>
-  </si>
-  <si>
-    <t>Low Growth Asset Play</t>
   </si>
   <si>
     <t>Portfolio Management Plan</t>
@@ -1474,77 +1444,14 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>ENG_01</t>
+  </si>
+  <si>
     <t>0857.HK</t>
-  </si>
-  <si>
-    <t>中国石油股份</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Negative Growth </t>
-  </si>
-  <si>
-    <t>ENG_01</t>
-  </si>
-  <si>
-    <t>0168.HK</t>
-  </si>
-  <si>
-    <t>青島啤酒股份</t>
-  </si>
-  <si>
-    <t>CNS_03</t>
-  </si>
-  <si>
-    <t>0857.HK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1910.HK</t>
-  </si>
-  <si>
-    <t>新秀麗</t>
-  </si>
-  <si>
-    <t>CNS_02</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High Growth </t>
-  </si>
-  <si>
-    <t>0303.HK</t>
-  </si>
-  <si>
-    <t>偉易達</t>
-  </si>
-  <si>
-    <t>SIRI</t>
-  </si>
-  <si>
-    <t>Sirius XM Holdings Inc.</t>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>TMT_05</t>
-  </si>
-  <si>
-    <t>KHC</t>
-  </si>
-  <si>
-    <t>The Kraft Heinz Company</t>
-  </si>
-  <si>
-    <t>CNS_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2331.HK</t>
-  </si>
-  <si>
-    <t>李宁</t>
   </si>
   <si>
     <t>Planning</t>
@@ -1598,49 +1505,148 @@
     <t>Execution</t>
   </si>
   <si>
+    <t>9959.HK</t>
+  </si>
+  <si>
+    <t>Expansion expected</t>
+  </si>
+  <si>
+    <t>Recession expected</t>
+  </si>
+  <si>
+    <t>中國石化</t>
+  </si>
+  <si>
+    <t>0386.HK</t>
+  </si>
+  <si>
+    <t>SINO LAND</t>
+  </si>
+  <si>
+    <t>Negative Growth Asset Play</t>
+  </si>
+  <si>
+    <t>RES_01</t>
+  </si>
+  <si>
+    <t>0303.HK</t>
+  </si>
+  <si>
+    <t>偉易達</t>
+  </si>
+  <si>
+    <t>CNS_02</t>
+  </si>
+  <si>
+    <t>0168.HK</t>
+  </si>
+  <si>
+    <t>青島啤酒股份</t>
+  </si>
+  <si>
+    <t>CNS_03</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>0857.HK</t>
+  </si>
+  <si>
+    <t>中国石油股份</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negative Growth </t>
+  </si>
+  <si>
+    <t>0398.HK</t>
+  </si>
+  <si>
+    <t>東方表行集團</t>
+  </si>
+  <si>
+    <t>CNS_05</t>
+  </si>
+  <si>
+    <t>0590.HK</t>
+  </si>
+  <si>
+    <t>六福珠宝</t>
+  </si>
+  <si>
+    <t>李宁</t>
+  </si>
+  <si>
+    <t>002304.SZ</t>
+  </si>
+  <si>
+    <t>洋河股份</t>
+  </si>
+  <si>
+    <t>CNY</t>
+  </si>
+  <si>
+    <t>1910.HK</t>
+  </si>
+  <si>
+    <t>新秀麗</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High Growth </t>
+  </si>
+  <si>
+    <t>聯易融科技</t>
+  </si>
+  <si>
+    <t>FIN_03</t>
+  </si>
+  <si>
+    <t>Low Growth Asset Play</t>
+  </si>
+  <si>
+    <t>3983.HK</t>
+  </si>
+  <si>
+    <t>中海石油化学</t>
+  </si>
+  <si>
+    <t>ENG_02</t>
+  </si>
+  <si>
+    <t>6601.HK</t>
+  </si>
+  <si>
+    <t>朝云集团</t>
+  </si>
+  <si>
+    <t>CNS_04</t>
+  </si>
+  <si>
+    <t>SIRI</t>
+  </si>
+  <si>
+    <t>Sirius XM Holdings Inc.</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>TMT_05</t>
+  </si>
+  <si>
+    <t>KHC</t>
+  </si>
+  <si>
+    <t>The Kraft Heinz Company</t>
+  </si>
+  <si>
+    <t>CNS_01</t>
+  </si>
+  <si>
     <t>600132.SS</t>
   </si>
   <si>
     <t>重庆啤酒</t>
-  </si>
-  <si>
-    <t>CNY</t>
-  </si>
-  <si>
-    <t>002304.SZ</t>
-  </si>
-  <si>
-    <t>洋河股份</t>
-  </si>
-  <si>
-    <t>9959.HK</t>
-  </si>
-  <si>
-    <t>聯易融科技</t>
-  </si>
-  <si>
-    <t>FIN_03</t>
-  </si>
-  <si>
-    <t>0398.HK</t>
-  </si>
-  <si>
-    <t>東方表行集團</t>
-  </si>
-  <si>
-    <t>Expansion expected</t>
-  </si>
-  <si>
-    <t>Recession expected</t>
-  </si>
-  <si>
-    <t>3983.HK</t>
-  </si>
-  <si>
-    <t>中海石油化学</t>
-  </si>
-  <si>
-    <t>ENG_02</t>
   </si>
 </sst>
 </file>
@@ -2216,17 +2222,17 @@
     <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2623,7 +2629,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="20" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2636,29 +2642,29 @@
       <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B4" s="94" t="s">
-        <v>219</v>
-      </c>
-      <c r="C4" s="94"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
+      <c r="B4" s="95" t="s">
+        <v>209</v>
+      </c>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="20" t="s">
         <v>66</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C6" s="61"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" s="94" t="s">
-        <v>207</v>
-      </c>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
+      <c r="B7" s="95" t="s">
+        <v>197</v>
+      </c>
+      <c r="C7" s="95"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="23" t="s">
@@ -2694,10 +2700,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="B14" s="1" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2733,7 +2739,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="B21" s="24" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2741,18 +2747,18 @@
         <v>67</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C23" s="61"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
-      <c r="B24" s="94" t="s">
-        <v>218</v>
-      </c>
-      <c r="C24" s="94"/>
-      <c r="D24" s="94"/>
-      <c r="E24" s="94"/>
+      <c r="B24" s="95" t="s">
+        <v>208</v>
+      </c>
+      <c r="C24" s="95"/>
+      <c r="D24" s="95"/>
+      <c r="E24" s="95"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
@@ -2840,7 +2846,7 @@
         <v>0.08</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>268</v>
+        <v>237</v>
       </c>
       <c r="E36" s="48">
         <v>0.2</v>
@@ -2852,24 +2858,24 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="B39" s="94" t="s">
+      <c r="B39" s="95" t="s">
         <v>154</v>
       </c>
-      <c r="C39" s="94"/>
-      <c r="D39" s="94"/>
-      <c r="E39" s="94"/>
+      <c r="C39" s="95"/>
+      <c r="D39" s="95"/>
+      <c r="E39" s="95"/>
     </row>
     <row r="40" spans="1:5" ht="46.6" customHeight="1">
-      <c r="B40" s="94" t="s">
-        <v>233</v>
-      </c>
-      <c r="C40" s="94"/>
-      <c r="D40" s="94"/>
-      <c r="E40" s="94"/>
+      <c r="B40" s="95" t="s">
+        <v>223</v>
+      </c>
+      <c r="C40" s="95"/>
+      <c r="D40" s="95"/>
+      <c r="E40" s="95"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="21" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="B42" s="21"/>
       <c r="C42" s="21"/>
@@ -2877,12 +2883,12 @@
       <c r="E42" s="21"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="B44" s="94" t="s">
-        <v>206</v>
-      </c>
-      <c r="C44" s="94"/>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
+      <c r="B44" s="95" t="s">
+        <v>196</v>
+      </c>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="23" t="s">
@@ -2894,7 +2900,7 @@
         <v>91</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D48" s="56"/>
       <c r="E48" s="56"/>
@@ -2927,7 +2933,7 @@
         <v>0.3</v>
       </c>
       <c r="D51" s="62" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="E51" s="55"/>
     </row>
@@ -2983,10 +2989,10 @@
         <v>71</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="D58" s="26" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="E58" s="41">
         <v>2</v>
@@ -3017,7 +3023,7 @@
     </row>
     <row r="61" spans="2:5" ht="12" thickBot="1">
       <c r="D61" s="42" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="E61" s="43">
         <f>IF(E60&lt;=2,C49,IF(E60&gt;=6,C51,C50))</f>
@@ -3027,12 +3033,12 @@
     <row r="62" spans="2:5" ht="12" thickTop="1"/>
     <row r="63" spans="2:5">
       <c r="B63" s="23" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
     </row>
     <row r="64" spans="2:5">
       <c r="B64" s="53" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C64" s="54">
         <f>-E61*(C35-Cash_Yield)</f>
@@ -3041,7 +3047,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="B65" s="53" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C65" s="54">
         <f>C35+C64</f>
@@ -3054,7 +3060,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="B67" s="39" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3067,29 +3073,29 @@
       <c r="E69" s="21"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="B71" s="94" t="s">
-        <v>194</v>
-      </c>
-      <c r="C71" s="94"/>
-      <c r="D71" s="94"/>
-      <c r="E71" s="94"/>
+      <c r="B71" s="95" t="s">
+        <v>184</v>
+      </c>
+      <c r="C71" s="95"/>
+      <c r="D71" s="95"/>
+      <c r="E71" s="95"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="28" t="s">
         <v>66</v>
       </c>
       <c r="B73" s="20" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="B74" s="24" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="B75" s="24" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -3097,27 +3103,27 @@
         <v>126</v>
       </c>
       <c r="B77" s="20" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="B78" s="39" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="B79" s="24" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="B80" s="24" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="B81" s="24" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -3125,131 +3131,131 @@
         <v>144</v>
       </c>
       <c r="B83" s="20" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="B84" s="24" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="B85" s="97" t="s">
-        <v>190</v>
-      </c>
-      <c r="C85" s="97"/>
-      <c r="D85" s="97"/>
-      <c r="E85" s="97"/>
+      <c r="B85" s="96" t="s">
+        <v>180</v>
+      </c>
+      <c r="C85" s="96"/>
+      <c r="D85" s="96"/>
+      <c r="E85" s="96"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="B86" s="96" t="s">
-        <v>188</v>
-      </c>
-      <c r="C86" s="96"/>
-      <c r="D86" s="96"/>
-      <c r="E86" s="96"/>
+      <c r="B86" s="94" t="s">
+        <v>178</v>
+      </c>
+      <c r="C86" s="94"/>
+      <c r="D86" s="94"/>
+      <c r="E86" s="94"/>
     </row>
     <row r="87" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B87" s="94" t="s">
-        <v>187</v>
-      </c>
-      <c r="C87" s="94"/>
-      <c r="D87" s="94"/>
-      <c r="E87" s="94"/>
+      <c r="B87" s="95" t="s">
+        <v>177</v>
+      </c>
+      <c r="C87" s="95"/>
+      <c r="D87" s="95"/>
+      <c r="E87" s="95"/>
     </row>
     <row r="88" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B88" s="94" t="s">
-        <v>223</v>
-      </c>
-      <c r="C88" s="94"/>
-      <c r="D88" s="94"/>
-      <c r="E88" s="94"/>
+      <c r="B88" s="95" t="s">
+        <v>213</v>
+      </c>
+      <c r="C88" s="95"/>
+      <c r="D88" s="95"/>
+      <c r="E88" s="95"/>
     </row>
     <row r="90" spans="1:5">
       <c r="B90" s="24" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="B91" s="1" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="B92" s="60" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="B93" s="24" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="B94" s="24" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="B96" s="24" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="B97" s="95" t="s">
-        <v>209</v>
-      </c>
-      <c r="C97" s="95"/>
-      <c r="D97" s="95"/>
-      <c r="E97" s="95"/>
+      <c r="B97" s="97" t="s">
+        <v>199</v>
+      </c>
+      <c r="C97" s="97"/>
+      <c r="D97" s="97"/>
+      <c r="E97" s="97"/>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" s="24" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="12.4">
-      <c r="B100" s="95" t="s">
-        <v>210</v>
-      </c>
-      <c r="C100" s="95"/>
-      <c r="D100" s="95"/>
-      <c r="E100" s="95"/>
+      <c r="B100" s="97" t="s">
+        <v>200</v>
+      </c>
+      <c r="C100" s="97"/>
+      <c r="D100" s="97"/>
+      <c r="E100" s="97"/>
     </row>
     <row r="101" spans="1:5" ht="58.5" customHeight="1">
-      <c r="B101" s="94" t="s">
-        <v>217</v>
-      </c>
-      <c r="C101" s="94"/>
-      <c r="D101" s="94"/>
-      <c r="E101" s="94"/>
+      <c r="B101" s="95" t="s">
+        <v>207</v>
+      </c>
+      <c r="C101" s="95"/>
+      <c r="D101" s="95"/>
+      <c r="E101" s="95"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="28" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="B103" s="20" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="B104" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="B105" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="B107" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="B108" s="1" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -3259,7 +3265,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="B111" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C111" s="44">
         <v>0.30000000000000004</v>
@@ -3267,10 +3273,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="B112" s="1" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="C112" s="44">
-        <v>0.17371081123875481</v>
+        <v>0.48555567224710755</v>
       </c>
       <c r="D112" s="61" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
@@ -3278,12 +3284,12 @@
       </c>
     </row>
     <row r="114" spans="1:5" ht="24.4" customHeight="1">
-      <c r="B114" s="94" t="s">
-        <v>215</v>
-      </c>
-      <c r="C114" s="94"/>
-      <c r="D114" s="94"/>
-      <c r="E114" s="94"/>
+      <c r="B114" s="95" t="s">
+        <v>205</v>
+      </c>
+      <c r="C114" s="95"/>
+      <c r="D114" s="95"/>
+      <c r="E114" s="95"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="21" t="s">
@@ -3311,11 +3317,17 @@
     </row>
     <row r="121" spans="1:5">
       <c r="B121" s="24" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
     <mergeCell ref="B86:E86"/>
     <mergeCell ref="B71:E71"/>
     <mergeCell ref="B85:E85"/>
@@ -3325,12 +3337,6 @@
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3385,7 +3391,7 @@
       </c>
       <c r="K1" s="103"/>
       <c r="L1" s="104" t="s">
-        <v>270</v>
+        <v>239</v>
       </c>
       <c r="M1" s="104"/>
       <c r="N1" s="98" t="s">
@@ -3393,7 +3399,7 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="102" t="s">
-        <v>267</v>
+        <v>236</v>
       </c>
       <c r="Q1" s="102"/>
       <c r="R1" s="102"/>
@@ -3428,7 +3434,7 @@
         <v>62</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>8</v>
@@ -3437,10 +3443,10 @@
         <v>12</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>269</v>
+        <v>238</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>260</v>
+        <v>229</v>
       </c>
       <c r="N2" s="7" t="s">
         <v>13</v>
@@ -3449,16 +3455,16 @@
         <v>7</v>
       </c>
       <c r="P2" s="7" t="s">
-        <v>264</v>
+        <v>233</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>263</v>
+        <v>232</v>
       </c>
       <c r="R2" s="7" t="s">
-        <v>266</v>
+        <v>235</v>
       </c>
       <c r="S2" s="7" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="T2" s="7" t="s">
         <v>6</v>
@@ -3475,86 +3481,86 @@
     </row>
     <row r="3" spans="1:23">
       <c r="B3" s="11" t="s">
-        <v>283</v>
+        <v>244</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="D3" s="2">
-        <v>1.95</v>
+        <v>3.99</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F3" s="15">
-        <v>0.27795596712109361</v>
+        <v>1.2976894231064677</v>
       </c>
       <c r="G3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$10</f>
-        <v>0.1605559671210936</v>
+        <v>1.1802894231064678</v>
       </c>
       <c r="H3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$11</f>
-        <v>0.2434559671210936</v>
+        <v>1.2631894231064678</v>
       </c>
       <c r="I3" s="15">
-        <v>0.27795596712109361</v>
+        <v>0.3</v>
       </c>
       <c r="J3" s="2">
-        <v>1.8570713816288429</v>
+        <v>17.696787580712193</v>
       </c>
       <c r="K3" s="2">
-        <v>3.5690743054385683</v>
+        <v>30.598710239352997</v>
       </c>
       <c r="L3" s="2">
-        <v>2.3351672600917639</v>
+        <v>22.07952964148442</v>
       </c>
       <c r="M3" s="86">
-        <v>3.1632383692769204</v>
+        <v>29.638934581958189</v>
       </c>
       <c r="N3" s="4">
-        <v>6.4603602738772095E-2</v>
+        <v>0.60941871295938521</v>
       </c>
       <c r="O3" s="4">
-        <v>6.5665641025641042E-2</v>
+        <v>0.52016834539178136</v>
       </c>
       <c r="P3" s="15">
-        <v>0.23422582328431374</v>
+        <v>0.5</v>
       </c>
       <c r="Q3" s="15">
-        <v>0.10863424600069688</v>
+        <v>0</v>
       </c>
       <c r="R3" s="92">
-        <v>2.2824569622635926</v>
+        <v>0</v>
       </c>
       <c r="S3" s="86">
-        <v>1.7907626778741865</v>
+        <v>5.243996058095486E-6</v>
       </c>
       <c r="T3" s="13" t="s">
-        <v>285</v>
+        <v>224</v>
       </c>
       <c r="U3" s="11" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="V3" s="14">
         <v>45900</v>
       </c>
       <c r="W3" s="11" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:23">
       <c r="B4" s="11" t="s">
-        <v>276</v>
+        <v>240</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="D4" s="2">
         <v>1.1599999999999999</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F4" s="15">
         <v>0.21955254305698646</v>
@@ -3598,940 +3604,1000 @@
         <v>3.4432102574884196</v>
       </c>
       <c r="S4" s="86">
-        <v>1.9115679363188245</v>
+        <v>2.0258239687205015</v>
       </c>
       <c r="T4" s="13" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>169</v>
+        <v>272</v>
       </c>
       <c r="V4" s="14">
         <v>45900</v>
       </c>
       <c r="W4" s="11" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:23">
       <c r="B5" s="11" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D5" s="2">
-        <v>15.38</v>
+        <v>1.95</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F5" s="15">
-        <v>0.18912881948046301</v>
+        <v>0.20890029037251456</v>
       </c>
       <c r="G5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$10</f>
-        <v>7.1728819480463002E-2</v>
+        <v>9.1500290372514559E-2</v>
       </c>
       <c r="H5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$11</f>
-        <v>0.154628819480463</v>
+        <v>0.17440029037251456</v>
       </c>
       <c r="I5" s="15">
-        <v>0.18912881948046303</v>
+        <v>0.18044745694301345</v>
       </c>
       <c r="J5" s="2">
-        <v>11.866845734983505</v>
+        <v>1.582657938626912</v>
       </c>
       <c r="K5" s="2">
-        <v>23.899333440997744</v>
+        <v>3.0780994911633259</v>
       </c>
       <c r="L5" s="2">
-        <v>14.977385795894701</v>
+        <v>1.9919557240528507</v>
       </c>
       <c r="M5" s="86">
-        <v>20.375014060112886</v>
+        <v>2.7012043158780146</v>
       </c>
       <c r="N5" s="4">
-        <v>6.5387552793081283E-2</v>
+        <v>6.7112926312535084E-2</v>
       </c>
       <c r="O5" s="4">
-        <v>3.5396140526234639E-2</v>
+        <v>5.1282051282051287E-2</v>
       </c>
       <c r="P5" s="15">
-        <v>0.36794481423679237</v>
+        <v>0.23422582328431374</v>
       </c>
       <c r="Q5" s="15">
-        <v>7.4171010848313429E-2</v>
+        <v>0.10863424600069688</v>
       </c>
       <c r="R5" s="92">
-        <v>0.60402076709908736</v>
+        <v>2.2824569622635926</v>
       </c>
       <c r="S5" s="86">
-        <v>4.5287238180520148</v>
+        <v>1.7907626778741865</v>
       </c>
       <c r="T5" s="13" t="s">
-        <v>244</v>
+        <v>275</v>
       </c>
       <c r="U5" s="11" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="V5" s="14">
         <v>45900</v>
       </c>
       <c r="W5" s="11" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:23">
       <c r="B6" s="11" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="D6" s="2">
-        <v>6.11</v>
+        <v>15.38</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F6" s="15">
-        <v>0.15926921829883645</v>
+        <v>0.18912881948046301</v>
       </c>
       <c r="G6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$10</f>
-        <v>4.1869218298836441E-2</v>
+        <v>7.1728819480463002E-2</v>
       </c>
       <c r="H6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$11</f>
-        <v>0.12476921829883644</v>
+        <v>0.154628819480463</v>
       </c>
       <c r="I6" s="15">
-        <v>1.3362670341456884E-2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>4.4306821973721187</v>
+        <v>11.866845734983505</v>
       </c>
       <c r="K6" s="2">
-        <v>7.970870141114629</v>
+        <v>23.899333440997744</v>
       </c>
       <c r="L6" s="2">
-        <v>5.5437094670052947</v>
+        <v>14.977385795894701</v>
       </c>
       <c r="M6" s="86">
-        <v>7.4664546878097049</v>
+        <v>20.375014060112886</v>
       </c>
       <c r="N6" s="4">
-        <v>0.12672849511458295</v>
+        <v>6.5387552793081283E-2</v>
       </c>
       <c r="O6" s="4">
-        <v>7.2330525434368076E-2</v>
+        <v>3.5396140526234639E-2</v>
       </c>
       <c r="P6" s="15">
-        <v>0.61007460831657279</v>
+        <v>0.36794481423679237</v>
       </c>
       <c r="Q6" s="15">
-        <v>0.16360901428944893</v>
+        <v>7.4171010848313429E-2</v>
       </c>
       <c r="R6" s="92">
-        <v>1.1309485990394448</v>
+        <v>0.60402076709908736</v>
       </c>
       <c r="S6" s="86">
-        <v>-3.8116415116695737</v>
+        <v>4.5287238180520148</v>
       </c>
       <c r="T6" s="13" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="U6" s="11" t="s">
-        <v>236</v>
+        <v>157</v>
       </c>
       <c r="V6" s="14">
         <v>45900</v>
       </c>
       <c r="W6" s="11" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:23">
       <c r="B7" s="11" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="D7" s="2">
-        <v>68.8</v>
+        <v>6.11</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>273</v>
+        <v>156</v>
       </c>
       <c r="F7" s="15">
-        <v>0.15867473171661994</v>
+        <v>0.15926921829883645</v>
       </c>
       <c r="G7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$10</f>
-        <v>4.1274731716619939E-2</v>
+        <v>4.1869218298836441E-2</v>
       </c>
       <c r="H7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$11</f>
-        <v>0.12417473171661994</v>
+        <v>0.12476921829883644</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>49.746673136282389</v>
+        <v>4.4306821973721187</v>
       </c>
       <c r="K7" s="2">
-        <v>90.751910880412424</v>
+        <v>7.970870141114629</v>
       </c>
       <c r="L7" s="2">
-        <v>62.307286389127562</v>
+        <v>5.5437094670052947</v>
       </c>
       <c r="M7" s="86">
-        <v>84.017562490801396</v>
+        <v>7.4664546878097049</v>
       </c>
       <c r="N7" s="4">
-        <v>7.6744210192842666E-2</v>
+        <v>0.12672849511458295</v>
       </c>
       <c r="O7" s="4">
-        <v>6.7543604651162797E-2</v>
+        <v>7.2330525434368076E-2</v>
       </c>
       <c r="P7" s="15">
-        <v>0.30279158651211824</v>
+        <v>0.61007460831657279</v>
       </c>
       <c r="Q7" s="15">
-        <v>7.7640983998987034E-4</v>
+        <v>0.16360901428944893</v>
       </c>
       <c r="R7" s="92">
-        <v>3.8209153156820415E-3</v>
+        <v>1.1309485990394448</v>
       </c>
       <c r="S7" s="86">
-        <v>15.284602440692964</v>
+        <v>-3.8116415116695737</v>
       </c>
       <c r="T7" s="13" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="U7" s="11" t="s">
-        <v>160</v>
+        <v>257</v>
       </c>
       <c r="V7" s="14">
         <v>45900</v>
       </c>
       <c r="W7" s="11" t="s">
-        <v>245</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:23">
       <c r="B8" s="11" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="D8" s="2">
-        <v>3.57</v>
+        <v>68.8</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>158</v>
+        <v>266</v>
       </c>
       <c r="F8" s="15">
-        <v>0.14834835832623461</v>
+        <v>0.15867473171661994</v>
       </c>
       <c r="G8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$10</f>
-        <v>3.0948358326234604E-2</v>
+        <v>4.1274731716619939E-2</v>
       </c>
       <c r="H8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$11</f>
-        <v>0.11384835832623461</v>
+        <v>0.12417473171661994</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
       </c>
       <c r="J8" s="2">
-        <v>2.4911701525888064</v>
+        <v>49.746673136282389</v>
       </c>
       <c r="K8" s="2">
-        <v>4.9623808252376094</v>
+        <v>90.751910880412424</v>
       </c>
       <c r="L8" s="2">
-        <v>3.1413777923828756</v>
+        <v>62.307286389127562</v>
       </c>
       <c r="M8" s="86">
-        <v>4.2691663056616189</v>
+        <v>84.017562490801396</v>
       </c>
       <c r="N8" s="4">
-        <v>7.9541327003833207E-2</v>
+        <v>7.6744210192842666E-2</v>
       </c>
       <c r="O8" s="4">
-        <v>3.5854341736694682E-2</v>
+        <v>6.7543604651162797E-2</v>
       </c>
       <c r="P8" s="15">
-        <v>0.40000523965699897</v>
+        <v>0.30279158651211824</v>
       </c>
       <c r="Q8" s="15">
-        <v>0.10646655543311496</v>
+        <v>7.7640983998987034E-4</v>
       </c>
       <c r="R8" s="92">
-        <v>0.9804830051022897</v>
+        <v>3.8209153156820415E-3</v>
       </c>
       <c r="S8" s="86">
-        <v>1.6698226477450393</v>
+        <v>15.284602440692964</v>
       </c>
       <c r="T8" s="13" t="s">
-        <v>159</v>
+        <v>253</v>
       </c>
       <c r="U8" s="11" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="V8" s="14">
-        <v>45808</v>
+        <v>45900</v>
       </c>
       <c r="W8" s="11" t="s">
-        <v>161</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:23">
       <c r="B9" s="11" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="D9" s="2">
-        <v>55.65</v>
+        <v>3.57</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F9" s="15">
-        <v>0.13918053194738822</v>
+        <v>0.14834835832623461</v>
       </c>
       <c r="G9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$10</f>
-        <v>2.1780531947388215E-2</v>
+        <v>3.0948358326234604E-2</v>
       </c>
       <c r="H9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$11</f>
-        <v>0.10468053194738822</v>
+        <v>0.11384835832623461</v>
       </c>
       <c r="I9" s="15">
         <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>38.719486313520228</v>
+        <v>2.4911701525888064</v>
       </c>
       <c r="K9" s="2">
-        <v>64.892912330803952</v>
+        <v>4.9623808252376094</v>
       </c>
       <c r="L9" s="2">
-        <v>48.204328663659695</v>
+        <v>3.1413777923828756</v>
       </c>
       <c r="M9" s="86">
-        <v>64.544120328141631</v>
+        <v>4.2691663056616189</v>
       </c>
       <c r="N9" s="4">
-        <v>9.4703343132953519E-2</v>
+        <v>7.9541327003833207E-2</v>
       </c>
       <c r="O9" s="4">
-        <v>9.085516621743038E-2</v>
+        <v>3.5854341736694682E-2</v>
       </c>
       <c r="P9" s="15">
-        <v>1.2907496012759174</v>
+        <v>0.40000523965699897</v>
       </c>
       <c r="Q9" s="15">
-        <v>0.24768740031897937</v>
+        <v>0.10646655543311496</v>
       </c>
       <c r="R9" s="92">
-        <v>0.73855199466278643</v>
+        <v>0.9804830051022897</v>
       </c>
       <c r="S9" s="86">
-        <v>-2.6504984195888377</v>
+        <v>1.6698226477450393</v>
       </c>
       <c r="T9" s="13" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="U9" s="11" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="V9" s="14">
         <v>45808</v>
       </c>
       <c r="W9" s="11" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:23">
       <c r="B10" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>250</v>
-      </c>
       <c r="D10" s="2">
-        <v>21.72</v>
+        <v>55.65</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>251</v>
+        <v>156</v>
       </c>
       <c r="F10" s="15">
-        <v>0.12990849663525528</v>
+        <v>0.13918053194738822</v>
       </c>
       <c r="G10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$10</f>
-        <v>1.2508496635255273E-2</v>
+        <v>2.1780531947388215E-2</v>
       </c>
       <c r="H10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$11</f>
-        <v>9.5408496635255274E-2</v>
+        <v>0.10468053194738822</v>
       </c>
       <c r="I10" s="15">
         <v>0</v>
       </c>
       <c r="J10" s="2">
-        <v>14.418941896437474</v>
+        <v>38.719486313520228</v>
       </c>
       <c r="K10" s="2">
-        <v>29.309951346473134</v>
+        <v>64.892912330803952</v>
       </c>
       <c r="L10" s="2">
-        <v>18.21218480698677</v>
+        <v>48.204328663659695</v>
       </c>
       <c r="M10" s="86">
-        <v>24.796949133193245</v>
+        <v>64.544120328141631</v>
       </c>
       <c r="N10" s="4">
-        <v>0.2098969404851839</v>
+        <v>9.4703343132953519E-2</v>
       </c>
       <c r="O10" s="4">
-        <v>2.7329650092081034E-2</v>
+        <v>9.085516621743038E-2</v>
       </c>
       <c r="P10" s="15">
-        <v>1.4851905363915479</v>
+        <v>1.2907496012759174</v>
       </c>
       <c r="Q10" s="15">
-        <v>0.95241105291674188</v>
+        <v>0.24768740031897937</v>
       </c>
       <c r="R10" s="92">
-        <v>4.0148803043206254</v>
+        <v>0.73855199466278643</v>
       </c>
       <c r="S10" s="86">
-        <v>-38.360607814419353</v>
+        <v>-2.6504984195888377</v>
       </c>
       <c r="T10" s="16" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="U10" s="11" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="V10" s="14">
-        <v>45900</v>
+        <v>45808</v>
       </c>
       <c r="W10" s="11" t="s">
-        <v>245</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:23">
       <c r="B11" s="11" t="s">
-        <v>156</v>
+        <v>279</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>157</v>
+        <v>280</v>
       </c>
       <c r="D11" s="2">
-        <v>17.82</v>
+        <v>21.72</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>158</v>
+        <v>281</v>
       </c>
       <c r="F11" s="15">
-        <v>0.1209941874823961</v>
+        <v>0.12990849663525528</v>
       </c>
       <c r="G11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$10</f>
-        <v>3.594187482396094E-3</v>
+        <v>1.2508496635255273E-2</v>
       </c>
       <c r="H11" s="15">
         <f>F11 - Portfolio_Mgmt!$C$11</f>
-        <v>8.6494187482396095E-2</v>
+        <v>9.5408496635255274E-2</v>
       </c>
       <c r="I11" s="15">
         <v>0</v>
       </c>
       <c r="J11" s="2">
-        <v>11.804906901225705</v>
+        <v>14.418941896437474</v>
       </c>
       <c r="K11" s="2">
-        <v>20.508980461992877</v>
+        <v>29.309951346473134</v>
       </c>
       <c r="L11" s="2">
-        <v>14.733437767356989</v>
+        <v>18.21218480698677</v>
       </c>
       <c r="M11" s="86">
-        <v>19.785541823839793</v>
+        <v>24.796949133193245</v>
       </c>
       <c r="N11" s="4">
-        <v>9.696891242253812E-2</v>
+        <v>0.2098969404851839</v>
       </c>
       <c r="O11" s="4">
-        <v>7.6318742985409652E-2</v>
+        <v>2.7329650092081034E-2</v>
       </c>
       <c r="P11" s="15">
-        <v>0.31018327415220487</v>
+        <v>1.4851905363915479</v>
       </c>
       <c r="Q11" s="15">
-        <v>0.15818859882129041</v>
+        <v>0.95241105291674188</v>
       </c>
       <c r="R11" s="92">
-        <v>1.4550387206421544</v>
+        <v>4.0148803043206254</v>
       </c>
       <c r="S11" s="86">
-        <v>5.8696003638854428</v>
+        <v>-38.360607814419353</v>
       </c>
       <c r="T11" s="13" t="s">
-        <v>159</v>
+        <v>282</v>
       </c>
       <c r="U11" s="11" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="V11" s="14">
-        <v>45808</v>
+        <v>45900</v>
       </c>
       <c r="W11" s="11" t="s">
-        <v>161</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" spans="1:23">
       <c r="B12" s="11" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="D12" s="2">
-        <v>53.55</v>
+        <v>17.82</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F12" s="15">
-        <v>0.11521291318800975</v>
+        <v>0.1209941874823961</v>
       </c>
       <c r="G12" s="15">
         <f>F12 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.1870868119902576E-3</v>
+        <v>3.594187482396094E-3</v>
       </c>
       <c r="H12" s="15">
         <f>F12 - Portfolio_Mgmt!$C$11</f>
-        <v>8.0712913188009744E-2</v>
+        <v>8.6494187482396095E-2</v>
       </c>
       <c r="I12" s="15">
         <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>34.394984382396515</v>
+        <v>11.804906901225705</v>
       </c>
       <c r="K12" s="2">
-        <v>67.394305644906538</v>
+        <v>20.508980461992877</v>
       </c>
       <c r="L12" s="2">
-        <v>43.315384624827814</v>
+        <v>14.733437767356989</v>
       </c>
       <c r="M12" s="86">
-        <v>58.777638274888893</v>
+        <v>19.785541823839793</v>
       </c>
       <c r="N12" s="4">
-        <v>4.2328511280438831E-2</v>
+        <v>9.696891242253812E-2</v>
       </c>
       <c r="O12" s="4">
-        <v>3.8244420777520896E-2</v>
+        <v>7.6318742985409652E-2</v>
       </c>
       <c r="P12" s="15">
-        <v>0.72207550313588764</v>
+        <v>0.31018327415220487</v>
       </c>
       <c r="Q12" s="15">
-        <v>9.5579625064196368E-3</v>
+        <v>0.15818859882129041</v>
       </c>
       <c r="R12" s="92">
-        <v>7.3592411949940734E-2</v>
+        <v>1.4550387206421544</v>
       </c>
       <c r="S12" s="86">
-        <v>1.3351546830236229</v>
+        <v>5.8696003638854428</v>
       </c>
       <c r="T12" s="13" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="U12" s="11" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="V12" s="14">
-        <v>45900</v>
+        <v>45808</v>
       </c>
       <c r="W12" s="11" t="s">
-        <v>245</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:23">
       <c r="B13" s="11" t="s">
-        <v>162</v>
+        <v>251</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>163</v>
+        <v>252</v>
       </c>
       <c r="D13" s="2">
-        <v>8.15</v>
+        <v>53.55</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F13" s="15">
-        <v>0.10840635294497614</v>
+        <v>0.11521291318800975</v>
       </c>
       <c r="G13" s="15">
         <f>F13 - Portfolio_Mgmt!$C$10</f>
-        <v>-8.9936470550238679E-3</v>
+        <v>-2.1870868119902576E-3</v>
       </c>
       <c r="H13" s="15">
         <f>F13 - Portfolio_Mgmt!$C$11</f>
-        <v>7.3906352944976134E-2</v>
+        <v>8.0712913188009744E-2</v>
       </c>
       <c r="I13" s="15">
         <v>0</v>
       </c>
       <c r="J13" s="2">
-        <v>5.2239462882061574</v>
+        <v>34.394984382396515</v>
       </c>
       <c r="K13" s="2">
-        <v>9.1628099951889297</v>
+        <v>67.394305644906538</v>
       </c>
       <c r="L13" s="2">
-        <v>6.5243113398084081</v>
+        <v>43.315384624827814</v>
       </c>
       <c r="M13" s="2">
-        <v>8.7684502451266084</v>
+        <v>58.777638274888893</v>
       </c>
       <c r="N13" s="4">
-        <v>3.7901640734020248E-2</v>
+        <v>4.2328511280438831E-2</v>
       </c>
       <c r="O13" s="4">
-        <v>7.1165644171779133E-2</v>
+        <v>3.8244420777520896E-2</v>
       </c>
       <c r="P13" s="15">
-        <v>8.3114411724224596E-2</v>
+        <v>0.72207550313588764</v>
       </c>
       <c r="Q13" s="15">
-        <v>1.8509098960546238E-2</v>
+        <v>9.5579625064196368E-3</v>
       </c>
       <c r="R13" s="92">
-        <v>1.1933697905849452</v>
+        <v>7.3592411949940734E-2</v>
       </c>
       <c r="S13" s="86">
-        <v>11.511512740854835</v>
+        <v>1.3351546830236229</v>
       </c>
       <c r="T13" s="13" t="s">
-        <v>164</v>
+        <v>253</v>
       </c>
       <c r="U13" s="11" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="V13" s="14">
         <v>45900</v>
       </c>
       <c r="W13" s="11" t="s">
-        <v>161</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:23">
       <c r="B14" s="11" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>167</v>
+        <v>245</v>
       </c>
       <c r="D14" s="2">
-        <v>2.2999999999999998</v>
+        <v>8.15</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F14" s="15">
-        <v>0.10392879009854439</v>
+        <v>0.10840635294497614</v>
       </c>
       <c r="G14" s="15">
         <f>F14 - Portfolio_Mgmt!$C$10</f>
-        <v>-1.3471209901455616E-2</v>
+        <v>-8.9936470550238679E-3</v>
       </c>
       <c r="H14" s="15">
         <f>F14 - Portfolio_Mgmt!$C$11</f>
-        <v>6.9428790098544385E-2</v>
+        <v>7.3906352944976134E-2</v>
       </c>
       <c r="I14" s="15">
         <v>0</v>
       </c>
       <c r="J14" s="2">
-        <v>1.4428843799519049</v>
+        <v>5.2239462882061574</v>
       </c>
       <c r="K14" s="2">
-        <v>2.7168715485394852</v>
+        <v>9.1628099951889297</v>
       </c>
       <c r="L14" s="2">
-        <v>1.8114973282765074</v>
+        <v>6.5243113398084081</v>
       </c>
       <c r="M14" s="2">
-        <v>2.4494218673596402</v>
+        <v>8.7684502451266084</v>
       </c>
       <c r="N14" s="4">
-        <v>3.5980231621691262E-2</v>
+        <v>3.7901640734020248E-2</v>
       </c>
       <c r="O14" s="4">
-        <v>4.9378384462771097E-2</v>
+        <v>7.1165644171779133E-2</v>
       </c>
       <c r="P14" s="15">
-        <v>0.20351769929714394</v>
+        <v>8.3114411724224596E-2</v>
       </c>
       <c r="Q14" s="15">
-        <v>1.0763175939415467E-2</v>
+        <v>1.8509098960546238E-2</v>
       </c>
       <c r="R14" s="92">
-        <v>0.29882156160837919</v>
+        <v>1.1933697905849452</v>
       </c>
       <c r="S14" s="86">
-        <v>1.8784842625371931</v>
+        <v>11.511512740854835</v>
       </c>
       <c r="T14" s="13" t="s">
-        <v>168</v>
+        <v>247</v>
       </c>
       <c r="U14" s="11" t="s">
-        <v>169</v>
+        <v>246</v>
       </c>
       <c r="V14" s="14">
         <v>45900</v>
       </c>
       <c r="W14" s="11" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:23">
       <c r="B15" s="11" t="s">
-        <v>242</v>
+        <v>276</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>243</v>
+        <v>277</v>
       </c>
       <c r="D15" s="2">
-        <v>14.62</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F15" s="15">
-        <v>0.10088016442395631</v>
+        <v>0.10392879009854439</v>
       </c>
       <c r="G15" s="15">
         <f>F15 - Portfolio_Mgmt!$C$10</f>
-        <v>-1.6519835576043695E-2</v>
+        <v>-1.3471209901455616E-2</v>
       </c>
       <c r="H15" s="15">
         <f>F15 - Portfolio_Mgmt!$C$11</f>
-        <v>6.6380164423956306E-2</v>
+        <v>6.9428790098544385E-2</v>
       </c>
       <c r="I15" s="15">
         <v>0</v>
       </c>
       <c r="J15" s="2">
-        <v>9.1359587259076722</v>
+        <v>1.4428843799519049</v>
       </c>
       <c r="K15" s="2">
-        <v>16.73836897721916</v>
+        <v>2.7168715485394852</v>
       </c>
       <c r="L15" s="2">
-        <v>11.446356334964792</v>
+        <v>1.8114973282765074</v>
       </c>
       <c r="M15" s="2">
-        <v>15.440419547734052</v>
+        <v>2.4494218673596402</v>
       </c>
       <c r="N15" s="4">
-        <v>0.10527247112980752</v>
+        <v>3.5980231621691262E-2</v>
       </c>
       <c r="O15" s="4">
-        <v>5.7142383036935702E-2</v>
+        <v>4.9378384462771097E-2</v>
       </c>
       <c r="P15" s="15">
-        <v>2.2875080906148866</v>
+        <v>0.20351769929714394</v>
       </c>
       <c r="Q15" s="15">
-        <v>1.5035598705501618</v>
+        <v>1.0763175939415467E-2</v>
       </c>
       <c r="R15" s="92">
-        <v>4.1998196571663646</v>
+        <v>0.29882156160837919</v>
       </c>
       <c r="S15" s="86">
-        <v>-12.166449024907546</v>
+        <v>1.8784842625371931</v>
       </c>
       <c r="T15" s="13" t="s">
-        <v>244</v>
+        <v>278</v>
       </c>
       <c r="U15" s="11" t="s">
-        <v>246</v>
+        <v>272</v>
       </c>
       <c r="V15" s="14">
         <v>45900</v>
       </c>
       <c r="W15" s="11" t="s">
-        <v>245</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:23">
       <c r="B16" s="11" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="D16" s="2">
-        <v>28.49</v>
+        <v>14.62</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>251</v>
+        <v>156</v>
       </c>
       <c r="F16" s="15">
-        <v>9.8376640230496193E-2</v>
+        <v>0.10088016442395631</v>
       </c>
       <c r="G16" s="15">
         <f>F16 - Portfolio_Mgmt!$C$10</f>
-        <v>-1.9023359769503811E-2</v>
+        <v>-1.6519835576043695E-2</v>
       </c>
       <c r="H16" s="15">
         <f>F16 - Portfolio_Mgmt!$C$11</f>
-        <v>6.387664023049619E-2</v>
+        <v>6.6380164423956306E-2</v>
       </c>
       <c r="I16" s="15">
         <v>0</v>
       </c>
       <c r="J16" s="2">
-        <v>17.682685147645955</v>
+        <v>9.1359587259076722</v>
       </c>
       <c r="K16" s="2">
-        <v>32.464859269378167</v>
+        <v>16.73836897721916</v>
       </c>
       <c r="L16" s="2">
-        <v>22.157904669779033</v>
+        <v>11.446356334964792</v>
       </c>
       <c r="M16" s="2">
-        <v>29.895007167811503</v>
+        <v>15.440419547734052</v>
       </c>
       <c r="N16" s="4">
-        <v>8.9124865124008343E-2</v>
+        <v>0.10527247112980752</v>
       </c>
       <c r="O16" s="4">
-        <v>5.616005616005617E-2</v>
+        <v>5.7142383036935702E-2</v>
       </c>
       <c r="P16" s="15">
-        <v>0.78990369994931575</v>
+        <v>2.2875080906148866</v>
       </c>
       <c r="Q16" s="15">
-        <v>0.40281804358844397</v>
+        <v>1.5035598705501618</v>
       </c>
       <c r="R16" s="92">
-        <v>3.955391512509995</v>
+        <v>4.1998196571663646</v>
       </c>
       <c r="S16" s="86">
-        <v>-26.938493611476797</v>
+        <v>-12.166449024907546</v>
       </c>
       <c r="T16" s="13" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="U16" s="11" t="s">
-        <v>160</v>
+        <v>269</v>
       </c>
       <c r="V16" s="14">
         <v>45900</v>
       </c>
       <c r="W16" s="11" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17" spans="2:23">
       <c r="B17" s="11" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="D17" s="2">
-        <v>57.21</v>
+        <v>28.49</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="F17" s="15">
-        <v>9.1887382418681218E-2</v>
+        <v>9.8376640230496193E-2</v>
       </c>
       <c r="G17" s="15">
         <f>F17 - Portfolio_Mgmt!$C$10</f>
-        <v>-2.5512617581318786E-2</v>
+        <v>-1.9023359769503811E-2</v>
       </c>
       <c r="H17" s="15">
         <f>F17 - Portfolio_Mgmt!$C$11</f>
-        <v>5.7387382418681215E-2</v>
+        <v>6.387664023049619E-2</v>
       </c>
       <c r="I17" s="15">
         <v>0</v>
       </c>
       <c r="J17" s="2">
+        <v>17.682685147645955</v>
+      </c>
+      <c r="K17" s="2">
+        <v>32.464859269378167</v>
+      </c>
+      <c r="L17" s="2">
+        <v>22.157904669779033</v>
+      </c>
+      <c r="M17" s="2">
+        <v>29.895007167811503</v>
+      </c>
+      <c r="N17" s="4">
+        <v>8.9124865124008343E-2</v>
+      </c>
+      <c r="O17" s="4">
+        <v>5.616005616005617E-2</v>
+      </c>
+      <c r="P17" s="15">
+        <v>0.78990369994931575</v>
+      </c>
+      <c r="Q17" s="15">
+        <v>0.40281804358844397</v>
+      </c>
+      <c r="R17" s="92">
+        <v>3.955391512509995</v>
+      </c>
+      <c r="S17" s="86">
+        <v>-26.938493611476797</v>
+      </c>
+      <c r="T17" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="U17" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="V17" s="14">
+        <v>45900</v>
+      </c>
+      <c r="W17" s="11" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="18" spans="2:23">
+      <c r="B18" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="D18" s="2">
+        <v>57.21</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="F18" s="15">
+        <v>9.1887382418681218E-2</v>
+      </c>
+      <c r="G18" s="15">
+        <f>F18 - Portfolio_Mgmt!$C$10</f>
+        <v>-2.5512617581318786E-2</v>
+      </c>
+      <c r="H18" s="15">
+        <f>F18 - Portfolio_Mgmt!$C$11</f>
+        <v>5.7387382418681215E-2</v>
+      </c>
+      <c r="I18" s="15">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2">
         <v>34.669224296258527</v>
       </c>
-      <c r="K17" s="2">
+      <c r="K18" s="2">
         <v>66.592285778879997</v>
       </c>
-      <c r="L17" s="2">
+      <c r="L18" s="2">
         <v>43.592757973888887</v>
       </c>
-      <c r="M17" s="2">
+      <c r="M18" s="2">
         <v>59.048136223898794</v>
       </c>
-      <c r="N17" s="4">
+      <c r="N18" s="4">
         <v>8.0319983221959892E-2</v>
       </c>
-      <c r="O17" s="4">
+      <c r="O18" s="4">
         <v>4.195070791819612E-2</v>
       </c>
-      <c r="P17" s="15">
+      <c r="P18" s="15">
         <v>3.4701988818540461</v>
       </c>
-      <c r="Q17" s="15">
+      <c r="Q18" s="15">
         <v>5.0341856510546588E-2</v>
       </c>
-      <c r="R17" s="92">
+      <c r="R18" s="92">
         <v>3.9546057100127742E-2</v>
       </c>
-      <c r="S17" s="86">
+      <c r="S18" s="86">
         <v>-13.312996389940134</v>
       </c>
-      <c r="T17" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="U17" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="V17" s="14">
+      <c r="T18" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="U18" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="V18" s="14">
         <v>45716</v>
       </c>
-      <c r="W17" s="11" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="18" spans="2:23">
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="E18" s="12"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
-      <c r="T18" s="13"/>
-      <c r="U18" s="11"/>
-      <c r="V18" s="14"/>
+      <c r="W18" s="11" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="19" spans="2:23">
       <c r="B19" s="11"/>
@@ -6862,7 +6928,7 @@
     <row r="1" spans="1:8" ht="13.15">
       <c r="A1" s="63"/>
       <c r="B1" s="64" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="29.65" customHeight="1">
@@ -6870,22 +6936,22 @@
         <v>3</v>
       </c>
       <c r="C2" s="66" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="D2" s="66" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="E2" s="66" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="G2" s="66" t="s">
-        <v>262</v>
+        <v>231</v>
       </c>
       <c r="H2" s="66" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6893,13 +6959,13 @@
         <v>30</v>
       </c>
       <c r="C3" s="75" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D3" s="74" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="E3" s="76" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="F3" s="71">
         <v>351395.62</v>
@@ -6915,7 +6981,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="B4" s="78" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C4" s="75">
         <f>VLOOKUP(B4,Opportunities!B$3:E$30,3,FALSE)</f>
@@ -6943,7 +7009,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="B5" s="78" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C5" s="75">
         <f>VLOOKUP(B5,Opportunities!B$3:E$30,3,FALSE)</f>
@@ -6972,7 +7038,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="B6" s="78" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="C6" s="75">
         <f>VLOOKUP(B6,Opportunities!B$3:E$30,3,FALSE)</f>
@@ -6995,12 +7061,12 @@
       </c>
       <c r="H6" s="73">
         <f>VLOOKUP(B6,Opportunities!B$3:I$30,8,FALSE)</f>
-        <v>1.3362670341456884E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="B7" s="78" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="C7" s="75">
         <f>VLOOKUP(B7,Opportunities!B$3:E$30,3,FALSE)</f>
@@ -7023,7 +7089,7 @@
       </c>
       <c r="H7" s="73">
         <f>VLOOKUP(B7,Opportunities!B$3:I$30,8,FALSE)</f>
-        <v>0.18912881948046303</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -7037,7 +7103,7 @@
       <c r="C9" s="80"/>
       <c r="D9" s="79"/>
       <c r="E9" s="81" t="s">
-        <v>261</v>
+        <v>230</v>
       </c>
       <c r="F9" s="81">
         <f>SUM(F3:F7)</f>
@@ -7049,7 +7115,7 @@
       </c>
       <c r="H9" s="89">
         <f>SUM(H4:H7)</f>
-        <v>0.20249148982191992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -7062,12 +7128,12 @@
     <row r="11" spans="1:8" ht="13.15">
       <c r="A11" s="63"/>
       <c r="B11" s="64" t="s">
-        <v>258</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="B12" s="78" t="s">
-        <v>276</v>
+        <v>240</v>
       </c>
       <c r="C12" s="75">
         <f>VLOOKUP(B12,Opportunities!B$3:E$30,3,FALSE)</f>
@@ -7096,7 +7162,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="B13" s="78" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C13" s="75">
         <f>VLOOKUP(B13,Opportunities!B$3:E$30,3,FALSE)</f>
@@ -7129,16 +7195,16 @@
     </row>
     <row r="15" spans="1:8" ht="13.15">
       <c r="B15" s="83" t="s">
-        <v>259</v>
+        <v>228</v>
       </c>
       <c r="C15" s="84" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D15" s="85" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E15" s="84" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="F15" s="81">
         <f>F3+F12</f>
@@ -7243,15 +7309,15 @@
       <c r="B5" s="106" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="95"/>
-      <c r="D5" s="95"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="97"/>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="106" t="s">
         <v>105</v>
       </c>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="97"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">

--- a/financial_models/Stock_Monitor.xlsx
+++ b/financial_models/Stock_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E1F7D68-215A-4D99-B41D-F08B07232298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274611EE-18B8-4C2E-97B4-8DAE09FE285F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3276,7 +3276,7 @@
         <v>164</v>
       </c>
       <c r="C112" s="44">
-        <v>0.48555567224710755</v>
+        <v>0.15108906655309656</v>
       </c>
       <c r="D112" s="61" t="str">
         <f>IF(C112&lt;benchmark,"Warning: Return is lower than the Benchmark.","")</f>
@@ -3481,66 +3481,66 @@
     </row>
     <row r="3" spans="1:23">
       <c r="B3" s="11" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="D3" s="2">
-        <v>3.99</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>156</v>
       </c>
       <c r="F3" s="15">
-        <v>1.2976894231064677</v>
+        <v>0.21955254305698646</v>
       </c>
       <c r="G3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$10</f>
-        <v>1.1802894231064678</v>
+        <v>0.10215254305698646</v>
       </c>
       <c r="H3" s="15">
         <f>F3 - Portfolio_Mgmt!$C$11</f>
-        <v>1.2631894231064678</v>
+        <v>0.18505254305698646</v>
       </c>
       <c r="I3" s="15">
-        <v>0.3</v>
+        <v>0.21955254305698646</v>
       </c>
       <c r="J3" s="2">
-        <v>17.696787580712193</v>
+        <v>0.9576999852710768</v>
       </c>
       <c r="K3" s="2">
-        <v>30.598710239352997</v>
+        <v>2.1040668676405563</v>
       </c>
       <c r="L3" s="2">
-        <v>22.07952964148442</v>
+        <v>1.2176312891438406</v>
       </c>
       <c r="M3" s="86">
-        <v>29.638934581958189</v>
+        <v>1.6702761167953912</v>
       </c>
       <c r="N3" s="4">
-        <v>0.60941871295938521</v>
+        <v>8.265220900462859E-3</v>
       </c>
       <c r="O3" s="4">
-        <v>0.52016834539178136</v>
+        <v>0</v>
       </c>
       <c r="P3" s="15">
-        <v>0.5</v>
+        <v>9.7057481271370302E-2</v>
       </c>
       <c r="Q3" s="15">
-        <v>0</v>
+        <v>1.4790654865358754E-2</v>
       </c>
       <c r="R3" s="92">
-        <v>0</v>
+        <v>3.4432102574884196</v>
       </c>
       <c r="S3" s="86">
-        <v>5.243996058095486E-6</v>
+        <v>2.0258239687205015</v>
       </c>
       <c r="T3" s="13" t="s">
-        <v>224</v>
+        <v>271</v>
       </c>
       <c r="U3" s="11" t="s">
-        <v>157</v>
+        <v>272</v>
       </c>
       <c r="V3" s="14">
         <v>45900</v>
@@ -3551,66 +3551,66 @@
     </row>
     <row r="4" spans="1:23">
       <c r="B4" s="11" t="s">
-        <v>240</v>
+        <v>273</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D4" s="2">
-        <v>1.1599999999999999</v>
+        <v>1.95</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>156</v>
       </c>
       <c r="F4" s="15">
-        <v>0.21955254305698646</v>
+        <v>0.20890029037251456</v>
       </c>
       <c r="G4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$10</f>
-        <v>0.10215254305698646</v>
+        <v>9.1500290372514559E-2</v>
       </c>
       <c r="H4" s="15">
         <f>F4 - Portfolio_Mgmt!$C$11</f>
-        <v>0.18505254305698646</v>
+        <v>0.17440029037251456</v>
       </c>
       <c r="I4" s="15">
-        <v>0.21955254305698646</v>
+        <v>0.20890029037251456</v>
       </c>
       <c r="J4" s="2">
-        <v>0.9576999852710768</v>
+        <v>1.582657938626912</v>
       </c>
       <c r="K4" s="2">
-        <v>2.1040668676405563</v>
+        <v>3.0780994911633259</v>
       </c>
       <c r="L4" s="2">
-        <v>1.2176312891438406</v>
+        <v>1.9919557240528507</v>
       </c>
       <c r="M4" s="86">
-        <v>1.6702761167953912</v>
+        <v>2.7012043158780146</v>
       </c>
       <c r="N4" s="4">
-        <v>8.265220900462859E-3</v>
+        <v>6.7112926312535084E-2</v>
       </c>
       <c r="O4" s="4">
-        <v>0</v>
+        <v>5.1282051282051287E-2</v>
       </c>
       <c r="P4" s="15">
-        <v>9.7057481271370302E-2</v>
+        <v>0.23422582328431374</v>
       </c>
       <c r="Q4" s="15">
-        <v>1.4790654865358754E-2</v>
+        <v>0.10863424600069688</v>
       </c>
       <c r="R4" s="92">
-        <v>3.4432102574884196</v>
+        <v>2.2824569622635926</v>
       </c>
       <c r="S4" s="86">
-        <v>2.0258239687205015</v>
+        <v>1.7907626778741865</v>
       </c>
       <c r="T4" s="13" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>272</v>
+        <v>157</v>
       </c>
       <c r="V4" s="14">
         <v>45900</v>
@@ -3621,63 +3621,63 @@
     </row>
     <row r="5" spans="1:23">
       <c r="B5" s="11" t="s">
-        <v>273</v>
+        <v>226</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="D5" s="2">
-        <v>1.95</v>
+        <v>15.38</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>156</v>
       </c>
       <c r="F5" s="15">
-        <v>0.20890029037251456</v>
+        <v>0.18912881948046301</v>
       </c>
       <c r="G5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$10</f>
-        <v>9.1500290372514559E-2</v>
+        <v>7.1728819480463002E-2</v>
       </c>
       <c r="H5" s="15">
         <f>F5 - Portfolio_Mgmt!$C$11</f>
-        <v>0.17440029037251456</v>
+        <v>0.154628819480463</v>
       </c>
       <c r="I5" s="15">
-        <v>0.18044745694301345</v>
+        <v>0.18912881948046303</v>
       </c>
       <c r="J5" s="2">
-        <v>1.582657938626912</v>
+        <v>11.866845734983505</v>
       </c>
       <c r="K5" s="2">
-        <v>3.0780994911633259</v>
+        <v>23.899333440997744</v>
       </c>
       <c r="L5" s="2">
-        <v>1.9919557240528507</v>
+        <v>14.977385795894701</v>
       </c>
       <c r="M5" s="86">
-        <v>2.7012043158780146</v>
+        <v>20.375014060112886</v>
       </c>
       <c r="N5" s="4">
-        <v>6.7112926312535084E-2</v>
+        <v>6.5387552793081283E-2</v>
       </c>
       <c r="O5" s="4">
-        <v>5.1282051282051287E-2</v>
+        <v>3.5396140526234639E-2</v>
       </c>
       <c r="P5" s="15">
-        <v>0.23422582328431374</v>
+        <v>0.36794481423679237</v>
       </c>
       <c r="Q5" s="15">
-        <v>0.10863424600069688</v>
+        <v>7.4171010848313429E-2</v>
       </c>
       <c r="R5" s="92">
-        <v>2.2824569622635926</v>
+        <v>0.60402076709908736</v>
       </c>
       <c r="S5" s="86">
-        <v>1.7907626778741865</v>
+        <v>4.5287238180520148</v>
       </c>
       <c r="T5" s="13" t="s">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="U5" s="11" t="s">
         <v>157</v>
@@ -3691,66 +3691,66 @@
     </row>
     <row r="6" spans="1:23">
       <c r="B6" s="11" t="s">
-        <v>226</v>
+        <v>255</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="D6" s="2">
-        <v>15.38</v>
+        <v>6.11</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>156</v>
       </c>
       <c r="F6" s="15">
-        <v>0.18912881948046301</v>
+        <v>0.15926921829883645</v>
       </c>
       <c r="G6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$10</f>
-        <v>7.1728819480463002E-2</v>
+        <v>4.1869218298836441E-2</v>
       </c>
       <c r="H6" s="15">
         <f>F6 - Portfolio_Mgmt!$C$11</f>
-        <v>0.154628819480463</v>
+        <v>0.12476921829883644</v>
       </c>
       <c r="I6" s="15">
-        <v>0</v>
+        <v>8.2418347090035926E-2</v>
       </c>
       <c r="J6" s="2">
-        <v>11.866845734983505</v>
+        <v>4.4306821973721187</v>
       </c>
       <c r="K6" s="2">
-        <v>23.899333440997744</v>
+        <v>7.970870141114629</v>
       </c>
       <c r="L6" s="2">
-        <v>14.977385795894701</v>
+        <v>5.5437094670052947</v>
       </c>
       <c r="M6" s="86">
-        <v>20.375014060112886</v>
+        <v>7.4664546878097049</v>
       </c>
       <c r="N6" s="4">
-        <v>6.5387552793081283E-2</v>
+        <v>0.12672849511458295</v>
       </c>
       <c r="O6" s="4">
-        <v>3.5396140526234639E-2</v>
+        <v>7.2330525434368076E-2</v>
       </c>
       <c r="P6" s="15">
-        <v>0.36794481423679237</v>
+        <v>0.61007460831657279</v>
       </c>
       <c r="Q6" s="15">
-        <v>7.4171010848313429E-2</v>
+        <v>0.16360901428944893</v>
       </c>
       <c r="R6" s="92">
-        <v>0.60402076709908736</v>
+        <v>1.1309485990394448</v>
       </c>
       <c r="S6" s="86">
-        <v>4.5287238180520148</v>
+        <v>-3.8116415116695737</v>
       </c>
       <c r="T6" s="13" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="U6" s="11" t="s">
-        <v>157</v>
+        <v>257</v>
       </c>
       <c r="V6" s="14">
         <v>45900</v>
@@ -3761,203 +3761,203 @@
     </row>
     <row r="7" spans="1:23">
       <c r="B7" s="11" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D7" s="2">
-        <v>6.11</v>
+        <v>68.8</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>156</v>
+        <v>266</v>
       </c>
       <c r="F7" s="15">
-        <v>0.15926921829883645</v>
+        <v>0.15867473171661994</v>
       </c>
       <c r="G7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$10</f>
-        <v>4.1869218298836441E-2</v>
+        <v>4.1274731716619939E-2</v>
       </c>
       <c r="H7" s="15">
         <f>F7 - Portfolio_Mgmt!$C$11</f>
-        <v>0.12476921829883644</v>
+        <v>0.12417473171661994</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>4.4306821973721187</v>
+        <v>49.746673136282389</v>
       </c>
       <c r="K7" s="2">
-        <v>7.970870141114629</v>
+        <v>90.751910880412424</v>
       </c>
       <c r="L7" s="2">
-        <v>5.5437094670052947</v>
+        <v>62.307286389127562</v>
       </c>
       <c r="M7" s="86">
-        <v>7.4664546878097049</v>
+        <v>84.017562490801396</v>
       </c>
       <c r="N7" s="4">
-        <v>0.12672849511458295</v>
+        <v>7.6744210192842666E-2</v>
       </c>
       <c r="O7" s="4">
-        <v>7.2330525434368076E-2</v>
+        <v>6.7543604651162797E-2</v>
       </c>
       <c r="P7" s="15">
-        <v>0.61007460831657279</v>
+        <v>0.30279158651211824</v>
       </c>
       <c r="Q7" s="15">
-        <v>0.16360901428944893</v>
+        <v>7.7640983998987034E-4</v>
       </c>
       <c r="R7" s="92">
-        <v>1.1309485990394448</v>
+        <v>3.8209153156820415E-3</v>
       </c>
       <c r="S7" s="86">
-        <v>-3.8116415116695737</v>
+        <v>15.284602440692964</v>
       </c>
       <c r="T7" s="13" t="s">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="U7" s="11" t="s">
-        <v>257</v>
+        <v>157</v>
       </c>
       <c r="V7" s="14">
         <v>45900</v>
       </c>
       <c r="W7" s="11" t="s">
-        <v>158</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:23">
       <c r="B8" s="11" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D8" s="2">
-        <v>68.8</v>
+        <v>3.57</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>266</v>
+        <v>156</v>
       </c>
       <c r="F8" s="15">
-        <v>0.15867473171661994</v>
+        <v>0.14834835832623461</v>
       </c>
       <c r="G8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$10</f>
-        <v>4.1274731716619939E-2</v>
+        <v>3.0948358326234604E-2</v>
       </c>
       <c r="H8" s="15">
         <f>F8 - Portfolio_Mgmt!$C$11</f>
-        <v>0.12417473171661994</v>
+        <v>0.11384835832623461</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
       </c>
       <c r="J8" s="2">
-        <v>49.746673136282389</v>
+        <v>2.4911701525888064</v>
       </c>
       <c r="K8" s="2">
-        <v>90.751910880412424</v>
+        <v>4.9623808252376094</v>
       </c>
       <c r="L8" s="2">
-        <v>62.307286389127562</v>
+        <v>3.1413777923828756</v>
       </c>
       <c r="M8" s="86">
-        <v>84.017562490801396</v>
+        <v>4.2691663056616189</v>
       </c>
       <c r="N8" s="4">
-        <v>7.6744210192842666E-2</v>
+        <v>7.9541327003833207E-2</v>
       </c>
       <c r="O8" s="4">
-        <v>6.7543604651162797E-2</v>
+        <v>3.5854341736694682E-2</v>
       </c>
       <c r="P8" s="15">
-        <v>0.30279158651211824</v>
+        <v>0.40000523965699897</v>
       </c>
       <c r="Q8" s="15">
-        <v>7.7640983998987034E-4</v>
+        <v>0.10646655543311496</v>
       </c>
       <c r="R8" s="92">
-        <v>3.8209153156820415E-3</v>
+        <v>0.9804830051022897</v>
       </c>
       <c r="S8" s="86">
-        <v>15.284602440692964</v>
+        <v>1.6698226477450393</v>
       </c>
       <c r="T8" s="13" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="U8" s="11" t="s">
         <v>157</v>
       </c>
       <c r="V8" s="14">
-        <v>45900</v>
+        <v>45808</v>
       </c>
       <c r="W8" s="11" t="s">
-        <v>254</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:23">
       <c r="B9" s="11" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="D9" s="2">
-        <v>3.57</v>
+        <v>55.65</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>156</v>
       </c>
       <c r="F9" s="15">
-        <v>0.14834835832623461</v>
+        <v>0.13918053194738822</v>
       </c>
       <c r="G9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$10</f>
-        <v>3.0948358326234604E-2</v>
+        <v>2.1780531947388215E-2</v>
       </c>
       <c r="H9" s="15">
         <f>F9 - Portfolio_Mgmt!$C$11</f>
-        <v>0.11384835832623461</v>
+        <v>0.10468053194738822</v>
       </c>
       <c r="I9" s="15">
         <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>2.4911701525888064</v>
+        <v>38.719486313520228</v>
       </c>
       <c r="K9" s="2">
-        <v>4.9623808252376094</v>
+        <v>64.892912330803952</v>
       </c>
       <c r="L9" s="2">
-        <v>3.1413777923828756</v>
+        <v>48.204328663659695</v>
       </c>
       <c r="M9" s="86">
-        <v>4.2691663056616189</v>
+        <v>64.544120328141631</v>
       </c>
       <c r="N9" s="4">
-        <v>7.9541327003833207E-2</v>
+        <v>9.4703343132953519E-2</v>
       </c>
       <c r="O9" s="4">
-        <v>3.5854341736694682E-2</v>
+        <v>9.085516621743038E-2</v>
       </c>
       <c r="P9" s="15">
-        <v>0.40000523965699897</v>
+        <v>1.2907496012759174</v>
       </c>
       <c r="Q9" s="15">
-        <v>0.10646655543311496</v>
+        <v>0.24768740031897937</v>
       </c>
       <c r="R9" s="92">
-        <v>0.9804830051022897</v>
+        <v>0.73855199466278643</v>
       </c>
       <c r="S9" s="86">
-        <v>1.6698226477450393</v>
+        <v>-2.6504984195888377</v>
       </c>
       <c r="T9" s="13" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="U9" s="11" t="s">
         <v>157</v>
@@ -3971,346 +3971,346 @@
     </row>
     <row r="10" spans="1:23">
       <c r="B10" s="11" t="s">
-        <v>248</v>
+        <v>279</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>249</v>
+        <v>280</v>
       </c>
       <c r="D10" s="2">
-        <v>55.65</v>
+        <v>21.72</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>156</v>
+        <v>281</v>
       </c>
       <c r="F10" s="15">
-        <v>0.13918053194738822</v>
+        <v>0.12990849663525528</v>
       </c>
       <c r="G10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$10</f>
-        <v>2.1780531947388215E-2</v>
+        <v>1.2508496635255273E-2</v>
       </c>
       <c r="H10" s="15">
         <f>F10 - Portfolio_Mgmt!$C$11</f>
-        <v>0.10468053194738822</v>
+        <v>9.5408496635255274E-2</v>
       </c>
       <c r="I10" s="15">
         <v>0</v>
       </c>
       <c r="J10" s="2">
-        <v>38.719486313520228</v>
+        <v>14.418941896437474</v>
       </c>
       <c r="K10" s="2">
-        <v>64.892912330803952</v>
+        <v>29.309951346473134</v>
       </c>
       <c r="L10" s="2">
-        <v>48.204328663659695</v>
+        <v>18.21218480698677</v>
       </c>
       <c r="M10" s="86">
-        <v>64.544120328141631</v>
+        <v>24.796949133193245</v>
       </c>
       <c r="N10" s="4">
-        <v>9.4703343132953519E-2</v>
+        <v>0.2098969404851839</v>
       </c>
       <c r="O10" s="4">
-        <v>9.085516621743038E-2</v>
+        <v>2.7329650092081034E-2</v>
       </c>
       <c r="P10" s="15">
-        <v>1.2907496012759174</v>
+        <v>1.4851905363915479</v>
       </c>
       <c r="Q10" s="15">
-        <v>0.24768740031897937</v>
+        <v>0.95241105291674188</v>
       </c>
       <c r="R10" s="92">
-        <v>0.73855199466278643</v>
+        <v>4.0148803043206254</v>
       </c>
       <c r="S10" s="86">
-        <v>-2.6504984195888377</v>
+        <v>-38.360607814419353</v>
       </c>
       <c r="T10" s="16" t="s">
-        <v>250</v>
+        <v>282</v>
       </c>
       <c r="U10" s="11" t="s">
         <v>157</v>
       </c>
       <c r="V10" s="14">
-        <v>45808</v>
+        <v>45900</v>
       </c>
       <c r="W10" s="11" t="s">
-        <v>158</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:23">
       <c r="B11" s="11" t="s"